--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_7F7C4E8459B100A1C535B6B72639F598B53CF5BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D482E9D1-9428-4966-8D89-410CFAFB7B01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6692614-9D76-463C-88F9-E97DB19F39C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
@@ -2369,7 +2369,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="12">
     <dxf>
       <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     </dxf>
@@ -2384,7 +2384,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -2394,7 +2394,11 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border>
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -2446,16 +2450,12 @@
 </styleSheet>
 </file>
 
-<file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
-<namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AV57" totalsRowShown="0">
   <autoFilter ref="A2:AV57" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="48">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA" dataDxfId="10"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NOMBRE PROYECTO"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="ALCANCE DEL PROYECTO"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SECTOR"/>
@@ -2473,11 +2473,11 @@
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="ULTIMA FECHA PAGO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="FECHA DE MIGRACIÓN A GESPROY"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="AVANCE FISICO" dataDxfId="7"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="AVANCE FINANCIERO" dataDxfId="6"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPI" dataDxfId="5"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="AVANCE FISICO" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="AVANCE FINANCIERO" dataDxfId="7"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPI" dataDxfId="6"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI" dataDxfId="5"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCION"/>
@@ -2868,30 +2868,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AV57"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="104.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="60.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="104.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="29.5546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="39" width="25.7109375" customWidth="1"/>
-    <col min="40" max="40" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="41" max="45" width="25.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="47" max="48" width="25.7109375" customWidth="1"/>
+    <col min="16" max="39" width="25.6640625" customWidth="1"/>
+    <col min="40" max="40" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="41" max="45" width="25.6640625" customWidth="1"/>
+    <col min="46" max="46" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="47" max="48" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:48" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -2947,7 +2947,7 @@
       <c r="AU1" s="10"/>
       <c r="AV1" s="10"/>
     </row>
-    <row r="2" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:48" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:48" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>663</v>
       </c>
@@ -3156,8 +3156,12 @@
       <c r="V3" s="9">
         <v>73.75</v>
       </c>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
+      <c r="W3" s="3">
+        <v>0.19700226802995546</v>
+      </c>
+      <c r="X3" s="3">
+        <v>0.23294706416270416</v>
+      </c>
       <c r="Y3" s="5">
         <v>41201</v>
       </c>
@@ -3218,7 +3222,7 @@
       </c>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>664</v>
       </c>
@@ -3281,8 +3285,12 @@
       <c r="V4" s="9">
         <v>100</v>
       </c>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
+      <c r="W4" s="3">
+        <v>0.19586548306885565</v>
+      </c>
+      <c r="X4" s="3">
+        <v>0.57181515733763577</v>
+      </c>
       <c r="Y4" s="5">
         <v>41263</v>
       </c>
@@ -3308,7 +3316,7 @@
       <c r="AK4" s="3"/>
       <c r="AL4" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>41.698947247312127</v>
       </c>
       <c r="AM4" s="3">
         <f t="shared" si="1"/>
@@ -3341,7 +3349,7 @@
       </c>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
         <v>665</v>
       </c>
@@ -3404,8 +3412,12 @@
       <c r="V5" s="9">
         <v>94.36</v>
       </c>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
+      <c r="W5" s="3">
+        <v>0.73828923793763479</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0.77504399577721039</v>
+      </c>
       <c r="Y5" s="5">
         <v>41565</v>
       </c>
@@ -3464,7 +3476,7 @@
       </c>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
         <v>666</v>
       </c>
@@ -3527,8 +3539,12 @@
       <c r="V6" s="9">
         <v>97.17</v>
       </c>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
+      <c r="W6" s="3">
+        <v>0.84594546217216782</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.11808774806850642</v>
+      </c>
       <c r="Y6" s="5">
         <v>41474</v>
       </c>
@@ -3560,7 +3576,7 @@
       </c>
       <c r="AM6" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN6" s="3">
         <f t="shared" si="2"/>
@@ -3587,7 +3603,7 @@
       </c>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>667</v>
       </c>
@@ -3650,8 +3666,12 @@
       <c r="V7" s="9">
         <v>97.87</v>
       </c>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
+      <c r="W7" s="3">
+        <v>0.18782732016716619</v>
+      </c>
+      <c r="X7" s="3">
+        <v>0.35770014469663869</v>
+      </c>
       <c r="Y7" s="5">
         <v>42657</v>
       </c>
@@ -3710,7 +3730,7 @@
       </c>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>668</v>
       </c>
@@ -3773,8 +3793,12 @@
       <c r="V8" s="9">
         <v>97.77</v>
       </c>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
+      <c r="W8" s="3">
+        <v>0.51686626822411597</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0.68892425309351379</v>
+      </c>
       <c r="Y8" s="5">
         <v>42801</v>
       </c>
@@ -3833,7 +3857,7 @@
       </c>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>669</v>
       </c>
@@ -3896,8 +3920,12 @@
       <c r="V9" s="9">
         <v>99.47</v>
       </c>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
+      <c r="W9" s="3">
+        <v>0.34249042603231938</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.50594470890294507</v>
+      </c>
       <c r="Y9" s="5">
         <v>42922</v>
       </c>
@@ -3923,7 +3951,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27.379284544118494</v>
       </c>
       <c r="AM9" s="3">
         <f t="shared" si="1"/>
@@ -3954,7 +3982,7 @@
       </c>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>670</v>
       </c>
@@ -4017,8 +4045,12 @@
       <c r="V10" s="9">
         <v>98.98</v>
       </c>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
+      <c r="W10" s="3">
+        <v>0.54660273231279333</v>
+      </c>
+      <c r="X10" s="3">
+        <v>0.98748704102583695</v>
+      </c>
       <c r="Y10" s="5">
         <v>43781</v>
       </c>
@@ -4075,7 +4107,7 @@
       </c>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>671</v>
       </c>
@@ -4138,8 +4170,12 @@
       <c r="V11" s="9">
         <v>97.61</v>
       </c>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
+      <c r="W11" s="3">
+        <v>0.40039648227630409</v>
+      </c>
+      <c r="X11" s="3">
+        <v>0.30823538441344922</v>
+      </c>
       <c r="Y11" s="5">
         <v>43322</v>
       </c>
@@ -4196,7 +4232,7 @@
       </c>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" spans="1:48" ht="195.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:48" ht="195.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>672</v>
       </c>
@@ -4259,8 +4295,12 @@
       <c r="V12" s="9">
         <v>97.41</v>
       </c>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
+      <c r="W12" s="3">
+        <v>0.83011227138822197</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0.26060983955167261</v>
+      </c>
       <c r="Y12" s="5">
         <v>43193</v>
       </c>
@@ -4317,7 +4357,7 @@
       </c>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>673</v>
       </c>
@@ -4382,8 +4422,12 @@
       <c r="V13" s="9">
         <v>90.58</v>
       </c>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
+      <c r="W13" s="3">
+        <v>0.86769791198875679</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.56971130573733264</v>
+      </c>
       <c r="Y13" s="5">
         <v>45064</v>
       </c>
@@ -4409,11 +4453,11 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>41.241588203767968</v>
       </c>
       <c r="AM13" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN13" s="3">
         <f t="shared" si="2"/>
@@ -4440,7 +4484,7 @@
       </c>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>674</v>
       </c>
@@ -4503,8 +4547,12 @@
       <c r="V14" s="9">
         <v>99.48</v>
       </c>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
+      <c r="W14" s="3">
+        <v>0.69905702736051822</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0.73042853445362699</v>
+      </c>
       <c r="Y14" s="5">
         <v>44195</v>
       </c>
@@ -4561,7 +4609,7 @@
       </c>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>675</v>
       </c>
@@ -4624,8 +4672,12 @@
       <c r="V15" s="9">
         <v>94.98</v>
       </c>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
+      <c r="W15" s="3">
+        <v>4.7751823873365185E-2</v>
+      </c>
+      <c r="X15" s="3">
+        <v>8.01898122609217E-2</v>
+      </c>
       <c r="Y15" s="5">
         <v>44183</v>
       </c>
@@ -4682,7 +4734,7 @@
       </c>
       <c r="AV15" s="3"/>
     </row>
-    <row r="16" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>676</v>
       </c>
@@ -4745,8 +4797,12 @@
       <c r="V16" s="9">
         <v>99.96</v>
       </c>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
+      <c r="W16" s="3">
+        <v>0.86665366364476493</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0.99746376259850156</v>
+      </c>
       <c r="Y16" s="5">
         <v>44728</v>
       </c>
@@ -4803,7 +4859,7 @@
       </c>
       <c r="AV16" s="3"/>
     </row>
-    <row r="17" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>677</v>
       </c>
@@ -4868,8 +4924,12 @@
       <c r="V17" s="9">
         <v>89.98</v>
       </c>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
+      <c r="W17" s="3">
+        <v>2.4250134270559442E-2</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.93555428656753647</v>
+      </c>
       <c r="Y17" s="5">
         <v>45064</v>
       </c>
@@ -4895,7 +4955,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM17" s="3">
         <f t="shared" si="1"/>
@@ -4926,7 +4986,7 @@
       </c>
       <c r="AV17" s="3"/>
     </row>
-    <row r="18" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
         <v>678</v>
       </c>
@@ -4989,8 +5049,12 @@
       <c r="V18" s="9">
         <v>87.49</v>
       </c>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
+      <c r="W18" s="3">
+        <v>0.57520609531084266</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.58205822169285859</v>
+      </c>
       <c r="Y18" s="5">
         <v>44552</v>
       </c>
@@ -5016,11 +5080,11 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.925700368012741</v>
       </c>
       <c r="AM18" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>42.436107676270147</v>
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="2"/>
@@ -5047,7 +5111,7 @@
       </c>
       <c r="AV18" s="3"/>
     </row>
-    <row r="19" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
         <v>679</v>
       </c>
@@ -5110,8 +5174,12 @@
       <c r="V19" s="9">
         <v>92.21</v>
       </c>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
+      <c r="W19" s="3">
+        <v>0.38409810393292376</v>
+      </c>
+      <c r="X19" s="3">
+        <v>0.99830506410843778</v>
+      </c>
       <c r="Y19" s="5">
         <v>44552</v>
       </c>
@@ -5137,11 +5205,11 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM19" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.89089215933125177</v>
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="2"/>
@@ -5168,7 +5236,7 @@
       </c>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7" t="s">
         <v>680</v>
       </c>
@@ -5231,8 +5299,12 @@
       <c r="V20" s="9">
         <v>100</v>
       </c>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
+      <c r="W20" s="3">
+        <v>0.50271568364227837</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0.4334408700933714</v>
+      </c>
       <c r="Y20" s="5">
         <v>44552</v>
       </c>
@@ -5289,7 +5361,7 @@
       </c>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7" t="s">
         <v>681</v>
       </c>
@@ -5352,8 +5424,12 @@
       <c r="V21" s="9">
         <v>82.09</v>
       </c>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
+      <c r="W21" s="3">
+        <v>0.60058484122286038</v>
+      </c>
+      <c r="X21" s="3">
+        <v>0.38079037162365692</v>
+      </c>
       <c r="Y21" s="5">
         <v>44685</v>
       </c>
@@ -5379,11 +5455,11 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.17181991818628606</v>
       </c>
       <c r="AM21" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>47.953226352795738</v>
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="2"/>
@@ -5410,7 +5486,7 @@
       </c>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7" t="s">
         <v>682</v>
       </c>
@@ -5473,8 +5549,12 @@
       <c r="V22" s="9">
         <v>74.13</v>
       </c>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
+      <c r="W22" s="3">
+        <v>0.95973883087992384</v>
+      </c>
+      <c r="X22" s="3">
+        <v>9.4214808536405625E-2</v>
+      </c>
       <c r="Y22" s="5">
         <v>45064</v>
       </c>
@@ -5504,7 +5584,7 @@
       </c>
       <c r="AM22" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="2"/>
@@ -5531,7 +5611,7 @@
       </c>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7" t="s">
         <v>683</v>
       </c>
@@ -5594,8 +5674,12 @@
       <c r="V23" s="9">
         <v>98.19</v>
       </c>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
+      <c r="W23" s="3">
+        <v>0.15921135532667852</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0.82898482948248853</v>
+      </c>
       <c r="Y23" s="5">
         <v>44508</v>
       </c>
@@ -5652,7 +5736,7 @@
       </c>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>684</v>
       </c>
@@ -5715,8 +5799,12 @@
       <c r="V24" s="9">
         <v>91.71</v>
       </c>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="W24" s="3">
+        <v>0.69200616484081656</v>
+      </c>
+      <c r="X24" s="3">
+        <v>7.5983218989369328E-2</v>
+      </c>
       <c r="Y24" s="5">
         <v>44389</v>
       </c>
@@ -5773,7 +5861,7 @@
       </c>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>685</v>
       </c>
@@ -5836,8 +5924,12 @@
       <c r="V25" s="9">
         <v>99.57</v>
       </c>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="W25" s="3">
+        <v>5.8700797109671798E-2</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0.23976466894393555</v>
+      </c>
       <c r="Y25" s="5">
         <v>44456</v>
       </c>
@@ -5894,7 +5986,7 @@
       </c>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>686</v>
       </c>
@@ -5959,8 +6051,12 @@
       <c r="V26" s="9">
         <v>46.95</v>
       </c>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
+      <c r="W26" s="3">
+        <v>5.58611580067776E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>0.41674409604557305</v>
+      </c>
       <c r="Y26" s="5">
         <v>45100</v>
       </c>
@@ -5986,7 +6082,7 @@
       <c r="AK26" s="3"/>
       <c r="AL26" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.9878469664289238</v>
       </c>
       <c r="AM26" s="3">
         <f t="shared" si="1"/>
@@ -6017,7 +6113,7 @@
       </c>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>687</v>
       </c>
@@ -6080,8 +6176,12 @@
       <c r="V27" s="9">
         <v>99.96</v>
       </c>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
+      <c r="W27" s="3">
+        <v>0.45893929422124558</v>
+      </c>
+      <c r="X27" s="3">
+        <v>0.14248249439054206</v>
+      </c>
       <c r="Y27" s="5">
         <v>44844</v>
       </c>
@@ -6138,7 +6238,7 @@
       </c>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>688</v>
       </c>
@@ -6201,8 +6301,12 @@
       <c r="V28" s="9">
         <v>100</v>
       </c>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
+      <c r="W28" s="3">
+        <v>0.14487904196633772</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0.56052003484427593</v>
+      </c>
       <c r="Y28" s="5">
         <v>44924</v>
       </c>
@@ -6259,7 +6363,7 @@
       </c>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>689</v>
       </c>
@@ -6322,8 +6426,12 @@
       <c r="V29" s="9">
         <v>88.77</v>
       </c>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
+      <c r="W29" s="3">
+        <v>0.25230203712702148</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0.7221569484580197</v>
+      </c>
       <c r="Y29" s="5">
         <v>44797</v>
       </c>
@@ -6380,7 +6488,7 @@
       </c>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>690</v>
       </c>
@@ -6443,8 +6551,12 @@
       <c r="V30" s="9">
         <v>100</v>
       </c>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
+      <c r="W30" s="3">
+        <v>0.66083806006470458</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0.96691030805453593</v>
+      </c>
       <c r="Y30" s="5">
         <v>44924</v>
       </c>
@@ -6501,7 +6613,7 @@
       </c>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>691</v>
       </c>
@@ -6564,8 +6676,12 @@
       <c r="V31" s="9">
         <v>95.46</v>
       </c>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
+      <c r="W31" s="3">
+        <v>0.71144981412176889</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0.71103331147167037</v>
+      </c>
       <c r="Y31" s="5">
         <v>45093</v>
       </c>
@@ -6591,11 +6707,11 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>71.963763363406613</v>
       </c>
       <c r="AM31" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72.05430741777586</v>
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="2"/>
@@ -6622,7 +6738,7 @@
       </c>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>692</v>
       </c>
@@ -6687,8 +6803,12 @@
       <c r="V32" s="9">
         <v>57.65</v>
       </c>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
+      <c r="W32" s="3">
+        <v>0.7763411533124942</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0.89048684551380064</v>
+      </c>
       <c r="Y32" s="5">
         <v>45471</v>
       </c>
@@ -6714,11 +6834,11 @@
       <c r="AK32" s="3"/>
       <c r="AL32" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM32" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>86.161120285324827</v>
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="2"/>
@@ -6745,7 +6865,7 @@
       </c>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>693</v>
       </c>
@@ -6810,8 +6930,12 @@
       <c r="V33" s="9">
         <v>39.020000000000003</v>
       </c>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
+      <c r="W33" s="3">
+        <v>0.62495198082045744</v>
+      </c>
+      <c r="X33" s="3">
+        <v>0.95670630900134546</v>
+      </c>
       <c r="Y33" s="5">
         <v>45093</v>
       </c>
@@ -6837,11 +6961,11 @@
       <c r="AK33" s="3"/>
       <c r="AL33" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM33" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>53.250430613142932</v>
       </c>
       <c r="AN33" s="3">
         <f t="shared" si="2"/>
@@ -6868,7 +6992,7 @@
       </c>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>694</v>
       </c>
@@ -6933,8 +7057,12 @@
       <c r="V34" s="9">
         <v>100</v>
       </c>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
+      <c r="W34" s="3">
+        <v>9.3686004959554814E-2</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0.19582723092810572</v>
+      </c>
       <c r="Y34" s="5">
         <v>45093</v>
       </c>
@@ -6991,7 +7119,7 @@
       </c>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
         <v>695</v>
       </c>
@@ -7054,8 +7182,12 @@
       <c r="V35" s="9">
         <v>94.43</v>
       </c>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
+      <c r="W35" s="3">
+        <v>0.64839375113380227</v>
+      </c>
+      <c r="X35" s="3">
+        <v>0.97522051580565627</v>
+      </c>
       <c r="Y35" s="5">
         <v>45100</v>
       </c>
@@ -7110,7 +7242,7 @@
       </c>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
         <v>696</v>
       </c>
@@ -7175,8 +7307,12 @@
       <c r="V36" s="9">
         <v>2.75</v>
       </c>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
+      <c r="W36" s="3">
+        <v>0.5625414864755045</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0.94119537798976449</v>
+      </c>
       <c r="Y36" s="5">
         <v>45505</v>
       </c>
@@ -7200,11 +7336,11 @@
       <c r="AK36" s="3"/>
       <c r="AL36" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM36" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>39.682931842500977</v>
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="9"/>
@@ -7231,7 +7367,7 @@
       </c>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
         <v>697</v>
       </c>
@@ -7296,8 +7432,12 @@
       <c r="V37" s="9">
         <v>100</v>
       </c>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
+      <c r="W37" s="3">
+        <v>0.29780370417714541</v>
+      </c>
+      <c r="X37" s="3">
+        <v>0.2310924547693104</v>
+      </c>
       <c r="Y37" s="5">
         <v>45233</v>
       </c>
@@ -7354,7 +7494,7 @@
       </c>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
         <v>698</v>
       </c>
@@ -7417,8 +7557,12 @@
       <c r="V38" s="9">
         <v>63.36</v>
       </c>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
+      <c r="W38" s="3">
+        <v>0.90855769655472329</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0.40771209437768896</v>
+      </c>
       <c r="Y38" s="5">
         <v>45290</v>
       </c>
@@ -7444,11 +7588,11 @@
       <c r="AK38" s="3"/>
       <c r="AL38" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>6.0243683429758601</v>
       </c>
       <c r="AM38" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="9"/>
@@ -7475,7 +7619,7 @@
       </c>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="7" t="s">
         <v>699</v>
       </c>
@@ -7540,8 +7684,12 @@
       <c r="V39" s="9">
         <v>77.42</v>
       </c>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
+      <c r="W39" s="3">
+        <v>0.61891373344081402</v>
+      </c>
+      <c r="X39" s="3">
+        <v>0.38780640295257818</v>
+      </c>
       <c r="Y39" s="5">
         <v>45329</v>
       </c>
@@ -7567,11 +7715,11 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1.6970441201256898</v>
       </c>
       <c r="AM39" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>51.937768139307394</v>
       </c>
       <c r="AN39" s="3">
         <f t="shared" si="9"/>
@@ -7598,7 +7746,7 @@
       </c>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="7" t="s">
         <v>700</v>
       </c>
@@ -7663,8 +7811,12 @@
       <c r="V40" s="9">
         <v>36.86</v>
       </c>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
+      <c r="W40" s="3">
+        <v>0.1054757156244911</v>
+      </c>
+      <c r="X40" s="3">
+        <v>0.6528529458510729</v>
+      </c>
       <c r="Y40" s="5">
         <v>45756</v>
       </c>
@@ -7690,7 +7842,7 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>59.315857793711501</v>
       </c>
       <c r="AM40" s="3">
         <f t="shared" si="8"/>
@@ -7721,7 +7873,7 @@
       </c>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>701</v>
       </c>
@@ -7786,8 +7938,12 @@
       <c r="V41" s="9">
         <v>66.13</v>
       </c>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
+      <c r="W41" s="3">
+        <v>0.92223126097989383</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0.87713096159901194</v>
+      </c>
       <c r="Y41" s="5">
         <v>45582</v>
       </c>
@@ -7813,11 +7969,11 @@
       <c r="AK41" s="3"/>
       <c r="AL41" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM41" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="9"/>
@@ -7844,7 +8000,7 @@
       </c>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>702</v>
       </c>
@@ -7909,8 +8065,12 @@
       <c r="V42" s="9">
         <v>32.83</v>
       </c>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
+      <c r="W42" s="3">
+        <v>0.18889088118506825</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0.15414020489933655</v>
+      </c>
       <c r="Y42" s="5">
         <v>45649</v>
       </c>
@@ -7965,7 +8125,7 @@
       </c>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>703</v>
       </c>
@@ -8024,8 +8184,12 @@
       <c r="V43" s="9">
         <v>0</v>
       </c>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
+      <c r="W43" s="3">
+        <v>0.49077555781094695</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0.40649356655517732</v>
+      </c>
       <c r="Y43" s="5">
         <v>45615</v>
       </c>
@@ -8080,7 +8244,7 @@
       </c>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>704</v>
       </c>
@@ -8145,8 +8309,12 @@
       <c r="V44" s="9">
         <v>28</v>
       </c>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
+      <c r="W44" s="3">
+        <v>0.40731020258753314</v>
+      </c>
+      <c r="X44" s="3">
+        <v>7.2633527497073413E-2</v>
+      </c>
       <c r="Y44" s="5">
         <v>45632</v>
       </c>
@@ -8176,7 +8344,7 @@
       </c>
       <c r="AM44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>5.9370005625072046</v>
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="9"/>
@@ -8203,7 +8371,7 @@
       </c>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>705</v>
       </c>
@@ -8268,8 +8436,12 @@
       <c r="V45" s="9">
         <v>1.08</v>
       </c>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
+      <c r="W45" s="3">
+        <v>0.24068738722230576</v>
+      </c>
+      <c r="X45" s="3">
+        <v>4.6576501713487928E-2</v>
+      </c>
       <c r="Y45" s="5">
         <v>45637</v>
       </c>
@@ -8324,7 +8496,7 @@
       </c>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>706</v>
       </c>
@@ -8387,8 +8559,12 @@
       <c r="V46" s="9">
         <v>0</v>
       </c>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
+      <c r="W46" s="3">
+        <v>0.29790508299462226</v>
+      </c>
+      <c r="X46" s="3">
+        <v>1.3218874800209779E-2</v>
+      </c>
       <c r="Y46" s="5">
         <v>45650</v>
       </c>
@@ -8449,7 +8625,7 @@
       </c>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>707</v>
       </c>
@@ -8514,8 +8690,12 @@
       <c r="V47" s="9">
         <v>34.75</v>
       </c>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
+      <c r="W47" s="3">
+        <v>0.9406661107184906</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0.91935964043193641</v>
+      </c>
       <c r="Y47" s="5">
         <v>45650</v>
       </c>
@@ -8541,11 +8721,11 @@
       <c r="AK47" s="3"/>
       <c r="AL47" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN47" s="3">
         <f t="shared" si="9"/>
@@ -8572,7 +8752,7 @@
       </c>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>708</v>
       </c>
@@ -8639,8 +8819,12 @@
       <c r="V48" s="9">
         <v>40.81</v>
       </c>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
+      <c r="W48" s="3">
+        <v>0.73082885939161779</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0.62516145220085451</v>
+      </c>
       <c r="Y48" s="5">
         <v>45888</v>
       </c>
@@ -8666,11 +8850,11 @@
       <c r="AK48" s="3"/>
       <c r="AL48" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>53.295967869750982</v>
       </c>
       <c r="AM48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>76.267143346003877</v>
       </c>
       <c r="AN48" s="3">
         <f t="shared" si="9"/>
@@ -8697,7 +8881,7 @@
       </c>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="7" t="s">
         <v>709</v>
       </c>
@@ -8762,8 +8946,12 @@
       <c r="V49" s="9">
         <v>27.19</v>
       </c>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
+      <c r="W49" s="3">
+        <v>0.64544248282512351</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0.43778772870692761</v>
+      </c>
       <c r="Y49" s="5">
         <v>45933</v>
       </c>
@@ -8820,7 +9008,7 @@
       </c>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" spans="1:48" ht="123" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" ht="123" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="7" t="s">
         <v>710</v>
       </c>
@@ -8885,8 +9073,12 @@
       <c r="V50" s="9">
         <v>30</v>
       </c>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
+      <c r="W50" s="3">
+        <v>0.59687080986255281</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0.71670143332727998</v>
+      </c>
       <c r="Y50" s="5">
         <v>45912</v>
       </c>
@@ -8912,11 +9104,11 @@
       <c r="AK50" s="3"/>
       <c r="AL50" s="3">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>73.195963766799991</v>
       </c>
       <c r="AM50" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>47.145828230989743</v>
       </c>
       <c r="AN50" s="3">
         <f t="shared" si="9"/>
@@ -8943,7 +9135,7 @@
       </c>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="7" t="s">
         <v>711</v>
       </c>
@@ -9002,8 +9194,12 @@
       <c r="V51" s="9">
         <v>0</v>
       </c>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
+      <c r="W51" s="3">
+        <v>0.54701762173245505</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0.60007862696667902</v>
+      </c>
       <c r="Y51" s="5">
         <v>46000</v>
       </c>
@@ -9058,7 +9254,7 @@
       </c>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" spans="1:48" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="7" t="s">
         <v>712</v>
       </c>
@@ -9111,8 +9307,12 @@
       <c r="V52" s="9">
         <v>0</v>
       </c>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
+      <c r="W52" s="3">
+        <v>2.916503540650206E-3</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0.50497470187688875</v>
+      </c>
       <c r="Y52" s="5">
         <v>46080</v>
       </c>
@@ -9167,7 +9367,7 @@
       </c>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" spans="1:48" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" ht="87" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="7" t="s">
         <v>713</v>
       </c>
@@ -9226,8 +9426,12 @@
       <c r="V53" s="9">
         <v>0</v>
       </c>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
+      <c r="W53" s="3">
+        <v>0.81820950941571691</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0.32766670167968315</v>
+      </c>
       <c r="Y53" s="5">
         <v>45967</v>
       </c>
@@ -9282,7 +9486,7 @@
       </c>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" spans="1:48" ht="127.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" ht="127.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="7" t="s">
         <v>714</v>
       </c>
@@ -9347,8 +9551,12 @@
       <c r="V54" s="9">
         <v>0</v>
       </c>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
+      <c r="W54" s="3">
+        <v>0.5440131551321582</v>
+      </c>
+      <c r="X54" s="3">
+        <v>0.23644271462239697</v>
+      </c>
       <c r="Y54" s="5">
         <v>45957</v>
       </c>
@@ -9405,7 +9613,7 @@
       </c>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="7" t="s">
         <v>715</v>
       </c>
@@ -9466,8 +9674,12 @@
       <c r="V55" s="9">
         <v>0</v>
       </c>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
+      <c r="W55" s="3">
+        <v>0.5662089061186103</v>
+      </c>
+      <c r="X55" s="3">
+        <v>0.90541474502084818</v>
+      </c>
       <c r="Y55" s="5">
         <v>45980</v>
       </c>
@@ -9522,7 +9734,7 @@
       </c>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" spans="1:48" ht="105.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:48" ht="105.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="7" t="s">
         <v>716</v>
       </c>
@@ -9581,8 +9793,12 @@
       <c r="V56" s="9">
         <v>0</v>
       </c>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
+      <c r="W56" s="3">
+        <v>0.3460250254461944</v>
+      </c>
+      <c r="X56" s="3">
+        <v>0.33853626156811079</v>
+      </c>
       <c r="Y56" s="5">
         <v>46010</v>
       </c>
@@ -9637,7 +9853,7 @@
       </c>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" spans="1:48" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="7" t="s">
         <v>717</v>
       </c>
@@ -9690,8 +9906,12 @@
       <c r="V57" s="9">
         <v>0</v>
       </c>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
+      <c r="W57" s="3">
+        <v>0.61811456992439773</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0.63060869676390574</v>
+      </c>
       <c r="Y57" s="5">
         <v>46080</v>
       </c>
@@ -9762,16 +9982,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="28" width="25.7109375" customWidth="1"/>
-    <col min="29" max="29" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="30" max="34" width="25.7109375" customWidth="1"/>
-    <col min="35" max="35" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="36" max="37" width="25.7109375" customWidth="1"/>
+    <col min="1" max="28" width="25.6640625" customWidth="1"/>
+    <col min="29" max="29" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="30" max="34" width="25.6640625" customWidth="1"/>
+    <col min="35" max="35" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="36" max="37" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -9816,7 +10036,7 @@
       <c r="AJ1" s="10"/>
       <c r="AK1" s="10"/>
     </row>
-    <row r="2" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -9929,7 +10149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>176</v>
       </c>
@@ -10016,7 +10236,7 @@
       </c>
       <c r="AK3" s="3"/>
     </row>
-    <row r="4" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>181</v>
       </c>
@@ -10103,7 +10323,7 @@
       </c>
       <c r="AK4" s="3"/>
     </row>
-    <row r="5" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>186</v>
       </c>
@@ -10194,7 +10414,7 @@
       </c>
       <c r="AK5" s="3"/>
     </row>
-    <row r="6" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>190</v>
       </c>
@@ -10285,7 +10505,7 @@
       </c>
       <c r="AK6" s="3"/>
     </row>
-    <row r="7" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>194</v>
       </c>
@@ -10372,7 +10592,7 @@
       </c>
       <c r="AK7" s="3"/>
     </row>
-    <row r="8" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>198</v>
       </c>
@@ -10459,7 +10679,7 @@
       </c>
       <c r="AK8" s="3"/>
     </row>
-    <row r="9" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>201</v>
       </c>
@@ -10546,7 +10766,7 @@
       </c>
       <c r="AK9" s="3"/>
     </row>
-    <row r="10" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>205</v>
       </c>
@@ -10633,7 +10853,7 @@
       </c>
       <c r="AK10" s="3"/>
     </row>
-    <row r="11" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>208</v>
       </c>
@@ -10720,7 +10940,7 @@
       </c>
       <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>211</v>
       </c>
@@ -10807,7 +11027,7 @@
       </c>
       <c r="AK12" s="3"/>
     </row>
-    <row r="13" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>215</v>
       </c>
@@ -10894,7 +11114,7 @@
       </c>
       <c r="AK13" s="3"/>
     </row>
-    <row r="14" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>218</v>
       </c>
@@ -10981,7 +11201,7 @@
       </c>
       <c r="AK14" s="3"/>
     </row>
-    <row r="15" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>221</v>
       </c>
@@ -11068,7 +11288,7 @@
       </c>
       <c r="AK15" s="3"/>
     </row>
-    <row r="16" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>224</v>
       </c>
@@ -11155,7 +11375,7 @@
       </c>
       <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="1:37" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>227</v>
       </c>
@@ -11258,12 +11478,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R104"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="25.7109375" customWidth="1"/>
+    <col min="1" max="18" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -11285,7 +11505,7 @@
       <c r="Q1" s="10"/>
       <c r="R1" s="10"/>
     </row>
-    <row r="2" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11341,7 +11561,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>231</v>
       </c>
@@ -11381,7 +11601,7 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>235</v>
       </c>
@@ -11421,7 +11641,7 @@
       <c r="Q4" s="4"/>
       <c r="R4" s="3"/>
     </row>
-    <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>239</v>
       </c>
@@ -11461,7 +11681,7 @@
       <c r="Q5" s="4"/>
       <c r="R5" s="3"/>
     </row>
-    <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>243</v>
       </c>
@@ -11501,7 +11721,7 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="3"/>
     </row>
-    <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>247</v>
       </c>
@@ -11541,7 +11761,7 @@
       <c r="Q7" s="4"/>
       <c r="R7" s="3"/>
     </row>
-    <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>251</v>
       </c>
@@ -11581,7 +11801,7 @@
       <c r="Q8" s="4"/>
       <c r="R8" s="3"/>
     </row>
-    <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>255</v>
       </c>
@@ -11621,7 +11841,7 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="3"/>
     </row>
-    <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>260</v>
       </c>
@@ -11661,7 +11881,7 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="3"/>
     </row>
-    <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>265</v>
       </c>
@@ -11701,7 +11921,7 @@
       <c r="Q11" s="4"/>
       <c r="R11" s="3"/>
     </row>
-    <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>269</v>
       </c>
@@ -11741,7 +11961,7 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>274</v>
       </c>
@@ -11781,7 +12001,7 @@
       <c r="Q13" s="4"/>
       <c r="R13" s="3"/>
     </row>
-    <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>279</v>
       </c>
@@ -11821,7 +12041,7 @@
       <c r="Q14" s="4"/>
       <c r="R14" s="3"/>
     </row>
-    <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>284</v>
       </c>
@@ -11861,7 +12081,7 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="3"/>
     </row>
-    <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>288</v>
       </c>
@@ -11901,7 +12121,7 @@
       <c r="Q16" s="4"/>
       <c r="R16" s="3"/>
     </row>
-    <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>292</v>
       </c>
@@ -11941,7 +12161,7 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="3"/>
     </row>
-    <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>296</v>
       </c>
@@ -11981,7 +12201,7 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="3"/>
     </row>
-    <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>300</v>
       </c>
@@ -12021,7 +12241,7 @@
       <c r="Q19" s="4"/>
       <c r="R19" s="3"/>
     </row>
-    <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>304</v>
       </c>
@@ -12061,7 +12281,7 @@
       <c r="Q20" s="4"/>
       <c r="R20" s="3"/>
     </row>
-    <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>308</v>
       </c>
@@ -12101,7 +12321,7 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="3"/>
     </row>
-    <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>312</v>
       </c>
@@ -12141,7 +12361,7 @@
       <c r="Q22" s="4"/>
       <c r="R22" s="3"/>
     </row>
-    <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>316</v>
       </c>
@@ -12181,7 +12401,7 @@
       <c r="Q23" s="4"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>320</v>
       </c>
@@ -12221,7 +12441,7 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="3"/>
     </row>
-    <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>324</v>
       </c>
@@ -12261,7 +12481,7 @@
       <c r="Q25" s="4"/>
       <c r="R25" s="3"/>
     </row>
-    <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>328</v>
       </c>
@@ -12301,7 +12521,7 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="3"/>
     </row>
-    <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>332</v>
       </c>
@@ -12341,7 +12561,7 @@
       <c r="Q27" s="4"/>
       <c r="R27" s="3"/>
     </row>
-    <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>336</v>
       </c>
@@ -12381,7 +12601,7 @@
       <c r="Q28" s="4"/>
       <c r="R28" s="3"/>
     </row>
-    <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>341</v>
       </c>
@@ -12421,7 +12641,7 @@
       <c r="Q29" s="4"/>
       <c r="R29" s="3"/>
     </row>
-    <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>345</v>
       </c>
@@ -12461,7 +12681,7 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="3"/>
     </row>
-    <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>348</v>
       </c>
@@ -12501,7 +12721,7 @@
       <c r="Q31" s="4"/>
       <c r="R31" s="3"/>
     </row>
-    <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>353</v>
       </c>
@@ -12541,7 +12761,7 @@
       <c r="Q32" s="4"/>
       <c r="R32" s="3"/>
     </row>
-    <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>356</v>
       </c>
@@ -12581,7 +12801,7 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="3"/>
     </row>
-    <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>359</v>
       </c>
@@ -12621,7 +12841,7 @@
       <c r="Q34" s="4"/>
       <c r="R34" s="3"/>
     </row>
-    <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>362</v>
       </c>
@@ -12661,7 +12881,7 @@
       <c r="Q35" s="4"/>
       <c r="R35" s="3"/>
     </row>
-    <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>366</v>
       </c>
@@ -12701,7 +12921,7 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="3"/>
     </row>
-    <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>370</v>
       </c>
@@ -12741,7 +12961,7 @@
       <c r="Q37" s="4"/>
       <c r="R37" s="3"/>
     </row>
-    <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>374</v>
       </c>
@@ -12781,7 +13001,7 @@
       <c r="Q38" s="4"/>
       <c r="R38" s="3"/>
     </row>
-    <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>378</v>
       </c>
@@ -12821,7 +13041,7 @@
       <c r="Q39" s="4"/>
       <c r="R39" s="3"/>
     </row>
-    <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>382</v>
       </c>
@@ -12861,7 +13081,7 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="3"/>
     </row>
-    <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>386</v>
       </c>
@@ -12901,7 +13121,7 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="3"/>
     </row>
-    <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>389</v>
       </c>
@@ -12941,7 +13161,7 @@
       <c r="Q42" s="4"/>
       <c r="R42" s="3"/>
     </row>
-    <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>392</v>
       </c>
@@ -12981,7 +13201,7 @@
       <c r="Q43" s="4"/>
       <c r="R43" s="3"/>
     </row>
-    <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>395</v>
       </c>
@@ -13021,7 +13241,7 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="3"/>
     </row>
-    <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>398</v>
       </c>
@@ -13061,7 +13281,7 @@
       <c r="Q45" s="4"/>
       <c r="R45" s="3"/>
     </row>
-    <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>402</v>
       </c>
@@ -13101,7 +13321,7 @@
       <c r="Q46" s="4"/>
       <c r="R46" s="3"/>
     </row>
-    <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>406</v>
       </c>
@@ -13141,7 +13361,7 @@
       <c r="Q47" s="4"/>
       <c r="R47" s="3"/>
     </row>
-    <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>409</v>
       </c>
@@ -13181,7 +13401,7 @@
       <c r="Q48" s="4"/>
       <c r="R48" s="3"/>
     </row>
-    <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>413</v>
       </c>
@@ -13221,7 +13441,7 @@
       <c r="Q49" s="4"/>
       <c r="R49" s="3"/>
     </row>
-    <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>416</v>
       </c>
@@ -13261,7 +13481,7 @@
       <c r="Q50" s="4"/>
       <c r="R50" s="3"/>
     </row>
-    <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>419</v>
       </c>
@@ -13301,7 +13521,7 @@
       <c r="Q51" s="4"/>
       <c r="R51" s="3"/>
     </row>
-    <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>423</v>
       </c>
@@ -13341,7 +13561,7 @@
       <c r="Q52" s="4"/>
       <c r="R52" s="3"/>
     </row>
-    <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>426</v>
       </c>
@@ -13381,7 +13601,7 @@
       <c r="Q53" s="4"/>
       <c r="R53" s="3"/>
     </row>
-    <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>429</v>
       </c>
@@ -13421,7 +13641,7 @@
       <c r="Q54" s="4"/>
       <c r="R54" s="3"/>
     </row>
-    <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>432</v>
       </c>
@@ -13461,7 +13681,7 @@
       <c r="Q55" s="4"/>
       <c r="R55" s="3"/>
     </row>
-    <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>435</v>
       </c>
@@ -13501,7 +13721,7 @@
       <c r="Q56" s="4"/>
       <c r="R56" s="3"/>
     </row>
-    <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>438</v>
       </c>
@@ -13541,7 +13761,7 @@
       <c r="Q57" s="4"/>
       <c r="R57" s="3"/>
     </row>
-    <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>442</v>
       </c>
@@ -13581,7 +13801,7 @@
       <c r="Q58" s="4"/>
       <c r="R58" s="3"/>
     </row>
-    <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>445</v>
       </c>
@@ -13621,7 +13841,7 @@
       <c r="Q59" s="4"/>
       <c r="R59" s="3"/>
     </row>
-    <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>448</v>
       </c>
@@ -13661,7 +13881,7 @@
       <c r="Q60" s="4"/>
       <c r="R60" s="3"/>
     </row>
-    <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>451</v>
       </c>
@@ -13701,7 +13921,7 @@
       <c r="Q61" s="4"/>
       <c r="R61" s="3"/>
     </row>
-    <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>455</v>
       </c>
@@ -13741,7 +13961,7 @@
       <c r="Q62" s="4"/>
       <c r="R62" s="3"/>
     </row>
-    <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>458</v>
       </c>
@@ -13781,7 +14001,7 @@
       <c r="Q63" s="4"/>
       <c r="R63" s="3"/>
     </row>
-    <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>462</v>
       </c>
@@ -13821,7 +14041,7 @@
       <c r="Q64" s="4"/>
       <c r="R64" s="3"/>
     </row>
-    <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>466</v>
       </c>
@@ -13861,7 +14081,7 @@
       <c r="Q65" s="4"/>
       <c r="R65" s="3"/>
     </row>
-    <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>469</v>
       </c>
@@ -13901,7 +14121,7 @@
       <c r="Q66" s="4"/>
       <c r="R66" s="3"/>
     </row>
-    <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>472</v>
       </c>
@@ -13941,7 +14161,7 @@
       <c r="Q67" s="4"/>
       <c r="R67" s="3"/>
     </row>
-    <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>475</v>
       </c>
@@ -13981,7 +14201,7 @@
       <c r="Q68" s="4"/>
       <c r="R68" s="3"/>
     </row>
-    <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>478</v>
       </c>
@@ -14021,7 +14241,7 @@
       <c r="Q69" s="4"/>
       <c r="R69" s="3"/>
     </row>
-    <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>481</v>
       </c>
@@ -14061,7 +14281,7 @@
       <c r="Q70" s="4"/>
       <c r="R70" s="3"/>
     </row>
-    <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>485</v>
       </c>
@@ -14101,7 +14321,7 @@
       <c r="Q71" s="4"/>
       <c r="R71" s="3"/>
     </row>
-    <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>488</v>
       </c>
@@ -14141,7 +14361,7 @@
       <c r="Q72" s="4"/>
       <c r="R72" s="3"/>
     </row>
-    <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>491</v>
       </c>
@@ -14181,7 +14401,7 @@
       <c r="Q73" s="4"/>
       <c r="R73" s="3"/>
     </row>
-    <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>494</v>
       </c>
@@ -14221,7 +14441,7 @@
       <c r="Q74" s="4"/>
       <c r="R74" s="3"/>
     </row>
-    <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>497</v>
       </c>
@@ -14261,7 +14481,7 @@
       <c r="Q75" s="4"/>
       <c r="R75" s="3"/>
     </row>
-    <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>500</v>
       </c>
@@ -14301,7 +14521,7 @@
       <c r="Q76" s="4"/>
       <c r="R76" s="3"/>
     </row>
-    <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>503</v>
       </c>
@@ -14339,7 +14559,7 @@
       <c r="Q77" s="4"/>
       <c r="R77" s="3"/>
     </row>
-    <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>507</v>
       </c>
@@ -14379,7 +14599,7 @@
       <c r="Q78" s="4"/>
       <c r="R78" s="3"/>
     </row>
-    <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>511</v>
       </c>
@@ -14419,7 +14639,7 @@
       <c r="Q79" s="4"/>
       <c r="R79" s="3"/>
     </row>
-    <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>515</v>
       </c>
@@ -14459,7 +14679,7 @@
       <c r="Q80" s="4"/>
       <c r="R80" s="3"/>
     </row>
-    <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>519</v>
       </c>
@@ -14499,7 +14719,7 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="3"/>
     </row>
-    <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>522</v>
       </c>
@@ -14539,7 +14759,7 @@
       <c r="Q82" s="4"/>
       <c r="R82" s="3"/>
     </row>
-    <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>525</v>
       </c>
@@ -14579,7 +14799,7 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="3"/>
     </row>
-    <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>529</v>
       </c>
@@ -14619,7 +14839,7 @@
       <c r="Q84" s="4"/>
       <c r="R84" s="3"/>
     </row>
-    <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>533</v>
       </c>
@@ -14659,7 +14879,7 @@
       <c r="Q85" s="4"/>
       <c r="R85" s="3"/>
     </row>
-    <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>537</v>
       </c>
@@ -14699,7 +14919,7 @@
       <c r="Q86" s="4"/>
       <c r="R86" s="3"/>
     </row>
-    <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>541</v>
       </c>
@@ -14739,7 +14959,7 @@
       <c r="Q87" s="4"/>
       <c r="R87" s="3"/>
     </row>
-    <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>545</v>
       </c>
@@ -14779,7 +14999,7 @@
       <c r="Q88" s="4"/>
       <c r="R88" s="3"/>
     </row>
-    <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>549</v>
       </c>
@@ -14819,7 +15039,7 @@
       <c r="Q89" s="4"/>
       <c r="R89" s="3"/>
     </row>
-    <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>554</v>
       </c>
@@ -14859,7 +15079,7 @@
       <c r="Q90" s="4"/>
       <c r="R90" s="3"/>
     </row>
-    <row r="91" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>558</v>
       </c>
@@ -14899,7 +15119,7 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="3"/>
     </row>
-    <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>561</v>
       </c>
@@ -14939,7 +15159,7 @@
       <c r="Q92" s="4"/>
       <c r="R92" s="3"/>
     </row>
-    <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>564</v>
       </c>
@@ -14977,7 +15197,7 @@
       <c r="Q93" s="4"/>
       <c r="R93" s="3"/>
     </row>
-    <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>566</v>
       </c>
@@ -15015,7 +15235,7 @@
       <c r="Q94" s="4"/>
       <c r="R94" s="3"/>
     </row>
-    <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>569</v>
       </c>
@@ -15055,7 +15275,7 @@
       <c r="Q95" s="4"/>
       <c r="R95" s="3"/>
     </row>
-    <row r="96" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>573</v>
       </c>
@@ -15093,7 +15313,7 @@
       <c r="Q96" s="4"/>
       <c r="R96" s="3"/>
     </row>
-    <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>576</v>
       </c>
@@ -15133,7 +15353,7 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="3"/>
     </row>
-    <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>580</v>
       </c>
@@ -15173,7 +15393,7 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="3"/>
     </row>
-    <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>584</v>
       </c>
@@ -15213,7 +15433,7 @@
       <c r="Q99" s="4"/>
       <c r="R99" s="3"/>
     </row>
-    <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>587</v>
       </c>
@@ -15253,7 +15473,7 @@
       <c r="Q100" s="4"/>
       <c r="R100" s="3"/>
     </row>
-    <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>591</v>
       </c>
@@ -15293,7 +15513,7 @@
       <c r="Q101" s="4"/>
       <c r="R101" s="3"/>
     </row>
-    <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>595</v>
       </c>
@@ -15333,7 +15553,7 @@
       <c r="Q102" s="4"/>
       <c r="R102" s="3"/>
     </row>
-    <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>599</v>
       </c>
@@ -15373,7 +15593,7 @@
       <c r="Q103" s="4"/>
       <c r="R103" s="3"/>
     </row>
-    <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>602</v>
       </c>

--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="364" documentId="11_A78776D1E842DF805D35AEE6E05861D715103029" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A374DD46-2B5A-4085-B2D1-575EA2C15AE1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{690FE775-1C55-4B7A-8805-B64E18B6F1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1821" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="923">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1121,9 +1121,6 @@
     <t>Se encuentra en el simulador de la página de Colombia Compra para el proceso de contrataciòn</t>
   </si>
   <si>
-    <t>Proyecto en estado “Sin contratar”, que desde su aprobación presenta 510 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II.</t>
-  </si>
-  <si>
     <t>2024002700176</t>
   </si>
   <si>
@@ -1201,10 +1198,6 @@
   </si>
   <si>
     <t>Contrato de obra contratado El contrato de Interventoría fue declarado desierto. No se ha publicado nuevo proceso.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026: El proyecto se encuentra en ejecución  sin acta de inicio desde junio de 2025, el contrato de obra fue adjudicado y suscrito mediante No de contrato LP-009-2025 el 05 de febrero de 2026. Mediante la resolución 0768 del 23 febrero de 2026, se aperturó el proceso CM-002-2026 para la interventorí, Actualmente se encuentra en proceso de evaluación y observaciones.
-Esta situación está generando una calificación de 0, debido a que no se cuenta con programación del proyecto ni con acta de inicio. </t>
   </si>
   <si>
     <t>2024002700184</t>
@@ -1318,9 +1311,6 @@
     <t>Resolución de adjudicación No. 1401 del 8 de abril de 2026 El proceso del contrato de interventoría, sin publicar</t>
   </si>
   <si>
-    <t>20/04/2026: El proyecto cuenta con el primer contrato de consultoría adjudicado el 08 de abril de 2026 y actualmente se encuentra en espera de la firma del contrato, adicionalmente, el proceso precontractual de la interventoría aún no ha sido publicado.</t>
-  </si>
-  <si>
     <t>2025002700021</t>
   </si>
   <si>
@@ -1334,10 +1324,6 @@
 Via terciaria mejorada</t>
   </si>
   <si>
-    <t xml:space="preserve">20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 47 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial
-</t>
-  </si>
-  <si>
     <t>2025002700023</t>
   </si>
   <si>
@@ -1356,9 +1342,6 @@
     <t>Nos permitimos informar que: • El proyecto se encuentra adjudicado desde el 13 de marzo de 2026 y contratado. • Cuenta con Registro Presupuesta (RP) No. 1426 de fecha 27 de marzo de 2026. • Se realizó el pago de las estampillas correspondientes. • Dispone de pólizas requeridas aprobadas. • Se encuentra pendiente la socialización, necesaria para el perfeccionamiento contractual. Una vez surtida la socialización, se procederá con la firma del acta de inicio y el posterior cargue de la programación en la plataforma GESPROY. Se anexan los siguientes documentos: Resolución de adjudicación, Registro Presupuestal, pólizas, soporte de pago de estampillas y pantallazo de aprobación de las pólizas del contrato en secop II.</t>
   </si>
   <si>
-    <t>Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 13 de marzo de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.</t>
-  </si>
-  <si>
     <t>2025002700025</t>
   </si>
   <si>
@@ -1380,9 +1363,6 @@
     <t>Nos permitimos informar que: • El contratista realizó el pago de las estampillas correspondientes. • El proyecto ya se encuentra contratado y cuenta con Registro Presupuestal (RP) No. 626 de fecha 4 de febrero de 2026. • Dispone de pólizas requeridas aprobadas. Se está a la espera de la firma del acta de inicio y posterior cargue de la programación en la plataforma de GESPROY. Se anexan los siguientes documentos: Estampillas, Registro Presupuestal, Pólizas del contrato y pantallazo de aprobación de las pólizas del contrato en secop II.</t>
   </si>
   <si>
-    <t>Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 04 de febrero  de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.</t>
-  </si>
-  <si>
     <t>2025002700033</t>
   </si>
   <si>
@@ -1401,9 +1381,6 @@
     <t>Resolución de apertura No. 1397 de 8 de abril de 2026, de la Consultoría Aviso de Convocatoria del Proceso No. CM-004-2026 El proceso del contrato de interventoría no se ha publicado</t>
   </si>
   <si>
-    <t>20/04/2026: Resolución de apertura No. 1397 de 8 de abril de 2026,  con  Proceso No. CM-004-2026 de la Consultoría.  El proceso del contrato de interventoría no se ha publicado.</t>
-  </si>
-  <si>
     <t>2025002700035</t>
   </si>
   <si>
@@ -1417,9 +1394,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Se encuentra en el aplicativo Gesproy en estado “SIN CONTRATAR”. Se solicita remitir información actualizada sobre el estado de contratación, la programación de los eventos de participación ciudadana, la modalidad de contratación prevista para cada uno de los procesos contractuales del proyecto, así como la fecha programada para la apertura de cada uno de dichos procesos.</t>
-  </si>
-  <si>
-    <t>20/04/2026: El proyecto cuenta con el proceso de contratación de la consultoría No. CM-003-2026 publicado en SECOP II desde el 13 de febrero de 2026; sin embargo, a la fecha aún no se ha iniciado el proceso de contratación de la interventoría.</t>
   </si>
   <si>
     <t>Mejoramiento en pavimento rígido y construcción de obras hidráulicas en tramos viales en las subregiones Sabana y Montes de María en el departamento de  Sucre</t>
@@ -1434,9 +1408,6 @@
     <t xml:space="preserve">SGR - Asignaciones directas
 Asignación para la inversión regional 60%
 </t>
-  </si>
-  <si>
-    <t>20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 47 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial</t>
   </si>
   <si>
     <t>EJECUTOR</t>
@@ -2861,12 +2832,6 @@
     <t>AGREGAR LAS DESCENTRALIZADAS</t>
   </si>
   <si>
-    <t>01/01/1753</t>
-  </si>
-  <si>
-    <t>29/12/202</t>
-  </si>
-  <si>
     <t>RESPONSABLE CARGUE EN GESPROY</t>
   </si>
   <si>
@@ -2894,11 +2859,74 @@
     <t>OSVALDO SIERRA CARVAJALINO</t>
   </si>
   <si>
-    <t xml:space="preserve">	07/04/2026	</t>
-  </si>
-  <si>
-    <t>20/04/2026: Proyecto en estado “Sin contratar”, que desde su aprobación presenta 34 días a la fecha de corte del 15 de abril de 2026, sin registro de proceso precontractual en SECOP II. Se realizó solicitud del CDP, aún no se ha publicado proceso de contratación, están en elaboración de estudios previos.
-27/04/2026: Ya cuenta con CDP, en elaboración de estudios previos</t>
+    <t>NOMBRE DE COLUMNA</t>
+  </si>
+  <si>
+    <t>DESCENTRALIZADAS Y MUNIICIPIOS</t>
+  </si>
+  <si>
+    <t>AGREGAR COLUMNA DE SECTOR</t>
+  </si>
+  <si>
+    <t>HITO 2 E HITO 1 QUE NO SE REPITAN LOS PROYECTOS</t>
+  </si>
+  <si>
+    <t>PAGINA FILTRO DE LOS MUNICIPIOS</t>
+  </si>
+  <si>
+    <t>DÍAS DE CORTE Y DÍAS A FECHA ACTUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGINA REPORTE SEGUIMIENTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSTRAR COMENTARIOS DE LA MATRIZ EN LOS HITOS </t>
+  </si>
+  <si>
+    <t>Pendiente agregar en la herramienta de consolidación</t>
+  </si>
+  <si>
+    <t>Realizado</t>
+  </si>
+  <si>
+    <t>5/05/2026: Proyecto realizó apertura de proceso de simulación en Colombia compra eficiente  de la  compra de maquinaria amarilla-agrícola (5-marzo de 2026), este proceso fue declarado desierto.
+Conforme a la información proporcionada por la sectorial ya fueron radicados nuevamente  los estudios previos  a contratación el 01/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II, cuenta con CDP, en elaboración de estudios previos por parte de la sectorial.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+05/05/2026: El 4 de mayo de 2026 se suscribió el contrato de obra. En cuanto al proceso para la contratación de la interventoría, el 24 de abril 2026 se radicaron en la oficina de subcontratación los estudios previos y demás documentación soporte, para su respectiva revisión y trámite; actualmente, se encuentra a la espera de la publicación del respectivo proceso contractual. Este proyecto debería aparecer en Gesproy "contratado sin acta de inicio", sin embargo, está a la espera de que migre el contrato a la plataforma.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+05/05/2026: Mediante la Resolución No. 1786 del 30 de abril de 2026, se adjudicó el Contrato No. CM-004-2026, no obstante, a la fecha no se ha suscrito el contrato correspondiente.
+En cuanto al proceso para la contratación de la interventoría, el día 24 de abril se radicaron en la oficina de subcontratación los estudios previos y demás documentación soporte, para su respectiva revisión y trámite. Actualmente, se encuentra a la espera de la publicación del respectivo proceso contractual.</t>
+  </si>
+  <si>
+    <t>05/05/2026 : El proyecto cuenta con el proceso de contratación de la consultoría No. CM-003-2026 publicado en SECOP II desde el 13 de febrero de 2026; sin embargo, a la fecha aún no se ha iniciado el proceso de contratación de la interventoría,  Se prevee que entre el 08 de mayo y 10 de mayo se aperture el proceso de contratación de la interventoría.</t>
+  </si>
+  <si>
+    <t>05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II. Se encuentra en elaboración de estudios previos por parte de la sectorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: El proyecto se encuentra en ejecución  sin acta de inicio desde junio de 2025, el contrato de obra fue adjudicado y suscrito mediante No de contrato LP-009-2025 el 05 de febrero de 2026. Mediante la resolución 0768 del 23 febrero de 2026, se aperturó el proceso CM-002-2026 para la interventoría, Actualmente se encuentra en proceso de evaluación y observaciones.
+Esta situación está generando una calificación de 0, debido a que no se cuenta con programación del proyecto ni con acta de inicio. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026: Proyecto en estado “Contratado sin acta de inicio”, a la espera de la programación inicial y la suscripción del acta de inicio para pasar a estado “en ejecución”. El contrato fue suscrito el 04 de febrero  de 2026, por lo cual se debe mantener alerta, teniendo en cuenta que se dispone de 30 días para cargar el acta de inicio y la programación, evitando así una calificación de 0 por parte del DNP.
+Conforme a lo informado por la sectorial, se requiere la modificación de una cláusula del convenio, en atención a ciertos requisitos que deben cumplirse previamente a la suscripción del acta de inicio. En consecuencia, se hace necesario la elaboración de un otrosí, el cual se prevé suscribir entre el 7 y el 9 de mayo, con el fin de proceder posteriormente a la firma del acta de inicio.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+05/05/2026: El proyecto ya cuenta con acta de inicio y programación inicial, las cuales serán cargadas en la plataforma Gesproy para su cambio al estado ‘En ejecución’. En consecuencia, el proyecto deja de presentar alerta por falta de acta  inicio.</t>
   </si>
 </sst>
 </file>
@@ -2910,7 +2938,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2955,6 +2983,19 @@
       <sz val="10"/>
       <name val="Roboto"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3037,7 +3078,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -3068,40 +3109,16 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3147,14 +3164,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3172,10 +3182,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3187,13 +3194,22 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3968,13 +3984,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AW58" totalsRowShown="0">
-  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="PARA CIERRE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="49">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -4049,7 +4059,7 @@
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="21">
       <calculatedColumnFormula>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="20"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="CPI"/>
@@ -4096,7 +4106,7 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="VALOR TOTAL" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="FECHA APROBACIÓN PROYECTO" dataDxfId="6"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="5"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS" dataDxfId="4"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS" dataDxfId="4"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO" dataDxfId="1"/>
@@ -4404,13 +4414,9 @@
     <col min="7" max="31" width="25.7109375" customWidth="1"/>
     <col min="32" max="32" width="56.7109375" customWidth="1"/>
     <col min="33" max="33" width="34.28515625" customWidth="1"/>
-    <col min="34" max="34" width="25.7109375" customWidth="1"/>
-    <col min="35" max="44" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="25.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="25.7109375" customWidth="1"/>
-    <col min="48" max="48" width="33" customWidth="1"/>
-    <col min="49" max="49" width="29.28515625" customWidth="1"/>
+    <col min="34" max="47" width="25.7109375" customWidth="1"/>
+    <col min="48" max="48" width="42.28515625" customWidth="1"/>
+    <col min="49" max="49" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
@@ -4614,11 +4620,11 @@
       <c r="AV2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="30" t="s">
-        <v>906</v>
+      <c r="AW2" s="26" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="112.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -4748,11 +4754,11 @@
       <c r="AV3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AW3" s="26" t="s">
-        <v>912</v>
+      <c r="AW3" s="23" t="s">
+        <v>901</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -4882,11 +4888,11 @@
       <c r="AV4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AW4" s="25" t="s">
-        <v>907</v>
+      <c r="AW4" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -5026,11 +5032,11 @@
       <c r="AV5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW5" s="25" t="s">
-        <v>907</v>
+      <c r="AW5" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>80</v>
       </c>
@@ -5172,11 +5178,11 @@
       <c r="AV6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AW6" s="25" t="s">
-        <v>907</v>
+      <c r="AW6" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="141.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -5316,11 +5322,11 @@
       <c r="AV7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AW7" s="25" t="s">
-        <v>908</v>
+      <c r="AW7" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>99</v>
       </c>
@@ -5452,11 +5458,11 @@
       <c r="AV8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AW8" s="26" t="s">
-        <v>912</v>
+      <c r="AW8" s="23" t="s">
+        <v>901</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="156.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -5600,11 +5606,11 @@
       <c r="AV9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AW9" s="25" t="s">
-        <v>907</v>
+      <c r="AW9" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>113</v>
       </c>
@@ -5744,11 +5750,11 @@
       <c r="AV10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW10" s="25" t="s">
-        <v>909</v>
+      <c r="AW10" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -5888,11 +5894,11 @@
       <c r="AV11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW11" s="25" t="s">
-        <v>907</v>
+      <c r="AW11" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>124</v>
       </c>
@@ -6032,11 +6038,11 @@
       <c r="AV12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW12" s="25" t="s">
-        <v>909</v>
+      <c r="AW12" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
@@ -6178,11 +6184,11 @@
       <c r="AV13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AW13" s="25" t="s">
-        <v>910</v>
+      <c r="AW13" s="22" t="s">
+        <v>899</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>142</v>
       </c>
@@ -6322,11 +6328,11 @@
       <c r="AV14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AW14" s="25" t="s">
-        <v>908</v>
+      <c r="AW14" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>149</v>
       </c>
@@ -6468,11 +6474,11 @@
       <c r="AV15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AW15" s="25" t="s">
-        <v>907</v>
+      <c r="AW15" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>155</v>
       </c>
@@ -6612,11 +6618,11 @@
       <c r="AV16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW16" s="25" t="s">
-        <v>909</v>
+      <c r="AW16" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>161</v>
       </c>
@@ -6758,11 +6764,11 @@
       <c r="AV17" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AW17" s="25" t="s">
-        <v>909</v>
+      <c r="AW17" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>169</v>
       </c>
@@ -6904,11 +6910,11 @@
       <c r="AV18" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AW18" s="25" t="s">
-        <v>907</v>
+      <c r="AW18" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>176</v>
       </c>
@@ -7050,11 +7056,11 @@
       <c r="AV19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AW19" s="25" t="s">
-        <v>907</v>
+      <c r="AW19" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>181</v>
       </c>
@@ -7194,11 +7200,11 @@
       <c r="AV20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW20" s="25" t="s">
-        <v>907</v>
+      <c r="AW20" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>186</v>
       </c>
@@ -7340,11 +7346,11 @@
       <c r="AV21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AW21" s="25" t="s">
-        <v>911</v>
+      <c r="AW21" s="22" t="s">
+        <v>900</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>195</v>
       </c>
@@ -7486,8 +7492,8 @@
       <c r="AV22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AW22" s="25" t="s">
-        <v>912</v>
+      <c r="AW22" s="22" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="23" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7622,11 +7628,11 @@
       <c r="AV23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW23" s="25" t="s">
-        <v>908</v>
+      <c r="AW23" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>209</v>
       </c>
@@ -7758,8 +7764,8 @@
       <c r="AV24" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AW24" s="25" t="s">
-        <v>907</v>
+      <c r="AW24" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
     <row r="25" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -7896,11 +7902,11 @@
       <c r="AV25" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW25" s="25" t="s">
-        <v>907</v>
+      <c r="AW25" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>222</v>
       </c>
@@ -8042,11 +8048,11 @@
       <c r="AV26" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="AW26" s="25" t="s">
-        <v>909</v>
+      <c r="AW26" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>229</v>
       </c>
@@ -8186,8 +8192,8 @@
       <c r="AV27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW27" s="25" t="s">
-        <v>912</v>
+      <c r="AW27" s="22" t="s">
+        <v>901</v>
       </c>
     </row>
     <row r="28" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8197,7 +8203,7 @@
       <c r="B28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="27" t="s">
         <v>236</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -8322,11 +8328,11 @@
       <c r="AV28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW28" s="25" t="s">
-        <v>908</v>
+      <c r="AW28" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>239</v>
       </c>
@@ -8466,8 +8472,8 @@
       <c r="AV29" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="AW29" s="25" t="s">
-        <v>909</v>
+      <c r="AW29" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="30" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -8602,11 +8608,11 @@
       <c r="AV30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW30" s="25" t="s">
-        <v>909</v>
+      <c r="AW30" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>250</v>
       </c>
@@ -8746,11 +8752,11 @@
       <c r="AV31" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AW31" s="25" t="s">
-        <v>908</v>
+      <c r="AW31" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>258</v>
       </c>
@@ -8892,11 +8898,11 @@
       <c r="AV32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="AW32" s="25" t="s">
-        <v>908</v>
+      <c r="AW32" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="33" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>266</v>
       </c>
@@ -9038,8 +9044,8 @@
       <c r="AV33" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AW33" s="25" t="s">
-        <v>909</v>
+      <c r="AW33" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="34" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9174,8 +9180,8 @@
       <c r="AV34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW34" s="25" t="s">
-        <v>908</v>
+      <c r="AW34" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
     <row r="35" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -9308,11 +9314,11 @@
       <c r="AV35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW35" s="25" t="s">
-        <v>907</v>
+      <c r="AW35" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="36" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>285</v>
       </c>
@@ -9452,11 +9458,11 @@
       <c r="AV36" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AW36" s="25" t="s">
-        <v>909</v>
+      <c r="AW36" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="37" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>292</v>
       </c>
@@ -9598,11 +9604,11 @@
       <c r="AV37" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AW37" s="25" t="s">
-        <v>907</v>
+      <c r="AW37" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>299</v>
       </c>
@@ -9744,11 +9750,11 @@
       <c r="AV38" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AW38" s="25" t="s">
-        <v>908</v>
+      <c r="AW38" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>307</v>
       </c>
@@ -9888,11 +9894,11 @@
       <c r="AV39" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AW39" s="25" t="s">
-        <v>907</v>
+      <c r="AW39" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="40" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>314</v>
       </c>
@@ -10034,11 +10040,11 @@
       <c r="AV40" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AW40" s="25" t="s">
-        <v>908</v>
+      <c r="AW40" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>320</v>
       </c>
@@ -10180,11 +10186,11 @@
       <c r="AV41" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="AW41" s="25" t="s">
-        <v>909</v>
+      <c r="AW41" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>327</v>
       </c>
@@ -10324,11 +10330,11 @@
       <c r="AV42" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="AW42" s="25" t="s">
-        <v>912</v>
+      <c r="AW42" s="22" t="s">
+        <v>901</v>
       </c>
     </row>
-    <row r="43" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:49" ht="183.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>332</v>
       </c>
@@ -10454,30 +10460,30 @@
         <v/>
       </c>
       <c r="AV43" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="AW43" s="22" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="44" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="AW43" s="25" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="44" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>267</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>68</v>
@@ -10553,10 +10559,10 @@
         <v>46127</v>
       </c>
       <c r="AF44" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="AG44" s="3" t="s">
         <v>344</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>345</v>
       </c>
       <c r="AH44" s="5">
         <v>46122</v>
@@ -10600,30 +10606,30 @@
         <v>36</v>
       </c>
       <c r="AV44" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="AW44" s="22" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="45" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>346</v>
-      </c>
-      <c r="AW44" s="25" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="45" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>347</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>68</v>
@@ -10632,10 +10638,10 @@
         <v>84</v>
       </c>
       <c r="I45" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>353</v>
       </c>
       <c r="K45" s="4">
         <v>1135083847</v>
@@ -10697,10 +10703,10 @@
         <v>46127</v>
       </c>
       <c r="AF45" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="AG45" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="AH45" s="5">
         <v>46126</v>
@@ -10744,42 +10750,42 @@
         <v>60</v>
       </c>
       <c r="AV45" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="AW45" s="22" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="46" spans="1:49" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="AW45" s="25" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="46" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>357</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>212</v>
       </c>
       <c r="F46" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="G46" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K46" s="4">
         <v>2439637568.0900002</v>
@@ -10835,10 +10841,10 @@
         <v>46127</v>
       </c>
       <c r="AF46" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="AG46" s="3" t="s">
         <v>364</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>365</v>
       </c>
       <c r="AH46" s="5">
         <v>46126</v>
@@ -10886,30 +10892,30 @@
         <v/>
       </c>
       <c r="AV46" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="AW46" s="25" t="s">
-        <v>909</v>
+        <v>920</v>
+      </c>
+      <c r="AW46" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>135</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>68</v>
@@ -10918,7 +10924,7 @@
         <v>84</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>95</v>
@@ -10985,10 +10991,10 @@
         <v>46127</v>
       </c>
       <c r="AF47" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG47" s="3" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AH47" s="5">
         <v>46126</v>
@@ -11032,13 +11038,13 @@
         <v>86.4</v>
       </c>
       <c r="AV47" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="AW47" s="25" t="s">
-        <v>909</v>
+        <v>371</v>
+      </c>
+      <c r="AW47" s="22" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="48" spans="1:49" ht="114.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:49" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2025000020006</v>
       </c>
@@ -11046,7 +11052,7 @@
         <v>89</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="3" t="s">
@@ -11148,42 +11154,42 @@
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="AW48" s="25" t="s">
-        <v>907</v>
+        <v>914</v>
+      </c>
+      <c r="AW48" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="49" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>159</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="K49" s="4">
         <v>15884181916</v>
@@ -11243,10 +11249,10 @@
         <v>46127</v>
       </c>
       <c r="AF49" s="3" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG49" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AH49" s="5">
         <v>46127</v>
@@ -11290,30 +11296,30 @@
         <v>40</v>
       </c>
       <c r="AV49" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="AW49" s="25" t="s">
-        <v>907</v>
+        <v>380</v>
+      </c>
+      <c r="AW49" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="50" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>68</v>
@@ -11322,7 +11328,7 @@
         <v>84</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>165</v>
@@ -11387,10 +11393,10 @@
         <v>46127</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AG50" s="3" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AH50" s="5">
         <v>46126</v>
@@ -11434,24 +11440,24 @@
         <v>100</v>
       </c>
       <c r="AV50" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="AW50" s="25" t="s">
-        <v>913</v>
+        <v>387</v>
+      </c>
+      <c r="AW50" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="51" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>89</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>278</v>
@@ -11533,10 +11539,10 @@
         <v>46127</v>
       </c>
       <c r="AF51" s="3" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AG51" s="3" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AH51" s="5">
         <v>46122</v>
@@ -11580,30 +11586,30 @@
         <v>100</v>
       </c>
       <c r="AV51" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="AW51" s="25" t="s">
-        <v>913</v>
+        <v>387</v>
+      </c>
+      <c r="AW51" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="52" spans="1:49" ht="135.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:49" ht="249" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>336</v>
@@ -11663,10 +11669,10 @@
         <v>46127</v>
       </c>
       <c r="AF52" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG52" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AH52" s="5">
         <v>46126</v>
@@ -11713,31 +11719,31 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV52" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="AW52" s="25" t="s">
-        <v>913</v>
+      <c r="AV52" s="30" t="s">
+        <v>915</v>
+      </c>
+      <c r="AW52" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="53" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:49" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>336</v>
@@ -11836,39 +11842,39 @@
         <v/>
       </c>
       <c r="AV53" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="AW53" s="25" t="s">
-        <v>907</v>
+        <v>916</v>
+      </c>
+      <c r="AW53" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="54" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" ht="179.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G54" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="I54" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>95</v>
@@ -11925,10 +11931,10 @@
         <v>46127</v>
       </c>
       <c r="AF54" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="AG54" s="3" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="AH54" s="5">
         <v>46122</v>
@@ -11976,42 +11982,42 @@
         <v/>
       </c>
       <c r="AV54" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="AW54" s="25" t="s">
-        <v>913</v>
+        <v>922</v>
+      </c>
+      <c r="AW54" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="55" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:49" ht="254.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B55" s="12" t="s">
         <v>267</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>270</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="G55" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>362</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="K55" s="4">
         <v>1631281390</v>
@@ -12065,10 +12071,10 @@
         <v>46127</v>
       </c>
       <c r="AF55" s="3" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AG55" s="3" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="AH55" s="5">
         <v>46122</v>
@@ -12115,31 +12121,31 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV55" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="AW55" s="25" t="s">
-        <v>913</v>
+      <c r="AV55" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="AW55" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="56" spans="1:49" ht="199.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:49" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>336</v>
@@ -12147,7 +12153,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K56" s="10">
         <v>2998247290</v>
@@ -12199,10 +12205,10 @@
         <v>46127</v>
       </c>
       <c r="AF56" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG56" s="3" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AH56" s="5">
         <v>46126</v>
@@ -12250,30 +12256,30 @@
         <v/>
       </c>
       <c r="AV56" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="AW56" s="25" t="s">
-        <v>913</v>
+        <v>917</v>
+      </c>
+      <c r="AW56" s="22" t="s">
+        <v>902</v>
       </c>
     </row>
-    <row r="57" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:49" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="12" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>212</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>336</v>
@@ -12281,7 +12287,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K57" s="10">
         <v>4190286255</v>
@@ -12331,7 +12337,7 @@
         <v>46127</v>
       </c>
       <c r="AF57" s="3" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="AG57" s="3"/>
       <c r="AH57" s="5">
@@ -12380,30 +12386,30 @@
         <v/>
       </c>
       <c r="AV57" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="AW57" s="25" t="s">
-        <v>908</v>
+        <v>918</v>
+      </c>
+      <c r="AW57" s="22" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="58" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="29">
+    <row r="58" spans="1:49" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="25">
         <v>2026002700001</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>336</v>
@@ -12411,7 +12417,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="K58" s="10">
         <v>15410127474</v>
@@ -12500,10 +12506,10 @@
         <v/>
       </c>
       <c r="AV58" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="AW58" s="27" t="s">
-        <v>907</v>
+        <v>919</v>
+      </c>
+      <c r="AW58" s="22" t="s">
+        <v>896</v>
       </c>
     </row>
   </sheetData>
@@ -12585,19 +12591,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -12609,10 +12615,10 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>20</v>
@@ -12621,10 +12627,10 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>446</v>
+        <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
@@ -12698,28 +12704,28 @@
     </row>
     <row r="3" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I3" s="4">
         <v>2006938345.6700001</v>
@@ -12737,7 +12743,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="17">
         <v>44326</v>
       </c>
       <c r="O3" s="4">
@@ -12798,33 +12804,33 @@
         <v/>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="4" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I4" s="4">
         <v>1295118639.0699999</v>
@@ -12842,7 +12848,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N4" s="19">
+      <c r="N4" s="17">
         <v>44326</v>
       </c>
       <c r="O4" s="4">
@@ -12903,7 +12909,7 @@
         <v/>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="156" customHeight="1" x14ac:dyDescent="0.25">
@@ -12911,13 +12917,13 @@
         <v>2021000020028</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
@@ -12929,7 +12935,7 @@
         <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I5" s="4">
         <v>3153851580.9099998</v>
@@ -12947,9 +12953,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44568</v>
       </c>
-      <c r="N5" s="19" t="s">
-        <v>904</v>
-      </c>
+      <c r="N5" s="28"/>
       <c r="O5" s="4">
         <v>96.02</v>
       </c>
@@ -13021,28 +13025,28 @@
     </row>
     <row r="6" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="I6" s="4">
         <v>6026477761</v>
@@ -13060,7 +13064,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44624</v>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="17">
         <v>44509</v>
       </c>
       <c r="O6" s="4">
@@ -13129,7 +13133,7 @@
         <v>20</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13137,25 +13141,25 @@
         <v>20221301010208</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I7" s="4">
         <v>1800000000</v>
@@ -13173,7 +13177,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44925</v>
       </c>
-      <c r="N7" s="19">
+      <c r="N7" s="17">
         <v>44930</v>
       </c>
       <c r="O7" s="4">
@@ -13242,21 +13246,21 @@
         <v>20</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>55</v>
@@ -13268,7 +13272,7 @@
         <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I8" s="4">
         <v>1702007732.2</v>
@@ -13286,7 +13290,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45226</v>
       </c>
-      <c r="N8" s="19">
+      <c r="N8" s="17">
         <v>45232</v>
       </c>
       <c r="O8" s="4">
@@ -13347,33 +13351,33 @@
         <v/>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I9" s="4">
         <v>13713002364.719999</v>
@@ -13391,7 +13395,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="17">
         <v>45290</v>
       </c>
       <c r="O9" s="4">
@@ -13456,21 +13460,21 @@
         <v/>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>220</v>
@@ -13482,7 +13486,7 @@
         <v>68</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I10" s="4">
         <v>9056051736.6399994</v>
@@ -13500,7 +13504,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="17">
         <v>45290</v>
       </c>
       <c r="O10" s="4">
@@ -13570,16 +13574,16 @@
     </row>
     <row r="11" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>278</v>
@@ -13591,7 +13595,7 @@
         <v>68</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I11" s="4">
         <v>7862105021</v>
@@ -13609,7 +13613,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45478</v>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="17">
         <v>45485</v>
       </c>
       <c r="O11" s="4">
@@ -13681,16 +13685,16 @@
     </row>
     <row r="12" spans="1:38" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>253</v>
@@ -13702,7 +13706,7 @@
         <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I12" s="4">
         <v>15100656106.639999</v>
@@ -13720,7 +13724,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45475</v>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="17">
         <v>45506</v>
       </c>
       <c r="O12" s="4">
@@ -13789,21 +13793,21 @@
         <v>36</v>
       </c>
       <c r="AL12" s="3" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="13" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>270</v>
@@ -13815,7 +13819,7 @@
         <v>68</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I13" s="4">
         <v>3068416428</v>
@@ -13833,7 +13837,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="17">
         <v>45656</v>
       </c>
       <c r="O13" s="4">
@@ -13906,13 +13910,13 @@
         <v>2024002700193</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>253</v>
@@ -13924,7 +13928,7 @@
         <v>68</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I14" s="4">
         <v>63850574205.629997</v>
@@ -13942,7 +13946,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N14" s="19">
+      <c r="N14" s="17">
         <v>45656</v>
       </c>
       <c r="O14" s="4">
@@ -14014,16 +14018,16 @@
     </row>
     <row r="15" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>278</v>
@@ -14035,7 +14039,7 @@
         <v>68</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I15" s="4">
         <v>11318403530.17</v>
@@ -14053,7 +14057,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45823</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="17">
         <v>45825</v>
       </c>
       <c r="O15" s="4">
@@ -14123,16 +14127,16 @@
     </row>
     <row r="16" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>253</v>
@@ -14141,10 +14145,10 @@
         <v>215</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I16" s="4">
         <v>1903272161</v>
@@ -14162,7 +14166,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45790</v>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="17">
         <v>45803</v>
       </c>
       <c r="O16" s="4">
@@ -14230,16 +14234,16 @@
     </row>
     <row r="17" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>253</v>
@@ -14251,7 +14255,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I17" s="4">
         <v>1484402616</v>
@@ -14263,11 +14267,8 @@
         <v>1884402616</v>
       </c>
       <c r="L17" s="5"/>
-      <c r="M17" s="5">
-        <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
-        <v>1</v>
-      </c>
-      <c r="N17" s="19">
+      <c r="M17" s="5"/>
+      <c r="N17" s="17">
         <v>45803</v>
       </c>
       <c r="O17" s="4">
@@ -14337,28 +14338,28 @@
     </row>
     <row r="18" spans="1:38" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>336</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="I18" s="4">
         <v>627486059.86000001</v>
@@ -14376,8 +14377,8 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>46119</v>
       </c>
-      <c r="N18" s="28" t="s">
-        <v>914</v>
+      <c r="N18" s="24">
+        <v>46119</v>
       </c>
       <c r="O18" s="4">
         <v>0</v>
@@ -14453,94 +14454,188 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41BB839-CD8D-4F7F-BBA8-C26EF6962443}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>880</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>883</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>881</v>
+      </c>
+      <c r="D2" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>882</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="D3" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>886</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>887</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="D4" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>889</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="D5" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>892</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="D6" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>893</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>894</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>887</v>
-      </c>
-      <c r="C1" s="13" t="s">
+      <c r="C8" s="16"/>
+      <c r="D8" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>903</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>904</v>
+      </c>
+      <c r="D9" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>905</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>907</v>
+      </c>
+      <c r="D10" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>906</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>888</v>
       </c>
+      <c r="D11" t="s">
+        <v>912</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>889</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>892</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>890</v>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>908</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>888</v>
+      </c>
+      <c r="D12" t="s">
+        <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>889</v>
-      </c>
-      <c r="B3" s="15" t="s">
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>891</v>
       </c>
-      <c r="C3" s="16" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>895</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>896</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>898</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>899</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>900</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>901</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>900</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>903</v>
+      <c r="B13" s="15" t="s">
+        <v>910</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>909</v>
+      </c>
+      <c r="D13" t="s">
+        <v>912</v>
       </c>
     </row>
   </sheetData>
@@ -14585,19 +14680,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -14612,7 +14707,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -14621,19 +14716,19 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>446</v>
+        <v>22</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14641,13 +14736,13 @@
         <v>2012000020042</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>92</v>
@@ -14659,7 +14754,7 @@
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I3" s="4">
         <v>22526692745</v>
@@ -14670,14 +14765,14 @@
       <c r="K3" s="4">
         <v>22526692745</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="17">
         <v>41201</v>
       </c>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19">
+      <c r="M3" s="17"/>
+      <c r="N3" s="17">
         <v>41829</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="17">
         <v>42072</v>
       </c>
       <c r="P3" s="4">
@@ -14693,13 +14788,13 @@
         <v>2012002700005</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>92</v>
@@ -14710,8 +14805,8 @@
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="22" t="s">
-        <v>453</v>
+      <c r="H4" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I4" s="4">
         <v>924979909</v>
@@ -14722,14 +14817,14 @@
       <c r="K4" s="4">
         <v>954979909</v>
       </c>
-      <c r="L4" s="19">
+      <c r="L4" s="17">
         <v>41191</v>
       </c>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19">
+      <c r="M4" s="17"/>
+      <c r="N4" s="17">
         <v>41304</v>
       </c>
-      <c r="O4" s="19">
+      <c r="O4" s="17">
         <v>41452</v>
       </c>
       <c r="P4" s="4">
@@ -14742,16 +14837,16 @@
     </row>
     <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>92</v>
@@ -14763,7 +14858,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I5" s="4">
         <v>999998309</v>
@@ -14774,14 +14869,14 @@
       <c r="K5" s="4">
         <v>1010998309</v>
       </c>
-      <c r="L5" s="19">
+      <c r="L5" s="17">
         <v>41191</v>
       </c>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19">
+      <c r="M5" s="17"/>
+      <c r="N5" s="17">
         <v>41276</v>
       </c>
-      <c r="O5" s="19">
+      <c r="O5" s="17">
         <v>41355</v>
       </c>
       <c r="P5" s="4">
@@ -14794,16 +14889,16 @@
     </row>
     <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>92</v>
@@ -14815,7 +14910,7 @@
         <v>57</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I6" s="4">
         <v>16567304387</v>
@@ -14826,14 +14921,14 @@
       <c r="K6" s="4">
         <v>16567304387</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>41533</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19">
+      <c r="M6" s="17"/>
+      <c r="N6" s="17">
         <v>41537</v>
       </c>
-      <c r="O6" s="19">
+      <c r="O6" s="17">
         <v>41669</v>
       </c>
       <c r="P6" s="4">
@@ -14846,28 +14941,28 @@
     </row>
     <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="22" t="s">
-        <v>453</v>
+      <c r="H7" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I7" s="4">
         <v>12429000000</v>
@@ -14878,14 +14973,14 @@
       <c r="K7" s="4">
         <v>12588110083</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <v>41907</v>
       </c>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19">
+      <c r="M7" s="17"/>
+      <c r="N7" s="17">
         <v>42821</v>
       </c>
-      <c r="O7" s="19">
+      <c r="O7" s="17">
         <v>42226</v>
       </c>
       <c r="P7" s="4">
@@ -14898,19 +14993,19 @@
     </row>
     <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>60</v>
@@ -14918,8 +15013,8 @@
       <c r="G8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="22" t="s">
-        <v>467</v>
+      <c r="H8" s="19" t="s">
+        <v>458</v>
       </c>
       <c r="I8" s="4">
         <v>14996018261</v>
@@ -14930,14 +15025,14 @@
       <c r="K8" s="4">
         <v>14996018261</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="17">
         <v>41376</v>
       </c>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19">
+      <c r="M8" s="17"/>
+      <c r="N8" s="17">
         <v>41380</v>
       </c>
-      <c r="O8" s="19">
+      <c r="O8" s="17">
         <v>41676</v>
       </c>
       <c r="P8" s="4">
@@ -14950,28 +15045,28 @@
     </row>
     <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="22" t="s">
-        <v>462</v>
+      <c r="H9" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I9" s="4">
         <v>14913362760</v>
@@ -14982,14 +15077,14 @@
       <c r="K9" s="4">
         <v>14913362760</v>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="17">
         <v>41907</v>
       </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19">
+      <c r="M9" s="17"/>
+      <c r="N9" s="17">
         <v>42990</v>
       </c>
-      <c r="O9" s="19">
+      <c r="O9" s="17">
         <v>42023</v>
       </c>
       <c r="P9" s="4">
@@ -15002,28 +15097,28 @@
     </row>
     <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="22" t="s">
-        <v>453</v>
+      <c r="H10" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I10" s="4">
         <v>7037696704</v>
@@ -15034,14 +15129,14 @@
       <c r="K10" s="4">
         <v>7738617014</v>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="17">
         <v>41907</v>
       </c>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19">
+      <c r="M10" s="17"/>
+      <c r="N10" s="17">
         <v>42006</v>
       </c>
-      <c r="O10" s="19">
+      <c r="O10" s="17">
         <v>42060</v>
       </c>
       <c r="P10" s="4">
@@ -15054,16 +15149,16 @@
     </row>
     <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>66</v>
@@ -15075,7 +15170,7 @@
         <v>57</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I11" s="4">
         <v>13800000000</v>
@@ -15086,14 +15181,14 @@
       <c r="K11" s="4">
         <v>15951400000</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="17">
         <v>41789</v>
       </c>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19">
+      <c r="M11" s="17"/>
+      <c r="N11" s="17">
         <v>44936</v>
       </c>
-      <c r="O11" s="19">
+      <c r="O11" s="17">
         <v>42128</v>
       </c>
       <c r="P11" s="4">
@@ -15106,28 +15201,28 @@
     </row>
     <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="22" t="s">
-        <v>453</v>
+      <c r="H12" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I12" s="4">
         <v>16094650077</v>
@@ -15138,14 +15233,14 @@
       <c r="K12" s="4">
         <v>16407417777</v>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="17">
         <v>43389</v>
       </c>
-      <c r="M12" s="19"/>
-      <c r="N12" s="19">
+      <c r="M12" s="17"/>
+      <c r="N12" s="17">
         <v>43495</v>
       </c>
-      <c r="O12" s="19">
+      <c r="O12" s="17">
         <v>43865</v>
       </c>
       <c r="P12" s="4">
@@ -15158,28 +15253,28 @@
     </row>
     <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="I13" s="4">
         <v>54337268559</v>
@@ -15190,14 +15285,14 @@
       <c r="K13" s="4">
         <v>62896276985</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="17">
         <v>43165</v>
       </c>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19">
+      <c r="M13" s="17"/>
+      <c r="N13" s="17">
         <v>43171</v>
       </c>
-      <c r="O13" s="19">
+      <c r="O13" s="17">
         <v>43410</v>
       </c>
       <c r="P13" s="4">
@@ -15210,28 +15305,28 @@
     </row>
     <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>453</v>
+      <c r="H14" s="20" t="s">
+        <v>444</v>
       </c>
       <c r="I14" s="4">
         <v>5261488233</v>
@@ -15242,14 +15337,14 @@
       <c r="K14" s="4">
         <v>5361488233</v>
       </c>
-      <c r="L14" s="19">
+      <c r="L14" s="17">
         <v>43636</v>
       </c>
-      <c r="M14" s="19"/>
-      <c r="N14" s="19">
+      <c r="M14" s="17"/>
+      <c r="N14" s="17">
         <v>43955</v>
       </c>
-      <c r="O14" s="19">
+      <c r="O14" s="17">
         <v>44138</v>
       </c>
       <c r="P14" s="4">
@@ -15262,16 +15357,16 @@
     </row>
     <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>135</v>
@@ -15282,8 +15377,8 @@
       <c r="G15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="22" t="s">
-        <v>453</v>
+      <c r="H15" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I15" s="4">
         <v>8077068482</v>
@@ -15294,14 +15389,14 @@
       <c r="K15" s="4">
         <v>8077068482</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="17">
         <v>43829</v>
       </c>
-      <c r="M15" s="19"/>
-      <c r="N15" s="19">
+      <c r="M15" s="17"/>
+      <c r="N15" s="17">
         <v>43843</v>
       </c>
-      <c r="O15" s="19">
+      <c r="O15" s="17">
         <v>44042</v>
       </c>
       <c r="P15" s="4">
@@ -15314,16 +15409,16 @@
     </row>
     <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>66</v>
@@ -15335,7 +15430,7 @@
         <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I16" s="4">
         <v>7750000000</v>
@@ -15346,14 +15441,14 @@
       <c r="K16" s="4">
         <v>7750000000</v>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="17">
         <v>43781</v>
       </c>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19">
+      <c r="M16" s="17"/>
+      <c r="N16" s="17">
         <v>43809</v>
       </c>
-      <c r="O16" s="19">
+      <c r="O16" s="17">
         <v>43831</v>
       </c>
       <c r="P16" s="4">
@@ -15366,16 +15461,16 @@
     </row>
     <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>66</v>
@@ -15387,7 +15482,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I17" s="4">
         <v>1027100000</v>
@@ -15398,14 +15493,14 @@
       <c r="K17" s="4">
         <v>1127675000</v>
       </c>
-      <c r="L17" s="19">
+      <c r="L17" s="17">
         <v>43781</v>
       </c>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19">
+      <c r="M17" s="17"/>
+      <c r="N17" s="17">
         <v>43948</v>
       </c>
-      <c r="O17" s="19">
+      <c r="O17" s="17">
         <v>44223</v>
       </c>
       <c r="P17" s="4">
@@ -15418,16 +15513,16 @@
     </row>
     <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>66</v>
@@ -15439,7 +15534,7 @@
         <v>68</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I18" s="4">
         <v>9491491960</v>
@@ -15450,14 +15545,14 @@
       <c r="K18" s="4">
         <v>9935241960</v>
       </c>
-      <c r="L18" s="19">
+      <c r="L18" s="17">
         <v>43781</v>
       </c>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19">
+      <c r="M18" s="17"/>
+      <c r="N18" s="17">
         <v>43872</v>
       </c>
-      <c r="O18" s="19">
+      <c r="O18" s="17">
         <v>43979</v>
       </c>
       <c r="P18" s="4">
@@ -15470,16 +15565,16 @@
     </row>
     <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>66</v>
@@ -15491,7 +15586,7 @@
         <v>68</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I19" s="4">
         <v>4024500000</v>
@@ -15502,14 +15597,14 @@
       <c r="K19" s="4">
         <v>4202000000</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="17">
         <v>43781</v>
       </c>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19">
+      <c r="M19" s="17"/>
+      <c r="N19" s="17">
         <v>43812</v>
       </c>
-      <c r="O19" s="19">
+      <c r="O19" s="17">
         <v>43958</v>
       </c>
       <c r="P19" s="4">
@@ -15522,16 +15617,16 @@
     </row>
     <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>66</v>
@@ -15543,7 +15638,7 @@
         <v>68</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I20" s="4">
         <v>20233937500</v>
@@ -15554,14 +15649,14 @@
       <c r="K20" s="4">
         <v>21162064500</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="17">
         <v>43781</v>
       </c>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19">
+      <c r="M20" s="17"/>
+      <c r="N20" s="17">
         <v>43902</v>
       </c>
-      <c r="O20" s="19">
+      <c r="O20" s="17">
         <v>43943</v>
       </c>
       <c r="P20" s="4">
@@ -15574,16 +15669,16 @@
     </row>
     <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>66</v>
@@ -15595,7 +15690,7 @@
         <v>68</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I21" s="4">
         <v>6524500000</v>
@@ -15606,14 +15701,14 @@
       <c r="K21" s="4">
         <v>6524500000</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="17">
         <v>43781</v>
       </c>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19">
+      <c r="M21" s="17"/>
+      <c r="N21" s="17">
         <v>43969</v>
       </c>
-      <c r="O21" s="19">
+      <c r="O21" s="17">
         <v>43949</v>
       </c>
       <c r="P21" s="4">
@@ -15626,16 +15721,16 @@
     </row>
     <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>66</v>
@@ -15647,7 +15742,7 @@
         <v>68</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I22" s="4">
         <v>2500000000</v>
@@ -15658,14 +15753,14 @@
       <c r="K22" s="4">
         <v>2588750000</v>
       </c>
-      <c r="L22" s="19">
+      <c r="L22" s="17">
         <v>43812</v>
       </c>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19">
+      <c r="M22" s="17"/>
+      <c r="N22" s="17">
         <v>43902</v>
       </c>
-      <c r="O22" s="19">
+      <c r="O22" s="17">
         <v>43938</v>
       </c>
       <c r="P22" s="4">
@@ -15678,16 +15773,16 @@
     </row>
     <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>66</v>
@@ -15699,7 +15794,7 @@
         <v>68</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I23" s="4">
         <v>3500000000</v>
@@ -15710,14 +15805,14 @@
       <c r="K23" s="4">
         <v>4154449000</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="17">
         <v>43812</v>
       </c>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19">
+      <c r="M23" s="17"/>
+      <c r="N23" s="17">
         <v>43864</v>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="17">
         <v>44742</v>
       </c>
       <c r="P23" s="4">
@@ -15730,16 +15825,16 @@
     </row>
     <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>66</v>
@@ -15751,7 +15846,7 @@
         <v>68</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I24" s="4">
         <v>3250000000</v>
@@ -15762,14 +15857,14 @@
       <c r="K24" s="4">
         <v>3477139308</v>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="17">
         <v>43798</v>
       </c>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19">
+      <c r="M24" s="17"/>
+      <c r="N24" s="17">
         <v>43882</v>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="17">
         <v>43957</v>
       </c>
       <c r="P24" s="4">
@@ -15782,16 +15877,16 @@
     </row>
     <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>66</v>
@@ -15803,7 +15898,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I25" s="4">
         <v>946000000</v>
@@ -15814,14 +15909,14 @@
       <c r="K25" s="4">
         <v>990375000</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="17">
         <v>43812</v>
       </c>
-      <c r="M25" s="19"/>
-      <c r="N25" s="19">
+      <c r="M25" s="17"/>
+      <c r="N25" s="17">
         <v>44043</v>
       </c>
-      <c r="O25" s="19">
+      <c r="O25" s="17">
         <v>43991</v>
       </c>
       <c r="P25" s="4">
@@ -15834,16 +15929,16 @@
     </row>
     <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>66</v>
@@ -15855,7 +15950,7 @@
         <v>68</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I26" s="4">
         <v>1943625000</v>
@@ -15866,14 +15961,14 @@
       <c r="K26" s="4">
         <v>2032375000</v>
       </c>
-      <c r="L26" s="19">
+      <c r="L26" s="17">
         <v>43830</v>
       </c>
-      <c r="M26" s="19"/>
-      <c r="N26" s="19">
+      <c r="M26" s="17"/>
+      <c r="N26" s="17">
         <v>44025</v>
       </c>
-      <c r="O26" s="19">
+      <c r="O26" s="17">
         <v>44046</v>
       </c>
       <c r="P26" s="4">
@@ -15886,16 +15981,16 @@
     </row>
     <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>66</v>
@@ -15907,7 +16002,7 @@
         <v>68</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I27" s="4">
         <v>1999999962.27</v>
@@ -15918,14 +16013,14 @@
       <c r="K27" s="4">
         <v>2667064893.9299998</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="17">
         <v>44111</v>
       </c>
-      <c r="M27" s="19"/>
-      <c r="N27" s="19">
+      <c r="M27" s="17"/>
+      <c r="N27" s="17">
         <v>44319</v>
       </c>
-      <c r="O27" s="19">
+      <c r="O27" s="17">
         <v>44448</v>
       </c>
       <c r="P27" s="4">
@@ -15938,28 +16033,28 @@
     </row>
     <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="22" t="s">
-        <v>453</v>
+      <c r="H28" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I28" s="4">
         <v>729826686</v>
@@ -15970,14 +16065,14 @@
       <c r="K28" s="4">
         <v>1195561547</v>
       </c>
-      <c r="L28" s="19">
+      <c r="L28" s="17">
         <v>43825</v>
       </c>
-      <c r="M28" s="19"/>
-      <c r="N28" s="19">
+      <c r="M28" s="17"/>
+      <c r="N28" s="17">
         <v>43875</v>
       </c>
-      <c r="O28" s="19">
+      <c r="O28" s="17">
         <v>44074</v>
       </c>
       <c r="P28" s="4">
@@ -15990,28 +16085,28 @@
     </row>
     <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>253</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="22" t="s">
-        <v>453</v>
+      <c r="H29" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I29" s="4">
         <v>37141732473</v>
@@ -16022,14 +16117,14 @@
       <c r="K29" s="4">
         <v>37141732473</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="17">
         <v>43812</v>
       </c>
-      <c r="M29" s="19"/>
-      <c r="N29" s="19">
+      <c r="M29" s="17"/>
+      <c r="N29" s="17">
         <v>43817</v>
       </c>
-      <c r="O29" s="19">
+      <c r="O29" s="17">
         <v>44228</v>
       </c>
       <c r="P29" s="4">
@@ -16042,16 +16137,16 @@
     </row>
     <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>92</v>
@@ -16062,8 +16157,8 @@
       <c r="G30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="23" t="s">
-        <v>462</v>
+      <c r="H30" s="20" t="s">
+        <v>453</v>
       </c>
       <c r="I30" s="4">
         <v>22507978719</v>
@@ -16074,14 +16169,14 @@
       <c r="K30" s="4">
         <v>22507978719</v>
       </c>
-      <c r="L30" s="19">
+      <c r="L30" s="17">
         <v>44536</v>
       </c>
-      <c r="M30" s="19"/>
-      <c r="N30" s="19">
+      <c r="M30" s="17"/>
+      <c r="N30" s="17">
         <v>44683</v>
       </c>
-      <c r="O30" s="19">
+      <c r="O30" s="17">
         <v>44837</v>
       </c>
       <c r="P30" s="4">
@@ -16094,28 +16189,28 @@
     </row>
     <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I31" s="4">
         <v>38700180208.470001</v>
@@ -16126,14 +16221,14 @@
       <c r="K31" s="4">
         <v>38936180208.470001</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="17">
         <v>44195</v>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19">
+      <c r="M31" s="17"/>
+      <c r="N31" s="17">
         <v>44952</v>
       </c>
-      <c r="O31" s="19">
+      <c r="O31" s="17">
         <v>44595</v>
       </c>
       <c r="P31" s="4">
@@ -16146,16 +16241,16 @@
     </row>
     <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>92</v>
@@ -16166,8 +16261,8 @@
       <c r="G32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="22" t="s">
-        <v>453</v>
+      <c r="H32" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I32" s="4">
         <v>75409582200</v>
@@ -16178,14 +16273,14 @@
       <c r="K32" s="4">
         <v>75409582200</v>
       </c>
-      <c r="L32" s="19">
+      <c r="L32" s="17">
         <v>44195</v>
       </c>
-      <c r="M32" s="19"/>
-      <c r="N32" s="19">
+      <c r="M32" s="17"/>
+      <c r="N32" s="17">
         <v>44326</v>
       </c>
-      <c r="O32" s="19">
+      <c r="O32" s="17">
         <v>44445</v>
       </c>
       <c r="P32" s="4">
@@ -16198,16 +16293,16 @@
     </row>
     <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>66</v>
@@ -16219,7 +16314,7 @@
         <v>57</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I33" s="4">
         <v>1998000000</v>
@@ -16230,14 +16325,14 @@
       <c r="K33" s="4">
         <v>2414100000</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="17">
         <v>43950</v>
       </c>
-      <c r="M33" s="19"/>
-      <c r="N33" s="19">
+      <c r="M33" s="17"/>
+      <c r="N33" s="17">
         <v>44001</v>
       </c>
-      <c r="O33" s="19">
+      <c r="O33" s="17">
         <v>44133</v>
       </c>
       <c r="P33" s="4">
@@ -16250,16 +16345,16 @@
     </row>
     <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>66</v>
@@ -16271,7 +16366,7 @@
         <v>57</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I34" s="4">
         <v>1999306318</v>
@@ -16282,14 +16377,14 @@
       <c r="K34" s="4">
         <v>3490315624.7199998</v>
       </c>
-      <c r="L34" s="19">
+      <c r="L34" s="17">
         <v>43924</v>
       </c>
-      <c r="M34" s="19"/>
-      <c r="N34" s="19">
+      <c r="M34" s="17"/>
+      <c r="N34" s="17">
         <v>44001</v>
       </c>
-      <c r="O34" s="19">
+      <c r="O34" s="17">
         <v>44118</v>
       </c>
       <c r="P34" s="4">
@@ -16302,16 +16397,16 @@
     </row>
     <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>66</v>
@@ -16323,7 +16418,7 @@
         <v>207</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I35" s="4">
         <v>1999910691</v>
@@ -16334,14 +16429,14 @@
       <c r="K35" s="4">
         <v>3839181953</v>
       </c>
-      <c r="L35" s="19">
+      <c r="L35" s="17">
         <v>44078</v>
       </c>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19">
+      <c r="M35" s="17"/>
+      <c r="N35" s="17">
         <v>45385</v>
       </c>
-      <c r="O35" s="19">
+      <c r="O35" s="17">
         <v>44252</v>
       </c>
       <c r="P35" s="4">
@@ -16354,16 +16449,16 @@
     </row>
     <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>66</v>
@@ -16375,7 +16470,7 @@
         <v>68</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I36" s="4">
         <v>1999433630</v>
@@ -16386,14 +16481,14 @@
       <c r="K36" s="4">
         <v>2930484800</v>
       </c>
-      <c r="L36" s="19">
+      <c r="L36" s="17">
         <v>43924</v>
       </c>
-      <c r="M36" s="19"/>
-      <c r="N36" s="19">
+      <c r="M36" s="17"/>
+      <c r="N36" s="17">
         <v>44106</v>
       </c>
-      <c r="O36" s="19">
+      <c r="O36" s="17">
         <v>44106</v>
       </c>
       <c r="P36" s="4">
@@ -16406,16 +16501,16 @@
     </row>
     <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>66</v>
@@ -16427,7 +16522,7 @@
         <v>68</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I37" s="4">
         <v>1999976897</v>
@@ -16438,14 +16533,14 @@
       <c r="K37" s="4">
         <v>2612747413</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="17">
         <v>44078</v>
       </c>
-      <c r="M37" s="19"/>
-      <c r="N37" s="19">
+      <c r="M37" s="17"/>
+      <c r="N37" s="17">
         <v>44179</v>
       </c>
-      <c r="O37" s="19">
+      <c r="O37" s="17">
         <v>44229</v>
       </c>
       <c r="P37" s="4">
@@ -16458,16 +16553,16 @@
     </row>
     <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>66</v>
@@ -16479,7 +16574,7 @@
         <v>57</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I38" s="4">
         <v>1272365336</v>
@@ -16490,14 +16585,12 @@
       <c r="K38" s="4">
         <v>1915671336</v>
       </c>
-      <c r="L38" s="19">
+      <c r="L38" s="17">
         <v>44078</v>
       </c>
-      <c r="M38" s="19"/>
-      <c r="N38" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="O38" s="19">
+      <c r="M38" s="17"/>
+      <c r="N38" s="29"/>
+      <c r="O38" s="17">
         <v>44421</v>
       </c>
       <c r="P38" s="4">
@@ -16510,16 +16603,16 @@
     </row>
     <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>66</v>
@@ -16531,7 +16624,7 @@
         <v>68</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I39" s="4">
         <v>1999833255</v>
@@ -16542,14 +16635,14 @@
       <c r="K39" s="4">
         <v>2948047175</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="17">
         <v>44078</v>
       </c>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19">
+      <c r="M39" s="17"/>
+      <c r="N39" s="17">
         <v>44113</v>
       </c>
-      <c r="O39" s="19">
+      <c r="O39" s="17">
         <v>44408</v>
       </c>
       <c r="P39" s="4">
@@ -16562,16 +16655,16 @@
     </row>
     <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>66</v>
@@ -16583,7 +16676,7 @@
         <v>57</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I40" s="4">
         <v>6559568533</v>
@@ -16594,14 +16687,14 @@
       <c r="K40" s="4">
         <v>6848145520</v>
       </c>
-      <c r="L40" s="19">
+      <c r="L40" s="17">
         <v>44159</v>
       </c>
-      <c r="M40" s="19"/>
-      <c r="N40" s="19">
+      <c r="M40" s="17"/>
+      <c r="N40" s="17">
         <v>44337</v>
       </c>
-      <c r="O40" s="19">
+      <c r="O40" s="17">
         <v>44410</v>
       </c>
       <c r="P40" s="4">
@@ -16614,16 +16707,16 @@
     </row>
     <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>66</v>
@@ -16635,7 +16728,7 @@
         <v>68</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I41" s="4">
         <v>1998890586.73</v>
@@ -16646,14 +16739,14 @@
       <c r="K41" s="4">
         <v>2898886012.6100001</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="17">
         <v>44078</v>
       </c>
-      <c r="M41" s="19"/>
-      <c r="N41" s="19">
+      <c r="M41" s="17"/>
+      <c r="N41" s="17">
         <v>44386</v>
       </c>
-      <c r="O41" s="19">
+      <c r="O41" s="17">
         <v>44335</v>
       </c>
       <c r="P41" s="4">
@@ -16666,16 +16759,16 @@
     </row>
     <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>66</v>
@@ -16687,7 +16780,7 @@
         <v>207</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I42" s="4">
         <v>5347795060</v>
@@ -16698,14 +16791,14 @@
       <c r="K42" s="4">
         <v>6581633763</v>
       </c>
-      <c r="L42" s="19">
+      <c r="L42" s="17">
         <v>43966</v>
       </c>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19">
+      <c r="M42" s="17"/>
+      <c r="N42" s="17">
         <v>43978</v>
       </c>
-      <c r="O42" s="19">
+      <c r="O42" s="17">
         <v>44097</v>
       </c>
       <c r="P42" s="4">
@@ -16717,17 +16810,17 @@
       <c r="R42" s="3"/>
     </row>
     <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>670</v>
+      <c r="A43" s="18" t="s">
+        <v>661</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>66</v>
@@ -16739,7 +16832,7 @@
         <v>68</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I43" s="4">
         <v>1965295196.9400001</v>
@@ -16750,12 +16843,12 @@
       <c r="K43" s="4">
         <v>4131804023.6700001</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="17">
         <v>44078</v>
       </c>
-      <c r="M43" s="19"/>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19">
+      <c r="M43" s="17"/>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17">
         <v>44421</v>
       </c>
       <c r="P43" s="4">
@@ -16768,16 +16861,16 @@
     </row>
     <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>66</v>
@@ -16789,7 +16882,7 @@
         <v>68</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I44" s="4">
         <v>8764697664</v>
@@ -16800,14 +16893,14 @@
       <c r="K44" s="4">
         <v>10308364564</v>
       </c>
-      <c r="L44" s="19">
+      <c r="L44" s="17">
         <v>44432</v>
       </c>
-      <c r="M44" s="19"/>
-      <c r="N44" s="19">
+      <c r="M44" s="17"/>
+      <c r="N44" s="17">
         <v>44480</v>
       </c>
-      <c r="O44" s="19">
+      <c r="O44" s="17">
         <v>44502</v>
       </c>
       <c r="P44" s="4">
@@ -16820,16 +16913,16 @@
     </row>
     <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>66</v>
@@ -16841,7 +16934,7 @@
         <v>57</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I45" s="4">
         <v>1349000868</v>
@@ -16852,14 +16945,14 @@
       <c r="K45" s="4">
         <v>1409240868</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="17">
         <v>44111</v>
       </c>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19">
+      <c r="M45" s="17"/>
+      <c r="N45" s="17">
         <v>44568</v>
       </c>
-      <c r="O45" s="19">
+      <c r="O45" s="17">
         <v>44594</v>
       </c>
       <c r="P45" s="4">
@@ -16872,16 +16965,16 @@
     </row>
     <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>66</v>
@@ -16893,7 +16986,7 @@
         <v>57</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I46" s="4">
         <v>3106000000</v>
@@ -16904,14 +16997,14 @@
       <c r="K46" s="4">
         <v>3156000000</v>
       </c>
-      <c r="L46" s="19">
+      <c r="L46" s="17">
         <v>44159</v>
       </c>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19">
+      <c r="M46" s="17"/>
+      <c r="N46" s="17">
         <v>44235</v>
       </c>
-      <c r="O46" s="19">
+      <c r="O46" s="17">
         <v>44327</v>
       </c>
       <c r="P46" s="4">
@@ -16924,16 +17017,16 @@
     </row>
     <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>66</v>
@@ -16945,7 +17038,7 @@
         <v>57</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I47" s="4">
         <v>8995267958.5699997</v>
@@ -16956,14 +17049,14 @@
       <c r="K47" s="4">
         <v>9177414454.0599995</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="17">
         <v>44159</v>
       </c>
-      <c r="M47" s="19"/>
-      <c r="N47" s="19">
+      <c r="M47" s="17"/>
+      <c r="N47" s="17">
         <v>44263</v>
       </c>
-      <c r="O47" s="19">
+      <c r="O47" s="17">
         <v>44365</v>
       </c>
       <c r="P47" s="4">
@@ -16976,16 +17069,16 @@
     </row>
     <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>66</v>
@@ -16997,7 +17090,7 @@
         <v>68</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I48" s="4">
         <v>6750000000</v>
@@ -17008,14 +17101,14 @@
       <c r="K48" s="4">
         <v>6920233499</v>
       </c>
-      <c r="L48" s="19">
+      <c r="L48" s="17">
         <v>44330</v>
       </c>
-      <c r="M48" s="19"/>
-      <c r="N48" s="19">
+      <c r="M48" s="17"/>
+      <c r="N48" s="17">
         <v>44362</v>
       </c>
-      <c r="O48" s="19">
+      <c r="O48" s="17">
         <v>44404</v>
       </c>
       <c r="P48" s="4">
@@ -17028,16 +17121,16 @@
     </row>
     <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>66</v>
@@ -17049,7 +17142,7 @@
         <v>68</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I49" s="4">
         <v>1998157618.8800001</v>
@@ -17060,14 +17153,14 @@
       <c r="K49" s="4">
         <v>2467892722.71</v>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="17">
         <v>44159</v>
       </c>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19">
+      <c r="M49" s="17"/>
+      <c r="N49" s="17">
         <v>44259</v>
       </c>
-      <c r="O49" s="19">
+      <c r="O49" s="17">
         <v>44567</v>
       </c>
       <c r="P49" s="4">
@@ -17080,16 +17173,16 @@
     </row>
     <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>66</v>
@@ -17101,7 +17194,7 @@
         <v>68</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I50" s="4">
         <v>2000000000</v>
@@ -17112,14 +17205,14 @@
       <c r="K50" s="4">
         <v>2474185221</v>
       </c>
-      <c r="L50" s="19">
+      <c r="L50" s="17">
         <v>44159</v>
       </c>
-      <c r="M50" s="19"/>
-      <c r="N50" s="19">
+      <c r="M50" s="17"/>
+      <c r="N50" s="17">
         <v>44246</v>
       </c>
-      <c r="O50" s="19">
+      <c r="O50" s="17">
         <v>44337</v>
       </c>
       <c r="P50" s="4">
@@ -17132,16 +17225,16 @@
     </row>
     <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>66</v>
@@ -17153,7 +17246,7 @@
         <v>68</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I51" s="4">
         <v>5335769261</v>
@@ -17164,14 +17257,12 @@
       <c r="K51" s="4">
         <v>5913070114</v>
       </c>
-      <c r="L51" s="19">
+      <c r="L51" s="17">
         <v>44348</v>
       </c>
-      <c r="M51" s="19"/>
-      <c r="N51" s="20" t="s">
-        <v>904</v>
-      </c>
-      <c r="O51" s="19">
+      <c r="M51" s="17"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="17">
         <v>44427</v>
       </c>
       <c r="P51" s="4">
@@ -17184,16 +17275,16 @@
     </row>
     <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>66</v>
@@ -17205,7 +17296,7 @@
         <v>68</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I52" s="4">
         <v>4940449374</v>
@@ -17216,14 +17307,14 @@
       <c r="K52" s="4">
         <v>5203930460</v>
       </c>
-      <c r="L52" s="19">
+      <c r="L52" s="17">
         <v>44432</v>
       </c>
-      <c r="M52" s="19"/>
-      <c r="N52" s="19">
+      <c r="M52" s="17"/>
+      <c r="N52" s="17">
         <v>44480</v>
       </c>
-      <c r="O52" s="19">
+      <c r="O52" s="17">
         <v>44517</v>
       </c>
       <c r="P52" s="4">
@@ -17236,16 +17327,16 @@
     </row>
     <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>66</v>
@@ -17257,7 +17348,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I53" s="4">
         <v>1999924866</v>
@@ -17268,14 +17359,14 @@
       <c r="K53" s="4">
         <v>3559208215</v>
       </c>
-      <c r="L53" s="19">
+      <c r="L53" s="17">
         <v>44159</v>
       </c>
-      <c r="M53" s="19"/>
-      <c r="N53" s="19">
+      <c r="M53" s="17"/>
+      <c r="N53" s="17">
         <v>44246</v>
       </c>
-      <c r="O53" s="19">
+      <c r="O53" s="17">
         <v>44341</v>
       </c>
       <c r="P53" s="4">
@@ -17288,16 +17379,16 @@
     </row>
     <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>66</v>
@@ -17309,7 +17400,7 @@
         <v>68</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I54" s="4">
         <v>3591118773</v>
@@ -17320,14 +17411,14 @@
       <c r="K54" s="4">
         <v>3768618773</v>
       </c>
-      <c r="L54" s="19">
+      <c r="L54" s="17">
         <v>44330</v>
       </c>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19">
+      <c r="M54" s="17"/>
+      <c r="N54" s="17">
         <v>44393</v>
       </c>
-      <c r="O54" s="19">
+      <c r="O54" s="17">
         <v>44418</v>
       </c>
       <c r="P54" s="4">
@@ -17340,16 +17431,16 @@
     </row>
     <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>66</v>
@@ -17361,7 +17452,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I55" s="4">
         <v>2000000000</v>
@@ -17372,14 +17463,14 @@
       <c r="K55" s="4">
         <v>3560969376</v>
       </c>
-      <c r="L55" s="19">
+      <c r="L55" s="17">
         <v>44159</v>
       </c>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19">
+      <c r="M55" s="17"/>
+      <c r="N55" s="17">
         <v>44246</v>
       </c>
-      <c r="O55" s="19">
+      <c r="O55" s="17">
         <v>44337</v>
       </c>
       <c r="P55" s="4">
@@ -17392,16 +17483,16 @@
     </row>
     <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>66</v>
@@ -17413,7 +17504,7 @@
         <v>68</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I56" s="4">
         <v>1999112638.9200001</v>
@@ -17424,14 +17515,14 @@
       <c r="K56" s="4">
         <v>2856350066.9200001</v>
       </c>
-      <c r="L56" s="19">
+      <c r="L56" s="17">
         <v>44159</v>
       </c>
-      <c r="M56" s="19"/>
-      <c r="N56" s="19">
+      <c r="M56" s="17"/>
+      <c r="N56" s="17">
         <v>44259</v>
       </c>
-      <c r="O56" s="19">
+      <c r="O56" s="17">
         <v>44474</v>
       </c>
       <c r="P56" s="4">
@@ -17444,16 +17535,16 @@
     </row>
     <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>66</v>
@@ -17465,7 +17556,7 @@
         <v>68</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I57" s="4">
         <v>7500000000</v>
@@ -17476,14 +17567,14 @@
       <c r="K57" s="4">
         <v>7500000000</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="17">
         <v>44348</v>
       </c>
-      <c r="M57" s="19"/>
-      <c r="N57" s="19">
+      <c r="M57" s="17"/>
+      <c r="N57" s="17">
         <v>44379</v>
       </c>
-      <c r="O57" s="19">
+      <c r="O57" s="17">
         <v>44407</v>
       </c>
       <c r="P57" s="4">
@@ -17496,16 +17587,16 @@
     </row>
     <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>66</v>
@@ -17517,7 +17608,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I58" s="4">
         <v>1999803848</v>
@@ -17528,14 +17619,14 @@
       <c r="K58" s="4">
         <v>3394230296</v>
       </c>
-      <c r="L58" s="19">
+      <c r="L58" s="17">
         <v>44159</v>
       </c>
-      <c r="M58" s="19"/>
-      <c r="N58" s="19">
+      <c r="M58" s="17"/>
+      <c r="N58" s="17">
         <v>44320</v>
       </c>
-      <c r="O58" s="19">
+      <c r="O58" s="17">
         <v>44467</v>
       </c>
       <c r="P58" s="4">
@@ -17548,16 +17639,16 @@
     </row>
     <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>66</v>
@@ -17569,7 +17660,7 @@
         <v>68</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I59" s="4">
         <v>1738785560</v>
@@ -17580,14 +17671,14 @@
       <c r="K59" s="4">
         <v>2346358031</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="17">
         <v>44159</v>
       </c>
-      <c r="M59" s="19"/>
-      <c r="N59" s="19">
+      <c r="M59" s="17"/>
+      <c r="N59" s="17">
         <v>44309</v>
       </c>
-      <c r="O59" s="19">
+      <c r="O59" s="17">
         <v>44337</v>
       </c>
       <c r="P59" s="4">
@@ -17600,16 +17691,16 @@
     </row>
     <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>66</v>
@@ -17621,7 +17712,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I60" s="4">
         <v>1999000000</v>
@@ -17632,14 +17723,14 @@
       <c r="K60" s="4">
         <v>2511000000</v>
       </c>
-      <c r="L60" s="19">
+      <c r="L60" s="17">
         <v>44159</v>
       </c>
-      <c r="M60" s="19"/>
-      <c r="N60" s="19">
+      <c r="M60" s="17"/>
+      <c r="N60" s="17">
         <v>44246</v>
       </c>
-      <c r="O60" s="19">
+      <c r="O60" s="17">
         <v>44340</v>
       </c>
       <c r="P60" s="4">
@@ -17652,16 +17743,16 @@
     </row>
     <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>66</v>
@@ -17673,7 +17764,7 @@
         <v>68</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I61" s="4">
         <v>1775630700</v>
@@ -17684,14 +17775,14 @@
       <c r="K61" s="4">
         <v>1894532100</v>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="17">
         <v>44368</v>
       </c>
-      <c r="M61" s="19"/>
-      <c r="N61" s="19">
+      <c r="M61" s="17"/>
+      <c r="N61" s="17">
         <v>44924</v>
       </c>
-      <c r="O61" s="19">
+      <c r="O61" s="17">
         <v>44456</v>
       </c>
       <c r="P61" s="4">
@@ -17704,16 +17795,16 @@
     </row>
     <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>66</v>
@@ -17725,7 +17816,7 @@
         <v>68</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I62" s="4">
         <v>750000000</v>
@@ -17736,14 +17827,14 @@
       <c r="K62" s="4">
         <v>918904760</v>
       </c>
-      <c r="L62" s="19">
+      <c r="L62" s="17">
         <v>44377</v>
       </c>
-      <c r="M62" s="19"/>
-      <c r="N62" s="19">
+      <c r="M62" s="17"/>
+      <c r="N62" s="17">
         <v>44440</v>
       </c>
-      <c r="O62" s="19">
+      <c r="O62" s="17">
         <v>44589</v>
       </c>
       <c r="P62" s="4">
@@ -17756,16 +17847,16 @@
     </row>
     <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>66</v>
@@ -17777,7 +17868,7 @@
         <v>68</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I63" s="4">
         <v>2828005287</v>
@@ -17788,14 +17879,14 @@
       <c r="K63" s="4">
         <v>3069617150</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="17">
         <v>44348</v>
       </c>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19">
+      <c r="M63" s="17"/>
+      <c r="N63" s="17">
         <v>44924</v>
       </c>
-      <c r="O63" s="19">
+      <c r="O63" s="17">
         <v>44410</v>
       </c>
       <c r="P63" s="4">
@@ -17808,28 +17899,28 @@
     </row>
     <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H64" s="22" t="s">
-        <v>467</v>
+      <c r="H64" s="19" t="s">
+        <v>458</v>
       </c>
       <c r="I64" s="4">
         <v>69047758069</v>
@@ -17840,14 +17931,14 @@
       <c r="K64" s="4">
         <v>69047758069</v>
       </c>
-      <c r="L64" s="19">
+      <c r="L64" s="17">
         <v>44551</v>
       </c>
-      <c r="M64" s="19"/>
-      <c r="N64" s="19">
+      <c r="M64" s="17"/>
+      <c r="N64" s="17">
         <v>44652</v>
       </c>
-      <c r="O64" s="19">
+      <c r="O64" s="17">
         <v>44810</v>
       </c>
       <c r="P64" s="4">
@@ -17860,16 +17951,16 @@
     </row>
     <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>66</v>
@@ -17881,7 +17972,7 @@
         <v>68</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I65" s="4">
         <v>17635937500</v>
@@ -17892,14 +17983,14 @@
       <c r="K65" s="4">
         <v>18418143500</v>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="17">
         <v>44330</v>
       </c>
-      <c r="M65" s="19"/>
-      <c r="N65" s="19">
+      <c r="M65" s="17"/>
+      <c r="N65" s="17">
         <v>44365</v>
       </c>
-      <c r="O65" s="19">
+      <c r="O65" s="17">
         <v>44438</v>
       </c>
       <c r="P65" s="4">
@@ -17912,16 +18003,16 @@
     </row>
     <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>66</v>
@@ -17933,7 +18024,7 @@
         <v>68</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I66" s="4">
         <v>1309600000</v>
@@ -17944,14 +18035,14 @@
       <c r="K66" s="4">
         <v>1519950000</v>
       </c>
-      <c r="L66" s="19">
+      <c r="L66" s="17">
         <v>44348</v>
       </c>
-      <c r="M66" s="19"/>
-      <c r="N66" s="19">
+      <c r="M66" s="17"/>
+      <c r="N66" s="17">
         <v>44924</v>
       </c>
-      <c r="O66" s="19">
+      <c r="O66" s="17">
         <v>44466</v>
       </c>
       <c r="P66" s="4">
@@ -17964,16 +18055,16 @@
     </row>
     <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>66</v>
@@ -17985,7 +18076,7 @@
         <v>68</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I67" s="4">
         <v>2750000000</v>
@@ -17996,14 +18087,14 @@
       <c r="K67" s="4">
         <v>2775000000</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="17">
         <v>44384</v>
       </c>
-      <c r="M67" s="19"/>
-      <c r="N67" s="19">
+      <c r="M67" s="17"/>
+      <c r="N67" s="17">
         <v>44429</v>
       </c>
-      <c r="O67" s="19">
+      <c r="O67" s="17">
         <v>44530</v>
       </c>
       <c r="P67" s="4">
@@ -18016,16 +18107,16 @@
     </row>
     <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>66</v>
@@ -18037,7 +18128,7 @@
         <v>68</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I68" s="4">
         <v>1500000000</v>
@@ -18048,14 +18139,14 @@
       <c r="K68" s="4">
         <v>1853734000</v>
       </c>
-      <c r="L68" s="19">
+      <c r="L68" s="17">
         <v>44368</v>
       </c>
-      <c r="M68" s="19"/>
-      <c r="N68" s="19">
+      <c r="M68" s="17"/>
+      <c r="N68" s="17">
         <v>44368</v>
       </c>
-      <c r="O68" s="19">
+      <c r="O68" s="17">
         <v>44433</v>
       </c>
       <c r="P68" s="4">
@@ -18068,16 +18159,16 @@
     </row>
     <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>66</v>
@@ -18089,7 +18180,7 @@
         <v>68</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I69" s="4">
         <v>1411798728</v>
@@ -18100,14 +18191,14 @@
       <c r="K69" s="4">
         <v>1532348536</v>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="17">
         <v>44368</v>
       </c>
-      <c r="M69" s="19"/>
-      <c r="N69" s="19">
+      <c r="M69" s="17"/>
+      <c r="N69" s="17">
         <v>44925</v>
       </c>
-      <c r="O69" s="19">
+      <c r="O69" s="17">
         <v>44407</v>
       </c>
       <c r="P69" s="4">
@@ -18120,16 +18211,16 @@
     </row>
     <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>66</v>
@@ -18141,7 +18232,7 @@
         <v>68</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I70" s="4">
         <v>1999997728</v>
@@ -18152,14 +18243,14 @@
       <c r="K70" s="4">
         <v>2663232448</v>
       </c>
-      <c r="L70" s="19">
+      <c r="L70" s="17">
         <v>44536</v>
       </c>
-      <c r="M70" s="19"/>
-      <c r="N70" s="19">
+      <c r="M70" s="17"/>
+      <c r="N70" s="17">
         <v>44533</v>
       </c>
-      <c r="O70" s="19">
+      <c r="O70" s="17">
         <v>44713</v>
       </c>
       <c r="P70" s="4">
@@ -18172,16 +18263,16 @@
     </row>
     <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>66</v>
@@ -18193,7 +18284,7 @@
         <v>68</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I71" s="4">
         <v>1999667231.96</v>
@@ -18204,14 +18295,14 @@
       <c r="K71" s="4">
         <v>3035821023.1599998</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="17">
         <v>44537</v>
       </c>
-      <c r="M71" s="19"/>
-      <c r="N71" s="19">
+      <c r="M71" s="17"/>
+      <c r="N71" s="17">
         <v>44606</v>
       </c>
-      <c r="O71" s="19">
+      <c r="O71" s="17">
         <v>44721</v>
       </c>
       <c r="P71" s="4">
@@ -18224,16 +18315,16 @@
     </row>
     <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>66</v>
@@ -18245,7 +18336,7 @@
         <v>207</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="I72" s="4">
         <v>2000000000</v>
@@ -18256,14 +18347,14 @@
       <c r="K72" s="4">
         <v>2896725569</v>
       </c>
-      <c r="L72" s="19">
+      <c r="L72" s="17">
         <v>44537</v>
       </c>
-      <c r="M72" s="19"/>
-      <c r="N72" s="19">
+      <c r="M72" s="17"/>
+      <c r="N72" s="17">
         <v>44606</v>
       </c>
-      <c r="O72" s="19">
+      <c r="O72" s="17">
         <v>44740</v>
       </c>
       <c r="P72" s="4">
@@ -18276,16 +18367,16 @@
     </row>
     <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>66</v>
@@ -18297,7 +18388,7 @@
         <v>68</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I73" s="4">
         <v>1953855779</v>
@@ -18308,14 +18399,14 @@
       <c r="K73" s="4">
         <v>2459776116</v>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="17">
         <v>44537</v>
       </c>
-      <c r="M73" s="19"/>
-      <c r="N73" s="19">
+      <c r="M73" s="17"/>
+      <c r="N73" s="17">
         <v>44606</v>
       </c>
-      <c r="O73" s="19">
+      <c r="O73" s="17">
         <v>44713</v>
       </c>
       <c r="P73" s="4">
@@ -18328,16 +18419,16 @@
     </row>
     <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>66</v>
@@ -18349,7 +18440,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="I74" s="4">
         <v>4351936180</v>
@@ -18360,14 +18451,14 @@
       <c r="K74" s="4">
         <v>4451936180</v>
       </c>
-      <c r="L74" s="19">
+      <c r="L74" s="17">
         <v>44552</v>
       </c>
-      <c r="M74" s="19"/>
-      <c r="N74" s="19">
+      <c r="M74" s="17"/>
+      <c r="N74" s="17">
         <v>44560</v>
       </c>
-      <c r="O74" s="19">
+      <c r="O74" s="17">
         <v>44588</v>
       </c>
       <c r="P74" s="4">
@@ -18380,16 +18471,16 @@
     </row>
     <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>66</v>
@@ -18401,7 +18492,7 @@
         <v>57</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I75" s="4">
         <v>19906880779</v>
@@ -18412,14 +18503,14 @@
       <c r="K75" s="4">
         <v>19978880779</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="17">
         <v>44700</v>
       </c>
-      <c r="M75" s="19"/>
-      <c r="N75" s="19">
+      <c r="M75" s="17"/>
+      <c r="N75" s="17">
         <v>44756</v>
       </c>
-      <c r="O75" s="19">
+      <c r="O75" s="17">
         <v>44783</v>
       </c>
       <c r="P75" s="4">
@@ -18432,16 +18523,16 @@
     </row>
     <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>253</v>
@@ -18452,8 +18543,8 @@
       <c r="G76" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="22" t="s">
-        <v>453</v>
+      <c r="H76" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I76" s="4">
         <v>3981132848.27</v>
@@ -18464,14 +18555,14 @@
       <c r="K76" s="4">
         <v>3981132848.27</v>
       </c>
-      <c r="L76" s="19">
+      <c r="L76" s="17">
         <v>44509</v>
       </c>
-      <c r="M76" s="19"/>
-      <c r="N76" s="19">
+      <c r="M76" s="17"/>
+      <c r="N76" s="17">
         <v>44511</v>
       </c>
-      <c r="O76" s="19">
+      <c r="O76" s="17">
         <v>44594</v>
       </c>
       <c r="P76" s="4">
@@ -18483,27 +18574,27 @@
       <c r="R76" s="3"/>
     </row>
     <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="21" t="s">
-        <v>782</v>
+      <c r="A77" s="18" t="s">
+        <v>773</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H77" s="24" t="s">
-        <v>507</v>
+      <c r="H77" s="21" t="s">
+        <v>498</v>
       </c>
       <c r="I77" s="4">
         <v>2407058486</v>
@@ -18514,12 +18605,12 @@
       <c r="K77" s="4">
         <v>2407275254.8200002</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="17">
         <v>44844</v>
       </c>
-      <c r="M77" s="19"/>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
+      <c r="M77" s="17"/>
+      <c r="N77" s="17"/>
+      <c r="O77" s="17"/>
       <c r="P77" s="4">
         <v>0</v>
       </c>
@@ -18530,28 +18621,28 @@
     </row>
     <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H78" s="22" t="s">
-        <v>462</v>
+      <c r="H78" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I78" s="4">
         <v>45601872749</v>
@@ -18562,14 +18653,14 @@
       <c r="K78" s="4">
         <v>45601872749</v>
       </c>
-      <c r="L78" s="19">
+      <c r="L78" s="17">
         <v>44560</v>
       </c>
-      <c r="M78" s="19"/>
-      <c r="N78" s="19">
+      <c r="M78" s="17"/>
+      <c r="N78" s="17">
         <v>44559</v>
       </c>
-      <c r="O78" s="19">
+      <c r="O78" s="17">
         <v>44669</v>
       </c>
       <c r="P78" s="4">
@@ -18582,16 +18673,16 @@
     </row>
     <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>92</v>
@@ -18602,8 +18693,8 @@
       <c r="G79" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="22" t="s">
-        <v>462</v>
+      <c r="H79" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I79" s="4">
         <v>2489078661</v>
@@ -18614,14 +18705,14 @@
       <c r="K79" s="4">
         <v>2489078661</v>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="17">
         <v>44559</v>
       </c>
-      <c r="M79" s="19"/>
-      <c r="N79" s="19" t="s">
-        <v>905</v>
-      </c>
-      <c r="O79" s="19">
+      <c r="M79" s="17"/>
+      <c r="N79" s="17">
+        <v>44559</v>
+      </c>
+      <c r="O79" s="17">
         <v>44810</v>
       </c>
       <c r="P79" s="4">
@@ -18634,16 +18725,16 @@
     </row>
     <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>92</v>
@@ -18654,8 +18745,8 @@
       <c r="G80" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H80" s="22" t="s">
-        <v>467</v>
+      <c r="H80" s="19" t="s">
+        <v>458</v>
       </c>
       <c r="I80" s="4">
         <v>18036167387.900002</v>
@@ -18666,14 +18757,12 @@
       <c r="K80" s="4">
         <v>18036167387.900002</v>
       </c>
-      <c r="L80" s="19">
+      <c r="L80" s="17">
         <v>44559</v>
       </c>
-      <c r="M80" s="19"/>
-      <c r="N80" s="19" t="s">
-        <v>904</v>
-      </c>
-      <c r="O80" s="19">
+      <c r="M80" s="17"/>
+      <c r="N80" s="29"/>
+      <c r="O80" s="17">
         <v>44708</v>
       </c>
       <c r="P80" s="4">
@@ -18686,16 +18775,16 @@
     </row>
     <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>800</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>92</v>
@@ -18706,8 +18795,8 @@
       <c r="G81" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H81" s="23" t="s">
-        <v>467</v>
+      <c r="H81" s="20" t="s">
+        <v>458</v>
       </c>
       <c r="I81" s="4">
         <v>41816156185</v>
@@ -18718,14 +18807,14 @@
       <c r="K81" s="4">
         <v>41816156185</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="17">
         <v>44624</v>
       </c>
-      <c r="M81" s="19"/>
-      <c r="N81" s="19">
+      <c r="M81" s="17"/>
+      <c r="N81" s="17">
         <v>44624</v>
       </c>
-      <c r="O81" s="19">
+      <c r="O81" s="17">
         <v>44873</v>
       </c>
       <c r="P81" s="4">
@@ -18738,16 +18827,16 @@
     </row>
     <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>66</v>
@@ -18759,7 +18848,7 @@
         <v>68</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I82" s="4">
         <v>9606506835</v>
@@ -18770,14 +18859,14 @@
       <c r="K82" s="4">
         <v>9696506835</v>
       </c>
-      <c r="L82" s="19">
+      <c r="L82" s="17">
         <v>44887</v>
       </c>
-      <c r="M82" s="19"/>
-      <c r="N82" s="19">
+      <c r="M82" s="17"/>
+      <c r="N82" s="17">
         <v>44911</v>
       </c>
-      <c r="O82" s="19">
+      <c r="O82" s="17">
         <v>45070</v>
       </c>
       <c r="P82" s="4">
@@ -18790,16 +18879,16 @@
     </row>
     <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>66</v>
@@ -18811,7 +18900,7 @@
         <v>57</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I83" s="4">
         <v>500000000</v>
@@ -18822,14 +18911,14 @@
       <c r="K83" s="4">
         <v>585470000</v>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="17">
         <v>44887</v>
       </c>
-      <c r="M83" s="19"/>
-      <c r="N83" s="19">
+      <c r="M83" s="17"/>
+      <c r="N83" s="17">
         <v>44930</v>
       </c>
-      <c r="O83" s="19">
+      <c r="O83" s="17">
         <v>44986</v>
       </c>
       <c r="P83" s="4">
@@ -18842,16 +18931,16 @@
     </row>
     <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>66</v>
@@ -18863,7 +18952,7 @@
         <v>68</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I84" s="4">
         <v>4299593384</v>
@@ -18874,14 +18963,14 @@
       <c r="K84" s="4">
         <v>4425738451</v>
       </c>
-      <c r="L84" s="19">
+      <c r="L84" s="17">
         <v>44914</v>
       </c>
-      <c r="M84" s="19"/>
-      <c r="N84" s="19">
+      <c r="M84" s="17"/>
+      <c r="N84" s="17">
         <v>45055</v>
       </c>
-      <c r="O84" s="19">
+      <c r="O84" s="17">
         <v>45139</v>
       </c>
       <c r="P84" s="4">
@@ -18894,16 +18983,16 @@
     </row>
     <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>198</v>
@@ -18914,8 +19003,8 @@
       <c r="G85" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H85" s="22" t="s">
-        <v>453</v>
+      <c r="H85" s="19" t="s">
+        <v>444</v>
       </c>
       <c r="I85" s="4">
         <v>29623316906.279999</v>
@@ -18926,14 +19015,14 @@
       <c r="K85" s="4">
         <v>29623316906.279999</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="17">
         <v>44925</v>
       </c>
-      <c r="M85" s="19"/>
-      <c r="N85" s="19">
+      <c r="M85" s="17"/>
+      <c r="N85" s="17">
         <v>44952</v>
       </c>
-      <c r="O85" s="19">
+      <c r="O85" s="17">
         <v>45030</v>
       </c>
       <c r="P85" s="4">
@@ -18946,16 +19035,16 @@
     </row>
     <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>92</v>
@@ -18966,8 +19055,8 @@
       <c r="G86" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H86" s="22" t="s">
-        <v>467</v>
+      <c r="H86" s="19" t="s">
+        <v>458</v>
       </c>
       <c r="I86" s="4">
         <v>30461715692</v>
@@ -18978,14 +19067,14 @@
       <c r="K86" s="4">
         <v>30461715692</v>
       </c>
-      <c r="L86" s="19">
+      <c r="L86" s="17">
         <v>45064</v>
       </c>
-      <c r="M86" s="19"/>
-      <c r="N86" s="19">
+      <c r="M86" s="17"/>
+      <c r="N86" s="17">
         <v>45202</v>
       </c>
-      <c r="O86" s="19">
+      <c r="O86" s="17">
         <v>45289</v>
       </c>
       <c r="P86" s="4">
@@ -18998,16 +19087,16 @@
     </row>
     <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>66</v>
@@ -19019,7 +19108,7 @@
         <v>68</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I87" s="4">
         <v>17454000000</v>
@@ -19030,14 +19119,14 @@
       <c r="K87" s="4">
         <v>17761000000</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="17">
         <v>45154</v>
       </c>
-      <c r="M87" s="19"/>
-      <c r="N87" s="19">
+      <c r="M87" s="17"/>
+      <c r="N87" s="17">
         <v>45428</v>
       </c>
-      <c r="O87" s="19">
+      <c r="O87" s="17">
         <v>45317</v>
       </c>
       <c r="P87" s="4">
@@ -19050,16 +19139,16 @@
     </row>
     <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>66</v>
@@ -19071,7 +19160,7 @@
         <v>68</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I88" s="4">
         <v>8419333809</v>
@@ -19082,14 +19171,14 @@
       <c r="K88" s="4">
         <v>9930787094</v>
       </c>
-      <c r="L88" s="19">
+      <c r="L88" s="17">
         <v>45154</v>
       </c>
-      <c r="M88" s="19"/>
-      <c r="N88" s="19">
+      <c r="M88" s="17"/>
+      <c r="N88" s="17">
         <v>45281</v>
       </c>
-      <c r="O88" s="19">
+      <c r="O88" s="17">
         <v>45328</v>
       </c>
       <c r="P88" s="4">
@@ -19102,28 +19191,28 @@
     </row>
     <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H89" s="22" t="s">
-        <v>462</v>
+      <c r="H89" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I89" s="4">
         <v>94461519789</v>
@@ -19134,14 +19223,14 @@
       <c r="K89" s="4">
         <v>94461519789</v>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="17">
         <v>45290</v>
       </c>
-      <c r="M89" s="19"/>
-      <c r="N89" s="19">
+      <c r="M89" s="17"/>
+      <c r="N89" s="17">
         <v>45369</v>
       </c>
-      <c r="O89" s="19">
+      <c r="O89" s="17">
         <v>45539</v>
       </c>
       <c r="P89" s="4">
@@ -19154,28 +19243,28 @@
     </row>
     <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I90" s="4">
         <v>3362968761</v>
@@ -19186,14 +19275,14 @@
       <c r="K90" s="4">
         <v>4543549645</v>
       </c>
-      <c r="L90" s="19">
+      <c r="L90" s="17">
         <v>45596</v>
       </c>
-      <c r="M90" s="19"/>
-      <c r="N90" s="19">
+      <c r="M90" s="17"/>
+      <c r="N90" s="17">
         <v>45649</v>
       </c>
-      <c r="O90" s="19">
+      <c r="O90" s="17">
         <v>45721</v>
       </c>
       <c r="P90" s="4">
@@ -19206,16 +19295,16 @@
     </row>
     <row r="91" spans="1:18" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>66</v>
@@ -19227,7 +19316,7 @@
         <v>68</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I91" s="4">
         <v>23600000000</v>
@@ -19238,14 +19327,14 @@
       <c r="K91" s="4">
         <v>24518488200</v>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="17">
         <v>45861</v>
       </c>
-      <c r="M91" s="19"/>
-      <c r="N91" s="19">
+      <c r="M91" s="17"/>
+      <c r="N91" s="17">
         <v>45916</v>
       </c>
-      <c r="O91" s="19">
+      <c r="O91" s="17">
         <v>45965</v>
       </c>
       <c r="P91" s="4">
@@ -19258,16 +19347,16 @@
     </row>
     <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>66</v>
@@ -19279,7 +19368,7 @@
         <v>68</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I92" s="4">
         <v>30000000000</v>
@@ -19290,14 +19379,14 @@
       <c r="K92" s="4">
         <v>31068885740</v>
       </c>
-      <c r="L92" s="19">
+      <c r="L92" s="17">
         <v>45861</v>
       </c>
-      <c r="M92" s="19"/>
-      <c r="N92" s="19">
+      <c r="M92" s="17"/>
+      <c r="N92" s="17">
         <v>45904</v>
       </c>
-      <c r="O92" s="19">
+      <c r="O92" s="17">
         <v>45976</v>
       </c>
       <c r="P92" s="4">
@@ -19310,13 +19399,13 @@
     </row>
     <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
@@ -19329,7 +19418,7 @@
         <v>68</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="I93" s="4">
         <v>30000000000</v>
@@ -19340,14 +19429,14 @@
       <c r="K93" s="4">
         <v>30899136874.049999</v>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="17">
         <v>45861</v>
       </c>
-      <c r="M93" s="19"/>
-      <c r="N93" s="19">
+      <c r="M93" s="17"/>
+      <c r="N93" s="17">
         <v>45926</v>
       </c>
-      <c r="O93" s="19">
+      <c r="O93" s="17">
         <v>45980</v>
       </c>
       <c r="P93" s="4">
@@ -19360,13 +19449,13 @@
     </row>
     <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
@@ -19378,8 +19467,8 @@
       <c r="G94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H94" s="22" t="s">
-        <v>462</v>
+      <c r="H94" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I94" s="4">
         <v>172253454</v>
@@ -19390,14 +19479,14 @@
       <c r="K94" s="4">
         <v>172253454</v>
       </c>
-      <c r="L94" s="19">
+      <c r="L94" s="17">
         <v>45715</v>
       </c>
-      <c r="M94" s="19"/>
-      <c r="N94" s="19">
+      <c r="M94" s="17"/>
+      <c r="N94" s="17">
         <v>46008</v>
       </c>
-      <c r="O94" s="19">
+      <c r="O94" s="17">
         <v>46014</v>
       </c>
       <c r="P94" s="4">
@@ -19410,16 +19499,16 @@
     </row>
     <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>212</v>
@@ -19430,8 +19519,8 @@
       <c r="G95" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H95" s="23" t="s">
-        <v>467</v>
+      <c r="H95" s="20" t="s">
+        <v>458</v>
       </c>
       <c r="I95" s="4">
         <v>511865531</v>
@@ -19442,14 +19531,14 @@
       <c r="K95" s="4">
         <v>711865531</v>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="17">
         <v>45756</v>
       </c>
-      <c r="M95" s="19"/>
-      <c r="N95" s="19">
+      <c r="M95" s="17"/>
+      <c r="N95" s="17">
         <v>45775</v>
       </c>
-      <c r="O95" s="19">
+      <c r="O95" s="17">
         <v>45922</v>
       </c>
       <c r="P95" s="4">
@@ -19462,13 +19551,13 @@
     </row>
     <row r="96" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
@@ -19480,8 +19569,8 @@
       <c r="G96" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H96" s="22" t="s">
-        <v>507</v>
+      <c r="H96" s="19" t="s">
+        <v>498</v>
       </c>
       <c r="I96" s="4">
         <v>386045990.94</v>
@@ -19492,14 +19581,14 @@
       <c r="K96" s="4">
         <v>586045990.94000006</v>
       </c>
-      <c r="L96" s="19">
+      <c r="L96" s="17">
         <v>45917</v>
       </c>
-      <c r="M96" s="19"/>
-      <c r="N96" s="19">
+      <c r="M96" s="17"/>
+      <c r="N96" s="17">
         <v>45938</v>
       </c>
-      <c r="O96" s="19"/>
+      <c r="O96" s="17"/>
       <c r="P96" s="4">
         <v>0</v>
       </c>
@@ -19510,16 +19599,16 @@
     </row>
     <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>92</v>
@@ -19530,8 +19619,8 @@
       <c r="G97" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H97" s="22" t="s">
-        <v>462</v>
+      <c r="H97" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I97" s="4">
         <v>59900815918</v>
@@ -19542,14 +19631,14 @@
       <c r="K97" s="4">
         <v>59900815918</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="17">
         <v>45911</v>
       </c>
-      <c r="M97" s="19"/>
-      <c r="N97" s="19">
+      <c r="M97" s="17"/>
+      <c r="N97" s="17">
         <v>45922</v>
       </c>
-      <c r="O97" s="19">
+      <c r="O97" s="17">
         <v>45974</v>
       </c>
       <c r="P97" s="4">
@@ -19562,28 +19651,28 @@
     </row>
     <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H98" s="22" t="s">
-        <v>462</v>
+      <c r="H98" s="19" t="s">
+        <v>453</v>
       </c>
       <c r="I98" s="4">
         <v>28121067144</v>
@@ -19594,14 +19683,14 @@
       <c r="K98" s="4">
         <v>28263067144</v>
       </c>
-      <c r="L98" s="19">
+      <c r="L98" s="17">
         <v>45861</v>
       </c>
-      <c r="M98" s="19"/>
-      <c r="N98" s="19">
+      <c r="M98" s="17"/>
+      <c r="N98" s="17">
         <v>45882</v>
       </c>
-      <c r="O98" s="19">
+      <c r="O98" s="17">
         <v>45926</v>
       </c>
       <c r="P98" s="4">
@@ -19614,16 +19703,16 @@
     </row>
     <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>66</v>
@@ -19635,7 +19724,7 @@
         <v>207</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I99" s="4">
         <v>1989520159</v>
@@ -19646,14 +19735,14 @@
       <c r="K99" s="4">
         <v>2825408806</v>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="17">
         <v>44078</v>
       </c>
-      <c r="M99" s="19"/>
-      <c r="N99" s="19">
+      <c r="M99" s="17"/>
+      <c r="N99" s="17">
         <v>44176</v>
       </c>
-      <c r="O99" s="19"/>
+      <c r="O99" s="17"/>
       <c r="P99" s="4">
         <v>98.57</v>
       </c>
@@ -19664,16 +19753,16 @@
     </row>
     <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>66</v>
@@ -19685,7 +19774,7 @@
         <v>207</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I100" s="4">
         <v>4869404585</v>
@@ -19696,14 +19785,14 @@
       <c r="K100" s="4">
         <v>5039787989</v>
       </c>
-      <c r="L100" s="19">
+      <c r="L100" s="17">
         <v>44384</v>
       </c>
-      <c r="M100" s="19"/>
-      <c r="N100" s="19">
+      <c r="M100" s="17"/>
+      <c r="N100" s="17">
         <v>44407</v>
       </c>
-      <c r="O100" s="19">
+      <c r="O100" s="17">
         <v>44560</v>
       </c>
       <c r="P100" s="4">
@@ -19716,28 +19805,28 @@
     </row>
     <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I101" s="4">
         <v>2644584337.2600002</v>
@@ -19748,14 +19837,14 @@
       <c r="K101" s="4">
         <v>2644584337.2600002</v>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="17">
         <v>44456</v>
       </c>
-      <c r="M101" s="19"/>
-      <c r="N101" s="19">
+      <c r="M101" s="17"/>
+      <c r="N101" s="17">
         <v>44489</v>
       </c>
-      <c r="O101" s="19">
+      <c r="O101" s="17">
         <v>44859</v>
       </c>
       <c r="P101" s="4">
@@ -19768,28 +19857,28 @@
     </row>
     <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I102" s="4">
         <v>6578630543.6700001</v>
@@ -19800,14 +19889,14 @@
       <c r="K102" s="4">
         <v>6578630543.6700001</v>
       </c>
-      <c r="L102" s="19">
+      <c r="L102" s="17">
         <v>44559</v>
       </c>
-      <c r="M102" s="19"/>
-      <c r="N102" s="19">
+      <c r="M102" s="17"/>
+      <c r="N102" s="17">
         <v>44566</v>
       </c>
-      <c r="O102" s="19">
+      <c r="O102" s="17">
         <v>44697</v>
       </c>
       <c r="P102" s="4">
@@ -19820,16 +19909,16 @@
     </row>
     <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>92</v>
@@ -19841,7 +19930,7 @@
         <v>207</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I103" s="4">
         <v>6853127845.6300001</v>
@@ -19852,14 +19941,14 @@
       <c r="K103" s="4">
         <v>6853127845.6300001</v>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="17">
         <v>45216</v>
       </c>
-      <c r="M103" s="19"/>
-      <c r="N103" s="19">
+      <c r="M103" s="17"/>
+      <c r="N103" s="17">
         <v>45219</v>
       </c>
-      <c r="O103" s="19">
+      <c r="O103" s="17">
         <v>45286</v>
       </c>
       <c r="P103" s="4">
@@ -19872,26 +19961,26 @@
     </row>
     <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>884</v>
-      </c>
-      <c r="H104" s="21" t="s">
-        <v>507</v>
+        <v>875</v>
+      </c>
+      <c r="H104" s="18" t="s">
+        <v>498</v>
       </c>
       <c r="I104" s="4">
         <v>36139210439</v>
@@ -19902,14 +19991,14 @@
       <c r="K104" s="4">
         <v>36139210439</v>
       </c>
-      <c r="L104" s="19">
+      <c r="L104" s="17">
         <v>46080</v>
       </c>
-      <c r="M104" s="19"/>
-      <c r="N104" s="19">
+      <c r="M104" s="17"/>
+      <c r="N104" s="17">
         <v>46091</v>
       </c>
-      <c r="O104" s="19"/>
+      <c r="O104" s="17"/>
       <c r="P104" s="4">
         <v>0</v>
       </c>
@@ -19930,21 +20019,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -20088,24 +20162,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA423ED4-21A6-41DF-89D7-6CD27D950967}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44576703-C4EA-42A2-935E-C76D3BE0FC53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20121,4 +20193,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA423ED4-21A6-41DF-89D7-6CD27D950967}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{690FE775-1C55-4B7A-8805-B64E18B6F1A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="560" documentId="11_A78776D1E842DF805D35AEE6E05861D715103029" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F10E625-1A77-4B56-A279-10417AF7031B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="925">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1422,13 +1422,7 @@
     <t>FUENTE</t>
   </si>
   <si>
-    <t xml:space="preserve">VALOR OTROS </t>
-  </si>
-  <si>
     <t>VALOR TOTAL</t>
-  </si>
-  <si>
-    <t>FECHA DE INCORPORACIÓN DE RECUROS</t>
   </si>
   <si>
     <t>AVANCE FÍSICO</t>
@@ -1625,9 +1619,6 @@
     <t>Sin contratar</t>
   </si>
   <si>
-    <t xml:space="preserve">COMENTARIOS </t>
-  </si>
-  <si>
     <t>MUNICIPIO DE MORROA</t>
   </si>
   <si>
@@ -2859,9 +2850,6 @@
     <t>OSVALDO SIERRA CARVAJALINO</t>
   </si>
   <si>
-    <t>NOMBRE DE COLUMNA</t>
-  </si>
-  <si>
     <t>DESCENTRALIZADAS Y MUNIICIPIOS</t>
   </si>
   <si>
@@ -2881,20 +2869,6 @@
   </si>
   <si>
     <t xml:space="preserve">MOSTRAR COMENTARIOS DE LA MATRIZ EN LOS HITOS </t>
-  </si>
-  <si>
-    <t>Pendiente agregar en la herramienta de consolidación</t>
-  </si>
-  <si>
-    <t>Realizado</t>
-  </si>
-  <si>
-    <t>5/05/2026: Proyecto realizó apertura de proceso de simulación en Colombia compra eficiente  de la  compra de maquinaria amarilla-agrícola (5-marzo de 2026), este proceso fue declarado desierto.
-Conforme a la información proporcionada por la sectorial ya fueron radicados nuevamente  los estudios previos  a contratación el 01/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II, cuenta con CDP, en elaboración de estudios previos por parte de la sectorial.
-</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -2927,6 +2901,38 @@
   <si>
     <t xml:space="preserve">
 05/05/2026: El proyecto ya cuenta con acta de inicio y programación inicial, las cuales serán cargadas en la plataforma Gesproy para su cambio al estado ‘En ejecución’. En consecuencia, el proyecto deja de presentar alerta por falta de acta  inicio.</t>
+  </si>
+  <si>
+    <t>COMENTARIOS</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>HERRAMIENTA</t>
+  </si>
+  <si>
+    <t>Consolidación regalías</t>
+  </si>
+  <si>
+    <t>Seguimiento Regalías</t>
+  </si>
+  <si>
+    <t>CAMBIO NOMBRE COLUMNA</t>
+  </si>
+  <si>
+    <t>FECHA DE INCORPORACIÓN DE RECUROS -&gt; FECHA DE INCORPORACIÓN DE RECURSOS</t>
+  </si>
+  <si>
+    <t>REALIZADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026: Proyecto en estado “Sin contratar”,  sin registro de proceso precontractual en SECOP II, cuenta con CDP, en elaboración de estudios previos por parte de la sectorial.
+</t>
+  </si>
+  <si>
+    <t>13/05/2026: Proyecto realizó apertura de proceso de simulación en Colombia compra eficiente  de la  compra de maquinaria amarilla-agrícola (5-marzo de 2026), este proceso fue declarado desierto.
+Conforme a la información proporcionada por la sectorial ya fueron radicados nuevamente  los estudios previos  a contratación el 04/05/2026</t>
   </si>
 </sst>
 </file>
@@ -2938,7 +2944,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2996,6 +3002,19 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="14">
@@ -3078,7 +3097,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -3114,11 +3133,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3156,14 +3258,6 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3206,6 +3300,33 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3216,7 +3337,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="33">
     <dxf>
       <font>
         <b val="0"/>
@@ -3969,6 +4090,225 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3984,7 +4324,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AW58" totalsRowShown="0">
-  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A2:AW58" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="6">
+      <filters>
+        <filter val="SIN CONTRATAR"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="49">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -4053,7 +4399,7 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="ESTADO PROYECTO"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="ESTADO CONTRATO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="VALOR SGR"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS "/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="FECHA DE MIGRACIÓN A GESPROY"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS" dataDxfId="21">
@@ -4090,6 +4436,20 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}" name="Tabla4" displayName="Tabla4" ref="A1:E13" totalsRowShown="0" headerRowDxfId="32" dataDxfId="30" headerRowBorderDxfId="31" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+  <autoFilter ref="A1:E13" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{9F035937-1E8B-4F24-8B80-B1B9E38B09D9}" name="TIPO DE CAMBIO" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{269A1A9F-830F-4DD1-884A-2D66D94C0DBF}" name="CAMBIO" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{65FD326A-CCAB-4CDD-AFB7-9A7F1FA3BF96}" name="MATRIZ" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{2AACFDF5-8DB9-4CEE-BDC7-28F42593E85C}" name="HERRAMIENTA" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{5504CFAF-1675-498C-A8A4-9B593D3E6460}" name="REALIZADO" dataDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:R104" totalsRowShown="0" dataDxfId="18">
   <autoFilter ref="A2:R104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="18">
@@ -4110,7 +4470,7 @@
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO" dataDxfId="3"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO" dataDxfId="1"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS " dataDxfId="0"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4420,60 +4780,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="32" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="32"/>
-      <c r="AH1" s="32"/>
-      <c r="AI1" s="32"/>
-      <c r="AJ1" s="32"/>
-      <c r="AK1" s="32"/>
-      <c r="AL1" s="32"/>
-      <c r="AM1" s="32"/>
-      <c r="AN1" s="32"/>
-      <c r="AO1" s="32"/>
-      <c r="AP1" s="32"/>
-      <c r="AQ1" s="31" t="s">
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="37"/>
+      <c r="AM1" s="37"/>
+      <c r="AN1" s="37"/>
+      <c r="AO1" s="37"/>
+      <c r="AP1" s="37"/>
+      <c r="AQ1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="AR1" s="31"/>
-      <c r="AS1" s="31"/>
-      <c r="AT1" s="31"/>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
+      <c r="AR1" s="36"/>
+      <c r="AS1" s="36"/>
+      <c r="AT1" s="36"/>
+      <c r="AU1" s="36"/>
+      <c r="AV1" s="36"/>
     </row>
     <row r="2" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4620,11 +4980,11 @@
       <c r="AV2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="26" t="s">
-        <v>895</v>
+      <c r="AW2" s="22" t="s">
+        <v>892</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="112.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -4754,11 +5114,11 @@
       <c r="AV3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AW3" s="23" t="s">
-        <v>901</v>
+      <c r="AW3" s="19" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -4888,11 +5248,11 @@
       <c r="AV4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="AW4" s="22" t="s">
-        <v>896</v>
+      <c r="AW4" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -5032,11 +5392,11 @@
       <c r="AV5" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW5" s="22" t="s">
-        <v>896</v>
+      <c r="AW5" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>80</v>
       </c>
@@ -5178,11 +5538,11 @@
       <c r="AV6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AW6" s="22" t="s">
-        <v>896</v>
+      <c r="AW6" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="141.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" ht="141.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>88</v>
       </c>
@@ -5322,11 +5682,11 @@
       <c r="AV7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AW7" s="22" t="s">
-        <v>897</v>
+      <c r="AW7" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>99</v>
       </c>
@@ -5458,11 +5818,11 @@
       <c r="AV8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AW8" s="23" t="s">
-        <v>901</v>
+      <c r="AW8" s="19" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="156.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="156.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>106</v>
       </c>
@@ -5606,11 +5966,11 @@
       <c r="AV9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AW9" s="22" t="s">
-        <v>896</v>
+      <c r="AW9" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>113</v>
       </c>
@@ -5750,11 +6110,11 @@
       <c r="AV10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW10" s="22" t="s">
-        <v>898</v>
+      <c r="AW10" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>119</v>
       </c>
@@ -5894,11 +6254,11 @@
       <c r="AV11" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW11" s="22" t="s">
-        <v>896</v>
+      <c r="AW11" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>124</v>
       </c>
@@ -6038,11 +6398,11 @@
       <c r="AV12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AW12" s="22" t="s">
-        <v>898</v>
+      <c r="AW12" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>132</v>
       </c>
@@ -6184,11 +6544,11 @@
       <c r="AV13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AW13" s="22" t="s">
-        <v>899</v>
+      <c r="AW13" s="18" t="s">
+        <v>896</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>142</v>
       </c>
@@ -6328,11 +6688,11 @@
       <c r="AV14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AW14" s="22" t="s">
-        <v>897</v>
+      <c r="AW14" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>149</v>
       </c>
@@ -6474,11 +6834,11 @@
       <c r="AV15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="AW15" s="22" t="s">
-        <v>896</v>
+      <c r="AW15" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>155</v>
       </c>
@@ -6618,11 +6978,11 @@
       <c r="AV16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW16" s="22" t="s">
-        <v>898</v>
+      <c r="AW16" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>161</v>
       </c>
@@ -6764,11 +7124,11 @@
       <c r="AV17" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AW17" s="22" t="s">
-        <v>898</v>
+      <c r="AW17" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>169</v>
       </c>
@@ -6910,11 +7270,11 @@
       <c r="AV18" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="AW18" s="22" t="s">
-        <v>896</v>
+      <c r="AW18" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>176</v>
       </c>
@@ -7056,11 +7416,11 @@
       <c r="AV19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AW19" s="22" t="s">
-        <v>896</v>
+      <c r="AW19" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>181</v>
       </c>
@@ -7200,11 +7560,11 @@
       <c r="AV20" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW20" s="22" t="s">
-        <v>896</v>
+      <c r="AW20" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>186</v>
       </c>
@@ -7346,11 +7706,11 @@
       <c r="AV21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AW21" s="22" t="s">
-        <v>900</v>
+      <c r="AW21" s="18" t="s">
+        <v>897</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>195</v>
       </c>
@@ -7492,11 +7852,11 @@
       <c r="AV22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AW22" s="22" t="s">
-        <v>901</v>
+      <c r="AW22" s="18" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>203</v>
       </c>
@@ -7628,11 +7988,11 @@
       <c r="AV23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW23" s="22" t="s">
-        <v>897</v>
+      <c r="AW23" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>209</v>
       </c>
@@ -7764,11 +8124,11 @@
       <c r="AV24" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="AW24" s="22" t="s">
-        <v>896</v>
+      <c r="AW24" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>217</v>
       </c>
@@ -7902,11 +8262,11 @@
       <c r="AV25" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW25" s="22" t="s">
-        <v>896</v>
+      <c r="AW25" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>222</v>
       </c>
@@ -8048,11 +8408,11 @@
       <c r="AV26" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="AW26" s="22" t="s">
-        <v>898</v>
+      <c r="AW26" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>229</v>
       </c>
@@ -8192,18 +8552,18 @@
       <c r="AV27" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="AW27" s="22" t="s">
-        <v>901</v>
+      <c r="AW27" s="18" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>235</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="23" t="s">
         <v>236</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -8328,11 +8688,11 @@
       <c r="AV28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW28" s="22" t="s">
-        <v>897</v>
+      <c r="AW28" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>239</v>
       </c>
@@ -8472,11 +8832,11 @@
       <c r="AV29" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="AW29" s="22" t="s">
-        <v>898</v>
+      <c r="AW29" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="30" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>246</v>
       </c>
@@ -8608,11 +8968,11 @@
       <c r="AV30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW30" s="22" t="s">
-        <v>898</v>
+      <c r="AW30" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>250</v>
       </c>
@@ -8752,11 +9112,11 @@
       <c r="AV31" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="AW31" s="22" t="s">
-        <v>897</v>
+      <c r="AW31" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>258</v>
       </c>
@@ -8898,11 +9258,11 @@
       <c r="AV32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="AW32" s="22" t="s">
-        <v>897</v>
+      <c r="AW32" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="33" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>266</v>
       </c>
@@ -9044,11 +9404,11 @@
       <c r="AV33" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AW33" s="22" t="s">
-        <v>898</v>
+      <c r="AW33" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="34" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>275</v>
       </c>
@@ -9180,11 +9540,11 @@
       <c r="AV34" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW34" s="22" t="s">
-        <v>897</v>
+      <c r="AW34" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="35" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>280</v>
       </c>
@@ -9314,11 +9674,11 @@
       <c r="AV35" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="AW35" s="22" t="s">
-        <v>896</v>
+      <c r="AW35" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="36" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>285</v>
       </c>
@@ -9458,11 +9818,11 @@
       <c r="AV36" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="AW36" s="22" t="s">
-        <v>898</v>
+      <c r="AW36" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="37" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>292</v>
       </c>
@@ -9604,11 +9964,11 @@
       <c r="AV37" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="AW37" s="22" t="s">
-        <v>896</v>
+      <c r="AW37" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="38" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>299</v>
       </c>
@@ -9750,11 +10110,11 @@
       <c r="AV38" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="AW38" s="22" t="s">
-        <v>897</v>
+      <c r="AW38" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="39" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>307</v>
       </c>
@@ -9894,11 +10254,11 @@
       <c r="AV39" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="AW39" s="22" t="s">
-        <v>896</v>
+      <c r="AW39" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="40" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>314</v>
       </c>
@@ -10040,11 +10400,11 @@
       <c r="AV40" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AW40" s="22" t="s">
-        <v>897</v>
+      <c r="AW40" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="41" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>320</v>
       </c>
@@ -10186,11 +10546,11 @@
       <c r="AV41" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="AW41" s="22" t="s">
-        <v>898</v>
+      <c r="AW41" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="42" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>327</v>
       </c>
@@ -10330,8 +10690,8 @@
       <c r="AV42" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="AW42" s="22" t="s">
-        <v>901</v>
+      <c r="AW42" s="18" t="s">
+        <v>898</v>
       </c>
     </row>
     <row r="43" spans="1:49" ht="183.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10400,7 +10760,9 @@
       <c r="Y43" s="5">
         <v>45615</v>
       </c>
-      <c r="Z43" s="5"/>
+      <c r="Z43" s="5">
+        <v>46086</v>
+      </c>
       <c r="AA43" s="5"/>
       <c r="AB43" s="5"/>
       <c r="AC43" s="5"/>
@@ -10460,13 +10822,13 @@
         <v/>
       </c>
       <c r="AV43" s="3" t="s">
-        <v>913</v>
-      </c>
-      <c r="AW43" s="22" t="s">
-        <v>901</v>
+        <v>924</v>
+      </c>
+      <c r="AW43" s="18" t="s">
+        <v>898</v>
       </c>
     </row>
-    <row r="44" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>339</v>
       </c>
@@ -10608,11 +10970,11 @@
       <c r="AV44" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="AW44" s="22" t="s">
-        <v>897</v>
+      <c r="AW44" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
-    <row r="45" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>346</v>
       </c>
@@ -10752,11 +11114,11 @@
       <c r="AV45" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="AW45" s="22" t="s">
-        <v>898</v>
+      <c r="AW45" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="46" spans="1:49" ht="177.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:49" ht="177.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>356</v>
       </c>
@@ -10892,13 +11254,13 @@
         <v/>
       </c>
       <c r="AV46" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="AW46" s="22" t="s">
-        <v>898</v>
+        <v>912</v>
+      </c>
+      <c r="AW46" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
-    <row r="47" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>365</v>
       </c>
@@ -11040,8 +11402,8 @@
       <c r="AV47" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="AW47" s="22" t="s">
-        <v>898</v>
+      <c r="AW47" s="18" t="s">
+        <v>895</v>
       </c>
     </row>
     <row r="48" spans="1:49" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11154,13 +11516,13 @@
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>914</v>
-      </c>
-      <c r="AW48" s="22" t="s">
-        <v>896</v>
+        <v>923</v>
+      </c>
+      <c r="AW48" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="49" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>373</v>
       </c>
@@ -11298,11 +11660,11 @@
       <c r="AV49" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="AW49" s="22" t="s">
-        <v>896</v>
+      <c r="AW49" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="50" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>381</v>
       </c>
@@ -11442,11 +11804,11 @@
       <c r="AV50" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="AW50" s="22" t="s">
-        <v>902</v>
+      <c r="AW50" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
-    <row r="51" spans="1:49" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" ht="69.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="12" t="s">
         <v>388</v>
       </c>
@@ -11588,8 +11950,8 @@
       <c r="AV51" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="AW51" s="22" t="s">
-        <v>902</v>
+      <c r="AW51" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="52" spans="1:49" ht="249" customHeight="1" x14ac:dyDescent="0.25">
@@ -11719,11 +12081,11 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV52" s="30" t="s">
-        <v>915</v>
-      </c>
-      <c r="AW52" s="22" t="s">
-        <v>902</v>
+      <c r="AV52" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="AW52" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="53" spans="1:49" ht="120" customHeight="1" x14ac:dyDescent="0.25">
@@ -11842,13 +12204,13 @@
         <v/>
       </c>
       <c r="AV53" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="AW53" s="22" t="s">
-        <v>896</v>
+        <v>908</v>
+      </c>
+      <c r="AW53" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
-    <row r="54" spans="1:49" ht="179.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" ht="179.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>403</v>
       </c>
@@ -11982,13 +12344,13 @@
         <v/>
       </c>
       <c r="AV54" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="AW54" s="22" t="s">
-        <v>902</v>
+        <v>914</v>
+      </c>
+      <c r="AW54" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
-    <row r="55" spans="1:49" ht="254.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:49" ht="254.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="12" t="s">
         <v>409</v>
       </c>
@@ -12121,11 +12483,11 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV55" s="30" t="s">
-        <v>921</v>
-      </c>
-      <c r="AW55" s="22" t="s">
-        <v>902</v>
+      <c r="AV55" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="AW55" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="56" spans="1:49" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12256,10 +12618,10 @@
         <v/>
       </c>
       <c r="AV56" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="AW56" s="22" t="s">
-        <v>902</v>
+        <v>909</v>
+      </c>
+      <c r="AW56" s="18" t="s">
+        <v>899</v>
       </c>
     </row>
     <row r="57" spans="1:49" ht="143.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -12308,9 +12670,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="5"/>
-      <c r="R57" s="5">
-        <v>0</v>
-      </c>
+      <c r="R57" s="5"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <v>46017</v>
@@ -12386,14 +12746,14 @@
         <v/>
       </c>
       <c r="AV57" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="AW57" s="22" t="s">
-        <v>897</v>
+        <v>910</v>
+      </c>
+      <c r="AW57" s="18" t="s">
+        <v>894</v>
       </c>
     </row>
     <row r="58" spans="1:49" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="25">
+      <c r="A58" s="21">
         <v>2026002700001</v>
       </c>
       <c r="B58" s="9" t="s">
@@ -12506,10 +12866,10 @@
         <v/>
       </c>
       <c r="AV58" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="AW58" s="22" t="s">
-        <v>896</v>
+        <v>911</v>
+      </c>
+      <c r="AW58" s="18" t="s">
+        <v>893</v>
       </c>
     </row>
   </sheetData>
@@ -12541,50 +12901,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="32" t="s">
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="31" t="s">
+      <c r="P1" s="37"/>
+      <c r="Q1" s="37"/>
+      <c r="R1" s="37"/>
+      <c r="S1" s="37"/>
+      <c r="T1" s="37"/>
+      <c r="U1" s="37"/>
+      <c r="V1" s="37"/>
+      <c r="W1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="36"/>
     </row>
     <row r="2" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12615,10 +12975,10 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>435</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>436</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>20</v>
@@ -12630,7 +12990,7 @@
         <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
@@ -12704,28 +13064,28 @@
     </row>
     <row r="3" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I3" s="4">
         <v>2006938345.6700001</v>
@@ -12743,7 +13103,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="13">
         <v>44326</v>
       </c>
       <c r="O3" s="4">
@@ -12804,33 +13164,33 @@
         <v/>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>448</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I4" s="4">
         <v>1295118639.0699999</v>
@@ -12848,7 +13208,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44197</v>
       </c>
-      <c r="N4" s="17">
+      <c r="N4" s="13">
         <v>44326</v>
       </c>
       <c r="O4" s="4">
@@ -12909,7 +13269,7 @@
         <v/>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:38" ht="156" customHeight="1" x14ac:dyDescent="0.25">
@@ -12917,13 +13277,13 @@
         <v>2021000020028</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>450</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
@@ -12935,7 +13295,7 @@
         <v>68</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I5" s="4">
         <v>3153851580.9099998</v>
@@ -12953,7 +13313,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44568</v>
       </c>
-      <c r="N5" s="28"/>
+      <c r="N5" s="24"/>
       <c r="O5" s="4">
         <v>96.02</v>
       </c>
@@ -13025,28 +13385,28 @@
     </row>
     <row r="6" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="I6" s="4">
         <v>6026477761</v>
@@ -13064,7 +13424,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44624</v>
       </c>
-      <c r="N6" s="17">
+      <c r="N6" s="13">
         <v>44509</v>
       </c>
       <c r="O6" s="4">
@@ -13133,7 +13493,7 @@
         <v>20</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -13141,25 +13501,25 @@
         <v>20221301010208</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I7" s="4">
         <v>1800000000</v>
@@ -13177,7 +13537,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>44925</v>
       </c>
-      <c r="N7" s="17">
+      <c r="N7" s="13">
         <v>44930</v>
       </c>
       <c r="O7" s="4">
@@ -13246,21 +13606,21 @@
         <v>20</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
     </row>
     <row r="8" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>55</v>
@@ -13272,7 +13632,7 @@
         <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I8" s="4">
         <v>1702007732.2</v>
@@ -13290,7 +13650,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45226</v>
       </c>
-      <c r="N8" s="17">
+      <c r="N8" s="13">
         <v>45232</v>
       </c>
       <c r="O8" s="4">
@@ -13351,33 +13711,33 @@
         <v/>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9" spans="1:38" ht="93" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>467</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>283</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I9" s="4">
         <v>13713002364.719999</v>
@@ -13395,7 +13755,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N9" s="17">
+      <c r="N9" s="13">
         <v>45290</v>
       </c>
       <c r="O9" s="4">
@@ -13460,21 +13820,21 @@
         <v/>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>471</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>220</v>
@@ -13486,7 +13846,7 @@
         <v>68</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I10" s="4">
         <v>9056051736.6399994</v>
@@ -13504,7 +13864,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45302</v>
       </c>
-      <c r="N10" s="17">
+      <c r="N10" s="13">
         <v>45290</v>
       </c>
       <c r="O10" s="4">
@@ -13574,16 +13934,16 @@
     </row>
     <row r="11" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>472</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>278</v>
@@ -13595,7 +13955,7 @@
         <v>68</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I11" s="4">
         <v>7862105021</v>
@@ -13613,7 +13973,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45478</v>
       </c>
-      <c r="N11" s="17">
+      <c r="N11" s="13">
         <v>45485</v>
       </c>
       <c r="O11" s="4">
@@ -13685,16 +14045,16 @@
     </row>
     <row r="12" spans="1:38" ht="97.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>476</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>253</v>
@@ -13706,7 +14066,7 @@
         <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I12" s="4">
         <v>15100656106.639999</v>
@@ -13724,7 +14084,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45475</v>
       </c>
-      <c r="N12" s="17">
+      <c r="N12" s="13">
         <v>45506</v>
       </c>
       <c r="O12" s="4">
@@ -13793,21 +14153,21 @@
         <v>36</v>
       </c>
       <c r="AL12" s="3" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
     </row>
     <row r="13" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>479</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>270</v>
@@ -13819,7 +14179,7 @@
         <v>68</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I13" s="4">
         <v>3068416428</v>
@@ -13837,7 +14197,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N13" s="17">
+      <c r="N13" s="13">
         <v>45656</v>
       </c>
       <c r="O13" s="4">
@@ -13910,13 +14270,13 @@
         <v>2024002700193</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>253</v>
@@ -13928,7 +14288,7 @@
         <v>68</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I14" s="4">
         <v>63850574205.629997</v>
@@ -13946,7 +14306,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45659</v>
       </c>
-      <c r="N14" s="17">
+      <c r="N14" s="13">
         <v>45656</v>
       </c>
       <c r="O14" s="4">
@@ -14018,16 +14378,16 @@
     </row>
     <row r="15" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>483</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>485</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>278</v>
@@ -14039,7 +14399,7 @@
         <v>68</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I15" s="4">
         <v>11318403530.17</v>
@@ -14057,7 +14417,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45823</v>
       </c>
-      <c r="N15" s="17">
+      <c r="N15" s="13">
         <v>45825</v>
       </c>
       <c r="O15" s="4">
@@ -14127,16 +14487,16 @@
     </row>
     <row r="16" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>488</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>489</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>253</v>
@@ -14148,7 +14508,7 @@
         <v>360</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I16" s="4">
         <v>1903272161</v>
@@ -14166,7 +14526,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>45790</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N16" s="13">
         <v>45803</v>
       </c>
       <c r="O16" s="4">
@@ -14234,16 +14594,16 @@
     </row>
     <row r="17" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>490</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>476</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>492</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>253</v>
@@ -14255,7 +14615,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I17" s="4">
         <v>1484402616</v>
@@ -14268,7 +14628,7 @@
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
-      <c r="N17" s="17">
+      <c r="N17" s="13">
         <v>45803</v>
       </c>
       <c r="O17" s="4">
@@ -14338,28 +14698,28 @@
     </row>
     <row r="18" spans="1:38" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>493</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>496</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>278</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>336</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="I18" s="4">
         <v>627486059.86000001</v>
@@ -14377,7 +14737,7 @@
         <f>+OtrosEjecutoresDescentralizadas[[#This Row],[FECHA DE MIGRACIÓN A GESPROY]]+1</f>
         <v>46119</v>
       </c>
-      <c r="N18" s="24">
+      <c r="N18" s="20">
         <v>46119</v>
       </c>
       <c r="O18" s="4">
@@ -14454,192 +14814,231 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A41BB839-CD8D-4F7F-BBA8-C26EF6962443}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.85546875" customWidth="1"/>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" customWidth="1"/>
+    <col min="3" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>882</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>875</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>876</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>917</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>877</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>880</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>878</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
+        <v>877</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>879</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>881</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>883</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>884</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
+        <v>886</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>887</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B6" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>890</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>891</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="30" t="s">
+        <v>920</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>921</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>918</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>877</v>
+      </c>
+      <c r="B10" s="31" t="s">
+        <v>901</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>902</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>885</v>
       </c>
-      <c r="B1" s="13" t="s">
-        <v>878</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>879</v>
+      <c r="D11" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>916</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>880</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>883</v>
-      </c>
-      <c r="C2" s="16" t="s">
-        <v>881</v>
-      </c>
-      <c r="D2" t="s">
-        <v>911</v>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>888</v>
+      </c>
+      <c r="B12" s="31" t="s">
+        <v>904</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>885</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>916</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>882</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>884</v>
-      </c>
-      <c r="D3" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>886</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>887</v>
-      </c>
-      <c r="C4" s="15" t="s">
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="33" t="s">
         <v>888</v>
       </c>
-      <c r="D4" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>889</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>890</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>888</v>
-      </c>
-      <c r="D5" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>892</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>888</v>
-      </c>
-      <c r="D6" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>893</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>894</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>903</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>904</v>
-      </c>
-      <c r="D9" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>880</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="B13" s="34" t="s">
+        <v>906</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>905</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>907</v>
-      </c>
-      <c r="D10" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>906</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>888</v>
-      </c>
-      <c r="D11" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>908</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>888</v>
-      </c>
-      <c r="D12" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>891</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>910</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>909</v>
-      </c>
-      <c r="D13" t="s">
-        <v>912</v>
+      <c r="D13" s="32" t="s">
+        <v>919</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>916</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -14654,26 +15053,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
+      <c r="A1" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
     </row>
     <row r="2" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -14707,7 +15106,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -14722,13 +15121,13 @@
         <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>499</v>
+        <v>915</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -14736,13 +15135,13 @@
         <v>2012000020042</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>92</v>
@@ -14754,7 +15153,7 @@
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I3" s="4">
         <v>22526692745</v>
@@ -14765,14 +15164,14 @@
       <c r="K3" s="4">
         <v>22526692745</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="13">
         <v>41201</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17">
+      <c r="M3" s="13"/>
+      <c r="N3" s="13">
         <v>41829</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="13">
         <v>42072</v>
       </c>
       <c r="P3" s="4">
@@ -14788,13 +15187,13 @@
         <v>2012002700005</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>92</v>
@@ -14805,8 +15204,8 @@
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="19" t="s">
-        <v>444</v>
+      <c r="H4" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I4" s="4">
         <v>924979909</v>
@@ -14817,14 +15216,14 @@
       <c r="K4" s="4">
         <v>954979909</v>
       </c>
-      <c r="L4" s="17">
+      <c r="L4" s="13">
         <v>41191</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17">
+      <c r="M4" s="13"/>
+      <c r="N4" s="13">
         <v>41304</v>
       </c>
-      <c r="O4" s="17">
+      <c r="O4" s="13">
         <v>41452</v>
       </c>
       <c r="P4" s="4">
@@ -14837,16 +15236,16 @@
     </row>
     <row r="5" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>507</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>92</v>
@@ -14858,7 +15257,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I5" s="4">
         <v>999998309</v>
@@ -14869,14 +15268,14 @@
       <c r="K5" s="4">
         <v>1010998309</v>
       </c>
-      <c r="L5" s="17">
+      <c r="L5" s="13">
         <v>41191</v>
       </c>
-      <c r="M5" s="17"/>
-      <c r="N5" s="17">
+      <c r="M5" s="13"/>
+      <c r="N5" s="13">
         <v>41276</v>
       </c>
-      <c r="O5" s="17">
+      <c r="O5" s="13">
         <v>41355</v>
       </c>
       <c r="P5" s="4">
@@ -14889,16 +15288,16 @@
     </row>
     <row r="6" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>511</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>514</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>92</v>
@@ -14910,7 +15309,7 @@
         <v>57</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I6" s="4">
         <v>16567304387</v>
@@ -14921,14 +15320,14 @@
       <c r="K6" s="4">
         <v>16567304387</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="13">
         <v>41533</v>
       </c>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17">
+      <c r="M6" s="13"/>
+      <c r="N6" s="13">
         <v>41537</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="13">
         <v>41669</v>
       </c>
       <c r="P6" s="4">
@@ -14941,28 +15340,28 @@
     </row>
     <row r="7" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="19" t="s">
-        <v>444</v>
+      <c r="H7" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I7" s="4">
         <v>12429000000</v>
@@ -14973,14 +15372,14 @@
       <c r="K7" s="4">
         <v>12588110083</v>
       </c>
-      <c r="L7" s="17">
+      <c r="L7" s="13">
         <v>41907</v>
       </c>
-      <c r="M7" s="17"/>
-      <c r="N7" s="17">
+      <c r="M7" s="13"/>
+      <c r="N7" s="13">
         <v>42821</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="13">
         <v>42226</v>
       </c>
       <c r="P7" s="4">
@@ -14993,16 +15392,16 @@
     </row>
     <row r="8" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>349</v>
@@ -15013,8 +15412,8 @@
       <c r="G8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="19" t="s">
-        <v>458</v>
+      <c r="H8" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I8" s="4">
         <v>14996018261</v>
@@ -15025,14 +15424,14 @@
       <c r="K8" s="4">
         <v>14996018261</v>
       </c>
-      <c r="L8" s="17">
+      <c r="L8" s="13">
         <v>41376</v>
       </c>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17">
+      <c r="M8" s="13"/>
+      <c r="N8" s="13">
         <v>41380</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="13">
         <v>41676</v>
       </c>
       <c r="P8" s="4">
@@ -15045,28 +15444,28 @@
     </row>
     <row r="9" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="19" t="s">
-        <v>453</v>
+      <c r="H9" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I9" s="4">
         <v>14913362760</v>
@@ -15077,14 +15476,14 @@
       <c r="K9" s="4">
         <v>14913362760</v>
       </c>
-      <c r="L9" s="17">
+      <c r="L9" s="13">
         <v>41907</v>
       </c>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17">
+      <c r="M9" s="13"/>
+      <c r="N9" s="13">
         <v>42990</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="13">
         <v>42023</v>
       </c>
       <c r="P9" s="4">
@@ -15097,28 +15496,28 @@
     </row>
     <row r="10" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>528</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H10" s="19" t="s">
-        <v>444</v>
+      <c r="H10" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I10" s="4">
         <v>7037696704</v>
@@ -15129,14 +15528,14 @@
       <c r="K10" s="4">
         <v>7738617014</v>
       </c>
-      <c r="L10" s="17">
+      <c r="L10" s="13">
         <v>41907</v>
       </c>
-      <c r="M10" s="17"/>
-      <c r="N10" s="17">
+      <c r="M10" s="13"/>
+      <c r="N10" s="13">
         <v>42006</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="13">
         <v>42060</v>
       </c>
       <c r="P10" s="4">
@@ -15149,16 +15548,16 @@
     </row>
     <row r="11" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>533</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>66</v>
@@ -15170,7 +15569,7 @@
         <v>57</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I11" s="4">
         <v>13800000000</v>
@@ -15181,14 +15580,14 @@
       <c r="K11" s="4">
         <v>15951400000</v>
       </c>
-      <c r="L11" s="17">
+      <c r="L11" s="13">
         <v>41789</v>
       </c>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17">
+      <c r="M11" s="13"/>
+      <c r="N11" s="13">
         <v>44936</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="13">
         <v>42128</v>
       </c>
       <c r="P11" s="4">
@@ -15201,28 +15600,28 @@
     </row>
     <row r="12" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="19" t="s">
-        <v>444</v>
+      <c r="H12" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I12" s="4">
         <v>16094650077</v>
@@ -15233,14 +15632,14 @@
       <c r="K12" s="4">
         <v>16407417777</v>
       </c>
-      <c r="L12" s="17">
+      <c r="L12" s="13">
         <v>43389</v>
       </c>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17">
+      <c r="M12" s="13"/>
+      <c r="N12" s="13">
         <v>43495</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="13">
         <v>43865</v>
       </c>
       <c r="P12" s="4">
@@ -15253,28 +15652,28 @@
     </row>
     <row r="13" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="I13" s="4">
         <v>54337268559</v>
@@ -15285,14 +15684,14 @@
       <c r="K13" s="4">
         <v>62896276985</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="13">
         <v>43165</v>
       </c>
-      <c r="M13" s="17"/>
-      <c r="N13" s="17">
+      <c r="M13" s="13"/>
+      <c r="N13" s="13">
         <v>43171</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="13">
         <v>43410</v>
       </c>
       <c r="P13" s="4">
@@ -15305,28 +15704,28 @@
     </row>
     <row r="14" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>551</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="20" t="s">
-        <v>444</v>
+      <c r="H14" s="16" t="s">
+        <v>442</v>
       </c>
       <c r="I14" s="4">
         <v>5261488233</v>
@@ -15337,14 +15736,14 @@
       <c r="K14" s="4">
         <v>5361488233</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="13">
         <v>43636</v>
       </c>
-      <c r="M14" s="17"/>
-      <c r="N14" s="17">
+      <c r="M14" s="13"/>
+      <c r="N14" s="13">
         <v>43955</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="13">
         <v>44138</v>
       </c>
       <c r="P14" s="4">
@@ -15357,16 +15756,16 @@
     </row>
     <row r="15" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>135</v>
@@ -15377,8 +15776,8 @@
       <c r="G15" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H15" s="19" t="s">
-        <v>444</v>
+      <c r="H15" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I15" s="4">
         <v>8077068482</v>
@@ -15389,14 +15788,14 @@
       <c r="K15" s="4">
         <v>8077068482</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="13">
         <v>43829</v>
       </c>
-      <c r="M15" s="17"/>
-      <c r="N15" s="17">
+      <c r="M15" s="13"/>
+      <c r="N15" s="13">
         <v>43843</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="13">
         <v>44042</v>
       </c>
       <c r="P15" s="4">
@@ -15409,16 +15808,16 @@
     </row>
     <row r="16" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>66</v>
@@ -15430,7 +15829,7 @@
         <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I16" s="4">
         <v>7750000000</v>
@@ -15441,14 +15840,14 @@
       <c r="K16" s="4">
         <v>7750000000</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L16" s="13">
         <v>43781</v>
       </c>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17">
+      <c r="M16" s="13"/>
+      <c r="N16" s="13">
         <v>43809</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="13">
         <v>43831</v>
       </c>
       <c r="P16" s="4">
@@ -15461,16 +15860,16 @@
     </row>
     <row r="17" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>66</v>
@@ -15482,7 +15881,7 @@
         <v>68</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I17" s="4">
         <v>1027100000</v>
@@ -15493,14 +15892,14 @@
       <c r="K17" s="4">
         <v>1127675000</v>
       </c>
-      <c r="L17" s="17">
+      <c r="L17" s="13">
         <v>43781</v>
       </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17">
+      <c r="M17" s="13"/>
+      <c r="N17" s="13">
         <v>43948</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="13">
         <v>44223</v>
       </c>
       <c r="P17" s="4">
@@ -15513,16 +15912,16 @@
     </row>
     <row r="18" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>565</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>66</v>
@@ -15534,7 +15933,7 @@
         <v>68</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I18" s="4">
         <v>9491491960</v>
@@ -15545,14 +15944,14 @@
       <c r="K18" s="4">
         <v>9935241960</v>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="13">
         <v>43781</v>
       </c>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17">
+      <c r="M18" s="13"/>
+      <c r="N18" s="13">
         <v>43872</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="13">
         <v>43979</v>
       </c>
       <c r="P18" s="4">
@@ -15565,16 +15964,16 @@
     </row>
     <row r="19" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>572</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>66</v>
@@ -15586,7 +15985,7 @@
         <v>68</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I19" s="4">
         <v>4024500000</v>
@@ -15597,14 +15996,14 @@
       <c r="K19" s="4">
         <v>4202000000</v>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="13">
         <v>43781</v>
       </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="17">
+      <c r="M19" s="13"/>
+      <c r="N19" s="13">
         <v>43812</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="13">
         <v>43958</v>
       </c>
       <c r="P19" s="4">
@@ -15617,16 +16016,16 @@
     </row>
     <row r="20" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>576</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>66</v>
@@ -15638,7 +16037,7 @@
         <v>68</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I20" s="4">
         <v>20233937500</v>
@@ -15649,14 +16048,14 @@
       <c r="K20" s="4">
         <v>21162064500</v>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="13">
         <v>43781</v>
       </c>
-      <c r="M20" s="17"/>
-      <c r="N20" s="17">
+      <c r="M20" s="13"/>
+      <c r="N20" s="13">
         <v>43902</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="13">
         <v>43943</v>
       </c>
       <c r="P20" s="4">
@@ -15669,16 +16068,16 @@
     </row>
     <row r="21" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>66</v>
@@ -15690,7 +16089,7 @@
         <v>68</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I21" s="4">
         <v>6524500000</v>
@@ -15701,14 +16100,14 @@
       <c r="K21" s="4">
         <v>6524500000</v>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="13">
         <v>43781</v>
       </c>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17">
+      <c r="M21" s="13"/>
+      <c r="N21" s="13">
         <v>43969</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="13">
         <v>43949</v>
       </c>
       <c r="P21" s="4">
@@ -15721,16 +16120,16 @@
     </row>
     <row r="22" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>581</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>584</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>66</v>
@@ -15742,7 +16141,7 @@
         <v>68</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I22" s="4">
         <v>2500000000</v>
@@ -15753,14 +16152,14 @@
       <c r="K22" s="4">
         <v>2588750000</v>
       </c>
-      <c r="L22" s="17">
+      <c r="L22" s="13">
         <v>43812</v>
       </c>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17">
+      <c r="M22" s="13"/>
+      <c r="N22" s="13">
         <v>43902</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="13">
         <v>43938</v>
       </c>
       <c r="P22" s="4">
@@ -15773,16 +16172,16 @@
     </row>
     <row r="23" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>588</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>66</v>
@@ -15794,7 +16193,7 @@
         <v>68</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I23" s="4">
         <v>3500000000</v>
@@ -15805,14 +16204,14 @@
       <c r="K23" s="4">
         <v>4154449000</v>
       </c>
-      <c r="L23" s="17">
+      <c r="L23" s="13">
         <v>43812</v>
       </c>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17">
+      <c r="M23" s="13"/>
+      <c r="N23" s="13">
         <v>43864</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="13">
         <v>44742</v>
       </c>
       <c r="P23" s="4">
@@ -15825,16 +16224,16 @@
     </row>
     <row r="24" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>589</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>592</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>66</v>
@@ -15846,7 +16245,7 @@
         <v>68</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I24" s="4">
         <v>3250000000</v>
@@ -15857,14 +16256,14 @@
       <c r="K24" s="4">
         <v>3477139308</v>
       </c>
-      <c r="L24" s="17">
+      <c r="L24" s="13">
         <v>43798</v>
       </c>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17">
+      <c r="M24" s="13"/>
+      <c r="N24" s="13">
         <v>43882</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="13">
         <v>43957</v>
       </c>
       <c r="P24" s="4">
@@ -15877,16 +16276,16 @@
     </row>
     <row r="25" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>596</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>66</v>
@@ -15898,7 +16297,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I25" s="4">
         <v>946000000</v>
@@ -15909,14 +16308,14 @@
       <c r="K25" s="4">
         <v>990375000</v>
       </c>
-      <c r="L25" s="17">
+      <c r="L25" s="13">
         <v>43812</v>
       </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17">
+      <c r="M25" s="13"/>
+      <c r="N25" s="13">
         <v>44043</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="13">
         <v>43991</v>
       </c>
       <c r="P25" s="4">
@@ -15929,16 +16328,16 @@
     </row>
     <row r="26" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>597</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>66</v>
@@ -15950,7 +16349,7 @@
         <v>68</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I26" s="4">
         <v>1943625000</v>
@@ -15961,14 +16360,14 @@
       <c r="K26" s="4">
         <v>2032375000</v>
       </c>
-      <c r="L26" s="17">
+      <c r="L26" s="13">
         <v>43830</v>
       </c>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17">
+      <c r="M26" s="13"/>
+      <c r="N26" s="13">
         <v>44025</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="13">
         <v>44046</v>
       </c>
       <c r="P26" s="4">
@@ -15981,16 +16380,16 @@
     </row>
     <row r="27" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>601</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>66</v>
@@ -16002,7 +16401,7 @@
         <v>68</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I27" s="4">
         <v>1999999962.27</v>
@@ -16013,14 +16412,14 @@
       <c r="K27" s="4">
         <v>2667064893.9299998</v>
       </c>
-      <c r="L27" s="17">
+      <c r="L27" s="13">
         <v>44111</v>
       </c>
-      <c r="M27" s="17"/>
-      <c r="N27" s="17">
+      <c r="M27" s="13"/>
+      <c r="N27" s="13">
         <v>44319</v>
       </c>
-      <c r="O27" s="17">
+      <c r="O27" s="13">
         <v>44448</v>
       </c>
       <c r="P27" s="4">
@@ -16033,28 +16432,28 @@
     </row>
     <row r="28" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>605</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>608</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="19" t="s">
-        <v>444</v>
+      <c r="H28" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I28" s="4">
         <v>729826686</v>
@@ -16065,14 +16464,14 @@
       <c r="K28" s="4">
         <v>1195561547</v>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="13">
         <v>43825</v>
       </c>
-      <c r="M28" s="17"/>
-      <c r="N28" s="17">
+      <c r="M28" s="13"/>
+      <c r="N28" s="13">
         <v>43875</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="13">
         <v>44074</v>
       </c>
       <c r="P28" s="4">
@@ -16085,28 +16484,28 @@
     </row>
     <row r="29" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>253</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="19" t="s">
-        <v>444</v>
+      <c r="H29" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I29" s="4">
         <v>37141732473</v>
@@ -16117,14 +16516,14 @@
       <c r="K29" s="4">
         <v>37141732473</v>
       </c>
-      <c r="L29" s="17">
+      <c r="L29" s="13">
         <v>43812</v>
       </c>
-      <c r="M29" s="17"/>
-      <c r="N29" s="17">
+      <c r="M29" s="13"/>
+      <c r="N29" s="13">
         <v>43817</v>
       </c>
-      <c r="O29" s="17">
+      <c r="O29" s="13">
         <v>44228</v>
       </c>
       <c r="P29" s="4">
@@ -16137,16 +16536,16 @@
     </row>
     <row r="30" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>92</v>
@@ -16157,8 +16556,8 @@
       <c r="G30" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H30" s="20" t="s">
-        <v>453</v>
+      <c r="H30" s="16" t="s">
+        <v>451</v>
       </c>
       <c r="I30" s="4">
         <v>22507978719</v>
@@ -16169,14 +16568,14 @@
       <c r="K30" s="4">
         <v>22507978719</v>
       </c>
-      <c r="L30" s="17">
+      <c r="L30" s="13">
         <v>44536</v>
       </c>
-      <c r="M30" s="17"/>
-      <c r="N30" s="17">
+      <c r="M30" s="13"/>
+      <c r="N30" s="13">
         <v>44683</v>
       </c>
-      <c r="O30" s="17">
+      <c r="O30" s="13">
         <v>44837</v>
       </c>
       <c r="P30" s="4">
@@ -16189,28 +16588,28 @@
     </row>
     <row r="31" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>617</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>620</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I31" s="4">
         <v>38700180208.470001</v>
@@ -16221,14 +16620,14 @@
       <c r="K31" s="4">
         <v>38936180208.470001</v>
       </c>
-      <c r="L31" s="17">
+      <c r="L31" s="13">
         <v>44195</v>
       </c>
-      <c r="M31" s="17"/>
-      <c r="N31" s="17">
+      <c r="M31" s="13"/>
+      <c r="N31" s="13">
         <v>44952</v>
       </c>
-      <c r="O31" s="17">
+      <c r="O31" s="13">
         <v>44595</v>
       </c>
       <c r="P31" s="4">
@@ -16241,16 +16640,16 @@
     </row>
     <row r="32" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>92</v>
@@ -16261,8 +16660,8 @@
       <c r="G32" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H32" s="19" t="s">
-        <v>444</v>
+      <c r="H32" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I32" s="4">
         <v>75409582200</v>
@@ -16273,14 +16672,14 @@
       <c r="K32" s="4">
         <v>75409582200</v>
       </c>
-      <c r="L32" s="17">
+      <c r="L32" s="13">
         <v>44195</v>
       </c>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17">
+      <c r="M32" s="13"/>
+      <c r="N32" s="13">
         <v>44326</v>
       </c>
-      <c r="O32" s="17">
+      <c r="O32" s="13">
         <v>44445</v>
       </c>
       <c r="P32" s="4">
@@ -16293,16 +16692,16 @@
     </row>
     <row r="33" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>66</v>
@@ -16314,7 +16713,7 @@
         <v>57</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I33" s="4">
         <v>1998000000</v>
@@ -16325,14 +16724,14 @@
       <c r="K33" s="4">
         <v>2414100000</v>
       </c>
-      <c r="L33" s="17">
+      <c r="L33" s="13">
         <v>43950</v>
       </c>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17">
+      <c r="M33" s="13"/>
+      <c r="N33" s="13">
         <v>44001</v>
       </c>
-      <c r="O33" s="17">
+      <c r="O33" s="13">
         <v>44133</v>
       </c>
       <c r="P33" s="4">
@@ -16345,16 +16744,16 @@
     </row>
     <row r="34" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>66</v>
@@ -16366,7 +16765,7 @@
         <v>57</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I34" s="4">
         <v>1999306318</v>
@@ -16377,14 +16776,14 @@
       <c r="K34" s="4">
         <v>3490315624.7199998</v>
       </c>
-      <c r="L34" s="17">
+      <c r="L34" s="13">
         <v>43924</v>
       </c>
-      <c r="M34" s="17"/>
-      <c r="N34" s="17">
+      <c r="M34" s="13"/>
+      <c r="N34" s="13">
         <v>44001</v>
       </c>
-      <c r="O34" s="17">
+      <c r="O34" s="13">
         <v>44118</v>
       </c>
       <c r="P34" s="4">
@@ -16397,16 +16796,16 @@
     </row>
     <row r="35" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>631</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>66</v>
@@ -16418,7 +16817,7 @@
         <v>207</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I35" s="4">
         <v>1999910691</v>
@@ -16429,14 +16828,14 @@
       <c r="K35" s="4">
         <v>3839181953</v>
       </c>
-      <c r="L35" s="17">
+      <c r="L35" s="13">
         <v>44078</v>
       </c>
-      <c r="M35" s="17"/>
-      <c r="N35" s="17">
+      <c r="M35" s="13"/>
+      <c r="N35" s="13">
         <v>45385</v>
       </c>
-      <c r="O35" s="17">
+      <c r="O35" s="13">
         <v>44252</v>
       </c>
       <c r="P35" s="4">
@@ -16449,16 +16848,16 @@
     </row>
     <row r="36" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>635</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>66</v>
@@ -16470,7 +16869,7 @@
         <v>68</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I36" s="4">
         <v>1999433630</v>
@@ -16481,14 +16880,14 @@
       <c r="K36" s="4">
         <v>2930484800</v>
       </c>
-      <c r="L36" s="17">
+      <c r="L36" s="13">
         <v>43924</v>
       </c>
-      <c r="M36" s="17"/>
-      <c r="N36" s="17">
+      <c r="M36" s="13"/>
+      <c r="N36" s="13">
         <v>44106</v>
       </c>
-      <c r="O36" s="17">
+      <c r="O36" s="13">
         <v>44106</v>
       </c>
       <c r="P36" s="4">
@@ -16501,16 +16900,16 @@
     </row>
     <row r="37" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>639</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>66</v>
@@ -16522,7 +16921,7 @@
         <v>68</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I37" s="4">
         <v>1999976897</v>
@@ -16533,14 +16932,14 @@
       <c r="K37" s="4">
         <v>2612747413</v>
       </c>
-      <c r="L37" s="17">
+      <c r="L37" s="13">
         <v>44078</v>
       </c>
-      <c r="M37" s="17"/>
-      <c r="N37" s="17">
+      <c r="M37" s="13"/>
+      <c r="N37" s="13">
         <v>44179</v>
       </c>
-      <c r="O37" s="17">
+      <c r="O37" s="13">
         <v>44229</v>
       </c>
       <c r="P37" s="4">
@@ -16553,16 +16952,16 @@
     </row>
     <row r="38" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>643</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>66</v>
@@ -16574,7 +16973,7 @@
         <v>57</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I38" s="4">
         <v>1272365336</v>
@@ -16585,12 +16984,12 @@
       <c r="K38" s="4">
         <v>1915671336</v>
       </c>
-      <c r="L38" s="17">
+      <c r="L38" s="13">
         <v>44078</v>
       </c>
-      <c r="M38" s="17"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="17">
+      <c r="M38" s="13"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="13">
         <v>44421</v>
       </c>
       <c r="P38" s="4">
@@ -16603,16 +17002,16 @@
     </row>
     <row r="39" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>647</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>650</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>66</v>
@@ -16624,7 +17023,7 @@
         <v>68</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I39" s="4">
         <v>1999833255</v>
@@ -16635,14 +17034,14 @@
       <c r="K39" s="4">
         <v>2948047175</v>
       </c>
-      <c r="L39" s="17">
+      <c r="L39" s="13">
         <v>44078</v>
       </c>
-      <c r="M39" s="17"/>
-      <c r="N39" s="17">
+      <c r="M39" s="13"/>
+      <c r="N39" s="13">
         <v>44113</v>
       </c>
-      <c r="O39" s="17">
+      <c r="O39" s="13">
         <v>44408</v>
       </c>
       <c r="P39" s="4">
@@ -16655,16 +17054,16 @@
     </row>
     <row r="40" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>651</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>66</v>
@@ -16676,7 +17075,7 @@
         <v>57</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I40" s="4">
         <v>6559568533</v>
@@ -16687,14 +17086,14 @@
       <c r="K40" s="4">
         <v>6848145520</v>
       </c>
-      <c r="L40" s="17">
+      <c r="L40" s="13">
         <v>44159</v>
       </c>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17">
+      <c r="M40" s="13"/>
+      <c r="N40" s="13">
         <v>44337</v>
       </c>
-      <c r="O40" s="17">
+      <c r="O40" s="13">
         <v>44410</v>
       </c>
       <c r="P40" s="4">
@@ -16707,16 +17106,16 @@
     </row>
     <row r="41" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>66</v>
@@ -16728,7 +17127,7 @@
         <v>68</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I41" s="4">
         <v>1998890586.73</v>
@@ -16739,14 +17138,14 @@
       <c r="K41" s="4">
         <v>2898886012.6100001</v>
       </c>
-      <c r="L41" s="17">
+      <c r="L41" s="13">
         <v>44078</v>
       </c>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17">
+      <c r="M41" s="13"/>
+      <c r="N41" s="13">
         <v>44386</v>
       </c>
-      <c r="O41" s="17">
+      <c r="O41" s="13">
         <v>44335</v>
       </c>
       <c r="P41" s="4">
@@ -16759,16 +17158,16 @@
     </row>
     <row r="42" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>66</v>
@@ -16780,7 +17179,7 @@
         <v>207</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I42" s="4">
         <v>5347795060</v>
@@ -16791,14 +17190,14 @@
       <c r="K42" s="4">
         <v>6581633763</v>
       </c>
-      <c r="L42" s="17">
+      <c r="L42" s="13">
         <v>43966</v>
       </c>
-      <c r="M42" s="17"/>
-      <c r="N42" s="17">
+      <c r="M42" s="13"/>
+      <c r="N42" s="13">
         <v>43978</v>
       </c>
-      <c r="O42" s="17">
+      <c r="O42" s="13">
         <v>44097</v>
       </c>
       <c r="P42" s="4">
@@ -16810,17 +17209,17 @@
       <c r="R42" s="3"/>
     </row>
     <row r="43" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="18" t="s">
-        <v>661</v>
+      <c r="A43" s="14" t="s">
+        <v>658</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>66</v>
@@ -16832,7 +17231,7 @@
         <v>68</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I43" s="4">
         <v>1965295196.9400001</v>
@@ -16843,12 +17242,12 @@
       <c r="K43" s="4">
         <v>4131804023.6700001</v>
       </c>
-      <c r="L43" s="17">
+      <c r="L43" s="13">
         <v>44078</v>
       </c>
-      <c r="M43" s="17"/>
-      <c r="N43" s="17"/>
-      <c r="O43" s="17">
+      <c r="M43" s="13"/>
+      <c r="N43" s="13"/>
+      <c r="O43" s="13">
         <v>44421</v>
       </c>
       <c r="P43" s="4">
@@ -16861,16 +17260,16 @@
     </row>
     <row r="44" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>66</v>
@@ -16882,7 +17281,7 @@
         <v>68</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I44" s="4">
         <v>8764697664</v>
@@ -16893,14 +17292,14 @@
       <c r="K44" s="4">
         <v>10308364564</v>
       </c>
-      <c r="L44" s="17">
+      <c r="L44" s="13">
         <v>44432</v>
       </c>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17">
+      <c r="M44" s="13"/>
+      <c r="N44" s="13">
         <v>44480</v>
       </c>
-      <c r="O44" s="17">
+      <c r="O44" s="13">
         <v>44502</v>
       </c>
       <c r="P44" s="4">
@@ -16913,16 +17312,16 @@
     </row>
     <row r="45" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>667</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>670</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>66</v>
@@ -16934,7 +17333,7 @@
         <v>57</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I45" s="4">
         <v>1349000868</v>
@@ -16945,14 +17344,14 @@
       <c r="K45" s="4">
         <v>1409240868</v>
       </c>
-      <c r="L45" s="17">
+      <c r="L45" s="13">
         <v>44111</v>
       </c>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17">
+      <c r="M45" s="13"/>
+      <c r="N45" s="13">
         <v>44568</v>
       </c>
-      <c r="O45" s="17">
+      <c r="O45" s="13">
         <v>44594</v>
       </c>
       <c r="P45" s="4">
@@ -16965,16 +17364,16 @@
     </row>
     <row r="46" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>674</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>66</v>
@@ -16986,7 +17385,7 @@
         <v>57</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I46" s="4">
         <v>3106000000</v>
@@ -16997,14 +17396,14 @@
       <c r="K46" s="4">
         <v>3156000000</v>
       </c>
-      <c r="L46" s="17">
+      <c r="L46" s="13">
         <v>44159</v>
       </c>
-      <c r="M46" s="17"/>
-      <c r="N46" s="17">
+      <c r="M46" s="13"/>
+      <c r="N46" s="13">
         <v>44235</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="13">
         <v>44327</v>
       </c>
       <c r="P46" s="4">
@@ -17017,16 +17416,16 @@
     </row>
     <row r="47" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>66</v>
@@ -17038,7 +17437,7 @@
         <v>57</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I47" s="4">
         <v>8995267958.5699997</v>
@@ -17049,14 +17448,14 @@
       <c r="K47" s="4">
         <v>9177414454.0599995</v>
       </c>
-      <c r="L47" s="17">
+      <c r="L47" s="13">
         <v>44159</v>
       </c>
-      <c r="M47" s="17"/>
-      <c r="N47" s="17">
+      <c r="M47" s="13"/>
+      <c r="N47" s="13">
         <v>44263</v>
       </c>
-      <c r="O47" s="17">
+      <c r="O47" s="13">
         <v>44365</v>
       </c>
       <c r="P47" s="4">
@@ -17069,16 +17468,16 @@
     </row>
     <row r="48" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>681</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>66</v>
@@ -17090,7 +17489,7 @@
         <v>68</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I48" s="4">
         <v>6750000000</v>
@@ -17101,14 +17500,14 @@
       <c r="K48" s="4">
         <v>6920233499</v>
       </c>
-      <c r="L48" s="17">
+      <c r="L48" s="13">
         <v>44330</v>
       </c>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17">
+      <c r="M48" s="13"/>
+      <c r="N48" s="13">
         <v>44362</v>
       </c>
-      <c r="O48" s="17">
+      <c r="O48" s="13">
         <v>44404</v>
       </c>
       <c r="P48" s="4">
@@ -17121,16 +17520,16 @@
     </row>
     <row r="49" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>66</v>
@@ -17142,7 +17541,7 @@
         <v>68</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I49" s="4">
         <v>1998157618.8800001</v>
@@ -17153,14 +17552,14 @@
       <c r="K49" s="4">
         <v>2467892722.71</v>
       </c>
-      <c r="L49" s="17">
+      <c r="L49" s="13">
         <v>44159</v>
       </c>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17">
+      <c r="M49" s="13"/>
+      <c r="N49" s="13">
         <v>44259</v>
       </c>
-      <c r="O49" s="17">
+      <c r="O49" s="13">
         <v>44567</v>
       </c>
       <c r="P49" s="4">
@@ -17173,16 +17572,16 @@
     </row>
     <row r="50" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>66</v>
@@ -17194,7 +17593,7 @@
         <v>68</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I50" s="4">
         <v>2000000000</v>
@@ -17205,14 +17604,14 @@
       <c r="K50" s="4">
         <v>2474185221</v>
       </c>
-      <c r="L50" s="17">
+      <c r="L50" s="13">
         <v>44159</v>
       </c>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17">
+      <c r="M50" s="13"/>
+      <c r="N50" s="13">
         <v>44246</v>
       </c>
-      <c r="O50" s="17">
+      <c r="O50" s="13">
         <v>44337</v>
       </c>
       <c r="P50" s="4">
@@ -17225,16 +17624,16 @@
     </row>
     <row r="51" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>691</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>66</v>
@@ -17246,7 +17645,7 @@
         <v>68</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I51" s="4">
         <v>5335769261</v>
@@ -17257,12 +17656,12 @@
       <c r="K51" s="4">
         <v>5913070114</v>
       </c>
-      <c r="L51" s="17">
+      <c r="L51" s="13">
         <v>44348</v>
       </c>
-      <c r="M51" s="17"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="17">
+      <c r="M51" s="13"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="13">
         <v>44427</v>
       </c>
       <c r="P51" s="4">
@@ -17275,16 +17674,16 @@
     </row>
     <row r="52" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>66</v>
@@ -17296,7 +17695,7 @@
         <v>68</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I52" s="4">
         <v>4940449374</v>
@@ -17307,14 +17706,14 @@
       <c r="K52" s="4">
         <v>5203930460</v>
       </c>
-      <c r="L52" s="17">
+      <c r="L52" s="13">
         <v>44432</v>
       </c>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17">
+      <c r="M52" s="13"/>
+      <c r="N52" s="13">
         <v>44480</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O52" s="13">
         <v>44517</v>
       </c>
       <c r="P52" s="4">
@@ -17327,16 +17726,16 @@
     </row>
     <row r="53" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>66</v>
@@ -17348,7 +17747,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I53" s="4">
         <v>1999924866</v>
@@ -17359,14 +17758,14 @@
       <c r="K53" s="4">
         <v>3559208215</v>
       </c>
-      <c r="L53" s="17">
+      <c r="L53" s="13">
         <v>44159</v>
       </c>
-      <c r="M53" s="17"/>
-      <c r="N53" s="17">
+      <c r="M53" s="13"/>
+      <c r="N53" s="13">
         <v>44246</v>
       </c>
-      <c r="O53" s="17">
+      <c r="O53" s="13">
         <v>44341</v>
       </c>
       <c r="P53" s="4">
@@ -17379,16 +17778,16 @@
     </row>
     <row r="54" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>66</v>
@@ -17400,7 +17799,7 @@
         <v>68</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I54" s="4">
         <v>3591118773</v>
@@ -17411,14 +17810,14 @@
       <c r="K54" s="4">
         <v>3768618773</v>
       </c>
-      <c r="L54" s="17">
+      <c r="L54" s="13">
         <v>44330</v>
       </c>
-      <c r="M54" s="17"/>
-      <c r="N54" s="17">
+      <c r="M54" s="13"/>
+      <c r="N54" s="13">
         <v>44393</v>
       </c>
-      <c r="O54" s="17">
+      <c r="O54" s="13">
         <v>44418</v>
       </c>
       <c r="P54" s="4">
@@ -17431,16 +17830,16 @@
     </row>
     <row r="55" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>66</v>
@@ -17452,7 +17851,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I55" s="4">
         <v>2000000000</v>
@@ -17463,14 +17862,14 @@
       <c r="K55" s="4">
         <v>3560969376</v>
       </c>
-      <c r="L55" s="17">
+      <c r="L55" s="13">
         <v>44159</v>
       </c>
-      <c r="M55" s="17"/>
-      <c r="N55" s="17">
+      <c r="M55" s="13"/>
+      <c r="N55" s="13">
         <v>44246</v>
       </c>
-      <c r="O55" s="17">
+      <c r="O55" s="13">
         <v>44337</v>
       </c>
       <c r="P55" s="4">
@@ -17483,16 +17882,16 @@
     </row>
     <row r="56" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>66</v>
@@ -17504,7 +17903,7 @@
         <v>68</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I56" s="4">
         <v>1999112638.9200001</v>
@@ -17515,14 +17914,14 @@
       <c r="K56" s="4">
         <v>2856350066.9200001</v>
       </c>
-      <c r="L56" s="17">
+      <c r="L56" s="13">
         <v>44159</v>
       </c>
-      <c r="M56" s="17"/>
-      <c r="N56" s="17">
+      <c r="M56" s="13"/>
+      <c r="N56" s="13">
         <v>44259</v>
       </c>
-      <c r="O56" s="17">
+      <c r="O56" s="13">
         <v>44474</v>
       </c>
       <c r="P56" s="4">
@@ -17535,16 +17934,16 @@
     </row>
     <row r="57" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>707</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>710</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>66</v>
@@ -17556,7 +17955,7 @@
         <v>68</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I57" s="4">
         <v>7500000000</v>
@@ -17567,14 +17966,14 @@
       <c r="K57" s="4">
         <v>7500000000</v>
       </c>
-      <c r="L57" s="17">
+      <c r="L57" s="13">
         <v>44348</v>
       </c>
-      <c r="M57" s="17"/>
-      <c r="N57" s="17">
+      <c r="M57" s="13"/>
+      <c r="N57" s="13">
         <v>44379</v>
       </c>
-      <c r="O57" s="17">
+      <c r="O57" s="13">
         <v>44407</v>
       </c>
       <c r="P57" s="4">
@@ -17587,16 +17986,16 @@
     </row>
     <row r="58" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>66</v>
@@ -17608,7 +18007,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I58" s="4">
         <v>1999803848</v>
@@ -17619,14 +18018,14 @@
       <c r="K58" s="4">
         <v>3394230296</v>
       </c>
-      <c r="L58" s="17">
+      <c r="L58" s="13">
         <v>44159</v>
       </c>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17">
+      <c r="M58" s="13"/>
+      <c r="N58" s="13">
         <v>44320</v>
       </c>
-      <c r="O58" s="17">
+      <c r="O58" s="13">
         <v>44467</v>
       </c>
       <c r="P58" s="4">
@@ -17639,16 +18038,16 @@
     </row>
     <row r="59" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>66</v>
@@ -17660,7 +18059,7 @@
         <v>68</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="I59" s="4">
         <v>1738785560</v>
@@ -17671,14 +18070,14 @@
       <c r="K59" s="4">
         <v>2346358031</v>
       </c>
-      <c r="L59" s="17">
+      <c r="L59" s="13">
         <v>44159</v>
       </c>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17">
+      <c r="M59" s="13"/>
+      <c r="N59" s="13">
         <v>44309</v>
       </c>
-      <c r="O59" s="17">
+      <c r="O59" s="13">
         <v>44337</v>
       </c>
       <c r="P59" s="4">
@@ -17691,16 +18090,16 @@
     </row>
     <row r="60" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>66</v>
@@ -17712,7 +18111,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I60" s="4">
         <v>1999000000</v>
@@ -17723,14 +18122,14 @@
       <c r="K60" s="4">
         <v>2511000000</v>
       </c>
-      <c r="L60" s="17">
+      <c r="L60" s="13">
         <v>44159</v>
       </c>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17">
+      <c r="M60" s="13"/>
+      <c r="N60" s="13">
         <v>44246</v>
       </c>
-      <c r="O60" s="17">
+      <c r="O60" s="13">
         <v>44340</v>
       </c>
       <c r="P60" s="4">
@@ -17743,16 +18142,16 @@
     </row>
     <row r="61" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>720</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>723</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>66</v>
@@ -17764,7 +18163,7 @@
         <v>68</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I61" s="4">
         <v>1775630700</v>
@@ -17775,14 +18174,14 @@
       <c r="K61" s="4">
         <v>1894532100</v>
       </c>
-      <c r="L61" s="17">
+      <c r="L61" s="13">
         <v>44368</v>
       </c>
-      <c r="M61" s="17"/>
-      <c r="N61" s="17">
+      <c r="M61" s="13"/>
+      <c r="N61" s="13">
         <v>44924</v>
       </c>
-      <c r="O61" s="17">
+      <c r="O61" s="13">
         <v>44456</v>
       </c>
       <c r="P61" s="4">
@@ -17795,16 +18194,16 @@
     </row>
     <row r="62" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>66</v>
@@ -17816,7 +18215,7 @@
         <v>68</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I62" s="4">
         <v>750000000</v>
@@ -17827,14 +18226,14 @@
       <c r="K62" s="4">
         <v>918904760</v>
       </c>
-      <c r="L62" s="17">
+      <c r="L62" s="13">
         <v>44377</v>
       </c>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17">
+      <c r="M62" s="13"/>
+      <c r="N62" s="13">
         <v>44440</v>
       </c>
-      <c r="O62" s="17">
+      <c r="O62" s="13">
         <v>44589</v>
       </c>
       <c r="P62" s="4">
@@ -17847,16 +18246,16 @@
     </row>
     <row r="63" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>730</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>66</v>
@@ -17868,7 +18267,7 @@
         <v>68</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I63" s="4">
         <v>2828005287</v>
@@ -17879,14 +18278,14 @@
       <c r="K63" s="4">
         <v>3069617150</v>
       </c>
-      <c r="L63" s="17">
+      <c r="L63" s="13">
         <v>44348</v>
       </c>
-      <c r="M63" s="17"/>
-      <c r="N63" s="17">
+      <c r="M63" s="13"/>
+      <c r="N63" s="13">
         <v>44924</v>
       </c>
-      <c r="O63" s="17">
+      <c r="O63" s="13">
         <v>44410</v>
       </c>
       <c r="P63" s="4">
@@ -17899,28 +18298,28 @@
     </row>
     <row r="64" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H64" s="19" t="s">
-        <v>458</v>
+      <c r="H64" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I64" s="4">
         <v>69047758069</v>
@@ -17931,14 +18330,14 @@
       <c r="K64" s="4">
         <v>69047758069</v>
       </c>
-      <c r="L64" s="17">
+      <c r="L64" s="13">
         <v>44551</v>
       </c>
-      <c r="M64" s="17"/>
-      <c r="N64" s="17">
+      <c r="M64" s="13"/>
+      <c r="N64" s="13">
         <v>44652</v>
       </c>
-      <c r="O64" s="17">
+      <c r="O64" s="13">
         <v>44810</v>
       </c>
       <c r="P64" s="4">
@@ -17951,16 +18350,16 @@
     </row>
     <row r="65" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>66</v>
@@ -17972,7 +18371,7 @@
         <v>68</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I65" s="4">
         <v>17635937500</v>
@@ -17983,14 +18382,14 @@
       <c r="K65" s="4">
         <v>18418143500</v>
       </c>
-      <c r="L65" s="17">
+      <c r="L65" s="13">
         <v>44330</v>
       </c>
-      <c r="M65" s="17"/>
-      <c r="N65" s="17">
+      <c r="M65" s="13"/>
+      <c r="N65" s="13">
         <v>44365</v>
       </c>
-      <c r="O65" s="17">
+      <c r="O65" s="13">
         <v>44438</v>
       </c>
       <c r="P65" s="4">
@@ -18003,16 +18402,16 @@
     </row>
     <row r="66" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>66</v>
@@ -18024,7 +18423,7 @@
         <v>68</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I66" s="4">
         <v>1309600000</v>
@@ -18035,14 +18434,14 @@
       <c r="K66" s="4">
         <v>1519950000</v>
       </c>
-      <c r="L66" s="17">
+      <c r="L66" s="13">
         <v>44348</v>
       </c>
-      <c r="M66" s="17"/>
-      <c r="N66" s="17">
+      <c r="M66" s="13"/>
+      <c r="N66" s="13">
         <v>44924</v>
       </c>
-      <c r="O66" s="17">
+      <c r="O66" s="13">
         <v>44466</v>
       </c>
       <c r="P66" s="4">
@@ -18055,16 +18454,16 @@
     </row>
     <row r="67" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>66</v>
@@ -18076,7 +18475,7 @@
         <v>68</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I67" s="4">
         <v>2750000000</v>
@@ -18087,14 +18486,14 @@
       <c r="K67" s="4">
         <v>2775000000</v>
       </c>
-      <c r="L67" s="17">
+      <c r="L67" s="13">
         <v>44384</v>
       </c>
-      <c r="M67" s="17"/>
-      <c r="N67" s="17">
+      <c r="M67" s="13"/>
+      <c r="N67" s="13">
         <v>44429</v>
       </c>
-      <c r="O67" s="17">
+      <c r="O67" s="13">
         <v>44530</v>
       </c>
       <c r="P67" s="4">
@@ -18107,16 +18506,16 @@
     </row>
     <row r="68" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>66</v>
@@ -18128,7 +18527,7 @@
         <v>68</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I68" s="4">
         <v>1500000000</v>
@@ -18139,14 +18538,14 @@
       <c r="K68" s="4">
         <v>1853734000</v>
       </c>
-      <c r="L68" s="17">
+      <c r="L68" s="13">
         <v>44368</v>
       </c>
-      <c r="M68" s="17"/>
-      <c r="N68" s="17">
+      <c r="M68" s="13"/>
+      <c r="N68" s="13">
         <v>44368</v>
       </c>
-      <c r="O68" s="17">
+      <c r="O68" s="13">
         <v>44433</v>
       </c>
       <c r="P68" s="4">
@@ -18159,16 +18558,16 @@
     </row>
     <row r="69" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>66</v>
@@ -18180,7 +18579,7 @@
         <v>68</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I69" s="4">
         <v>1411798728</v>
@@ -18191,14 +18590,14 @@
       <c r="K69" s="4">
         <v>1532348536</v>
       </c>
-      <c r="L69" s="17">
+      <c r="L69" s="13">
         <v>44368</v>
       </c>
-      <c r="M69" s="17"/>
-      <c r="N69" s="17">
+      <c r="M69" s="13"/>
+      <c r="N69" s="13">
         <v>44925</v>
       </c>
-      <c r="O69" s="17">
+      <c r="O69" s="13">
         <v>44407</v>
       </c>
       <c r="P69" s="4">
@@ -18211,16 +18610,16 @@
     </row>
     <row r="70" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>750</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>66</v>
@@ -18232,7 +18631,7 @@
         <v>68</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I70" s="4">
         <v>1999997728</v>
@@ -18243,14 +18642,14 @@
       <c r="K70" s="4">
         <v>2663232448</v>
       </c>
-      <c r="L70" s="17">
+      <c r="L70" s="13">
         <v>44536</v>
       </c>
-      <c r="M70" s="17"/>
-      <c r="N70" s="17">
+      <c r="M70" s="13"/>
+      <c r="N70" s="13">
         <v>44533</v>
       </c>
-      <c r="O70" s="17">
+      <c r="O70" s="13">
         <v>44713</v>
       </c>
       <c r="P70" s="4">
@@ -18263,16 +18662,16 @@
     </row>
     <row r="71" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>66</v>
@@ -18284,7 +18683,7 @@
         <v>68</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I71" s="4">
         <v>1999667231.96</v>
@@ -18295,14 +18694,14 @@
       <c r="K71" s="4">
         <v>3035821023.1599998</v>
       </c>
-      <c r="L71" s="17">
+      <c r="L71" s="13">
         <v>44537</v>
       </c>
-      <c r="M71" s="17"/>
-      <c r="N71" s="17">
+      <c r="M71" s="13"/>
+      <c r="N71" s="13">
         <v>44606</v>
       </c>
-      <c r="O71" s="17">
+      <c r="O71" s="13">
         <v>44721</v>
       </c>
       <c r="P71" s="4">
@@ -18315,16 +18714,16 @@
     </row>
     <row r="72" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>66</v>
@@ -18336,7 +18735,7 @@
         <v>207</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="I72" s="4">
         <v>2000000000</v>
@@ -18347,14 +18746,14 @@
       <c r="K72" s="4">
         <v>2896725569</v>
       </c>
-      <c r="L72" s="17">
+      <c r="L72" s="13">
         <v>44537</v>
       </c>
-      <c r="M72" s="17"/>
-      <c r="N72" s="17">
+      <c r="M72" s="13"/>
+      <c r="N72" s="13">
         <v>44606</v>
       </c>
-      <c r="O72" s="17">
+      <c r="O72" s="13">
         <v>44740</v>
       </c>
       <c r="P72" s="4">
@@ -18367,16 +18766,16 @@
     </row>
     <row r="73" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>66</v>
@@ -18388,7 +18787,7 @@
         <v>68</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I73" s="4">
         <v>1953855779</v>
@@ -18399,14 +18798,14 @@
       <c r="K73" s="4">
         <v>2459776116</v>
       </c>
-      <c r="L73" s="17">
+      <c r="L73" s="13">
         <v>44537</v>
       </c>
-      <c r="M73" s="17"/>
-      <c r="N73" s="17">
+      <c r="M73" s="13"/>
+      <c r="N73" s="13">
         <v>44606</v>
       </c>
-      <c r="O73" s="17">
+      <c r="O73" s="13">
         <v>44713</v>
       </c>
       <c r="P73" s="4">
@@ -18419,16 +18818,16 @@
     </row>
     <row r="74" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>66</v>
@@ -18440,7 +18839,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="I74" s="4">
         <v>4351936180</v>
@@ -18451,14 +18850,14 @@
       <c r="K74" s="4">
         <v>4451936180</v>
       </c>
-      <c r="L74" s="17">
+      <c r="L74" s="13">
         <v>44552</v>
       </c>
-      <c r="M74" s="17"/>
-      <c r="N74" s="17">
+      <c r="M74" s="13"/>
+      <c r="N74" s="13">
         <v>44560</v>
       </c>
-      <c r="O74" s="17">
+      <c r="O74" s="13">
         <v>44588</v>
       </c>
       <c r="P74" s="4">
@@ -18471,16 +18870,16 @@
     </row>
     <row r="75" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>66</v>
@@ -18492,7 +18891,7 @@
         <v>57</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I75" s="4">
         <v>19906880779</v>
@@ -18503,14 +18902,14 @@
       <c r="K75" s="4">
         <v>19978880779</v>
       </c>
-      <c r="L75" s="17">
+      <c r="L75" s="13">
         <v>44700</v>
       </c>
-      <c r="M75" s="17"/>
-      <c r="N75" s="17">
+      <c r="M75" s="13"/>
+      <c r="N75" s="13">
         <v>44756</v>
       </c>
-      <c r="O75" s="17">
+      <c r="O75" s="13">
         <v>44783</v>
       </c>
       <c r="P75" s="4">
@@ -18523,16 +18922,16 @@
     </row>
     <row r="76" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>253</v>
@@ -18543,8 +18942,8 @@
       <c r="G76" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H76" s="19" t="s">
-        <v>444</v>
+      <c r="H76" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I76" s="4">
         <v>3981132848.27</v>
@@ -18555,14 +18954,14 @@
       <c r="K76" s="4">
         <v>3981132848.27</v>
       </c>
-      <c r="L76" s="17">
+      <c r="L76" s="13">
         <v>44509</v>
       </c>
-      <c r="M76" s="17"/>
-      <c r="N76" s="17">
+      <c r="M76" s="13"/>
+      <c r="N76" s="13">
         <v>44511</v>
       </c>
-      <c r="O76" s="17">
+      <c r="O76" s="13">
         <v>44594</v>
       </c>
       <c r="P76" s="4">
@@ -18574,27 +18973,27 @@
       <c r="R76" s="3"/>
     </row>
     <row r="77" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="18" t="s">
-        <v>773</v>
+      <c r="A77" s="14" t="s">
+        <v>770</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H77" s="21" t="s">
-        <v>498</v>
+      <c r="H77" s="17" t="s">
+        <v>496</v>
       </c>
       <c r="I77" s="4">
         <v>2407058486</v>
@@ -18605,12 +19004,12 @@
       <c r="K77" s="4">
         <v>2407275254.8200002</v>
       </c>
-      <c r="L77" s="17">
+      <c r="L77" s="13">
         <v>44844</v>
       </c>
-      <c r="M77" s="17"/>
-      <c r="N77" s="17"/>
-      <c r="O77" s="17"/>
+      <c r="M77" s="13"/>
+      <c r="N77" s="13"/>
+      <c r="O77" s="13"/>
       <c r="P77" s="4">
         <v>0</v>
       </c>
@@ -18621,28 +19020,28 @@
     </row>
     <row r="78" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H78" s="19" t="s">
-        <v>453</v>
+      <c r="H78" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I78" s="4">
         <v>45601872749</v>
@@ -18653,14 +19052,14 @@
       <c r="K78" s="4">
         <v>45601872749</v>
       </c>
-      <c r="L78" s="17">
+      <c r="L78" s="13">
         <v>44560</v>
       </c>
-      <c r="M78" s="17"/>
-      <c r="N78" s="17">
+      <c r="M78" s="13"/>
+      <c r="N78" s="13">
         <v>44559</v>
       </c>
-      <c r="O78" s="17">
+      <c r="O78" s="13">
         <v>44669</v>
       </c>
       <c r="P78" s="4">
@@ -18673,16 +19072,16 @@
     </row>
     <row r="79" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>784</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>92</v>
@@ -18693,8 +19092,8 @@
       <c r="G79" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H79" s="19" t="s">
-        <v>453</v>
+      <c r="H79" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I79" s="4">
         <v>2489078661</v>
@@ -18705,14 +19104,14 @@
       <c r="K79" s="4">
         <v>2489078661</v>
       </c>
-      <c r="L79" s="17">
+      <c r="L79" s="13">
         <v>44559</v>
       </c>
-      <c r="M79" s="17"/>
-      <c r="N79" s="17">
+      <c r="M79" s="13"/>
+      <c r="N79" s="13">
         <v>44559</v>
       </c>
-      <c r="O79" s="17">
+      <c r="O79" s="13">
         <v>44810</v>
       </c>
       <c r="P79" s="4">
@@ -18725,16 +19124,16 @@
     </row>
     <row r="80" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>785</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>788</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>92</v>
@@ -18745,8 +19144,8 @@
       <c r="G80" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H80" s="19" t="s">
-        <v>458</v>
+      <c r="H80" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I80" s="4">
         <v>18036167387.900002</v>
@@ -18757,12 +19156,12 @@
       <c r="K80" s="4">
         <v>18036167387.900002</v>
       </c>
-      <c r="L80" s="17">
+      <c r="L80" s="13">
         <v>44559</v>
       </c>
-      <c r="M80" s="17"/>
-      <c r="N80" s="29"/>
-      <c r="O80" s="17">
+      <c r="M80" s="13"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="13">
         <v>44708</v>
       </c>
       <c r="P80" s="4">
@@ -18775,16 +19174,16 @@
     </row>
     <row r="81" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>92</v>
@@ -18795,8 +19194,8 @@
       <c r="G81" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H81" s="20" t="s">
-        <v>458</v>
+      <c r="H81" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="I81" s="4">
         <v>41816156185</v>
@@ -18807,14 +19206,14 @@
       <c r="K81" s="4">
         <v>41816156185</v>
       </c>
-      <c r="L81" s="17">
+      <c r="L81" s="13">
         <v>44624</v>
       </c>
-      <c r="M81" s="17"/>
-      <c r="N81" s="17">
+      <c r="M81" s="13"/>
+      <c r="N81" s="13">
         <v>44624</v>
       </c>
-      <c r="O81" s="17">
+      <c r="O81" s="13">
         <v>44873</v>
       </c>
       <c r="P81" s="4">
@@ -18827,16 +19226,16 @@
     </row>
     <row r="82" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>66</v>
@@ -18848,7 +19247,7 @@
         <v>68</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I82" s="4">
         <v>9606506835</v>
@@ -18859,14 +19258,14 @@
       <c r="K82" s="4">
         <v>9696506835</v>
       </c>
-      <c r="L82" s="17">
+      <c r="L82" s="13">
         <v>44887</v>
       </c>
-      <c r="M82" s="17"/>
-      <c r="N82" s="17">
+      <c r="M82" s="13"/>
+      <c r="N82" s="13">
         <v>44911</v>
       </c>
-      <c r="O82" s="17">
+      <c r="O82" s="13">
         <v>45070</v>
       </c>
       <c r="P82" s="4">
@@ -18879,16 +19278,16 @@
     </row>
     <row r="83" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>795</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>796</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>798</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>66</v>
@@ -18900,7 +19299,7 @@
         <v>57</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I83" s="4">
         <v>500000000</v>
@@ -18911,14 +19310,14 @@
       <c r="K83" s="4">
         <v>585470000</v>
       </c>
-      <c r="L83" s="17">
+      <c r="L83" s="13">
         <v>44887</v>
       </c>
-      <c r="M83" s="17"/>
-      <c r="N83" s="17">
+      <c r="M83" s="13"/>
+      <c r="N83" s="13">
         <v>44930</v>
       </c>
-      <c r="O83" s="17">
+      <c r="O83" s="13">
         <v>44986</v>
       </c>
       <c r="P83" s="4">
@@ -18931,16 +19330,16 @@
     </row>
     <row r="84" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>799</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>66</v>
@@ -18952,7 +19351,7 @@
         <v>68</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I84" s="4">
         <v>4299593384</v>
@@ -18963,14 +19362,14 @@
       <c r="K84" s="4">
         <v>4425738451</v>
       </c>
-      <c r="L84" s="17">
+      <c r="L84" s="13">
         <v>44914</v>
       </c>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17">
+      <c r="M84" s="13"/>
+      <c r="N84" s="13">
         <v>45055</v>
       </c>
-      <c r="O84" s="17">
+      <c r="O84" s="13">
         <v>45139</v>
       </c>
       <c r="P84" s="4">
@@ -18983,16 +19382,16 @@
     </row>
     <row r="85" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>803</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>805</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>806</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>198</v>
@@ -19003,8 +19402,8 @@
       <c r="G85" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H85" s="19" t="s">
-        <v>444</v>
+      <c r="H85" s="15" t="s">
+        <v>442</v>
       </c>
       <c r="I85" s="4">
         <v>29623316906.279999</v>
@@ -19015,14 +19414,14 @@
       <c r="K85" s="4">
         <v>29623316906.279999</v>
       </c>
-      <c r="L85" s="17">
+      <c r="L85" s="13">
         <v>44925</v>
       </c>
-      <c r="M85" s="17"/>
-      <c r="N85" s="17">
+      <c r="M85" s="13"/>
+      <c r="N85" s="13">
         <v>44952</v>
       </c>
-      <c r="O85" s="17">
+      <c r="O85" s="13">
         <v>45030</v>
       </c>
       <c r="P85" s="4">
@@ -19035,16 +19434,16 @@
     </row>
     <row r="86" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>810</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>92</v>
@@ -19055,8 +19454,8 @@
       <c r="G86" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H86" s="19" t="s">
-        <v>458</v>
+      <c r="H86" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="I86" s="4">
         <v>30461715692</v>
@@ -19067,14 +19466,14 @@
       <c r="K86" s="4">
         <v>30461715692</v>
       </c>
-      <c r="L86" s="17">
+      <c r="L86" s="13">
         <v>45064</v>
       </c>
-      <c r="M86" s="17"/>
-      <c r="N86" s="17">
+      <c r="M86" s="13"/>
+      <c r="N86" s="13">
         <v>45202</v>
       </c>
-      <c r="O86" s="17">
+      <c r="O86" s="13">
         <v>45289</v>
       </c>
       <c r="P86" s="4">
@@ -19087,16 +19486,16 @@
     </row>
     <row r="87" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>811</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>66</v>
@@ -19108,7 +19507,7 @@
         <v>68</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I87" s="4">
         <v>17454000000</v>
@@ -19119,14 +19518,14 @@
       <c r="K87" s="4">
         <v>17761000000</v>
       </c>
-      <c r="L87" s="17">
+      <c r="L87" s="13">
         <v>45154</v>
       </c>
-      <c r="M87" s="17"/>
-      <c r="N87" s="17">
+      <c r="M87" s="13"/>
+      <c r="N87" s="13">
         <v>45428</v>
       </c>
-      <c r="O87" s="17">
+      <c r="O87" s="13">
         <v>45317</v>
       </c>
       <c r="P87" s="4">
@@ -19139,16 +19538,16 @@
     </row>
     <row r="88" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>815</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>816</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>818</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>66</v>
@@ -19160,7 +19559,7 @@
         <v>68</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I88" s="4">
         <v>8419333809</v>
@@ -19171,14 +19570,14 @@
       <c r="K88" s="4">
         <v>9930787094</v>
       </c>
-      <c r="L88" s="17">
+      <c r="L88" s="13">
         <v>45154</v>
       </c>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17">
+      <c r="M88" s="13"/>
+      <c r="N88" s="13">
         <v>45281</v>
       </c>
-      <c r="O88" s="17">
+      <c r="O88" s="13">
         <v>45328</v>
       </c>
       <c r="P88" s="4">
@@ -19191,28 +19590,28 @@
     </row>
     <row r="89" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>821</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>822</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>349</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H89" s="19" t="s">
-        <v>453</v>
+      <c r="H89" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I89" s="4">
         <v>94461519789</v>
@@ -19223,14 +19622,14 @@
       <c r="K89" s="4">
         <v>94461519789</v>
       </c>
-      <c r="L89" s="17">
+      <c r="L89" s="13">
         <v>45290</v>
       </c>
-      <c r="M89" s="17"/>
-      <c r="N89" s="17">
+      <c r="M89" s="13"/>
+      <c r="N89" s="13">
         <v>45369</v>
       </c>
-      <c r="O89" s="17">
+      <c r="O89" s="13">
         <v>45539</v>
       </c>
       <c r="P89" s="4">
@@ -19243,28 +19642,28 @@
     </row>
     <row r="90" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>66</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I90" s="4">
         <v>3362968761</v>
@@ -19275,14 +19674,14 @@
       <c r="K90" s="4">
         <v>4543549645</v>
       </c>
-      <c r="L90" s="17">
+      <c r="L90" s="13">
         <v>45596</v>
       </c>
-      <c r="M90" s="17"/>
-      <c r="N90" s="17">
+      <c r="M90" s="13"/>
+      <c r="N90" s="13">
         <v>45649</v>
       </c>
-      <c r="O90" s="17">
+      <c r="O90" s="13">
         <v>45721</v>
       </c>
       <c r="P90" s="4">
@@ -19295,16 +19694,16 @@
     </row>
     <row r="91" spans="1:18" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>66</v>
@@ -19316,7 +19715,7 @@
         <v>68</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I91" s="4">
         <v>23600000000</v>
@@ -19327,14 +19726,14 @@
       <c r="K91" s="4">
         <v>24518488200</v>
       </c>
-      <c r="L91" s="17">
+      <c r="L91" s="13">
         <v>45861</v>
       </c>
-      <c r="M91" s="17"/>
-      <c r="N91" s="17">
+      <c r="M91" s="13"/>
+      <c r="N91" s="13">
         <v>45916</v>
       </c>
-      <c r="O91" s="17">
+      <c r="O91" s="13">
         <v>45965</v>
       </c>
       <c r="P91" s="4">
@@ -19347,16 +19746,16 @@
     </row>
     <row r="92" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>66</v>
@@ -19368,7 +19767,7 @@
         <v>68</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I92" s="4">
         <v>30000000000</v>
@@ -19379,14 +19778,14 @@
       <c r="K92" s="4">
         <v>31068885740</v>
       </c>
-      <c r="L92" s="17">
+      <c r="L92" s="13">
         <v>45861</v>
       </c>
-      <c r="M92" s="17"/>
-      <c r="N92" s="17">
+      <c r="M92" s="13"/>
+      <c r="N92" s="13">
         <v>45904</v>
       </c>
-      <c r="O92" s="17">
+      <c r="O92" s="13">
         <v>45976</v>
       </c>
       <c r="P92" s="4">
@@ -19399,13 +19798,13 @@
     </row>
     <row r="93" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
@@ -19418,7 +19817,7 @@
         <v>68</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="I93" s="4">
         <v>30000000000</v>
@@ -19429,14 +19828,14 @@
       <c r="K93" s="4">
         <v>30899136874.049999</v>
       </c>
-      <c r="L93" s="17">
+      <c r="L93" s="13">
         <v>45861</v>
       </c>
-      <c r="M93" s="17"/>
-      <c r="N93" s="17">
+      <c r="M93" s="13"/>
+      <c r="N93" s="13">
         <v>45926</v>
       </c>
-      <c r="O93" s="17">
+      <c r="O93" s="13">
         <v>45980</v>
       </c>
       <c r="P93" s="4">
@@ -19449,13 +19848,13 @@
     </row>
     <row r="94" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
@@ -19467,8 +19866,8 @@
       <c r="G94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H94" s="19" t="s">
-        <v>453</v>
+      <c r="H94" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I94" s="4">
         <v>172253454</v>
@@ -19479,14 +19878,14 @@
       <c r="K94" s="4">
         <v>172253454</v>
       </c>
-      <c r="L94" s="17">
+      <c r="L94" s="13">
         <v>45715</v>
       </c>
-      <c r="M94" s="17"/>
-      <c r="N94" s="17">
+      <c r="M94" s="13"/>
+      <c r="N94" s="13">
         <v>46008</v>
       </c>
-      <c r="O94" s="17">
+      <c r="O94" s="13">
         <v>46014</v>
       </c>
       <c r="P94" s="4">
@@ -19499,16 +19898,16 @@
     </row>
     <row r="95" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>839</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>842</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>212</v>
@@ -19519,8 +19918,8 @@
       <c r="G95" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H95" s="20" t="s">
-        <v>458</v>
+      <c r="H95" s="16" t="s">
+        <v>456</v>
       </c>
       <c r="I95" s="4">
         <v>511865531</v>
@@ -19531,14 +19930,14 @@
       <c r="K95" s="4">
         <v>711865531</v>
       </c>
-      <c r="L95" s="17">
+      <c r="L95" s="13">
         <v>45756</v>
       </c>
-      <c r="M95" s="17"/>
-      <c r="N95" s="17">
+      <c r="M95" s="13"/>
+      <c r="N95" s="13">
         <v>45775</v>
       </c>
-      <c r="O95" s="17">
+      <c r="O95" s="13">
         <v>45922</v>
       </c>
       <c r="P95" s="4">
@@ -19551,13 +19950,13 @@
     </row>
     <row r="96" spans="1:18" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
@@ -19569,8 +19968,8 @@
       <c r="G96" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="H96" s="19" t="s">
-        <v>498</v>
+      <c r="H96" s="15" t="s">
+        <v>496</v>
       </c>
       <c r="I96" s="4">
         <v>386045990.94</v>
@@ -19581,14 +19980,14 @@
       <c r="K96" s="4">
         <v>586045990.94000006</v>
       </c>
-      <c r="L96" s="17">
+      <c r="L96" s="13">
         <v>45917</v>
       </c>
-      <c r="M96" s="17"/>
-      <c r="N96" s="17">
+      <c r="M96" s="13"/>
+      <c r="N96" s="13">
         <v>45938</v>
       </c>
-      <c r="O96" s="17"/>
+      <c r="O96" s="13"/>
       <c r="P96" s="4">
         <v>0</v>
       </c>
@@ -19599,16 +19998,16 @@
     </row>
     <row r="97" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>848</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>849</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>92</v>
@@ -19619,8 +20018,8 @@
       <c r="G97" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H97" s="19" t="s">
-        <v>453</v>
+      <c r="H97" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I97" s="4">
         <v>59900815918</v>
@@ -19631,14 +20030,14 @@
       <c r="K97" s="4">
         <v>59900815918</v>
       </c>
-      <c r="L97" s="17">
+      <c r="L97" s="13">
         <v>45911</v>
       </c>
-      <c r="M97" s="17"/>
-      <c r="N97" s="17">
+      <c r="M97" s="13"/>
+      <c r="N97" s="13">
         <v>45922</v>
       </c>
-      <c r="O97" s="17">
+      <c r="O97" s="13">
         <v>45974</v>
       </c>
       <c r="P97" s="4">
@@ -19651,28 +20050,28 @@
     </row>
     <row r="98" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>349</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H98" s="19" t="s">
-        <v>453</v>
+      <c r="H98" s="15" t="s">
+        <v>451</v>
       </c>
       <c r="I98" s="4">
         <v>28121067144</v>
@@ -19683,14 +20082,14 @@
       <c r="K98" s="4">
         <v>28263067144</v>
       </c>
-      <c r="L98" s="17">
+      <c r="L98" s="13">
         <v>45861</v>
       </c>
-      <c r="M98" s="17"/>
-      <c r="N98" s="17">
+      <c r="M98" s="13"/>
+      <c r="N98" s="13">
         <v>45882</v>
       </c>
-      <c r="O98" s="17">
+      <c r="O98" s="13">
         <v>45926</v>
       </c>
       <c r="P98" s="4">
@@ -19703,16 +20102,16 @@
     </row>
     <row r="99" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>66</v>
@@ -19724,7 +20123,7 @@
         <v>207</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I99" s="4">
         <v>1989520159</v>
@@ -19735,14 +20134,14 @@
       <c r="K99" s="4">
         <v>2825408806</v>
       </c>
-      <c r="L99" s="17">
+      <c r="L99" s="13">
         <v>44078</v>
       </c>
-      <c r="M99" s="17"/>
-      <c r="N99" s="17">
+      <c r="M99" s="13"/>
+      <c r="N99" s="13">
         <v>44176</v>
       </c>
-      <c r="O99" s="17"/>
+      <c r="O99" s="13"/>
       <c r="P99" s="4">
         <v>98.57</v>
       </c>
@@ -19753,16 +20152,16 @@
     </row>
     <row r="100" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>857</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>858</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>860</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>66</v>
@@ -19774,7 +20173,7 @@
         <v>207</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I100" s="4">
         <v>4869404585</v>
@@ -19785,14 +20184,14 @@
       <c r="K100" s="4">
         <v>5039787989</v>
       </c>
-      <c r="L100" s="17">
+      <c r="L100" s="13">
         <v>44384</v>
       </c>
-      <c r="M100" s="17"/>
-      <c r="N100" s="17">
+      <c r="M100" s="13"/>
+      <c r="N100" s="13">
         <v>44407</v>
       </c>
-      <c r="O100" s="17">
+      <c r="O100" s="13">
         <v>44560</v>
       </c>
       <c r="P100" s="4">
@@ -19805,28 +20204,28 @@
     </row>
     <row r="101" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I101" s="4">
         <v>2644584337.2600002</v>
@@ -19837,14 +20236,14 @@
       <c r="K101" s="4">
         <v>2644584337.2600002</v>
       </c>
-      <c r="L101" s="17">
+      <c r="L101" s="13">
         <v>44456</v>
       </c>
-      <c r="M101" s="17"/>
-      <c r="N101" s="17">
+      <c r="M101" s="13"/>
+      <c r="N101" s="13">
         <v>44489</v>
       </c>
-      <c r="O101" s="17">
+      <c r="O101" s="13">
         <v>44859</v>
       </c>
       <c r="P101" s="4">
@@ -19857,28 +20256,28 @@
     </row>
     <row r="102" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>207</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I102" s="4">
         <v>6578630543.6700001</v>
@@ -19889,14 +20288,14 @@
       <c r="K102" s="4">
         <v>6578630543.6700001</v>
       </c>
-      <c r="L102" s="17">
+      <c r="L102" s="13">
         <v>44559</v>
       </c>
-      <c r="M102" s="17"/>
-      <c r="N102" s="17">
+      <c r="M102" s="13"/>
+      <c r="N102" s="13">
         <v>44566</v>
       </c>
-      <c r="O102" s="17">
+      <c r="O102" s="13">
         <v>44697</v>
       </c>
       <c r="P102" s="4">
@@ -19909,16 +20308,16 @@
     </row>
     <row r="103" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>92</v>
@@ -19930,7 +20329,7 @@
         <v>207</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="I103" s="4">
         <v>6853127845.6300001</v>
@@ -19941,14 +20340,14 @@
       <c r="K103" s="4">
         <v>6853127845.6300001</v>
       </c>
-      <c r="L103" s="17">
+      <c r="L103" s="13">
         <v>45216</v>
       </c>
-      <c r="M103" s="17"/>
-      <c r="N103" s="17">
+      <c r="M103" s="13"/>
+      <c r="N103" s="13">
         <v>45219</v>
       </c>
-      <c r="O103" s="17">
+      <c r="O103" s="13">
         <v>45286</v>
       </c>
       <c r="P103" s="4">
@@ -19961,26 +20360,26 @@
     </row>
     <row r="104" spans="1:18" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="H104" s="18" t="s">
-        <v>498</v>
+        <v>872</v>
+      </c>
+      <c r="H104" s="14" t="s">
+        <v>496</v>
       </c>
       <c r="I104" s="4">
         <v>36139210439</v>
@@ -19991,14 +20390,14 @@
       <c r="K104" s="4">
         <v>36139210439</v>
       </c>
-      <c r="L104" s="17">
+      <c r="L104" s="13">
         <v>46080</v>
       </c>
-      <c r="M104" s="17"/>
-      <c r="N104" s="17">
+      <c r="M104" s="13"/>
+      <c r="N104" s="13">
         <v>46091</v>
       </c>
-      <c r="O104" s="17"/>
+      <c r="O104" s="13"/>
       <c r="P104" s="4">
         <v>0</v>
       </c>
@@ -20019,6 +20418,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -20162,15 +20570,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -20178,6 +20577,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44576703-C4EA-42A2-935E-C76D3BE0FC53}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20195,14 +20602,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8937D50-EA8A-4E8E-9144-993F62C56134}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA423ED4-21A6-41DF-89D7-6CD27D950967}">
   <ds:schemaRefs>

--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F4B5D88F-83F5-4D05-9DE3-907F17EA7CC9}"/>
+  <xr:revisionPtr revIDLastSave="155" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21DFF438-96BB-406B-9FF1-B0352D687B6F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="942">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -2985,6 +2985,9 @@
   </si>
   <si>
     <t>San José de Toluviejo, Sincelejo, Galeras</t>
+  </si>
+  <si>
+    <t>Planeación</t>
   </si>
 </sst>
 </file>
@@ -3180,6 +3183,12 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3193,12 +3202,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3261,13 +3264,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AZ61" totalsRowShown="0">
-  <autoFilter ref="A2:AZ61" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="CONTRATADO EN EJECUCIÓN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:AZ61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="52">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -3705,9 +3702,7 @@
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
     <col min="3" max="3" width="32.21875" customWidth="1"/>
-    <col min="4" max="6" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="24" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="4" max="24" width="25.6640625" customWidth="1"/>
     <col min="25" max="25" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="25.6640625" customWidth="1"/>
     <col min="27" max="47" width="25.6640625" hidden="1" customWidth="1"/>
@@ -3719,62 +3714,62 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:52" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="11" t="s">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-      <c r="AI1" s="11"/>
-      <c r="AJ1" s="11"/>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="11"/>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
-      <c r="AO1" s="11"/>
-      <c r="AP1" s="11"/>
-      <c r="AQ1" s="11"/>
-      <c r="AR1" s="10" t="s">
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="13"/>
+      <c r="AH1" s="13"/>
+      <c r="AI1" s="13"/>
+      <c r="AJ1" s="13"/>
+      <c r="AK1" s="13"/>
+      <c r="AL1" s="13"/>
+      <c r="AM1" s="13"/>
+      <c r="AN1" s="13"/>
+      <c r="AO1" s="13"/>
+      <c r="AP1" s="13"/>
+      <c r="AQ1" s="13"/>
+      <c r="AR1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="AS1" s="10"/>
-      <c r="AT1" s="10"/>
-      <c r="AU1" s="10"/>
-      <c r="AV1" s="10"/>
-      <c r="AW1" s="10"/>
-      <c r="AX1" s="10"/>
+      <c r="AS1" s="12"/>
+      <c r="AT1" s="12"/>
+      <c r="AU1" s="12"/>
+      <c r="AV1" s="12"/>
+      <c r="AW1" s="12"/>
+      <c r="AX1" s="12"/>
     </row>
     <row r="2" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3934,12 +3929,12 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="210.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" ht="210.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>941</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -4081,8 +4076,14 @@
       <c r="AX3" s="4" t="s">
         <v>65</v>
       </c>
+      <c r="AY3">
+        <v>39</v>
+      </c>
+      <c r="AZ3" s="10" t="s">
+        <v>910</v>
+      </c>
     </row>
-    <row r="4" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>66</v>
       </c>
@@ -4219,8 +4220,11 @@
       <c r="AX4" s="4" t="s">
         <v>75</v>
       </c>
+      <c r="AZ4" s="11" t="s">
+        <v>911</v>
+      </c>
     </row>
-    <row r="5" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>76</v>
       </c>
@@ -4367,6 +4371,9 @@
       <c r="AX5" s="4" t="s">
         <v>75</v>
       </c>
+      <c r="AZ5" s="11" t="s">
+        <v>910</v>
+      </c>
     </row>
     <row r="6" spans="1:52" ht="139.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -4518,13 +4525,13 @@
         <v>75</v>
       </c>
       <c r="AY6">
-        <v>39</v>
-      </c>
-      <c r="AZ6" s="15" t="s">
-        <v>910</v>
+        <v>45</v>
+      </c>
+      <c r="AZ6" s="11" t="s">
+        <v>912</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>92</v>
       </c>
@@ -4671,11 +4678,14 @@
       <c r="AX7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ7" s="16" t="s">
-        <v>911</v>
+      <c r="AY7">
+        <v>100</v>
+      </c>
+      <c r="AZ7" s="11" t="s">
+        <v>913</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
@@ -4822,8 +4832,11 @@
       <c r="AX8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AZ8" s="16" t="s">
-        <v>910</v>
+      <c r="AY8">
+        <v>100</v>
+      </c>
+      <c r="AZ8" s="10" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="9" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -4978,13 +4991,13 @@
         <v>75</v>
       </c>
       <c r="AY9">
-        <v>45</v>
-      </c>
-      <c r="AZ9" s="16" t="s">
-        <v>912</v>
+        <v>90</v>
+      </c>
+      <c r="AZ9" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>118</v>
       </c>
@@ -5131,14 +5144,11 @@
       <c r="AX10" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AY10">
-        <v>100</v>
-      </c>
-      <c r="AZ10" s="16" t="s">
-        <v>913</v>
+      <c r="AZ10" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
@@ -5285,14 +5295,11 @@
       <c r="AX11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AY11">
-        <v>100</v>
-      </c>
-      <c r="AZ11" s="15" t="s">
-        <v>914</v>
+      <c r="AZ11" s="11" t="s">
+        <v>915</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>131</v>
       </c>
@@ -5439,11 +5446,8 @@
       <c r="AX12" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AY12">
-        <v>90</v>
-      </c>
-      <c r="AZ12" s="16" t="s">
-        <v>914</v>
+      <c r="AZ12" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="13" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5595,11 +5599,14 @@
       <c r="AX13" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="AZ13" s="16" t="s">
+      <c r="AY13">
+        <v>100</v>
+      </c>
+      <c r="AZ13" s="11" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>150</v>
       </c>
@@ -5746,8 +5753,8 @@
       <c r="AX14" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ14" s="16" t="s">
-        <v>915</v>
+      <c r="AZ14" s="11" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="15" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -5899,11 +5906,11 @@
       <c r="AX15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AZ15" s="16" t="s">
-        <v>910</v>
+      <c r="AZ15" s="11" t="s">
+        <v>917</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>163</v>
       </c>
@@ -6053,8 +6060,8 @@
       <c r="AY16">
         <v>100</v>
       </c>
-      <c r="AZ16" s="16" t="s">
-        <v>914</v>
+      <c r="AZ16" s="11" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="17" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6206,8 +6213,8 @@
       <c r="AX17" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AZ17" s="16" t="s">
-        <v>916</v>
+      <c r="AZ17" s="11" t="s">
+        <v>919</v>
       </c>
     </row>
     <row r="18" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6359,8 +6366,11 @@
       <c r="AX18" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AZ18" s="16" t="s">
-        <v>917</v>
+      <c r="AY18">
+        <v>90</v>
+      </c>
+      <c r="AZ18" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="19" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6512,14 +6522,11 @@
       <c r="AX19" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AY19">
-        <v>100</v>
-      </c>
-      <c r="AZ19" s="16" t="s">
-        <v>918</v>
+      <c r="AZ19" s="11" t="s">
+        <v>920</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>189</v>
       </c>
@@ -6666,8 +6673,11 @@
       <c r="AX20" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AZ20" s="16" t="s">
-        <v>919</v>
+      <c r="AY20">
+        <v>98.4</v>
+      </c>
+      <c r="AZ20" s="11" t="s">
+        <v>921</v>
       </c>
     </row>
     <row r="21" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -6822,8 +6832,8 @@
       <c r="AY21">
         <v>90</v>
       </c>
-      <c r="AZ21" s="16" t="s">
-        <v>914</v>
+      <c r="AZ21" s="11" t="s">
+        <v>922</v>
       </c>
     </row>
     <row r="22" spans="1:52" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -6975,11 +6985,14 @@
       <c r="AX22" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AZ22" s="16" t="s">
-        <v>920</v>
+      <c r="AY22">
+        <v>94.8</v>
+      </c>
+      <c r="AZ22" s="11" t="s">
+        <v>923</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>211</v>
       </c>
@@ -7121,18 +7134,18 @@
         <v>103</v>
       </c>
       <c r="AY23">
-        <v>98.4</v>
-      </c>
-      <c r="AZ23" s="16" t="s">
-        <v>921</v>
+        <v>79.2</v>
+      </c>
+      <c r="AZ23" s="11" t="s">
+        <v>924</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>217</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>93</v>
+        <v>941</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>218</v>
@@ -7271,11 +7284,11 @@
       <c r="AY24">
         <v>90</v>
       </c>
-      <c r="AZ24" s="16" t="s">
-        <v>922</v>
+      <c r="AZ24" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>225</v>
       </c>
@@ -7414,11 +7427,8 @@
       <c r="AX25" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AY25">
-        <v>94.8</v>
-      </c>
-      <c r="AZ25" s="16" t="s">
-        <v>923</v>
+      <c r="AZ25" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="26" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -7570,14 +7580,11 @@
       <c r="AX26" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AY26">
-        <v>79.2</v>
-      </c>
-      <c r="AZ26" s="16" t="s">
-        <v>924</v>
+      <c r="AZ26" s="11" t="s">
+        <v>925</v>
       </c>
     </row>
-    <row r="27" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>238</v>
       </c>
@@ -7724,14 +7731,11 @@
       <c r="AX27" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AY27">
-        <v>90</v>
-      </c>
-      <c r="AZ27" s="16" t="s">
-        <v>910</v>
+      <c r="AZ27" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>244</v>
       </c>
@@ -7876,11 +7880,14 @@
       <c r="AX28" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ28" s="16" t="s">
-        <v>914</v>
+      <c r="AY28">
+        <v>100</v>
+      </c>
+      <c r="AZ28" s="11" t="s">
+        <v>926</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>250</v>
       </c>
@@ -8027,11 +8034,11 @@
       <c r="AX29" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AZ29" s="16" t="s">
-        <v>925</v>
+      <c r="AZ29" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>257</v>
       </c>
@@ -8172,11 +8179,11 @@
       <c r="AX30" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AZ30" s="16" t="s">
-        <v>914</v>
+      <c r="AZ30" s="11" t="s">
+        <v>927</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>261</v>
       </c>
@@ -8322,10 +8329,10 @@
         <v>103</v>
       </c>
       <c r="AY31">
-        <v>100</v>
-      </c>
-      <c r="AZ31" s="16" t="s">
-        <v>926</v>
+        <v>90</v>
+      </c>
+      <c r="AZ31" s="11" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="32" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8477,8 +8484,8 @@
       <c r="AX32" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ32" s="16" t="s">
-        <v>910</v>
+      <c r="AZ32" s="11" t="s">
+        <v>928</v>
       </c>
     </row>
     <row r="33" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -8630,11 +8637,11 @@
       <c r="AX33" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AZ33" s="16" t="s">
-        <v>927</v>
+      <c r="AZ33" s="11" t="s">
+        <v>929</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>283</v>
       </c>
@@ -8780,13 +8787,13 @@
         <v>103</v>
       </c>
       <c r="AY34">
-        <v>90</v>
-      </c>
-      <c r="AZ34" s="16" t="s">
-        <v>925</v>
+        <v>100</v>
+      </c>
+      <c r="AZ34" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="35" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>289</v>
       </c>
@@ -8923,8 +8930,8 @@
       <c r="AX35" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AZ35" s="16" t="s">
-        <v>928</v>
+      <c r="AZ35" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="36" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9074,11 +9081,11 @@
       <c r="AX36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="AZ36" s="16" t="s">
-        <v>929</v>
+      <c r="AZ36" s="11" t="s">
+        <v>930</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>300</v>
       </c>
@@ -9223,10 +9230,7 @@
       <c r="AX37" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AY37">
-        <v>100</v>
-      </c>
-      <c r="AZ37" s="16" t="s">
+      <c r="AZ37" s="11" t="s">
         <v>910</v>
       </c>
     </row>
@@ -9379,11 +9383,14 @@
       <c r="AX38" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ38" s="16" t="s">
-        <v>914</v>
+      <c r="AY38">
+        <v>14</v>
+      </c>
+      <c r="AZ38" s="11" t="s">
+        <v>931</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>313</v>
       </c>
@@ -9530,8 +9537,8 @@
       <c r="AX39" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AZ39" s="16" t="s">
-        <v>930</v>
+      <c r="AZ39" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="40" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9683,7 +9690,10 @@
       <c r="AX40" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="AZ40" s="16" t="s">
+      <c r="AY40">
+        <v>100</v>
+      </c>
+      <c r="AZ40" s="11" t="s">
         <v>910</v>
       </c>
     </row>
@@ -9837,10 +9847,10 @@
         <v>125</v>
       </c>
       <c r="AY41">
-        <v>14</v>
-      </c>
-      <c r="AZ41" s="16" t="s">
-        <v>931</v>
+        <v>23</v>
+      </c>
+      <c r="AZ41" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
     <row r="42" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9990,11 +10000,14 @@
       <c r="AX42" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AZ42" s="16" t="s">
-        <v>910</v>
+      <c r="AY42">
+        <v>17.5</v>
+      </c>
+      <c r="AZ42" s="11" t="s">
+        <v>932</v>
       </c>
     </row>
-    <row r="43" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>336</v>
       </c>
@@ -10132,10 +10145,10 @@
         <v>65</v>
       </c>
       <c r="AY43">
-        <v>100</v>
-      </c>
-      <c r="AZ43" s="16" t="s">
-        <v>910</v>
+        <v>17.5</v>
+      </c>
+      <c r="AZ43" s="11" t="s">
+        <v>933</v>
       </c>
     </row>
     <row r="44" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10288,9 +10301,9 @@
         <v>103</v>
       </c>
       <c r="AY44">
-        <v>23</v>
-      </c>
-      <c r="AZ44" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="AZ44" s="11" t="s">
         <v>910</v>
       </c>
     </row>
@@ -10442,13 +10455,13 @@
         <v>125</v>
       </c>
       <c r="AY45">
-        <v>17.5</v>
-      </c>
-      <c r="AZ45" s="16" t="s">
-        <v>932</v>
+        <v>40</v>
+      </c>
+      <c r="AZ45" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>360</v>
       </c>
@@ -10591,10 +10604,10 @@
         <v>125</v>
       </c>
       <c r="AY46">
-        <v>17.5</v>
-      </c>
-      <c r="AZ46" s="16" t="s">
-        <v>933</v>
+        <v>33.5</v>
+      </c>
+      <c r="AZ46" s="11" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="47" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10747,13 +10760,13 @@
         <v>125</v>
       </c>
       <c r="AY47">
-        <v>100</v>
-      </c>
-      <c r="AZ47" s="16" t="s">
-        <v>910</v>
+        <v>0</v>
+      </c>
+      <c r="AZ47" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>376</v>
       </c>
@@ -10880,10 +10893,10 @@
         <v>75</v>
       </c>
       <c r="AY48">
-        <v>40</v>
-      </c>
-      <c r="AZ48" s="16" t="s">
-        <v>910</v>
+        <v>50</v>
+      </c>
+      <c r="AZ48" s="11" t="s">
+        <v>934</v>
       </c>
     </row>
     <row r="49" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11033,11 +11046,8 @@
       <c r="AX49" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="AY49">
-        <v>33.5</v>
-      </c>
-      <c r="AZ49" s="16" t="s">
-        <v>925</v>
+      <c r="AZ49" s="11" t="s">
+        <v>935</v>
       </c>
     </row>
     <row r="50" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11190,8 +11200,8 @@
       <c r="AY50">
         <v>0</v>
       </c>
-      <c r="AZ50" s="16" t="s">
-        <v>914</v>
+      <c r="AZ50" s="11" t="s">
+        <v>936</v>
       </c>
     </row>
     <row r="51" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11344,13 +11354,13 @@
         <v>395</v>
       </c>
       <c r="AY51">
-        <v>50</v>
-      </c>
-      <c r="AZ51" s="16" t="s">
-        <v>934</v>
+        <v>32.4</v>
+      </c>
+      <c r="AZ51" s="11" t="s">
+        <v>937</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>400</v>
       </c>
@@ -11486,11 +11496,14 @@
       <c r="AX52" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="AZ52" s="16" t="s">
-        <v>935</v>
+      <c r="AY52">
+        <v>30</v>
+      </c>
+      <c r="AZ52" s="11" t="s">
+        <v>938</v>
       </c>
     </row>
-    <row r="53" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>407</v>
       </c>
@@ -11623,10 +11636,10 @@
         <v>75</v>
       </c>
       <c r="AY53">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="16" t="s">
-        <v>936</v>
+        <v>100</v>
+      </c>
+      <c r="AZ53" s="11" t="s">
+        <v>929</v>
       </c>
     </row>
     <row r="54" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11775,13 +11788,13 @@
         <v>395</v>
       </c>
       <c r="AY54">
-        <v>32.4</v>
-      </c>
-      <c r="AZ54" s="16" t="s">
-        <v>937</v>
+        <v>100</v>
+      </c>
+      <c r="AZ54" s="11" t="s">
+        <v>910</v>
       </c>
     </row>
-    <row r="55" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>419</v>
       </c>
@@ -11925,13 +11938,13 @@
         <v>395</v>
       </c>
       <c r="AY55">
-        <v>30</v>
-      </c>
-      <c r="AZ55" s="16" t="s">
-        <v>938</v>
+        <v>100</v>
+      </c>
+      <c r="AZ55" s="11" t="s">
+        <v>939</v>
       </c>
     </row>
-    <row r="56" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>427</v>
       </c>
@@ -12068,13 +12081,13 @@
         <v>395</v>
       </c>
       <c r="AY56">
-        <v>100</v>
-      </c>
-      <c r="AZ56" s="16" t="s">
-        <v>929</v>
+        <v>0</v>
+      </c>
+      <c r="AZ56" s="11" t="s">
+        <v>940</v>
       </c>
     </row>
-    <row r="57" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>435</v>
       </c>
@@ -12209,11 +12222,11 @@
       <c r="AY57">
         <v>100</v>
       </c>
-      <c r="AZ57" s="16" t="s">
+      <c r="AZ57" s="11" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="58" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>441</v>
       </c>
@@ -12346,44 +12359,26 @@
       <c r="AY58">
         <v>100</v>
       </c>
-      <c r="AZ58" s="16" t="s">
-        <v>939</v>
+      <c r="AZ58" s="11" t="s">
+        <v>914</v>
       </c>
     </row>
-    <row r="59" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
       <c r="Y59" s="7">
         <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
         <v>1.9743336623889436E-3</v>
       </c>
-      <c r="AY59">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="16" t="s">
-        <v>940</v>
-      </c>
     </row>
-    <row r="60" spans="1:52" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
       <c r="Y60" s="7">
         <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
         <v>1.9743336623889436E-3</v>
-      </c>
-      <c r="AY60">
-        <v>100</v>
-      </c>
-      <c r="AZ60" s="16" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="61" spans="1:52" x14ac:dyDescent="0.3">
       <c r="Y61" s="7">
         <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
         <v>1.9743336623889436E-3</v>
-      </c>
-      <c r="AY61">
-        <v>100</v>
-      </c>
-      <c r="AZ61" s="16" t="s">
-        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -12419,50 +12414,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="11" t="s">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11"/>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11"/>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="12" t="s">
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="13"/>
+      <c r="AG1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="13"/>
-      <c r="AI1" s="13"/>
-      <c r="AJ1" s="13"/>
-      <c r="AK1" s="13"/>
-      <c r="AL1" s="14"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="16"/>
     </row>
     <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -14320,26 +14315,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -19685,21 +19680,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19843,24 +19823,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55278F2-F788-4282-8A5E-A876C5B8CDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19876,4 +19854,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="155" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21DFF438-96BB-406B-9FF1-B0352D687B6F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="21576" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
@@ -19680,6 +19680,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19823,22 +19838,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55278F2-F788-4282-8A5E-A876C5B8CDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19854,21 +19871,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="155" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21DFF438-96BB-406B-9FF1-B0352D687B6F}"/>
+  <xr:revisionPtr revIDLastSave="157" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08CCB9A-21A2-499F-AFEB-F92C13FDF3D8}"/>
   <bookViews>
     <workbookView xWindow="1116" yWindow="1116" windowWidth="21576" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3258,13 +3258,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AZ61" totalsRowShown="0">
-  <autoFilter ref="A2:AZ61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AZ58" totalsRowShown="0">
+  <autoFilter ref="A2:AZ58" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="52">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -3697,7 +3697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AZ61"/>
+  <dimension ref="A1:AZ58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
@@ -3929,7 +3929,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="210.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" ht="210.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>66</v>
       </c>
@@ -4224,7 +4224,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>76</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="139.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" ht="139.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>84</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>92</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>111</v>
       </c>
@@ -4997,7 +4997,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>118</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
@@ -5299,7 +5299,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>131</v>
       </c>
@@ -5450,7 +5450,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>139</v>
       </c>
@@ -5606,7 +5606,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>150</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>157</v>
       </c>
@@ -5910,7 +5910,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>163</v>
       </c>
@@ -6064,7 +6064,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="17" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>169</v>
       </c>
@@ -6217,7 +6217,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>177</v>
       </c>
@@ -6373,7 +6373,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>184</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>189</v>
       </c>
@@ -6680,7 +6680,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>194</v>
       </c>
@@ -6836,7 +6836,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:52" ht="130.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>203</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>211</v>
       </c>
@@ -7140,7 +7140,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>217</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>225</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="26" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>230</v>
       </c>
@@ -7584,7 +7584,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="27" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>238</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>244</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>250</v>
       </c>
@@ -8038,7 +8038,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>257</v>
       </c>
@@ -8183,7 +8183,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>261</v>
       </c>
@@ -8335,7 +8335,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>267</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>274</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>283</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="35" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>289</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="36" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>294</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>300</v>
       </c>
@@ -9234,7 +9234,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="38" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>307</v>
       </c>
@@ -9390,7 +9390,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>313</v>
       </c>
@@ -9541,7 +9541,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>320</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>2024002700066</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>331</v>
       </c>
@@ -10007,7 +10007,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="43" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>336</v>
       </c>
@@ -10151,7 +10151,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>343</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>350</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>360</v>
       </c>
@@ -10610,7 +10610,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="47" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>370</v>
       </c>
@@ -10766,7 +10766,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>376</v>
       </c>
@@ -10899,7 +10899,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="49" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>381</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="50" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>388</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="51" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>396</v>
       </c>
@@ -11360,7 +11360,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>400</v>
       </c>
@@ -11503,7 +11503,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="53" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>407</v>
       </c>
@@ -11642,7 +11642,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="54" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>2025002700023</v>
       </c>
@@ -11794,7 +11794,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="55" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>419</v>
       </c>
@@ -11944,7 +11944,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="56" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>427</v>
       </c>
@@ -12087,7 +12087,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="57" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>435</v>
       </c>
@@ -12226,7 +12226,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="58" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>441</v>
       </c>
@@ -12361,24 +12361,6 @@
       </c>
       <c r="AZ58" s="11" t="s">
         <v>914</v>
-      </c>
-    </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="Y59" s="7">
-        <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
-        <v>1.9743336623889436E-3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="Y60" s="7">
-        <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
-        <v>1.9743336623889436E-3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.3">
-      <c r="Y61" s="7">
-        <f>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</f>
-        <v>1.9743336623889436E-3</v>
       </c>
     </row>
   </sheetData>
@@ -19680,21 +19662,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19838,24 +19805,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55278F2-F788-4282-8A5E-A876C5B8CDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19871,4 +19836,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="157" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E08CCB9A-21A2-499F-AFEB-F92C13FDF3D8}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="8_{037BA787-73DB-464D-8B77-8A9A8F3F6EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F70AF538-1509-476A-9790-A2983A1F79C1}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="21576" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="942">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="942">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -2891,9 +2891,6 @@
     <t>PUNTAJE IGPR I TRIMESTRE  2026</t>
   </si>
   <si>
-    <t>RESPONSABLE CARGUE EN GESPROY3</t>
-  </si>
-  <si>
     <t>Todo el Departamento de Sucre</t>
   </si>
   <si>
@@ -2988,6 +2985,9 @@
   </si>
   <si>
     <t>Planeación</t>
+  </si>
+  <si>
+    <t>MUNICIPIOS</t>
   </si>
 </sst>
 </file>
@@ -3154,7 +3154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3204,11 +3204,56 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3260,11 +3305,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AZ58" totalsRowShown="0">
-  <autoFilter ref="A2:AZ58" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="1">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:AZ58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="52">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -3290,7 +3331,7 @@
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="CPI"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI"/>
-    <tableColumn id="50" xr3:uid="{C64E2821-0C69-4C80-A69F-50A65BC919C7}" name="Columna1" dataDxfId="0">
+    <tableColumn id="50" xr3:uid="{C64E2821-0C69-4C80-A69F-50A65BC919C7}" name="Columna1" dataDxfId="2">
       <calculatedColumnFormula>4/2026-MatrizSeguimientoEvaluacion[[#This Row],[FECHA APROBACIÓN PROYECTO]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
@@ -3319,27 +3360,16 @@
     <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN"/>
     <tableColumn id="49" xr3:uid="{00000000-0010-0000-0000-000031000000}" name="RESPONSABLE CARGUE EN GESPROY"/>
     <tableColumn id="51" xr3:uid="{27DE60B2-C6BC-4DFF-81AD-2BE35C6BC934}" name="PUNTAJE IGPR I TRIMESTRE  2026"/>
-    <tableColumn id="52" xr3:uid="{05922F1C-DD22-4A44-94DA-C0753FF4FADE}" name="RESPONSABLE CARGUE EN GESPROY3"/>
+    <tableColumn id="52" xr3:uid="{05922F1C-DD22-4A44-94DA-C0753FF4FADE}" name="MUNICIPIOS"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AL18" totalsRowShown="0">
-  <autoFilter ref="A2:AL18" xr:uid="{00000000-0009-0000-0100-000002000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="INSTITUTO DEPARTAMENTAL DE DEPORTES Y RECREACION DE SUCRE INDERSUCRE"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="CONTRATADO EN EJECUCIÓN"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AM18" totalsRowShown="0">
+  <autoFilter ref="A2:AM18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -3378,15 +3408,16 @@
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="COLUMNA APOYO 2"/>
     <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
     <tableColumn id="38" xr3:uid="{00000000-0010-0000-0100-000026000000}" name="COMENTARIOS CALIFICACIÓN"/>
+    <tableColumn id="39" xr3:uid="{70821DFD-2BD0-427E-82C9-FEFAF0A89EC6}" name="MUNICIPIOS" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:R104" totalsRowShown="0">
-  <autoFilter ref="A2:R104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:S104" totalsRowShown="0">
+  <autoFilter ref="A2:S104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -3405,6 +3436,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS"/>
+    <tableColumn id="19" xr3:uid="{919A2533-AF79-467F-8ACE-9F670265502F}" name="MUNICIPIOS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3926,15 +3958,15 @@
         <v>908</v>
       </c>
       <c r="AZ2" s="3" t="s">
-        <v>909</v>
+        <v>941</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="210.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:52" ht="210.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>54</v>
@@ -4080,10 +4112,10 @@
         <v>39</v>
       </c>
       <c r="AZ3" s="10" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>66</v>
       </c>
@@ -4221,10 +4253,10 @@
         <v>75</v>
       </c>
       <c r="AZ4" s="11" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>76</v>
       </c>
@@ -4372,10 +4404,10 @@
         <v>75</v>
       </c>
       <c r="AZ5" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="139.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:52" ht="139.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>84</v>
       </c>
@@ -4528,10 +4560,10 @@
         <v>45</v>
       </c>
       <c r="AZ6" s="11" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>92</v>
       </c>
@@ -4682,10 +4714,10 @@
         <v>100</v>
       </c>
       <c r="AZ7" s="11" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>104</v>
       </c>
@@ -4836,10 +4868,10 @@
         <v>100</v>
       </c>
       <c r="AZ8" s="10" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>111</v>
       </c>
@@ -4994,10 +5026,10 @@
         <v>90</v>
       </c>
       <c r="AZ9" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>118</v>
       </c>
@@ -5145,10 +5177,10 @@
         <v>125</v>
       </c>
       <c r="AZ10" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>126</v>
       </c>
@@ -5296,10 +5328,10 @@
         <v>75</v>
       </c>
       <c r="AZ11" s="11" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>131</v>
       </c>
@@ -5447,10 +5479,10 @@
         <v>125</v>
       </c>
       <c r="AZ12" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>139</v>
       </c>
@@ -5603,10 +5635,10 @@
         <v>100</v>
       </c>
       <c r="AZ13" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>150</v>
       </c>
@@ -5754,10 +5786,10 @@
         <v>103</v>
       </c>
       <c r="AZ14" s="11" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>157</v>
       </c>
@@ -5907,10 +5939,10 @@
         <v>75</v>
       </c>
       <c r="AZ15" s="11" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>163</v>
       </c>
@@ -6061,10 +6093,10 @@
         <v>100</v>
       </c>
       <c r="AZ16" s="11" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
-    <row r="17" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>169</v>
       </c>
@@ -6214,10 +6246,10 @@
         <v>125</v>
       </c>
       <c r="AZ17" s="11" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>177</v>
       </c>
@@ -6370,10 +6402,10 @@
         <v>90</v>
       </c>
       <c r="AZ18" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>184</v>
       </c>
@@ -6523,10 +6555,10 @@
         <v>75</v>
       </c>
       <c r="AZ19" s="11" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>189</v>
       </c>
@@ -6677,10 +6709,10 @@
         <v>98.4</v>
       </c>
       <c r="AZ20" s="11" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>194</v>
       </c>
@@ -6833,10 +6865,10 @@
         <v>90</v>
       </c>
       <c r="AZ21" s="11" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="130.19999999999999" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:52" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>203</v>
       </c>
@@ -6989,10 +7021,10 @@
         <v>94.8</v>
       </c>
       <c r="AZ22" s="11" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>211</v>
       </c>
@@ -7137,15 +7169,15 @@
         <v>79.2</v>
       </c>
       <c r="AZ23" s="11" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>217</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>218</v>
@@ -7285,10 +7317,10 @@
         <v>90</v>
       </c>
       <c r="AZ24" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>225</v>
       </c>
@@ -7428,10 +7460,10 @@
         <v>75</v>
       </c>
       <c r="AZ25" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="26" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>230</v>
       </c>
@@ -7581,10 +7613,10 @@
         <v>125</v>
       </c>
       <c r="AZ26" s="11" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
-    <row r="27" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>238</v>
       </c>
@@ -7732,10 +7764,10 @@
         <v>65</v>
       </c>
       <c r="AZ27" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>244</v>
       </c>
@@ -7884,10 +7916,10 @@
         <v>100</v>
       </c>
       <c r="AZ28" s="11" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>250</v>
       </c>
@@ -8035,10 +8067,10 @@
         <v>125</v>
       </c>
       <c r="AZ29" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>257</v>
       </c>
@@ -8180,10 +8212,10 @@
         <v>125</v>
       </c>
       <c r="AZ30" s="11" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>261</v>
       </c>
@@ -8332,10 +8364,10 @@
         <v>90</v>
       </c>
       <c r="AZ31" s="11" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>267</v>
       </c>
@@ -8485,10 +8517,10 @@
         <v>103</v>
       </c>
       <c r="AZ32" s="11" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>274</v>
       </c>
@@ -8638,10 +8670,10 @@
         <v>125</v>
       </c>
       <c r="AZ33" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>283</v>
       </c>
@@ -8790,10 +8822,10 @@
         <v>100</v>
       </c>
       <c r="AZ34" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="35" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>289</v>
       </c>
@@ -8931,10 +8963,10 @@
         <v>75</v>
       </c>
       <c r="AZ35" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="36" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>294</v>
       </c>
@@ -9082,10 +9114,10 @@
         <v>125</v>
       </c>
       <c r="AZ36" s="11" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>300</v>
       </c>
@@ -9231,10 +9263,10 @@
         <v>75</v>
       </c>
       <c r="AZ37" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="38" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>307</v>
       </c>
@@ -9387,10 +9419,10 @@
         <v>14</v>
       </c>
       <c r="AZ38" s="11" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>313</v>
       </c>
@@ -9538,10 +9570,10 @@
         <v>75</v>
       </c>
       <c r="AZ39" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>320</v>
       </c>
@@ -9694,10 +9726,10 @@
         <v>100</v>
       </c>
       <c r="AZ40" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>2024002700066</v>
       </c>
@@ -9850,10 +9882,10 @@
         <v>23</v>
       </c>
       <c r="AZ41" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>331</v>
       </c>
@@ -10004,10 +10036,10 @@
         <v>17.5</v>
       </c>
       <c r="AZ42" s="11" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
-    <row r="43" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>336</v>
       </c>
@@ -10148,10 +10180,10 @@
         <v>17.5</v>
       </c>
       <c r="AZ43" s="11" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>343</v>
       </c>
@@ -10304,10 +10336,10 @@
         <v>100</v>
       </c>
       <c r="AZ44" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>350</v>
       </c>
@@ -10458,10 +10490,10 @@
         <v>40</v>
       </c>
       <c r="AZ45" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>360</v>
       </c>
@@ -10607,10 +10639,10 @@
         <v>33.5</v>
       </c>
       <c r="AZ46" s="11" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
-    <row r="47" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>370</v>
       </c>
@@ -10763,10 +10795,10 @@
         <v>0</v>
       </c>
       <c r="AZ47" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>376</v>
       </c>
@@ -10896,10 +10928,10 @@
         <v>50</v>
       </c>
       <c r="AZ48" s="11" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
-    <row r="49" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>381</v>
       </c>
@@ -11047,10 +11079,10 @@
         <v>75</v>
       </c>
       <c r="AZ49" s="11" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
-    <row r="50" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>388</v>
       </c>
@@ -11201,10 +11233,10 @@
         <v>0</v>
       </c>
       <c r="AZ50" s="11" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
-    <row r="51" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>396</v>
       </c>
@@ -11357,10 +11389,10 @@
         <v>32.4</v>
       </c>
       <c r="AZ51" s="11" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>400</v>
       </c>
@@ -11500,10 +11532,10 @@
         <v>30</v>
       </c>
       <c r="AZ52" s="11" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
-    <row r="53" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>407</v>
       </c>
@@ -11639,10 +11671,10 @@
         <v>100</v>
       </c>
       <c r="AZ53" s="11" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
-    <row r="54" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>2025002700023</v>
       </c>
@@ -11791,10 +11823,10 @@
         <v>100</v>
       </c>
       <c r="AZ54" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="55" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>419</v>
       </c>
@@ -11941,10 +11973,10 @@
         <v>100</v>
       </c>
       <c r="AZ55" s="11" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
-    <row r="56" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>427</v>
       </c>
@@ -12084,10 +12116,10 @@
         <v>0</v>
       </c>
       <c r="AZ56" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
-    <row r="57" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>435</v>
       </c>
@@ -12223,10 +12255,10 @@
         <v>100</v>
       </c>
       <c r="AZ57" s="11" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
-    <row r="58" spans="1:52" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:52" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>441</v>
       </c>
@@ -12360,7 +12392,7 @@
         <v>100</v>
       </c>
       <c r="AZ58" s="11" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -12378,7 +12410,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="25.6640625" customWidth="1"/>
@@ -12395,7 +12427,7 @@
     <col min="40" max="41" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -12441,7 +12473,7 @@
       <c r="AK1" s="15"/>
       <c r="AL1" s="16"/>
     </row>
-    <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -12556,8 +12588,11 @@
       <c r="AL2" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="AM2" s="3" t="s">
+        <v>941</v>
+      </c>
     </row>
-    <row r="3" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>454</v>
       </c>
@@ -12660,8 +12695,9 @@
       <c r="AL3" s="4" t="s">
         <v>460</v>
       </c>
+      <c r="AM3" s="17"/>
     </row>
-    <row r="4" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>461</v>
       </c>
@@ -12764,8 +12800,9 @@
       <c r="AL4" s="4" t="s">
         <v>460</v>
       </c>
+      <c r="AM4" s="17"/>
     </row>
-    <row r="5" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>465</v>
       </c>
@@ -12874,8 +12911,9 @@
       <c r="AL5" s="4" t="s">
         <v>470</v>
       </c>
+      <c r="AM5" s="17"/>
     </row>
-    <row r="6" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>471</v>
       </c>
@@ -12986,8 +13024,9 @@
       <c r="AL6" s="4" t="s">
         <v>476</v>
       </c>
+      <c r="AM6" s="17"/>
     </row>
-    <row r="7" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>477</v>
       </c>
@@ -13098,8 +13137,9 @@
       <c r="AL7" s="4" t="s">
         <v>476</v>
       </c>
+      <c r="AM7" s="17"/>
     </row>
-    <row r="8" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>481</v>
       </c>
@@ -13202,8 +13242,9 @@
       <c r="AL8" s="4" t="s">
         <v>460</v>
       </c>
+      <c r="AM8" s="17"/>
     </row>
-    <row r="9" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>484</v>
       </c>
@@ -13314,8 +13355,9 @@
       <c r="AL9" s="4" t="s">
         <v>460</v>
       </c>
+      <c r="AM9" s="17"/>
     </row>
-    <row r="10" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>488</v>
       </c>
@@ -13422,8 +13464,9 @@
         <v>100</v>
       </c>
       <c r="AL10" s="4"/>
+      <c r="AM10" s="17"/>
     </row>
-    <row r="11" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>491</v>
       </c>
@@ -13532,8 +13575,9 @@
         <v>60</v>
       </c>
       <c r="AL11" s="4"/>
+      <c r="AM11" s="17"/>
     </row>
-    <row r="12" spans="1:38" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>494</v>
       </c>
@@ -13644,8 +13688,9 @@
       <c r="AL12" s="4" t="s">
         <v>498</v>
       </c>
+      <c r="AM12" s="17"/>
     </row>
-    <row r="13" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>499</v>
       </c>
@@ -13752,8 +13797,9 @@
         <v/>
       </c>
       <c r="AL13" s="4"/>
+      <c r="AM13" s="17"/>
     </row>
-    <row r="14" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>502</v>
       </c>
@@ -13862,8 +13908,9 @@
         <v>30</v>
       </c>
       <c r="AL14" s="4"/>
+      <c r="AM14" s="17"/>
     </row>
-    <row r="15" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>505</v>
       </c>
@@ -13970,8 +14017,9 @@
         <v>100</v>
       </c>
       <c r="AL15" s="4"/>
+      <c r="AM15" s="17"/>
     </row>
-    <row r="16" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>2025002700010</v>
       </c>
@@ -14076,8 +14124,9 @@
         <v/>
       </c>
       <c r="AL16" s="4"/>
+      <c r="AM16" s="17"/>
     </row>
-    <row r="17" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>511</v>
       </c>
@@ -14176,8 +14225,9 @@
         <v>40</v>
       </c>
       <c r="AL17" s="4"/>
+      <c r="AM17" s="17"/>
     </row>
-    <row r="18" spans="1:38" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>514</v>
       </c>
@@ -14274,6 +14324,7 @@
         <v/>
       </c>
       <c r="AL18" s="4"/>
+      <c r="AM18" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -14290,13 +14341,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:S104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="18" width="25.6640625" customWidth="1"/>
+    <col min="19" max="19" width="30.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -14318,7 +14370,7 @@
       <c r="Q1" s="12"/>
       <c r="R1" s="12"/>
     </row>
-    <row r="2" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -14373,8 +14425,11 @@
       <c r="R2" s="1" t="s">
         <v>519</v>
       </c>
+      <c r="S2" s="3" t="s">
+        <v>941</v>
+      </c>
     </row>
-    <row r="3" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>520</v>
       </c>
@@ -14425,8 +14480,9 @@
         <v>99.82</v>
       </c>
       <c r="R3" s="4"/>
+      <c r="S3" s="17"/>
     </row>
-    <row r="4" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>525</v>
       </c>
@@ -14477,8 +14533,9 @@
         <v>0</v>
       </c>
       <c r="R4" s="4"/>
+      <c r="S4" s="17"/>
     </row>
-    <row r="5" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>529</v>
       </c>
@@ -14529,8 +14586,9 @@
         <v>98.2</v>
       </c>
       <c r="R5" s="4"/>
+      <c r="S5" s="17"/>
     </row>
-    <row r="6" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>533</v>
       </c>
@@ -14581,8 +14639,9 @@
         <v>99.98</v>
       </c>
       <c r="R6" s="4"/>
+      <c r="S6" s="17"/>
     </row>
-    <row r="7" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>537</v>
       </c>
@@ -14633,8 +14692,9 @@
         <v>99.51</v>
       </c>
       <c r="R7" s="4"/>
+      <c r="S7" s="17"/>
     </row>
-    <row r="8" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>541</v>
       </c>
@@ -14685,8 +14745,9 @@
         <v>49.54</v>
       </c>
       <c r="R8" s="4"/>
+      <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>545</v>
       </c>
@@ -14737,8 +14798,9 @@
         <v>99.56</v>
       </c>
       <c r="R9" s="4"/>
+      <c r="S9" s="17"/>
     </row>
-    <row r="10" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>550</v>
       </c>
@@ -14789,8 +14851,9 @@
         <v>85.88</v>
       </c>
       <c r="R10" s="4"/>
+      <c r="S10" s="17"/>
     </row>
-    <row r="11" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>555</v>
       </c>
@@ -14841,8 +14904,9 @@
         <v>89.9</v>
       </c>
       <c r="R11" s="4"/>
+      <c r="S11" s="17"/>
     </row>
-    <row r="12" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>559</v>
       </c>
@@ -14893,8 +14957,9 @@
         <v>97.78</v>
       </c>
       <c r="R12" s="4"/>
+      <c r="S12" s="17"/>
     </row>
-    <row r="13" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>564</v>
       </c>
@@ -14945,8 +15010,9 @@
         <v>99.87</v>
       </c>
       <c r="R13" s="4"/>
+      <c r="S13" s="17"/>
     </row>
-    <row r="14" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>570</v>
       </c>
@@ -14997,8 +15063,9 @@
         <v>95.45</v>
       </c>
       <c r="R14" s="4"/>
+      <c r="S14" s="17"/>
     </row>
-    <row r="15" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>575</v>
       </c>
@@ -15049,8 +15116,9 @@
         <v>99.97</v>
       </c>
       <c r="R15" s="4"/>
+      <c r="S15" s="17"/>
     </row>
-    <row r="16" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>579</v>
       </c>
@@ -15101,8 +15169,9 @@
         <v>97.25</v>
       </c>
       <c r="R16" s="4"/>
+      <c r="S16" s="17"/>
     </row>
-    <row r="17" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>583</v>
       </c>
@@ -15153,8 +15222,9 @@
         <v>97.16</v>
       </c>
       <c r="R17" s="4"/>
+      <c r="S17" s="17"/>
     </row>
-    <row r="18" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>587</v>
       </c>
@@ -15205,8 +15275,9 @@
         <v>86.62</v>
       </c>
       <c r="R18" s="4"/>
+      <c r="S18" s="17"/>
     </row>
-    <row r="19" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>591</v>
       </c>
@@ -15257,8 +15328,9 @@
         <v>77.59</v>
       </c>
       <c r="R19" s="4"/>
+      <c r="S19" s="17"/>
     </row>
-    <row r="20" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>595</v>
       </c>
@@ -15309,8 +15381,9 @@
         <v>181.2</v>
       </c>
       <c r="R20" s="4"/>
+      <c r="S20" s="17"/>
     </row>
-    <row r="21" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>599</v>
       </c>
@@ -15361,8 +15434,9 @@
         <v>89.3</v>
       </c>
       <c r="R21" s="4"/>
+      <c r="S21" s="17"/>
     </row>
-    <row r="22" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>603</v>
       </c>
@@ -15413,8 +15487,9 @@
         <v>97.57</v>
       </c>
       <c r="R22" s="4"/>
+      <c r="S22" s="17"/>
     </row>
-    <row r="23" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>607</v>
       </c>
@@ -15465,8 +15540,9 @@
         <v>91.85</v>
       </c>
       <c r="R23" s="4"/>
+      <c r="S23" s="17"/>
     </row>
-    <row r="24" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>611</v>
       </c>
@@ -15517,8 +15593,9 @@
         <v>95.75</v>
       </c>
       <c r="R24" s="4"/>
+      <c r="S24" s="17"/>
     </row>
-    <row r="25" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>615</v>
       </c>
@@ -15569,8 +15646,9 @@
         <v>97.23</v>
       </c>
       <c r="R25" s="4"/>
+      <c r="S25" s="17"/>
     </row>
-    <row r="26" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>619</v>
       </c>
@@ -15621,8 +15699,9 @@
         <v>86.53</v>
       </c>
       <c r="R26" s="4"/>
+      <c r="S26" s="17"/>
     </row>
-    <row r="27" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>623</v>
       </c>
@@ -15673,8 +15752,9 @@
         <v>87.69</v>
       </c>
       <c r="R27" s="4"/>
+      <c r="S27" s="17"/>
     </row>
-    <row r="28" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>627</v>
       </c>
@@ -15725,8 +15805,9 @@
         <v>99.24</v>
       </c>
       <c r="R28" s="4"/>
+      <c r="S28" s="17"/>
     </row>
-    <row r="29" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>632</v>
       </c>
@@ -15777,8 +15858,9 @@
         <v>97.75</v>
       </c>
       <c r="R29" s="4"/>
+      <c r="S29" s="17"/>
     </row>
-    <row r="30" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>636</v>
       </c>
@@ -15829,8 +15911,9 @@
         <v>93.98</v>
       </c>
       <c r="R30" s="4"/>
+      <c r="S30" s="17"/>
     </row>
-    <row r="31" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>639</v>
       </c>
@@ -15881,8 +15964,9 @@
         <v>100</v>
       </c>
       <c r="R31" s="4"/>
+      <c r="S31" s="17"/>
     </row>
-    <row r="32" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>644</v>
       </c>
@@ -15933,8 +16017,9 @@
         <v>99.73</v>
       </c>
       <c r="R32" s="4"/>
+      <c r="S32" s="17"/>
     </row>
-    <row r="33" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>647</v>
       </c>
@@ -15985,8 +16070,9 @@
         <v>100</v>
       </c>
       <c r="R33" s="4"/>
+      <c r="S33" s="17"/>
     </row>
-    <row r="34" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>650</v>
       </c>
@@ -16037,8 +16123,9 @@
         <v>100</v>
       </c>
       <c r="R34" s="4"/>
+      <c r="S34" s="17"/>
     </row>
-    <row r="35" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>653</v>
       </c>
@@ -16089,8 +16176,9 @@
         <v>100</v>
       </c>
       <c r="R35" s="4"/>
+      <c r="S35" s="17"/>
     </row>
-    <row r="36" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>657</v>
       </c>
@@ -16141,8 +16229,9 @@
         <v>99.14</v>
       </c>
       <c r="R36" s="4"/>
+      <c r="S36" s="17"/>
     </row>
-    <row r="37" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>661</v>
       </c>
@@ -16193,8 +16282,9 @@
         <v>76.930000000000007</v>
       </c>
       <c r="R37" s="4"/>
+      <c r="S37" s="17"/>
     </row>
-    <row r="38" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>665</v>
       </c>
@@ -16243,8 +16333,9 @@
         <v>101.36</v>
       </c>
       <c r="R38" s="4"/>
+      <c r="S38" s="17"/>
     </row>
-    <row r="39" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>669</v>
       </c>
@@ -16295,8 +16386,9 @@
         <v>99.96</v>
       </c>
       <c r="R39" s="4"/>
+      <c r="S39" s="17"/>
     </row>
-    <row r="40" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>673</v>
       </c>
@@ -16347,8 +16439,9 @@
         <v>98.42</v>
       </c>
       <c r="R40" s="4"/>
+      <c r="S40" s="17"/>
     </row>
-    <row r="41" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>677</v>
       </c>
@@ -16399,8 +16492,9 @@
         <v>98.28</v>
       </c>
       <c r="R41" s="4"/>
+      <c r="S41" s="17"/>
     </row>
-    <row r="42" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>680</v>
       </c>
@@ -16451,8 +16545,9 @@
         <v>99.17</v>
       </c>
       <c r="R42" s="4"/>
+      <c r="S42" s="17"/>
     </row>
-    <row r="43" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>683</v>
       </c>
@@ -16501,8 +16596,9 @@
         <v>102.12</v>
       </c>
       <c r="R43" s="4"/>
+      <c r="S43" s="17"/>
     </row>
-    <row r="44" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>686</v>
       </c>
@@ -16553,8 +16649,9 @@
         <v>90.22</v>
       </c>
       <c r="R44" s="4"/>
+      <c r="S44" s="17"/>
     </row>
-    <row r="45" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>689</v>
       </c>
@@ -16605,8 +16702,9 @@
         <v>90.65</v>
       </c>
       <c r="R45" s="4"/>
+      <c r="S45" s="17"/>
     </row>
-    <row r="46" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>693</v>
       </c>
@@ -16657,8 +16755,9 @@
         <v>93.32</v>
       </c>
       <c r="R46" s="4"/>
+      <c r="S46" s="17"/>
     </row>
-    <row r="47" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>697</v>
       </c>
@@ -16709,8 +16808,9 @@
         <v>100</v>
       </c>
       <c r="R47" s="4"/>
+      <c r="S47" s="17"/>
     </row>
-    <row r="48" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>700</v>
       </c>
@@ -16761,8 +16861,9 @@
         <v>86.25</v>
       </c>
       <c r="R48" s="4"/>
+      <c r="S48" s="17"/>
     </row>
-    <row r="49" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>704</v>
       </c>
@@ -16813,8 +16914,9 @@
         <v>98.13</v>
       </c>
       <c r="R49" s="4"/>
+      <c r="S49" s="17"/>
     </row>
-    <row r="50" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>707</v>
       </c>
@@ -16865,8 +16967,9 @@
         <v>100</v>
       </c>
       <c r="R50" s="4"/>
+      <c r="S50" s="17"/>
     </row>
-    <row r="51" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>710</v>
       </c>
@@ -16915,8 +17018,9 @@
         <v>65.83</v>
       </c>
       <c r="R51" s="4"/>
+      <c r="S51" s="17"/>
     </row>
-    <row r="52" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>714</v>
       </c>
@@ -16967,8 +17071,9 @@
         <v>99.91</v>
       </c>
       <c r="R52" s="4"/>
+      <c r="S52" s="17"/>
     </row>
-    <row r="53" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>717</v>
       </c>
@@ -17019,8 +17124,9 @@
         <v>87.3</v>
       </c>
       <c r="R53" s="4"/>
+      <c r="S53" s="17"/>
     </row>
-    <row r="54" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>720</v>
       </c>
@@ -17071,8 +17177,9 @@
         <v>84.17</v>
       </c>
       <c r="R54" s="4"/>
+      <c r="S54" s="17"/>
     </row>
-    <row r="55" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>723</v>
       </c>
@@ -17123,8 +17230,9 @@
         <v>100</v>
       </c>
       <c r="R55" s="4"/>
+      <c r="S55" s="17"/>
     </row>
-    <row r="56" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>726</v>
       </c>
@@ -17175,8 +17283,9 @@
         <v>99.46</v>
       </c>
       <c r="R56" s="4"/>
+      <c r="S56" s="17"/>
     </row>
-    <row r="57" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>729</v>
       </c>
@@ -17227,8 +17336,9 @@
         <v>58.7</v>
       </c>
       <c r="R57" s="4"/>
+      <c r="S57" s="17"/>
     </row>
-    <row r="58" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>733</v>
       </c>
@@ -17279,8 +17389,9 @@
         <v>100.53</v>
       </c>
       <c r="R58" s="4"/>
+      <c r="S58" s="17"/>
     </row>
-    <row r="59" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>736</v>
       </c>
@@ -17331,8 +17442,9 @@
         <v>61.03</v>
       </c>
       <c r="R59" s="4"/>
+      <c r="S59" s="17"/>
     </row>
-    <row r="60" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>739</v>
       </c>
@@ -17383,8 +17495,9 @@
         <v>100</v>
       </c>
       <c r="R60" s="4"/>
+      <c r="S60" s="17"/>
     </row>
-    <row r="61" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
         <v>742</v>
       </c>
@@ -17435,8 +17548,9 @@
         <v>94.38</v>
       </c>
       <c r="R61" s="4"/>
+      <c r="S61" s="17"/>
     </row>
-    <row r="62" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
         <v>746</v>
       </c>
@@ -17487,8 +17601,9 @@
         <v>60.48</v>
       </c>
       <c r="R62" s="4"/>
+      <c r="S62" s="17"/>
     </row>
-    <row r="63" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
         <v>749</v>
       </c>
@@ -17539,8 +17654,9 @@
         <v>83.98</v>
       </c>
       <c r="R63" s="4"/>
+      <c r="S63" s="17"/>
     </row>
-    <row r="64" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
         <v>753</v>
       </c>
@@ -17591,8 +17707,9 @@
         <v>94.51</v>
       </c>
       <c r="R64" s="4"/>
+      <c r="S64" s="17"/>
     </row>
-    <row r="65" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
         <v>757</v>
       </c>
@@ -17643,8 +17760,9 @@
         <v>81.650000000000006</v>
       </c>
       <c r="R65" s="4"/>
+      <c r="S65" s="17"/>
     </row>
-    <row r="66" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
         <v>760</v>
       </c>
@@ -17695,8 +17813,9 @@
         <v>95.06</v>
       </c>
       <c r="R66" s="4"/>
+      <c r="S66" s="17"/>
     </row>
-    <row r="67" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
         <v>763</v>
       </c>
@@ -17747,8 +17866,9 @@
         <v>96.7</v>
       </c>
       <c r="R67" s="4"/>
+      <c r="S67" s="17"/>
     </row>
-    <row r="68" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
         <v>766</v>
       </c>
@@ -17799,8 +17919,9 @@
         <v>93.62</v>
       </c>
       <c r="R68" s="4"/>
+      <c r="S68" s="17"/>
     </row>
-    <row r="69" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
         <v>769</v>
       </c>
@@ -17851,8 +17972,9 @@
         <v>88.96</v>
       </c>
       <c r="R69" s="4"/>
+      <c r="S69" s="17"/>
     </row>
-    <row r="70" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
         <v>772</v>
       </c>
@@ -17903,8 +18025,9 @@
         <v>43.52</v>
       </c>
       <c r="R70" s="4"/>
+      <c r="S70" s="17"/>
     </row>
-    <row r="71" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
         <v>776</v>
       </c>
@@ -17955,8 +18078,9 @@
         <v>98.96</v>
       </c>
       <c r="R71" s="4"/>
+      <c r="S71" s="17"/>
     </row>
-    <row r="72" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
         <v>779</v>
       </c>
@@ -18007,8 +18131,9 @@
         <v>99.66</v>
       </c>
       <c r="R72" s="4"/>
+      <c r="S72" s="17"/>
     </row>
-    <row r="73" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
         <v>783</v>
       </c>
@@ -18059,8 +18184,9 @@
         <v>98.46</v>
       </c>
       <c r="R73" s="4"/>
+      <c r="S73" s="17"/>
     </row>
-    <row r="74" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
         <v>786</v>
       </c>
@@ -18111,8 +18237,9 @@
         <v>99.61</v>
       </c>
       <c r="R74" s="4"/>
+      <c r="S74" s="17"/>
     </row>
-    <row r="75" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
         <v>789</v>
       </c>
@@ -18163,8 +18290,9 @@
         <v>99.34</v>
       </c>
       <c r="R75" s="4"/>
+      <c r="S75" s="17"/>
     </row>
-    <row r="76" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
         <v>792</v>
       </c>
@@ -18215,8 +18343,9 @@
         <v>99.86</v>
       </c>
       <c r="R76" s="4"/>
+      <c r="S76" s="17"/>
     </row>
-    <row r="77" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
         <v>795</v>
       </c>
@@ -18261,8 +18390,9 @@
         <v>0</v>
       </c>
       <c r="R77" s="4"/>
+      <c r="S77" s="17"/>
     </row>
-    <row r="78" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
         <v>799</v>
       </c>
@@ -18313,8 +18443,9 @@
         <v>92.14</v>
       </c>
       <c r="R78" s="4"/>
+      <c r="S78" s="17"/>
     </row>
-    <row r="79" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
         <v>803</v>
       </c>
@@ -18365,8 +18496,9 @@
         <v>99.97</v>
       </c>
       <c r="R79" s="4"/>
+      <c r="S79" s="17"/>
     </row>
-    <row r="80" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
         <v>807</v>
       </c>
@@ -18415,8 +18547,9 @@
         <v>82.2</v>
       </c>
       <c r="R80" s="4"/>
+      <c r="S80" s="17"/>
     </row>
-    <row r="81" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
         <v>811</v>
       </c>
@@ -18467,8 +18600,9 @@
         <v>73.13</v>
       </c>
       <c r="R81" s="4"/>
+      <c r="S81" s="17"/>
     </row>
-    <row r="82" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
         <v>814</v>
       </c>
@@ -18519,8 +18653,9 @@
         <v>92.4</v>
       </c>
       <c r="R82" s="4"/>
+      <c r="S82" s="17"/>
     </row>
-    <row r="83" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
         <v>817</v>
       </c>
@@ -18571,8 +18706,9 @@
         <v>95.06</v>
       </c>
       <c r="R83" s="4"/>
+      <c r="S83" s="17"/>
     </row>
-    <row r="84" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
         <v>821</v>
       </c>
@@ -18623,8 +18759,9 @@
         <v>82.73</v>
       </c>
       <c r="R84" s="4"/>
+      <c r="S84" s="17"/>
     </row>
-    <row r="85" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
         <v>825</v>
       </c>
@@ -18675,8 +18812,9 @@
         <v>93.6</v>
       </c>
       <c r="R85" s="4"/>
+      <c r="S85" s="17"/>
     </row>
-    <row r="86" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>829</v>
       </c>
@@ -18727,8 +18865,9 @@
         <v>90.33</v>
       </c>
       <c r="R86" s="4"/>
+      <c r="S86" s="17"/>
     </row>
-    <row r="87" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4" t="s">
         <v>833</v>
       </c>
@@ -18779,8 +18918,9 @@
         <v>66.63</v>
       </c>
       <c r="R87" s="4"/>
+      <c r="S87" s="17"/>
     </row>
-    <row r="88" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4" t="s">
         <v>837</v>
       </c>
@@ -18831,8 +18971,9 @@
         <v>75.38</v>
       </c>
       <c r="R88" s="4"/>
+      <c r="S88" s="17"/>
     </row>
-    <row r="89" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
         <v>841</v>
       </c>
@@ -18883,8 +19024,9 @@
         <v>92.23</v>
       </c>
       <c r="R89" s="4"/>
+      <c r="S89" s="17"/>
     </row>
-    <row r="90" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="4" t="s">
         <v>846</v>
       </c>
@@ -18935,8 +19077,9 @@
         <v>22.96</v>
       </c>
       <c r="R90" s="4"/>
+      <c r="S90" s="17"/>
     </row>
-    <row r="91" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="4" t="s">
         <v>850</v>
       </c>
@@ -18987,8 +19130,9 @@
         <v>0</v>
       </c>
       <c r="R91" s="4"/>
+      <c r="S91" s="17"/>
     </row>
-    <row r="92" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="4" t="s">
         <v>853</v>
       </c>
@@ -19039,8 +19183,9 @@
         <v>1.17</v>
       </c>
       <c r="R92" s="4"/>
+      <c r="S92" s="17"/>
     </row>
-    <row r="93" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4" t="s">
         <v>856</v>
       </c>
@@ -19089,8 +19234,9 @@
         <v>10.53</v>
       </c>
       <c r="R93" s="4"/>
+      <c r="S93" s="17"/>
     </row>
-    <row r="94" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="4" t="s">
         <v>858</v>
       </c>
@@ -19139,8 +19285,9 @@
         <v>90</v>
       </c>
       <c r="R94" s="4"/>
+      <c r="S94" s="17"/>
     </row>
-    <row r="95" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="4" t="s">
         <v>861</v>
       </c>
@@ -19191,8 +19338,9 @@
         <v>69.88</v>
       </c>
       <c r="R95" s="4"/>
+      <c r="S95" s="17"/>
     </row>
-    <row r="96" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="4" t="s">
         <v>865</v>
       </c>
@@ -19239,8 +19387,9 @@
         <v>0</v>
       </c>
       <c r="R96" s="4"/>
+      <c r="S96" s="17"/>
     </row>
-    <row r="97" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4" t="s">
         <v>868</v>
       </c>
@@ -19291,8 +19440,9 @@
         <v>24.54</v>
       </c>
       <c r="R97" s="4"/>
+      <c r="S97" s="17"/>
     </row>
-    <row r="98" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="4" t="s">
         <v>872</v>
       </c>
@@ -19343,8 +19493,9 @@
         <v>27.96</v>
       </c>
       <c r="R98" s="4"/>
+      <c r="S98" s="17"/>
     </row>
-    <row r="99" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="4" t="s">
         <v>876</v>
       </c>
@@ -19393,8 +19544,9 @@
         <v>98.93</v>
       </c>
       <c r="R99" s="4"/>
+      <c r="S99" s="17"/>
     </row>
-    <row r="100" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="4" t="s">
         <v>879</v>
       </c>
@@ -19445,8 +19597,9 @@
         <v>99.22</v>
       </c>
       <c r="R100" s="4"/>
+      <c r="S100" s="17"/>
     </row>
-    <row r="101" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4" t="s">
         <v>883</v>
       </c>
@@ -19497,8 +19650,9 @@
         <v>99.98</v>
       </c>
       <c r="R101" s="4"/>
+      <c r="S101" s="17"/>
     </row>
-    <row r="102" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4" t="s">
         <v>887</v>
       </c>
@@ -19549,8 +19703,9 @@
         <v>100</v>
       </c>
       <c r="R102" s="4"/>
+      <c r="S102" s="17"/>
     </row>
-    <row r="103" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4" t="s">
         <v>891</v>
       </c>
@@ -19601,8 +19756,9 @@
         <v>99.99</v>
       </c>
       <c r="R103" s="4"/>
+      <c r="S103" s="17"/>
     </row>
-    <row r="104" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4" t="s">
         <v>894</v>
       </c>
@@ -19649,6 +19805,7 @@
         <v>0</v>
       </c>
       <c r="R104" s="4"/>
+      <c r="S104" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -19662,6 +19819,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19805,22 +19977,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55278F2-F788-4282-8A5E-A876C5B8CDED}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19836,21 +20010,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D57C589-B523-487F-B667-E8243D17AABA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41194656-B86B-41A7-B0B7-6431E5F99E02}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -2,20 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zgama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7012361-61F7-406D-ACA9-00C5E962322E}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
-    <sheet name="OtrosEjecutoresDescentralizadas" sheetId="2" r:id="rId2"/>
-    <sheet name="OtrosEjecutoresMunicipios" sheetId="3" r:id="rId3"/>
+    <sheet name="ListadoMunicipios" sheetId="5" r:id="rId1"/>
+    <sheet name="Ajustes" sheetId="4" r:id="rId2"/>
+    <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId3"/>
+    <sheet name="OtrosEjecutoresDescentralizadas" sheetId="2" r:id="rId4"/>
+    <sheet name="OtrosEjecutoresMunicipios" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="909">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1069">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -2888,6 +2890,489 @@
   <si>
     <t>Proyecto en estado “Sin contratar”, recién aprobado</t>
   </si>
+  <si>
+    <t>RESPONSABLE CARGUE EN GESPROY</t>
+  </si>
+  <si>
+    <t>MUNICIPIOS</t>
+  </si>
+  <si>
+    <t>ZAMARA GARCÍA MARTÍNEZ</t>
+  </si>
+  <si>
+    <t>YEIMI MONTAÑA DÍAZ</t>
+  </si>
+  <si>
+    <t>SERGIO VILLALBA MERCADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS FERNANDO ARRIETA PINZÓN </t>
+  </si>
+  <si>
+    <t>YEIMI MONTAÑA DÍAZ
+ASDRUVAL AVILEZ DÍAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERGIO VILLALBA MERCADO
+ASDRUVAL AVILEZ DÍAZ
+</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>OSVALDO SIERRA CARVAJALINO</t>
+  </si>
+  <si>
+    <t>Sincelejo</t>
+  </si>
+  <si>
+    <t>Todo el Departamento de Sucre</t>
+  </si>
+  <si>
+    <t>San Benito Abad, Majagual, Sucre</t>
+  </si>
+  <si>
+    <t>El Roble, Caimito, San Marcos</t>
+  </si>
+  <si>
+    <t>Corozal, San Onofre, Morroa, Majagual, San Marcos</t>
+  </si>
+  <si>
+    <t>San Benito Abad</t>
+  </si>
+  <si>
+    <t>San Onofre</t>
+  </si>
+  <si>
+    <t>Morroa, Colosó, San Marcos, San José de Toluviejo, Coveñas, Majagual, Sucre, Ovejas, San Benito Abad, Santiago de Tolú, San Pedro, Los Palmitos, Sincelejo, Corozal, Buenavista, Caimito, Sampués, Guaranda, San Luis de Sincé, San Onofre, San Juan de Betulia, El Roble, Palmito, Galeras, La Unión, Chalán</t>
+  </si>
+  <si>
+    <t>San Marcos, Caimito, San Benito Abad, Guaranda, Sucre, Majagual</t>
+  </si>
+  <si>
+    <t>La Unión</t>
+  </si>
+  <si>
+    <t>Majagual, San Benito Abad, Corozal, Ovejas, San Onofre</t>
+  </si>
+  <si>
+    <t>Santiago de Tolú</t>
+  </si>
+  <si>
+    <t>Colosó, Morroa</t>
+  </si>
+  <si>
+    <t>Sucre</t>
+  </si>
+  <si>
+    <t>Corozal</t>
+  </si>
+  <si>
+    <t>El Roble, Sampués, Galeras, Buenavista, Los Palmitos, Corozal, Ovejas, Colosó, San José de Toluviejo</t>
+  </si>
+  <si>
+    <t>San Juan de Betulia, San Marcos</t>
+  </si>
+  <si>
+    <t>Colosó, San José de Toluviejo</t>
+  </si>
+  <si>
+    <t>Sucre, San Marcos, Guaranda, Caimito, La Unión, San Benito Abad, Majagual</t>
+  </si>
+  <si>
+    <t>Ovejas, Santiago de Tolú, Corozal</t>
+  </si>
+  <si>
+    <t>San José de Toluviejo</t>
+  </si>
+  <si>
+    <t>San Marcos, Sucre</t>
+  </si>
+  <si>
+    <t>Chalán</t>
+  </si>
+  <si>
+    <t>Coveñas</t>
+  </si>
+  <si>
+    <t>Sincelejo, Sampués, Morroa</t>
+  </si>
+  <si>
+    <t>San Benito Abad, Galeras</t>
+  </si>
+  <si>
+    <t>Caimito, El Roble, San Onofre, Palmito, Santiago de Tolú</t>
+  </si>
+  <si>
+    <t>San José de Toluviejo, Sincelejo, Galeras</t>
+  </si>
+  <si>
+    <t>2024702150036</t>
+  </si>
+  <si>
+    <t>Morroa, San Pedro, Santiago de Tolú, Sincelejo, Corozal</t>
+  </si>
+  <si>
+    <t>San Luis de Sincé, Caimito</t>
+  </si>
+  <si>
+    <t>Sincelejo, Santiago de Tolú</t>
+  </si>
+  <si>
+    <t>Chalán, Sincelejo, Ovejas, Buenavista, San Juan de Betulia, Los Palmitos, Galeras, Sampués, El Roble, Corozal, San Pedro, Colosó, Morroa, San Luis de Sincé</t>
+  </si>
+  <si>
+    <t>El Roble</t>
+  </si>
+  <si>
+    <t>Majagual</t>
+  </si>
+  <si>
+    <t>Morroa, Colosó</t>
+  </si>
+  <si>
+    <t>Ovejas</t>
+  </si>
+  <si>
+    <t>San Pedro</t>
+  </si>
+  <si>
+    <t>Sucre, Majagual, Guaranda</t>
+  </si>
+  <si>
+    <t>Coveñas, Santiago de Tolú</t>
+  </si>
+  <si>
+    <t>Los Palmitos</t>
+  </si>
+  <si>
+    <t>Buenavista, San Luis de Sincé</t>
+  </si>
+  <si>
+    <t>Los Palmitos, Ovejas, Colosó, San José de Toluviejo</t>
+  </si>
+  <si>
+    <t>Barranquilla</t>
+  </si>
+  <si>
+    <t>Chía</t>
+  </si>
+  <si>
+    <t>Santiago de Cali</t>
+  </si>
+  <si>
+    <t>Cartagena de Indias</t>
+  </si>
+  <si>
+    <t>Medellín, San Andrés, Leticia, Bogotá, D.C., Palmira, Manizales</t>
+  </si>
+  <si>
+    <t>Manizales</t>
+  </si>
+  <si>
+    <t>Cartagena de Indias, Sincelejo, Valledupar</t>
+  </si>
+  <si>
+    <t>Medellín</t>
+  </si>
+  <si>
+    <t>Chimichagua, El Paso, Gamarra, La Paz, Valledupar, Chiriguaná, Pueblo Bello, Aguachica, Curumaní</t>
+  </si>
+  <si>
+    <t>Galeras</t>
+  </si>
+  <si>
+    <t>La Unión, Caimito</t>
+  </si>
+  <si>
+    <t>San Juan de Betulia, Corozal, San Luis de Sincé</t>
+  </si>
+  <si>
+    <t>Achí, Magangué, Arjona</t>
+  </si>
+  <si>
+    <t>Puerto Colombia</t>
+  </si>
+  <si>
+    <t>Cartagena de Indias, Santiago de Tolú, Coveñas</t>
+  </si>
+  <si>
+    <t>Santa Marta, Puebloviejo</t>
+  </si>
+  <si>
+    <t>Ayapel, Unión Panamericana, San Marcos, Majagual</t>
+  </si>
+  <si>
+    <t>Santa Marta, Puerto Colombia, Sitionuevo, San Andrés, Piojó, Barranquilla, Juan de Acosta, Tubará, Ciénaga, Puebloviejo</t>
+  </si>
+  <si>
+    <t>Palmito, Sincelejo, Corozal, Sampués, San Benito Abad</t>
+  </si>
+  <si>
+    <t>Cereté, Pueblo Bello, Aguachica, Los Córdobas, Montería, Manaure Balcón del Cesar, Tierralta, Lorica, Valledupar</t>
+  </si>
+  <si>
+    <t>Barranquilla, Cartagena de Indias</t>
+  </si>
+  <si>
+    <t>Caimito, Majagual, La Unión, San Benito Abad, Sucre, Guaranda, San Marcos</t>
+  </si>
+  <si>
+    <t>Santa Marta, Cartagena de Indias</t>
+  </si>
+  <si>
+    <t>Clemencia, Cartagena de Indias, Santa Catalina, Sincelejo</t>
+  </si>
+  <si>
+    <t>Tierralta, Valencia</t>
+  </si>
+  <si>
+    <t>Dibulla, Riohacha, Santa Marta, Zona Bananera</t>
+  </si>
+  <si>
+    <t>Cartagena de Indias, San Martín de Loba</t>
+  </si>
+  <si>
+    <t>Chalán, Colosó, Ovejas</t>
+  </si>
+  <si>
+    <t>Manizales, Bogotá, D.C., Palmira, Medellín, San Andrés</t>
+  </si>
+  <si>
+    <t>Montería</t>
+  </si>
+  <si>
+    <t>San Andrés</t>
+  </si>
+  <si>
+    <t>San Antero, Guaranda, Chinú, Montería, Sincelejo, Moñitos, Cereté, Los Córdobas, Puerto Escondido, Sucre, San Bernardo del Viento, Majagual</t>
+  </si>
+  <si>
+    <t>Cotorra, Montería, Santa Marta, Cereté, Fundación, Plato</t>
+  </si>
+  <si>
+    <t>Santa Cruz de Mompox, Planeta Rica, San Benito Abad, Ayapel, San Marcos, Montería, Morales, Magangué, Sucre</t>
+  </si>
+  <si>
+    <t>San Luis de Sincé</t>
+  </si>
+  <si>
+    <t>San Marcos</t>
+  </si>
+  <si>
+    <t>Bogotá, D.C., Villa de Leyva</t>
+  </si>
+  <si>
+    <t>Ovejas, Colosó, Morroa</t>
+  </si>
+  <si>
+    <t>Buenavista</t>
+  </si>
+  <si>
+    <t>Sampués</t>
+  </si>
+  <si>
+    <t>Guaranda, Majagual</t>
+  </si>
+  <si>
+    <t>Cartagena de Indias, Caimito, Guaranda, San Juan de Betulia, Santiago de Tolú, Ciénaga, Majagual</t>
+  </si>
+  <si>
+    <t>TIPO DE CAMBIO</t>
+  </si>
+  <si>
+    <t>CAMBIO</t>
+  </si>
+  <si>
+    <t>MATRIZ</t>
+  </si>
+  <si>
+    <t>HERRAMIENTA</t>
+  </si>
+  <si>
+    <t>REALIZADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGREGAR COLUMNA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPONSABLE DEL PROYECTO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPARTAMENTO </t>
+  </si>
+  <si>
+    <t>Consolidación regalías</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>HORIZONTE EN DESCENTRALIZADAS</t>
+  </si>
+  <si>
+    <t>DESCENTRALIZADAS</t>
+  </si>
+  <si>
+    <t>AGREGAR CARACTERISTICAS</t>
+  </si>
+  <si>
+    <t>% FÍSICO Y FINANCIERO EN LA TARJETA DE ESTADO DEL PROYECTO</t>
+  </si>
+  <si>
+    <t>Seguimiento Regalías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVISIÓN </t>
+  </si>
+  <si>
+    <t>REPORTE DE EXCEL</t>
+  </si>
+  <si>
+    <t>AJUSTE</t>
+  </si>
+  <si>
+    <t>CÁLCULO H2</t>
+  </si>
+  <si>
+    <t>AGREGAR LOS MUNICIPIOS</t>
+  </si>
+  <si>
+    <t>AGREGAR LAS DESCENTRALIZADAS</t>
+  </si>
+  <si>
+    <t>CAMBIO NOMBRE COLUMNA</t>
+  </si>
+  <si>
+    <t>FECHA DE INCORPORACIÓN DE RECUROS -&gt; FECHA DE INCORPORACIÓN DE RECURSOS</t>
+  </si>
+  <si>
+    <t>DESCENTRALIZADAS Y MUNIICIPIOS</t>
+  </si>
+  <si>
+    <t>AGREGAR COLUMNA DE SECTOR</t>
+  </si>
+  <si>
+    <t>PAGINA FILTRO DE LOS MUNICIPIOS</t>
+  </si>
+  <si>
+    <t>HITO 2 E HITO 1 QUE NO SE REPITAN LOS PROYECTOS</t>
+  </si>
+  <si>
+    <t>PÁGINA REPORTE  SEGUIMIENTO</t>
+  </si>
+  <si>
+    <t>DÍAS DE CORTE Y DÍAS A FECHA ACTUAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOSTRAR COMENTARIOS DE LA MATRIZ EN LOS HITOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGINA REPORTE SEGUIMIENTO </t>
+  </si>
+  <si>
+    <t>AGREGAR LINK SECOP CONTRATOS</t>
+  </si>
+  <si>
+    <t>MATRIZ CONTRATOS REPORTE GESPROY</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>AGREGAR IGPR 2026</t>
+  </si>
+  <si>
+    <t>GRÁFICA EN TIEMPO REAL DE LOS PROYECTOS, MAYOR DINÁMICA</t>
+  </si>
+  <si>
+    <t>SUSPENDIDOS OTRO HITO</t>
+  </si>
+  <si>
+    <t>en el estado que diga el Hito CON SU APELLIDO</t>
+  </si>
+  <si>
+    <t>AJUSTAR LOS QUE ESTÁN EN EJECUCIÓN CONFORME A SU CLASIFICACIÓN</t>
+  </si>
+  <si>
+    <t>HORIZONTE VENCIDO EN 0</t>
+  </si>
+  <si>
+    <t>LIQUIDACIONES QUE SE VEAN LAS FECHAS</t>
+  </si>
+  <si>
+    <t>AGREGAR LOS PROYECTOS EN EJECUCIÓN SOLITOS EN LOS HITOS (CON SU ALERTA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONFIGURAR LOS HITOS QUE NO SE DUPLIQUEN LOS DE CIERRE EN LOS TERMINADOS </t>
+  </si>
+  <si>
+    <t>AJUSTAR DESCENTRALIZADA QUE QUEDE MUY PARECIDO A EL DE DEPARTAMENTOS</t>
+  </si>
+  <si>
+    <t>RESUMEN POR CADA ENTIDAD SE MUESTRE CUANTO ESTÁN POR ESTADO</t>
+  </si>
+  <si>
+    <t>LOS PROYECTOS SIN CONTRATAR QUE CUENTE DÍAS GENERALES</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Subregión</t>
+  </si>
+  <si>
+    <t>Nombre Municipio DANE</t>
+  </si>
+  <si>
+    <t>Nombre Municipios SUTEC</t>
+  </si>
+  <si>
+    <t>Sabanas</t>
+  </si>
+  <si>
+    <t>Morroa</t>
+  </si>
+  <si>
+    <t>San Juan de Betulia</t>
+  </si>
+  <si>
+    <t>San Juan De Betulia</t>
+  </si>
+  <si>
+    <t>San Luis De Sincé</t>
+  </si>
+  <si>
+    <t>Montes de María</t>
+  </si>
+  <si>
+    <t>Colosó</t>
+  </si>
+  <si>
+    <t>Golfo de Morrosquillo</t>
+  </si>
+  <si>
+    <t>San José De Toluviejo</t>
+  </si>
+  <si>
+    <t>Palmito</t>
+  </si>
+  <si>
+    <t>San Jorge</t>
+  </si>
+  <si>
+    <t>Caimito</t>
+  </si>
+  <si>
+    <t>Mojana</t>
+  </si>
+  <si>
+    <t>Guaranda</t>
+  </si>
+  <si>
+    <t>Todas las Subregiones</t>
+  </si>
 </sst>
 </file>
 
@@ -2897,7 +3382,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2925,8 +3410,35 @@
       <name val="Roboto"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Roboto"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2957,8 +3469,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -2981,11 +3505,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3008,11 +3628,377 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3026,9 +4012,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AV59" totalsRowShown="0">
-  <autoFilter ref="A2:AV59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="A1:E26" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AX59" totalsRowShown="0">
+  <autoFilter ref="A2:AX59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="50">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NOMBRE PROYECTO"/>
@@ -3076,16 +4076,18 @@
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
     <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="15"/>
+    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="14"/>
+    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AK18" totalsRowShown="0">
-  <autoFilter ref="A2:AK18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="37">
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AL18" totalsRowShown="0">
+  <autoFilter ref="A2:AL18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -3122,16 +4124,17 @@
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0100-000022000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0100-000023000000}" name="COLUMNA APOYO 2"/>
     <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="12"/>
+    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:R104" totalsRowShown="0">
-  <autoFilter ref="A2:R104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
-  <tableColumns count="18">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="OtrosEjecutoresMunicipios" displayName="OtrosEjecutoresMunicipios" ref="A2:S104" totalsRowShown="0">
+  <autoFilter ref="A2:S104" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
+  <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -3150,6 +4153,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS "/>
+    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3441,18 +4445,843 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146B246E-1041-42FC-9276-EE9890517FFA}">
+  <sheetPr codeName="Hoja5"/>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="24">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>919</v>
+      </c>
+      <c r="D2" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="24">
+        <v>2</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>933</v>
+      </c>
+      <c r="D3" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
+        <v>3</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="24">
+        <v>4</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>959</v>
+      </c>
+      <c r="D5" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="24">
+        <v>6</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="24">
+        <v>7</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
+        <v>8</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>996</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="24">
+        <v>9</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>956</v>
+      </c>
+      <c r="D10" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="24">
+        <v>10</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>971</v>
+      </c>
+      <c r="D11" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="24">
+        <v>11</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>952</v>
+      </c>
+      <c r="D12" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="24">
+        <v>12</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>955</v>
+      </c>
+      <c r="D13" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="24">
+        <v>13</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>941</v>
+      </c>
+      <c r="D14" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="24">
+        <v>14</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="24">
+        <v>15</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>930</v>
+      </c>
+      <c r="D16" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="24">
+        <v>16</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>939</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="24">
+        <v>17</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>942</v>
+      </c>
+      <c r="D18" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="24">
+        <v>18</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>925</v>
+      </c>
+      <c r="D19" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="24">
+        <v>19</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="24">
+        <v>20</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>997</v>
+      </c>
+      <c r="D21" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="24">
+        <v>21</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>924</v>
+      </c>
+      <c r="D22" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="24">
+        <v>22</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>928</v>
+      </c>
+      <c r="D24" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="24">
+        <v>24</v>
+      </c>
+      <c r="B25" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>932</v>
+      </c>
+      <c r="D25" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="24">
+        <v>25</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>953</v>
+      </c>
+      <c r="D26" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="24">
+        <v>26</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C27" s="24" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B28" s="24" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>920</v>
+      </c>
+      <c r="D28" t="s">
+        <v>920</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40494E-F5FA-45B0-8046-A8A35D593322}">
+  <sheetPr codeName="Hoja4"/>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C6" s="15"/>
+      <c r="D6" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="20" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E18" s="19"/>
+    </row>
+    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E19" s="19"/>
+    </row>
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E20" s="19"/>
+    </row>
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E22" s="19"/>
+    </row>
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E23" s="19"/>
+    </row>
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="17"/>
+      <c r="B24" s="18" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+    </row>
+    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="17"/>
+      <c r="B25" s="18" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+    </row>
+    <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV59"/>
+  <sheetPr codeName="Hoja1"/>
+  <dimension ref="A1:AX59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="39" width="25.6640625" customWidth="1"/>
     <col min="40" max="40" width="25.6640625" hidden="1" customWidth="1"/>
     <col min="41" max="45" width="25.6640625" customWidth="1"/>
     <col min="46" max="46" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="47" max="48" width="25.6640625" customWidth="1"/>
+    <col min="47" max="47" width="25.6640625" customWidth="1"/>
+    <col min="48" max="48" width="41.21875" customWidth="1"/>
+    <col min="49" max="49" width="25.21875" customWidth="1"/>
+    <col min="50" max="50" width="25.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:50" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3508,7 +5337,7 @@
       <c r="AU1" s="6"/>
       <c r="AV1" s="6"/>
     </row>
-    <row r="2" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3653,8 +5482,14 @@
       <c r="AV2" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW2" s="8" t="s">
+        <v>909</v>
+      </c>
+      <c r="AX2" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -3794,8 +5629,14 @@
       <c r="AV3" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW3" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX3" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
@@ -3925,8 +5766,14 @@
       <c r="AV4" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW4" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX4" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>73</v>
       </c>
@@ -4066,8 +5913,14 @@
       <c r="AV5" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW5" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX5" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -4209,8 +6062,12 @@
       <c r="AV6" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW6" s="9"/>
+      <c r="AX6" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>90</v>
       </c>
@@ -4350,8 +6207,14 @@
       <c r="AV7" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW7" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX7" s="9" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>101</v>
       </c>
@@ -4491,8 +6354,14 @@
       <c r="AV8" s="3" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="9" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW8" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX8" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>108</v>
       </c>
@@ -4636,8 +6505,14 @@
       <c r="AV9" s="3" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="10" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW9" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX9" s="9" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>115</v>
       </c>
@@ -4777,8 +6652,14 @@
       <c r="AV10" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW10" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX10" s="9" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>122</v>
       </c>
@@ -4918,8 +6799,14 @@
       <c r="AV11" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW11" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX11" s="9" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>127</v>
       </c>
@@ -5059,8 +6946,14 @@
       <c r="AV12" s="3" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="13" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW12" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX12" s="9" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>135</v>
       </c>
@@ -5202,8 +7095,14 @@
       <c r="AV13" s="3" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="14" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW13" s="9" t="s">
+        <v>915</v>
+      </c>
+      <c r="AX13" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>145</v>
       </c>
@@ -5343,8 +7242,14 @@
       <c r="AV14" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="15" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW14" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX14" s="9" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>152</v>
       </c>
@@ -5486,8 +7391,14 @@
       <c r="AV15" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="16" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW15" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX15" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>158</v>
       </c>
@@ -5627,8 +7538,14 @@
       <c r="AV16" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="17" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW16" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX16" s="9" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>164</v>
       </c>
@@ -5770,8 +7687,14 @@
       <c r="AV17" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="18" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW17" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX17" s="9" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>172</v>
       </c>
@@ -5913,8 +7836,14 @@
       <c r="AV18" s="3" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="19" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW18" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX18" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>179</v>
       </c>
@@ -6056,8 +7985,14 @@
       <c r="AV19" s="3" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="20" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW19" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX19" s="9" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>184</v>
       </c>
@@ -6197,8 +8132,14 @@
       <c r="AV20" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW20" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX20" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>189</v>
       </c>
@@ -6340,8 +8281,14 @@
       <c r="AV21" s="3" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="22" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW21" s="9" t="s">
+        <v>916</v>
+      </c>
+      <c r="AX21" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>197</v>
       </c>
@@ -6483,8 +8430,14 @@
       <c r="AV22" s="3" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="23" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW22" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX22" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>205</v>
       </c>
@@ -6618,8 +8571,14 @@
       <c r="AV23" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="24" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW23" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX23" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>211</v>
       </c>
@@ -6753,8 +8712,14 @@
       <c r="AV24" s="3" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="25" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW24" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX24" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>219</v>
       </c>
@@ -6886,8 +8851,14 @@
       <c r="AV25" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="26" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW25" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX25" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>224</v>
       </c>
@@ -7029,8 +9000,14 @@
       <c r="AV26" s="3" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="27" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW26" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX26" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>232</v>
       </c>
@@ -7170,8 +9147,14 @@
       <c r="AV27" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="28" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW27" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX27" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>238</v>
       </c>
@@ -7309,8 +9292,14 @@
       <c r="AV28" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="29" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW28" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX28" s="9" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>244</v>
       </c>
@@ -7450,8 +9439,14 @@
       <c r="AV29" s="3" t="s">
         <v>250</v>
       </c>
-    </row>
-    <row r="30" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW29" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX29" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>251</v>
       </c>
@@ -7585,8 +9580,14 @@
       <c r="AV30" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="31" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW30" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX30" s="9" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>255</v>
       </c>
@@ -7724,8 +9725,14 @@
       <c r="AV31" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW31" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX31" s="9" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>261</v>
       </c>
@@ -7867,8 +9874,14 @@
       <c r="AV32" s="3" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="33" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW32" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX32" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>269</v>
       </c>
@@ -8010,8 +10023,14 @@
       <c r="AV33" s="3" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="34" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW33" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX33" s="9" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>278</v>
       </c>
@@ -8149,8 +10168,14 @@
       <c r="AV34" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="35" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW34" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX34" s="9" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="35" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>284</v>
       </c>
@@ -8280,8 +10305,14 @@
       <c r="AV35" s="3" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="36" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW35" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX35" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="36" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>289</v>
       </c>
@@ -8421,8 +10452,12 @@
       <c r="AV36" s="3" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="37" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW36" s="9"/>
+      <c r="AX36" s="9" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="37" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>296</v>
       </c>
@@ -8560,8 +10595,14 @@
       <c r="AV37" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="38" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW37" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX37" s="9" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>303</v>
       </c>
@@ -8703,8 +10744,14 @@
       <c r="AV38" s="3" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="39" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW38" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX38" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>310</v>
       </c>
@@ -8844,8 +10891,14 @@
       <c r="AV39" s="3" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="40" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW39" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX39" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="40" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>317</v>
       </c>
@@ -8987,8 +11040,14 @@
       <c r="AV40" s="3" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="41" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW40" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX40" s="9" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="41" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>324</v>
       </c>
@@ -9130,8 +11189,14 @@
       <c r="AV41" s="3" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="42" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW41" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX41" s="9" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="42" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>331</v>
       </c>
@@ -9271,8 +11336,14 @@
       <c r="AV42" s="3" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="43" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW42" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX42" s="9" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="43" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>337</v>
       </c>
@@ -9402,8 +11473,14 @@
       <c r="AV43" s="3" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="44" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW43" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="AX43" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="44" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>345</v>
       </c>
@@ -9545,8 +11622,14 @@
       <c r="AV44" s="3" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="45" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW44" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX44" s="9" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="45" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>352</v>
       </c>
@@ -9686,8 +11769,14 @@
       <c r="AV45" s="3" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="46" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW45" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX45" s="9" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="46" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>362</v>
       </c>
@@ -9823,8 +11912,14 @@
       <c r="AV46" s="3" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="47" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW46" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX46" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="47" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>372</v>
       </c>
@@ -9966,10 +12061,16 @@
       <c r="AV47" s="3" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="48" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
-        <v>2024702150036</v>
+      <c r="AW47" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="AX47" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="48" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="10" t="s">
+        <v>947</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>270</v>
@@ -10083,8 +12184,14 @@
       <c r="AV48" s="3" t="s">
         <v>908</v>
       </c>
-    </row>
-    <row r="49" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW48" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="AX48" s="9" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="49" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>380</v>
       </c>
@@ -10204,8 +12311,14 @@
       <c r="AV49" s="3" t="s">
         <v>384</v>
       </c>
-    </row>
-    <row r="50" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW49" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX49" s="9" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="50" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>385</v>
       </c>
@@ -10345,8 +12458,14 @@
       <c r="AV50" s="3" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="51" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW50" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX50" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="51" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>392</v>
       </c>
@@ -10486,8 +12605,14 @@
       <c r="AV51" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="52" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW51" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX51" s="9" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="52" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>399</v>
       </c>
@@ -10629,8 +12754,14 @@
       <c r="AV52" s="3" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="53" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW52" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX52" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="53" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>403</v>
       </c>
@@ -10764,8 +12895,14 @@
       <c r="AV53" s="3" t="s">
         <v>409</v>
       </c>
-    </row>
-    <row r="54" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW53" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX53" s="9" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="54" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>410</v>
       </c>
@@ -10891,8 +13028,14 @@
       <c r="AV54" s="3" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="55" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW54" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="AX54" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="55" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>417</v>
       </c>
@@ -11030,8 +13173,14 @@
       <c r="AV55" s="3" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="56" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW55" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX55" s="9" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="56" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>424</v>
       </c>
@@ -11167,8 +13316,14 @@
       <c r="AV56" s="3" t="s">
         <v>431</v>
       </c>
-    </row>
-    <row r="57" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW56" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX56" s="9" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>432</v>
       </c>
@@ -11298,8 +13453,14 @@
       <c r="AV57" s="3" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="58" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW57" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="AX57" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="58" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>440</v>
       </c>
@@ -11425,8 +13586,14 @@
       <c r="AV58" s="3" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="59" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AW58" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="AX58" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="59" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>446</v>
       </c>
@@ -11549,6 +13716,10 @@
       </c>
       <c r="AV59" s="3" t="s">
         <v>452</v>
+      </c>
+      <c r="AW59" s="9"/>
+      <c r="AX59" s="9" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -11564,9 +13735,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AK18"/>
+  <sheetPr codeName="Hoja2"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="28" width="25.6640625" customWidth="1"/>
@@ -11574,9 +13746,10 @@
     <col min="30" max="34" width="25.6640625" customWidth="1"/>
     <col min="35" max="35" width="25.6640625" hidden="1" customWidth="1"/>
     <col min="36" max="37" width="25.6640625" customWidth="1"/>
+    <col min="38" max="39" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11621,7 +13794,7 @@
       <c r="AJ1" s="6"/>
       <c r="AK1" s="6"/>
     </row>
-    <row r="2" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11733,8 +13906,11 @@
       <c r="AK2" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="3" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL2" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>461</v>
       </c>
@@ -11836,8 +14012,11 @@
       <c r="AK3" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="4" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL3" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>468</v>
       </c>
@@ -11939,8 +14118,11 @@
       <c r="AK4" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL4" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>472</v>
       </c>
@@ -12048,8 +14230,11 @@
       <c r="AK5" s="3" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL5" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>478</v>
       </c>
@@ -12159,8 +14344,11 @@
       <c r="AK6" s="3" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="7" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL6" s="9" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>484</v>
       </c>
@@ -12270,8 +14458,11 @@
       <c r="AK7" s="3" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="8" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL7" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>488</v>
       </c>
@@ -12373,8 +14564,11 @@
       <c r="AK8" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="9" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL8" s="9" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="9" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>491</v>
       </c>
@@ -12484,8 +14678,11 @@
       <c r="AK9" s="3" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="10" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL9" s="9" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="10" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>495</v>
       </c>
@@ -12591,8 +14788,11 @@
         <v>100</v>
       </c>
       <c r="AK10" s="3"/>
-    </row>
-    <row r="11" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL10" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="11" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>498</v>
       </c>
@@ -12700,8 +14900,11 @@
         <v>60</v>
       </c>
       <c r="AK11" s="3"/>
-    </row>
-    <row r="12" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL11" s="9" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>501</v>
       </c>
@@ -12811,8 +15014,11 @@
       <c r="AK12" s="3" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="13" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL12" s="9" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="13" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>506</v>
       </c>
@@ -12918,8 +15124,11 @@
         <v/>
       </c>
       <c r="AK13" s="3"/>
-    </row>
-    <row r="14" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL13" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>509</v>
       </c>
@@ -13027,8 +15236,11 @@
         <v>30</v>
       </c>
       <c r="AK14" s="3"/>
-    </row>
-    <row r="15" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL14" s="9" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>513</v>
       </c>
@@ -13134,8 +15346,11 @@
         <v>100</v>
       </c>
       <c r="AK15" s="3"/>
-    </row>
-    <row r="16" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL15" s="9" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>516</v>
       </c>
@@ -13239,8 +15454,11 @@
         <v/>
       </c>
       <c r="AK16" s="3"/>
-    </row>
-    <row r="17" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL16" s="9" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>519</v>
       </c>
@@ -13338,8 +15556,11 @@
         <v>40</v>
       </c>
       <c r="AK17" s="3"/>
-    </row>
-    <row r="18" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AL17" s="9" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>522</v>
       </c>
@@ -13435,6 +15656,9 @@
         <v/>
       </c>
       <c r="AK18" s="3"/>
+      <c r="AL18" s="9" t="s">
+        <v>953</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -13449,15 +15673,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:R104"/>
+  <sheetPr codeName="Hoja3"/>
+  <dimension ref="A1:S104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="18" width="25.6640625" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -13479,7 +15705,7 @@
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -13534,8 +15760,11 @@
       <c r="R2" s="1" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S2" s="8" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>528</v>
       </c>
@@ -13586,8 +15815,11 @@
         <v>99.82</v>
       </c>
       <c r="R3" s="3"/>
-    </row>
-    <row r="4" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S3" s="9" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>533</v>
       </c>
@@ -13638,8 +15870,11 @@
         <v>0</v>
       </c>
       <c r="R4" s="3"/>
-    </row>
-    <row r="5" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S4" s="9" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>537</v>
       </c>
@@ -13690,8 +15925,11 @@
         <v>98.2</v>
       </c>
       <c r="R5" s="3"/>
-    </row>
-    <row r="6" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S5" s="9" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>541</v>
       </c>
@@ -13742,8 +15980,11 @@
         <v>99.98</v>
       </c>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S6" s="9" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>545</v>
       </c>
@@ -13794,8 +16035,11 @@
         <v>99.51</v>
       </c>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S7" s="9" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>549</v>
       </c>
@@ -13846,8 +16090,11 @@
         <v>49.54</v>
       </c>
       <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S8" s="9" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>553</v>
       </c>
@@ -13898,8 +16145,11 @@
         <v>99.56</v>
       </c>
       <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S9" s="9" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>558</v>
       </c>
@@ -13950,8 +16200,11 @@
         <v>85.88</v>
       </c>
       <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S10" s="9" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>563</v>
       </c>
@@ -14002,8 +16255,11 @@
         <v>89.9</v>
       </c>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S11" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>567</v>
       </c>
@@ -14054,8 +16310,11 @@
         <v>97.78</v>
       </c>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S12" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>572</v>
       </c>
@@ -14106,8 +16365,11 @@
         <v>99.87</v>
       </c>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S13" s="9" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>578</v>
       </c>
@@ -14158,8 +16420,11 @@
         <v>95.45</v>
       </c>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S14" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>583</v>
       </c>
@@ -14210,8 +16475,11 @@
         <v>99.97</v>
       </c>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S15" s="9" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>587</v>
       </c>
@@ -14262,8 +16530,11 @@
         <v>97.25</v>
       </c>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S16" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>591</v>
       </c>
@@ -14314,8 +16585,11 @@
         <v>97.16</v>
       </c>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S17" s="9" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>595</v>
       </c>
@@ -14366,8 +16640,11 @@
         <v>86.62</v>
       </c>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S18" s="9" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>599</v>
       </c>
@@ -14418,8 +16695,11 @@
         <v>77.59</v>
       </c>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S19" s="9" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>603</v>
       </c>
@@ -14470,8 +16750,11 @@
         <v>181.2</v>
       </c>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S20" s="9" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>607</v>
       </c>
@@ -14522,8 +16805,11 @@
         <v>89.3</v>
       </c>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S21" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>611</v>
       </c>
@@ -14574,8 +16860,11 @@
         <v>97.57</v>
       </c>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S22" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>615</v>
       </c>
@@ -14626,8 +16915,11 @@
         <v>91.85</v>
       </c>
       <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S23" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>619</v>
       </c>
@@ -14678,8 +16970,11 @@
         <v>95.75</v>
       </c>
       <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S24" s="9" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>623</v>
       </c>
@@ -14730,8 +17025,11 @@
         <v>97.23</v>
       </c>
       <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S25" s="9" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>627</v>
       </c>
@@ -14782,8 +17080,11 @@
         <v>86.53</v>
       </c>
       <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S26" s="9" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>631</v>
       </c>
@@ -14834,8 +17135,11 @@
         <v>87.69</v>
       </c>
       <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S27" s="9" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>635</v>
       </c>
@@ -14886,8 +17190,11 @@
         <v>99.24</v>
       </c>
       <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S28" s="9" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>640</v>
       </c>
@@ -14938,8 +17245,11 @@
         <v>97.75</v>
       </c>
       <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S29" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>644</v>
       </c>
@@ -14990,8 +17300,11 @@
         <v>93.98</v>
       </c>
       <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S30" s="9" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>647</v>
       </c>
@@ -15042,8 +17355,11 @@
         <v>100</v>
       </c>
       <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S31" s="9" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>652</v>
       </c>
@@ -15094,8 +17410,11 @@
         <v>99.73</v>
       </c>
       <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S32" s="9" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>655</v>
       </c>
@@ -15146,8 +17465,11 @@
         <v>100</v>
       </c>
       <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S33" s="9" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>658</v>
       </c>
@@ -15198,8 +17520,11 @@
         <v>100</v>
       </c>
       <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S34" s="9" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>661</v>
       </c>
@@ -15250,8 +17575,11 @@
         <v>100</v>
       </c>
       <c r="R35" s="3"/>
-    </row>
-    <row r="36" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S35" s="9" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>665</v>
       </c>
@@ -15302,8 +17630,11 @@
         <v>99.14</v>
       </c>
       <c r="R36" s="3"/>
-    </row>
-    <row r="37" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S36" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>669</v>
       </c>
@@ -15354,8 +17685,11 @@
         <v>76.930000000000007</v>
       </c>
       <c r="R37" s="3"/>
-    </row>
-    <row r="38" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S37" s="9" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>673</v>
       </c>
@@ -15404,8 +17738,11 @@
         <v>101.36</v>
       </c>
       <c r="R38" s="3"/>
-    </row>
-    <row r="39" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S38" s="9" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>677</v>
       </c>
@@ -15456,8 +17793,11 @@
         <v>99.96</v>
       </c>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S39" s="9" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>681</v>
       </c>
@@ -15508,8 +17848,11 @@
         <v>98.42</v>
       </c>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S40" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>685</v>
       </c>
@@ -15560,8 +17903,11 @@
         <v>98.28</v>
       </c>
       <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S41" s="9" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>688</v>
       </c>
@@ -15612,8 +17958,11 @@
         <v>99.17</v>
       </c>
       <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S42" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>691</v>
       </c>
@@ -15662,8 +18011,11 @@
         <v>102.12</v>
       </c>
       <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S43" s="9" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>694</v>
       </c>
@@ -15714,8 +18066,11 @@
         <v>90.22</v>
       </c>
       <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S44" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>697</v>
       </c>
@@ -15766,8 +18121,11 @@
         <v>90.65</v>
       </c>
       <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S45" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>701</v>
       </c>
@@ -15818,8 +18176,11 @@
         <v>93.32</v>
       </c>
       <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S46" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>705</v>
       </c>
@@ -15870,8 +18231,11 @@
         <v>100</v>
       </c>
       <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S47" s="9" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>708</v>
       </c>
@@ -15922,8 +18286,11 @@
         <v>86.25</v>
       </c>
       <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S48" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>712</v>
       </c>
@@ -15974,8 +18341,11 @@
         <v>98.13</v>
       </c>
       <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S49" s="9" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>715</v>
       </c>
@@ -16026,8 +18396,11 @@
         <v>100</v>
       </c>
       <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S50" s="9" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>718</v>
       </c>
@@ -16076,8 +18449,11 @@
         <v>65.83</v>
       </c>
       <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S51" s="9" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>722</v>
       </c>
@@ -16128,8 +18504,11 @@
         <v>99.91</v>
       </c>
       <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S52" s="9" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>725</v>
       </c>
@@ -16180,8 +18559,11 @@
         <v>87.3</v>
       </c>
       <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S53" s="9" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>728</v>
       </c>
@@ -16232,8 +18614,11 @@
         <v>84.17</v>
       </c>
       <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S54" s="9" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>731</v>
       </c>
@@ -16284,8 +18669,11 @@
         <v>100</v>
       </c>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S55" s="9" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>734</v>
       </c>
@@ -16336,8 +18724,11 @@
         <v>99.46</v>
       </c>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S56" s="9" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>737</v>
       </c>
@@ -16388,8 +18779,11 @@
         <v>58.7</v>
       </c>
       <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S57" s="9" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>741</v>
       </c>
@@ -16440,8 +18834,11 @@
         <v>100.53</v>
       </c>
       <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S58" s="9" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>744</v>
       </c>
@@ -16492,8 +18889,11 @@
         <v>61.03</v>
       </c>
       <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S59" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>747</v>
       </c>
@@ -16544,8 +18944,11 @@
         <v>100</v>
       </c>
       <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S60" s="9" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>750</v>
       </c>
@@ -16596,8 +18999,11 @@
         <v>94.38</v>
       </c>
       <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S61" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>754</v>
       </c>
@@ -16648,8 +19054,11 @@
         <v>60.48</v>
       </c>
       <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S62" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>757</v>
       </c>
@@ -16700,8 +19109,11 @@
         <v>83.98</v>
       </c>
       <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S63" s="9" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>761</v>
       </c>
@@ -16752,8 +19164,11 @@
         <v>94.51</v>
       </c>
       <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S64" s="9" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>765</v>
       </c>
@@ -16804,8 +19219,11 @@
         <v>81.650000000000006</v>
       </c>
       <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S65" s="9" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>768</v>
       </c>
@@ -16856,8 +19274,11 @@
         <v>95.06</v>
       </c>
       <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S66" s="9" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>771</v>
       </c>
@@ -16908,8 +19329,11 @@
         <v>96.7</v>
       </c>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S67" s="9" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>774</v>
       </c>
@@ -16960,8 +19384,11 @@
         <v>93.62</v>
       </c>
       <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S68" s="9" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>777</v>
       </c>
@@ -17012,8 +19439,11 @@
         <v>88.96</v>
       </c>
       <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S69" s="9" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>780</v>
       </c>
@@ -17064,8 +19494,11 @@
         <v>43.52</v>
       </c>
       <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S70" s="9" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>784</v>
       </c>
@@ -17116,8 +19549,11 @@
         <v>98.96</v>
       </c>
       <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S71" s="9" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>787</v>
       </c>
@@ -17168,8 +19604,11 @@
         <v>99.66</v>
       </c>
       <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S72" s="9" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>791</v>
       </c>
@@ -17220,8 +19659,11 @@
         <v>98.46</v>
       </c>
       <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S73" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>794</v>
       </c>
@@ -17272,8 +19714,11 @@
         <v>99.61</v>
       </c>
       <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S74" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>797</v>
       </c>
@@ -17324,8 +19769,11 @@
         <v>99.34</v>
       </c>
       <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S75" s="9" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>800</v>
       </c>
@@ -17376,8 +19824,11 @@
         <v>99.86</v>
       </c>
       <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S76" s="9" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>803</v>
       </c>
@@ -17422,8 +19873,11 @@
         <v>0</v>
       </c>
       <c r="R77" s="3"/>
-    </row>
-    <row r="78" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S77" s="9" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>807</v>
       </c>
@@ -17474,8 +19928,11 @@
         <v>92.14</v>
       </c>
       <c r="R78" s="3"/>
-    </row>
-    <row r="79" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S78" s="9" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>811</v>
       </c>
@@ -17526,8 +19983,11 @@
         <v>99.97</v>
       </c>
       <c r="R79" s="3"/>
-    </row>
-    <row r="80" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S79" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>815</v>
       </c>
@@ -17576,8 +20036,11 @@
         <v>82.2</v>
       </c>
       <c r="R80" s="3"/>
-    </row>
-    <row r="81" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S80" s="9" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>819</v>
       </c>
@@ -17628,8 +20091,11 @@
         <v>73.13</v>
       </c>
       <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S81" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>822</v>
       </c>
@@ -17680,8 +20146,11 @@
         <v>92.4</v>
       </c>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S82" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>825</v>
       </c>
@@ -17732,8 +20201,11 @@
         <v>95.06</v>
       </c>
       <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S83" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>829</v>
       </c>
@@ -17784,8 +20256,11 @@
         <v>82.73</v>
       </c>
       <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S84" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>833</v>
       </c>
@@ -17836,8 +20311,11 @@
         <v>93.6</v>
       </c>
       <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S85" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>837</v>
       </c>
@@ -17888,8 +20366,11 @@
         <v>90.33</v>
       </c>
       <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S86" s="9" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>841</v>
       </c>
@@ -17940,8 +20421,11 @@
         <v>66.63</v>
       </c>
       <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S87" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>845</v>
       </c>
@@ -17992,8 +20476,11 @@
         <v>75.38</v>
       </c>
       <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S88" s="9" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>849</v>
       </c>
@@ -18044,8 +20531,11 @@
         <v>92.23</v>
       </c>
       <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S89" s="9" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>854</v>
       </c>
@@ -18096,8 +20586,11 @@
         <v>22.96</v>
       </c>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S90" s="9" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>858</v>
       </c>
@@ -18148,8 +20641,11 @@
         <v>0</v>
       </c>
       <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S91" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>861</v>
       </c>
@@ -18200,8 +20696,11 @@
         <v>1.17</v>
       </c>
       <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S92" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>864</v>
       </c>
@@ -18250,8 +20749,11 @@
         <v>10.53</v>
       </c>
       <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S93" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>866</v>
       </c>
@@ -18300,8 +20802,11 @@
         <v>90</v>
       </c>
       <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S94" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>869</v>
       </c>
@@ -18352,8 +20857,11 @@
         <v>69.88</v>
       </c>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S95" s="9" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>873</v>
       </c>
@@ -18400,8 +20908,11 @@
         <v>0</v>
       </c>
       <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S96" s="9" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>876</v>
       </c>
@@ -18452,8 +20963,11 @@
         <v>24.54</v>
       </c>
       <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S97" s="9" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>880</v>
       </c>
@@ -18504,8 +21018,11 @@
         <v>27.96</v>
       </c>
       <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S98" s="9" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>884</v>
       </c>
@@ -18554,8 +21071,11 @@
         <v>98.93</v>
       </c>
       <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S99" s="9" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>887</v>
       </c>
@@ -18606,8 +21126,11 @@
         <v>99.22</v>
       </c>
       <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S100" s="9" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>891</v>
       </c>
@@ -18658,8 +21181,11 @@
         <v>99.98</v>
       </c>
       <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S101" s="9" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>895</v>
       </c>
@@ -18710,8 +21236,11 @@
         <v>100</v>
       </c>
       <c r="R102" s="3"/>
-    </row>
-    <row r="103" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S102" s="9" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>899</v>
       </c>
@@ -18762,8 +21291,11 @@
         <v>99.99</v>
       </c>
       <c r="R103" s="3"/>
-    </row>
-    <row r="104" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S103" s="9" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>902</v>
       </c>
@@ -18810,6 +21342,9 @@
         <v>0</v>
       </c>
       <c r="R104" s="3"/>
+      <c r="S104" s="9" t="s">
+        <v>933</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -18823,6 +21358,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -18966,15 +21510,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -18982,13 +21517,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA898CCD-AE0E-4187-8A1B-FE0621426781}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA898CCD-AE0E-4187-8A1B-FE0621426781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7012361-61F7-406D-ACA9-00C5E962322E}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756A7DC6-C7E1-4A10-9285-8ED480A28480}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListadoMunicipios" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2193" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1069">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -3622,12 +3622,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3682,11 +3676,151 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="19">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -3840,13 +3974,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -3878,6 +4005,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3906,98 +4040,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4012,14 +4054,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="A1:E26" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -4075,19 +4117,21 @@
     <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="15"/>
-    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="14"/>
-    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="13"/>
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(IF(AND(ISNUMBER($AC3),ISNUMBER($AE3),$AC3&lt;$AE3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="8"/>
+    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="7"/>
+    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AL18" totalsRowShown="0">
-  <autoFilter ref="A2:AL18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AM18" totalsRowShown="0">
+  <autoFilter ref="A2:AM18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -4110,6 +4154,7 @@
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
+    <tableColumn id="39" xr3:uid="{EB9A8E1B-7DA7-46A0-8178-E11424FA43F8}" name="HORIZONTE DEL PROYECTO" dataDxfId="2"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="DIAS DESDE LA APERTURA HASTA LA FIRMA DEL PRIMER CONTRATO"/>
@@ -4123,9 +4168,11 @@
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0100-000021000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0100-000022000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0100-000023000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO"/>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="12"/>
-    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="11"/>
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="1">
+      <calculatedColumnFormula>IFERROR(IF(AND(ISNUMBER($W3),ISNUMBER($X3),$W3&lt;$X3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AF3&gt;=1),(IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))*$AJ3/100,IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))),0)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="5"/>
+    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4153,7 +4200,7 @@
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS "/>
-    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4456,27 +4503,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>1050</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>1051</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="21" t="s">
         <v>1052</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="21" t="s">
         <v>1053</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="24">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>919</v>
       </c>
       <c r="D2" t="s">
@@ -4484,13 +4531,13 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="22" t="s">
         <v>933</v>
       </c>
       <c r="D3" t="s">
@@ -4498,13 +4545,13 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
+      <c r="A4" s="22">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="22" t="s">
         <v>1055</v>
       </c>
       <c r="D4" t="s">
@@ -4512,13 +4559,13 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
+      <c r="A5" s="22">
         <v>4</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="22" t="s">
         <v>959</v>
       </c>
       <c r="D5" t="s">
@@ -4526,13 +4573,13 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
+      <c r="A6" s="22">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="22" t="s">
         <v>1001</v>
       </c>
       <c r="D6" t="s">
@@ -4540,13 +4587,13 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="24">
+      <c r="A7" s="22">
         <v>6</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="22" t="s">
         <v>1056</v>
       </c>
       <c r="D7" t="s">
@@ -4554,13 +4601,13 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="24">
+      <c r="A8" s="22">
         <v>7</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="22" t="s">
         <v>1000</v>
       </c>
       <c r="D8" t="s">
@@ -4568,13 +4615,13 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="24">
+      <c r="A9" s="22">
         <v>8</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>996</v>
       </c>
       <c r="D9" t="s">
@@ -4582,13 +4629,13 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="24">
+      <c r="A10" s="22">
         <v>9</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="22" t="s">
         <v>956</v>
       </c>
       <c r="D10" t="s">
@@ -4596,13 +4643,13 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="24">
+      <c r="A11" s="22">
         <v>10</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="22" t="s">
         <v>971</v>
       </c>
       <c r="D11" t="s">
@@ -4610,13 +4657,13 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="24">
+      <c r="A12" s="22">
         <v>11</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="22" t="s">
         <v>952</v>
       </c>
       <c r="D12" t="s">
@@ -4624,13 +4671,13 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="24">
+      <c r="A13" s="22">
         <v>12</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="22" t="s">
         <v>1059</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="22" t="s">
         <v>955</v>
       </c>
       <c r="D13" t="s">
@@ -4638,13 +4685,13 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="24">
+      <c r="A14" s="22">
         <v>13</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="22" t="s">
         <v>1059</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="22" t="s">
         <v>941</v>
       </c>
       <c r="D14" t="s">
@@ -4652,13 +4699,13 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="24">
+      <c r="A15" s="22">
         <v>14</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="22" t="s">
         <v>1059</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="22" t="s">
         <v>1060</v>
       </c>
       <c r="D15" t="s">
@@ -4666,13 +4713,13 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="24">
+      <c r="A16" s="22">
         <v>15</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="23" t="s">
         <v>930</v>
       </c>
       <c r="D16" t="s">
@@ -4680,13 +4727,13 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="24">
+      <c r="A17" s="22">
         <v>16</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="23" t="s">
         <v>939</v>
       </c>
       <c r="D17" t="s">
@@ -4694,13 +4741,13 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="24">
+      <c r="A18" s="22">
         <v>17</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="22" t="s">
         <v>942</v>
       </c>
       <c r="D18" t="s">
@@ -4708,13 +4755,13 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="24">
+      <c r="A19" s="22">
         <v>18</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="22" t="s">
         <v>925</v>
       </c>
       <c r="D19" t="s">
@@ -4722,13 +4769,13 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="24">
+      <c r="A20" s="22">
         <v>19</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="22" t="s">
         <v>1061</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="23" t="s">
         <v>1063</v>
       </c>
       <c r="D20" t="s">
@@ -4736,13 +4783,13 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="24">
+      <c r="A21" s="22">
         <v>20</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="22" t="s">
         <v>1064</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="22" t="s">
         <v>997</v>
       </c>
       <c r="D21" t="s">
@@ -4750,13 +4797,13 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="24">
+      <c r="A22" s="22">
         <v>21</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="22" t="s">
         <v>1064</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="22" t="s">
         <v>924</v>
       </c>
       <c r="D22" t="s">
@@ -4764,13 +4811,13 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="24">
+      <c r="A23" s="22">
         <v>22</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="22" t="s">
         <v>1064</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="22" t="s">
         <v>1065</v>
       </c>
       <c r="D23" t="s">
@@ -4778,13 +4825,13 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="24">
+      <c r="A24" s="22">
         <v>23</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="22" t="s">
         <v>1064</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="22" t="s">
         <v>928</v>
       </c>
       <c r="D24" t="s">
@@ -4792,13 +4839,13 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="24">
+      <c r="A25" s="22">
         <v>24</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="22" t="s">
         <v>1066</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="22" t="s">
         <v>932</v>
       </c>
       <c r="D25" t="s">
@@ -4806,13 +4853,13 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="24">
+      <c r="A26" s="22">
         <v>25</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="22" t="s">
         <v>1066</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="22" t="s">
         <v>953</v>
       </c>
       <c r="D26" t="s">
@@ -4820,13 +4867,13 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="24">
+      <c r="A27" s="22">
         <v>26</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="22" t="s">
         <v>1066</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="22" t="s">
         <v>1067</v>
       </c>
       <c r="D27" t="s">
@@ -4834,10 +4881,10 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="22" t="s">
         <v>1068</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="22" t="s">
         <v>920</v>
       </c>
       <c r="D28" t="s">
@@ -4862,400 +4909,400 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1005</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>1006</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="11" t="s">
         <v>1007</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>1008</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="13" t="s">
         <v>1010</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="13" t="s">
         <v>1011</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="13" t="s">
         <v>1014</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>1015</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="12" t="s">
         <v>1016</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="13" t="s">
         <v>1017</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>1019</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="13" t="s">
         <v>1020</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="13"/>
+      <c r="D5" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="13" t="s">
         <v>1022</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16" t="s">
+      <c r="C6" s="13"/>
+      <c r="D6" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="13" t="s">
         <v>1023</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="13" t="s">
         <v>1024</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>1025</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="12" t="s">
         <v>1026</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="13" t="s">
         <v>1027</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>1009</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="13" t="s">
         <v>1028</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="13" t="s">
         <v>1029</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>1030</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="13" t="s">
         <v>1031</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="12" t="s">
         <v>1021</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="13" t="s">
         <v>1032</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="13" t="s">
         <v>1031</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="14" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="16" t="s">
         <v>1033</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>1034</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
         <v>1018</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="17" t="s">
         <v>1013</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>1035</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>1036</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="17" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="16" t="s">
         <v>1038</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="17" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="18" t="s">
         <v>1021</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="19" t="s">
         <v>1039</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="19" t="s">
         <v>1031</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="20" t="s">
         <v>1018</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="16" t="s">
         <v>1040</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="17" t="s">
         <v>1037</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>1041</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E18" s="19"/>
+      <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="16" t="s">
         <v>1042</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="D19" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E19" s="19"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>1043</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E20" s="19"/>
+      <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="16" t="s">
         <v>1044</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E21" s="19"/>
+      <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>1045</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E22" s="19"/>
+      <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="15" t="s">
         <v>1021</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="16" t="s">
         <v>1046</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="16" t="s">
         <v>1031</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="17" t="s">
         <v>1018</v>
       </c>
-      <c r="E23" s="19"/>
+      <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="18" t="s">
+      <c r="A24" s="15"/>
+      <c r="B24" s="16" t="s">
         <v>1047</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
     </row>
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="18" t="s">
+      <c r="A25" s="15"/>
+      <c r="B25" s="16" t="s">
         <v>1048</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-    </row>
-    <row r="26" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="17"/>
-      <c r="B26" s="18" t="s">
+      <c r="C25" s="16"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+    </row>
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="15"/>
+      <c r="B26" s="16" t="s">
         <v>1049</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5282,60 +5329,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:50" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="7" t="s">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
+      <c r="S1" s="24"/>
+      <c r="T1" s="24"/>
+      <c r="U1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="7"/>
-      <c r="AG1" s="7"/>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="7"/>
-      <c r="AN1" s="7"/>
-      <c r="AO1" s="7"/>
-      <c r="AP1" s="7"/>
-      <c r="AQ1" s="6" t="s">
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="25"/>
+      <c r="AH1" s="25"/>
+      <c r="AI1" s="25"/>
+      <c r="AJ1" s="25"/>
+      <c r="AK1" s="25"/>
+      <c r="AL1" s="25"/>
+      <c r="AM1" s="25"/>
+      <c r="AN1" s="25"/>
+      <c r="AO1" s="25"/>
+      <c r="AP1" s="25"/>
+      <c r="AQ1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="AR1" s="6"/>
-      <c r="AS1" s="6"/>
-      <c r="AT1" s="6"/>
-      <c r="AU1" s="6"/>
-      <c r="AV1" s="6"/>
+      <c r="AR1" s="24"/>
+      <c r="AS1" s="24"/>
+      <c r="AT1" s="24"/>
+      <c r="AU1" s="24"/>
+      <c r="AV1" s="24"/>
     </row>
     <row r="2" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -5482,10 +5529,10 @@
       <c r="AV2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="8" t="s">
+      <c r="AW2" s="6" t="s">
         <v>909</v>
       </c>
-      <c r="AX2" s="8" t="s">
+      <c r="AX2" s="6" t="s">
         <v>910</v>
       </c>
     </row>
@@ -5623,16 +5670,16 @@
         <v>100</v>
       </c>
       <c r="AU3" s="3" t="str">
-        <f t="shared" ref="AU3:AU34" si="6">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),"")),0)</f>
+        <f t="shared" ref="AU3:AU59" si="6">IFERROR(IF(AND(ISNUMBER($AC3),ISNUMBER($AE3),$AC3&lt;$AE3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))),0)</f>
         <v/>
       </c>
       <c r="AV3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AW3" s="9" t="s">
+      <c r="AW3" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX3" s="9" t="s">
+      <c r="AX3" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -5766,10 +5813,10 @@
       <c r="AV4" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="AW4" s="9" t="s">
+      <c r="AW4" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX4" s="9" t="s">
+      <c r="AX4" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -5913,10 +5960,10 @@
       <c r="AV5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW5" s="9" t="s">
+      <c r="AW5" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX5" s="9" t="s">
+      <c r="AX5" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -6057,13 +6104,13 @@
       </c>
       <c r="AU6" s="3">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AV6" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AW6" s="9"/>
-      <c r="AX6" s="9" t="s">
+      <c r="AW6" s="7"/>
+      <c r="AX6" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -6207,10 +6254,10 @@
       <c r="AV7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AW7" s="9" t="s">
+      <c r="AW7" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX7" s="9" t="s">
+      <c r="AX7" s="7" t="s">
         <v>921</v>
       </c>
     </row>
@@ -6354,10 +6401,10 @@
       <c r="AV8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AW8" s="9" t="s">
+      <c r="AW8" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX8" s="9" t="s">
+      <c r="AX8" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -6500,15 +6547,15 @@
       </c>
       <c r="AU9" s="3">
         <f t="shared" si="6"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AV9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="AW9" s="9" t="s">
+      <c r="AW9" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX9" s="9" t="s">
+      <c r="AX9" s="7" t="s">
         <v>922</v>
       </c>
     </row>
@@ -6652,10 +6699,10 @@
       <c r="AV10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW10" s="9" t="s">
+      <c r="AW10" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX10" s="9" t="s">
+      <c r="AX10" s="7" t="s">
         <v>923</v>
       </c>
     </row>
@@ -6799,10 +6846,10 @@
       <c r="AV11" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW11" s="9" t="s">
+      <c r="AW11" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX11" s="9" t="s">
+      <c r="AX11" s="7" t="s">
         <v>924</v>
       </c>
     </row>
@@ -6946,10 +6993,10 @@
       <c r="AV12" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AW12" s="9" t="s">
+      <c r="AW12" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX12" s="9" t="s">
+      <c r="AX12" s="7" t="s">
         <v>925</v>
       </c>
     </row>
@@ -7095,10 +7142,10 @@
       <c r="AV13" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="AW13" s="9" t="s">
+      <c r="AW13" s="7" t="s">
         <v>915</v>
       </c>
-      <c r="AX13" s="9" t="s">
+      <c r="AX13" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -7242,10 +7289,10 @@
       <c r="AV14" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="AW14" s="9" t="s">
+      <c r="AW14" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX14" s="9" t="s">
+      <c r="AX14" s="7" t="s">
         <v>926</v>
       </c>
     </row>
@@ -7391,10 +7438,10 @@
       <c r="AV15" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="AW15" s="9" t="s">
+      <c r="AW15" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX15" s="9" t="s">
+      <c r="AX15" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -7538,10 +7585,10 @@
       <c r="AV16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW16" s="9" t="s">
+      <c r="AW16" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX16" s="9" t="s">
+      <c r="AX16" s="7" t="s">
         <v>927</v>
       </c>
     </row>
@@ -7682,15 +7729,15 @@
       </c>
       <c r="AU17" s="3">
         <f t="shared" si="6"/>
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AV17" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="AW17" s="9" t="s">
+      <c r="AW17" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX17" s="9" t="s">
+      <c r="AX17" s="7" t="s">
         <v>928</v>
       </c>
     </row>
@@ -7831,15 +7878,15 @@
       </c>
       <c r="AU18" s="3">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AV18" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="AW18" s="9" t="s">
+      <c r="AW18" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX18" s="9" t="s">
+      <c r="AX18" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -7980,15 +8027,15 @@
       </c>
       <c r="AU19" s="3">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AV19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="AW19" s="9" t="s">
+      <c r="AW19" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX19" s="9" t="s">
+      <c r="AX19" s="7" t="s">
         <v>929</v>
       </c>
     </row>
@@ -8132,10 +8179,10 @@
       <c r="AV20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW20" s="9" t="s">
+      <c r="AW20" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX20" s="9" t="s">
+      <c r="AX20" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -8276,15 +8323,15 @@
       </c>
       <c r="AU21" s="3">
         <f t="shared" si="6"/>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AV21" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="AW21" s="9" t="s">
+      <c r="AW21" s="7" t="s">
         <v>916</v>
       </c>
-      <c r="AX21" s="9" t="s">
+      <c r="AX21" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -8425,15 +8472,15 @@
       </c>
       <c r="AU22" s="3">
         <f t="shared" si="6"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AV22" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="AW22" s="9" t="s">
+      <c r="AW22" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX22" s="9" t="s">
+      <c r="AX22" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -8571,10 +8618,10 @@
       <c r="AV23" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW23" s="9" t="s">
+      <c r="AW23" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX23" s="9" t="s">
+      <c r="AX23" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -8712,10 +8759,10 @@
       <c r="AV24" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="AW24" s="9" t="s">
+      <c r="AW24" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX24" s="9" t="s">
+      <c r="AX24" s="7" t="s">
         <v>930</v>
       </c>
     </row>
@@ -8851,10 +8898,10 @@
       <c r="AV25" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW25" s="9" t="s">
+      <c r="AW25" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX25" s="9" t="s">
+      <c r="AX25" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -8995,15 +9042,15 @@
       </c>
       <c r="AU26" s="3">
         <f t="shared" si="6"/>
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AV26" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="AW26" s="9" t="s">
+      <c r="AW26" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX26" s="9" t="s">
+      <c r="AX26" s="7" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9147,10 +9194,10 @@
       <c r="AV27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="AW27" s="9" t="s">
+      <c r="AW27" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX27" s="9" t="s">
+      <c r="AX27" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -9292,10 +9339,10 @@
       <c r="AV28" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW28" s="9" t="s">
+      <c r="AW28" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX28" s="9" t="s">
+      <c r="AX28" s="7" t="s">
         <v>931</v>
       </c>
     </row>
@@ -9439,10 +9486,10 @@
       <c r="AV29" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="AW29" s="9" t="s">
+      <c r="AW29" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX29" s="9" t="s">
+      <c r="AX29" s="7" t="s">
         <v>930</v>
       </c>
     </row>
@@ -9580,10 +9627,10 @@
       <c r="AV30" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW30" s="9" t="s">
+      <c r="AW30" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX30" s="9" t="s">
+      <c r="AX30" s="7" t="s">
         <v>932</v>
       </c>
     </row>
@@ -9725,10 +9772,10 @@
       <c r="AV31" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW31" s="9" t="s">
+      <c r="AW31" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX31" s="9" t="s">
+      <c r="AX31" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -9869,15 +9916,15 @@
       </c>
       <c r="AU32" s="3">
         <f t="shared" si="6"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AV32" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="AW32" s="9" t="s">
+      <c r="AW32" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX32" s="9" t="s">
+      <c r="AX32" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -10018,15 +10065,15 @@
       </c>
       <c r="AU33" s="3">
         <f t="shared" si="6"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AV33" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="AW33" s="9" t="s">
+      <c r="AW33" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX33" s="9" t="s">
+      <c r="AX33" s="7" t="s">
         <v>934</v>
       </c>
     </row>
@@ -10168,10 +10215,10 @@
       <c r="AV34" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW34" s="9" t="s">
+      <c r="AW34" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX34" s="9" t="s">
+      <c r="AX34" s="7" t="s">
         <v>935</v>
       </c>
     </row>
@@ -10299,16 +10346,16 @@
         <v>100</v>
       </c>
       <c r="AU35" s="3" t="str">
-        <f t="shared" ref="AU35:AU59" si="13">IFERROR(IF(AND($G35="CONTRATADO EN EJECUCIÓN",$AP35&gt;=1),(IFERROR(IF(ISTEXT($AF35),($AL35*0.4+$AM35*0.2+$AO35*0.4),""),""))*$AT35/100,IFERROR(IF(ISTEXT($AF35),($AL35*0.4+$AM35*0.2+$AO35*0.4),""),"")),0)</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV35" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="AW35" s="9" t="s">
+      <c r="AW35" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX35" s="9" t="s">
+      <c r="AX35" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -10446,14 +10493,14 @@
         <v>100</v>
       </c>
       <c r="AU36" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>88.695652173913047</v>
       </c>
       <c r="AV36" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="AW36" s="9"/>
-      <c r="AX36" s="9" t="s">
+      <c r="AW36" s="7"/>
+      <c r="AX36" s="7" t="s">
         <v>936</v>
       </c>
     </row>
@@ -10589,16 +10636,16 @@
         <v>90</v>
       </c>
       <c r="AU37" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV37" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="AW37" s="9" t="s">
+      <c r="AW37" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX37" s="9" t="s">
+      <c r="AX37" s="7" t="s">
         <v>937</v>
       </c>
     </row>
@@ -10738,16 +10785,16 @@
         <v>90</v>
       </c>
       <c r="AU38" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>79.043478260869563</v>
       </c>
       <c r="AV38" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="AW38" s="9" t="s">
+      <c r="AW38" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX38" s="9" t="s">
+      <c r="AX38" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -10885,16 +10932,16 @@
         <v>90</v>
       </c>
       <c r="AU39" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV39" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="AW39" s="9" t="s">
+      <c r="AW39" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX39" s="9" t="s">
+      <c r="AX39" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -11034,16 +11081,16 @@
         <v>100</v>
       </c>
       <c r="AU40" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>86.956521739130437</v>
       </c>
       <c r="AV40" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="AW40" s="9" t="s">
+      <c r="AW40" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX40" s="9" t="s">
+      <c r="AX40" s="7" t="s">
         <v>938</v>
       </c>
     </row>
@@ -11183,16 +11230,16 @@
         <v>75</v>
       </c>
       <c r="AU41" s="3">
-        <f t="shared" si="13"/>
-        <v>75</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AV41" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="AW41" s="9" t="s">
+      <c r="AW41" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX41" s="9" t="s">
+      <c r="AX41" s="7" t="s">
         <v>939</v>
       </c>
     </row>
@@ -11330,16 +11377,16 @@
         <v>100</v>
       </c>
       <c r="AU42" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="AV42" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="AW42" s="9" t="s">
+      <c r="AW42" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX42" s="9" t="s">
+      <c r="AX42" s="7" t="s">
         <v>940</v>
       </c>
     </row>
@@ -11467,16 +11514,16 @@
         <v>100</v>
       </c>
       <c r="AU43" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV43" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="AW43" s="9" t="s">
+      <c r="AW43" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="AX43" s="9" t="s">
+      <c r="AX43" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -11616,16 +11663,16 @@
         <v>90</v>
       </c>
       <c r="AU44" s="3">
-        <f t="shared" si="13"/>
-        <v>36</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AV44" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="AW44" s="9" t="s">
+      <c r="AW44" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX44" s="9" t="s">
+      <c r="AX44" s="7" t="s">
         <v>941</v>
       </c>
     </row>
@@ -11763,16 +11810,16 @@
         <v>100</v>
       </c>
       <c r="AU45" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="AV45" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="AW45" s="9" t="s">
+      <c r="AW45" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX45" s="9" t="s">
+      <c r="AX45" s="7" t="s">
         <v>942</v>
       </c>
     </row>
@@ -11906,16 +11953,16 @@
         <v>100</v>
       </c>
       <c r="AU46" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV46" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="AW46" s="9" t="s">
+      <c r="AW46" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX46" s="9" t="s">
+      <c r="AX46" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -12055,21 +12102,21 @@
         <v>90</v>
       </c>
       <c r="AU47" s="3">
-        <f t="shared" si="13"/>
-        <v>88.434782608695656</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AV47" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="AW47" s="9" t="s">
+      <c r="AW47" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="AX47" s="9" t="s">
+      <c r="AX47" s="7" t="s">
         <v>920</v>
       </c>
     </row>
     <row r="48" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>947</v>
       </c>
       <c r="B48" s="3" t="s">
@@ -12178,16 +12225,16 @@
         <v>100</v>
       </c>
       <c r="AU48" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="AW48" s="9" t="s">
+      <c r="AW48" s="7" t="s">
         <v>917</v>
       </c>
-      <c r="AX48" s="9" t="s">
+      <c r="AX48" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -12305,16 +12352,16 @@
         <v>100</v>
       </c>
       <c r="AU49" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV49" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="AW49" s="9" t="s">
+      <c r="AW49" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX49" s="9" t="s">
+      <c r="AX49" s="7" t="s">
         <v>943</v>
       </c>
     </row>
@@ -12452,16 +12499,16 @@
         <v>100</v>
       </c>
       <c r="AU50" s="3">
-        <f t="shared" si="13"/>
-        <v>40</v>
+        <f t="shared" si="6"/>
+        <v>0</v>
       </c>
       <c r="AV50" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="AW50" s="9" t="s">
+      <c r="AW50" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX50" s="9" t="s">
+      <c r="AX50" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -12599,16 +12646,16 @@
         <v>100</v>
       </c>
       <c r="AU51" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>60</v>
       </c>
       <c r="AV51" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="AW51" s="9" t="s">
+      <c r="AW51" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX51" s="9" t="s">
+      <c r="AX51" s="7" t="s">
         <v>944</v>
       </c>
     </row>
@@ -12748,16 +12795,16 @@
         <v>100</v>
       </c>
       <c r="AU52" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="AV52" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="AW52" s="9" t="s">
+      <c r="AW52" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX52" s="9" t="s">
+      <c r="AX52" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -12889,16 +12936,16 @@
         <v>100</v>
       </c>
       <c r="AU53" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV53" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="AW53" s="9" t="s">
+      <c r="AW53" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX53" s="9" t="s">
+      <c r="AX53" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -13022,16 +13069,16 @@
         <v>100</v>
       </c>
       <c r="AU54" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV54" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="AW54" s="9" t="s">
+      <c r="AW54" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="AX54" s="9" t="s">
+      <c r="AX54" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -13167,16 +13214,16 @@
         <v>100</v>
       </c>
       <c r="AU55" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v>100</v>
       </c>
       <c r="AV55" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="AW55" s="9" t="s">
+      <c r="AW55" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX55" s="9" t="s">
+      <c r="AX55" s="7" t="s">
         <v>945</v>
       </c>
     </row>
@@ -13310,16 +13357,16 @@
         <v>100</v>
       </c>
       <c r="AU56" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV56" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="AW56" s="9" t="s">
+      <c r="AW56" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX56" s="9" t="s">
+      <c r="AX56" s="7" t="s">
         <v>946</v>
       </c>
     </row>
@@ -13447,16 +13494,16 @@
         <v>100</v>
       </c>
       <c r="AU57" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV57" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="AW57" s="9" t="s">
+      <c r="AW57" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX57" s="9" t="s">
+      <c r="AX57" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -13580,16 +13627,16 @@
         <v>100</v>
       </c>
       <c r="AU58" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV58" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="AW58" s="9" t="s">
+      <c r="AW58" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="AX58" s="9" t="s">
+      <c r="AX58" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -13711,14 +13758,14 @@
         <v>100</v>
       </c>
       <c r="AU59" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AV59" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="AW59" s="9"/>
-      <c r="AX59" s="9" t="s">
+      <c r="AW59" s="7"/>
+      <c r="AX59" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -13738,63 +13785,64 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AL18"/>
+  <dimension ref="A1:AM18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="28" width="25.6640625" customWidth="1"/>
-    <col min="29" max="29" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="30" max="34" width="25.6640625" customWidth="1"/>
-    <col min="35" max="35" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="36" max="37" width="25.6640625" customWidth="1"/>
-    <col min="38" max="39" width="23.77734375" customWidth="1"/>
+    <col min="1" max="29" width="25.6640625" customWidth="1"/>
+    <col min="30" max="30" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="36" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="25.6640625" customWidth="1"/>
+    <col min="39" max="40" width="23.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="7" t="s">
+    <row r="1" spans="1:39" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-      <c r="W1" s="7"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="7"/>
-      <c r="Z1" s="7"/>
-      <c r="AA1" s="7"/>
-      <c r="AB1" s="7"/>
-      <c r="AC1" s="7"/>
-      <c r="AD1" s="7"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="6" t="s">
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="25"/>
+      <c r="AC1" s="25"/>
+      <c r="AD1" s="25"/>
+      <c r="AE1" s="25"/>
+      <c r="AF1" s="25"/>
+      <c r="AG1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="6"/>
-      <c r="AH1" s="6"/>
-      <c r="AI1" s="6"/>
-      <c r="AJ1" s="6"/>
-      <c r="AK1" s="6"/>
-    </row>
-    <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AH1" s="24"/>
+      <c r="AI1" s="24"/>
+      <c r="AJ1" s="24"/>
+      <c r="AK1" s="24"/>
+      <c r="AL1" s="24"/>
+    </row>
+    <row r="2" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -13862,55 +13910,58 @@
         <v>30</v>
       </c>
       <c r="W2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AL2" s="8" t="s">
+      <c r="AM2" s="6" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="3" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>461</v>
       </c>
@@ -13973,50 +14024,51 @@
       <c r="V3" s="5">
         <v>44593</v>
       </c>
-      <c r="W3" s="5">
+      <c r="W3" s="5"/>
+      <c r="X3" s="5">
         <v>46127</v>
       </c>
-      <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="str">
-        <f t="shared" ref="AA3:AA18" si="0">IF(AND($R3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($R3&gt;1.25,$R3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($R3&gt;1.2,$R3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($R3&gt;=0.84,$R3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($R3&gt;=0.38,$R3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($R3-0.38)/(0.84-0.38))*100,IF(AND($R3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3" t="str">
+        <f t="shared" ref="AB3:AB18" si="0">IF(AND($R3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($R3&gt;1.25,$R3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($R3&gt;1.2,$R3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($R3&gt;=0.84,$R3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($R3&gt;=0.38,$R3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($R3-0.38)/(0.84-0.38))*100,IF(AND($R3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AB3" s="3" t="str">
-        <f t="shared" ref="AB3:AB18" si="1">IF(AND($Q3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($Q3&gt;1.25,$Q3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($Q3&gt;1.2,$Q3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($Q3&gt;=0.84,$Q3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($Q3&gt;=0.38,$Q3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($Q3-0.38)/(0.84-0.38))*100,IF(AND($Q3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AC3" s="3" t="str">
+        <f t="shared" ref="AC3:AC18" si="1">IF(AND($Q3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($Q3&gt;1.25,$Q3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($Q3&gt;1.2,$Q3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($Q3&gt;=0.84,$Q3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($Q3&gt;=0.38,$Q3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($Q3-0.38)/(0.84-0.38))*100,IF(AND($Q3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AC3" s="3">
-        <f t="shared" ref="AC3:AC18" si="2">IF(AND($P3&lt;60,($P3-$O3)&lt;=50),100,IF(AND($P3&lt;60,($P3-$O3)&gt;50),0,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&lt;=40),100,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&gt;40),0,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&lt;=30),100,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&gt;30),0,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&lt;=20),100,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&gt;20),0,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&lt;=10),100,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AD3" s="3" t="str">
-        <f t="shared" ref="AD3:AD18" si="3">IF(AND($O3&gt;$P3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($P3&gt;$O3,($P3-$O3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&lt;=60),100,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&gt;60),$AC3,""))))</f>
+      <c r="AD3" s="3">
+        <f t="shared" ref="AD3:AD18" si="2">IF(AND($P3&lt;60,($P3-$O3)&lt;=50),100,IF(AND($P3&lt;60,($P3-$O3)&gt;50),0,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&lt;=40),100,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&gt;40),0,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&lt;=30),100,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&gt;30),0,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&lt;=20),100,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&gt;20),0,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&lt;=10),100,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AE3" s="3" t="str">
+        <f t="shared" ref="AE3:AE18" si="3">IF(AND($O3&gt;$P3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($P3&gt;$O3,($P3-$O3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&lt;=60),100,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&gt;60),$AD3,""))))</f>
         <v/>
       </c>
-      <c r="AE3" s="3">
+      <c r="AF3" s="3">
         <v>2</v>
       </c>
-      <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
-      <c r="AI3" s="3">
-        <f t="shared" ref="AI3:AI18" si="4">IF($AE3=0,100,IF($AE3=1,90,IF($AE3=2,75,IF($AE3=3,60,IF($AE3=4,50,IF($AE3=5,25,IF($AE3&gt;=6,0,"")))))))</f>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3">
+        <f t="shared" ref="AJ3:AJ18" si="4">IF($AF3=0,100,IF($AF3=1,90,IF($AF3=2,75,IF($AF3=3,60,IF($AF3=4,50,IF($AF3=5,25,IF($AF3&gt;=6,0,"")))))))</f>
         <v>75</v>
       </c>
-      <c r="AJ3" s="3" t="str">
-        <f t="shared" ref="AJ3:AJ18" si="5">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AE3&gt;=1),(IFERROR(IF(ISNUMBER($AG3),($AA3*0.4+$AB3*0.2+$AD3*0.4),""),""))*$AI3/100,IFERROR(IF(ISNUMBER($AG3),($AA3*0.4+$AB3*0.2+$AD3*0.4),""),"")),0)</f>
+      <c r="AK3" s="3" t="str">
+        <f t="shared" ref="AK3:AK18" si="5">IFERROR(IF(AND(ISNUMBER($W3),ISNUMBER($X3),$W3&lt;$X3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AF3&gt;=1),(IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))*$AJ3/100,IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="AL3" s="9" t="s">
+      <c r="AM3" s="7" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="4" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>468</v>
       </c>
@@ -14079,50 +14131,51 @@
       <c r="V4" s="5">
         <v>44567</v>
       </c>
-      <c r="W4" s="5">
+      <c r="W4" s="5"/>
+      <c r="X4" s="5">
         <v>46127</v>
       </c>
-      <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="str">
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB4" s="3" t="str">
+      <c r="AC4" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC4" s="3">
+      <c r="AD4" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD4" s="3" t="str">
+      <c r="AE4" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3"/>
+      <c r="AF4" s="3">
+        <v>0</v>
+      </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
-      <c r="AI4" s="3">
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ4" s="3" t="str">
+      <c r="AK4" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="AL4" s="9" t="s">
+      <c r="AM4" s="7" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="5" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>472</v>
       </c>
@@ -14187,54 +14240,55 @@
       <c r="V5" s="5">
         <v>44722</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="5"/>
+      <c r="X5" s="5">
         <v>46096</v>
       </c>
-      <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3">
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AC5" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AD5" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AE5" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AF5" s="3">
         <v>2</v>
       </c>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG5" s="3"/>
       <c r="AH5" s="3">
         <v>100</v>
       </c>
       <c r="AI5" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ5" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AK5" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AK5" s="3" t="s">
+      <c r="AL5" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="AL5" s="9" t="s">
+      <c r="AM5" s="7" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>478</v>
       </c>
@@ -14301,54 +14355,55 @@
       <c r="V6" s="5">
         <v>44810</v>
       </c>
-      <c r="W6" s="5">
+      <c r="W6" s="5"/>
+      <c r="X6" s="5">
         <v>46127</v>
       </c>
-      <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3">
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AC6" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AD6" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AE6" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AF6" s="3">
         <v>4</v>
       </c>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG6" s="3"/>
       <c r="AH6" s="3">
         <v>100</v>
       </c>
       <c r="AI6" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ6" s="3">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AK6" s="3">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AK6" s="3" t="s">
+      <c r="AL6" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="AL6" s="9" t="s">
+      <c r="AM6" s="7" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="7" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>484</v>
       </c>
@@ -14415,54 +14470,55 @@
       <c r="V7" s="5">
         <v>45175</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="5"/>
+      <c r="X7" s="5">
         <v>46127</v>
       </c>
-      <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3">
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AC7" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AD7" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AE7" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AF7" s="3">
         <v>4</v>
       </c>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG7" s="3"/>
       <c r="AH7" s="3">
         <v>100</v>
       </c>
       <c r="AI7" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ7" s="3">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AK7" s="3">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AK7" s="3" t="s">
+      <c r="AL7" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="AL7" s="9" t="s">
+      <c r="AM7" s="7" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="8" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>488</v>
       </c>
@@ -14525,50 +14581,51 @@
       <c r="V8" s="5">
         <v>45300</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="5"/>
+      <c r="X8" s="5">
         <v>46096</v>
       </c>
-      <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3" t="str">
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB8" s="3" t="str">
+      <c r="AC8" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD8" s="3" t="str">
+      <c r="AE8" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3"/>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ8" s="3" t="str">
+      <c r="AK8" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="AL8" s="9" t="s">
+      <c r="AM8" s="7" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="9" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>491</v>
       </c>
@@ -14635,54 +14692,55 @@
       <c r="V9" s="5">
         <v>45567</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="5"/>
+      <c r="X9" s="5">
         <v>46096</v>
       </c>
-      <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3" t="str">
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB9" s="3" t="str">
+      <c r="AC9" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD9" s="3" t="str">
+      <c r="AE9" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2</v>
       </c>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG9" s="3"/>
       <c r="AH9" s="3">
         <v>100</v>
       </c>
       <c r="AI9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ9" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ9" s="3" t="str">
+      <c r="AK9" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="AL9" s="9" t="s">
+      <c r="AM9" s="7" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="10" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>495</v>
       </c>
@@ -14749,50 +14807,51 @@
       <c r="V10" s="5">
         <v>45772</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="5"/>
+      <c r="X10" s="5">
         <v>46096</v>
       </c>
-      <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-      <c r="AG10" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG10" s="3"/>
       <c r="AH10" s="3">
         <v>100</v>
       </c>
       <c r="AI10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ10" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="9" t="s">
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="7" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="11" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>498</v>
       </c>
@@ -14859,52 +14918,53 @@
       <c r="V11" s="5">
         <v>45624</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="5"/>
+      <c r="X11" s="5">
         <v>46127</v>
       </c>
-      <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="3">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AC11" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AD11" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AE11" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AF11" s="3">
         <v>3</v>
       </c>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG11" s="3"/>
       <c r="AH11" s="3">
         <v>100</v>
       </c>
       <c r="AI11" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ11" s="3">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AK11" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="9" t="s">
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="7" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="12" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>501</v>
       </c>
@@ -14971,54 +15031,55 @@
       <c r="V12" s="5">
         <v>45723</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W12" s="5"/>
+      <c r="X12" s="5">
         <v>46096</v>
       </c>
-      <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
-      <c r="AA12" s="3">
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1</v>
       </c>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG12" s="3"/>
       <c r="AH12" s="3">
         <v>100</v>
       </c>
       <c r="AI12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ12" s="3">
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AK12" s="3" t="s">
+      <c r="AL12" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="AL12" s="9" t="s">
+      <c r="AM12" s="7" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>506</v>
       </c>
@@ -15085,50 +15146,51 @@
       <c r="V13" s="5">
         <v>45863</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="5"/>
+      <c r="X13" s="5">
         <v>46127</v>
       </c>
-      <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="3" t="str">
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB13" s="3" t="str">
+      <c r="AC13" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC13" s="3">
+      <c r="AD13" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD13" s="3" t="str">
+      <c r="AE13" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG13" s="3"/>
       <c r="AH13" s="3">
         <v>100</v>
       </c>
       <c r="AI13" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ13" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ13" s="3" t="str">
+      <c r="AK13" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="9" t="s">
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="7" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="14" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>509</v>
       </c>
@@ -15195,52 +15257,53 @@
       <c r="V14" s="5">
         <v>45672</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="5"/>
+      <c r="X14" s="5">
         <v>46096</v>
       </c>
-      <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2</v>
       </c>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG14" s="3"/>
       <c r="AH14" s="3">
         <v>100</v>
       </c>
       <c r="AI14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ14" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="9" t="s">
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="7" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="15" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>513</v>
       </c>
@@ -15307,50 +15370,51 @@
       <c r="V15" s="5">
         <v>46030</v>
       </c>
-      <c r="W15" s="5">
+      <c r="W15" s="5"/>
+      <c r="X15" s="5">
         <v>46127</v>
       </c>
-      <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
-      <c r="AG15" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG15" s="3"/>
       <c r="AH15" s="3">
         <v>100</v>
       </c>
       <c r="AI15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ15" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="9" t="s">
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="7" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="16" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>516</v>
       </c>
@@ -15411,54 +15475,55 @@
         <v>46058</v>
       </c>
       <c r="V16" s="5"/>
-      <c r="W16" s="5">
+      <c r="W16" s="5"/>
+      <c r="X16" s="5">
         <v>46096</v>
       </c>
-      <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="3">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3">
         <v>38</v>
       </c>
-      <c r="AA16" s="3" t="str">
+      <c r="AB16" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB16" s="3" t="str">
+      <c r="AC16" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC16" s="3">
+      <c r="AD16" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD16" s="3" t="str">
+      <c r="AE16" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3">
         <v>75.862068965517238</v>
       </c>
-      <c r="AG16" s="3">
-        <v>100</v>
-      </c>
       <c r="AH16" s="3">
         <v>100</v>
       </c>
       <c r="AI16" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ16" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ16" s="3" t="str">
+      <c r="AK16" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="9" t="s">
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="7" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="17" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>519</v>
       </c>
@@ -15517,50 +15582,51 @@
       <c r="V17" s="5">
         <v>46120</v>
       </c>
-      <c r="W17" s="5">
+      <c r="W17" s="5"/>
+      <c r="X17" s="5">
         <v>46096</v>
       </c>
-      <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
-      <c r="AG17" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG17" s="3"/>
       <c r="AH17" s="3">
         <v>100</v>
       </c>
       <c r="AI17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ17" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="9" t="s">
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="7" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="18" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>522</v>
       </c>
@@ -15613,34 +15679,32 @@
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
       <c r="V18" s="5"/>
-      <c r="W18" s="5">
+      <c r="W18" s="5"/>
+      <c r="X18" s="5">
         <v>46127</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20</v>
       </c>
-      <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3" t="str">
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB18" s="3" t="str">
+      <c r="AC18" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD18" s="3" t="str">
+      <c r="AE18" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3">
-        <v>100</v>
-      </c>
+      <c r="AF18" s="3"/>
       <c r="AG18" s="3">
         <v>100</v>
       </c>
@@ -15648,23 +15712,26 @@
         <v>100</v>
       </c>
       <c r="AI18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ18" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ18" s="3" t="str">
+      <c r="AK18" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="9" t="s">
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="7" t="s">
         <v>953</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="O1:AF1"/>
+    <mergeCell ref="AG1:AL1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -15684,26 +15751,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="24"/>
+      <c r="Q1" s="24"/>
+      <c r="R1" s="24"/>
     </row>
     <row r="2" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -15760,7 +15827,7 @@
       <c r="R2" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="S2" s="6" t="s">
         <v>910</v>
       </c>
     </row>
@@ -15815,7 +15882,7 @@
         <v>99.82</v>
       </c>
       <c r="R3" s="3"/>
-      <c r="S3" s="9" t="s">
+      <c r="S3" s="7" t="s">
         <v>954</v>
       </c>
     </row>
@@ -15870,7 +15937,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3"/>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="7" t="s">
         <v>955</v>
       </c>
     </row>
@@ -15925,7 +15992,7 @@
         <v>98.2</v>
       </c>
       <c r="R5" s="3"/>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="7" t="s">
         <v>956</v>
       </c>
     </row>
@@ -15980,7 +16047,7 @@
         <v>99.98</v>
       </c>
       <c r="R6" s="3"/>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="7" t="s">
         <v>957</v>
       </c>
     </row>
@@ -16035,7 +16102,7 @@
         <v>99.51</v>
       </c>
       <c r="R7" s="3"/>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="7" t="s">
         <v>956</v>
       </c>
     </row>
@@ -16090,7 +16157,7 @@
         <v>49.54</v>
       </c>
       <c r="R8" s="3"/>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="7" t="s">
         <v>958</v>
       </c>
     </row>
@@ -16145,7 +16212,7 @@
         <v>99.56</v>
       </c>
       <c r="R9" s="3"/>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="7" t="s">
         <v>936</v>
       </c>
     </row>
@@ -16200,7 +16267,7 @@
         <v>85.88</v>
       </c>
       <c r="R10" s="3"/>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="7" t="s">
         <v>959</v>
       </c>
     </row>
@@ -16255,7 +16322,7 @@
         <v>89.9</v>
       </c>
       <c r="R11" s="3"/>
-      <c r="S11" s="9" t="s">
+      <c r="S11" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -16310,7 +16377,7 @@
         <v>97.78</v>
       </c>
       <c r="R12" s="3"/>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -16365,7 +16432,7 @@
         <v>99.87</v>
       </c>
       <c r="R13" s="3"/>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="7" t="s">
         <v>960</v>
       </c>
     </row>
@@ -16420,7 +16487,7 @@
         <v>95.45</v>
       </c>
       <c r="R14" s="3"/>
-      <c r="S14" s="9" t="s">
+      <c r="S14" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -16475,7 +16542,7 @@
         <v>99.97</v>
       </c>
       <c r="R15" s="3"/>
-      <c r="S15" s="9" t="s">
+      <c r="S15" s="7" t="s">
         <v>961</v>
       </c>
     </row>
@@ -16530,7 +16597,7 @@
         <v>97.25</v>
       </c>
       <c r="R16" s="3"/>
-      <c r="S16" s="9" t="s">
+      <c r="S16" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -16585,7 +16652,7 @@
         <v>97.16</v>
       </c>
       <c r="R17" s="3"/>
-      <c r="S17" s="9" t="s">
+      <c r="S17" s="7" t="s">
         <v>963</v>
       </c>
     </row>
@@ -16640,7 +16707,7 @@
         <v>86.62</v>
       </c>
       <c r="R18" s="3"/>
-      <c r="S18" s="9" t="s">
+      <c r="S18" s="7" t="s">
         <v>964</v>
       </c>
     </row>
@@ -16695,7 +16762,7 @@
         <v>77.59</v>
       </c>
       <c r="R19" s="3"/>
-      <c r="S19" s="9" t="s">
+      <c r="S19" s="7" t="s">
         <v>965</v>
       </c>
     </row>
@@ -16750,7 +16817,7 @@
         <v>181.2</v>
       </c>
       <c r="R20" s="3"/>
-      <c r="S20" s="9" t="s">
+      <c r="S20" s="7" t="s">
         <v>966</v>
       </c>
     </row>
@@ -16805,7 +16872,7 @@
         <v>89.3</v>
       </c>
       <c r="R21" s="3"/>
-      <c r="S21" s="9" t="s">
+      <c r="S21" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -16860,7 +16927,7 @@
         <v>97.57</v>
       </c>
       <c r="R22" s="3"/>
-      <c r="S22" s="9" t="s">
+      <c r="S22" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -16915,7 +16982,7 @@
         <v>91.85</v>
       </c>
       <c r="R23" s="3"/>
-      <c r="S23" s="9" t="s">
+      <c r="S23" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -16970,7 +17037,7 @@
         <v>95.75</v>
       </c>
       <c r="R24" s="3"/>
-      <c r="S24" s="9" t="s">
+      <c r="S24" s="7" t="s">
         <v>967</v>
       </c>
     </row>
@@ -17025,7 +17092,7 @@
         <v>97.23</v>
       </c>
       <c r="R25" s="3"/>
-      <c r="S25" s="9" t="s">
+      <c r="S25" s="7" t="s">
         <v>968</v>
       </c>
     </row>
@@ -17080,7 +17147,7 @@
         <v>86.53</v>
       </c>
       <c r="R26" s="3"/>
-      <c r="S26" s="9" t="s">
+      <c r="S26" s="7" t="s">
         <v>969</v>
       </c>
     </row>
@@ -17135,7 +17202,7 @@
         <v>87.69</v>
       </c>
       <c r="R27" s="3"/>
-      <c r="S27" s="9" t="s">
+      <c r="S27" s="7" t="s">
         <v>970</v>
       </c>
     </row>
@@ -17190,7 +17257,7 @@
         <v>99.24</v>
       </c>
       <c r="R28" s="3"/>
-      <c r="S28" s="9" t="s">
+      <c r="S28" s="7" t="s">
         <v>971</v>
       </c>
     </row>
@@ -17245,7 +17312,7 @@
         <v>97.75</v>
       </c>
       <c r="R29" s="3"/>
-      <c r="S29" s="9" t="s">
+      <c r="S29" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -17300,7 +17367,7 @@
         <v>93.98</v>
       </c>
       <c r="R30" s="3"/>
-      <c r="S30" s="9" t="s">
+      <c r="S30" s="7" t="s">
         <v>956</v>
       </c>
     </row>
@@ -17355,7 +17422,7 @@
         <v>100</v>
       </c>
       <c r="R31" s="3"/>
-      <c r="S31" s="9" t="s">
+      <c r="S31" s="7" t="s">
         <v>972</v>
       </c>
     </row>
@@ -17410,7 +17477,7 @@
         <v>99.73</v>
       </c>
       <c r="R32" s="3"/>
-      <c r="S32" s="9" t="s">
+      <c r="S32" s="7" t="s">
         <v>973</v>
       </c>
     </row>
@@ -17465,7 +17532,7 @@
         <v>100</v>
       </c>
       <c r="R33" s="3"/>
-      <c r="S33" s="9" t="s">
+      <c r="S33" s="7" t="s">
         <v>974</v>
       </c>
     </row>
@@ -17520,7 +17587,7 @@
         <v>100</v>
       </c>
       <c r="R34" s="3"/>
-      <c r="S34" s="9" t="s">
+      <c r="S34" s="7" t="s">
         <v>965</v>
       </c>
     </row>
@@ -17575,7 +17642,7 @@
         <v>100</v>
       </c>
       <c r="R35" s="3"/>
-      <c r="S35" s="9" t="s">
+      <c r="S35" s="7" t="s">
         <v>975</v>
       </c>
     </row>
@@ -17630,7 +17697,7 @@
         <v>99.14</v>
       </c>
       <c r="R36" s="3"/>
-      <c r="S36" s="9" t="s">
+      <c r="S36" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -17685,7 +17752,7 @@
         <v>76.930000000000007</v>
       </c>
       <c r="R37" s="3"/>
-      <c r="S37" s="9" t="s">
+      <c r="S37" s="7" t="s">
         <v>976</v>
       </c>
     </row>
@@ -17738,7 +17805,7 @@
         <v>101.36</v>
       </c>
       <c r="R38" s="3"/>
-      <c r="S38" s="9" t="s">
+      <c r="S38" s="7" t="s">
         <v>977</v>
       </c>
     </row>
@@ -17793,7 +17860,7 @@
         <v>99.96</v>
       </c>
       <c r="R39" s="3"/>
-      <c r="S39" s="9" t="s">
+      <c r="S39" s="7" t="s">
         <v>978</v>
       </c>
     </row>
@@ -17848,7 +17915,7 @@
         <v>98.42</v>
       </c>
       <c r="R40" s="3"/>
-      <c r="S40" s="9" t="s">
+      <c r="S40" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -17903,7 +17970,7 @@
         <v>98.28</v>
       </c>
       <c r="R41" s="3"/>
-      <c r="S41" s="9" t="s">
+      <c r="S41" s="7" t="s">
         <v>979</v>
       </c>
     </row>
@@ -17958,7 +18025,7 @@
         <v>99.17</v>
       </c>
       <c r="R42" s="3"/>
-      <c r="S42" s="9" t="s">
+      <c r="S42" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -18011,7 +18078,7 @@
         <v>102.12</v>
       </c>
       <c r="R43" s="3"/>
-      <c r="S43" s="9" t="s">
+      <c r="S43" s="7" t="s">
         <v>917</v>
       </c>
     </row>
@@ -18066,7 +18133,7 @@
         <v>90.22</v>
       </c>
       <c r="R44" s="3"/>
-      <c r="S44" s="9" t="s">
+      <c r="S44" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -18121,7 +18188,7 @@
         <v>90.65</v>
       </c>
       <c r="R45" s="3"/>
-      <c r="S45" s="9" t="s">
+      <c r="S45" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -18176,7 +18243,7 @@
         <v>93.32</v>
       </c>
       <c r="R46" s="3"/>
-      <c r="S46" s="9" t="s">
+      <c r="S46" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -18231,7 +18298,7 @@
         <v>100</v>
       </c>
       <c r="R47" s="3"/>
-      <c r="S47" s="9" t="s">
+      <c r="S47" s="7" t="s">
         <v>980</v>
       </c>
     </row>
@@ -18286,7 +18353,7 @@
         <v>86.25</v>
       </c>
       <c r="R48" s="3"/>
-      <c r="S48" s="9" t="s">
+      <c r="S48" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -18341,7 +18408,7 @@
         <v>98.13</v>
       </c>
       <c r="R49" s="3"/>
-      <c r="S49" s="9" t="s">
+      <c r="S49" s="7" t="s">
         <v>981</v>
       </c>
     </row>
@@ -18396,7 +18463,7 @@
         <v>100</v>
       </c>
       <c r="R50" s="3"/>
-      <c r="S50" s="9" t="s">
+      <c r="S50" s="7" t="s">
         <v>982</v>
       </c>
     </row>
@@ -18449,7 +18516,7 @@
         <v>65.83</v>
       </c>
       <c r="R51" s="3"/>
-      <c r="S51" s="9" t="s">
+      <c r="S51" s="7" t="s">
         <v>964</v>
       </c>
     </row>
@@ -18504,7 +18571,7 @@
         <v>99.91</v>
       </c>
       <c r="R52" s="3"/>
-      <c r="S52" s="9" t="s">
+      <c r="S52" s="7" t="s">
         <v>983</v>
       </c>
     </row>
@@ -18559,7 +18626,7 @@
         <v>87.3</v>
       </c>
       <c r="R53" s="3"/>
-      <c r="S53" s="9" t="s">
+      <c r="S53" s="7" t="s">
         <v>984</v>
       </c>
     </row>
@@ -18614,7 +18681,7 @@
         <v>84.17</v>
       </c>
       <c r="R54" s="3"/>
-      <c r="S54" s="9" t="s">
+      <c r="S54" s="7" t="s">
         <v>965</v>
       </c>
     </row>
@@ -18669,7 +18736,7 @@
         <v>100</v>
       </c>
       <c r="R55" s="3"/>
-      <c r="S55" s="9" t="s">
+      <c r="S55" s="7" t="s">
         <v>985</v>
       </c>
     </row>
@@ -18724,7 +18791,7 @@
         <v>99.46</v>
       </c>
       <c r="R56" s="3"/>
-      <c r="S56" s="9" t="s">
+      <c r="S56" s="7" t="s">
         <v>986</v>
       </c>
     </row>
@@ -18779,7 +18846,7 @@
         <v>58.7</v>
       </c>
       <c r="R57" s="3"/>
-      <c r="S57" s="9" t="s">
+      <c r="S57" s="7" t="s">
         <v>969</v>
       </c>
     </row>
@@ -18834,7 +18901,7 @@
         <v>100.53</v>
       </c>
       <c r="R58" s="3"/>
-      <c r="S58" s="9" t="s">
+      <c r="S58" s="7" t="s">
         <v>987</v>
       </c>
     </row>
@@ -18889,7 +18956,7 @@
         <v>61.03</v>
       </c>
       <c r="R59" s="3"/>
-      <c r="S59" s="9" t="s">
+      <c r="S59" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -18944,7 +19011,7 @@
         <v>100</v>
       </c>
       <c r="R60" s="3"/>
-      <c r="S60" s="9" t="s">
+      <c r="S60" s="7" t="s">
         <v>988</v>
       </c>
     </row>
@@ -18999,7 +19066,7 @@
         <v>94.38</v>
       </c>
       <c r="R61" s="3"/>
-      <c r="S61" s="9" t="s">
+      <c r="S61" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -19054,7 +19121,7 @@
         <v>60.48</v>
       </c>
       <c r="R62" s="3"/>
-      <c r="S62" s="9" t="s">
+      <c r="S62" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -19109,7 +19176,7 @@
         <v>83.98</v>
       </c>
       <c r="R63" s="3"/>
-      <c r="S63" s="9" t="s">
+      <c r="S63" s="7" t="s">
         <v>969</v>
       </c>
     </row>
@@ -19164,7 +19231,7 @@
         <v>94.51</v>
       </c>
       <c r="R64" s="3"/>
-      <c r="S64" s="9" t="s">
+      <c r="S64" s="7" t="s">
         <v>989</v>
       </c>
     </row>
@@ -19219,7 +19286,7 @@
         <v>81.650000000000006</v>
       </c>
       <c r="R65" s="3"/>
-      <c r="S65" s="9" t="s">
+      <c r="S65" s="7" t="s">
         <v>990</v>
       </c>
     </row>
@@ -19274,7 +19341,7 @@
         <v>95.06</v>
       </c>
       <c r="R66" s="3"/>
-      <c r="S66" s="9" t="s">
+      <c r="S66" s="7" t="s">
         <v>963</v>
       </c>
     </row>
@@ -19329,7 +19396,7 @@
         <v>96.7</v>
       </c>
       <c r="R67" s="3"/>
-      <c r="S67" s="9" t="s">
+      <c r="S67" s="7" t="s">
         <v>991</v>
       </c>
     </row>
@@ -19384,7 +19451,7 @@
         <v>93.62</v>
       </c>
       <c r="R68" s="3"/>
-      <c r="S68" s="9" t="s">
+      <c r="S68" s="7" t="s">
         <v>962</v>
       </c>
     </row>
@@ -19439,7 +19506,7 @@
         <v>88.96</v>
       </c>
       <c r="R69" s="3"/>
-      <c r="S69" s="9" t="s">
+      <c r="S69" s="7" t="s">
         <v>965</v>
       </c>
     </row>
@@ -19494,7 +19561,7 @@
         <v>43.52</v>
       </c>
       <c r="R70" s="3"/>
-      <c r="S70" s="9" t="s">
+      <c r="S70" s="7" t="s">
         <v>992</v>
       </c>
     </row>
@@ -19549,7 +19616,7 @@
         <v>98.96</v>
       </c>
       <c r="R71" s="3"/>
-      <c r="S71" s="9" t="s">
+      <c r="S71" s="7" t="s">
         <v>993</v>
       </c>
     </row>
@@ -19604,7 +19671,7 @@
         <v>99.66</v>
       </c>
       <c r="R72" s="3"/>
-      <c r="S72" s="9" t="s">
+      <c r="S72" s="7" t="s">
         <v>994</v>
       </c>
     </row>
@@ -19659,7 +19726,7 @@
         <v>98.46</v>
       </c>
       <c r="R73" s="3"/>
-      <c r="S73" s="9" t="s">
+      <c r="S73" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -19714,7 +19781,7 @@
         <v>99.61</v>
       </c>
       <c r="R74" s="3"/>
-      <c r="S74" s="9" t="s">
+      <c r="S74" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -19769,7 +19836,7 @@
         <v>99.34</v>
       </c>
       <c r="R75" s="3"/>
-      <c r="S75" s="9" t="s">
+      <c r="S75" s="7" t="s">
         <v>995</v>
       </c>
     </row>
@@ -19824,7 +19891,7 @@
         <v>99.86</v>
       </c>
       <c r="R76" s="3"/>
-      <c r="S76" s="9" t="s">
+      <c r="S76" s="7" t="s">
         <v>996</v>
       </c>
     </row>
@@ -19873,7 +19940,7 @@
         <v>0</v>
       </c>
       <c r="R77" s="3"/>
-      <c r="S77" s="9" t="s">
+      <c r="S77" s="7" t="s">
         <v>924</v>
       </c>
     </row>
@@ -19928,7 +19995,7 @@
         <v>92.14</v>
       </c>
       <c r="R78" s="3"/>
-      <c r="S78" s="9" t="s">
+      <c r="S78" s="7" t="s">
         <v>996</v>
       </c>
     </row>
@@ -19983,7 +20050,7 @@
         <v>99.97</v>
       </c>
       <c r="R79" s="3"/>
-      <c r="S79" s="9" t="s">
+      <c r="S79" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20036,7 +20103,7 @@
         <v>82.2</v>
       </c>
       <c r="R80" s="3"/>
-      <c r="S80" s="9" t="s">
+      <c r="S80" s="7" t="s">
         <v>924</v>
       </c>
     </row>
@@ -20091,7 +20158,7 @@
         <v>73.13</v>
       </c>
       <c r="R81" s="3"/>
-      <c r="S81" s="9" t="s">
+      <c r="S81" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20146,7 +20213,7 @@
         <v>92.4</v>
       </c>
       <c r="R82" s="3"/>
-      <c r="S82" s="9" t="s">
+      <c r="S82" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -20201,7 +20268,7 @@
         <v>95.06</v>
       </c>
       <c r="R83" s="3"/>
-      <c r="S83" s="9" t="s">
+      <c r="S83" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20256,7 +20323,7 @@
         <v>82.73</v>
       </c>
       <c r="R84" s="3"/>
-      <c r="S84" s="9" t="s">
+      <c r="S84" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20311,7 +20378,7 @@
         <v>93.6</v>
       </c>
       <c r="R85" s="3"/>
-      <c r="S85" s="9" t="s">
+      <c r="S85" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20366,7 +20433,7 @@
         <v>90.33</v>
       </c>
       <c r="R86" s="3"/>
-      <c r="S86" s="9" t="s">
+      <c r="S86" s="7" t="s">
         <v>997</v>
       </c>
     </row>
@@ -20421,7 +20488,7 @@
         <v>66.63</v>
       </c>
       <c r="R87" s="3"/>
-      <c r="S87" s="9" t="s">
+      <c r="S87" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20476,7 +20543,7 @@
         <v>75.38</v>
       </c>
       <c r="R88" s="3"/>
-      <c r="S88" s="9" t="s">
+      <c r="S88" s="7" t="s">
         <v>998</v>
       </c>
     </row>
@@ -20531,7 +20598,7 @@
         <v>92.23</v>
       </c>
       <c r="R89" s="3"/>
-      <c r="S89" s="9" t="s">
+      <c r="S89" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -20586,7 +20653,7 @@
         <v>22.96</v>
       </c>
       <c r="R90" s="3"/>
-      <c r="S90" s="9" t="s">
+      <c r="S90" s="7" t="s">
         <v>999</v>
       </c>
     </row>
@@ -20641,7 +20708,7 @@
         <v>0</v>
       </c>
       <c r="R91" s="3"/>
-      <c r="S91" s="9" t="s">
+      <c r="S91" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20696,7 +20763,7 @@
         <v>1.17</v>
       </c>
       <c r="R92" s="3"/>
-      <c r="S92" s="9" t="s">
+      <c r="S92" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20749,7 +20816,7 @@
         <v>10.53</v>
       </c>
       <c r="R93" s="3"/>
-      <c r="S93" s="9" t="s">
+      <c r="S93" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20802,7 +20869,7 @@
         <v>90</v>
       </c>
       <c r="R94" s="3"/>
-      <c r="S94" s="9" t="s">
+      <c r="S94" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -20857,7 +20924,7 @@
         <v>69.88</v>
       </c>
       <c r="R95" s="3"/>
-      <c r="S95" s="9" t="s">
+      <c r="S95" s="7" t="s">
         <v>1000</v>
       </c>
     </row>
@@ -20908,7 +20975,7 @@
         <v>0</v>
       </c>
       <c r="R96" s="3"/>
-      <c r="S96" s="9" t="s">
+      <c r="S96" s="7" t="s">
         <v>1001</v>
       </c>
     </row>
@@ -20963,7 +21030,7 @@
         <v>24.54</v>
       </c>
       <c r="R97" s="3"/>
-      <c r="S97" s="9" t="s">
+      <c r="S97" s="7" t="s">
         <v>919</v>
       </c>
     </row>
@@ -21018,7 +21085,7 @@
         <v>27.96</v>
       </c>
       <c r="R98" s="3"/>
-      <c r="S98" s="9" t="s">
+      <c r="S98" s="7" t="s">
         <v>1002</v>
       </c>
     </row>
@@ -21071,7 +21138,7 @@
         <v>98.93</v>
       </c>
       <c r="R99" s="3"/>
-      <c r="S99" s="9" t="s">
+      <c r="S99" s="7" t="s">
         <v>1003</v>
       </c>
     </row>
@@ -21126,7 +21193,7 @@
         <v>99.22</v>
       </c>
       <c r="R100" s="3"/>
-      <c r="S100" s="9" t="s">
+      <c r="S100" s="7" t="s">
         <v>920</v>
       </c>
     </row>
@@ -21181,7 +21248,7 @@
         <v>99.98</v>
       </c>
       <c r="R101" s="3"/>
-      <c r="S101" s="9" t="s">
+      <c r="S101" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -21236,7 +21303,7 @@
         <v>100</v>
       </c>
       <c r="R102" s="3"/>
-      <c r="S102" s="9" t="s">
+      <c r="S102" s="7" t="s">
         <v>956</v>
       </c>
     </row>
@@ -21291,7 +21358,7 @@
         <v>99.99</v>
       </c>
       <c r="R103" s="3"/>
-      <c r="S103" s="9" t="s">
+      <c r="S103" s="7" t="s">
         <v>1000</v>
       </c>
     </row>
@@ -21342,7 +21409,7 @@
         <v>0</v>
       </c>
       <c r="R104" s="3"/>
-      <c r="S104" s="9" t="s">
+      <c r="S104" s="7" t="s">
         <v>933</v>
       </c>
     </row>
@@ -21358,12 +21425,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21511,15 +21575,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21543,10 +21611,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756A7DC6-C7E1-4A10-9285-8ED480A28480}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{109AD901-52CD-4EF7-A580-DA1182E466FC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListadoMunicipios" sheetId="5" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2194" uniqueCount="1067">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1504,13 +1504,7 @@
     <t>FUENTE</t>
   </si>
   <si>
-    <t xml:space="preserve">VALOR OTROS </t>
-  </si>
-  <si>
     <t>VALOR TOTAL</t>
-  </si>
-  <si>
-    <t>FECHA DE INCORPORACIÓN DE RECUROS</t>
   </si>
   <si>
     <t>AVANCE FÍSICO</t>
@@ -3689,48 +3683,6 @@
   <dxfs count="19">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Roboto"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3780,45 +3732,41 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
         </left>
         <right style="thin">
           <color auto="1"/>
         </right>
         <top style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </top>
         <bottom style="thin">
-          <color indexed="64"/>
+          <color auto="1"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color auto="1"/>
-        </right>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -4040,6 +3988,52 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4053,15 +4047,19 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="18" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="14" dataDxfId="12" headerRowBorderDxfId="13" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="A1:E26" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -4069,7 +4067,18 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AX59" totalsRowShown="0">
-  <autoFilter ref="A2:AX59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A2:AX59" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Infraestructura"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="CONTRATADO SIN ACTA DE INICIO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="50">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -4117,12 +4126,12 @@
     <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="0">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="18">
       <calculatedColumnFormula>IFERROR(IF(AND(ISNUMBER($AC3),ISNUMBER($AE3),$AC3&lt;$AE3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="8"/>
-    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="7"/>
-    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="6"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="17"/>
+    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="16"/>
+    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4141,11 +4150,11 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="ESTADO PROYECTO"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="ESTADO CONTRATO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="VALOR SGR"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS "/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="FECHA DE MIGRACIÓN A GESPROY"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="CPI"/>
@@ -4154,7 +4163,7 @@
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
-    <tableColumn id="39" xr3:uid="{EB9A8E1B-7DA7-46A0-8178-E11424FA43F8}" name="HORIZONTE DEL PROYECTO" dataDxfId="2"/>
+    <tableColumn id="39" xr3:uid="{EB9A8E1B-7DA7-46A0-8178-E11424FA43F8}" name="HORIZONTE DEL PROYECTO" dataDxfId="4"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0100-000019000000}" name="DIAS DESDE LA APERTURA HASTA LA FIRMA DEL PRIMER CONTRATO"/>
@@ -4168,11 +4177,11 @@
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0100-000021000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0100-000022000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0100-000023000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="1">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(IF(AND(ISNUMBER($W3),ISNUMBER($X3),$W3&lt;$X3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AF3&gt;=1),(IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))*$AJ3/100,IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="5"/>
-    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="4"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="2"/>
+    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4195,12 +4204,12 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS "/>
-    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="3"/>
+    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4504,16 +4513,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C1" s="21" t="s">
         <v>1050</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="D1" s="21" t="s">
         <v>1051</v>
-      </c>
-      <c r="C1" s="21" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4521,13 +4530,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="D2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4535,13 +4544,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="D3" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -4549,13 +4558,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="D4" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -4563,13 +4572,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="D5" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -4577,13 +4586,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="D6" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -4591,13 +4600,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="22" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>1054</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>1056</v>
-      </c>
       <c r="D7" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -4605,13 +4614,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D8" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -4619,13 +4628,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="D9" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -4633,13 +4642,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="D10" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -4647,13 +4656,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="D11" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -4661,13 +4670,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="D12" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -4675,13 +4684,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="D13" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -4689,13 +4698,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="D14" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -4703,13 +4712,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D15" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -4717,13 +4726,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="D16" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -4731,13 +4740,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="D17" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -4745,13 +4754,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D18" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -4759,13 +4768,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D19" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -4773,13 +4782,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="22" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C20" s="23" t="s">
         <v>1061</v>
       </c>
-      <c r="C20" s="23" t="s">
-        <v>1063</v>
-      </c>
       <c r="D20" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -4787,13 +4796,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C21" s="22" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="D21" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -4801,13 +4810,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="D22" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -4815,13 +4824,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C23" s="22" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="D23" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -4829,13 +4838,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C24" s="22" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="D24" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -4843,13 +4852,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D25" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -4857,13 +4866,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C26" s="22" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D26" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -4871,24 +4880,24 @@
         <v>26</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="D27" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B28" s="22" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C28" s="22" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D28" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -4910,377 +4919,377 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>1004</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>1005</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>1006</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>1009</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>1010</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>1011</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E5" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>1021</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>1023</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>1025</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>1027</v>
-      </c>
       <c r="D9" s="14" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B14" s="16" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E14" s="17" t="s">
         <v>1035</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>1018</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E18" s="17"/>
     </row>
     <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E20" s="17"/>
     </row>
     <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E21" s="17"/>
     </row>
     <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E22" s="17"/>
     </row>
     <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E23" s="17"/>
     </row>
     <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="17"/>
@@ -5289,7 +5298,7 @@
     <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25" s="16" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="17"/>
@@ -5298,7 +5307,7 @@
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="17"/>
@@ -5530,13 +5539,13 @@
         <v>50</v>
       </c>
       <c r="AW2" s="6" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="AX2" s="6" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>51</v>
       </c>
@@ -5677,13 +5686,13 @@
         <v>63</v>
       </c>
       <c r="AW3" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="4" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
@@ -5814,13 +5823,13 @@
         <v>72</v>
       </c>
       <c r="AW4" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX4" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="5" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>73</v>
       </c>
@@ -5961,13 +5970,13 @@
         <v>80</v>
       </c>
       <c r="AW5" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX5" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="6" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>81</v>
       </c>
@@ -6111,10 +6120,10 @@
       </c>
       <c r="AW6" s="7"/>
       <c r="AX6" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="7" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>90</v>
       </c>
@@ -6255,13 +6264,13 @@
         <v>100</v>
       </c>
       <c r="AW7" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX7" s="7" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="8" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>101</v>
       </c>
@@ -6402,13 +6411,13 @@
         <v>107</v>
       </c>
       <c r="AW8" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX8" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="9" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>108</v>
       </c>
@@ -6553,13 +6562,13 @@
         <v>114</v>
       </c>
       <c r="AW9" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX9" s="7" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="10" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>115</v>
       </c>
@@ -6700,13 +6709,13 @@
         <v>80</v>
       </c>
       <c r="AW10" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX10" s="7" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="11" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>122</v>
       </c>
@@ -6847,13 +6856,13 @@
         <v>80</v>
       </c>
       <c r="AW11" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX11" s="7" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="12" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>127</v>
       </c>
@@ -6994,13 +7003,13 @@
         <v>134</v>
       </c>
       <c r="AW12" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX12" s="7" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="13" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>135</v>
       </c>
@@ -7143,13 +7152,13 @@
         <v>144</v>
       </c>
       <c r="AW13" s="7" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="AX13" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="14" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>145</v>
       </c>
@@ -7290,13 +7299,13 @@
         <v>151</v>
       </c>
       <c r="AW14" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX14" s="7" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="15" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>152</v>
       </c>
@@ -7439,13 +7448,13 @@
         <v>157</v>
       </c>
       <c r="AW15" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX15" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="16" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>158</v>
       </c>
@@ -7586,13 +7595,13 @@
         <v>80</v>
       </c>
       <c r="AW16" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX16" s="7" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="17" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>164</v>
       </c>
@@ -7735,13 +7744,13 @@
         <v>171</v>
       </c>
       <c r="AW17" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX17" s="7" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="18" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>172</v>
       </c>
@@ -7884,13 +7893,13 @@
         <v>178</v>
       </c>
       <c r="AW18" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX18" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="19" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>179</v>
       </c>
@@ -8033,13 +8042,13 @@
         <v>183</v>
       </c>
       <c r="AW19" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX19" s="7" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="20" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>184</v>
       </c>
@@ -8180,13 +8189,13 @@
         <v>80</v>
       </c>
       <c r="AW20" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX20" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="21" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>189</v>
       </c>
@@ -8329,13 +8338,13 @@
         <v>196</v>
       </c>
       <c r="AW21" s="7" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="AX21" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="22" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>197</v>
       </c>
@@ -8478,13 +8487,13 @@
         <v>204</v>
       </c>
       <c r="AW22" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX22" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="23" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>205</v>
       </c>
@@ -8619,13 +8628,13 @@
         <v>210</v>
       </c>
       <c r="AW23" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX23" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="24" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>211</v>
       </c>
@@ -8760,13 +8769,13 @@
         <v>218</v>
       </c>
       <c r="AW24" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX24" s="7" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="25" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>219</v>
       </c>
@@ -8899,13 +8908,13 @@
         <v>210</v>
       </c>
       <c r="AW25" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX25" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="26" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>224</v>
       </c>
@@ -9048,13 +9057,13 @@
         <v>231</v>
       </c>
       <c r="AW26" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX26" s="7" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="27" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>232</v>
       </c>
@@ -9195,13 +9204,13 @@
         <v>80</v>
       </c>
       <c r="AW27" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX27" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="28" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>238</v>
       </c>
@@ -9340,13 +9349,13 @@
         <v>210</v>
       </c>
       <c r="AW28" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX28" s="7" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="29" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>244</v>
       </c>
@@ -9487,13 +9496,13 @@
         <v>250</v>
       </c>
       <c r="AW29" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX29" s="7" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="30" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>251</v>
       </c>
@@ -9628,13 +9637,13 @@
         <v>210</v>
       </c>
       <c r="AW30" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX30" s="7" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="31" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>255</v>
       </c>
@@ -9773,13 +9782,13 @@
         <v>210</v>
       </c>
       <c r="AW31" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX31" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="32" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>261</v>
       </c>
@@ -9922,13 +9931,13 @@
         <v>268</v>
       </c>
       <c r="AW32" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX32" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="33" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="33" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>269</v>
       </c>
@@ -10071,13 +10080,13 @@
         <v>277</v>
       </c>
       <c r="AW33" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX33" s="7" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="34" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="34" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>278</v>
       </c>
@@ -10216,13 +10225,13 @@
         <v>210</v>
       </c>
       <c r="AW34" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX34" s="7" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="35" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="35" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>284</v>
       </c>
@@ -10353,13 +10362,13 @@
         <v>210</v>
       </c>
       <c r="AW35" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX35" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="36" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="36" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>289</v>
       </c>
@@ -10501,10 +10510,10 @@
       </c>
       <c r="AW36" s="7"/>
       <c r="AX36" s="7" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="37" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="37" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>296</v>
       </c>
@@ -10643,13 +10652,13 @@
         <v>302</v>
       </c>
       <c r="AW37" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX37" s="7" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="38" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="38" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>303</v>
       </c>
@@ -10792,13 +10801,13 @@
         <v>309</v>
       </c>
       <c r="AW38" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX38" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="39" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="39" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>310</v>
       </c>
@@ -10939,13 +10948,13 @@
         <v>316</v>
       </c>
       <c r="AW39" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX39" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="40" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="40" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>317</v>
       </c>
@@ -11088,13 +11097,13 @@
         <v>323</v>
       </c>
       <c r="AW40" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX40" s="7" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="41" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="41" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>324</v>
       </c>
@@ -11237,13 +11246,13 @@
         <v>330</v>
       </c>
       <c r="AW41" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX41" s="7" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="42" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="42" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>331</v>
       </c>
@@ -11384,13 +11393,13 @@
         <v>336</v>
       </c>
       <c r="AW42" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX42" s="7" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="43" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="43" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>337</v>
       </c>
@@ -11521,13 +11530,13 @@
         <v>344</v>
       </c>
       <c r="AW43" s="7" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="AX43" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="44" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="44" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>345</v>
       </c>
@@ -11670,13 +11679,13 @@
         <v>351</v>
       </c>
       <c r="AW44" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX44" s="7" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="45" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="45" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>352</v>
       </c>
@@ -11817,10 +11826,10 @@
         <v>361</v>
       </c>
       <c r="AW45" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX45" s="7" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="46" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -11897,11 +11906,9 @@
         <v>45827</v>
       </c>
       <c r="AA46" s="5">
-        <v>46161</v>
-      </c>
-      <c r="AB46" s="5">
         <v>45827</v>
       </c>
+      <c r="AB46" s="5"/>
       <c r="AC46" s="5"/>
       <c r="AD46" s="5"/>
       <c r="AE46" s="5">
@@ -11960,13 +11967,13 @@
         <v>371</v>
       </c>
       <c r="AW46" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX46" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="47" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="47" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>372</v>
       </c>
@@ -12109,15 +12116,15 @@
         <v>378</v>
       </c>
       <c r="AW47" s="7" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="AX47" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="48" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="48" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>270</v>
@@ -12130,7 +12137,7 @@
         <v>273</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>341</v>
@@ -12138,7 +12145,7 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="K48" s="4">
         <v>1361249394</v>
@@ -12229,16 +12236,16 @@
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="AW48" s="7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="AX48" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="49" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="49" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>380</v>
       </c>
@@ -12359,13 +12366,13 @@
         <v>384</v>
       </c>
       <c r="AW49" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX49" s="7" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="50" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="50" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>385</v>
       </c>
@@ -12506,13 +12513,13 @@
         <v>391</v>
       </c>
       <c r="AW50" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX50" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="51" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="51" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>392</v>
       </c>
@@ -12653,13 +12660,13 @@
         <v>398</v>
       </c>
       <c r="AW51" s="7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AX51" s="7" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="52" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="52" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>399</v>
       </c>
@@ -12802,10 +12809,10 @@
         <v>398</v>
       </c>
       <c r="AW52" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="AX52" s="7" t="s">
         <v>918</v>
-      </c>
-      <c r="AX52" s="7" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="53" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12943,13 +12950,13 @@
         <v>409</v>
       </c>
       <c r="AW53" s="7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AX53" s="7" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="54" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="54" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>410</v>
       </c>
@@ -13076,13 +13083,13 @@
         <v>416</v>
       </c>
       <c r="AW54" s="7" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="AX54" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="55" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="55" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>417</v>
       </c>
@@ -13221,13 +13228,13 @@
         <v>423</v>
       </c>
       <c r="AW55" s="7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AX55" s="7" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="56" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="56" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>424</v>
       </c>
@@ -13364,13 +13371,13 @@
         <v>431</v>
       </c>
       <c r="AW56" s="7" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="AX56" s="7" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="57" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="57" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>432</v>
       </c>
@@ -13501,13 +13508,13 @@
         <v>439</v>
       </c>
       <c r="AW57" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="AX57" s="7" t="s">
         <v>918</v>
       </c>
-      <c r="AX57" s="7" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="58" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>440</v>
       </c>
@@ -13634,13 +13641,13 @@
         <v>445</v>
       </c>
       <c r="AW58" s="7" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="AX58" s="7" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="59" spans="1:50" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="59" spans="1:50" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>446</v>
       </c>
@@ -13766,7 +13773,7 @@
       </c>
       <c r="AW59" s="7"/>
       <c r="AX59" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -13871,10 +13878,10 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>457</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>458</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>20</v>
@@ -13883,10 +13890,10 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>459</v>
+        <v>22</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
@@ -13958,33 +13965,33 @@
         <v>50</v>
       </c>
       <c r="AM2" s="6" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>281</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I3" s="4">
         <v>2006938345.6700001</v>
@@ -14062,36 +14069,36 @@
         <v/>
       </c>
       <c r="AL3" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>468</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>281</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I4" s="4">
         <v>1295118639.0699999</v>
@@ -14169,24 +14176,24 @@
         <v/>
       </c>
       <c r="AL4" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM4" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="5" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
@@ -14198,7 +14205,7 @@
         <v>86</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I5" s="4">
         <v>3153851580.9099998</v>
@@ -14282,36 +14289,36 @@
         <v>75</v>
       </c>
       <c r="AL5" s="3" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="AM5" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>478</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>480</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>281</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I6" s="4">
         <v>6026477761</v>
@@ -14397,36 +14404,36 @@
         <v>50</v>
       </c>
       <c r="AL6" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM6" s="7" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>484</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>486</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>281</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I7" s="4">
         <v>1800000000</v>
@@ -14512,24 +14519,24 @@
         <v>50</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="AM7" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>488</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>55</v>
@@ -14541,7 +14548,7 @@
         <v>57</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I8" s="4">
         <v>1702007732.2</v>
@@ -14619,36 +14626,36 @@
         <v/>
       </c>
       <c r="AL8" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM8" s="7" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>491</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I9" s="4">
         <v>13713002364.719999</v>
@@ -14734,24 +14741,24 @@
         <v/>
       </c>
       <c r="AL9" s="3" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="AM9" s="7" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="10" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>497</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>222</v>
@@ -14763,7 +14770,7 @@
         <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I10" s="4">
         <v>9056051736.6399994</v>
@@ -14848,21 +14855,21 @@
       </c>
       <c r="AL10" s="3"/>
       <c r="AM10" s="7" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>500</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>281</v>
@@ -14874,7 +14881,7 @@
         <v>86</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I11" s="4">
         <v>7862105021</v>
@@ -14961,21 +14968,21 @@
       </c>
       <c r="AL11" s="3"/>
       <c r="AM11" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="12" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>504</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>258</v>
@@ -14987,7 +14994,7 @@
         <v>86</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I12" s="4">
         <v>15100656106.639999</v>
@@ -15073,24 +15080,24 @@
         <v>90</v>
       </c>
       <c r="AL12" s="3" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="AM12" s="7" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="13" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>508</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>273</v>
@@ -15102,7 +15109,7 @@
         <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I13" s="4">
         <v>3068416428</v>
@@ -15187,21 +15194,21 @@
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>511</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>258</v>
@@ -15213,7 +15220,7 @@
         <v>86</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I14" s="4">
         <v>63850574205.629997</v>
@@ -15300,21 +15307,21 @@
       </c>
       <c r="AL14" s="3"/>
       <c r="AM14" s="7" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="15" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>513</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>515</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>281</v>
@@ -15326,7 +15333,7 @@
         <v>86</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I15" s="4">
         <v>11318403530.17</v>
@@ -15411,21 +15418,21 @@
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="7" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="16" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>516</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>258</v>
@@ -15437,7 +15444,7 @@
         <v>366</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I16" s="4">
         <v>1903272161</v>
@@ -15520,21 +15527,21 @@
       </c>
       <c r="AL16" s="3"/>
       <c r="AM16" s="7" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="17" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>519</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>521</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>258</v>
@@ -15546,7 +15553,7 @@
         <v>86</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I17" s="4">
         <v>1484402616</v>
@@ -15623,33 +15630,33 @@
       </c>
       <c r="AL17" s="3"/>
       <c r="AM17" s="7" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="18" spans="1:39" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>522</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>524</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>281</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>341</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I18" s="4">
         <v>627486059.86000001</v>
@@ -15724,7 +15731,7 @@
       </c>
       <c r="AL18" s="3"/>
       <c r="AM18" s="7" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
   </sheetData>
@@ -15804,7 +15811,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -15813,36 +15820,36 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>459</v>
+        <v>22</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>30</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>94</v>
@@ -15854,7 +15861,7 @@
         <v>57</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I3" s="4">
         <v>22526692745</v>
@@ -15883,21 +15890,21 @@
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="7" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>534</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>94</v>
@@ -15909,7 +15916,7 @@
         <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I4" s="4">
         <v>924979909</v>
@@ -15938,21 +15945,21 @@
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="7" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>538</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>94</v>
@@ -15964,7 +15971,7 @@
         <v>57</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I5" s="4">
         <v>999998309</v>
@@ -15993,21 +16000,21 @@
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="7" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>542</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>544</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>94</v>
@@ -16019,7 +16026,7 @@
         <v>57</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I6" s="4">
         <v>16567304387</v>
@@ -16048,33 +16055,33 @@
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="7" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>545</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>547</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I7" s="4">
         <v>12429000000</v>
@@ -16103,21 +16110,21 @@
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="7" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>552</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>355</v>
@@ -16129,7 +16136,7 @@
         <v>86</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I8" s="4">
         <v>14996018261</v>
@@ -16158,33 +16165,33 @@
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="7" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>554</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I9" s="4">
         <v>14913362760</v>
@@ -16213,33 +16220,33 @@
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="7" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I10" s="4">
         <v>7037696704</v>
@@ -16268,21 +16275,21 @@
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="7" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>564</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>566</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>68</v>
@@ -16294,7 +16301,7 @@
         <v>57</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I11" s="4">
         <v>13800000000</v>
@@ -16323,33 +16330,33 @@
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>568</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>570</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I12" s="4">
         <v>16094650077</v>
@@ -16378,33 +16385,33 @@
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>573</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>575</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="I13" s="4">
         <v>54337268559</v>
@@ -16433,33 +16440,33 @@
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="7" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>581</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I14" s="4">
         <v>5261488233</v>
@@ -16488,21 +16495,21 @@
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>138</v>
@@ -16514,7 +16521,7 @@
         <v>57</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I15" s="4">
         <v>8077068482</v>
@@ -16543,21 +16550,21 @@
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="7" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>590</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>68</v>
@@ -16569,7 +16576,7 @@
         <v>86</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I16" s="4">
         <v>7750000000</v>
@@ -16598,21 +16605,21 @@
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>592</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>68</v>
@@ -16624,7 +16631,7 @@
         <v>86</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I17" s="4">
         <v>1027100000</v>
@@ -16653,21 +16660,21 @@
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="7" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>598</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>68</v>
@@ -16679,7 +16686,7 @@
         <v>86</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I18" s="4">
         <v>9491491960</v>
@@ -16708,21 +16715,21 @@
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="7" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>602</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>68</v>
@@ -16734,7 +16741,7 @@
         <v>86</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I19" s="4">
         <v>4024500000</v>
@@ -16763,21 +16770,21 @@
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="7" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>604</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>606</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>68</v>
@@ -16789,7 +16796,7 @@
         <v>86</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I20" s="4">
         <v>20233937500</v>
@@ -16818,21 +16825,21 @@
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="7" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>608</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>610</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>68</v>
@@ -16844,7 +16851,7 @@
         <v>86</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I21" s="4">
         <v>6524500000</v>
@@ -16873,21 +16880,21 @@
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>612</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>614</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>68</v>
@@ -16899,7 +16906,7 @@
         <v>86</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I22" s="4">
         <v>2500000000</v>
@@ -16928,21 +16935,21 @@
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>618</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>68</v>
@@ -16954,7 +16961,7 @@
         <v>86</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I23" s="4">
         <v>3500000000</v>
@@ -16983,21 +16990,21 @@
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>620</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>622</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>68</v>
@@ -17009,7 +17016,7 @@
         <v>86</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I24" s="4">
         <v>3250000000</v>
@@ -17038,21 +17045,21 @@
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="7" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>624</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>626</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>68</v>
@@ -17064,7 +17071,7 @@
         <v>86</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I25" s="4">
         <v>946000000</v>
@@ -17093,21 +17100,21 @@
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="7" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>628</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>630</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>68</v>
@@ -17119,7 +17126,7 @@
         <v>86</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I26" s="4">
         <v>1943625000</v>
@@ -17148,21 +17155,21 @@
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="7" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>634</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>68</v>
@@ -17174,7 +17181,7 @@
         <v>86</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I27" s="4">
         <v>1999999962.27</v>
@@ -17203,33 +17210,33 @@
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="7" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>636</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>638</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I28" s="4">
         <v>729826686</v>
@@ -17258,33 +17265,33 @@
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="7" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>640</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>642</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>258</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>57</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I29" s="4">
         <v>37141732473</v>
@@ -17313,21 +17320,21 @@
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>644</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>646</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>94</v>
@@ -17339,7 +17346,7 @@
         <v>86</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I30" s="4">
         <v>22507978719</v>
@@ -17368,33 +17375,33 @@
       </c>
       <c r="R30" s="3"/>
       <c r="S30" s="7" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>650</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I31" s="4">
         <v>38700180208.470001</v>
@@ -17423,21 +17430,21 @@
       </c>
       <c r="R31" s="3"/>
       <c r="S31" s="7" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>652</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>654</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>94</v>
@@ -17449,7 +17456,7 @@
         <v>57</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I32" s="4">
         <v>75409582200</v>
@@ -17478,21 +17485,21 @@
       </c>
       <c r="R32" s="3"/>
       <c r="S32" s="7" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>655</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>657</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>68</v>
@@ -17504,7 +17511,7 @@
         <v>57</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I33" s="4">
         <v>1998000000</v>
@@ -17533,21 +17540,21 @@
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="7" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>658</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>660</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>68</v>
@@ -17559,7 +17566,7 @@
         <v>57</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I34" s="4">
         <v>1999306318</v>
@@ -17588,21 +17595,21 @@
       </c>
       <c r="R34" s="3"/>
       <c r="S34" s="7" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>664</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>68</v>
@@ -17614,7 +17621,7 @@
         <v>209</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I35" s="4">
         <v>1999910691</v>
@@ -17643,21 +17650,21 @@
       </c>
       <c r="R35" s="3"/>
       <c r="S35" s="7" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>666</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>668</v>
       </c>
       <c r="E36" s="3" t="s">
         <v>68</v>
@@ -17669,7 +17676,7 @@
         <v>86</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I36" s="4">
         <v>1999433630</v>
@@ -17698,21 +17705,21 @@
       </c>
       <c r="R36" s="3"/>
       <c r="S36" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>670</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>672</v>
       </c>
       <c r="E37" s="3" t="s">
         <v>68</v>
@@ -17724,7 +17731,7 @@
         <v>86</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I37" s="4">
         <v>1999976897</v>
@@ -17753,21 +17760,21 @@
       </c>
       <c r="R37" s="3"/>
       <c r="S37" s="7" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>676</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>68</v>
@@ -17779,7 +17786,7 @@
         <v>57</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I38" s="4">
         <v>1272365336</v>
@@ -17806,21 +17813,21 @@
       </c>
       <c r="R38" s="3"/>
       <c r="S38" s="7" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>678</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>680</v>
       </c>
       <c r="E39" s="3" t="s">
         <v>68</v>
@@ -17832,7 +17839,7 @@
         <v>86</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I39" s="4">
         <v>1999833255</v>
@@ -17861,21 +17868,21 @@
       </c>
       <c r="R39" s="3"/>
       <c r="S39" s="7" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>682</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>684</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>68</v>
@@ -17887,7 +17894,7 @@
         <v>57</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I40" s="4">
         <v>6559568533</v>
@@ -17916,21 +17923,21 @@
       </c>
       <c r="R40" s="3"/>
       <c r="S40" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>685</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>687</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>68</v>
@@ -17942,7 +17949,7 @@
         <v>86</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I41" s="4">
         <v>1998890586.73</v>
@@ -17971,21 +17978,21 @@
       </c>
       <c r="R41" s="3"/>
       <c r="S41" s="7" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>688</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>690</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>68</v>
@@ -17997,7 +18004,7 @@
         <v>209</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I42" s="4">
         <v>5347795060</v>
@@ -18026,21 +18033,21 @@
       </c>
       <c r="R42" s="3"/>
       <c r="S42" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>691</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>693</v>
       </c>
       <c r="E43" s="3" t="s">
         <v>68</v>
@@ -18052,7 +18059,7 @@
         <v>86</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I43" s="4">
         <v>1965295196.9400001</v>
@@ -18079,21 +18086,21 @@
       </c>
       <c r="R43" s="3"/>
       <c r="S43" s="7" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>694</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>696</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>68</v>
@@ -18105,7 +18112,7 @@
         <v>86</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I44" s="4">
         <v>8764697664</v>
@@ -18134,21 +18141,21 @@
       </c>
       <c r="R44" s="3"/>
       <c r="S44" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>698</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>700</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>68</v>
@@ -18160,7 +18167,7 @@
         <v>57</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I45" s="4">
         <v>1349000868</v>
@@ -18189,21 +18196,21 @@
       </c>
       <c r="R45" s="3"/>
       <c r="S45" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>702</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>68</v>
@@ -18215,7 +18222,7 @@
         <v>57</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I46" s="4">
         <v>3106000000</v>
@@ -18244,21 +18251,21 @@
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>705</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>707</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>68</v>
@@ -18270,7 +18277,7 @@
         <v>57</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I47" s="4">
         <v>8995267958.5699997</v>
@@ -18299,21 +18306,21 @@
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="7" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>709</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>711</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>68</v>
@@ -18325,7 +18332,7 @@
         <v>86</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I48" s="4">
         <v>6750000000</v>
@@ -18354,21 +18361,21 @@
       </c>
       <c r="R48" s="3"/>
       <c r="S48" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="49" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>712</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>714</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>68</v>
@@ -18380,7 +18387,7 @@
         <v>86</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I49" s="4">
         <v>1998157618.8800001</v>
@@ -18409,21 +18416,21 @@
       </c>
       <c r="R49" s="3"/>
       <c r="S49" s="7" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="50" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>715</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>717</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>68</v>
@@ -18435,7 +18442,7 @@
         <v>86</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I50" s="4">
         <v>2000000000</v>
@@ -18464,21 +18471,21 @@
       </c>
       <c r="R50" s="3"/>
       <c r="S50" s="7" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>719</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>721</v>
       </c>
       <c r="E51" s="3" t="s">
         <v>68</v>
@@ -18490,7 +18497,7 @@
         <v>86</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I51" s="4">
         <v>5335769261</v>
@@ -18517,21 +18524,21 @@
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="7" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="52" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>722</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>724</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>68</v>
@@ -18543,7 +18550,7 @@
         <v>86</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I52" s="4">
         <v>4940449374</v>
@@ -18572,21 +18579,21 @@
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="7" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>725</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>727</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>68</v>
@@ -18598,7 +18605,7 @@
         <v>57</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I53" s="4">
         <v>1999924866</v>
@@ -18627,21 +18634,21 @@
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="7" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>728</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>730</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>68</v>
@@ -18653,7 +18660,7 @@
         <v>86</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I54" s="4">
         <v>3591118773</v>
@@ -18682,21 +18689,21 @@
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="7" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>731</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>733</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>68</v>
@@ -18708,7 +18715,7 @@
         <v>57</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I55" s="4">
         <v>2000000000</v>
@@ -18737,21 +18744,21 @@
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="7" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>734</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>736</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>68</v>
@@ -18763,7 +18770,7 @@
         <v>86</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I56" s="4">
         <v>1999112638.9200001</v>
@@ -18792,21 +18799,21 @@
       </c>
       <c r="R56" s="3"/>
       <c r="S56" s="7" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="57" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>738</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>740</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>68</v>
@@ -18818,7 +18825,7 @@
         <v>86</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I57" s="4">
         <v>7500000000</v>
@@ -18847,21 +18854,21 @@
       </c>
       <c r="R57" s="3"/>
       <c r="S57" s="7" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="58" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>741</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>743</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>68</v>
@@ -18873,7 +18880,7 @@
         <v>57</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I58" s="4">
         <v>1999803848</v>
@@ -18902,21 +18909,21 @@
       </c>
       <c r="R58" s="3"/>
       <c r="S58" s="7" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="59" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>743</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>744</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>746</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>68</v>
@@ -18928,7 +18935,7 @@
         <v>86</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="I59" s="4">
         <v>1738785560</v>
@@ -18957,21 +18964,21 @@
       </c>
       <c r="R59" s="3"/>
       <c r="S59" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="60" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>747</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>749</v>
       </c>
       <c r="E60" s="3" t="s">
         <v>68</v>
@@ -18983,7 +18990,7 @@
         <v>57</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I60" s="4">
         <v>1999000000</v>
@@ -19012,21 +19019,21 @@
       </c>
       <c r="R60" s="3"/>
       <c r="S60" s="7" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>751</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>753</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>68</v>
@@ -19038,7 +19045,7 @@
         <v>86</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I61" s="4">
         <v>1775630700</v>
@@ -19067,21 +19074,21 @@
       </c>
       <c r="R61" s="3"/>
       <c r="S61" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>754</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>756</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>68</v>
@@ -19093,7 +19100,7 @@
         <v>86</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I62" s="4">
         <v>750000000</v>
@@ -19122,21 +19129,21 @@
       </c>
       <c r="R62" s="3"/>
       <c r="S62" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="63" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>758</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>760</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>68</v>
@@ -19148,7 +19155,7 @@
         <v>86</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I63" s="4">
         <v>2828005287</v>
@@ -19177,33 +19184,33 @@
       </c>
       <c r="R63" s="3"/>
       <c r="S63" s="7" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="64" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>761</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>763</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I64" s="4">
         <v>69047758069</v>
@@ -19232,21 +19239,21 @@
       </c>
       <c r="R64" s="3"/>
       <c r="S64" s="7" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="65" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>763</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>765</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>767</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>68</v>
@@ -19258,7 +19265,7 @@
         <v>86</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I65" s="4">
         <v>17635937500</v>
@@ -19287,21 +19294,21 @@
       </c>
       <c r="R65" s="3"/>
       <c r="S65" s="7" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>768</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>770</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>68</v>
@@ -19313,7 +19320,7 @@
         <v>86</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I66" s="4">
         <v>1309600000</v>
@@ -19342,21 +19349,21 @@
       </c>
       <c r="R66" s="3"/>
       <c r="S66" s="7" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="67" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>771</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>773</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>68</v>
@@ -19368,7 +19375,7 @@
         <v>86</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I67" s="4">
         <v>2750000000</v>
@@ -19397,21 +19404,21 @@
       </c>
       <c r="R67" s="3"/>
       <c r="S67" s="7" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="68" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>774</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>776</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>68</v>
@@ -19423,7 +19430,7 @@
         <v>86</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I68" s="4">
         <v>1500000000</v>
@@ -19452,21 +19459,21 @@
       </c>
       <c r="R68" s="3"/>
       <c r="S68" s="7" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>777</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>779</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>68</v>
@@ -19478,7 +19485,7 @@
         <v>86</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I69" s="4">
         <v>1411798728</v>
@@ -19507,21 +19514,21 @@
       </c>
       <c r="R69" s="3"/>
       <c r="S69" s="7" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>781</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>783</v>
       </c>
       <c r="E70" s="3" t="s">
         <v>68</v>
@@ -19533,7 +19540,7 @@
         <v>86</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I70" s="4">
         <v>1999997728</v>
@@ -19562,21 +19569,21 @@
       </c>
       <c r="R70" s="3"/>
       <c r="S70" s="7" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="71" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>784</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>786</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>68</v>
@@ -19588,7 +19595,7 @@
         <v>86</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I71" s="4">
         <v>1999667231.96</v>
@@ -19617,21 +19624,21 @@
       </c>
       <c r="R71" s="3"/>
       <c r="S71" s="7" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="72" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>787</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>789</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>68</v>
@@ -19643,7 +19650,7 @@
         <v>209</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="I72" s="4">
         <v>2000000000</v>
@@ -19672,21 +19679,21 @@
       </c>
       <c r="R72" s="3"/>
       <c r="S72" s="7" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>792</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>793</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>68</v>
@@ -19698,7 +19705,7 @@
         <v>86</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I73" s="4">
         <v>1953855779</v>
@@ -19727,21 +19734,21 @@
       </c>
       <c r="R73" s="3"/>
       <c r="S73" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="74" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>794</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>795</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>796</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>68</v>
@@ -19753,7 +19760,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I74" s="4">
         <v>4351936180</v>
@@ -19782,21 +19789,21 @@
       </c>
       <c r="R74" s="3"/>
       <c r="S74" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="75" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>799</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>68</v>
@@ -19808,7 +19815,7 @@
         <v>57</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I75" s="4">
         <v>19906880779</v>
@@ -19837,21 +19844,21 @@
       </c>
       <c r="R75" s="3"/>
       <c r="S75" s="7" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="76" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>800</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>801</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>802</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>258</v>
@@ -19863,7 +19870,7 @@
         <v>57</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I76" s="4">
         <v>3981132848.27</v>
@@ -19892,31 +19899,31 @@
       </c>
       <c r="R76" s="3"/>
       <c r="S76" s="7" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="77" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>803</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>805</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>341</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I77" s="4">
         <v>2407058486</v>
@@ -19941,33 +19948,33 @@
       </c>
       <c r="R77" s="3"/>
       <c r="S77" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="78" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>807</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>809</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I78" s="4">
         <v>45601872749</v>
@@ -19996,21 +20003,21 @@
       </c>
       <c r="R78" s="3"/>
       <c r="S78" s="7" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>811</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>812</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>814</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>94</v>
@@ -20022,7 +20029,7 @@
         <v>57</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I79" s="4">
         <v>2489078661</v>
@@ -20051,21 +20058,21 @@
       </c>
       <c r="R79" s="3"/>
       <c r="S79" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>816</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>818</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>94</v>
@@ -20077,7 +20084,7 @@
         <v>86</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I80" s="4">
         <v>18036167387.900002</v>
@@ -20104,21 +20111,21 @@
       </c>
       <c r="R80" s="3"/>
       <c r="S80" s="7" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>819</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>820</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>821</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>94</v>
@@ -20130,7 +20137,7 @@
         <v>86</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I81" s="4">
         <v>41816156185</v>
@@ -20159,21 +20166,21 @@
       </c>
       <c r="R81" s="3"/>
       <c r="S81" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="82" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>824</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>68</v>
@@ -20185,7 +20192,7 @@
         <v>86</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I82" s="4">
         <v>9606506835</v>
@@ -20214,21 +20221,21 @@
       </c>
       <c r="R82" s="3"/>
       <c r="S82" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>826</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>827</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>828</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>68</v>
@@ -20240,7 +20247,7 @@
         <v>57</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I83" s="4">
         <v>500000000</v>
@@ -20269,21 +20276,21 @@
       </c>
       <c r="R83" s="3"/>
       <c r="S83" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>830</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>832</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>68</v>
@@ -20295,7 +20302,7 @@
         <v>86</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I84" s="4">
         <v>4299593384</v>
@@ -20324,21 +20331,21 @@
       </c>
       <c r="R84" s="3"/>
       <c r="S84" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="85" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>834</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>835</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>836</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>200</v>
@@ -20350,7 +20357,7 @@
         <v>57</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="I85" s="4">
         <v>29623316906.279999</v>
@@ -20379,21 +20386,21 @@
       </c>
       <c r="R85" s="3"/>
       <c r="S85" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="86" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>838</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>839</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>840</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>94</v>
@@ -20405,7 +20412,7 @@
         <v>86</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I86" s="4">
         <v>30461715692</v>
@@ -20434,21 +20441,21 @@
       </c>
       <c r="R86" s="3"/>
       <c r="S86" s="7" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>842</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>843</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>844</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>68</v>
@@ -20460,7 +20467,7 @@
         <v>86</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I87" s="4">
         <v>17454000000</v>
@@ -20489,21 +20496,21 @@
       </c>
       <c r="R87" s="3"/>
       <c r="S87" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="88" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>846</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>847</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>848</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>68</v>
@@ -20515,7 +20522,7 @@
         <v>86</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I88" s="4">
         <v>8419333809</v>
@@ -20544,33 +20551,33 @@
       </c>
       <c r="R88" s="3"/>
       <c r="S88" s="7" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>850</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>851</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>852</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I89" s="4">
         <v>94461519789</v>
@@ -20599,33 +20606,33 @@
       </c>
       <c r="R89" s="3"/>
       <c r="S89" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>854</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>856</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>68</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I90" s="4">
         <v>3362968761</v>
@@ -20654,21 +20661,21 @@
       </c>
       <c r="R90" s="3"/>
       <c r="S90" s="7" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>858</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>860</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>68</v>
@@ -20680,7 +20687,7 @@
         <v>86</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I91" s="4">
         <v>23600000000</v>
@@ -20709,21 +20716,21 @@
       </c>
       <c r="R91" s="3"/>
       <c r="S91" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>861</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>863</v>
       </c>
       <c r="E92" s="3" t="s">
         <v>68</v>
@@ -20735,7 +20742,7 @@
         <v>86</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I92" s="4">
         <v>30000000000</v>
@@ -20764,18 +20771,18 @@
       </c>
       <c r="R92" s="3"/>
       <c r="S92" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
@@ -20788,7 +20795,7 @@
         <v>86</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I93" s="4">
         <v>30000000000</v>
@@ -20817,18 +20824,18 @@
       </c>
       <c r="R93" s="3"/>
       <c r="S93" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>866</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>868</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
@@ -20841,7 +20848,7 @@
         <v>86</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I94" s="4">
         <v>172253454</v>
@@ -20870,21 +20877,21 @@
       </c>
       <c r="R94" s="3"/>
       <c r="S94" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>869</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>871</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>872</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>214</v>
@@ -20896,7 +20903,7 @@
         <v>86</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="I95" s="4">
         <v>511865531</v>
@@ -20925,18 +20932,18 @@
       </c>
       <c r="R95" s="3"/>
       <c r="S95" s="7" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C96" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>875</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
@@ -20949,7 +20956,7 @@
         <v>341</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I96" s="4">
         <v>386045990.94</v>
@@ -20976,21 +20983,21 @@
       </c>
       <c r="R96" s="3"/>
       <c r="S96" s="7" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="C97" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>877</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>879</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>94</v>
@@ -21002,7 +21009,7 @@
         <v>86</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I97" s="4">
         <v>59900815918</v>
@@ -21031,33 +21038,33 @@
       </c>
       <c r="R97" s="3"/>
       <c r="S97" s="7" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="98" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>882</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>355</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G98" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="I98" s="4">
         <v>28121067144</v>
@@ -21086,21 +21093,21 @@
       </c>
       <c r="R98" s="3"/>
       <c r="S98" s="7" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>884</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>886</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>68</v>
@@ -21112,7 +21119,7 @@
         <v>209</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I99" s="4">
         <v>1989520159</v>
@@ -21139,21 +21146,21 @@
       </c>
       <c r="R99" s="3"/>
       <c r="S99" s="7" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="100" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="C100" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>888</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>890</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>68</v>
@@ -21165,7 +21172,7 @@
         <v>209</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I100" s="4">
         <v>4869404585</v>
@@ -21194,33 +21201,33 @@
       </c>
       <c r="R100" s="3"/>
       <c r="S100" s="7" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="101" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>893</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I101" s="4">
         <v>2644584337.2600002</v>
@@ -21249,33 +21256,33 @@
       </c>
       <c r="R101" s="3"/>
       <c r="S101" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="102" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>895</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>897</v>
       </c>
       <c r="E102" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="G102" s="3" t="s">
         <v>209</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I102" s="4">
         <v>6578630543.6700001</v>
@@ -21304,21 +21311,21 @@
       </c>
       <c r="R102" s="3"/>
       <c r="S102" s="7" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>897</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>899</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="C103" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>901</v>
       </c>
       <c r="E103" s="3" t="s">
         <v>94</v>
@@ -21330,7 +21337,7 @@
         <v>209</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="I103" s="4">
         <v>6853127845.6300001</v>
@@ -21359,31 +21366,31 @@
       </c>
       <c r="R103" s="3"/>
       <c r="S103" s="7" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
         <v>94</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I104" s="4">
         <v>36139210439</v>
@@ -21410,7 +21417,7 @@
       </c>
       <c r="R104" s="3"/>
       <c r="S104" s="7" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
@@ -21425,12 +21432,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -21574,7 +21575,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -21583,16 +21584,13 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA898CCD-AE0E-4187-8A1B-FE0621426781}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21610,10 +21608,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95B9A2D5-57A1-450D-BE5F-ECB3662998D9}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E4931FA-B607-44C2-B58E-F809161D3F88}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ListadoMunicipios" sheetId="5" r:id="rId1"/>
@@ -3396,7 +3396,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3797,7 +3797,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3926,13 +3926,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -3944,6 +3937,13 @@
         </top>
         <bottom style="thin">
           <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -3981,52 +3981,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -4181,13 +4135,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4219,6 +4166,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4247,6 +4201,52 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4261,14 +4261,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" headerRowBorderDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="21" dataDxfId="19" headerRowBorderDxfId="20" tableBorderDxfId="18" totalsRowBorderDxfId="17">
   <autoFilter ref="A1:E26" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -4277,11 +4277,9 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AX59" totalsRowShown="0">
   <autoFilter ref="A2:AX59" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="0">
+    <filterColumn colId="1">
       <filters>
-        <filter val="2,023E+12"/>
-        <filter val="2,024E+12"/>
-        <filter val="2,025E+12"/>
+        <filter val="Desarrollo Económico"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -4332,19 +4330,19 @@
     <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="15">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="25">
       <calculatedColumnFormula>IFERROR(IF(AND(ISNUMBER($AC3),ISNUMBER($AE3),$AC3&lt;$AE3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="14"/>
-    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="13"/>
-    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="12"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="24"/>
+    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="23"/>
+    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}" name="Tabla5" displayName="Tabla5" ref="A1:C176" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}" name="Tabla5" displayName="Tabla5" ref="A1:C176" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:C176" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{99E997E3-2CEC-4F3E-8738-BC5E0E5CF370}" name="BPIN" dataDxfId="7"/>
@@ -4722,14 +4720,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{146B246E-1041-42FC-9276-EE9890517FFA}">
   <sheetPr codeName="Hoja5"/>
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="46.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4743,7 +4741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="22">
         <v>1</v>
       </c>
@@ -4757,7 +4755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="22">
         <v>2</v>
       </c>
@@ -4771,7 +4769,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="22">
         <v>3</v>
       </c>
@@ -4785,7 +4783,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="22">
         <v>4</v>
       </c>
@@ -4799,7 +4797,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
         <v>5</v>
       </c>
@@ -4813,7 +4811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="22">
         <v>6</v>
       </c>
@@ -4827,7 +4825,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="22">
         <v>7</v>
       </c>
@@ -4841,7 +4839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="22">
         <v>8</v>
       </c>
@@ -4855,7 +4853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="22">
         <v>9</v>
       </c>
@@ -4869,7 +4867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="22">
         <v>10</v>
       </c>
@@ -4883,7 +4881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="22">
         <v>11</v>
       </c>
@@ -4897,7 +4895,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="22">
         <v>12</v>
       </c>
@@ -4911,7 +4909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="22">
         <v>13</v>
       </c>
@@ -4925,7 +4923,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="22">
         <v>14</v>
       </c>
@@ -4939,7 +4937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="22">
         <v>15</v>
       </c>
@@ -4953,7 +4951,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="22">
         <v>16</v>
       </c>
@@ -4967,7 +4965,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="22">
         <v>17</v>
       </c>
@@ -4981,7 +4979,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="22">
         <v>18</v>
       </c>
@@ -4995,7 +4993,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="22">
         <v>19</v>
       </c>
@@ -5009,7 +5007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="22">
         <v>20</v>
       </c>
@@ -5023,7 +5021,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="22">
         <v>21</v>
       </c>
@@ -5037,7 +5035,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="22">
         <v>22</v>
       </c>
@@ -5051,7 +5049,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="22">
         <v>23</v>
       </c>
@@ -5065,7 +5063,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="22">
         <v>24</v>
       </c>
@@ -5079,7 +5077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="22">
         <v>25</v>
       </c>
@@ -5093,7 +5091,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="22">
         <v>26</v>
       </c>
@@ -5107,7 +5105,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B28" s="22" t="s">
         <v>38</v>
       </c>
@@ -5127,15 +5125,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D40494E-F5FA-45B0-8046-A8A35D593322}">
   <sheetPr codeName="Hoja4"/>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" customWidth="1"/>
-    <col min="3" max="4" width="20.140625" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" customWidth="1"/>
+    <col min="1" max="1" width="28.88671875" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" customWidth="1"/>
+    <col min="3" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>40</v>
       </c>
@@ -5152,7 +5150,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>45</v>
       </c>
@@ -5169,7 +5167,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
         <v>45</v>
       </c>
@@ -5186,7 +5184,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45">
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>52</v>
       </c>
@@ -5201,7 +5199,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>55</v>
       </c>
@@ -5216,7 +5214,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>57</v>
       </c>
@@ -5231,7 +5229,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>57</v>
       </c>
@@ -5246,7 +5244,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30">
+    <row r="8" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>57</v>
       </c>
@@ -5261,7 +5259,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="60">
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>61</v>
       </c>
@@ -5278,7 +5276,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30">
+    <row r="10" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>45</v>
       </c>
@@ -5295,7 +5293,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30">
+    <row r="11" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>57</v>
       </c>
@@ -5312,7 +5310,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30">
+    <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>57</v>
       </c>
@@ -5329,7 +5327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30">
+    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>57</v>
       </c>
@@ -5346,7 +5344,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="30">
+    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>57</v>
       </c>
@@ -5363,7 +5361,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30">
+    <row r="15" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>57</v>
       </c>
@@ -5380,7 +5378,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="45">
+    <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
         <v>57</v>
       </c>
@@ -5397,7 +5395,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="30">
+    <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>57</v>
       </c>
@@ -5414,7 +5412,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="30">
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>57</v>
       </c>
@@ -5429,7 +5427,7 @@
       </c>
       <c r="E18" s="17"/>
     </row>
-    <row r="19" spans="1:5" ht="45">
+    <row r="19" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>57</v>
       </c>
@@ -5444,7 +5442,7 @@
       </c>
       <c r="E19" s="17"/>
     </row>
-    <row r="20" spans="1:5" ht="30">
+    <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>57</v>
       </c>
@@ -5459,7 +5457,7 @@
       </c>
       <c r="E20" s="17"/>
     </row>
-    <row r="21" spans="1:5" ht="30">
+    <row r="21" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>57</v>
       </c>
@@ -5474,7 +5472,7 @@
       </c>
       <c r="E21" s="17"/>
     </row>
-    <row r="22" spans="1:5" ht="45">
+    <row r="22" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>57</v>
       </c>
@@ -5489,7 +5487,7 @@
       </c>
       <c r="E22" s="17"/>
     </row>
-    <row r="23" spans="1:5" ht="45">
+    <row r="23" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>57</v>
       </c>
@@ -5504,7 +5502,7 @@
       </c>
       <c r="E23" s="17"/>
     </row>
-    <row r="24" spans="1:5" ht="45">
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="15"/>
       <c r="B24" s="16" t="s">
         <v>83</v>
@@ -5513,7 +5511,7 @@
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
     </row>
-    <row r="25" spans="1:5" ht="45">
+    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="15"/>
       <c r="B25" s="16" t="s">
         <v>84</v>
@@ -5522,7 +5520,7 @@
       <c r="D25" s="17"/>
       <c r="E25" s="17"/>
     </row>
-    <row r="26" spans="1:5" ht="45">
+    <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="15"/>
       <c r="B26" s="16" t="s">
         <v>85</v>
@@ -5543,25 +5541,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
   <dimension ref="A1:AX59"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.7109375" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="42.140625" customWidth="1"/>
-    <col min="7" max="7" width="29.42578125" customWidth="1"/>
-    <col min="8" max="39" width="25.7109375" customWidth="1"/>
-    <col min="40" max="40" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="41" max="45" width="25.7109375" customWidth="1"/>
-    <col min="46" max="46" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="47" max="47" width="25.7109375" customWidth="1"/>
-    <col min="48" max="48" width="55.28515625" customWidth="1"/>
-    <col min="49" max="49" width="25.28515625" customWidth="1"/>
-    <col min="50" max="50" width="25.7109375" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="43.6640625" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="42.109375" customWidth="1"/>
+    <col min="7" max="7" width="29.44140625" customWidth="1"/>
+    <col min="8" max="39" width="25.6640625" customWidth="1"/>
+    <col min="40" max="40" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="41" max="45" width="25.6640625" customWidth="1"/>
+    <col min="46" max="46" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="25.6640625" customWidth="1"/>
+    <col min="48" max="48" width="55.33203125" customWidth="1"/>
+    <col min="49" max="49" width="25.33203125" customWidth="1"/>
+    <col min="50" max="50" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="40.15" customHeight="1">
+    <row r="1" spans="1:50" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>86</v>
       </c>
@@ -5617,7 +5615,7 @@
       <c r="AU1" s="33"/>
       <c r="AV1" s="33"/>
     </row>
-    <row r="2" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="2" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -5769,7 +5767,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:50" ht="166.15" hidden="1" customHeight="1">
+    <row r="3" spans="1:50" ht="166.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>139</v>
       </c>
@@ -5916,7 +5914,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="4" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>153</v>
       </c>
@@ -6053,7 +6051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="5" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>163</v>
       </c>
@@ -6200,7 +6198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:50" ht="156" hidden="1" customHeight="1">
+    <row r="6" spans="1:50" ht="156" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>171</v>
       </c>
@@ -6347,7 +6345,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="7" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>180</v>
       </c>
@@ -6494,7 +6492,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="8" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="8" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>193</v>
       </c>
@@ -6641,7 +6639,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="9" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>200</v>
       </c>
@@ -6792,7 +6790,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="10" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>208</v>
       </c>
@@ -6939,7 +6937,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="11" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>217</v>
       </c>
@@ -7086,7 +7084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="12" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>222</v>
       </c>
@@ -7233,7 +7231,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="13" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>230</v>
       </c>
@@ -7382,7 +7380,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="14" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>241</v>
       </c>
@@ -7529,7 +7527,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="15" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>249</v>
       </c>
@@ -7678,7 +7676,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="16" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>255</v>
       </c>
@@ -7825,7 +7823,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="17" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="17" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>262</v>
       </c>
@@ -7974,7 +7972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="18" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>270</v>
       </c>
@@ -8123,7 +8121,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:50" ht="142.5" hidden="1" customHeight="1">
+    <row r="19" spans="1:50" ht="142.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>277</v>
       </c>
@@ -8272,7 +8270,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="20" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="20" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>283</v>
       </c>
@@ -8419,7 +8417,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:50" ht="115.5" hidden="1" customHeight="1">
+    <row r="21" spans="1:50" ht="115.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>288</v>
       </c>
@@ -8568,7 +8566,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="22" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>297</v>
       </c>
@@ -8717,7 +8715,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="23" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>305</v>
       </c>
@@ -8858,7 +8856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="24" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>311</v>
       </c>
@@ -8999,7 +8997,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="25" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>319</v>
       </c>
@@ -9138,7 +9136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="26" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>324</v>
       </c>
@@ -9287,7 +9285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="27" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>332</v>
       </c>
@@ -9434,7 +9432,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="28" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="28" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>338</v>
       </c>
@@ -9579,7 +9577,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="29" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="29" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>345</v>
       </c>
@@ -9726,7 +9724,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="30" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>352</v>
       </c>
@@ -9867,7 +9865,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="31" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>356</v>
       </c>
@@ -10012,7 +10010,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="32" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>362</v>
       </c>
@@ -10161,7 +10159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="33" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>370</v>
       </c>
@@ -10310,7 +10308,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="34" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="34" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>380</v>
       </c>
@@ -10455,7 +10453,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="35" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="35" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>387</v>
       </c>
@@ -10592,7 +10590,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="36" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>392</v>
       </c>
@@ -10737,7 +10735,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="37" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="37" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>400</v>
       </c>
@@ -10821,7 +10819,9 @@
       <c r="AC37" s="5">
         <v>45900</v>
       </c>
-      <c r="AD37" s="5"/>
+      <c r="AD37" s="5">
+        <v>45968</v>
+      </c>
       <c r="AE37" s="5">
         <v>46157</v>
       </c>
@@ -10882,7 +10882,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="38" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="38" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>2023002700171</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="39" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>414</v>
       </c>
@@ -11178,7 +11178,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="40" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>421</v>
       </c>
@@ -11327,7 +11327,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="41" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="41" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>2024002700066</v>
       </c>
@@ -11476,7 +11476,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="42" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>435</v>
       </c>
@@ -11623,7 +11623,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="43" spans="1:50" ht="252" hidden="1" customHeight="1">
+    <row r="43" spans="1:50" ht="252" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>442</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="44" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="44" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>2024002700176</v>
       </c>
@@ -11909,7 +11909,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="45" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>456</v>
       </c>
@@ -12056,7 +12056,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="46" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>466</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="47" spans="1:50" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>2024002700184</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="48" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>482</v>
       </c>
@@ -12469,7 +12469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="49" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>488</v>
       </c>
@@ -12596,7 +12596,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="50" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="50" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>494</v>
       </c>
@@ -12743,7 +12743,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="51" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>501</v>
       </c>
@@ -12890,7 +12890,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="52" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="52" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>510</v>
       </c>
@@ -13039,7 +13039,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="53" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="53" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>514</v>
       </c>
@@ -13180,7 +13180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="54" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>521</v>
       </c>
@@ -13313,7 +13313,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="55" spans="1:50" ht="70.150000000000006" customHeight="1">
+    <row r="55" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3">
         <v>2025002700023</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="56" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="56" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>535</v>
       </c>
@@ -13603,7 +13603,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="57" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="57" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>544</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="58" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="58" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>552</v>
       </c>
@@ -13873,7 +13873,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:50" ht="70.150000000000006" hidden="1" customHeight="1">
+    <row r="59" spans="1:50" ht="70.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>558</v>
       </c>
@@ -14018,14 +14018,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22E2D74-A76C-4FC9-B876-7060D9042D53}">
   <dimension ref="A1:C176"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>89</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="25.5">
+    <row r="2" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>139</v>
       </c>
@@ -14047,7 +14047,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>153</v>
       </c>
@@ -14058,7 +14058,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="25.5">
+    <row r="4" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="24" t="s">
         <v>163</v>
       </c>
@@ -14069,7 +14069,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="25.5">
+    <row r="5" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
         <v>171</v>
       </c>
@@ -14080,7 +14080,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="25.5">
+    <row r="6" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
         <v>180</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
         <v>193</v>
       </c>
@@ -14102,7 +14102,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="25.5">
+    <row r="8" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
         <v>200</v>
       </c>
@@ -14113,7 +14113,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="25.5">
+    <row r="9" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="24" t="s">
         <v>208</v>
       </c>
@@ -14124,7 +14124,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="25.5">
+    <row r="10" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="24" t="s">
         <v>217</v>
       </c>
@@ -14135,7 +14135,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="25.5">
+    <row r="11" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>222</v>
       </c>
@@ -14146,7 +14146,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="25.5">
+    <row r="12" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="24" t="s">
         <v>230</v>
       </c>
@@ -14157,7 +14157,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="25.5">
+    <row r="13" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
         <v>241</v>
       </c>
@@ -14168,7 +14168,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="25.5">
+    <row r="14" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="24" t="s">
         <v>249</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="25.5">
+    <row r="15" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
         <v>255</v>
       </c>
@@ -14190,7 +14190,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="25.5">
+    <row r="16" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="24" t="s">
         <v>262</v>
       </c>
@@ -14201,7 +14201,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="25.5">
+    <row r="17" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
         <v>270</v>
       </c>
@@ -14212,7 +14212,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="25.5">
+    <row r="18" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A18" s="24" t="s">
         <v>277</v>
       </c>
@@ -14223,7 +14223,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="25.5">
+    <row r="19" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
         <v>283</v>
       </c>
@@ -14234,7 +14234,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="25.5">
+    <row r="20" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
         <v>288</v>
       </c>
@@ -14245,7 +14245,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="25.5">
+    <row r="21" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
         <v>297</v>
       </c>
@@ -14256,7 +14256,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="25.5">
+    <row r="22" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
         <v>305</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="25.5">
+    <row r="23" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
         <v>311</v>
       </c>
@@ -14278,7 +14278,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="25.5">
+    <row r="24" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A24" s="24" t="s">
         <v>319</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="25.5">
+    <row r="25" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>324</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="25.5">
+    <row r="26" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
         <v>332</v>
       </c>
@@ -14311,7 +14311,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="25.5">
+    <row r="27" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A27" s="24" t="s">
         <v>338</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="25.5">
+    <row r="28" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
         <v>345</v>
       </c>
@@ -14333,7 +14333,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="25.5">
+    <row r="29" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A29" s="24" t="s">
         <v>352</v>
       </c>
@@ -14344,7 +14344,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="25.5">
+    <row r="30" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
         <v>356</v>
       </c>
@@ -14355,7 +14355,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="25.5">
+    <row r="31" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
         <v>362</v>
       </c>
@@ -14366,7 +14366,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="25.5">
+    <row r="32" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A32" s="24" t="s">
         <v>370</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="25.5">
+    <row r="33" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A33" s="24" t="s">
         <v>380</v>
       </c>
@@ -14388,7 +14388,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A34" s="24" t="s">
         <v>387</v>
       </c>
@@ -14399,7 +14399,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="25.5">
+    <row r="35" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="s">
         <v>392</v>
       </c>
@@ -14410,7 +14410,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="25.5">
+    <row r="36" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A36" s="24" t="s">
         <v>400</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="25.5">
+    <row r="37" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
         <v>571</v>
       </c>
@@ -14432,7 +14432,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="38" spans="1:3">
+    <row r="38" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A38" s="24" t="s">
         <v>414</v>
       </c>
@@ -14443,7 +14443,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="25.5">
+    <row r="39" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
         <v>421</v>
       </c>
@@ -14454,7 +14454,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="25.5">
+    <row r="40" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A40" s="24" t="s">
         <v>572</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="25.5">
+    <row r="41" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
         <v>435</v>
       </c>
@@ -14476,7 +14476,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="25.5">
+    <row r="42" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A42" s="24" t="s">
         <v>442</v>
       </c>
@@ -14487,7 +14487,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="25.5">
+    <row r="43" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
         <v>573</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="25.5">
+    <row r="44" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
         <v>456</v>
       </c>
@@ -14509,7 +14509,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="25.5">
+    <row r="45" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
         <v>466</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="25.5">
+    <row r="46" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A46" s="24" t="s">
         <v>574</v>
       </c>
@@ -14531,7 +14531,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="25" t="s">
         <v>482</v>
       </c>
@@ -14542,7 +14542,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="25.5">
+    <row r="48" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A48" s="24" t="s">
         <v>488</v>
       </c>
@@ -14553,7 +14553,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="25.5">
+    <row r="49" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A49" s="24" t="s">
         <v>494</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="25.5">
+    <row r="50" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="s">
         <v>501</v>
       </c>
@@ -14575,7 +14575,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="25.5">
+    <row r="51" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="s">
         <v>510</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="25.5">
+    <row r="52" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A52" s="24" t="s">
         <v>514</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="25.5">
+    <row r="53" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
         <v>521</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="25.5">
+    <row r="54" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A54" s="24" t="s">
         <v>575</v>
       </c>
@@ -14619,7 +14619,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="25.5">
+    <row r="55" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A55" s="24" t="s">
         <v>535</v>
       </c>
@@ -14630,7 +14630,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="25.5">
+    <row r="56" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="s">
         <v>544</v>
       </c>
@@ -14641,7 +14641,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="25.5">
+    <row r="57" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A57" s="24" t="s">
         <v>552</v>
       </c>
@@ -14652,7 +14652,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="25.5">
+    <row r="58" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A58" s="24" t="s">
         <v>558</v>
       </c>
@@ -14663,7 +14663,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="25.5">
+    <row r="59" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
         <v>576</v>
       </c>
@@ -14674,7 +14674,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="25.5">
+    <row r="60" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A60" s="24" t="s">
         <v>578</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="38.25">
+    <row r="61" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
         <v>579</v>
       </c>
@@ -14696,7 +14696,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="25.5">
+    <row r="62" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A62" s="24" t="s">
         <v>581</v>
       </c>
@@ -14707,7 +14707,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="25.5">
+    <row r="63" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A63" s="24" t="s">
         <v>582</v>
       </c>
@@ -14718,7 +14718,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="38.25">
+    <row r="64" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
         <v>583</v>
       </c>
@@ -14729,7 +14729,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="38.25">
+    <row r="65" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A65" s="24" t="s">
         <v>584</v>
       </c>
@@ -14740,7 +14740,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="38.25">
+    <row r="66" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A66" s="24" t="s">
         <v>585</v>
       </c>
@@ -14751,7 +14751,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="25.5">
+    <row r="67" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
         <v>586</v>
       </c>
@@ -14762,7 +14762,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="38.25">
+    <row r="68" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A68" s="24" t="s">
         <v>587</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="25.5">
+    <row r="69" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A69" s="24" t="s">
         <v>589</v>
       </c>
@@ -14784,7 +14784,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="38.25">
+    <row r="70" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
         <v>590</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="25.5">
+    <row r="71" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="s">
         <v>591</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="38.25">
+    <row r="72" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A72" s="24" t="s">
         <v>592</v>
       </c>
@@ -14817,7 +14817,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="38.25">
+    <row r="73" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="s">
         <v>593</v>
       </c>
@@ -14828,7 +14828,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="25.5">
+    <row r="74" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A74" s="24" t="s">
         <v>594</v>
       </c>
@@ -14839,7 +14839,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="75" spans="1:3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="24" t="s">
         <v>595</v>
       </c>
@@ -14850,7 +14850,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="76" spans="1:3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="24" t="s">
         <v>597</v>
       </c>
@@ -14861,7 +14861,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="77" spans="1:3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>599</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="78" spans="1:3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="24" t="s">
         <v>601</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="79" spans="1:3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="24" t="s">
         <v>603</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="25.5">
+    <row r="80" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A80" s="24" t="s">
         <v>604</v>
       </c>
@@ -14905,7 +14905,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="24" t="s">
         <v>606</v>
       </c>
@@ -14916,7 +14916,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="82" spans="1:3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="24" t="s">
         <v>608</v>
       </c>
@@ -14927,7 +14927,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="51">
+    <row r="83" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A83" s="24" t="s">
         <v>610</v>
       </c>
@@ -14938,7 +14938,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="24" t="s">
         <v>612</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="85" spans="1:3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="24" t="s">
         <v>614</v>
       </c>
@@ -14960,7 +14960,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="25.5">
+    <row r="86" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A86" s="24" t="s">
         <v>616</v>
       </c>
@@ -14971,7 +14971,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="87" spans="1:3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" s="24" t="s">
         <v>618</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="25.5">
+    <row r="88" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A88" s="24" t="s">
         <v>620</v>
       </c>
@@ -14993,7 +14993,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="25.5">
+    <row r="89" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A89" s="24" t="s">
         <v>622</v>
       </c>
@@ -15004,7 +15004,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="25.5">
+    <row r="90" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A90" s="24" t="s">
         <v>624</v>
       </c>
@@ -15015,7 +15015,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="25.5">
+    <row r="91" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A91" s="24" t="s">
         <v>626</v>
       </c>
@@ -15026,7 +15026,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="25.5">
+    <row r="92" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A92" s="24" t="s">
         <v>628</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="25.5">
+    <row r="93" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A93" s="24" t="s">
         <v>630</v>
       </c>
@@ -15048,7 +15048,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="25.5">
+    <row r="94" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A94" s="24" t="s">
         <v>632</v>
       </c>
@@ -15059,7 +15059,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="25.5">
+    <row r="95" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A95" s="24" t="s">
         <v>634</v>
       </c>
@@ -15070,7 +15070,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="25.5">
+    <row r="96" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A96" s="24" t="s">
         <v>636</v>
       </c>
@@ -15081,7 +15081,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="25.5">
+    <row r="97" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A97" s="24" t="s">
         <v>638</v>
       </c>
@@ -15092,7 +15092,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="25.5">
+    <row r="98" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A98" s="24" t="s">
         <v>640</v>
       </c>
@@ -15103,7 +15103,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="25.5">
+    <row r="99" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A99" s="24" t="s">
         <v>642</v>
       </c>
@@ -15114,7 +15114,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="100" spans="1:3">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="24" t="s">
         <v>644</v>
       </c>
@@ -15125,7 +15125,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="101" spans="1:3">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101" s="24" t="s">
         <v>646</v>
       </c>
@@ -15136,7 +15136,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="25.5">
+    <row r="102" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A102" s="24" t="s">
         <v>647</v>
       </c>
@@ -15147,7 +15147,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="103" spans="1:3">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103" s="24" t="s">
         <v>648</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="104" spans="1:3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104" s="24" t="s">
         <v>650</v>
       </c>
@@ -15169,7 +15169,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="105" spans="1:3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" s="24" t="s">
         <v>651</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="106" spans="1:3">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106" s="24" t="s">
         <v>652</v>
       </c>
@@ -15191,7 +15191,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="107" spans="1:3">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107" s="24" t="s">
         <v>653</v>
       </c>
@@ -15202,7 +15202,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="25.5">
+    <row r="108" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A108" s="24" t="s">
         <v>655</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="25.5">
+    <row r="109" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A109" s="24" t="s">
         <v>657</v>
       </c>
@@ -15224,7 +15224,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="110" spans="1:3">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110" s="24" t="s">
         <v>659</v>
       </c>
@@ -15235,7 +15235,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="25.5">
+    <row r="111" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A111" s="24" t="s">
         <v>661</v>
       </c>
@@ -15246,7 +15246,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="38.25">
+    <row r="112" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A112" s="24" t="s">
         <v>663</v>
       </c>
@@ -15257,7 +15257,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="25.5">
+    <row r="113" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A113" s="24" t="s">
         <v>665</v>
       </c>
@@ -15268,7 +15268,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="114" spans="1:3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114" s="24" t="s">
         <v>666</v>
       </c>
@@ -15279,7 +15279,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="25.5">
+    <row r="115" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A115" s="24" t="s">
         <v>667</v>
       </c>
@@ -15290,7 +15290,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="25.5">
+    <row r="116" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A116" s="24" t="s">
         <v>668</v>
       </c>
@@ -15301,7 +15301,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="25.5">
+    <row r="117" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A117" s="24" t="s">
         <v>669</v>
       </c>
@@ -15312,7 +15312,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="38.25">
+    <row r="118" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A118" s="24" t="s">
         <v>671</v>
       </c>
@@ -15323,7 +15323,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="25.5">
+    <row r="119" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A119" s="24" t="s">
         <v>673</v>
       </c>
@@ -15334,7 +15334,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="25.5">
+    <row r="120" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A120" s="24" t="s">
         <v>674</v>
       </c>
@@ -15345,7 +15345,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="25.5">
+    <row r="121" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A121" s="24" t="s">
         <v>676</v>
       </c>
@@ -15356,7 +15356,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="25.5">
+    <row r="122" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A122" s="24" t="s">
         <v>677</v>
       </c>
@@ -15367,7 +15367,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="25.5">
+    <row r="123" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A123" s="24" t="s">
         <v>678</v>
       </c>
@@ -15378,7 +15378,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="25.5">
+    <row r="124" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A124" s="24" t="s">
         <v>680</v>
       </c>
@@ -15389,7 +15389,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="125" spans="1:3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125" s="24" t="s">
         <v>681</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="25.5">
+    <row r="126" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A126" s="24" t="s">
         <v>682</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="127" spans="1:3">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A127" s="24" t="s">
         <v>683</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="25.5">
+    <row r="128" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A128" s="24" t="s">
         <v>684</v>
       </c>
@@ -15433,7 +15433,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="25.5">
+    <row r="129" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A129" s="24" t="s">
         <v>685</v>
       </c>
@@ -15444,7 +15444,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="130" spans="1:3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130" s="24" t="s">
         <v>687</v>
       </c>
@@ -15455,7 +15455,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="25.5">
+    <row r="131" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A131" s="24" t="s">
         <v>688</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A132" s="24" t="s">
         <v>689</v>
       </c>
@@ -15477,7 +15477,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="25.5">
+    <row r="133" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A133" s="24" t="s">
         <v>690</v>
       </c>
@@ -15488,7 +15488,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="25.5">
+    <row r="134" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A134" s="24" t="s">
         <v>692</v>
       </c>
@@ -15499,7 +15499,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="25.5">
+    <row r="135" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A135" s="24" t="s">
         <v>693</v>
       </c>
@@ -15510,7 +15510,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="25.5">
+    <row r="136" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A136" s="24" t="s">
         <v>695</v>
       </c>
@@ -15521,7 +15521,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="25.5">
+    <row r="137" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A137" s="24" t="s">
         <v>696</v>
       </c>
@@ -15532,7 +15532,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="25.5">
+    <row r="138" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A138" s="24" t="s">
         <v>697</v>
       </c>
@@ -15543,7 +15543,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="25.5">
+    <row r="139" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A139" s="24" t="s">
         <v>698</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="25.5">
+    <row r="140" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A140" s="24" t="s">
         <v>699</v>
       </c>
@@ -15565,7 +15565,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="25.5">
+    <row r="141" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A141" s="24" t="s">
         <v>700</v>
       </c>
@@ -15576,7 +15576,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="25.5">
+    <row r="142" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A142" s="24" t="s">
         <v>701</v>
       </c>
@@ -15587,7 +15587,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="25.5">
+    <row r="143" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A143" s="24" t="s">
         <v>703</v>
       </c>
@@ -15598,7 +15598,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="144" spans="1:3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144" s="24" t="s">
         <v>704</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="25.5">
+    <row r="145" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A145" s="24" t="s">
         <v>705</v>
       </c>
@@ -15620,7 +15620,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="146" spans="1:3">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A146" s="24" t="s">
         <v>706</v>
       </c>
@@ -15631,7 +15631,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="147" spans="1:3">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A147" s="24" t="s">
         <v>707</v>
       </c>
@@ -15642,7 +15642,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148" s="24" t="s">
         <v>708</v>
       </c>
@@ -15653,7 +15653,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="149" spans="1:3">
+    <row r="149" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A149" s="24" t="s">
         <v>709</v>
       </c>
@@ -15664,7 +15664,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="25.5">
+    <row r="150" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A150" s="24" t="s">
         <v>711</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="151" spans="1:3">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A151" s="24" t="s">
         <v>712</v>
       </c>
@@ -15686,7 +15686,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="25.5">
+    <row r="152" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A152" s="24" t="s">
         <v>714</v>
       </c>
@@ -15697,7 +15697,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="25.5">
+    <row r="153" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A153" s="24" t="s">
         <v>716</v>
       </c>
@@ -15708,7 +15708,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="25.5">
+    <row r="154" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A154" s="24" t="s">
         <v>717</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="25.5">
+    <row r="155" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A155" s="24" t="s">
         <v>718</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="25.5">
+    <row r="156" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A156" s="24" t="s">
         <v>720</v>
       </c>
@@ -15741,7 +15741,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="25.5">
+    <row r="157" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A157" s="24" t="s">
         <v>722</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="25.5">
+    <row r="158" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A158" s="24" t="s">
         <v>724</v>
       </c>
@@ -15763,7 +15763,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="25.5">
+    <row r="159" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A159" s="24" t="s">
         <v>726</v>
       </c>
@@ -15774,7 +15774,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="38.25">
+    <row r="160" spans="1:3" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A160" s="24" t="s">
         <v>728</v>
       </c>
@@ -15785,7 +15785,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="38.25">
+    <row r="161" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A161" s="24" t="s">
         <v>730</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="25.5">
+    <row r="162" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A162" s="24" t="s">
         <v>732</v>
       </c>
@@ -15807,7 +15807,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="25.5">
+    <row r="163" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A163" s="24" t="s">
         <v>733</v>
       </c>
@@ -15818,7 +15818,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="25.5">
+    <row r="164" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A164" s="24" t="s">
         <v>734</v>
       </c>
@@ -15829,7 +15829,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="25.5">
+    <row r="165" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A165" s="24" t="s">
         <v>735</v>
       </c>
@@ -15840,7 +15840,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="51">
+    <row r="166" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A166" s="24" t="s">
         <v>736</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="25.5">
+    <row r="167" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A167" s="24" t="s">
         <v>738</v>
       </c>
@@ -15862,7 +15862,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="168" spans="1:3">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A168" s="24" t="s">
         <v>740</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="38.25">
+    <row r="169" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A169" s="24" t="s">
         <v>742</v>
       </c>
@@ -15884,7 +15884,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="25.5">
+    <row r="170" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A170" s="24" t="s">
         <v>744</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="171" spans="1:3">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A171" s="24" t="s">
         <v>745</v>
       </c>
@@ -15906,7 +15906,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="25.5">
+    <row r="172" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A172" s="24" t="s">
         <v>746</v>
       </c>
@@ -15917,7 +15917,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="173" spans="1:3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173" s="24" t="s">
         <v>748</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="174" spans="1:3">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A174" s="24" t="s">
         <v>749</v>
       </c>
@@ -15939,7 +15939,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="175" spans="1:3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" s="24" t="s">
         <v>750</v>
       </c>
@@ -15950,7 +15950,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="38.25">
+    <row r="176" spans="1:3" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A176" s="30" t="s">
         <v>751</v>
       </c>
@@ -15973,19 +15973,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="A1:AM18"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="25.7109375" customWidth="1"/>
-    <col min="4" max="4" width="34.28515625" customWidth="1"/>
-    <col min="5" max="29" width="25.7109375" customWidth="1"/>
-    <col min="30" max="30" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="31" max="35" width="25.7109375" customWidth="1"/>
-    <col min="36" max="36" width="25.7109375" hidden="1" customWidth="1"/>
-    <col min="37" max="38" width="25.7109375" customWidth="1"/>
-    <col min="39" max="40" width="23.7109375" customWidth="1"/>
+    <col min="1" max="3" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="34.33203125" customWidth="1"/>
+    <col min="5" max="29" width="25.6640625" customWidth="1"/>
+    <col min="30" max="30" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="36" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="25.6640625" customWidth="1"/>
+    <col min="39" max="40" width="23.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="40.15" customHeight="1">
+    <row r="1" spans="1:39" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>86</v>
       </c>
@@ -16031,7 +16031,7 @@
       <c r="AK1" s="33"/>
       <c r="AL1" s="33"/>
     </row>
-    <row r="2" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="2" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="3" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>576</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="4" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>578</v>
       </c>
@@ -16364,7 +16364,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="5" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>579</v>
       </c>
@@ -16477,7 +16477,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="6" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>581</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="7" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>582</v>
       </c>
@@ -16707,7 +16707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="8" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>583</v>
       </c>
@@ -16814,7 +16814,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="9" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>584</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="10" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>585</v>
       </c>
@@ -17040,7 +17040,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="11" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>586</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="12" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>587</v>
       </c>
@@ -17268,7 +17268,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="13" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>589</v>
       </c>
@@ -17379,7 +17379,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="14" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>590</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="15" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>591</v>
       </c>
@@ -17603,7 +17603,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="16" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>592</v>
       </c>
@@ -17712,7 +17712,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="17" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>593</v>
       </c>
@@ -17815,7 +17815,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="70.150000000000006" customHeight="1">
+    <row r="18" spans="1:39" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>594</v>
       </c>
@@ -17933,13 +17933,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja3"/>
   <dimension ref="A1:S104"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="18" width="25.7109375" customWidth="1"/>
-    <col min="19" max="19" width="33.28515625" customWidth="1"/>
+    <col min="1" max="18" width="25.6640625" customWidth="1"/>
+    <col min="19" max="19" width="33.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="40.15" customHeight="1">
+    <row r="1" spans="1:19" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33" t="s">
         <v>86</v>
       </c>
@@ -17961,7 +17961,7 @@
       <c r="Q1" s="33"/>
       <c r="R1" s="33"/>
     </row>
-    <row r="2" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="2" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>89</v>
       </c>
@@ -18020,7 +18020,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="3" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>595</v>
       </c>
@@ -18075,7 +18075,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="4" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>597</v>
       </c>
@@ -18130,7 +18130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="5" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>599</v>
       </c>
@@ -18185,7 +18185,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="6" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>601</v>
       </c>
@@ -18240,7 +18240,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="7" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>603</v>
       </c>
@@ -18295,7 +18295,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="8" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>604</v>
       </c>
@@ -18350,7 +18350,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="9" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>606</v>
       </c>
@@ -18405,7 +18405,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="10" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>608</v>
       </c>
@@ -18460,7 +18460,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="11" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>610</v>
       </c>
@@ -18515,7 +18515,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="12" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>612</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="13" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>614</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="14" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>616</v>
       </c>
@@ -18680,7 +18680,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="15" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>618</v>
       </c>
@@ -18735,7 +18735,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="16" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>620</v>
       </c>
@@ -18790,7 +18790,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="17" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>622</v>
       </c>
@@ -18845,7 +18845,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="18" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>624</v>
       </c>
@@ -18900,7 +18900,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="19" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>626</v>
       </c>
@@ -18955,7 +18955,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="20" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>628</v>
       </c>
@@ -19010,7 +19010,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="21" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>630</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="22" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>632</v>
       </c>
@@ -19120,7 +19120,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="23" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>634</v>
       </c>
@@ -19175,7 +19175,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="24" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>636</v>
       </c>
@@ -19230,7 +19230,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="25" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>638</v>
       </c>
@@ -19285,7 +19285,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="26" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>640</v>
       </c>
@@ -19340,7 +19340,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="27" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>642</v>
       </c>
@@ -19395,7 +19395,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="28" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>644</v>
       </c>
@@ -19450,7 +19450,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="29" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>646</v>
       </c>
@@ -19505,7 +19505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="30" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>647</v>
       </c>
@@ -19560,7 +19560,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="31" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>648</v>
       </c>
@@ -19615,7 +19615,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="32" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>650</v>
       </c>
@@ -19670,7 +19670,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="33" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>651</v>
       </c>
@@ -19725,7 +19725,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="34" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>652</v>
       </c>
@@ -19780,7 +19780,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="35" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>653</v>
       </c>
@@ -19835,7 +19835,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="36" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>655</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="37" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>657</v>
       </c>
@@ -19945,7 +19945,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="38" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>659</v>
       </c>
@@ -19998,7 +19998,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="39" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>661</v>
       </c>
@@ -20053,7 +20053,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="40" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>663</v>
       </c>
@@ -20108,7 +20108,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="41" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>665</v>
       </c>
@@ -20163,7 +20163,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="42" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>666</v>
       </c>
@@ -20218,7 +20218,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="43" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>667</v>
       </c>
@@ -20271,7 +20271,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="44" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>668</v>
       </c>
@@ -20326,7 +20326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="45" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>669</v>
       </c>
@@ -20381,7 +20381,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="46" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>671</v>
       </c>
@@ -20436,7 +20436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="47" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>673</v>
       </c>
@@ -20491,7 +20491,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="48" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>674</v>
       </c>
@@ -20546,7 +20546,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="49" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>676</v>
       </c>
@@ -20601,7 +20601,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="50" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>677</v>
       </c>
@@ -20656,7 +20656,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="51" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>678</v>
       </c>
@@ -20709,7 +20709,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="52" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>680</v>
       </c>
@@ -20764,7 +20764,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="53" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>681</v>
       </c>
@@ -20819,7 +20819,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="54" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>682</v>
       </c>
@@ -20874,7 +20874,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="55" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>683</v>
       </c>
@@ -20929,7 +20929,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="56" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>684</v>
       </c>
@@ -20984,7 +20984,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="57" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>685</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="58" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>687</v>
       </c>
@@ -21094,7 +21094,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="59" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>688</v>
       </c>
@@ -21149,7 +21149,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="60" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>689</v>
       </c>
@@ -21204,7 +21204,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="61" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>690</v>
       </c>
@@ -21259,7 +21259,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="62" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>692</v>
       </c>
@@ -21314,7 +21314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="63" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>693</v>
       </c>
@@ -21369,7 +21369,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="64" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>695</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="65" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>696</v>
       </c>
@@ -21479,7 +21479,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="66" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>697</v>
       </c>
@@ -21534,7 +21534,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="67" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>698</v>
       </c>
@@ -21589,7 +21589,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="68" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>699</v>
       </c>
@@ -21644,7 +21644,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="69" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>700</v>
       </c>
@@ -21699,7 +21699,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="70" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>701</v>
       </c>
@@ -21754,7 +21754,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="71" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>703</v>
       </c>
@@ -21809,7 +21809,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="72" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>704</v>
       </c>
@@ -21864,7 +21864,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="73" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>705</v>
       </c>
@@ -21919,7 +21919,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="74" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>706</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="75" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>707</v>
       </c>
@@ -22029,7 +22029,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="76" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>708</v>
       </c>
@@ -22084,7 +22084,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="77" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>709</v>
       </c>
@@ -22133,7 +22133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="78" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>711</v>
       </c>
@@ -22188,7 +22188,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="79" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>712</v>
       </c>
@@ -22243,7 +22243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="80" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>714</v>
       </c>
@@ -22296,7 +22296,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="81" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>716</v>
       </c>
@@ -22351,7 +22351,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="82" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>717</v>
       </c>
@@ -22406,7 +22406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="83" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>718</v>
       </c>
@@ -22461,7 +22461,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="84" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>720</v>
       </c>
@@ -22516,7 +22516,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="85" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>722</v>
       </c>
@@ -22571,7 +22571,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="86" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>724</v>
       </c>
@@ -22626,7 +22626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="87" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>726</v>
       </c>
@@ -22681,7 +22681,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="88" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>728</v>
       </c>
@@ -22736,7 +22736,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="89" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>730</v>
       </c>
@@ -22791,7 +22791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="90" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>732</v>
       </c>
@@ -22846,7 +22846,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="91" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>733</v>
       </c>
@@ -22901,7 +22901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="92" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>734</v>
       </c>
@@ -22956,7 +22956,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="93" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>735</v>
       </c>
@@ -23009,7 +23009,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="94" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>736</v>
       </c>
@@ -23062,7 +23062,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="95" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>738</v>
       </c>
@@ -23117,7 +23117,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="96" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>740</v>
       </c>
@@ -23168,7 +23168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="97" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>742</v>
       </c>
@@ -23223,7 +23223,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="98" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
         <v>744</v>
       </c>
@@ -23278,7 +23278,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="99" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
         <v>745</v>
       </c>
@@ -23331,7 +23331,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="100" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
         <v>746</v>
       </c>
@@ -23386,7 +23386,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="101" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>748</v>
       </c>
@@ -23441,7 +23441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="102" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
         <v>749</v>
       </c>
@@ -23496,7 +23496,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="103" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
         <v>750</v>
       </c>
@@ -23551,7 +23551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="70.150000000000006" customHeight="1">
+    <row r="104" spans="1:19" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
         <v>751</v>
       </c>
@@ -23614,6 +23614,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -23757,12 +23763,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -23773,13 +23773,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA898CCD-AE0E-4187-8A1B-FE0621426781}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD862E6B-081C-4342-B56B-50B245C893EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA898CCD-AE0E-4187-8A1B-FE0621426781}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F8375F1-E5BC-404D-A299-BBBC9823C452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAD32A22-6EB5-4FA3-A1C4-509D94B5C091}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="13_ncr:1_{665C029F-5FE1-4B2C-9738-45AB1492435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00C69CA9-029D-4816-BC04-B5F85D4286D5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
     <comment ref="AB53" authorId="0" shapeId="0" xr:uid="{82B7C04B-F0DD-44EA-B29D-6728FBCFCE51}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Revisar si este es el primero</t>
       </text>
@@ -67,7 +67,7 @@
     <comment ref="V16" authorId="0" shapeId="0" xr:uid="{3DC57012-9491-4551-95BD-F507AF7C73BC}">
       <text>
         <t>[Comentario encadenado]
-Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
 Comentario:
     Revisar si es la primera fecha</t>
       </text>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2730" uniqueCount="1083">
   <si>
     <t>#</t>
   </si>
@@ -3448,6 +3448,15 @@
   </si>
   <si>
     <t>FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALOR OTROS </t>
+  </si>
+  <si>
+    <t>FECHA DE INCORPORACIÓN DE RECUROS</t>
+  </si>
+  <si>
+    <t>FECHA SUSCRIPCION</t>
   </si>
 </sst>
 </file>
@@ -3801,9 +3810,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="32">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4357,6 +4363,9 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <sz val="10"/>
         <name val="Roboto"/>
@@ -4474,14 +4483,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2F680A93-E09F-4D4D-8A62-9297A36F47BF}" name="Tabla4" displayName="Tabla4" ref="A1:E26" totalsRowShown="0" headerRowDxfId="25" dataDxfId="23" headerRowBorderDxfId="24" tableBorderDxfId="22" totalsRowBorderDxfId="21">
   <autoFilter ref="A1:E26" xr:uid="{BC95059C-E8C7-402F-ACB5-3A5EFCDC0A8F}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{00B5684D-680D-4F06-B17A-D246DA7EC4BA}" name="TIPO DE CAMBIO" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{0850F860-206F-4E5D-9ACB-330185397342}" name="CAMBIO" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{C43A50F7-2A5D-4E87-9AB5-4E8D0692A798}" name="MATRIZ" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{C3391573-845D-42B8-B32F-883FF2105ADC}" name="HERRAMIENTA" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{7ED62F82-5B10-4EAC-8EDB-F8190150BB06}" name="REALIZADO" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -4491,8 +4500,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AZ59" totalsRowShown="0">
   <autoFilter ref="A2:AZ59" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="52">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NOMBRE PROYECTO"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="ALCANCE DEL PROYECTO"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SECTOR"/>
@@ -4518,11 +4527,11 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
-    <tableColumn id="52" xr3:uid="{E036A4E5-34E4-46E7-A1F3-AD83D6363F18}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="14"/>
+    <tableColumn id="52" xr3:uid="{E036A4E5-34E4-46E7-A1F3-AD83D6363F18}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="13"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
-    <tableColumn id="51" xr3:uid="{C090CC8F-BACE-4FF3-860D-E39729285D80}" name="FECHA EN LA QUE PASO A ESTADO PARA CIERRE" dataDxfId="13"/>
+    <tableColumn id="51" xr3:uid="{C090CC8F-BACE-4FF3-860D-E39729285D80}" name="FECHA EN LA QUE PASO A ESTADO PARA CIERRE" dataDxfId="12"/>
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="INFORMACIÓN SOLICITADA"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="INFORMACIÓN RECIBIDA"/>
@@ -4539,24 +4548,24 @@
     <tableColumn id="44" xr3:uid="{00000000-0010-0000-0000-00002C000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="45" xr3:uid="{00000000-0010-0000-0000-00002D000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="46" xr3:uid="{00000000-0010-0000-0000-00002E000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="12">
+    <tableColumn id="47" xr3:uid="{00000000-0010-0000-0000-00002F000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="11">
       <calculatedColumnFormula>IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($AD3),ISNUMBER($AG3),$AD3&lt;$AG3),0,IF($AR3&gt;=1,(IFERROR(IF(ISTEXT($AH3),($AN3*0.4+$AO3*0.2+$AQ3*0.4),""),""))*$AV3/100,IFERROR(IF(ISTEXT($AH3),($AN3*0.4+$AO3*0.2+$AQ3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($AG3-$AB3&gt;=0,$AG3-$AB3&lt;=30),100,0),"")),"Revisar")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="11"/>
-    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="10"/>
-    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="9"/>
+    <tableColumn id="48" xr3:uid="{00000000-0010-0000-0000-000030000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="10"/>
+    <tableColumn id="49" xr3:uid="{0B47AE52-5D8E-41D9-8E02-B1CBE91FBD9C}" name="RESPONSABLE CARGUE EN GESPROY" dataDxfId="9"/>
+    <tableColumn id="50" xr3:uid="{85EBF371-8E1F-4E2C-843F-EB6B2D1C1455}" name="MUNICIPIOS" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}" name="Tabla5" displayName="Tabla5" ref="A1:C176" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}" name="Tabla5" displayName="Tabla5" ref="A1:C176" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:C176" xr:uid="{901D5E7F-886B-44F6-87F1-2B9EB2A93D0D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{99E997E3-2CEC-4F3E-8738-BC5E0E5CF370}" name="BPIN" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E64283D6-49A8-4042-B70A-6E95EF68760C}" name="ENTIDAD O SECRETARIA" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{7014C4E2-CB40-4F80-9DA5-BA0A2FF8DFBF}" name="ESTADO PROYECTO" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{99E997E3-2CEC-4F3E-8738-BC5E0E5CF370}" name="BPIN" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{E64283D6-49A8-4042-B70A-6E95EF68760C}" name="ENTIDAD O SECRETARIA" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{7014C4E2-CB40-4F80-9DA5-BA0A2FF8DFBF}" name="ESTADO PROYECTO" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="1"/>
 </table>
@@ -4575,18 +4584,18 @@
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="ESTADO PROYECTO"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="ESTADO CONTRATO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="VALOR SGR"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="VALOR OTROS "/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="FECHA DE MIGRACIÓN A GESPROY"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0100-00000F000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0100-000010000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="CPI"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="SPI"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION"/>
     <tableColumn id="41" xr3:uid="{A8611C6E-E2F8-4180-8834-5CB2E451BADE}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="31"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="39" xr3:uid="{EB9A8E1B-7DA7-46A0-8178-E11424FA43F8}" name="HORIZONTE DEL PROYECTO" dataDxfId="30"/>
@@ -4604,11 +4613,11 @@
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0100-000021000000}" name="CALIFICACIÓN INFORMACIÓN A TIEMPO"/>
     <tableColumn id="34" xr3:uid="{00000000-0010-0000-0100-000022000000}" name="CALIFICACIÓN CALIDAD INFORMACIÓN"/>
     <tableColumn id="35" xr3:uid="{00000000-0010-0000-0100-000023000000}" name="COLUMNA APOYO 2"/>
-    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="0">
+    <tableColumn id="36" xr3:uid="{00000000-0010-0000-0100-000024000000}" name="CALIFICACIÓN EJECUCIÓN DEL PROYECTO" dataDxfId="28">
       <calculatedColumnFormula>IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($X3),ISNUMBER($Z3),$X3&lt;$Z3),0,IF($AH3&gt;=1,(IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))*$AL3/100,IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($Z3-$V3&gt;=0,$Z3-$V3&lt;=30),100,0),"")),"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="28"/>
-    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="27"/>
+    <tableColumn id="37" xr3:uid="{00000000-0010-0000-0100-000025000000}" name="COMENTARIOS CALIFICACIÓN" dataDxfId="27"/>
+    <tableColumn id="38" xr3:uid="{D24D1609-6988-4A97-9BB0-284F74971309}" name="MUNICIPIOS" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4631,12 +4640,12 @@
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0200-00000B000000}" name="VALOR TOTAL"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0200-00000C000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0200-00000D000000}" name="FECHA DE ASIGNACIÓN DE RECURSOS"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECURSOS"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0200-00000E000000}" name="FECHA DE INCORPORACIÓN DE RECUROS"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0200-00000F000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0200-000010000000}" name="AVANCE FÍSICO"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0200-000011000000}" name="AVANCE FINANCIERO"/>
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0200-000012000000}" name="COMENTARIOS "/>
-    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{CA52A6B0-FF19-445D-8675-847F209870D3}" name="MUNICIPIOS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16519,7 +16528,7 @@
         <v>99</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>101</v>
+        <v>1080</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>753</v>
@@ -16531,7 +16540,7 @@
         <v>107</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>1081</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>754</v>
@@ -16552,7 +16561,7 @@
         <v>114</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="V2" s="2" t="s">
         <v>1079</v>
@@ -18502,7 +18511,7 @@
         <v>107</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>108</v>
+        <v>1081</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>115</v>

--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zgama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A947CB4-1F92-4737-8963-9DBBC253EF0F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>FECHA DE APERTURA DEL PRIMER PROCESO</t>
   </si>
   <si>
-    <t>FECHA SUSCRIPCION</t>
-  </si>
-  <si>
     <t>FECHA ACTA INICIO</t>
   </si>
   <si>
@@ -2910,6 +2907,9 @@
   </si>
   <si>
     <t>MEJORAMIENTO INTEGRAL DE LA INSTITUCIÓN EDUCATIVA GABRIEL GARCÍA MÁRQUEZ SEDE OSPINA PÉREZ II DEL MUNICIPIO DE COROZAL, MEDIANTE LA INTERVENCIÓN DE SU INFRAESTRUCTURA FÍSICA Y ELÉCTRICA PARA MEJORAR LAS CONDICIONES DE FORMACIÓN Y APRENDIZAJE DE LA COMUNIDAD EDUCATIVA.</t>
+  </si>
+  <si>
+    <t>FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL</t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3082,7 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCION"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
@@ -3133,7 +3133,7 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="SPI"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
@@ -3618,102 +3618,102 @@
         <v>28</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="K3" s="4">
         <v>1548027380</v>
@@ -3775,10 +3775,10 @@
         <v>46157</v>
       </c>
       <c r="AF3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG3" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="AH3" s="5">
         <v>46157</v>
@@ -3822,39 +3822,39 @@
         <v/>
       </c>
       <c r="AV3" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="K4" s="4">
         <v>5000000000</v>
@@ -3953,39 +3953,39 @@
         <v/>
       </c>
       <c r="AV4" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="K5" s="4">
         <v>4081742194</v>
@@ -4047,10 +4047,10 @@
         <v>46157</v>
       </c>
       <c r="AF5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG5" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="AH5" s="5">
         <v>46157</v>
@@ -4094,39 +4094,39 @@
         <v/>
       </c>
       <c r="AV5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="K6" s="4">
         <v>14661580598</v>
@@ -4190,10 +4190,10 @@
         <v>46157</v>
       </c>
       <c r="AF6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AH6" s="5">
         <v>46157</v>
@@ -4237,39 +4237,39 @@
         <v>40</v>
       </c>
       <c r="AV6" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K7" s="4">
         <v>30476618849</v>
@@ -4331,10 +4331,10 @@
         <v>46157</v>
       </c>
       <c r="AF7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG7" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="AG7" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="AH7" s="5">
         <v>46152</v>
@@ -4378,39 +4378,39 @@
         <v/>
       </c>
       <c r="AV7" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="K8" s="4">
         <v>11741345301</v>
@@ -4472,10 +4472,10 @@
         <v>46157</v>
       </c>
       <c r="AF8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG8" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="AG8" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="AH8" s="5">
         <v>46157</v>
@@ -4519,39 +4519,39 @@
         <v/>
       </c>
       <c r="AV8" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="G9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K9" s="4">
         <v>189749519481.00461</v>
@@ -4617,10 +4617,10 @@
         <v>46157</v>
       </c>
       <c r="AF9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG9" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="AG9" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="AH9" s="5">
         <v>46152</v>
@@ -4664,39 +4664,39 @@
         <v>40</v>
       </c>
       <c r="AV9" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K10" s="4">
         <v>15331463849</v>
@@ -4758,10 +4758,10 @@
         <v>46157</v>
       </c>
       <c r="AF10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AG10" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="AG10" s="3" t="s">
-        <v>121</v>
       </c>
       <c r="AH10" s="5">
         <v>46157</v>
@@ -4805,39 +4805,39 @@
         <v/>
       </c>
       <c r="AV10" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="G11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="K11" s="4">
         <v>14300800098.139999</v>
@@ -4899,10 +4899,10 @@
         <v>46157</v>
       </c>
       <c r="AF11" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG11" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH11" s="5">
         <v>46157</v>
@@ -4946,39 +4946,39 @@
         <v/>
       </c>
       <c r="AV11" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="K12" s="4">
         <v>66912604863.639999</v>
@@ -5040,10 +5040,10 @@
         <v>46157</v>
       </c>
       <c r="AF12" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="AG12" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="AG12" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="AH12" s="5">
         <v>46152</v>
@@ -5087,39 +5087,39 @@
         <v/>
       </c>
       <c r="AV12" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="K13" s="4">
         <v>14525812035</v>
@@ -5183,10 +5183,10 @@
         <v>46157</v>
       </c>
       <c r="AF13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG13" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="AG13" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="AH13" s="5">
         <v>46152</v>
@@ -5230,39 +5230,39 @@
         <v>0</v>
       </c>
       <c r="AV13" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="G14" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K14" s="4">
         <v>4457416400</v>
@@ -5324,10 +5324,10 @@
         <v>46157</v>
       </c>
       <c r="AF14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AG14" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="AH14" s="5">
         <v>46152</v>
@@ -5371,39 +5371,39 @@
         <v/>
       </c>
       <c r="AV14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="G15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I15" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K15" s="4">
         <v>9991937324.4500008</v>
@@ -5467,10 +5467,10 @@
         <v>46157</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH15" s="5">
         <v>46157</v>
@@ -5514,39 +5514,39 @@
         <v>0</v>
       </c>
       <c r="AV15" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K16" s="4">
         <v>1582195518</v>
@@ -5608,10 +5608,10 @@
         <v>46157</v>
       </c>
       <c r="AF16" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH16" s="5">
         <v>46157</v>
@@ -5655,39 +5655,39 @@
         <v/>
       </c>
       <c r="AV16" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="K17" s="4">
         <v>16839824924.799999</v>
@@ -5751,10 +5751,10 @@
         <v>46157</v>
       </c>
       <c r="AF17" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="AG17" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="AG17" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="AH17" s="5">
         <v>46152</v>
@@ -5798,39 +5798,39 @@
         <v>75</v>
       </c>
       <c r="AV17" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="K18" s="4">
         <v>3342400000</v>
@@ -5894,10 +5894,10 @@
         <v>46157</v>
       </c>
       <c r="AF18" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AG18" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH18" s="5">
         <v>46157</v>
@@ -5941,39 +5941,39 @@
         <v>36</v>
       </c>
       <c r="AV18" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="K19" s="4">
         <v>990000000</v>
@@ -6037,10 +6037,10 @@
         <v>46157</v>
       </c>
       <c r="AF19" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AG19" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH19" s="5">
         <v>46157</v>
@@ -6084,39 +6084,39 @@
         <v>36</v>
       </c>
       <c r="AV19" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="G20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K20" s="4">
         <v>1000000000</v>
@@ -6178,10 +6178,10 @@
         <v>46157</v>
       </c>
       <c r="AF20" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AH20" s="5">
         <v>46157</v>
@@ -6225,39 +6225,39 @@
         <v/>
       </c>
       <c r="AV20" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="K21" s="4">
         <v>4300000000</v>
@@ -6321,10 +6321,10 @@
         <v>46157</v>
       </c>
       <c r="AF21" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="AG21" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>195</v>
       </c>
       <c r="AH21" s="5">
         <v>46152</v>
@@ -6368,39 +6368,39 @@
         <v>36</v>
       </c>
       <c r="AV21" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="G22" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I22" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K22" s="4">
         <v>24245749081.080002</v>
@@ -6464,10 +6464,10 @@
         <v>46157</v>
       </c>
       <c r="AF22" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="AG22" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="AH22" s="5">
         <v>46152</v>
@@ -6511,39 +6511,39 @@
         <v>90</v>
       </c>
       <c r="AV22" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K23" s="4">
         <v>1498986578.77</v>
@@ -6646,39 +6646,39 @@
         <v/>
       </c>
       <c r="AV23" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="24" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="K24" s="4">
         <v>621744000</v>
@@ -6781,39 +6781,39 @@
         <v/>
       </c>
       <c r="AV24" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="G25" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K25" s="4">
         <v>899027939.82000005</v>
@@ -6914,39 +6914,39 @@
         <v/>
       </c>
       <c r="AV25" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>228</v>
-      </c>
       <c r="I26" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K26" s="4">
         <v>8561481683</v>
@@ -7010,10 +7010,10 @@
         <v>46157</v>
       </c>
       <c r="AF26" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG26" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="AG26" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="AH26" s="5">
         <v>46152</v>
@@ -7057,39 +7057,39 @@
         <v>30</v>
       </c>
       <c r="AV26" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>236</v>
-      </c>
       <c r="G27" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I27" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K27" s="4">
         <v>13470040052.48</v>
@@ -7151,10 +7151,10 @@
         <v>46157</v>
       </c>
       <c r="AF27" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG27" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AH27" s="5">
         <v>46157</v>
@@ -7198,39 +7198,39 @@
         <v/>
       </c>
       <c r="AV27" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>241</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K28" s="4">
         <v>10889084257</v>
@@ -7292,10 +7292,10 @@
         <v>46157</v>
       </c>
       <c r="AF28" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="AG28" s="3" t="s">
         <v>242</v>
-      </c>
-      <c r="AG28" s="3" t="s">
-        <v>243</v>
       </c>
       <c r="AH28" s="5">
         <v>46152</v>
@@ -7337,39 +7337,39 @@
         <v/>
       </c>
       <c r="AV28" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>247</v>
-      </c>
       <c r="G29" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H29" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="I29" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K29" s="4">
         <v>9528331044</v>
@@ -7431,10 +7431,10 @@
         <v>46157</v>
       </c>
       <c r="AF29" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AG29" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>249</v>
       </c>
       <c r="AH29" s="5">
         <v>46152</v>
@@ -7478,39 +7478,39 @@
         <v/>
       </c>
       <c r="AV29" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>254</v>
-      </c>
       <c r="G30" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K30" s="4">
         <v>14530936843.950001</v>
@@ -7572,7 +7572,7 @@
         <v>46157</v>
       </c>
       <c r="AF30" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AG30" s="3"/>
       <c r="AH30" s="5"/>
@@ -7613,39 +7613,39 @@
         <v/>
       </c>
       <c r="AV30" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K31" s="4">
         <v>1226001186</v>
@@ -7707,10 +7707,10 @@
         <v>46157</v>
       </c>
       <c r="AF31" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AG31" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AH31" s="5">
         <v>46152</v>
@@ -7752,39 +7752,39 @@
         <v/>
       </c>
       <c r="AV31" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>264</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>265</v>
       </c>
       <c r="K32" s="4">
         <v>10940798931</v>
@@ -7848,10 +7848,10 @@
         <v>46157</v>
       </c>
       <c r="AF32" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="AG32" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="AG32" s="3" t="s">
-        <v>267</v>
       </c>
       <c r="AH32" s="5">
         <v>46152</v>
@@ -7895,39 +7895,39 @@
         <v>100</v>
       </c>
       <c r="AV32" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="F33" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="G33" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K33" s="4">
         <v>8600669220</v>
@@ -7991,10 +7991,10 @@
         <v>46157</v>
       </c>
       <c r="AF33" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AG33" s="3" t="s">
         <v>275</v>
-      </c>
-      <c r="AG33" s="3" t="s">
-        <v>276</v>
       </c>
       <c r="AH33" s="5">
         <v>46152</v>
@@ -8038,39 +8038,39 @@
         <v>24</v>
       </c>
       <c r="AV33" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="34" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I34" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J34" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K34" s="4">
         <v>1657061525</v>
@@ -8132,10 +8132,10 @@
         <v>46157</v>
       </c>
       <c r="AF34" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AG34" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AH34" s="5">
         <v>46152</v>
@@ -8177,39 +8177,39 @@
         <v/>
       </c>
       <c r="AV34" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="F35" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K35" s="4">
         <v>14555629486.65</v>
@@ -8308,39 +8308,39 @@
         <v/>
       </c>
       <c r="AV35" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="36" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="E36" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="G36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I36" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="K36" s="4">
         <v>23521931236</v>
@@ -8402,10 +8402,10 @@
         <v>46157</v>
       </c>
       <c r="AF36" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="AG36" s="3" t="s">
         <v>293</v>
-      </c>
-      <c r="AG36" s="3" t="s">
-        <v>294</v>
       </c>
       <c r="AH36" s="5">
         <v>46152</v>
@@ -8449,39 +8449,39 @@
         <v>88.695652173913047</v>
       </c>
       <c r="AV36" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="E37" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>299</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K37" s="4">
         <v>2999999744</v>
@@ -8543,10 +8543,10 @@
         <v>46157</v>
       </c>
       <c r="AF37" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="AG37" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="AG37" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="AH37" s="5">
         <v>46155</v>
@@ -8590,39 +8590,39 @@
         <v/>
       </c>
       <c r="AV37" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="K38" s="4">
         <v>10877971203</v>
@@ -8686,10 +8686,10 @@
         <v>46157</v>
       </c>
       <c r="AF38" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG38" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AH38" s="5">
         <v>46152</v>
@@ -8733,39 +8733,39 @@
         <v>79.043478260869563</v>
       </c>
       <c r="AV38" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="D39" s="3" t="s">
+      <c r="E39" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F39" s="3" t="s">
+      <c r="G39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="K39" s="4">
         <v>20000000000</v>
@@ -8827,10 +8827,10 @@
         <v>46157</v>
       </c>
       <c r="AF39" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG39" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AH39" s="5">
         <v>46157</v>
@@ -8874,39 +8874,39 @@
         <v/>
       </c>
       <c r="AV39" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F40" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>320</v>
-      </c>
       <c r="G40" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I40" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K40" s="4">
         <v>2401226400</v>
@@ -8970,10 +8970,10 @@
         <v>46157</v>
       </c>
       <c r="AF40" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="AG40" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="AG40" s="3" t="s">
-        <v>322</v>
       </c>
       <c r="AH40" s="5">
         <v>46152</v>
@@ -9017,39 +9017,39 @@
         <v>86.956521739130437</v>
       </c>
       <c r="AV40" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="41" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="D41" s="3" t="s">
+      <c r="E41" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>327</v>
-      </c>
       <c r="G41" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I41" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K41" s="4">
         <v>1207242704</v>
@@ -9113,10 +9113,10 @@
         <v>46157</v>
       </c>
       <c r="AF41" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="AG41" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="AG41" s="3" t="s">
-        <v>329</v>
       </c>
       <c r="AH41" s="5">
         <v>46152</v>
@@ -9160,39 +9160,39 @@
         <v>75</v>
       </c>
       <c r="AV41" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="42" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>333</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I42" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K42" s="4">
         <v>7025611116</v>
@@ -9254,10 +9254,10 @@
         <v>46157</v>
       </c>
       <c r="AF42" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="AG42" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="AG42" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="AH42" s="5">
         <v>46152</v>
@@ -9301,35 +9301,35 @@
         <v>100</v>
       </c>
       <c r="AV42" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D43" s="3" t="s">
+      <c r="E43" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F43" s="3" t="s">
+      <c r="G43" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K43" s="4">
         <v>2942601333.2800002</v>
@@ -9381,10 +9381,10 @@
         <v>46157</v>
       </c>
       <c r="AF43" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="AG43" s="3" t="s">
         <v>342</v>
-      </c>
-      <c r="AG43" s="3" t="s">
-        <v>343</v>
       </c>
       <c r="AH43" s="5">
         <v>46152</v>
@@ -9432,39 +9432,39 @@
         <v/>
       </c>
       <c r="AV43" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="44" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="E44" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K44" s="4">
         <v>689677427</v>
@@ -9528,10 +9528,10 @@
         <v>46157</v>
       </c>
       <c r="AF44" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="AG44" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="AG44" s="3" t="s">
-        <v>350</v>
       </c>
       <c r="AH44" s="5">
         <v>46152</v>
@@ -9575,39 +9575,39 @@
         <v>36</v>
       </c>
       <c r="AV44" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="45" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I45" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>358</v>
       </c>
       <c r="K45" s="4">
         <v>1135083847</v>
@@ -9669,10 +9669,10 @@
         <v>46157</v>
       </c>
       <c r="AF45" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="AG45" s="3" t="s">
         <v>359</v>
-      </c>
-      <c r="AG45" s="3" t="s">
-        <v>360</v>
       </c>
       <c r="AH45" s="5">
         <v>46152</v>
@@ -9716,39 +9716,39 @@
         <v>60</v>
       </c>
       <c r="AV45" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F46" s="3" t="s">
+      <c r="G46" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="G46" s="3" t="s">
+      <c r="H46" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="I46" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>368</v>
       </c>
       <c r="K46" s="4">
         <v>2439637568.0900002</v>
@@ -9804,10 +9804,10 @@
         <v>46157</v>
       </c>
       <c r="AF46" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="AG46" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="AG46" s="3" t="s">
-        <v>370</v>
       </c>
       <c r="AH46" s="5">
         <v>46152</v>
@@ -9855,39 +9855,39 @@
         <v/>
       </c>
       <c r="AV46" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="47" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="D47" s="3" t="s">
+      <c r="E47" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E47" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>375</v>
-      </c>
       <c r="G47" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H47" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I47" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K47" s="4">
         <v>2653691597.3099999</v>
@@ -9951,10 +9951,10 @@
         <v>46157</v>
       </c>
       <c r="AF47" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="AG47" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="AG47" s="3" t="s">
-        <v>377</v>
       </c>
       <c r="AH47" s="5">
         <v>46152</v>
@@ -9998,7 +9998,7 @@
         <v>88.434782608695656</v>
       </c>
       <c r="AV47" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48" spans="1:48" ht="96" customHeight="1" x14ac:dyDescent="0.3">
@@ -10006,27 +10006,27 @@
         <v>2024702150036</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>380</v>
-      </c>
       <c r="G48" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K48" s="4">
         <v>1361249394</v>
@@ -10117,35 +10117,35 @@
         <v/>
       </c>
       <c r="AV48" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="49" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K49" s="4">
         <v>39069417997</v>
@@ -10193,10 +10193,10 @@
         <v>46157</v>
       </c>
       <c r="AF49" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="AG49" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="AG49" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="AH49" s="5">
         <v>46152</v>
@@ -10242,39 +10242,39 @@
         <v/>
       </c>
       <c r="AV49" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="50" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J50" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>394</v>
       </c>
       <c r="K50" s="4">
         <v>15884181916</v>
@@ -10336,10 +10336,10 @@
         <v>46157</v>
       </c>
       <c r="AF50" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG50" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AH50" s="5">
         <v>46157</v>
@@ -10383,39 +10383,39 @@
         <v/>
       </c>
       <c r="AV50" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>400</v>
-      </c>
       <c r="G51" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I51" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K51" s="4">
         <v>79715601771.679993</v>
@@ -10477,10 +10477,10 @@
         <v>46157</v>
       </c>
       <c r="AF51" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="AG51" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="AG51" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="AH51" s="5">
         <v>46152</v>
@@ -10524,39 +10524,39 @@
         <v>60</v>
       </c>
       <c r="AV51" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="52" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>406</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G52" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I52" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K52" s="4">
         <v>1000000435</v>
@@ -10620,10 +10620,10 @@
         <v>46157</v>
       </c>
       <c r="AF52" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AG52" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH52" s="5">
         <v>46152</v>
@@ -10667,39 +10667,39 @@
         <v>100</v>
       </c>
       <c r="AV52" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="53" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="G53" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H53" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="I53" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K53" s="4">
         <v>910271851.27999997</v>
@@ -10753,10 +10753,10 @@
         <v>46163</v>
       </c>
       <c r="AF53" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="AG53" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="AG53" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="AH53" s="5">
         <v>46152</v>
@@ -10804,35 +10804,35 @@
         <v/>
       </c>
       <c r="AV53" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="54" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="G54" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K54" s="4">
         <v>9230360486</v>
@@ -10880,10 +10880,10 @@
         <v>46157</v>
       </c>
       <c r="AF54" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="AG54" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="AG54" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="AH54" s="5">
         <v>46152</v>
@@ -10931,39 +10931,39 @@
         <v/>
       </c>
       <c r="AV54" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E55" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="G55" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H55" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="I55" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K55" s="4">
         <v>1265672010</v>
@@ -11025,10 +11025,10 @@
         <v>46157</v>
       </c>
       <c r="AF55" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="AG55" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="AG55" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="AH55" s="5">
         <v>46152</v>
@@ -11072,39 +11072,39 @@
         <v>100</v>
       </c>
       <c r="AV55" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="56" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F56" s="3" t="s">
+      <c r="G56" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="J56" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="K56" s="4">
         <v>1631281390</v>
@@ -11158,10 +11158,10 @@
         <v>46157</v>
       </c>
       <c r="AF56" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="AG56" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="AG56" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="AH56" s="5">
         <v>46152</v>
@@ -11209,35 +11209,35 @@
         <v/>
       </c>
       <c r="AV56" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="57" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="G57" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K57" s="4">
         <v>2998247290</v>
@@ -11289,10 +11289,10 @@
         <v>46157</v>
       </c>
       <c r="AF57" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="AG57" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="AG57" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="AH57" s="5">
         <v>46152</v>
@@ -11340,35 +11340,35 @@
         <v/>
       </c>
       <c r="AV57" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="58" spans="1:48" ht="123.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="G58" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K58" s="4">
         <v>4190286255</v>
@@ -11416,10 +11416,10 @@
         <v>46157</v>
       </c>
       <c r="AF58" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG58" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AH58" s="5">
         <v>46152</v>
@@ -11467,35 +11467,35 @@
         <v/>
       </c>
       <c r="AV58" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="59" spans="1:48" ht="135" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="D59" s="3" t="s">
+      <c r="E59" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="G59" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K59" s="4">
         <v>15410127474</v>
@@ -11541,10 +11541,10 @@
         <v>46157</v>
       </c>
       <c r="AF59" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG59" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AH59" s="5">
         <v>46152</v>
@@ -11592,7 +11592,7 @@
         <v/>
       </c>
       <c r="AV59" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="60" spans="1:48" ht="123" customHeight="1" x14ac:dyDescent="0.3">
@@ -11600,27 +11600,27 @@
         <v>2026002700007</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="K60" s="4">
         <v>783362744.10000002</v>
@@ -11711,7 +11711,7 @@
         <v/>
       </c>
       <c r="AV60" s="3" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -11789,19 +11789,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -11813,10 +11813,10 @@
         <v>13</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>20</v>
@@ -11825,10 +11825,10 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>24</v>
@@ -11846,81 +11846,81 @@
         <v>28</v>
       </c>
       <c r="U2" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="V2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="V2" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="W2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Y2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>472</v>
       </c>
       <c r="I3" s="4">
         <v>2006938345.6700001</v>
@@ -11997,33 +11997,33 @@
         <v/>
       </c>
       <c r="AK3" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I4" s="4">
         <v>1295118639.0699999</v>
@@ -12100,33 +12100,33 @@
         <v/>
       </c>
       <c r="AK4" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>482</v>
       </c>
       <c r="I5" s="4">
         <v>3153851580.9099998</v>
@@ -12209,33 +12209,33 @@
         <v>75</v>
       </c>
       <c r="AK5" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>487</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>488</v>
       </c>
       <c r="I6" s="4">
         <v>6026477761</v>
@@ -12320,33 +12320,33 @@
         <v>50</v>
       </c>
       <c r="AK6" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>493</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I7" s="4">
         <v>1800000000</v>
@@ -12431,33 +12431,33 @@
         <v>50</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="8" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>496</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I8" s="4">
         <v>1702007732.2</v>
@@ -12534,33 +12534,33 @@
         <v/>
       </c>
       <c r="AK8" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I9" s="4">
         <v>13713002364.719999</v>
@@ -12645,33 +12645,33 @@
         <v/>
       </c>
       <c r="AK9" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>503</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I10" s="4">
         <v>9056051736.6399994</v>
@@ -12757,28 +12757,28 @@
     </row>
     <row r="11" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>506</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I11" s="4">
         <v>7862105021</v>
@@ -12866,28 +12866,28 @@
     </row>
     <row r="12" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>510</v>
-      </c>
       <c r="E12" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I12" s="4">
         <v>15100656106.639999</v>
@@ -12972,33 +12972,33 @@
         <v>90</v>
       </c>
       <c r="AK12" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I13" s="4">
         <v>3068416428</v>
@@ -13084,28 +13084,28 @@
     </row>
     <row r="14" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>518</v>
       </c>
       <c r="I14" s="4">
         <v>63850574205.629997</v>
@@ -13193,28 +13193,28 @@
     </row>
     <row r="15" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>521</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I15" s="4">
         <v>11318403530.17</v>
@@ -13300,28 +13300,28 @@
     </row>
     <row r="16" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>524</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I16" s="4">
         <v>1903272161</v>
@@ -13405,28 +13405,28 @@
     </row>
     <row r="17" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>527</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I17" s="4">
         <v>1484402616</v>
@@ -13504,28 +13504,28 @@
     </row>
     <row r="18" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>532</v>
       </c>
       <c r="I18" s="4">
         <v>627486059.86000001</v>
@@ -13647,19 +13647,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>9</v>
@@ -13674,7 +13674,7 @@
         <v>15</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>27</v>
@@ -13683,45 +13683,45 @@
         <v>21</v>
       </c>
       <c r="N2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>465</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>466</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="I3" s="4">
         <v>22526692745</v>
@@ -13752,28 +13752,28 @@
     </row>
     <row r="4" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>542</v>
-      </c>
       <c r="E4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I4" s="4">
         <v>924979909</v>
@@ -13804,28 +13804,28 @@
     </row>
     <row r="5" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>546</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I5" s="4">
         <v>999998309</v>
@@ -13856,28 +13856,28 @@
     </row>
     <row r="6" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>550</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I6" s="4">
         <v>16567304387</v>
@@ -13908,28 +13908,28 @@
     </row>
     <row r="7" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>554</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I7" s="4">
         <v>12429000000</v>
@@ -13960,28 +13960,28 @@
     </row>
     <row r="8" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>558</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I8" s="4">
         <v>14996018261</v>
@@ -14012,28 +14012,28 @@
     </row>
     <row r="9" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>563</v>
-      </c>
       <c r="G9" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I9" s="4">
         <v>14913362760</v>
@@ -14064,28 +14064,28 @@
     </row>
     <row r="10" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>568</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I10" s="4">
         <v>7037696704</v>
@@ -14116,28 +14116,28 @@
     </row>
     <row r="11" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>572</v>
-      </c>
       <c r="E11" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I11" s="4">
         <v>13800000000</v>
@@ -14168,28 +14168,28 @@
     </row>
     <row r="12" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>577</v>
-      </c>
       <c r="G12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I12" s="4">
         <v>16094650077</v>
@@ -14220,28 +14220,28 @@
     </row>
     <row r="13" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="I13" s="4">
         <v>54337268559</v>
@@ -14272,28 +14272,28 @@
     </row>
     <row r="14" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>588</v>
-      </c>
       <c r="G14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I14" s="4">
         <v>5261488233</v>
@@ -14324,28 +14324,28 @@
     </row>
     <row r="15" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>592</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I15" s="4">
         <v>8077068482</v>
@@ -14376,28 +14376,28 @@
     </row>
     <row r="16" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>596</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I16" s="4">
         <v>7750000000</v>
@@ -14428,28 +14428,28 @@
     </row>
     <row r="17" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>600</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I17" s="4">
         <v>1027100000</v>
@@ -14480,28 +14480,28 @@
     </row>
     <row r="18" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>604</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I18" s="4">
         <v>9491491960</v>
@@ -14532,28 +14532,28 @@
     </row>
     <row r="19" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>608</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I19" s="4">
         <v>4024500000</v>
@@ -14584,28 +14584,28 @@
     </row>
     <row r="20" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>612</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I20" s="4">
         <v>20233937500</v>
@@ -14636,28 +14636,28 @@
     </row>
     <row r="21" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>616</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I21" s="4">
         <v>6524500000</v>
@@ -14688,28 +14688,28 @@
     </row>
     <row r="22" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>620</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I22" s="4">
         <v>2500000000</v>
@@ -14740,28 +14740,28 @@
     </row>
     <row r="23" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>624</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I23" s="4">
         <v>3500000000</v>
@@ -14792,28 +14792,28 @@
     </row>
     <row r="24" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>628</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I24" s="4">
         <v>3250000000</v>
@@ -14844,28 +14844,28 @@
     </row>
     <row r="25" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>632</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I25" s="4">
         <v>946000000</v>
@@ -14896,28 +14896,28 @@
     </row>
     <row r="26" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>636</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I26" s="4">
         <v>1943625000</v>
@@ -14948,28 +14948,28 @@
     </row>
     <row r="27" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>640</v>
-      </c>
       <c r="E27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I27" s="4">
         <v>1999999962.27</v>
@@ -15000,28 +15000,28 @@
     </row>
     <row r="28" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>645</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I28" s="4">
         <v>729826686</v>
@@ -15052,28 +15052,28 @@
     </row>
     <row r="29" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>649</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I29" s="4">
         <v>37141732473</v>
@@ -15104,28 +15104,28 @@
     </row>
     <row r="30" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="E30" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I30" s="4">
         <v>22507978719</v>
@@ -15156,28 +15156,28 @@
     </row>
     <row r="31" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="C31" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="E31" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="E31" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>657</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I31" s="4">
         <v>38700180208.470001</v>
@@ -15208,28 +15208,28 @@
     </row>
     <row r="32" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>660</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I32" s="4">
         <v>75409582200</v>
@@ -15260,28 +15260,28 @@
     </row>
     <row r="33" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>663</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I33" s="4">
         <v>1998000000</v>
@@ -15312,28 +15312,28 @@
     </row>
     <row r="34" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>666</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I34" s="4">
         <v>1999306318</v>
@@ -15364,28 +15364,28 @@
     </row>
     <row r="35" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>670</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I35" s="4">
         <v>1999910691</v>
@@ -15416,28 +15416,28 @@
     </row>
     <row r="36" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>674</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I36" s="4">
         <v>1999433630</v>
@@ -15468,28 +15468,28 @@
     </row>
     <row r="37" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>678</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I37" s="4">
         <v>1999976897</v>
@@ -15520,28 +15520,28 @@
     </row>
     <row r="38" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>682</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I38" s="4">
         <v>1272365336</v>
@@ -15570,28 +15570,28 @@
     </row>
     <row r="39" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>686</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I39" s="4">
         <v>1999833255</v>
@@ -15622,28 +15622,28 @@
     </row>
     <row r="40" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>690</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I40" s="4">
         <v>6559568533</v>
@@ -15674,28 +15674,28 @@
     </row>
     <row r="41" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="D41" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>693</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I41" s="4">
         <v>1998890586.73</v>
@@ -15726,28 +15726,28 @@
     </row>
     <row r="42" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C42" s="3" t="s">
+      <c r="D42" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>696</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I42" s="4">
         <v>5347795060</v>
@@ -15778,28 +15778,28 @@
     </row>
     <row r="43" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="D43" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>699</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I43" s="4">
         <v>1965295196.9400001</v>
@@ -15828,28 +15828,28 @@
     </row>
     <row r="44" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>702</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I44" s="4">
         <v>8764697664</v>
@@ -15880,28 +15880,28 @@
     </row>
     <row r="45" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>706</v>
-      </c>
       <c r="E45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I45" s="4">
         <v>1349000868</v>
@@ -15932,28 +15932,28 @@
     </row>
     <row r="46" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>710</v>
-      </c>
       <c r="E46" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I46" s="4">
         <v>3106000000</v>
@@ -15984,28 +15984,28 @@
     </row>
     <row r="47" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>713</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I47" s="4">
         <v>8995267958.5699997</v>
@@ -16036,28 +16036,28 @@
     </row>
     <row r="48" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="D48" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>717</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I48" s="4">
         <v>6750000000</v>
@@ -16088,28 +16088,28 @@
     </row>
     <row r="49" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>720</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I49" s="4">
         <v>1998157618.8800001</v>
@@ -16140,28 +16140,28 @@
     </row>
     <row r="50" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>723</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I50" s="4">
         <v>2000000000</v>
@@ -16192,28 +16192,28 @@
     </row>
     <row r="51" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>727</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I51" s="4">
         <v>5335769261</v>
@@ -16242,28 +16242,28 @@
     </row>
     <row r="52" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>730</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I52" s="4">
         <v>4940449374</v>
@@ -16294,28 +16294,28 @@
     </row>
     <row r="53" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>733</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I53" s="4">
         <v>1999924866</v>
@@ -16346,28 +16346,28 @@
     </row>
     <row r="54" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>736</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I54" s="4">
         <v>3591118773</v>
@@ -16398,28 +16398,28 @@
     </row>
     <row r="55" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>739</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I55" s="4">
         <v>2000000000</v>
@@ -16450,28 +16450,28 @@
     </row>
     <row r="56" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="B56" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>742</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I56" s="4">
         <v>1999112638.9200001</v>
@@ -16502,28 +16502,28 @@
     </row>
     <row r="57" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>746</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I57" s="4">
         <v>7500000000</v>
@@ -16554,28 +16554,28 @@
     </row>
     <row r="58" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="B58" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>749</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I58" s="4">
         <v>1999803848</v>
@@ -16606,28 +16606,28 @@
     </row>
     <row r="59" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>752</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I59" s="4">
         <v>1738785560</v>
@@ -16658,28 +16658,28 @@
     </row>
     <row r="60" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>755</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I60" s="4">
         <v>1999000000</v>
@@ -16710,28 +16710,28 @@
     </row>
     <row r="61" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>759</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I61" s="4">
         <v>1775630700</v>
@@ -16762,28 +16762,28 @@
     </row>
     <row r="62" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>762</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I62" s="4">
         <v>750000000</v>
@@ -16814,28 +16814,28 @@
     </row>
     <row r="63" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>766</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I63" s="4">
         <v>2828005287</v>
@@ -16866,28 +16866,28 @@
     </row>
     <row r="64" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="C64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="E64" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="E64" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>770</v>
-      </c>
       <c r="G64" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I64" s="4">
         <v>69047758069</v>
@@ -16918,28 +16918,28 @@
     </row>
     <row r="65" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="B65" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>773</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I65" s="4">
         <v>17635937500</v>
@@ -16970,28 +16970,28 @@
     </row>
     <row r="66" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>776</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I66" s="4">
         <v>1309600000</v>
@@ -17022,28 +17022,28 @@
     </row>
     <row r="67" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B67" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>779</v>
-      </c>
       <c r="E67" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I67" s="4">
         <v>2750000000</v>
@@ -17074,28 +17074,28 @@
     </row>
     <row r="68" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>782</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I68" s="4">
         <v>1500000000</v>
@@ -17126,28 +17126,28 @@
     </row>
     <row r="69" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="D69" s="3" t="s">
-        <v>785</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I69" s="4">
         <v>1411798728</v>
@@ -17178,28 +17178,28 @@
     </row>
     <row r="70" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="D70" s="3" t="s">
-        <v>789</v>
-      </c>
       <c r="E70" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I70" s="4">
         <v>1999997728</v>
@@ -17230,28 +17230,28 @@
     </row>
     <row r="71" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>792</v>
-      </c>
       <c r="E71" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I71" s="4">
         <v>1999667231.96</v>
@@ -17282,28 +17282,28 @@
     </row>
     <row r="72" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="E72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>795</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>796</v>
       </c>
       <c r="I72" s="4">
         <v>2000000000</v>
@@ -17334,28 +17334,28 @@
     </row>
     <row r="73" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>799</v>
-      </c>
       <c r="E73" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I73" s="4">
         <v>1953855779</v>
@@ -17386,28 +17386,28 @@
     </row>
     <row r="74" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>800</v>
       </c>
-      <c r="B74" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="D74" s="3" t="s">
-        <v>802</v>
-      </c>
       <c r="E74" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I74" s="4">
         <v>4351936180</v>
@@ -17438,28 +17438,28 @@
     </row>
     <row r="75" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>804</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>805</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I75" s="4">
         <v>19906880779</v>
@@ -17490,28 +17490,28 @@
     </row>
     <row r="76" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>807</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>808</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I76" s="4">
         <v>3981132848.27</v>
@@ -17542,26 +17542,26 @@
     </row>
     <row r="77" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>809</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>810</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>811</v>
       </c>
       <c r="D77" s="3"/>
       <c r="E77" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I77" s="4">
         <v>2407058486</v>
@@ -17588,28 +17588,28 @@
     </row>
     <row r="78" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>816</v>
-      </c>
       <c r="G78" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I78" s="4">
         <v>45601872749</v>
@@ -17640,28 +17640,28 @@
     </row>
     <row r="79" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>817</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>818</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
         <v>819</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>820</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I79" s="4">
         <v>2489078661</v>
@@ -17692,28 +17692,28 @@
     </row>
     <row r="80" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="C80" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="C80" s="3" t="s">
+      <c r="D80" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>824</v>
-      </c>
       <c r="E80" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I80" s="4">
         <v>18036167387.900002</v>
@@ -17742,28 +17742,28 @@
     </row>
     <row r="81" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>818</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="3" t="s">
         <v>826</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>827</v>
-      </c>
       <c r="E81" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I81" s="4">
         <v>41816156185</v>
@@ -17794,28 +17794,28 @@
     </row>
     <row r="82" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C82" s="3" t="s">
+      <c r="D82" s="3" t="s">
         <v>829</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>830</v>
-      </c>
       <c r="E82" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I82" s="4">
         <v>9606506835</v>
@@ -17846,28 +17846,28 @@
     </row>
     <row r="83" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>834</v>
-      </c>
       <c r="E83" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I83" s="4">
         <v>500000000</v>
@@ -17898,28 +17898,28 @@
     </row>
     <row r="84" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>835</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="C84" s="3" t="s">
         <v>836</v>
       </c>
-      <c r="C84" s="3" t="s">
+      <c r="D84" s="3" t="s">
         <v>837</v>
       </c>
-      <c r="D84" s="3" t="s">
-        <v>838</v>
-      </c>
       <c r="E84" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I84" s="4">
         <v>4299593384</v>
@@ -17950,28 +17950,28 @@
     </row>
     <row r="85" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>839</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="3" t="s">
         <v>841</v>
       </c>
-      <c r="D85" s="3" t="s">
-        <v>842</v>
-      </c>
       <c r="E85" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="I85" s="4">
         <v>29623316906.279999</v>
@@ -18002,28 +18002,28 @@
     </row>
     <row r="86" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>843</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="C86" s="3" t="s">
         <v>844</v>
       </c>
-      <c r="C86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>845</v>
       </c>
-      <c r="D86" s="3" t="s">
-        <v>846</v>
-      </c>
       <c r="E86" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I86" s="4">
         <v>30461715692</v>
@@ -18054,28 +18054,28 @@
     </row>
     <row r="87" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="C87" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="C87" s="3" t="s">
+      <c r="D87" s="3" t="s">
         <v>849</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>850</v>
-      </c>
       <c r="E87" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I87" s="4">
         <v>17454000000</v>
@@ -18106,28 +18106,28 @@
     </row>
     <row r="88" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>851</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
         <v>852</v>
       </c>
-      <c r="C88" s="3" t="s">
+      <c r="D88" s="3" t="s">
         <v>853</v>
       </c>
-      <c r="D88" s="3" t="s">
-        <v>854</v>
-      </c>
       <c r="E88" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I88" s="4">
         <v>8419333809</v>
@@ -18158,28 +18158,28 @@
     </row>
     <row r="89" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>855</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="C89" s="3" t="s">
+      <c r="D89" s="3" t="s">
         <v>857</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="E89" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F89" s="3" t="s">
         <v>858</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>859</v>
-      </c>
       <c r="G89" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I89" s="4">
         <v>94461519789</v>
@@ -18210,28 +18210,28 @@
     </row>
     <row r="90" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C90" s="3" t="s">
         <v>860</v>
       </c>
-      <c r="B90" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C90" s="3" t="s">
+      <c r="D90" s="3" t="s">
         <v>861</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="E90" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>862</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>863</v>
-      </c>
       <c r="G90" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I90" s="4">
         <v>3362968761</v>
@@ -18262,28 +18262,28 @@
     </row>
     <row r="91" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="C91" s="3" t="s">
         <v>864</v>
       </c>
-      <c r="B91" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="C91" s="3" t="s">
+      <c r="D91" s="3" t="s">
         <v>865</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>866</v>
-      </c>
       <c r="E91" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I91" s="4">
         <v>23600000000</v>
@@ -18314,28 +18314,28 @@
     </row>
     <row r="92" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="C92" s="3" t="s">
         <v>867</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="C92" s="3" t="s">
+      <c r="D92" s="3" t="s">
         <v>868</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>869</v>
-      </c>
       <c r="E92" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I92" s="4">
         <v>30000000000</v>
@@ -18366,26 +18366,26 @@
     </row>
     <row r="93" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="C93" s="3" t="s">
         <v>870</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>871</v>
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I93" s="4">
         <v>30000000000</v>
@@ -18416,26 +18416,26 @@
     </row>
     <row r="94" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>872</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="C94" s="3" t="s">
         <v>873</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>874</v>
       </c>
       <c r="D94" s="3"/>
       <c r="E94" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I94" s="4">
         <v>172253454</v>
@@ -18466,28 +18466,28 @@
     </row>
     <row r="95" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
         <v>876</v>
       </c>
-      <c r="C95" s="3" t="s">
+      <c r="D95" s="3" t="s">
         <v>877</v>
       </c>
-      <c r="D95" s="3" t="s">
-        <v>878</v>
-      </c>
       <c r="E95" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I95" s="4">
         <v>511865531</v>
@@ -18518,26 +18518,26 @@
     </row>
     <row r="96" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>879</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="C96" s="3" t="s">
         <v>880</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>881</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I96" s="4">
         <v>386045990.94</v>
@@ -18566,28 +18566,28 @@
     </row>
     <row r="97" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="C97" s="3" t="s">
         <v>883</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="D97" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="D97" s="3" t="s">
-        <v>885</v>
-      </c>
       <c r="E97" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I97" s="4">
         <v>59900815918</v>
@@ -18618,28 +18618,28 @@
     </row>
     <row r="98" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C98" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="C98" s="3" t="s">
+      <c r="D98" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="E98" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="F98" s="3" t="s">
         <v>888</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>889</v>
-      </c>
       <c r="G98" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I98" s="4">
         <v>28121067144</v>
@@ -18670,28 +18670,28 @@
     </row>
     <row r="99" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C99" s="3" t="s">
         <v>890</v>
       </c>
-      <c r="B99" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C99" s="3" t="s">
+      <c r="D99" s="3" t="s">
         <v>891</v>
       </c>
-      <c r="D99" s="3" t="s">
-        <v>892</v>
-      </c>
       <c r="E99" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I99" s="4">
         <v>1989520159</v>
@@ -18720,28 +18720,28 @@
     </row>
     <row r="100" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>893</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="C100" s="3" t="s">
         <v>894</v>
       </c>
-      <c r="C100" s="3" t="s">
+      <c r="D100" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>896</v>
-      </c>
       <c r="E100" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I100" s="4">
         <v>4869404585</v>
@@ -18772,28 +18772,28 @@
     </row>
     <row r="101" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="B101" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="C101" s="3" t="s">
+      <c r="D101" s="3" t="s">
         <v>898</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="E101" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>900</v>
-      </c>
       <c r="G101" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I101" s="4">
         <v>2644584337.2600002</v>
@@ -18824,28 +18824,28 @@
     </row>
     <row r="102" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C102" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="B102" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="C102" s="3" t="s">
+      <c r="D102" s="3" t="s">
         <v>902</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="E102" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>903</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>904</v>
-      </c>
       <c r="G102" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I102" s="4">
         <v>6578630543.6700001</v>
@@ -18876,28 +18876,28 @@
     </row>
     <row r="103" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="C103" s="3" t="s">
         <v>905</v>
       </c>
-      <c r="B103" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="C103" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>906</v>
       </c>
-      <c r="D103" s="3" t="s">
-        <v>907</v>
-      </c>
       <c r="E103" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="I103" s="4">
         <v>6853127845.6300001</v>
@@ -18928,26 +18928,26 @@
     </row>
     <row r="104" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="C104" s="3" t="s">
         <v>908</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="C104" s="3" t="s">
-        <v>909</v>
       </c>
       <c r="D104" s="3"/>
       <c r="E104" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F104" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="G104" s="3" t="s">
         <v>910</v>
       </c>
-      <c r="G104" s="3" t="s">
-        <v>911</v>
-      </c>
       <c r="H104" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="I104" s="4">
         <v>36139210439</v>
@@ -18986,6 +18986,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19129,29 +19144,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B1288D-E17B-41C7-8BDA-3DFB9BA1125D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B1288D-E17B-41C7-8BDA-3DFB9BA1125D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A947CB4-1F92-4737-8963-9DBBC253EF0F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5F42E3-8845-4FF1-B2D3-5824D7E25C8E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="918">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -2910,6 +2910,9 @@
   </si>
   <si>
     <t>FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL</t>
+  </si>
+  <si>
+    <t>FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL</t>
   </si>
 </sst>
 </file>
@@ -3082,7 +3085,7 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
@@ -3618,7 +3621,7 @@
         <v>28</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AB2" s="2" t="s">
         <v>29</v>
@@ -18986,21 +18989,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19144,24 +19132,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B1288D-E17B-41C7-8BDA-3DFB9BA1125D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19177,4 +19163,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E5F42E3-8845-4FF1-B2D3-5824D7E25C8E}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A685D9CD-037F-4F59-B409-B2502AC628BA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MatrizSeguimientoEvaluacion" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="920">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -2913,6 +2913,12 @@
   </si>
   <si>
     <t>FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL</t>
+  </si>
+  <si>
+    <t>FECHA SUSCRIPCION</t>
+  </si>
+  <si>
+    <t>FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO</t>
   </si>
 </sst>
 </file>
@@ -3011,7 +3017,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3034,11 +3040,123 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="d/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3052,13 +3170,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AV60" totalsRowShown="0">
-  <autoFilter ref="A2:AV60" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="3">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:AW60" totalsRowShown="0">
+  <autoFilter ref="A2:AW60" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="49">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NOMBRE PROYECTO"/>
@@ -3085,7 +3199,8 @@
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="SPI"/>
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
+    <tableColumn id="49" xr3:uid="{4504867D-40BB-4895-B8F9-7569A94E115D}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL" dataDxfId="2"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
@@ -3113,9 +3228,9 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AK18" totalsRowShown="0">
-  <autoFilter ref="A2:AK18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
-  <tableColumns count="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AL18" totalsRowShown="0">
+  <autoFilter ref="A2:AL18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <tableColumns count="38">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EJECUTOR"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="NOMBRE DEL PROYECTO"/>
@@ -3136,7 +3251,8 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="SPI"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION" dataDxfId="1"/>
+    <tableColumn id="38" xr3:uid="{5127B442-BBCD-41A9-9DD8-B336C15E70D5}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="0"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
@@ -3472,20 +3588,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV60"/>
+  <dimension ref="A1:AW60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
     <col min="3" max="3" width="33.6640625" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
-    <col min="5" max="39" width="25.6640625" customWidth="1"/>
-    <col min="40" max="40" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="41" max="45" width="25.6640625" customWidth="1"/>
-    <col min="46" max="46" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="47" max="48" width="25.6640625" customWidth="1"/>
+    <col min="5" max="40" width="25.6640625" customWidth="1"/>
+    <col min="41" max="41" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="42" max="46" width="25.6640625" customWidth="1"/>
+    <col min="47" max="47" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="48" max="49" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:48" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:49" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -3532,16 +3648,17 @@
       <c r="AN1" s="7"/>
       <c r="AO1" s="7"/>
       <c r="AP1" s="7"/>
-      <c r="AQ1" s="6" t="s">
+      <c r="AQ1" s="7"/>
+      <c r="AR1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AR1" s="6"/>
       <c r="AS1" s="6"/>
       <c r="AT1" s="6"/>
       <c r="AU1" s="6"/>
       <c r="AV1" s="6"/>
+      <c r="AW1" s="6"/>
     </row>
-    <row r="2" spans="1:48" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3621,73 +3738,76 @@
         <v>28</v>
       </c>
       <c r="AA2" s="2" t="s">
+        <v>916</v>
+      </c>
+      <c r="AB2" s="2" t="s">
         <v>917</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
@@ -3765,70 +3885,73 @@
       <c r="AA3" s="5">
         <v>42254</v>
       </c>
-      <c r="AB3" s="5">
+      <c r="AB3" s="8">
+        <v>42254</v>
+      </c>
+      <c r="AC3" s="5">
         <v>42277</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>45260</v>
       </c>
       <c r="AD3" s="5">
         <v>45260</v>
       </c>
       <c r="AE3" s="5">
+        <v>45260</v>
+      </c>
+      <c r="AF3" s="5">
         <v>46157</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AH3" s="5">
+      <c r="AI3" s="5">
         <v>46157</v>
       </c>
-      <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
-      <c r="AL3" s="3" t="str">
-        <f t="shared" ref="AL3:AL34" si="0">IF(AND($X3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X3&gt;1.25,$X3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X3&gt;1.2,$X3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X3&gt;=0.84,$X3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X3&gt;=0.38,$X3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($X3-0.38)/(0.84-0.38))*100,IF(AND($X3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AL3" s="3"/>
+      <c r="AM3" s="3" t="str">
+        <f t="shared" ref="AM3:AM34" si="0">IF(AND($X3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X3&gt;1.25,$X3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X3&gt;1.2,$X3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X3&gt;=0.84,$X3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X3&gt;=0.38,$X3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($X3-0.38)/(0.84-0.38))*100,IF(AND($X3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AM3" s="3" t="str">
-        <f t="shared" ref="AM3:AM34" si="1">IF(AND($W3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W3&gt;1.25,$W3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W3&gt;1.2,$W3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W3&gt;=0.84,$W3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W3&gt;=0.38,$W3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($W3-0.38)/(0.84-0.38))*100,IF(AND($W3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AN3" s="3" t="str">
+        <f t="shared" ref="AN3:AN34" si="1">IF(AND($W3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W3&gt;1.25,$W3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W3&gt;1.2,$W3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W3&gt;=0.84,$W3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W3&gt;=0.38,$W3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($W3-0.38)/(0.84-0.38))*100,IF(AND($W3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AN3" s="3">
-        <f t="shared" ref="AN3:AN34" si="2">IF(AND($V3&lt;60,($V3-$U3)&lt;=50),100,IF(AND($V3&lt;60,($V3-$U3)&gt;50),0,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&lt;=40),100,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&gt;40),0,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&lt;=30),100,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&gt;30),0,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&lt;=20),100,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&gt;20),0,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&lt;=10),100,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AO3" s="3" t="str">
-        <f t="shared" ref="AO3:AO34" si="3">IF(AND($U3&gt;$V3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V3&gt;$U3,($V3-$U3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&lt;=60),100,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&gt;60),$AN3,""))))</f>
+      <c r="AO3" s="3">
+        <f t="shared" ref="AO3:AO34" si="2">IF(AND($V3&lt;60,($V3-$U3)&lt;=50),100,IF(AND($V3&lt;60,($V3-$U3)&gt;50),0,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&lt;=40),100,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&gt;40),0,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&lt;=30),100,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&gt;30),0,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&lt;=20),100,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&gt;20),0,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&lt;=10),100,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AP3" s="3" t="str">
+        <f t="shared" ref="AP3:AP34" si="3">IF(AND($U3&gt;$V3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V3&gt;$U3,($V3-$U3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&lt;=60),100,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&gt;60),$AO3,""))))</f>
         <v/>
       </c>
-      <c r="AP3" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3">
-        <f t="shared" ref="AR3:AR34" si="4">IF(ISNUMBER($AH3),IF(DAY($AH3)=10,100,IF(DAY($AH3)=11,80,IF(DAY($AH3)=12,50,0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AS3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="3">
-        <f t="shared" ref="AT3:AT34" si="5">IF($AP3=0,100,IF($AP3=1,90,IF($AP3=2,75,IF($AP3=3,60,IF($AP3=4,50,IF($AP3=5,25,IF($AP3&gt;=6,0,"")))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AU3" s="3" t="str">
-        <f t="shared" ref="AU3:AU34" si="6">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AP3&gt;=1),(IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),""))*$AT3/100,IFERROR(IF(ISTEXT($AF3),($AL3*0.4+$AM3*0.2+$AO3*0.4),""),"")),0)</f>
+      <c r="AQ3" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="3"/>
+      <c r="AS3" s="3">
+        <f t="shared" ref="AS3:AS34" si="4">IF(ISNUMBER($AI3),IF(DAY($AI3)=10,100,IF(DAY($AI3)=11,80,IF(DAY($AI3)=12,50,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="3">
+        <f t="shared" ref="AU3:AU34" si="5">IF($AQ3=0,100,IF($AQ3=1,90,IF($AQ3=2,75,IF($AQ3=3,60,IF($AQ3=4,50,IF($AQ3=5,25,IF($AQ3&gt;=6,0,"")))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AV3" s="3" t="str">
+        <f t="shared" ref="AV3:AV34" si="6">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AQ3&gt;=1),(IFERROR(IF(ISTEXT($AG3),($AM3*0.4+$AN3*0.2+$AP3*0.4),""),""))*$AU3/100,IFERROR(IF(ISTEXT($AG3),($AM3*0.4+$AN3*0.2+$AP3*0.4),""),"")),0)</f>
         <v/>
       </c>
-      <c r="AV3" s="3" t="s">
+      <c r="AW3" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>63</v>
       </c>
@@ -3906,60 +4029,63 @@
       <c r="AA4" s="5">
         <v>41586</v>
       </c>
-      <c r="AB4" s="5">
+      <c r="AB4" s="8">
+        <v>41586</v>
+      </c>
+      <c r="AC4" s="5">
         <v>41803</v>
       </c>
-      <c r="AC4" s="5">
+      <c r="AD4" s="5">
         <v>44742</v>
       </c>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5">
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5">
         <v>46157</v>
       </c>
-      <c r="AF4" s="3"/>
       <c r="AG4" s="3"/>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="3"/>
+      <c r="AH4" s="3"/>
+      <c r="AI4" s="5"/>
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
-      <c r="AL4" s="3" t="str">
+      <c r="AL4" s="3"/>
+      <c r="AM4" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM4" s="3" t="str">
+      <c r="AN4" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN4" s="3">
+      <c r="AO4" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO4" s="3">
+      <c r="AP4" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="3"/>
-      <c r="AR4" s="3" t="str">
+      <c r="AQ4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR4" s="3"/>
+      <c r="AS4" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AS4" s="4"/>
-      <c r="AT4" s="3">
+      <c r="AT4" s="4"/>
+      <c r="AU4" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU4" s="3" t="str">
+      <c r="AV4" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV4" s="3" t="s">
+      <c r="AW4" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
@@ -4037,70 +4163,73 @@
       <c r="AA5" s="5">
         <v>41908</v>
       </c>
-      <c r="AB5" s="5">
+      <c r="AB5" s="8">
+        <v>41908</v>
+      </c>
+      <c r="AC5" s="5">
         <v>42038</v>
       </c>
-      <c r="AC5" s="5">
+      <c r="AD5" s="5">
         <v>44561</v>
       </c>
-      <c r="AD5" s="5">
+      <c r="AE5" s="5">
         <v>45689</v>
       </c>
-      <c r="AE5" s="5">
+      <c r="AF5" s="5">
         <v>46157</v>
       </c>
-      <c r="AF5" s="3" t="s">
+      <c r="AG5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="AG5" s="3" t="s">
+      <c r="AH5" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AH5" s="5">
+      <c r="AI5" s="5">
         <v>46157</v>
       </c>
-      <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
-      <c r="AL5" s="3" t="str">
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM5" s="3" t="str">
+      <c r="AN5" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN5" s="3">
+      <c r="AO5" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO5" s="3" t="str">
+      <c r="AP5" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP5" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="3"/>
-      <c r="AR5" s="3">
+      <c r="AQ5" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR5" s="3"/>
+      <c r="AS5" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT5" s="3">
+      <c r="AT5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU5" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU5" s="3" t="str">
+      <c r="AV5" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV5" s="3" t="s">
+      <c r="AW5" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="6" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>80</v>
       </c>
@@ -4182,68 +4311,71 @@
       <c r="AA6" s="5">
         <v>41586</v>
       </c>
-      <c r="AB6" s="5">
+      <c r="AB6" s="8">
         <v>41586</v>
       </c>
       <c r="AC6" s="5">
+        <v>41586</v>
+      </c>
+      <c r="AD6" s="5">
         <v>45260</v>
       </c>
-      <c r="AD6" s="5"/>
-      <c r="AE6" s="5">
+      <c r="AE6" s="5"/>
+      <c r="AF6" s="5">
         <v>46157</v>
       </c>
-      <c r="AF6" s="3" t="s">
+      <c r="AG6" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AG6" s="3" t="s">
+      <c r="AH6" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AH6" s="5">
+      <c r="AI6" s="5">
         <v>46157</v>
       </c>
-      <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
-      <c r="AL6" s="3">
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM6" s="3">
+      <c r="AN6" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN6" s="3">
+      <c r="AO6" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO6" s="3">
+      <c r="AP6" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ6" s="3"/>
-      <c r="AR6" s="3">
+      <c r="AQ6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="3"/>
+      <c r="AS6" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT6" s="3">
+      <c r="AT6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU6" s="3">
+      <c r="AV6" s="3">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AV6" s="3" t="s">
+      <c r="AW6" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>89</v>
       </c>
@@ -4321,70 +4453,73 @@
       <c r="AA7" s="5">
         <v>42986</v>
       </c>
-      <c r="AB7" s="5">
+      <c r="AB7" s="8">
+        <v>42986</v>
+      </c>
+      <c r="AC7" s="5">
         <v>43207</v>
-      </c>
-      <c r="AC7" s="5">
-        <v>45527</v>
       </c>
       <c r="AD7" s="5">
         <v>45527</v>
       </c>
       <c r="AE7" s="5">
+        <v>45527</v>
+      </c>
+      <c r="AF7" s="5">
         <v>46157</v>
       </c>
-      <c r="AF7" s="3" t="s">
+      <c r="AG7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AG7" s="3" t="s">
+      <c r="AH7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AH7" s="5">
+      <c r="AI7" s="5">
         <v>46152</v>
       </c>
-      <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
-      <c r="AL7" s="3" t="str">
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM7" s="3" t="str">
+      <c r="AN7" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN7" s="3">
+      <c r="AO7" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO7" s="3" t="str">
+      <c r="AP7" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP7" s="3">
+      <c r="AQ7" s="3">
         <v>1</v>
       </c>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="3">
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS7" s="4">
+      <c r="AT7" s="4">
         <v>50</v>
       </c>
-      <c r="AT7" s="3">
+      <c r="AU7" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU7" s="3" t="str">
+      <c r="AV7" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV7" s="3" t="s">
+      <c r="AW7" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>100</v>
       </c>
@@ -4462,70 +4597,73 @@
       <c r="AA8" s="5">
         <v>43095</v>
       </c>
-      <c r="AB8" s="5">
+      <c r="AB8" s="8">
+        <v>43095</v>
+      </c>
+      <c r="AC8" s="5">
         <v>43280</v>
-      </c>
-      <c r="AC8" s="5">
-        <v>44926</v>
       </c>
       <c r="AD8" s="5">
         <v>44926</v>
       </c>
       <c r="AE8" s="5">
+        <v>44926</v>
+      </c>
+      <c r="AF8" s="5">
         <v>46157</v>
       </c>
-      <c r="AF8" s="3" t="s">
+      <c r="AG8" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="AG8" s="3" t="s">
+      <c r="AH8" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AH8" s="5">
+      <c r="AI8" s="5">
         <v>46157</v>
       </c>
-      <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
-      <c r="AL8" s="3" t="str">
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM8" s="3" t="str">
+      <c r="AN8" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO8" s="3" t="str">
+      <c r="AP8" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3">
+      <c r="AQ8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT8" s="3">
+      <c r="AT8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU8" s="3" t="str">
+      <c r="AV8" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV8" s="3" t="s">
+      <c r="AW8" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>107</v>
       </c>
@@ -4607,70 +4745,73 @@
       <c r="AA9" s="5">
         <v>43532</v>
       </c>
-      <c r="AB9" s="5">
+      <c r="AB9" s="8">
+        <v>43532</v>
+      </c>
+      <c r="AC9" s="5">
         <v>43591</v>
-      </c>
-      <c r="AC9" s="5">
-        <v>45467</v>
       </c>
       <c r="AD9" s="5">
         <v>45467</v>
       </c>
       <c r="AE9" s="5">
+        <v>45467</v>
+      </c>
+      <c r="AF9" s="5">
         <v>46157</v>
       </c>
-      <c r="AF9" s="3" t="s">
+      <c r="AG9" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AG9" s="3" t="s">
+      <c r="AH9" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AH9" s="5">
+      <c r="AI9" s="5">
         <v>46152</v>
       </c>
-      <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
-      <c r="AL9" s="3">
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP9" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3">
+      <c r="AQ9" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT9" s="3">
+      <c r="AT9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU9" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU9" s="3">
+      <c r="AV9" s="3">
         <f t="shared" si="6"/>
         <v>40</v>
       </c>
-      <c r="AV9" s="3" t="s">
+      <c r="AW9" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>114</v>
       </c>
@@ -4748,70 +4889,73 @@
       <c r="AA10" s="5">
         <v>43826</v>
       </c>
-      <c r="AB10" s="5">
+      <c r="AB10" s="8">
+        <v>43826</v>
+      </c>
+      <c r="AC10" s="5">
         <v>43908</v>
-      </c>
-      <c r="AC10" s="5">
-        <v>44742</v>
       </c>
       <c r="AD10" s="5">
         <v>44742</v>
       </c>
       <c r="AE10" s="5">
+        <v>44742</v>
+      </c>
+      <c r="AF10" s="5">
         <v>46157</v>
       </c>
-      <c r="AF10" s="3" t="s">
+      <c r="AG10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="AG10" s="3" t="s">
+      <c r="AH10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH10" s="5">
+      <c r="AI10" s="5">
         <v>46157</v>
       </c>
-      <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
-      <c r="AL10" s="3" t="str">
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM10" s="3" t="str">
+      <c r="AN10" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO10" s="3" t="str">
+      <c r="AP10" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP10" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3">
+      <c r="AQ10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT10" s="3">
+      <c r="AT10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU10" s="3" t="str">
+      <c r="AV10" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV10" s="3" t="s">
+      <c r="AW10" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>121</v>
       </c>
@@ -4889,70 +5033,73 @@
       <c r="AA11" s="5">
         <v>43508</v>
       </c>
-      <c r="AB11" s="5">
+      <c r="AB11" s="8">
+        <v>43508</v>
+      </c>
+      <c r="AC11" s="5">
         <v>43543</v>
-      </c>
-      <c r="AC11" s="5">
-        <v>44592</v>
       </c>
       <c r="AD11" s="5">
         <v>44592</v>
       </c>
       <c r="AE11" s="5">
+        <v>44592</v>
+      </c>
+      <c r="AF11" s="5">
         <v>46157</v>
       </c>
-      <c r="AF11" s="3" t="s">
+      <c r="AG11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="AG11" s="3" t="s">
+      <c r="AH11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH11" s="5">
+      <c r="AI11" s="5">
         <v>46157</v>
       </c>
-      <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
-      <c r="AL11" s="3" t="str">
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM11" s="3" t="str">
+      <c r="AN11" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN11" s="3">
+      <c r="AO11" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO11" s="3">
+      <c r="AP11" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP11" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="3"/>
-      <c r="AR11" s="3">
+      <c r="AQ11" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT11" s="3">
+      <c r="AT11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU11" s="3" t="str">
+      <c r="AV11" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV11" s="3" t="s">
+      <c r="AW11" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>126</v>
       </c>
@@ -5030,70 +5177,73 @@
       <c r="AA12" s="5">
         <v>43753</v>
       </c>
-      <c r="AB12" s="5">
+      <c r="AB12" s="8">
+        <v>43753</v>
+      </c>
+      <c r="AC12" s="5">
         <v>43781</v>
-      </c>
-      <c r="AC12" s="5">
-        <v>45351</v>
       </c>
       <c r="AD12" s="5">
         <v>45351</v>
       </c>
       <c r="AE12" s="5">
+        <v>45351</v>
+      </c>
+      <c r="AF12" s="5">
         <v>46157</v>
       </c>
-      <c r="AF12" s="3" t="s">
+      <c r="AG12" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="AG12" s="3" t="s">
+      <c r="AH12" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="AH12" s="5">
+      <c r="AI12" s="5">
         <v>46152</v>
       </c>
-      <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
-      <c r="AL12" s="3" t="str">
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM12" s="3" t="str">
+      <c r="AN12" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO12" s="3" t="str">
+      <c r="AP12" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP12" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3">
+      <c r="AQ12" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT12" s="3">
+      <c r="AT12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU12" s="3" t="str">
+      <c r="AV12" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV12" s="3" t="s">
+      <c r="AW12" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>134</v>
       </c>
@@ -5175,68 +5325,71 @@
       <c r="AA13" s="5">
         <v>45289</v>
       </c>
-      <c r="AB13" s="5">
+      <c r="AB13" s="8">
+        <v>45289</v>
+      </c>
+      <c r="AC13" s="5">
         <v>45301</v>
       </c>
-      <c r="AC13" s="5">
+      <c r="AD13" s="5">
         <v>45987</v>
       </c>
-      <c r="AD13" s="5"/>
-      <c r="AE13" s="5">
+      <c r="AE13" s="5"/>
+      <c r="AF13" s="5">
         <v>46157</v>
       </c>
-      <c r="AF13" s="3" t="s">
+      <c r="AG13" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AG13" s="3" t="s">
+      <c r="AH13" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="AH13" s="5">
+      <c r="AI13" s="5">
         <v>46152</v>
       </c>
-      <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
-      <c r="AL13" s="3">
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM13" s="3">
+      <c r="AN13" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="3">
+      <c r="AO13" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO13" s="3">
+      <c r="AP13" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="3">
+      <c r="AQ13" s="3">
         <v>1</v>
       </c>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3">
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS13" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT13" s="3">
+      <c r="AT13" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU13" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU13" s="3">
+      <c r="AV13" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AV13" s="3" t="s">
+      <c r="AW13" s="3" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="14" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>144</v>
       </c>
@@ -5314,70 +5467,73 @@
       <c r="AA14" s="5">
         <v>44410</v>
       </c>
-      <c r="AB14" s="5">
+      <c r="AB14" s="8">
+        <v>44410</v>
+      </c>
+      <c r="AC14" s="5">
         <v>44504</v>
-      </c>
-      <c r="AC14" s="5">
-        <v>45577</v>
       </c>
       <c r="AD14" s="5">
         <v>45577</v>
       </c>
       <c r="AE14" s="5">
+        <v>45577</v>
+      </c>
+      <c r="AF14" s="5">
         <v>46157</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AG14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="AH14" s="5">
+      <c r="AI14" s="5">
         <v>46152</v>
       </c>
-      <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
-      <c r="AL14" s="3" t="str">
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM14" s="3" t="str">
+      <c r="AN14" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO14" s="3" t="str">
+      <c r="AP14" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>1</v>
       </c>
-      <c r="AQ14" s="3"/>
-      <c r="AR14" s="3">
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT14" s="3">
+      <c r="AT14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU14" s="3" t="str">
+      <c r="AV14" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV14" s="3" t="s">
+      <c r="AW14" s="3" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>151</v>
       </c>
@@ -5459,68 +5615,71 @@
       <c r="AA15" s="5">
         <v>44463</v>
       </c>
-      <c r="AB15" s="5">
+      <c r="AB15" s="8">
+        <v>44463</v>
+      </c>
+      <c r="AC15" s="5">
         <v>44545</v>
       </c>
-      <c r="AC15" s="5">
+      <c r="AD15" s="5">
         <v>46022</v>
       </c>
-      <c r="AD15" s="5"/>
-      <c r="AE15" s="5">
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5">
         <v>46157</v>
       </c>
-      <c r="AF15" s="3" t="s">
+      <c r="AG15" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="AG15" s="3" t="s">
+      <c r="AH15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH15" s="5">
+      <c r="AI15" s="5">
         <v>46157</v>
       </c>
-      <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
-      <c r="AL15" s="3">
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>1</v>
       </c>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3">
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS15" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="3">
+      <c r="AT15" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU15" s="3">
+      <c r="AV15" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AV15" s="3" t="s">
+      <c r="AW15" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>157</v>
       </c>
@@ -5598,70 +5757,73 @@
       <c r="AA16" s="5">
         <v>44902</v>
       </c>
-      <c r="AB16" s="5">
+      <c r="AB16" s="8">
+        <v>44902</v>
+      </c>
+      <c r="AC16" s="5">
         <v>44980</v>
-      </c>
-      <c r="AC16" s="5">
-        <v>45287</v>
       </c>
       <c r="AD16" s="5">
         <v>45287</v>
       </c>
       <c r="AE16" s="5">
+        <v>45287</v>
+      </c>
+      <c r="AF16" s="5">
         <v>46157</v>
       </c>
-      <c r="AF16" s="3" t="s">
+      <c r="AG16" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="AG16" s="3" t="s">
+      <c r="AH16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH16" s="5">
+      <c r="AI16" s="5">
         <v>46157</v>
       </c>
-      <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
-      <c r="AL16" s="3" t="str">
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM16" s="3" t="str">
+      <c r="AN16" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN16" s="3">
+      <c r="AO16" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO16" s="3">
+      <c r="AP16" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP16" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3">
+      <c r="AQ16" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="3"/>
+      <c r="AS16" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="3">
+      <c r="AT16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU16" s="3" t="str">
+      <c r="AV16" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV16" s="3" t="s">
+      <c r="AW16" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="17" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>163</v>
       </c>
@@ -5743,68 +5905,71 @@
       <c r="AA17" s="5">
         <v>45450</v>
       </c>
-      <c r="AB17" s="5">
+      <c r="AB17" s="8">
+        <v>45450</v>
+      </c>
+      <c r="AC17" s="5">
         <v>45469</v>
       </c>
-      <c r="AC17" s="5">
+      <c r="AD17" s="5">
         <v>46137</v>
       </c>
-      <c r="AD17" s="5"/>
-      <c r="AE17" s="5">
+      <c r="AE17" s="5"/>
+      <c r="AF17" s="5">
         <v>46157</v>
       </c>
-      <c r="AF17" s="3" t="s">
+      <c r="AG17" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="AG17" s="3" t="s">
+      <c r="AH17" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="AH17" s="5">
+      <c r="AI17" s="5">
         <v>46152</v>
       </c>
-      <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
-      <c r="AL17" s="3">
+      <c r="AL17" s="3"/>
+      <c r="AM17" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2</v>
       </c>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3">
+      <c r="AR17" s="3"/>
+      <c r="AS17" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS17" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT17" s="3">
+      <c r="AT17" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU17" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AU17" s="3">
+      <c r="AV17" s="3">
         <f t="shared" si="6"/>
         <v>75</v>
       </c>
-      <c r="AV17" s="3" t="s">
+      <c r="AW17" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>171</v>
       </c>
@@ -5886,68 +6051,71 @@
       <c r="AA18" s="5">
         <v>44833</v>
       </c>
-      <c r="AB18" s="5">
+      <c r="AB18" s="8">
+        <v>44833</v>
+      </c>
+      <c r="AC18" s="5">
         <v>44925</v>
       </c>
-      <c r="AC18" s="5">
+      <c r="AD18" s="5">
         <v>45549</v>
       </c>
-      <c r="AD18" s="5"/>
-      <c r="AE18" s="5">
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5">
         <v>46157</v>
       </c>
-      <c r="AF18" s="3" t="s">
+      <c r="AG18" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="AG18" s="3" t="s">
+      <c r="AH18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH18" s="5">
+      <c r="AI18" s="5">
         <v>46157</v>
       </c>
-      <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
-      <c r="AL18" s="3">
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1</v>
       </c>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3">
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT18" s="3">
+      <c r="AT18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU18" s="3">
+      <c r="AV18" s="3">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="AV18" s="3" t="s">
+      <c r="AW18" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>178</v>
       </c>
@@ -6029,68 +6197,71 @@
       <c r="AA19" s="5">
         <v>44833</v>
       </c>
-      <c r="AB19" s="5">
+      <c r="AB19" s="8">
+        <v>44833</v>
+      </c>
+      <c r="AC19" s="5">
         <v>44925</v>
       </c>
-      <c r="AC19" s="5">
+      <c r="AD19" s="5">
         <v>45549</v>
       </c>
-      <c r="AD19" s="5"/>
-      <c r="AE19" s="5">
+      <c r="AE19" s="5"/>
+      <c r="AF19" s="5">
         <v>46157</v>
       </c>
-      <c r="AF19" s="3" t="s">
+      <c r="AG19" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AG19" s="3" t="s">
+      <c r="AH19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH19" s="5">
+      <c r="AI19" s="5">
         <v>46157</v>
       </c>
-      <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
-      <c r="AL19" s="3">
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM19" s="3">
+      <c r="AN19" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN19" s="3">
+      <c r="AO19" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO19" s="3">
+      <c r="AP19" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP19" s="3">
+      <c r="AQ19" s="3">
         <v>1</v>
       </c>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3">
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT19" s="3">
+      <c r="AT19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU19" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU19" s="3">
+      <c r="AV19" s="3">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="AV19" s="3" t="s">
+      <c r="AW19" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>183</v>
       </c>
@@ -6168,70 +6339,73 @@
       <c r="AA20" s="5">
         <v>44833</v>
       </c>
-      <c r="AB20" s="5">
+      <c r="AB20" s="8">
+        <v>44833</v>
+      </c>
+      <c r="AC20" s="5">
         <v>44925</v>
-      </c>
-      <c r="AC20" s="5">
-        <v>45549</v>
       </c>
       <c r="AD20" s="5">
         <v>45549</v>
       </c>
       <c r="AE20" s="5">
+        <v>45549</v>
+      </c>
+      <c r="AF20" s="5">
         <v>46157</v>
       </c>
-      <c r="AF20" s="3" t="s">
+      <c r="AG20" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="AG20" s="3" t="s">
+      <c r="AH20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH20" s="5">
+      <c r="AI20" s="5">
         <v>46157</v>
       </c>
-      <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
-      <c r="AL20" s="3" t="str">
+      <c r="AL20" s="3"/>
+      <c r="AM20" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM20" s="3" t="str">
+      <c r="AN20" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN20" s="3" t="str">
+      <c r="AO20" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AO20" s="3" t="str">
+      <c r="AP20" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>1</v>
       </c>
-      <c r="AQ20" s="3"/>
-      <c r="AR20" s="3">
+      <c r="AR20" s="3"/>
+      <c r="AS20" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS20" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT20" s="3">
+      <c r="AT20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU20" s="3" t="str">
+      <c r="AV20" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV20" s="3" t="s">
+      <c r="AW20" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>188</v>
       </c>
@@ -6313,68 +6487,71 @@
       <c r="AA21" s="5">
         <v>44917</v>
       </c>
-      <c r="AB21" s="5">
+      <c r="AB21" s="8">
+        <v>44917</v>
+      </c>
+      <c r="AC21" s="5">
         <v>44998</v>
       </c>
-      <c r="AC21" s="5">
+      <c r="AD21" s="5">
         <v>45912</v>
       </c>
-      <c r="AD21" s="5"/>
-      <c r="AE21" s="5">
+      <c r="AE21" s="5"/>
+      <c r="AF21" s="5">
         <v>46157</v>
       </c>
-      <c r="AF21" s="3" t="s">
+      <c r="AG21" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AG21" s="3" t="s">
+      <c r="AH21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="AH21" s="5">
+      <c r="AI21" s="5">
         <v>46152</v>
       </c>
-      <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
-      <c r="AL21" s="3">
+      <c r="AL21" s="3"/>
+      <c r="AM21" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1</v>
       </c>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3">
+      <c r="AR21" s="3"/>
+      <c r="AS21" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS21" s="4">
+      <c r="AT21" s="4">
         <v>10</v>
       </c>
-      <c r="AT21" s="3">
+      <c r="AU21" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU21" s="3">
+      <c r="AV21" s="3">
         <f t="shared" si="6"/>
         <v>36</v>
       </c>
-      <c r="AV21" s="3" t="s">
+      <c r="AW21" s="3" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>196</v>
       </c>
@@ -6456,68 +6633,71 @@
       <c r="AA22" s="5">
         <v>45709</v>
       </c>
-      <c r="AB22" s="5">
+      <c r="AB22" s="8">
+        <v>45709</v>
+      </c>
+      <c r="AC22" s="5">
         <v>45714</v>
       </c>
-      <c r="AC22" s="5">
+      <c r="AD22" s="5">
         <v>46214</v>
       </c>
-      <c r="AD22" s="5"/>
-      <c r="AE22" s="5">
+      <c r="AE22" s="5"/>
+      <c r="AF22" s="5">
         <v>46157</v>
       </c>
-      <c r="AF22" s="3" t="s">
+      <c r="AG22" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="AG22" s="3" t="s">
+      <c r="AH22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="AH22" s="5">
+      <c r="AI22" s="5">
         <v>46152</v>
       </c>
-      <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
-      <c r="AL22" s="3">
+      <c r="AL22" s="3"/>
+      <c r="AM22" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>1</v>
       </c>
-      <c r="AQ22" s="3"/>
-      <c r="AR22" s="3">
+      <c r="AR22" s="3"/>
+      <c r="AS22" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS22" s="4">
+      <c r="AT22" s="4">
         <v>90</v>
       </c>
-      <c r="AT22" s="3">
+      <c r="AU22" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU22" s="3">
+      <c r="AV22" s="3">
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="AV22" s="3" t="s">
+      <c r="AW22" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="23" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>204</v>
       </c>
@@ -6595,64 +6775,67 @@
       <c r="AA23" s="5">
         <v>44817</v>
       </c>
-      <c r="AB23" s="5">
+      <c r="AB23" s="8">
+        <v>44817</v>
+      </c>
+      <c r="AC23" s="5">
         <v>44869</v>
-      </c>
-      <c r="AC23" s="5">
-        <v>45407</v>
       </c>
       <c r="AD23" s="5">
         <v>45407</v>
       </c>
       <c r="AE23" s="5">
+        <v>45407</v>
+      </c>
+      <c r="AF23" s="5">
         <v>46157</v>
       </c>
-      <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
-      <c r="AH23" s="5">
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="5">
         <v>46152</v>
       </c>
-      <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
-      <c r="AL23" s="3" t="str">
+      <c r="AL23" s="3"/>
+      <c r="AM23" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM23" s="3" t="str">
+      <c r="AN23" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO23" s="3" t="str">
+      <c r="AP23" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1</v>
       </c>
-      <c r="AQ23" s="3"/>
-      <c r="AR23" s="3">
+      <c r="AR23" s="3"/>
+      <c r="AS23" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS23" s="4"/>
-      <c r="AT23" s="3">
+      <c r="AT23" s="4"/>
+      <c r="AU23" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU23" s="3" t="str">
+      <c r="AV23" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV23" s="3" t="s">
+      <c r="AW23" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="24" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>210</v>
       </c>
@@ -6730,64 +6913,67 @@
       <c r="AA24" s="5">
         <v>44475</v>
       </c>
-      <c r="AB24" s="5">
+      <c r="AB24" s="8">
+        <v>44475</v>
+      </c>
+      <c r="AC24" s="5">
         <v>44495</v>
-      </c>
-      <c r="AC24" s="5">
-        <v>44651</v>
       </c>
       <c r="AD24" s="5">
         <v>44651</v>
       </c>
       <c r="AE24" s="5">
+        <v>44651</v>
+      </c>
+      <c r="AF24" s="5">
         <v>46157</v>
       </c>
-      <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
-      <c r="AH24" s="5">
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="5">
         <v>46152</v>
       </c>
-      <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
-      <c r="AL24" s="3" t="str">
+      <c r="AL24" s="3"/>
+      <c r="AM24" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM24" s="3" t="str">
+      <c r="AN24" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO24" s="3" t="str">
+      <c r="AP24" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP24" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ24" s="3"/>
-      <c r="AR24" s="3">
+      <c r="AQ24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR24" s="3"/>
+      <c r="AS24" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS24" s="4"/>
-      <c r="AT24" s="3">
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU24" s="3" t="str">
+      <c r="AV24" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV24" s="3" t="s">
+      <c r="AW24" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="25" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>218</v>
       </c>
@@ -6865,62 +7051,65 @@
       <c r="AA25" s="5">
         <v>44687</v>
       </c>
-      <c r="AB25" s="5">
+      <c r="AB25" s="8">
+        <v>44687</v>
+      </c>
+      <c r="AC25" s="5">
         <v>44698</v>
-      </c>
-      <c r="AC25" s="5">
-        <v>45046</v>
       </c>
       <c r="AD25" s="5">
         <v>45046</v>
       </c>
       <c r="AE25" s="5">
+        <v>45046</v>
+      </c>
+      <c r="AF25" s="5">
         <v>46157</v>
       </c>
-      <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
-      <c r="AH25" s="5"/>
-      <c r="AI25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="5"/>
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
-      <c r="AL25" s="3" t="str">
+      <c r="AL25" s="3"/>
+      <c r="AM25" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM25" s="3" t="str">
+      <c r="AN25" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN25" s="3">
+      <c r="AO25" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO25" s="3" t="str">
+      <c r="AP25" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ25" s="3"/>
-      <c r="AR25" s="3" t="str">
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR25" s="3"/>
+      <c r="AS25" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AS25" s="4"/>
-      <c r="AT25" s="3">
+      <c r="AT25" s="4"/>
+      <c r="AU25" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU25" s="3" t="str">
+      <c r="AV25" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV25" s="3" t="s">
+      <c r="AW25" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="26" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>223</v>
       </c>
@@ -7002,68 +7191,71 @@
       <c r="AA26" s="5">
         <v>45433</v>
       </c>
-      <c r="AB26" s="5">
+      <c r="AB26" s="8">
+        <v>45433</v>
+      </c>
+      <c r="AC26" s="5">
         <v>45509</v>
       </c>
-      <c r="AC26" s="5">
+      <c r="AD26" s="5">
         <v>46204</v>
       </c>
-      <c r="AD26" s="5"/>
-      <c r="AE26" s="5">
+      <c r="AE26" s="5"/>
+      <c r="AF26" s="5">
         <v>46157</v>
       </c>
-      <c r="AF26" s="3" t="s">
+      <c r="AG26" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="AG26" s="3" t="s">
+      <c r="AH26" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="AH26" s="5">
+      <c r="AI26" s="5">
         <v>46152</v>
       </c>
-      <c r="AI26" s="3"/>
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
-      <c r="AL26" s="3">
+      <c r="AL26" s="3"/>
+      <c r="AM26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>2</v>
       </c>
-      <c r="AQ26" s="3"/>
-      <c r="AR26" s="3">
+      <c r="AR26" s="3"/>
+      <c r="AS26" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS26" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT26" s="3">
+      <c r="AT26" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU26" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AU26" s="3">
+      <c r="AV26" s="3">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="AV26" s="3" t="s">
+      <c r="AW26" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="27" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>231</v>
       </c>
@@ -7141,70 +7333,73 @@
       <c r="AA27" s="5">
         <v>45028</v>
       </c>
-      <c r="AB27" s="5">
+      <c r="AB27" s="8">
         <v>45028</v>
       </c>
       <c r="AC27" s="5">
-        <v>45412</v>
+        <v>45028</v>
       </c>
       <c r="AD27" s="5">
         <v>45412</v>
       </c>
       <c r="AE27" s="5">
+        <v>45412</v>
+      </c>
+      <c r="AF27" s="5">
         <v>46157</v>
       </c>
-      <c r="AF27" s="3" t="s">
+      <c r="AG27" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="AG27" s="3" t="s">
+      <c r="AH27" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="AH27" s="5">
+      <c r="AI27" s="5">
         <v>46157</v>
       </c>
-      <c r="AI27" s="3"/>
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
-      <c r="AL27" s="3" t="str">
+      <c r="AL27" s="3"/>
+      <c r="AM27" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM27" s="3" t="str">
+      <c r="AN27" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO27" s="3" t="str">
+      <c r="AP27" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1</v>
       </c>
-      <c r="AQ27" s="3"/>
-      <c r="AR27" s="3">
+      <c r="AR27" s="3"/>
+      <c r="AS27" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AS27" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT27" s="3">
+      <c r="AT27" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU27" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU27" s="3" t="str">
+      <c r="AV27" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV27" s="3" t="s">
+      <c r="AW27" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>237</v>
       </c>
@@ -7282,68 +7477,71 @@
       <c r="AA28" s="5">
         <v>45107</v>
       </c>
-      <c r="AB28" s="5">
+      <c r="AB28" s="8">
+        <v>45107</v>
+      </c>
+      <c r="AC28" s="5">
         <v>45139</v>
-      </c>
-      <c r="AC28" s="5">
-        <v>45746</v>
       </c>
       <c r="AD28" s="5">
         <v>45746</v>
       </c>
       <c r="AE28" s="5">
+        <v>45746</v>
+      </c>
+      <c r="AF28" s="5">
         <v>46157</v>
       </c>
-      <c r="AF28" s="3" t="s">
+      <c r="AG28" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="AG28" s="3" t="s">
+      <c r="AH28" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="AH28" s="5">
+      <c r="AI28" s="5">
         <v>46152</v>
       </c>
-      <c r="AI28" s="3"/>
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
-      <c r="AL28" s="3" t="str">
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM28" s="3" t="str">
+      <c r="AN28" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN28" s="3">
+      <c r="AO28" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO28" s="3" t="str">
+      <c r="AP28" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP28" s="3">
+      <c r="AQ28" s="3">
         <v>1</v>
       </c>
-      <c r="AQ28" s="3"/>
-      <c r="AR28" s="3">
+      <c r="AR28" s="3"/>
+      <c r="AS28" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS28" s="4"/>
-      <c r="AT28" s="3">
+      <c r="AT28" s="4"/>
+      <c r="AU28" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU28" s="3" t="str">
+      <c r="AV28" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV28" s="3" t="s">
+      <c r="AW28" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>243</v>
       </c>
@@ -7421,70 +7619,73 @@
       <c r="AA29" s="5">
         <v>45054</v>
       </c>
-      <c r="AB29" s="5">
+      <c r="AB29" s="8">
+        <v>45054</v>
+      </c>
+      <c r="AC29" s="5">
         <v>45111</v>
-      </c>
-      <c r="AC29" s="5">
-        <v>45858</v>
       </c>
       <c r="AD29" s="5">
         <v>45858</v>
       </c>
       <c r="AE29" s="5">
+        <v>45858</v>
+      </c>
+      <c r="AF29" s="5">
         <v>46157</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="AG29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="AH29" s="5">
+      <c r="AI29" s="5">
         <v>46152</v>
       </c>
-      <c r="AI29" s="3"/>
       <c r="AJ29" s="3"/>
       <c r="AK29" s="3"/>
-      <c r="AL29" s="3" t="str">
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM29" s="3" t="str">
+      <c r="AN29" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO29" s="3" t="str">
+      <c r="AP29" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP29" s="3">
+      <c r="AQ29" s="3">
         <v>2</v>
       </c>
-      <c r="AQ29" s="3"/>
-      <c r="AR29" s="3">
+      <c r="AR29" s="3"/>
+      <c r="AS29" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS29" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT29" s="3">
+      <c r="AT29" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU29" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AU29" s="3" t="str">
+      <c r="AV29" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV29" s="3" t="s">
+      <c r="AW29" s="3" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="30" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>250</v>
       </c>
@@ -7562,64 +7763,67 @@
       <c r="AA30" s="5">
         <v>45077</v>
       </c>
-      <c r="AB30" s="5">
+      <c r="AB30" s="8">
+        <v>45077</v>
+      </c>
+      <c r="AC30" s="5">
         <v>45112</v>
-      </c>
-      <c r="AC30" s="5">
-        <v>45569</v>
       </c>
       <c r="AD30" s="5">
         <v>45569</v>
       </c>
       <c r="AE30" s="5">
+        <v>45569</v>
+      </c>
+      <c r="AF30" s="5">
         <v>46157</v>
       </c>
-      <c r="AF30" s="3" t="s">
+      <c r="AG30" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="AG30" s="3"/>
-      <c r="AH30" s="5"/>
-      <c r="AI30" s="3"/>
+      <c r="AH30" s="3"/>
+      <c r="AI30" s="5"/>
       <c r="AJ30" s="3"/>
       <c r="AK30" s="3"/>
-      <c r="AL30" s="3" t="str">
+      <c r="AL30" s="3"/>
+      <c r="AM30" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM30" s="3" t="str">
+      <c r="AN30" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN30" s="3">
+      <c r="AO30" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO30" s="3" t="str">
+      <c r="AP30" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP30" s="3">
+      <c r="AQ30" s="3">
         <v>1</v>
       </c>
-      <c r="AQ30" s="3"/>
-      <c r="AR30" s="3" t="str">
+      <c r="AR30" s="3"/>
+      <c r="AS30" s="3" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AS30" s="4"/>
-      <c r="AT30" s="3">
+      <c r="AT30" s="4"/>
+      <c r="AU30" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU30" s="3" t="str">
+      <c r="AV30" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV30" s="3" t="s">
+      <c r="AW30" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="31" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>254</v>
       </c>
@@ -7697,68 +7901,71 @@
       <c r="AA31" s="5">
         <v>45348</v>
       </c>
-      <c r="AB31" s="5">
+      <c r="AB31" s="8">
+        <v>45348</v>
+      </c>
+      <c r="AC31" s="5">
         <v>45426</v>
-      </c>
-      <c r="AC31" s="5">
-        <v>45900</v>
       </c>
       <c r="AD31" s="5">
         <v>45900</v>
       </c>
       <c r="AE31" s="5">
+        <v>45900</v>
+      </c>
+      <c r="AF31" s="5">
         <v>46157</v>
       </c>
-      <c r="AF31" s="3" t="s">
+      <c r="AG31" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="AG31" s="3" t="s">
+      <c r="AH31" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="AH31" s="5">
+      <c r="AI31" s="5">
         <v>46152</v>
       </c>
-      <c r="AI31" s="3"/>
       <c r="AJ31" s="3"/>
       <c r="AK31" s="3"/>
-      <c r="AL31" s="3" t="str">
+      <c r="AL31" s="3"/>
+      <c r="AM31" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM31" s="3" t="str">
+      <c r="AN31" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN31" s="3">
+      <c r="AO31" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO31" s="3" t="str">
+      <c r="AP31" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP31" s="3">
+      <c r="AQ31" s="3">
         <v>2</v>
       </c>
-      <c r="AQ31" s="3"/>
-      <c r="AR31" s="3">
+      <c r="AR31" s="3"/>
+      <c r="AS31" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS31" s="4"/>
-      <c r="AT31" s="3">
+      <c r="AT31" s="4"/>
+      <c r="AU31" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AU31" s="3" t="str">
+      <c r="AV31" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV31" s="3" t="s">
+      <c r="AW31" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="32" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>260</v>
       </c>
@@ -7840,68 +8047,71 @@
       <c r="AA32" s="5">
         <v>45793</v>
       </c>
-      <c r="AB32" s="5">
+      <c r="AB32" s="8">
+        <v>45793</v>
+      </c>
+      <c r="AC32" s="5">
         <v>45847</v>
       </c>
-      <c r="AC32" s="5">
+      <c r="AD32" s="5">
         <v>46151</v>
       </c>
-      <c r="AD32" s="5"/>
-      <c r="AE32" s="5">
+      <c r="AE32" s="5"/>
+      <c r="AF32" s="5">
         <v>46157</v>
       </c>
-      <c r="AF32" s="3" t="s">
+      <c r="AG32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="AG32" s="3" t="s">
+      <c r="AH32" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="AH32" s="5">
+      <c r="AI32" s="5">
         <v>46152</v>
       </c>
-      <c r="AI32" s="3"/>
       <c r="AJ32" s="3"/>
       <c r="AK32" s="3"/>
-      <c r="AL32" s="3">
+      <c r="AL32" s="3"/>
+      <c r="AM32" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ32" s="3"/>
-      <c r="AR32" s="3">
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR32" s="3"/>
+      <c r="AS32" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS32" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT32" s="3">
+      <c r="AT32" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU32" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AU32" s="3">
+      <c r="AV32" s="3">
         <f t="shared" si="6"/>
         <v>100</v>
       </c>
-      <c r="AV32" s="3" t="s">
+      <c r="AW32" s="3" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="33" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>268</v>
       </c>
@@ -7983,68 +8193,71 @@
       <c r="AA33" s="5">
         <v>45188</v>
       </c>
-      <c r="AB33" s="5">
+      <c r="AB33" s="8">
+        <v>45188</v>
+      </c>
+      <c r="AC33" s="5">
         <v>45202</v>
       </c>
-      <c r="AC33" s="5">
+      <c r="AD33" s="5">
         <v>46056</v>
       </c>
-      <c r="AD33" s="5"/>
-      <c r="AE33" s="5">
+      <c r="AE33" s="5"/>
+      <c r="AF33" s="5">
         <v>46157</v>
       </c>
-      <c r="AF33" s="3" t="s">
+      <c r="AG33" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="AG33" s="3" t="s">
+      <c r="AH33" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="AH33" s="5">
+      <c r="AI33" s="5">
         <v>46152</v>
       </c>
-      <c r="AI33" s="3"/>
       <c r="AJ33" s="3"/>
       <c r="AK33" s="3"/>
-      <c r="AL33" s="3">
+      <c r="AL33" s="3"/>
+      <c r="AM33" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>3</v>
       </c>
-      <c r="AQ33" s="3"/>
-      <c r="AR33" s="3">
+      <c r="AR33" s="3"/>
+      <c r="AS33" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS33" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT33" s="3">
+      <c r="AT33" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU33" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="AU33" s="3">
+      <c r="AV33" s="3">
         <f t="shared" si="6"/>
         <v>24</v>
       </c>
-      <c r="AV33" s="3" t="s">
+      <c r="AW33" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="34" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>277</v>
       </c>
@@ -8122,68 +8335,71 @@
       <c r="AA34" s="5">
         <v>45386</v>
       </c>
-      <c r="AB34" s="5">
+      <c r="AB34" s="8">
+        <v>45386</v>
+      </c>
+      <c r="AC34" s="5">
         <v>45411</v>
-      </c>
-      <c r="AC34" s="5">
-        <v>45716</v>
       </c>
       <c r="AD34" s="5">
         <v>45716</v>
       </c>
       <c r="AE34" s="5">
+        <v>45716</v>
+      </c>
+      <c r="AF34" s="5">
         <v>46157</v>
       </c>
-      <c r="AF34" s="3" t="s">
+      <c r="AG34" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="AG34" s="3" t="s">
+      <c r="AH34" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="AH34" s="5">
+      <c r="AI34" s="5">
         <v>46152</v>
       </c>
-      <c r="AI34" s="3"/>
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
-      <c r="AL34" s="3" t="str">
+      <c r="AL34" s="3"/>
+      <c r="AM34" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AM34" s="3" t="str">
+      <c r="AN34" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AN34" s="3">
+      <c r="AO34" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AO34" s="3" t="str">
+      <c r="AP34" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AP34" s="3">
+      <c r="AQ34" s="3">
         <v>1</v>
       </c>
-      <c r="AQ34" s="3"/>
-      <c r="AR34" s="3">
+      <c r="AR34" s="3"/>
+      <c r="AS34" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AS34" s="4"/>
-      <c r="AT34" s="3">
+      <c r="AT34" s="4"/>
+      <c r="AU34" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AU34" s="3" t="str">
+      <c r="AV34" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AV34" s="3" t="s">
+      <c r="AW34" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>283</v>
       </c>
@@ -8259,62 +8475,65 @@
       <c r="AA35" s="5">
         <v>45223</v>
       </c>
-      <c r="AB35" s="5">
+      <c r="AB35" s="8">
         <v>45223</v>
       </c>
       <c r="AC35" s="5">
-        <v>45288</v>
+        <v>45223</v>
       </c>
       <c r="AD35" s="5">
         <v>45288</v>
       </c>
       <c r="AE35" s="5">
+        <v>45288</v>
+      </c>
+      <c r="AF35" s="5">
         <v>46157</v>
       </c>
-      <c r="AF35" s="3"/>
       <c r="AG35" s="3"/>
-      <c r="AH35" s="5"/>
-      <c r="AI35" s="3"/>
+      <c r="AH35" s="3"/>
+      <c r="AI35" s="5"/>
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
-      <c r="AL35" s="3" t="str">
-        <f t="shared" ref="AL35:AL60" si="7">IF(AND($X35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X35&gt;1.25,$X35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X35&gt;1.2,$X35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X35&gt;=0.84,$X35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X35&gt;=0.38,$X35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($X35-0.38)/(0.84-0.38))*100,IF(AND($X35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AL35" s="3"/>
+      <c r="AM35" s="3" t="str">
+        <f t="shared" ref="AM35:AM60" si="7">IF(AND($X35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X35&gt;1.25,$X35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X35&gt;1.2,$X35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X35&gt;=0.84,$X35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X35&gt;=0.38,$X35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($X35-0.38)/(0.84-0.38))*100,IF(AND($X35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AM35" s="3" t="str">
-        <f t="shared" ref="AM35:AM60" si="8">IF(AND($W35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W35&gt;1.25,$W35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W35&gt;1.2,$W35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W35&gt;=0.84,$W35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W35&gt;=0.38,$W35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($W35-0.38)/(0.84-0.38))*100,IF(AND($W35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AN35" s="3" t="str">
+        <f t="shared" ref="AN35:AN60" si="8">IF(AND($W35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W35&gt;1.25,$W35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W35&gt;1.2,$W35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W35&gt;=0.84,$W35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W35&gt;=0.38,$W35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($W35-0.38)/(0.84-0.38))*100,IF(AND($W35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AN35" s="3">
-        <f t="shared" ref="AN35:AN60" si="9">IF(AND($V35&lt;60,($V35-$U35)&lt;=50),100,IF(AND($V35&lt;60,($V35-$U35)&gt;50),0,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&lt;=40),100,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&gt;40),0,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&lt;=30),100,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&gt;30),0,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&lt;=20),100,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&gt;20),0,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&lt;=10),100,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AO35" s="3" t="str">
-        <f t="shared" ref="AO35:AO60" si="10">IF(AND($U35&gt;$V35,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V35&gt;$U35,($V35-$U35)&gt;50,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&lt;=60),100,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&gt;60),$AN35,""))))</f>
+      <c r="AO35" s="3">
+        <f t="shared" ref="AO35:AO60" si="9">IF(AND($V35&lt;60,($V35-$U35)&lt;=50),100,IF(AND($V35&lt;60,($V35-$U35)&gt;50),0,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&lt;=40),100,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&gt;40),0,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&lt;=30),100,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&gt;30),0,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&lt;=20),100,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&gt;20),0,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&lt;=10),100,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AP35" s="3" t="str">
+        <f t="shared" ref="AP35:AP60" si="10">IF(AND($U35&gt;$V35,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V35&gt;$U35,($V35-$U35)&gt;50,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&lt;=60),100,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&gt;60),$AO35,""))))</f>
         <v/>
       </c>
-      <c r="AP35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ35" s="3"/>
-      <c r="AR35" s="3" t="str">
-        <f t="shared" ref="AR35:AR60" si="11">IF(ISNUMBER($AH35),IF(DAY($AH35)=10,100,IF(DAY($AH35)=11,80,IF(DAY($AH35)=12,50,0))),"")</f>
+      <c r="AQ35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR35" s="3"/>
+      <c r="AS35" s="3" t="str">
+        <f t="shared" ref="AS35:AS60" si="11">IF(ISNUMBER($AI35),IF(DAY($AI35)=10,100,IF(DAY($AI35)=11,80,IF(DAY($AI35)=12,50,0))),"")</f>
         <v/>
       </c>
-      <c r="AS35" s="4"/>
-      <c r="AT35" s="3">
-        <f t="shared" ref="AT35:AT60" si="12">IF($AP35=0,100,IF($AP35=1,90,IF($AP35=2,75,IF($AP35=3,60,IF($AP35=4,50,IF($AP35=5,25,IF($AP35&gt;=6,0,"")))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AU35" s="3" t="str">
-        <f t="shared" ref="AU35:AU60" si="13">IFERROR(IF(AND($G35="CONTRATADO EN EJECUCIÓN",$AP35&gt;=1),(IFERROR(IF(ISTEXT($AF35),($AL35*0.4+$AM35*0.2+$AO35*0.4),""),""))*$AT35/100,IFERROR(IF(ISTEXT($AF35),($AL35*0.4+$AM35*0.2+$AO35*0.4),""),"")),0)</f>
+      <c r="AT35" s="4"/>
+      <c r="AU35" s="3">
+        <f t="shared" ref="AU35:AU60" si="12">IF($AQ35=0,100,IF($AQ35=1,90,IF($AQ35=2,75,IF($AQ35=3,60,IF($AQ35=4,50,IF($AQ35=5,25,IF($AQ35&gt;=6,0,"")))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AV35" s="3" t="str">
+        <f t="shared" ref="AV35:AV60" si="13">IFERROR(IF(AND($G35="CONTRATADO EN EJECUCIÓN",$AQ35&gt;=1),(IFERROR(IF(ISTEXT($AG35),($AM35*0.4+$AN35*0.2+$AP35*0.4),""),""))*$AU35/100,IFERROR(IF(ISTEXT($AG35),($AM35*0.4+$AN35*0.2+$AP35*0.4),""),"")),0)</f>
         <v/>
       </c>
-      <c r="AV35" s="3" t="s">
+      <c r="AW35" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>288</v>
       </c>
@@ -8394,68 +8613,71 @@
       <c r="AA36" s="5">
         <v>45953</v>
       </c>
-      <c r="AB36" s="5">
+      <c r="AB36" s="8">
+        <v>45953</v>
+      </c>
+      <c r="AC36" s="5">
         <v>45967</v>
       </c>
-      <c r="AC36" s="5">
+      <c r="AD36" s="5">
         <v>46727</v>
       </c>
-      <c r="AD36" s="5"/>
-      <c r="AE36" s="5">
+      <c r="AE36" s="5"/>
+      <c r="AF36" s="5">
         <v>46157</v>
       </c>
-      <c r="AF36" s="3" t="s">
+      <c r="AG36" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AG36" s="3" t="s">
+      <c r="AH36" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="AH36" s="5">
+      <c r="AI36" s="5">
         <v>46152</v>
       </c>
-      <c r="AI36" s="3"/>
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
-      <c r="AL36" s="3">
+      <c r="AL36" s="3"/>
+      <c r="AM36" s="3">
         <f t="shared" si="7"/>
         <v>71.739130434782609</v>
       </c>
-      <c r="AM36" s="3">
+      <c r="AN36" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN36" s="3">
+      <c r="AO36" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO36" s="3">
+      <c r="AP36" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP36" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ36" s="3"/>
-      <c r="AR36" s="3">
+      <c r="AQ36" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR36" s="3"/>
+      <c r="AS36" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS36" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT36" s="3">
+      <c r="AT36" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU36" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU36" s="3">
+      <c r="AV36" s="3">
         <f t="shared" si="13"/>
         <v>88.695652173913047</v>
       </c>
-      <c r="AV36" s="3" t="s">
+      <c r="AW36" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="37" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>295</v>
       </c>
@@ -8533,70 +8755,73 @@
       <c r="AA37" s="5">
         <v>45427</v>
       </c>
-      <c r="AB37" s="5">
+      <c r="AB37" s="8">
+        <v>45427</v>
+      </c>
+      <c r="AC37" s="5">
         <v>45440</v>
       </c>
-      <c r="AC37" s="5">
+      <c r="AD37" s="5">
         <v>45900</v>
       </c>
-      <c r="AD37" s="5">
+      <c r="AE37" s="5">
         <v>45968</v>
       </c>
-      <c r="AE37" s="5">
+      <c r="AF37" s="5">
         <v>46157</v>
       </c>
-      <c r="AF37" s="3" t="s">
+      <c r="AG37" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="AG37" s="3" t="s">
+      <c r="AH37" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="AH37" s="5">
+      <c r="AI37" s="5">
         <v>46155</v>
       </c>
-      <c r="AI37" s="3"/>
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
-      <c r="AL37" s="3" t="str">
+      <c r="AL37" s="3"/>
+      <c r="AM37" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM37" s="3" t="str">
+      <c r="AN37" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN37" s="3">
+      <c r="AO37" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO37" s="3">
+      <c r="AP37" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP37" s="3">
+      <c r="AQ37" s="3">
         <v>1</v>
       </c>
-      <c r="AQ37" s="3"/>
-      <c r="AR37" s="3">
+      <c r="AR37" s="3"/>
+      <c r="AS37" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS37" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT37" s="3">
+      <c r="AT37" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU37" s="3">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AU37" s="3" t="str">
+      <c r="AV37" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV37" s="3" t="s">
+      <c r="AW37" s="3" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="38" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>302</v>
       </c>
@@ -8678,68 +8903,71 @@
       <c r="AA38" s="5">
         <v>45573</v>
       </c>
-      <c r="AB38" s="5">
+      <c r="AB38" s="8">
+        <v>45573</v>
+      </c>
+      <c r="AC38" s="5">
         <v>45616</v>
       </c>
-      <c r="AC38" s="5">
+      <c r="AD38" s="5">
         <v>46177</v>
       </c>
-      <c r="AD38" s="5"/>
-      <c r="AE38" s="5">
+      <c r="AE38" s="5"/>
+      <c r="AF38" s="5">
         <v>46157</v>
       </c>
-      <c r="AF38" s="3" t="s">
+      <c r="AG38" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="AG38" s="3" t="s">
+      <c r="AH38" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="AH38" s="5">
+      <c r="AI38" s="5">
         <v>46152</v>
       </c>
-      <c r="AI38" s="3"/>
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
-      <c r="AL38" s="3">
+      <c r="AL38" s="3"/>
+      <c r="AM38" s="3">
         <f t="shared" si="7"/>
         <v>69.565217391304344</v>
       </c>
-      <c r="AM38" s="3">
+      <c r="AN38" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN38" s="3">
+      <c r="AO38" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO38" s="3">
+      <c r="AP38" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP38" s="3">
+      <c r="AQ38" s="3">
         <v>1</v>
       </c>
-      <c r="AQ38" s="3"/>
-      <c r="AR38" s="3">
+      <c r="AR38" s="3"/>
+      <c r="AS38" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS38" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT38" s="3">
+      <c r="AT38" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU38" s="3">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AU38" s="3">
+      <c r="AV38" s="3">
         <f t="shared" si="13"/>
         <v>79.043478260869563</v>
       </c>
-      <c r="AV38" s="3" t="s">
+      <c r="AW38" s="3" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="39" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>309</v>
       </c>
@@ -8817,70 +9045,73 @@
       <c r="AA39" s="5">
         <v>45575</v>
       </c>
-      <c r="AB39" s="5">
+      <c r="AB39" s="8">
+        <v>45575</v>
+      </c>
+      <c r="AC39" s="5">
         <v>45580</v>
-      </c>
-      <c r="AC39" s="5">
-        <v>45656</v>
       </c>
       <c r="AD39" s="5">
         <v>45656</v>
       </c>
       <c r="AE39" s="5">
+        <v>45656</v>
+      </c>
+      <c r="AF39" s="5">
         <v>46157</v>
       </c>
-      <c r="AF39" s="3" t="s">
+      <c r="AG39" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="AG39" s="3" t="s">
+      <c r="AH39" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AH39" s="5">
+      <c r="AI39" s="5">
         <v>46157</v>
       </c>
-      <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
-      <c r="AL39" s="3" t="str">
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM39" s="3" t="str">
+      <c r="AN39" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN39" s="3">
+      <c r="AO39" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO39" s="3" t="str">
+      <c r="AP39" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP39" s="3">
+      <c r="AQ39" s="3">
         <v>1</v>
       </c>
-      <c r="AQ39" s="3"/>
-      <c r="AR39" s="3">
+      <c r="AR39" s="3"/>
+      <c r="AS39" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS39" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT39" s="3">
+      <c r="AT39" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU39" s="3">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AU39" s="3" t="str">
+      <c r="AV39" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV39" s="3" t="s">
+      <c r="AW39" s="3" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="40" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>316</v>
       </c>
@@ -8962,68 +9193,71 @@
       <c r="AA40" s="5">
         <v>45994</v>
       </c>
-      <c r="AB40" s="5">
+      <c r="AB40" s="8">
+        <v>45994</v>
+      </c>
+      <c r="AC40" s="5">
         <v>46006</v>
       </c>
-      <c r="AC40" s="5">
+      <c r="AD40" s="5">
         <v>46198</v>
       </c>
-      <c r="AD40" s="5"/>
-      <c r="AE40" s="5">
+      <c r="AE40" s="5"/>
+      <c r="AF40" s="5">
         <v>46157</v>
       </c>
-      <c r="AF40" s="3" t="s">
+      <c r="AG40" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AG40" s="3" t="s">
+      <c r="AH40" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AH40" s="5">
+      <c r="AI40" s="5">
         <v>46152</v>
       </c>
-      <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
-      <c r="AL40" s="3">
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3">
         <f t="shared" si="7"/>
         <v>67.391304347826079</v>
       </c>
-      <c r="AM40" s="3">
+      <c r="AN40" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN40" s="3">
+      <c r="AO40" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO40" s="3">
+      <c r="AP40" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP40" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ40" s="3"/>
-      <c r="AR40" s="3">
+      <c r="AQ40" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="3"/>
+      <c r="AS40" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS40" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT40" s="3">
+      <c r="AT40" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU40" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU40" s="3">
+      <c r="AV40" s="3">
         <f t="shared" si="13"/>
         <v>86.956521739130437</v>
       </c>
-      <c r="AV40" s="3" t="s">
+      <c r="AW40" s="3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="41" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>323</v>
       </c>
@@ -9105,68 +9339,71 @@
       <c r="AA41" s="5">
         <v>45762</v>
       </c>
-      <c r="AB41" s="5">
+      <c r="AB41" s="8">
+        <v>45762</v>
+      </c>
+      <c r="AC41" s="5">
         <v>45793</v>
       </c>
-      <c r="AC41" s="5">
+      <c r="AD41" s="5">
         <v>46127</v>
       </c>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="5">
+      <c r="AE41" s="5"/>
+      <c r="AF41" s="5">
         <v>46157</v>
       </c>
-      <c r="AF41" s="3" t="s">
+      <c r="AG41" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="AG41" s="3" t="s">
+      <c r="AH41" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="AH41" s="5">
+      <c r="AI41" s="5">
         <v>46152</v>
       </c>
-      <c r="AI41" s="3"/>
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
-      <c r="AL41" s="3">
+      <c r="AL41" s="3"/>
+      <c r="AM41" s="3">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>2</v>
       </c>
-      <c r="AQ41" s="3"/>
-      <c r="AR41" s="3">
+      <c r="AR41" s="3"/>
+      <c r="AS41" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS41" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT41" s="3">
+      <c r="AT41" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU41" s="3">
         <f t="shared" si="12"/>
         <v>75</v>
       </c>
-      <c r="AU41" s="3">
+      <c r="AV41" s="3">
         <f t="shared" si="13"/>
         <v>75</v>
       </c>
-      <c r="AV41" s="3" t="s">
+      <c r="AW41" s="3" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="42" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>330</v>
       </c>
@@ -9246,68 +9483,71 @@
       <c r="AA42" s="5">
         <v>45813</v>
       </c>
-      <c r="AB42" s="5">
+      <c r="AB42" s="8">
+        <v>45813</v>
+      </c>
+      <c r="AC42" s="5">
         <v>45869</v>
       </c>
-      <c r="AC42" s="5">
+      <c r="AD42" s="5">
         <v>46234</v>
       </c>
-      <c r="AD42" s="5"/>
-      <c r="AE42" s="5">
+      <c r="AE42" s="5"/>
+      <c r="AF42" s="5">
         <v>46157</v>
       </c>
-      <c r="AF42" s="3" t="s">
+      <c r="AG42" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="AG42" s="3" t="s">
+      <c r="AH42" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="AH42" s="5">
+      <c r="AI42" s="5">
         <v>46152</v>
       </c>
-      <c r="AI42" s="3"/>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
-      <c r="AL42" s="3">
+      <c r="AL42" s="3"/>
+      <c r="AM42" s="3">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP42" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ42" s="3"/>
-      <c r="AR42" s="3">
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR42" s="3"/>
+      <c r="AS42" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS42" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT42" s="3">
+      <c r="AT42" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU42" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU42" s="3">
+      <c r="AV42" s="3">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AV42" s="3" t="s">
+      <c r="AW42" s="3" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="43" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>336</v>
       </c>
@@ -9377,68 +9617,69 @@
         <v>46086</v>
       </c>
       <c r="AA43" s="5"/>
-      <c r="AB43" s="5"/>
+      <c r="AB43" s="8"/>
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
-      <c r="AE43" s="5">
+      <c r="AE43" s="5"/>
+      <c r="AF43" s="5">
         <v>46157</v>
       </c>
-      <c r="AF43" s="3" t="s">
+      <c r="AG43" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="AG43" s="3" t="s">
+      <c r="AH43" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="AH43" s="5">
+      <c r="AI43" s="5">
         <v>46152</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>542</v>
       </c>
-      <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
-      <c r="AL43" s="3" t="str">
+      <c r="AL43" s="3"/>
+      <c r="AM43" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM43" s="3" t="str">
+      <c r="AN43" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO43" s="3" t="str">
+      <c r="AP43" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP43" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR43" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS43" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS43" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT43" s="3">
+      <c r="AT43" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU43" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU43" s="3" t="str">
+      <c r="AV43" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV43" s="3" t="s">
+      <c r="AW43" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="44" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>344</v>
       </c>
@@ -9520,68 +9761,71 @@
       <c r="AA44" s="5">
         <v>45903</v>
       </c>
-      <c r="AB44" s="5">
+      <c r="AB44" s="8">
+        <v>45903</v>
+      </c>
+      <c r="AC44" s="5">
         <v>45911</v>
       </c>
-      <c r="AC44" s="5">
+      <c r="AD44" s="5">
         <v>46077</v>
       </c>
-      <c r="AD44" s="5"/>
-      <c r="AE44" s="5">
+      <c r="AE44" s="5"/>
+      <c r="AF44" s="5">
         <v>46157</v>
       </c>
-      <c r="AF44" s="3" t="s">
+      <c r="AG44" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="AG44" s="3" t="s">
+      <c r="AH44" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="AH44" s="5">
+      <c r="AI44" s="5">
         <v>46152</v>
       </c>
-      <c r="AI44" s="3"/>
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
-      <c r="AL44" s="3">
+      <c r="AL44" s="3"/>
+      <c r="AM44" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1</v>
       </c>
-      <c r="AQ44" s="3"/>
-      <c r="AR44" s="3">
+      <c r="AR44" s="3"/>
+      <c r="AS44" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS44" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT44" s="3">
+      <c r="AT44" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU44" s="3">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AU44" s="3">
+      <c r="AV44" s="3">
         <f t="shared" si="13"/>
         <v>36</v>
       </c>
-      <c r="AV44" s="3" t="s">
+      <c r="AW44" s="3" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="45" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>351</v>
       </c>
@@ -9661,68 +9905,71 @@
       <c r="AA45" s="5">
         <v>45856</v>
       </c>
-      <c r="AB45" s="5">
+      <c r="AB45" s="8">
+        <v>45806</v>
+      </c>
+      <c r="AC45" s="5">
         <v>45860</v>
       </c>
-      <c r="AC45" s="5">
+      <c r="AD45" s="5">
         <v>46354</v>
       </c>
-      <c r="AD45" s="5"/>
-      <c r="AE45" s="5">
+      <c r="AE45" s="5"/>
+      <c r="AF45" s="5">
         <v>46157</v>
       </c>
-      <c r="AF45" s="3" t="s">
+      <c r="AG45" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="AG45" s="3" t="s">
+      <c r="AH45" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="AH45" s="5">
+      <c r="AI45" s="5">
         <v>46152</v>
       </c>
-      <c r="AI45" s="3"/>
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
-      <c r="AL45" s="3">
+      <c r="AL45" s="3"/>
+      <c r="AM45" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP45" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ45" s="3"/>
-      <c r="AR45" s="3">
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR45" s="3"/>
+      <c r="AS45" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS45" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT45" s="3">
+      <c r="AT45" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU45" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU45" s="3">
+      <c r="AV45" s="3">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="AV45" s="3" t="s">
+      <c r="AW45" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="46" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>361</v>
       </c>
@@ -9798,70 +10045,73 @@
       <c r="AA46" s="5">
         <v>45827</v>
       </c>
-      <c r="AB46" s="5">
+      <c r="AB46" s="8">
         <v>45827</v>
       </c>
-      <c r="AC46" s="5"/>
+      <c r="AC46" s="5">
+        <v>45827</v>
+      </c>
       <c r="AD46" s="5"/>
-      <c r="AE46" s="5">
+      <c r="AE46" s="5"/>
+      <c r="AF46" s="5">
         <v>46157</v>
       </c>
-      <c r="AF46" s="3" t="s">
+      <c r="AG46" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="AG46" s="3" t="s">
+      <c r="AH46" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="AH46" s="5">
+      <c r="AI46" s="5">
         <v>46152</v>
       </c>
-      <c r="AI46" s="3"/>
       <c r="AJ46" s="3"/>
-      <c r="AK46" s="3">
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3">
         <v>330</v>
       </c>
-      <c r="AL46" s="3" t="str">
+      <c r="AM46" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM46" s="3" t="str">
+      <c r="AN46" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO46" s="3" t="str">
+      <c r="AP46" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP46" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ46" s="3">
         <v>0</v>
       </c>
       <c r="AR46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS46" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="3">
+      <c r="AT46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU46" s="3" t="str">
+      <c r="AV46" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV46" s="3" t="s">
+      <c r="AW46" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>371</v>
       </c>
@@ -9943,68 +10193,71 @@
       <c r="AA47" s="5">
         <v>45805</v>
       </c>
-      <c r="AB47" s="5">
+      <c r="AB47" s="8">
+        <v>45805</v>
+      </c>
+      <c r="AC47" s="5">
         <v>45960</v>
       </c>
-      <c r="AC47" s="5">
+      <c r="AD47" s="5">
         <v>46139</v>
       </c>
-      <c r="AD47" s="5"/>
-      <c r="AE47" s="5">
+      <c r="AE47" s="5"/>
+      <c r="AF47" s="5">
         <v>46157</v>
       </c>
-      <c r="AF47" s="3" t="s">
+      <c r="AG47" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="AG47" s="3" t="s">
+      <c r="AH47" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="AH47" s="5">
+      <c r="AI47" s="5">
         <v>46152</v>
       </c>
-      <c r="AI47" s="3"/>
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
-      <c r="AL47" s="3">
+      <c r="AL47" s="3"/>
+      <c r="AM47" s="3">
         <f t="shared" si="7"/>
         <v>95.65217391304347</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>1</v>
       </c>
-      <c r="AQ47" s="3"/>
-      <c r="AR47" s="3">
+      <c r="AR47" s="3"/>
+      <c r="AS47" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS47" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT47" s="3">
+      <c r="AT47" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU47" s="3">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AU47" s="3">
+      <c r="AV47" s="3">
         <f t="shared" si="13"/>
         <v>88.434782608695656</v>
       </c>
-      <c r="AV47" s="3" t="s">
+      <c r="AW47" s="3" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="48" spans="1:48" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:49" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>2024702150036</v>
       </c>
@@ -10072,58 +10325,59 @@
       </c>
       <c r="Z48" s="5"/>
       <c r="AA48" s="5"/>
-      <c r="AB48" s="5"/>
+      <c r="AB48" s="8"/>
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
-      <c r="AE48" s="5">
+      <c r="AE48" s="5"/>
+      <c r="AF48" s="5">
         <v>46157</v>
       </c>
-      <c r="AF48" s="3"/>
       <c r="AG48" s="3"/>
-      <c r="AH48" s="5"/>
-      <c r="AI48" s="3">
+      <c r="AH48" s="3"/>
+      <c r="AI48" s="5"/>
+      <c r="AJ48" s="3">
         <v>36</v>
       </c>
-      <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
-      <c r="AL48" s="3" t="str">
+      <c r="AL48" s="3"/>
+      <c r="AM48" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM48" s="3" t="str">
+      <c r="AN48" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO48" s="3" t="str">
+      <c r="AP48" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP48" s="3"/>
-      <c r="AQ48" s="3">
-        <v>100</v>
-      </c>
-      <c r="AR48" s="3" t="str">
+      <c r="AQ48" s="3"/>
+      <c r="AR48" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS48" s="3" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="3">
+      <c r="AT48" s="4"/>
+      <c r="AU48" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU48" s="3" t="str">
+      <c r="AV48" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV48" s="3" t="s">
+      <c r="AW48" s="3" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="49" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>382</v>
       </c>
@@ -10189,66 +10443,67 @@
       </c>
       <c r="Z49" s="5"/>
       <c r="AA49" s="5"/>
-      <c r="AB49" s="5"/>
+      <c r="AB49" s="8"/>
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
-      <c r="AE49" s="5">
+      <c r="AE49" s="5"/>
+      <c r="AF49" s="5">
         <v>46157</v>
       </c>
-      <c r="AF49" s="3" t="s">
+      <c r="AG49" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="AG49" s="3" t="s">
+      <c r="AH49" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="AH49" s="5">
+      <c r="AI49" s="5">
         <v>46152</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>64</v>
       </c>
-      <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
-      <c r="AL49" s="3" t="str">
+      <c r="AL49" s="3"/>
+      <c r="AM49" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM49" s="3" t="str">
+      <c r="AN49" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO49" s="3" t="str">
+      <c r="AP49" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP49" s="3"/>
-      <c r="AQ49" s="3">
-        <v>100</v>
-      </c>
+      <c r="AQ49" s="3"/>
       <c r="AR49" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS49" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS49" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT49" s="3">
+      <c r="AT49" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU49" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU49" s="3" t="str">
+      <c r="AV49" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV49" s="3" t="s">
+      <c r="AW49" s="3" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="50" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>389</v>
       </c>
@@ -10326,70 +10581,73 @@
       <c r="AA50" s="5">
         <v>45929</v>
       </c>
-      <c r="AB50" s="5">
+      <c r="AB50" s="8">
+        <v>45929</v>
+      </c>
+      <c r="AC50" s="5">
         <v>45930</v>
-      </c>
-      <c r="AC50" s="5">
-        <v>46021</v>
       </c>
       <c r="AD50" s="5">
         <v>46021</v>
       </c>
       <c r="AE50" s="5">
+        <v>46021</v>
+      </c>
+      <c r="AF50" s="5">
         <v>46157</v>
       </c>
-      <c r="AF50" s="3" t="s">
+      <c r="AG50" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="AG50" s="3" t="s">
+      <c r="AH50" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AH50" s="5">
+      <c r="AI50" s="5">
         <v>46157</v>
       </c>
-      <c r="AI50" s="3"/>
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
-      <c r="AL50" s="3" t="str">
+      <c r="AL50" s="3"/>
+      <c r="AM50" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM50" s="3" t="str">
+      <c r="AN50" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN50" s="3">
+      <c r="AO50" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO50" s="3">
+      <c r="AP50" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ50" s="3"/>
-      <c r="AR50" s="3">
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR50" s="3"/>
+      <c r="AS50" s="3">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AS50" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT50" s="3">
+      <c r="AT50" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU50" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU50" s="3" t="str">
+      <c r="AV50" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV50" s="3" t="s">
+      <c r="AW50" s="3" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="51" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>396</v>
       </c>
@@ -10469,68 +10727,71 @@
       <c r="AA51" s="5">
         <v>46058</v>
       </c>
-      <c r="AB51" s="5">
+      <c r="AB51" s="8">
+        <v>46058</v>
+      </c>
+      <c r="AC51" s="5">
         <v>46064</v>
       </c>
-      <c r="AC51" s="5">
+      <c r="AD51" s="5">
         <v>46798</v>
       </c>
-      <c r="AD51" s="5"/>
-      <c r="AE51" s="5">
+      <c r="AE51" s="5"/>
+      <c r="AF51" s="5">
         <v>46157</v>
       </c>
-      <c r="AF51" s="3" t="s">
+      <c r="AG51" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="AG51" s="3" t="s">
+      <c r="AH51" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="AH51" s="5">
+      <c r="AI51" s="5">
         <v>46152</v>
       </c>
-      <c r="AI51" s="3"/>
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
-      <c r="AL51" s="3">
+      <c r="AL51" s="3"/>
+      <c r="AM51" s="3">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AM51" s="3">
+      <c r="AN51" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN51" s="3">
+      <c r="AO51" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO51" s="3">
+      <c r="AP51" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="3"/>
-      <c r="AR51" s="3">
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="3"/>
+      <c r="AS51" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS51" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT51" s="3">
+      <c r="AT51" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU51" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU51" s="3">
+      <c r="AV51" s="3">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="AV51" s="3" t="s">
+      <c r="AW51" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="52" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>403</v>
       </c>
@@ -10612,68 +10873,71 @@
       <c r="AA52" s="5">
         <v>46008</v>
       </c>
-      <c r="AB52" s="5">
+      <c r="AB52" s="8">
+        <v>46008</v>
+      </c>
+      <c r="AC52" s="5">
         <v>46009</v>
       </c>
-      <c r="AC52" s="5">
+      <c r="AD52" s="5">
         <v>46191</v>
       </c>
-      <c r="AD52" s="5"/>
-      <c r="AE52" s="5">
+      <c r="AE52" s="5"/>
+      <c r="AF52" s="5">
         <v>46157</v>
       </c>
-      <c r="AF52" s="3" t="s">
+      <c r="AG52" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="AG52" s="3" t="s">
+      <c r="AH52" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="AH52" s="5">
+      <c r="AI52" s="5">
         <v>46152</v>
       </c>
-      <c r="AI52" s="3"/>
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
-      <c r="AL52" s="3">
+      <c r="AL52" s="3"/>
+      <c r="AM52" s="3">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP52" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="3"/>
-      <c r="AR52" s="3">
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="3"/>
+      <c r="AS52" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS52" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT52" s="3">
+      <c r="AT52" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU52" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU52" s="3">
+      <c r="AV52" s="3">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AV52" s="3" t="s">
+      <c r="AW52" s="3" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="53" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>407</v>
       </c>
@@ -10749,68 +11013,71 @@
       <c r="AA53" s="5">
         <v>46163</v>
       </c>
-      <c r="AB53" s="5"/>
+      <c r="AB53" s="8">
+        <v>46163</v>
+      </c>
       <c r="AC53" s="5"/>
       <c r="AD53" s="5"/>
-      <c r="AE53" s="5">
+      <c r="AE53" s="5"/>
+      <c r="AF53" s="5">
         <v>46163</v>
       </c>
-      <c r="AF53" s="3" t="s">
+      <c r="AG53" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="AG53" s="3" t="s">
+      <c r="AH53" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="AH53" s="5">
+      <c r="AI53" s="5">
         <v>46152</v>
       </c>
-      <c r="AI53" s="3"/>
       <c r="AJ53" s="3"/>
-      <c r="AK53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AL53" s="3" t="str">
+      <c r="AK53" s="3"/>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM53" s="3" t="str">
+      <c r="AN53" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN53" s="3">
+      <c r="AO53" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO53" s="3" t="str">
+      <c r="AP53" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP53" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ53" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR53" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS53" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS53" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT53" s="3">
+      <c r="AT53" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU53" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU53" s="3" t="str">
+      <c r="AV53" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV53" s="3" t="s">
+      <c r="AW53" s="3" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="54" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>414</v>
       </c>
@@ -10876,68 +11143,69 @@
       </c>
       <c r="Z54" s="5"/>
       <c r="AA54" s="5"/>
-      <c r="AB54" s="5"/>
+      <c r="AB54" s="8"/>
       <c r="AC54" s="5"/>
       <c r="AD54" s="5"/>
-      <c r="AE54" s="5">
+      <c r="AE54" s="5"/>
+      <c r="AF54" s="5">
         <v>46157</v>
       </c>
-      <c r="AF54" s="3" t="s">
+      <c r="AG54" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="AG54" s="3" t="s">
+      <c r="AH54" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="AH54" s="5">
+      <c r="AI54" s="5">
         <v>46152</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>77</v>
       </c>
-      <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
-      <c r="AL54" s="3" t="str">
+      <c r="AL54" s="3"/>
+      <c r="AM54" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM54" s="3" t="str">
+      <c r="AN54" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO54" s="3" t="str">
+      <c r="AP54" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP54" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ54" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR54" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS54" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS54" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT54" s="3">
+      <c r="AT54" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU54" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU54" s="3" t="str">
+      <c r="AV54" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV54" s="3" t="s">
+      <c r="AW54" s="3" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="55" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>421</v>
       </c>
@@ -11017,68 +11285,71 @@
       <c r="AA55" s="5">
         <v>46094</v>
       </c>
-      <c r="AB55" s="5">
+      <c r="AB55" s="8">
+        <v>46094</v>
+      </c>
+      <c r="AC55" s="5">
         <v>46139</v>
       </c>
-      <c r="AC55" s="5">
+      <c r="AD55" s="5">
         <v>46199</v>
       </c>
-      <c r="AD55" s="5"/>
-      <c r="AE55" s="5">
+      <c r="AE55" s="5"/>
+      <c r="AF55" s="5">
         <v>46157</v>
       </c>
-      <c r="AF55" s="3" t="s">
+      <c r="AG55" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="AG55" s="3" t="s">
+      <c r="AH55" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="AH55" s="5">
+      <c r="AI55" s="5">
         <v>46152</v>
       </c>
-      <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
-      <c r="AL55" s="3">
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AM55" s="3">
+      <c r="AN55" s="3">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AN55" s="3">
+      <c r="AO55" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO55" s="3">
+      <c r="AP55" s="3">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AP55" s="3">
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="3"/>
-      <c r="AR55" s="3">
+      <c r="AQ55" s="3">
+        <v>0</v>
+      </c>
+      <c r="AR55" s="3"/>
+      <c r="AS55" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS55" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT55" s="3">
+      <c r="AT55" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU55" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU55" s="3">
+      <c r="AV55" s="3">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AV55" s="3" t="s">
+      <c r="AW55" s="3" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="56" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>428</v>
       </c>
@@ -11154,68 +11425,71 @@
       <c r="AA56" s="5">
         <v>46057</v>
       </c>
-      <c r="AB56" s="5"/>
+      <c r="AB56" s="8">
+        <v>46057</v>
+      </c>
       <c r="AC56" s="5"/>
       <c r="AD56" s="5"/>
-      <c r="AE56" s="5">
+      <c r="AE56" s="5"/>
+      <c r="AF56" s="5">
         <v>46157</v>
       </c>
-      <c r="AF56" s="3" t="s">
+      <c r="AG56" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="AG56" s="3" t="s">
+      <c r="AH56" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="AH56" s="5">
+      <c r="AI56" s="5">
         <v>46152</v>
       </c>
-      <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
-      <c r="AK56" s="3">
-        <v>100</v>
-      </c>
-      <c r="AL56" s="3" t="str">
+      <c r="AK56" s="3"/>
+      <c r="AL56" s="3">
+        <v>100</v>
+      </c>
+      <c r="AM56" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM56" s="3" t="str">
+      <c r="AN56" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN56" s="3">
+      <c r="AO56" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO56" s="3" t="str">
+      <c r="AP56" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP56" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ56" s="3">
         <v>0</v>
       </c>
       <c r="AR56" s="3">
+        <v>0</v>
+      </c>
+      <c r="AS56" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS56" s="4">
-        <v>0</v>
-      </c>
-      <c r="AT56" s="3">
+      <c r="AT56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU56" s="3" t="str">
+      <c r="AV56" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV56" s="3" t="s">
+      <c r="AW56" s="3" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="57" spans="1:48" ht="70.05" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>436</v>
       </c>
@@ -11285,68 +11559,69 @@
         <v>46120</v>
       </c>
       <c r="AA57" s="5"/>
-      <c r="AB57" s="5"/>
+      <c r="AB57" s="8"/>
       <c r="AC57" s="5"/>
       <c r="AD57" s="5"/>
-      <c r="AE57" s="5">
+      <c r="AE57" s="5"/>
+      <c r="AF57" s="5">
         <v>46157</v>
       </c>
-      <c r="AF57" s="3" t="s">
+      <c r="AG57" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="AG57" s="3" t="s">
+      <c r="AH57" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="AH57" s="5">
+      <c r="AI57" s="5">
         <v>46152</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>177</v>
       </c>
-      <c r="AJ57" s="3"/>
       <c r="AK57" s="3"/>
-      <c r="AL57" s="3" t="str">
+      <c r="AL57" s="3"/>
+      <c r="AM57" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM57" s="3" t="str">
+      <c r="AN57" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO57" s="3" t="str">
+      <c r="AP57" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP57" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR57" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS57" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS57" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT57" s="3">
+      <c r="AT57" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU57" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU57" s="3" t="str">
+      <c r="AV57" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV57" s="3" t="s">
+      <c r="AW57" s="3" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="58" spans="1:48" ht="123.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:49" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>444</v>
       </c>
@@ -11412,68 +11687,69 @@
         <v>46066</v>
       </c>
       <c r="AA58" s="5"/>
-      <c r="AB58" s="5"/>
+      <c r="AB58" s="8"/>
       <c r="AC58" s="5"/>
       <c r="AD58" s="5"/>
-      <c r="AE58" s="5">
+      <c r="AE58" s="5"/>
+      <c r="AF58" s="5">
         <v>46157</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AG58" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="AG58" s="3" t="s">
+      <c r="AH58" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="AH58" s="5">
+      <c r="AI58" s="5">
         <v>46152</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>147</v>
       </c>
-      <c r="AJ58" s="3"/>
       <c r="AK58" s="3"/>
-      <c r="AL58" s="3" t="str">
+      <c r="AL58" s="3"/>
+      <c r="AM58" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM58" s="3" t="str">
+      <c r="AN58" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO58" s="3" t="str">
+      <c r="AP58" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP58" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR58" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS58" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS58" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT58" s="3">
+      <c r="AT58" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU58" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU58" s="3" t="str">
+      <c r="AV58" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV58" s="3" t="s">
+      <c r="AW58" s="3" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="59" spans="1:48" ht="135" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:49" ht="135" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>450</v>
       </c>
@@ -11537,68 +11813,69 @@
       </c>
       <c r="Z59" s="5"/>
       <c r="AA59" s="5"/>
-      <c r="AB59" s="5"/>
+      <c r="AB59" s="8"/>
       <c r="AC59" s="5"/>
       <c r="AD59" s="5"/>
-      <c r="AE59" s="5">
+      <c r="AE59" s="5"/>
+      <c r="AF59" s="5">
         <v>46157</v>
       </c>
-      <c r="AF59" s="3" t="s">
+      <c r="AG59" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="AG59" s="3" t="s">
+      <c r="AH59" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="AH59" s="5">
+      <c r="AI59" s="5">
         <v>46152</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>77</v>
       </c>
-      <c r="AJ59" s="3"/>
       <c r="AK59" s="3"/>
-      <c r="AL59" s="3" t="str">
+      <c r="AL59" s="3"/>
+      <c r="AM59" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM59" s="3" t="str">
+      <c r="AN59" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO59" s="3" t="str">
+      <c r="AP59" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP59" s="3">
-        <v>0</v>
-      </c>
       <c r="AQ59" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AR59" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS59" s="3">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AS59" s="4">
-        <v>100</v>
-      </c>
-      <c r="AT59" s="3">
+      <c r="AT59" s="4">
+        <v>100</v>
+      </c>
+      <c r="AU59" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU59" s="3" t="str">
+      <c r="AV59" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV59" s="3" t="s">
+      <c r="AW59" s="3" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="60" spans="1:48" ht="123" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:49" ht="123" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3">
         <v>2026002700007</v>
       </c>
@@ -11669,59 +11946,60 @@
       <c r="AB60" s="5"/>
       <c r="AC60" s="5"/>
       <c r="AD60" s="5"/>
-      <c r="AE60" s="5">
+      <c r="AE60" s="5"/>
+      <c r="AF60" s="5">
         <v>46188</v>
       </c>
-      <c r="AF60" s="3"/>
       <c r="AG60" s="3"/>
-      <c r="AH60" s="5"/>
-      <c r="AI60" s="3">
+      <c r="AH60" s="3"/>
+      <c r="AI60" s="5"/>
+      <c r="AJ60" s="3">
         <v>19</v>
       </c>
-      <c r="AJ60" s="3"/>
       <c r="AK60" s="3"/>
-      <c r="AL60" s="3" t="str">
+      <c r="AL60" s="3"/>
+      <c r="AM60" s="3" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AM60" s="3" t="str">
+      <c r="AN60" s="3" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AO60" s="3" t="str">
+      <c r="AP60" s="3" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AP60" s="3"/>
-      <c r="AQ60" s="3">
-        <v>100</v>
-      </c>
-      <c r="AR60" s="3" t="str">
+      <c r="AQ60" s="3"/>
+      <c r="AR60" s="3">
+        <v>100</v>
+      </c>
+      <c r="AS60" s="3" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AS60" s="4"/>
-      <c r="AT60" s="3">
+      <c r="AT60" s="4"/>
+      <c r="AU60" s="3">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AU60" s="3" t="str">
+      <c r="AV60" s="3" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AV60" s="3" t="s">
+      <c r="AW60" s="3" t="s">
         <v>913</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="U1:AP1"/>
-    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="U1:AQ1"/>
+    <mergeCell ref="AR1:AW1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -11732,17 +12010,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AL18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="28" width="25.6640625" customWidth="1"/>
-    <col min="29" max="29" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="30" max="34" width="25.6640625" customWidth="1"/>
-    <col min="35" max="35" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="36" max="37" width="25.6640625" customWidth="1"/>
+    <col min="1" max="29" width="25.6640625" customWidth="1"/>
+    <col min="30" max="30" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="31" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="36" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="37" max="38" width="25.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11778,16 +12056,17 @@
       <c r="AC1" s="7"/>
       <c r="AD1" s="7"/>
       <c r="AE1" s="7"/>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="7"/>
+      <c r="AG1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="6"/>
       <c r="AH1" s="6"/>
       <c r="AI1" s="6"/>
       <c r="AJ1" s="6"/>
       <c r="AK1" s="6"/>
+      <c r="AL1" s="6"/>
     </row>
-    <row r="2" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -11849,58 +12128,61 @@
         <v>28</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="V2" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="W2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>466</v>
       </c>
@@ -11957,53 +12239,54 @@
       <c r="T3" s="5">
         <v>44412</v>
       </c>
-      <c r="U3" s="5">
+      <c r="U3" s="8">
         <v>44342</v>
       </c>
-      <c r="V3" s="5">
+      <c r="V3" s="8"/>
+      <c r="W3" s="5">
         <v>44593</v>
       </c>
-      <c r="W3" s="5">
+      <c r="X3" s="5">
         <v>46127</v>
       </c>
-      <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
-      <c r="AA3" s="3" t="str">
-        <f t="shared" ref="AA3:AA18" si="0">IF(AND($R3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($R3&gt;1.25,$R3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($R3&gt;1.2,$R3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($R3&gt;=0.84,$R3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($R3&gt;=0.38,$R3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($R3-0.38)/(0.84-0.38))*100,IF(AND($R3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3" t="str">
+        <f t="shared" ref="AB3:AB18" si="0">IF(AND($R3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($R3&gt;1.25,$R3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($R3&gt;1.2,$R3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($R3&gt;=0.84,$R3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($R3&gt;=0.38,$R3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($R3-0.38)/(0.84-0.38))*100,IF(AND($R3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AB3" s="3" t="str">
-        <f t="shared" ref="AB3:AB18" si="1">IF(AND($Q3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($Q3&gt;1.25,$Q3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($Q3&gt;1.2,$Q3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($Q3&gt;=0.84,$Q3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($Q3&gt;=0.38,$Q3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($Q3-0.38)/(0.84-0.38))*100,IF(AND($Q3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AC3" s="3" t="str">
+        <f t="shared" ref="AC3:AC18" si="1">IF(AND($Q3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($Q3&gt;1.25,$Q3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($Q3&gt;1.2,$Q3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($Q3&gt;=0.84,$Q3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($Q3&gt;=0.38,$Q3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($Q3-0.38)/(0.84-0.38))*100,IF(AND($Q3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AC3" s="3">
-        <f t="shared" ref="AC3:AC18" si="2">IF(AND($P3&lt;60,($P3-$O3)&lt;=50),100,IF(AND($P3&lt;60,($P3-$O3)&gt;50),0,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&lt;=40),100,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&gt;40),0,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&lt;=30),100,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&gt;30),0,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&lt;=20),100,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&gt;20),0,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&lt;=10),100,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AD3" s="3" t="str">
-        <f t="shared" ref="AD3:AD18" si="3">IF(AND($O3&gt;$P3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($P3&gt;$O3,($P3-$O3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&lt;=60),100,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&gt;60),$AC3,""))))</f>
+      <c r="AD3" s="3">
+        <f t="shared" ref="AD3:AD18" si="2">IF(AND($P3&lt;60,($P3-$O3)&lt;=50),100,IF(AND($P3&lt;60,($P3-$O3)&gt;50),0,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&lt;=40),100,IF(AND($P3&gt;=60,$P3&lt;70,($P3-$O3)&gt;40),0,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&lt;=30),100,IF(AND($P3&gt;=70,$P3&lt;80,($P3-$O3)&gt;30),0,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&lt;=20),100,IF(AND($P3&gt;=80,$P3&lt;90,($P3-$O3)&gt;20),0,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&lt;=10),100,IF(AND($P3&gt;=90,$P3&lt;=100,($P3-$O3)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AE3" s="3" t="str">
+        <f t="shared" ref="AE3:AE18" si="3">IF(AND($O3&gt;$P3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($P3&gt;$O3,($P3-$O3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&lt;=60),100,IF(AND($P3&gt;$O3,($P3-$O3)&lt;=50,$P3&gt;60),$AD3,""))))</f>
         <v/>
       </c>
-      <c r="AE3" s="3">
+      <c r="AF3" s="3">
         <v>2</v>
       </c>
-      <c r="AF3" s="3"/>
       <c r="AG3" s="3"/>
       <c r="AH3" s="3"/>
-      <c r="AI3" s="3">
-        <f t="shared" ref="AI3:AI18" si="4">IF($AE3=0,100,IF($AE3=1,90,IF($AE3=2,75,IF($AE3=3,60,IF($AE3=4,50,IF($AE3=5,25,IF($AE3&gt;=6,0,"")))))))</f>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3">
+        <f t="shared" ref="AJ3:AJ18" si="4">IF($AF3=0,100,IF($AF3=1,90,IF($AF3=2,75,IF($AF3=3,60,IF($AF3=4,50,IF($AF3=5,25,IF($AF3&gt;=6,0,"")))))))</f>
         <v>75</v>
       </c>
-      <c r="AJ3" s="3" t="str">
-        <f t="shared" ref="AJ3:AJ18" si="5">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AE3&gt;=1),(IFERROR(IF(ISNUMBER($AG3),($AA3*0.4+$AB3*0.2+$AD3*0.4),""),""))*$AI3/100,IFERROR(IF(ISNUMBER($AG3),($AA3*0.4+$AB3*0.2+$AD3*0.4),""),"")),0)</f>
+      <c r="AK3" s="3" t="str">
+        <f t="shared" ref="AK3:AK18" si="5">IFERROR(IF(AND($G3="CONTRATADO EN EJECUCIÓN",$AF3&gt;=1),(IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),""))*$AJ3/100,IFERROR(IF(ISNUMBER($AH3),($AB3*0.4+$AC3*0.2+$AE3*0.4),""),"")),0)</f>
         <v/>
       </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>473</v>
       </c>
@@ -12060,53 +12343,54 @@
       <c r="T4" s="5">
         <v>44412</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U4" s="8">
         <v>44462</v>
       </c>
-      <c r="V4" s="5">
+      <c r="V4" s="8"/>
+      <c r="W4" s="5">
         <v>44567</v>
       </c>
-      <c r="W4" s="5">
+      <c r="X4" s="5">
         <v>46127</v>
       </c>
-      <c r="X4" s="3"/>
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
-      <c r="AA4" s="3" t="str">
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB4" s="3" t="str">
+      <c r="AC4" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC4" s="3">
+      <c r="AD4" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD4" s="3" t="str">
+      <c r="AE4" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="3"/>
+      <c r="AF4" s="3">
+        <v>0</v>
+      </c>
       <c r="AG4" s="3"/>
       <c r="AH4" s="3"/>
-      <c r="AI4" s="3">
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ4" s="3" t="str">
+      <c r="AK4" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK4" s="3" t="s">
+      <c r="AL4" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>477</v>
       </c>
@@ -12165,57 +12449,58 @@
       <c r="T5" s="5">
         <v>44930</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5" s="8">
         <v>44718</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V5" s="8"/>
+      <c r="W5" s="5">
         <v>44722</v>
       </c>
-      <c r="W5" s="5">
+      <c r="X5" s="5">
         <v>46096</v>
       </c>
-      <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
-      <c r="AA5" s="3">
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AC5" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AD5" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD5" s="3">
+      <c r="AE5" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE5" s="3">
+      <c r="AF5" s="3">
         <v>2</v>
       </c>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG5" s="3"/>
       <c r="AH5" s="3">
         <v>100</v>
       </c>
       <c r="AI5" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ5" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ5" s="3">
+      <c r="AK5" s="3">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AK5" s="3" t="s">
+      <c r="AL5" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>483</v>
       </c>
@@ -12276,57 +12561,58 @@
       <c r="T6" s="5">
         <v>44643</v>
       </c>
-      <c r="U6" s="5">
+      <c r="U6" s="8">
         <v>44706</v>
       </c>
-      <c r="V6" s="5">
+      <c r="V6" s="8"/>
+      <c r="W6" s="5">
         <v>44810</v>
       </c>
-      <c r="W6" s="5">
+      <c r="X6" s="5">
         <v>46127</v>
       </c>
-      <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
-      <c r="AA6" s="3">
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AC6" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AD6" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD6" s="3">
+      <c r="AE6" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE6" s="3">
+      <c r="AF6" s="3">
         <v>4</v>
       </c>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG6" s="3"/>
       <c r="AH6" s="3">
         <v>100</v>
       </c>
       <c r="AI6" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ6" s="3">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="AJ6" s="3">
+      <c r="AK6" s="3">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AK6" s="3" t="s">
+      <c r="AL6" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>489</v>
       </c>
@@ -12387,57 +12673,58 @@
       <c r="T7" s="5">
         <v>45093</v>
       </c>
-      <c r="U7" s="5">
+      <c r="U7" s="8">
         <v>45043</v>
       </c>
-      <c r="V7" s="5">
+      <c r="V7" s="8"/>
+      <c r="W7" s="5">
         <v>45175</v>
       </c>
-      <c r="W7" s="5">
+      <c r="X7" s="5">
         <v>46127</v>
       </c>
-      <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
-      <c r="AA7" s="3">
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AC7" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AD7" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD7" s="3">
+      <c r="AE7" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AF7" s="3">
         <v>4</v>
       </c>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG7" s="3"/>
       <c r="AH7" s="3">
         <v>100</v>
       </c>
       <c r="AI7" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ7" s="3">
         <f t="shared" si="4"/>
         <v>50</v>
       </c>
-      <c r="AJ7" s="3">
+      <c r="AK7" s="3">
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="AK7" s="3" t="s">
+      <c r="AL7" s="3" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>493</v>
       </c>
@@ -12494,53 +12781,54 @@
       <c r="T8" s="5">
         <v>45274</v>
       </c>
-      <c r="U8" s="5">
+      <c r="U8" s="8">
         <v>45289</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V8" s="8"/>
+      <c r="W8" s="5">
         <v>45300</v>
       </c>
-      <c r="W8" s="5">
+      <c r="X8" s="5">
         <v>46096</v>
       </c>
-      <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
-      <c r="AA8" s="3" t="str">
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB8" s="3" t="str">
+      <c r="AC8" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD8" s="3" t="str">
+      <c r="AE8" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="3"/>
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="3">
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ8" s="3" t="str">
+      <c r="AK8" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK8" s="3" t="s">
+      <c r="AL8" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>496</v>
       </c>
@@ -12601,57 +12889,58 @@
       <c r="T9" s="5">
         <v>45433</v>
       </c>
-      <c r="U9" s="5">
+      <c r="U9" s="8">
         <v>45505</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="8"/>
+      <c r="W9" s="5">
         <v>45567</v>
       </c>
-      <c r="W9" s="5">
+      <c r="X9" s="5">
         <v>46096</v>
       </c>
-      <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
-      <c r="AA9" s="3" t="str">
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB9" s="3" t="str">
+      <c r="AC9" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD9" s="3" t="str">
+      <c r="AE9" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2</v>
       </c>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG9" s="3"/>
       <c r="AH9" s="3">
         <v>100</v>
       </c>
       <c r="AI9" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ9" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ9" s="3" t="str">
+      <c r="AK9" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK9" s="3" t="s">
+      <c r="AL9" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>500</v>
       </c>
@@ -12712,53 +13001,54 @@
       <c r="T10" s="5">
         <v>45491</v>
       </c>
-      <c r="U10" s="5">
+      <c r="U10" s="8">
         <v>45582</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10" s="8"/>
+      <c r="W10" s="5">
         <v>45772</v>
       </c>
-      <c r="W10" s="5">
+      <c r="X10" s="5">
         <v>46096</v>
       </c>
-      <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
-      <c r="AA10" s="3">
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-      <c r="AG10" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG10" s="3"/>
       <c r="AH10" s="3">
         <v>100</v>
       </c>
       <c r="AI10" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ10" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
     </row>
-    <row r="11" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>503</v>
       </c>
@@ -12819,55 +13109,56 @@
       <c r="T11" s="5">
         <v>45539</v>
       </c>
-      <c r="U11" s="5">
+      <c r="U11" s="8">
         <v>45609</v>
       </c>
-      <c r="V11" s="5">
+      <c r="V11" s="8"/>
+      <c r="W11" s="5">
         <v>45624</v>
       </c>
-      <c r="W11" s="5">
+      <c r="X11" s="5">
         <v>46127</v>
       </c>
-      <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-      <c r="AA11" s="3">
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AC11" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AD11" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD11" s="3">
+      <c r="AE11" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE11" s="3">
+      <c r="AF11" s="3">
         <v>3</v>
       </c>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG11" s="3"/>
       <c r="AH11" s="3">
         <v>100</v>
       </c>
       <c r="AI11" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ11" s="3">
         <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AK11" s="3">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>506</v>
       </c>
@@ -12928,57 +13219,58 @@
       <c r="T12" s="5">
         <v>45544</v>
       </c>
-      <c r="U12" s="5">
+      <c r="U12" s="8">
         <v>45716</v>
       </c>
-      <c r="V12" s="5">
+      <c r="V12" s="8"/>
+      <c r="W12" s="5">
         <v>45723</v>
       </c>
-      <c r="W12" s="5">
+      <c r="X12" s="5">
         <v>46096</v>
       </c>
-      <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
-      <c r="AA12" s="3">
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1</v>
       </c>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG12" s="3"/>
       <c r="AH12" s="3">
         <v>100</v>
       </c>
       <c r="AI12" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ12" s="3">
         <f t="shared" si="4"/>
         <v>90</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AK12" s="3" t="s">
+      <c r="AL12" s="3" t="s">
         <v>510</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>511</v>
       </c>
@@ -13039,53 +13331,54 @@
       <c r="T13" s="5">
         <v>45849</v>
       </c>
-      <c r="U13" s="5">
+      <c r="U13" s="8">
         <v>45852</v>
       </c>
-      <c r="V13" s="5">
+      <c r="V13" s="8"/>
+      <c r="W13" s="5">
         <v>45863</v>
       </c>
-      <c r="W13" s="5">
+      <c r="X13" s="5">
         <v>46127</v>
       </c>
-      <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
-      <c r="AA13" s="3" t="str">
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB13" s="3" t="str">
+      <c r="AC13" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC13" s="3">
+      <c r="AD13" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD13" s="3" t="str">
+      <c r="AE13" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG13" s="3"/>
       <c r="AH13" s="3">
         <v>100</v>
       </c>
       <c r="AI13" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ13" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ13" s="3" t="str">
+      <c r="AK13" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
     </row>
-    <row r="14" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>514</v>
       </c>
@@ -13146,55 +13439,56 @@
       <c r="T14" s="5">
         <v>45656</v>
       </c>
-      <c r="U14" s="5">
+      <c r="U14" s="8">
         <v>45672</v>
       </c>
-      <c r="V14" s="5">
+      <c r="V14" s="8"/>
+      <c r="W14" s="5">
         <v>45672</v>
       </c>
-      <c r="W14" s="5">
+      <c r="X14" s="5">
         <v>46096</v>
       </c>
-      <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2</v>
       </c>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG14" s="3"/>
       <c r="AH14" s="3">
         <v>100</v>
       </c>
       <c r="AI14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ14" s="3">
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <f t="shared" si="5"/>
         <v>30</v>
       </c>
-      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
     </row>
-    <row r="15" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>518</v>
       </c>
@@ -13255,53 +13549,54 @@
       <c r="T15" s="5">
         <v>45926</v>
       </c>
-      <c r="U15" s="5">
+      <c r="U15" s="8">
         <v>45981</v>
       </c>
-      <c r="V15" s="5">
+      <c r="V15" s="8"/>
+      <c r="W15" s="5">
         <v>46030</v>
       </c>
-      <c r="W15" s="5">
+      <c r="X15" s="5">
         <v>46127</v>
       </c>
-      <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
-      <c r="AA15" s="3">
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
-      <c r="AG15" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG15" s="3"/>
       <c r="AH15" s="3">
         <v>100</v>
       </c>
       <c r="AI15" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ15" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>521</v>
       </c>
@@ -13358,55 +13653,56 @@
       <c r="T16" s="5">
         <v>45838</v>
       </c>
-      <c r="U16" s="5">
+      <c r="U16" s="8">
         <v>46058</v>
       </c>
-      <c r="V16" s="5"/>
-      <c r="W16" s="5">
+      <c r="V16" s="8"/>
+      <c r="W16" s="5"/>
+      <c r="X16" s="5">
         <v>46096</v>
       </c>
-      <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-      <c r="Z16" s="3">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3">
         <v>38</v>
       </c>
-      <c r="AA16" s="3" t="str">
+      <c r="AB16" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB16" s="3" t="str">
+      <c r="AC16" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC16" s="3">
+      <c r="AD16" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD16" s="3" t="str">
+      <c r="AE16" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3">
         <v>75.862068965517238</v>
       </c>
-      <c r="AG16" s="3">
-        <v>100</v>
-      </c>
       <c r="AH16" s="3">
         <v>100</v>
       </c>
       <c r="AI16" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ16" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ16" s="3" t="str">
+      <c r="AK16" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>524</v>
       </c>
@@ -13459,53 +13755,54 @@
       <c r="T17" s="5">
         <v>45947</v>
       </c>
-      <c r="U17" s="5">
+      <c r="U17" s="8">
         <v>46112</v>
       </c>
-      <c r="V17" s="5">
+      <c r="V17" s="8"/>
+      <c r="W17" s="5">
         <v>46120</v>
       </c>
-      <c r="W17" s="5">
+      <c r="X17" s="5">
         <v>46096</v>
       </c>
-      <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
-      <c r="AA17" s="3">
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AE17" s="3"/>
       <c r="AF17" s="3"/>
-      <c r="AG17" s="3">
-        <v>100</v>
-      </c>
+      <c r="AG17" s="3"/>
       <c r="AH17" s="3">
         <v>100</v>
       </c>
       <c r="AI17" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ17" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <f t="shared" si="5"/>
         <v>40</v>
       </c>
-      <c r="AK17" s="3"/>
+      <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:37" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>527</v>
       </c>
@@ -13556,36 +13853,34 @@
         <v>46107</v>
       </c>
       <c r="T18" s="5"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="5"/>
-      <c r="W18" s="5">
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="5"/>
+      <c r="X18" s="5">
         <v>46127</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>20</v>
       </c>
-      <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
-      <c r="AA18" s="3" t="str">
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AB18" s="3" t="str">
+      <c r="AC18" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AD18" s="3" t="str">
+      <c r="AE18" s="3" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3">
-        <v>100</v>
-      </c>
+      <c r="AF18" s="3"/>
       <c r="AG18" s="3">
         <v>100</v>
       </c>
@@ -13593,20 +13888,23 @@
         <v>100</v>
       </c>
       <c r="AI18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ18" s="3">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AJ18" s="3" t="str">
+      <c r="AK18" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="O1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="O1:AF1"/>
+    <mergeCell ref="AG1:AL1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB5B2B5E-73C9-4B48-87F5-A2BEABD01B16}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28608DBC-82FB-453D-9902-EA61F7064E5F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3034,13 +3034,13 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3200,7 +3200,7 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
-    <tableColumn id="49" xr3:uid="{4504867D-40BB-4895-B8F9-7569A94E115D}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="2"/>
+    <tableColumn id="49" xr3:uid="{4504867D-40BB-4895-B8F9-7569A94E115D}" name="FECHA SUSCRIPCION" dataDxfId="2"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
@@ -3602,61 +3602,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:49" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="8" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="8"/>
-      <c r="AL1" s="8"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="8"/>
-      <c r="AO1" s="8"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="7" t="s">
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
+      <c r="AM1" s="9"/>
+      <c r="AN1" s="9"/>
+      <c r="AO1" s="9"/>
+      <c r="AP1" s="9"/>
+      <c r="AQ1" s="9"/>
+      <c r="AR1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="7"/>
-      <c r="AU1" s="7"/>
-      <c r="AV1" s="7"/>
-      <c r="AW1" s="7"/>
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="8"/>
+      <c r="AU1" s="8"/>
+      <c r="AV1" s="8"/>
+      <c r="AW1" s="8"/>
     </row>
     <row r="2" spans="1:49" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3741,7 +3741,7 @@
         <v>916</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="AC2" s="2" t="s">
         <v>29</v>
@@ -11876,7 +11876,7 @@
       </c>
     </row>
     <row r="60" spans="1:49" ht="123" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="9">
+      <c r="A60" s="7">
         <v>2026002700007</v>
       </c>
       <c r="B60" s="3" t="s">
@@ -12021,50 +12021,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="8" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="8"/>
-      <c r="AE1" s="8"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="7" t="s">
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="7"/>
-      <c r="AI1" s="7"/>
-      <c r="AJ1" s="7"/>
-      <c r="AK1" s="7"/>
-      <c r="AL1" s="7"/>
+      <c r="AH1" s="8"/>
+      <c r="AI1" s="8"/>
+      <c r="AJ1" s="8"/>
+      <c r="AK1" s="8"/>
+      <c r="AL1" s="8"/>
     </row>
     <row r="2" spans="1:38" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -13922,26 +13922,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
     </row>
     <row r="2" spans="1:18" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -19287,6 +19287,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19430,22 +19445,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B1288D-E17B-41C7-8BDA-3DFB9BA1125D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19461,21 +19478,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28608DBC-82FB-453D-9902-EA61F7064E5F}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{8A5C9491-4771-48A1-BD83-F2BEDE4C7C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30E943D1-DA38-45B9-A331-06E8BDA1EFB0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3047,7 +3047,42 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3179,7 +3214,7 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="ALCANCE DEL PROYECTO"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="SECTOR"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="INDICADOR DE PRODUCTO MGA"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ESTADO PROYECTO"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ESTADO PROYECTO" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ESTADO CONTRATO"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="TIPO CONTRATO"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="FUENTE DE FINANCIACIÓN"/>
@@ -3200,7 +3235,7 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name="FECHA DE SUSCRIPCIÓN DEL CONTRATO PRINCIPAL"/>
-    <tableColumn id="49" xr3:uid="{4504867D-40BB-4895-B8F9-7569A94E115D}" name="FECHA SUSCRIPCION" dataDxfId="2"/>
+    <tableColumn id="49" xr3:uid="{4504867D-40BB-4895-B8F9-7569A94E115D}" name="FECHA SUSCRIPCION" dataDxfId="3"/>
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="HORIZONTE DEL PROYECTO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="FECHA DE FINALIZACIÓN"/>
@@ -3251,8 +3286,8 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0100-000012000000}" name="SPI"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="FECHA APROBACIÓN PROYECTO"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="FECHA DE APERTURA DEL PRIMER PROCESO"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION" dataDxfId="1"/>
-    <tableColumn id="38" xr3:uid="{5127B442-BBCD-41A9-9DD8-B336C15E70D5}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="0"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="FECHA SUSCRIPCION" dataDxfId="2"/>
+    <tableColumn id="38" xr3:uid="{5127B442-BBCD-41A9-9DD8-B336C15E70D5}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO" dataDxfId="1"/>
     <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="23" xr3:uid="{00000000-0010-0000-0100-000017000000}" name="FECHA DE CORTE GESPROY"/>
     <tableColumn id="24" xr3:uid="{00000000-0010-0000-0100-000018000000}" name="DIAS DESDE LA APROBACIÓN HASTA APERTURA DEL PRIMER PROCESO"/>
@@ -4539,7 +4574,7 @@
         <v>103</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>56</v>
+        <v>208</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>104</v>
@@ -19287,21 +19322,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -19445,24 +19465,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76B1288D-E17B-41C7-8BDA-3DFB9BA1125D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19478,4 +19496,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BFC0EBF-E5CA-453E-96B6-D9E35E8DEB4E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A8443F4-0206-4A7A-8CAD-F7F3FD43B967}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zgama\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6976D422-6619-4961-9443-0A3B7DFE6DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{6976D422-6619-4961-9443-0A3B7DFE6DFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9B1D70B-C6F5-4423-8656-01DBF6787A28}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="1016">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -3211,6 +3211,9 @@
   </si>
   <si>
     <t>SGR-Asignaciones directas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FECHA DE SUSPENSIÓN DEL CONTRATO </t>
   </si>
 </sst>
 </file>
@@ -3345,7 +3348,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
     <dxf>
       <font>
         <b val="0"/>
@@ -3381,6 +3384,42 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Roboto"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3395,9 +3434,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:BA60" totalsRowShown="0">
-  <autoFilter ref="A2:BA60" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:BB60" totalsRowShown="0">
+  <autoFilter ref="A2:BB60" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="54">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="NOMBRE PROYECTO"/>
@@ -3428,6 +3467,7 @@
     <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="FECHA DE SUSCRIPCIÓN DEL PRIMER CONTRATO"/>
     <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="FECHA ACTA INICIO"/>
     <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="HORIZONTE DEL PROYECTO"/>
+    <tableColumn id="54" xr3:uid="{5E233D81-7827-4B0C-BCCB-CBA1ADD4E332}" name="FECHA DE SUSPENSIÓN DEL CONTRATO " dataDxfId="1"/>
     <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="FECHA DE FINALIZACIÓN"/>
     <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="FECHA EN LA QUE PASO A ESTADO PARA CIERRE"/>
     <tableColumn id="33" xr3:uid="{00000000-0010-0000-0000-000021000000}" name="FECHA DE CORTE GESPROY"/>
@@ -3821,20 +3861,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA60"/>
+  <dimension ref="A1:BB60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="41" width="25.6640625" customWidth="1"/>
-    <col min="42" max="42" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="43" max="47" width="25.6640625" customWidth="1"/>
-    <col min="48" max="48" width="25.6640625" hidden="1" customWidth="1"/>
-    <col min="49" max="50" width="25.6640625" customWidth="1"/>
-    <col min="51" max="51" width="41" customWidth="1"/>
-    <col min="52" max="52" width="33.88671875" customWidth="1"/>
-    <col min="53" max="53" width="35.109375" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="34.44140625" customWidth="1"/>
+    <col min="4" max="35" width="25.6640625" customWidth="1"/>
+    <col min="36" max="43" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="44" max="51" width="25.6640625" customWidth="1"/>
+    <col min="52" max="52" width="74.44140625" customWidth="1"/>
+    <col min="53" max="53" width="33.88671875" customWidth="1"/>
+    <col min="54" max="54" width="35.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -3883,10 +3923,10 @@
       <c r="AP1" s="8"/>
       <c r="AQ1" s="8"/>
       <c r="AR1" s="8"/>
-      <c r="AS1" s="7" t="s">
+      <c r="AS1" s="8"/>
+      <c r="AT1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AT1" s="7"/>
       <c r="AU1" s="7"/>
       <c r="AV1" s="7"/>
       <c r="AW1" s="7"/>
@@ -3894,8 +3934,9 @@
       <c r="AY1" s="7"/>
       <c r="AZ1" s="7"/>
       <c r="BA1" s="7"/>
+      <c r="BB1" s="7"/>
     </row>
-    <row r="2" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -3987,76 +4028,79 @@
         <v>32</v>
       </c>
       <c r="AE2" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AF2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AT2" s="1" t="s">
+      <c r="AU2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AV2" s="1" t="s">
+      <c r="AW2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AW2" s="1" t="s">
+      <c r="AX2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AX2" s="1" t="s">
+      <c r="AY2" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="AY2" s="1" t="s">
+      <c r="AZ2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AZ2" s="3" t="s">
+      <c r="BA2" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BB2" s="3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:54" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
@@ -4143,72 +4187,73 @@
       <c r="AD3" s="6">
         <v>45260</v>
       </c>
-      <c r="AE3" s="6">
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6">
         <v>45260</v>
       </c>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6">
+      <c r="AG3" s="6"/>
+      <c r="AH3" s="6">
         <v>46157</v>
       </c>
-      <c r="AH3" s="4" t="s">
+      <c r="AI3" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AI3" s="4" t="s">
+      <c r="AJ3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AJ3" s="6">
+      <c r="AK3" s="6">
         <v>46157</v>
       </c>
-      <c r="AK3" s="4"/>
       <c r="AL3" s="4"/>
       <c r="AM3" s="4"/>
-      <c r="AN3" s="4" t="str">
-        <f t="shared" ref="AN3:AN34" si="0">IF(AND($X3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X3&gt;1.25,$X3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X3&gt;1.2,$X3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X3&gt;=0.84,$X3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X3&gt;=0.38,$X3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($X3-0.38)/(0.84-0.38))*100,IF(AND($X3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4" t="str">
+        <f t="shared" ref="AO3:AO34" si="0">IF(AND($X3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X3&gt;1.25,$X3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X3&gt;1.2,$X3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X3&gt;=0.84,$X3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X3&gt;=0.38,$X3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($X3-0.38)/(0.84-0.38))*100,IF(AND($X3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AO3" s="4" t="str">
-        <f t="shared" ref="AO3:AO34" si="1">IF(AND($W3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W3&gt;1.25,$W3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W3&gt;1.2,$W3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W3&gt;=0.84,$W3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W3&gt;=0.38,$W3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($W3-0.38)/(0.84-0.38))*100,IF(AND($W3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AP3" s="4" t="str">
+        <f t="shared" ref="AP3:AP34" si="1">IF(AND($W3&gt;1.3,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W3&gt;1.25,$W3&lt;=1.3,$G3="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W3&gt;1.2,$W3&lt;=1.25,$G3="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W3&gt;=0.84,$W3&lt;1.2,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W3&gt;=0.38,$W3&lt;0.84,$G3="CONTRATADO EN EJECUCIÓN"),(($W3-0.38)/(0.84-0.38))*100,IF(AND($W3&lt;0.38,$G3="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AP3" s="4">
-        <f t="shared" ref="AP3:AP34" si="2">IF(AND($V3&lt;60,($V3-$U3)&lt;=50),100,IF(AND($V3&lt;60,($V3-$U3)&gt;50),0,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&lt;=40),100,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&gt;40),0,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&lt;=30),100,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&gt;30),0,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&lt;=20),100,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&gt;20),0,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&lt;=10),100,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AQ3" s="4" t="str">
-        <f t="shared" ref="AQ3:AQ34" si="3">IF(AND($U3&gt;$V3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V3&gt;$U3,($V3-$U3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&lt;=60),100,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&gt;60),$AP3,""))))</f>
+      <c r="AQ3" s="4">
+        <f t="shared" ref="AQ3:AQ34" si="2">IF(AND($V3&lt;60,($V3-$U3)&lt;=50),100,IF(AND($V3&lt;60,($V3-$U3)&gt;50),0,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&lt;=40),100,IF(AND($V3&gt;=60,$V3&lt;70,($V3-$U3)&gt;40),0,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&lt;=30),100,IF(AND($V3&gt;=70,$V3&lt;80,($V3-$U3)&gt;30),0,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&lt;=20),100,IF(AND($V3&gt;=80,$V3&lt;90,($V3-$U3)&gt;20),0,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&lt;=10),100,IF(AND($V3&gt;=90,$V3&lt;=100,($V3-$U3)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AR3" s="4" t="str">
+        <f t="shared" ref="AR3:AR34" si="3">IF(AND($U3&gt;$V3,$G3="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V3&gt;$U3,($V3-$U3)&gt;50,$G3="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&lt;=60),100,IF(AND($V3&gt;$U3,($V3-$U3)&lt;=50,$V3&gt;60),$AQ3,""))))</f>
         <v/>
       </c>
-      <c r="AR3" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="5"/>
-      <c r="AT3" s="4">
-        <f t="shared" ref="AT3:AT34" si="4">IF(ISNUMBER($AJ3),IF(DAY($AJ3)=10,100,IF(DAY($AJ3)=11,80,IF(DAY($AJ3)=12,50,0))),"")</f>
-        <v>0</v>
-      </c>
-      <c r="AU3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV3" s="4">
-        <f t="shared" ref="AV3:AV34" si="5">IF($AR3=0,100,IF($AR3=1,90,IF($AR3=2,75,IF($AR3=3,60,IF($AR3=4,50,IF($AR3=5,25,IF($AR3&gt;=6,0,"")))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AW3" s="4" t="str">
-        <f t="shared" ref="AW3:AW34" si="6">IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($AD3),ISNUMBER($AG3),$AD3&lt;$AG3),0,IF($AR3&gt;=1,(IFERROR(IF(ISTEXT($AH3),($AN3*0.4+$AO3*0.2+$AQ3*0.4),""),""))*$AV3/100,IFERROR(IF(ISTEXT($AH3),($AN3*0.4+$AO3*0.2+$AQ3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($AG3-$AB3&gt;=0,$AG3-$AB3&lt;=30),100,0),"")),"Revisar")</f>
+      <c r="AS3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="5"/>
+      <c r="AU3" s="4">
+        <f t="shared" ref="AU3:AU34" si="4">IF(ISNUMBER($AK3),IF(DAY($AK3)=10,100,IF(DAY($AK3)=11,80,IF(DAY($AK3)=12,50,0))),"")</f>
+        <v>0</v>
+      </c>
+      <c r="AV3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <f t="shared" ref="AW3:AW34" si="5">IF($AS3=0,100,IF($AS3=1,90,IF($AS3=2,75,IF($AS3=3,60,IF($AS3=4,50,IF($AS3=5,25,IF($AS3&gt;=6,0,"")))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AX3" s="4" t="str">
+        <f t="shared" ref="AX3:AX34" si="6">IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($AD3),ISNUMBER($AH3),$AD3&lt;$AH3),0,IF($AS3&gt;=1,(IFERROR(IF(ISTEXT($AI3),($AO3*0.4+$AP3*0.2+$AR3*0.4),""),""))*$AW3/100,IFERROR(IF(ISTEXT($AI3),($AO3*0.4+$AP3*0.2+$AR3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($AH3-$AB3&gt;=0,$AH3-$AB3&lt;=30),100,0),"")),"Revisar")</f>
         <v/>
       </c>
-      <c r="AX3" s="4"/>
-      <c r="AY3" s="4" t="s">
+      <c r="AY3" s="4"/>
+      <c r="AZ3" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="AZ3" s="4" t="s">
+      <c r="BA3" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA3" s="4" t="s">
+      <c r="BB3" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>70</v>
       </c>
@@ -4297,60 +4342,61 @@
       </c>
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
-      <c r="AG4" s="6">
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6">
         <v>46157</v>
       </c>
-      <c r="AH4" s="4"/>
       <c r="AI4" s="4"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="4"/>
+      <c r="AJ4" s="4"/>
+      <c r="AK4" s="6"/>
       <c r="AL4" s="4"/>
       <c r="AM4" s="4"/>
-      <c r="AN4" s="4" t="str">
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO4" s="4" t="str">
+      <c r="AP4" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP4" s="4">
+      <c r="AQ4" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AR4" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="5"/>
-      <c r="AT4" s="4" t="str">
+      <c r="AS4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="5"/>
+      <c r="AU4" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AU4" s="5"/>
-      <c r="AV4" s="4">
+      <c r="AV4" s="5"/>
+      <c r="AW4" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW4" s="4" t="str">
+      <c r="AX4" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX4" s="4"/>
-      <c r="AY4" s="4" t="s">
+      <c r="AY4" s="4"/>
+      <c r="AZ4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="AZ4" s="4" t="s">
+      <c r="BA4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA4" s="4" t="s">
+      <c r="BB4" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>80</v>
       </c>
@@ -4437,72 +4483,73 @@
       <c r="AD5" s="6">
         <v>44561</v>
       </c>
-      <c r="AE5" s="6">
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6">
         <v>45689</v>
       </c>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6">
+      <c r="AG5" s="6"/>
+      <c r="AH5" s="6">
         <v>46157</v>
       </c>
-      <c r="AH5" s="4" t="s">
+      <c r="AI5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="AI5" s="4" t="s">
+      <c r="AJ5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AJ5" s="6">
+      <c r="AK5" s="6">
         <v>46157</v>
       </c>
-      <c r="AK5" s="4"/>
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
-      <c r="AN5" s="4" t="str">
+      <c r="AN5" s="4"/>
+      <c r="AO5" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO5" s="4" t="str">
+      <c r="AP5" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP5" s="4">
+      <c r="AQ5" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ5" s="4" t="str">
+      <c r="AR5" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS5" s="5"/>
-      <c r="AT5" s="4">
+      <c r="AS5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT5" s="5"/>
+      <c r="AU5" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV5" s="4">
+      <c r="AV5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW5" s="4" t="str">
+      <c r="AX5" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX5" s="4"/>
-      <c r="AY5" s="4" t="s">
+      <c r="AY5" s="4"/>
+      <c r="AZ5" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ5" s="4" t="s">
+      <c r="BA5" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA5" s="4" t="s">
+      <c r="BB5" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>88</v>
       </c>
@@ -4595,68 +4642,69 @@
       </c>
       <c r="AE6" s="6"/>
       <c r="AF6" s="6"/>
-      <c r="AG6" s="6">
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6">
         <v>46157</v>
       </c>
-      <c r="AH6" s="4" t="s">
+      <c r="AI6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="AI6" s="4" t="s">
+      <c r="AJ6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AJ6" s="6">
+      <c r="AK6" s="6">
         <v>46157</v>
       </c>
-      <c r="AK6" s="4"/>
       <c r="AL6" s="4"/>
       <c r="AM6" s="4"/>
-      <c r="AN6" s="4">
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO6" s="4">
+      <c r="AP6" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="AQ6" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="AR6" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR6" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS6" s="5"/>
-      <c r="AT6" s="4">
+      <c r="AS6" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="5"/>
+      <c r="AU6" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU6" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV6" s="4">
+      <c r="AV6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW6" s="4">
+      <c r="AX6" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX6" s="4"/>
-      <c r="AY6" s="4" t="s">
+      <c r="AY6" s="4"/>
+      <c r="AZ6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="AZ6" s="4" t="s">
+      <c r="BA6" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA6" s="4" t="s">
+      <c r="BB6" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>98</v>
       </c>
@@ -4743,72 +4791,73 @@
       <c r="AD7" s="6">
         <v>45527</v>
       </c>
-      <c r="AE7" s="6">
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6">
         <v>45527</v>
       </c>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6">
+      <c r="AG7" s="6"/>
+      <c r="AH7" s="6">
         <v>46157</v>
       </c>
-      <c r="AH7" s="4" t="s">
+      <c r="AI7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="AI7" s="4" t="s">
+      <c r="AJ7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="AJ7" s="6">
+      <c r="AK7" s="6">
         <v>46152</v>
       </c>
-      <c r="AK7" s="4"/>
       <c r="AL7" s="4"/>
       <c r="AM7" s="4"/>
-      <c r="AN7" s="4" t="str">
+      <c r="AN7" s="4"/>
+      <c r="AO7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO7" s="4" t="str">
+      <c r="AP7" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP7" s="4">
+      <c r="AQ7" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ7" s="4" t="str">
+      <c r="AR7" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR7" s="4">
+      <c r="AS7" s="4">
         <v>1</v>
       </c>
-      <c r="AS7" s="5"/>
-      <c r="AT7" s="4">
+      <c r="AT7" s="5"/>
+      <c r="AU7" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU7" s="5">
+      <c r="AV7" s="5">
         <v>50</v>
       </c>
-      <c r="AV7" s="4">
+      <c r="AW7" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW7" s="4" t="str">
+      <c r="AX7" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX7" s="4"/>
-      <c r="AY7" s="4" t="s">
+      <c r="AY7" s="4"/>
+      <c r="AZ7" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="AZ7" s="4" t="s">
+      <c r="BA7" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA7" s="4" t="s">
+      <c r="BB7" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>111</v>
       </c>
@@ -4895,72 +4944,73 @@
       <c r="AD8" s="6">
         <v>44926</v>
       </c>
-      <c r="AE8" s="6">
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6">
         <v>44926</v>
       </c>
-      <c r="AF8" s="6"/>
-      <c r="AG8" s="6">
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6">
         <v>46157</v>
       </c>
-      <c r="AH8" s="4" t="s">
+      <c r="AI8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="AI8" s="4" t="s">
+      <c r="AJ8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AJ8" s="6">
+      <c r="AK8" s="6">
         <v>46157</v>
       </c>
-      <c r="AK8" s="4"/>
       <c r="AL8" s="4"/>
       <c r="AM8" s="4"/>
-      <c r="AN8" s="4" t="str">
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO8" s="4" t="str">
+      <c r="AP8" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP8" s="4">
+      <c r="AQ8" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ8" s="4" t="str">
+      <c r="AR8" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR8" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS8" s="5"/>
-      <c r="AT8" s="4">
+      <c r="AS8" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="5"/>
+      <c r="AU8" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU8" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV8" s="4">
+      <c r="AV8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW8" s="4" t="str">
+      <c r="AX8" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX8" s="4"/>
-      <c r="AY8" s="4" t="s">
+      <c r="AY8" s="4"/>
+      <c r="AZ8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="AZ8" s="4" t="s">
+      <c r="BA8" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA8" s="4" t="s">
+      <c r="BB8" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>118</v>
       </c>
@@ -5051,72 +5101,73 @@
       <c r="AD9" s="6">
         <v>45467</v>
       </c>
-      <c r="AE9" s="6">
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6">
         <v>45467</v>
       </c>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6">
+      <c r="AG9" s="6"/>
+      <c r="AH9" s="6">
         <v>46157</v>
       </c>
-      <c r="AH9" s="4" t="s">
+      <c r="AI9" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="AI9" s="4" t="s">
+      <c r="AJ9" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="AJ9" s="6">
+      <c r="AK9" s="6">
         <v>46152</v>
       </c>
-      <c r="AK9" s="4"/>
       <c r="AL9" s="4"/>
       <c r="AM9" s="4"/>
-      <c r="AN9" s="4">
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO9" s="4">
+      <c r="AP9" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP9" s="4">
+      <c r="AQ9" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ9" s="4">
+      <c r="AR9" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS9" s="5"/>
-      <c r="AT9" s="4">
+      <c r="AS9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT9" s="5"/>
+      <c r="AU9" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU9" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV9" s="4">
+      <c r="AV9" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW9" s="4">
+      <c r="AX9" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX9" s="4"/>
-      <c r="AY9" s="4" t="s">
+      <c r="AY9" s="4"/>
+      <c r="AZ9" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AZ9" s="4" t="s">
+      <c r="BA9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA9" s="4" t="s">
+      <c r="BB9" s="4" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>126</v>
       </c>
@@ -5203,72 +5254,73 @@
       <c r="AD10" s="6">
         <v>44742</v>
       </c>
-      <c r="AE10" s="6">
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6">
         <v>44742</v>
       </c>
-      <c r="AF10" s="6"/>
-      <c r="AG10" s="6">
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6">
         <v>46157</v>
       </c>
-      <c r="AH10" s="4" t="s">
+      <c r="AI10" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="AI10" s="4" t="s">
+      <c r="AJ10" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ10" s="6">
+      <c r="AK10" s="6">
         <v>46157</v>
       </c>
-      <c r="AK10" s="4"/>
       <c r="AL10" s="4"/>
       <c r="AM10" s="4"/>
-      <c r="AN10" s="4" t="str">
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO10" s="4" t="str">
+      <c r="AP10" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP10" s="4">
+      <c r="AQ10" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ10" s="4" t="str">
+      <c r="AR10" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS10" s="5"/>
-      <c r="AT10" s="4">
+      <c r="AS10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="5"/>
+      <c r="AU10" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU10" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV10" s="4">
+      <c r="AV10" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW10" s="4" t="str">
+      <c r="AX10" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX10" s="4"/>
-      <c r="AY10" s="4" t="s">
+      <c r="AY10" s="4"/>
+      <c r="AZ10" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ10" s="4" t="s">
+      <c r="BA10" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA10" s="4" t="s">
+      <c r="BB10" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>135</v>
       </c>
@@ -5355,72 +5407,73 @@
       <c r="AD11" s="6">
         <v>44592</v>
       </c>
-      <c r="AE11" s="6">
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6">
         <v>44592</v>
       </c>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6">
+      <c r="AG11" s="6"/>
+      <c r="AH11" s="6">
         <v>46157</v>
       </c>
-      <c r="AH11" s="4" t="s">
+      <c r="AI11" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="AI11" s="4" t="s">
+      <c r="AJ11" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ11" s="6">
+      <c r="AK11" s="6">
         <v>46157</v>
       </c>
-      <c r="AK11" s="4"/>
       <c r="AL11" s="4"/>
       <c r="AM11" s="4"/>
-      <c r="AN11" s="4" t="str">
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO11" s="4" t="str">
+      <c r="AP11" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP11" s="4">
+      <c r="AQ11" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ11" s="4">
+      <c r="AR11" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS11" s="5"/>
-      <c r="AT11" s="4">
+      <c r="AS11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT11" s="5"/>
+      <c r="AU11" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV11" s="4">
+      <c r="AV11" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW11" s="4" t="str">
+      <c r="AX11" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX11" s="4"/>
-      <c r="AY11" s="4" t="s">
+      <c r="AY11" s="4"/>
+      <c r="AZ11" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ11" s="4" t="s">
+      <c r="BA11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA11" s="4" t="s">
+      <c r="BB11" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>141</v>
       </c>
@@ -5507,72 +5560,73 @@
       <c r="AD12" s="6">
         <v>45351</v>
       </c>
-      <c r="AE12" s="6">
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6">
         <v>45351</v>
       </c>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6">
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6">
         <v>46157</v>
       </c>
-      <c r="AH12" s="4" t="s">
+      <c r="AI12" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="AI12" s="4" t="s">
+      <c r="AJ12" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="AJ12" s="6">
+      <c r="AK12" s="6">
         <v>46152</v>
       </c>
-      <c r="AK12" s="4"/>
       <c r="AL12" s="4"/>
       <c r="AM12" s="4"/>
-      <c r="AN12" s="4" t="str">
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO12" s="4" t="str">
+      <c r="AP12" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP12" s="4">
+      <c r="AQ12" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ12" s="4" t="str">
+      <c r="AR12" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR12" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS12" s="5"/>
-      <c r="AT12" s="4">
+      <c r="AS12" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="5"/>
+      <c r="AU12" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU12" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV12" s="4">
+      <c r="AV12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW12" s="4" t="str">
+      <c r="AX12" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX12" s="4"/>
-      <c r="AY12" s="4" t="s">
+      <c r="AY12" s="4"/>
+      <c r="AZ12" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="AZ12" s="4" t="s">
+      <c r="BA12" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA12" s="4" t="s">
+      <c r="BB12" s="4" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>150</v>
       </c>
@@ -5665,68 +5719,69 @@
       </c>
       <c r="AE13" s="6"/>
       <c r="AF13" s="6"/>
-      <c r="AG13" s="6">
+      <c r="AG13" s="6"/>
+      <c r="AH13" s="6">
         <v>46157</v>
       </c>
-      <c r="AH13" s="4" t="s">
+      <c r="AI13" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="AI13" s="4" t="s">
+      <c r="AJ13" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="AJ13" s="6">
+      <c r="AK13" s="6">
         <v>46152</v>
       </c>
-      <c r="AK13" s="4"/>
       <c r="AL13" s="4"/>
       <c r="AM13" s="4"/>
-      <c r="AN13" s="4">
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO13" s="4">
+      <c r="AP13" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP13" s="4">
+      <c r="AQ13" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ13" s="4">
+      <c r="AR13" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR13" s="4">
+      <c r="AS13" s="4">
         <v>1</v>
       </c>
-      <c r="AS13" s="5"/>
-      <c r="AT13" s="4">
+      <c r="AT13" s="5"/>
+      <c r="AU13" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU13" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV13" s="4">
+      <c r="AV13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW13" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW13" s="4">
+      <c r="AX13" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX13" s="4"/>
-      <c r="AY13" s="4" t="s">
+      <c r="AY13" s="4"/>
+      <c r="AZ13" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="AZ13" s="4" t="s">
+      <c r="BA13" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="BA13" s="4" t="s">
+      <c r="BB13" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>161</v>
       </c>
@@ -5813,72 +5868,73 @@
       <c r="AD14" s="6">
         <v>45577</v>
       </c>
-      <c r="AE14" s="6">
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6">
         <v>45577</v>
       </c>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6">
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6">
         <v>46157</v>
       </c>
-      <c r="AH14" s="4" t="s">
+      <c r="AI14" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="AI14" s="4" t="s">
+      <c r="AJ14" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="AJ14" s="6">
+      <c r="AK14" s="6">
         <v>46152</v>
       </c>
-      <c r="AK14" s="4"/>
       <c r="AL14" s="4"/>
       <c r="AM14" s="4"/>
-      <c r="AN14" s="4" t="str">
+      <c r="AN14" s="4"/>
+      <c r="AO14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO14" s="4" t="str">
+      <c r="AP14" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP14" s="4">
+      <c r="AQ14" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ14" s="4" t="str">
+      <c r="AR14" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR14" s="4">
+      <c r="AS14" s="4">
         <v>1</v>
       </c>
-      <c r="AS14" s="5"/>
-      <c r="AT14" s="4">
+      <c r="AT14" s="5"/>
+      <c r="AU14" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV14" s="4">
+      <c r="AV14" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW14" s="4" t="str">
+      <c r="AX14" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX14" s="4"/>
-      <c r="AY14" s="4" t="s">
+      <c r="AY14" s="4"/>
+      <c r="AZ14" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="AZ14" s="4" t="s">
+      <c r="BA14" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA14" s="4" t="s">
+      <c r="BB14" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>169</v>
       </c>
@@ -5971,68 +6027,69 @@
       </c>
       <c r="AE15" s="6"/>
       <c r="AF15" s="6"/>
-      <c r="AG15" s="6">
+      <c r="AG15" s="6"/>
+      <c r="AH15" s="6">
         <v>46157</v>
       </c>
-      <c r="AH15" s="4" t="s">
+      <c r="AI15" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="AI15" s="4" t="s">
+      <c r="AJ15" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ15" s="6">
+      <c r="AK15" s="6">
         <v>46157</v>
       </c>
-      <c r="AK15" s="4"/>
       <c r="AL15" s="4"/>
       <c r="AM15" s="4"/>
-      <c r="AN15" s="4">
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO15" s="4">
+      <c r="AP15" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP15" s="4">
+      <c r="AQ15" s="4">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AQ15" s="4">
+      <c r="AR15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AR15" s="4">
+      <c r="AS15" s="4">
         <v>1</v>
       </c>
-      <c r="AS15" s="5"/>
-      <c r="AT15" s="4">
+      <c r="AT15" s="5"/>
+      <c r="AU15" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU15" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV15" s="4">
+      <c r="AV15" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW15" s="4">
+      <c r="AX15" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX15" s="4"/>
-      <c r="AY15" s="4" t="s">
+      <c r="AY15" s="4"/>
+      <c r="AZ15" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="AZ15" s="4" t="s">
+      <c r="BA15" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA15" s="4" t="s">
+      <c r="BB15" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>175</v>
       </c>
@@ -6119,72 +6176,73 @@
       <c r="AD16" s="6">
         <v>45287</v>
       </c>
-      <c r="AE16" s="6">
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6">
         <v>45287</v>
       </c>
-      <c r="AF16" s="6"/>
-      <c r="AG16" s="6">
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6">
         <v>46157</v>
       </c>
-      <c r="AH16" s="4" t="s">
+      <c r="AI16" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="AI16" s="4" t="s">
+      <c r="AJ16" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ16" s="6">
+      <c r="AK16" s="6">
         <v>46157</v>
       </c>
-      <c r="AK16" s="4"/>
       <c r="AL16" s="4"/>
       <c r="AM16" s="4"/>
-      <c r="AN16" s="4" t="str">
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO16" s="4" t="str">
+      <c r="AP16" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP16" s="4">
+      <c r="AQ16" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ16" s="4">
+      <c r="AR16" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="5"/>
-      <c r="AT16" s="4">
+      <c r="AS16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="5"/>
+      <c r="AU16" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV16" s="4">
+      <c r="AV16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW16" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW16" s="4" t="str">
+      <c r="AX16" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX16" s="4"/>
-      <c r="AY16" s="4" t="s">
+      <c r="AY16" s="4"/>
+      <c r="AZ16" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ16" s="4" t="s">
+      <c r="BA16" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA16" s="4" t="s">
+      <c r="BB16" s="4" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>182</v>
       </c>
@@ -6277,68 +6335,69 @@
       </c>
       <c r="AE17" s="6"/>
       <c r="AF17" s="6"/>
-      <c r="AG17" s="6">
+      <c r="AG17" s="6"/>
+      <c r="AH17" s="6">
         <v>46157</v>
       </c>
-      <c r="AH17" s="4" t="s">
+      <c r="AI17" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="AI17" s="4" t="s">
+      <c r="AJ17" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="AJ17" s="6">
+      <c r="AK17" s="6">
         <v>46152</v>
       </c>
-      <c r="AK17" s="4"/>
       <c r="AL17" s="4"/>
       <c r="AM17" s="4"/>
-      <c r="AN17" s="4">
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AO17" s="4">
+      <c r="AP17" s="4">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AP17" s="4">
+      <c r="AQ17" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ17" s="4">
+      <c r="AR17" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR17" s="4">
+      <c r="AS17" s="4">
         <v>2</v>
       </c>
-      <c r="AS17" s="5"/>
-      <c r="AT17" s="4">
+      <c r="AT17" s="5"/>
+      <c r="AU17" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU17" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV17" s="4">
+      <c r="AV17" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW17" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AW17" s="4">
+      <c r="AX17" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX17" s="4"/>
-      <c r="AY17" s="4" t="s">
+      <c r="AY17" s="4"/>
+      <c r="AZ17" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="AZ17" s="4" t="s">
+      <c r="BA17" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA17" s="4" t="s">
+      <c r="BB17" s="4" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>191</v>
       </c>
@@ -6431,68 +6490,69 @@
       </c>
       <c r="AE18" s="6"/>
       <c r="AF18" s="6"/>
-      <c r="AG18" s="6">
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6">
         <v>46157</v>
       </c>
-      <c r="AH18" s="4" t="s">
+      <c r="AI18" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="AI18" s="4" t="s">
+      <c r="AJ18" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ18" s="6">
+      <c r="AK18" s="6">
         <v>46157</v>
       </c>
-      <c r="AK18" s="4"/>
       <c r="AL18" s="4"/>
       <c r="AM18" s="4"/>
-      <c r="AN18" s="4">
+      <c r="AN18" s="4"/>
+      <c r="AO18" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO18" s="4">
+      <c r="AP18" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP18" s="4">
+      <c r="AQ18" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ18" s="4">
+      <c r="AR18" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR18" s="4">
+      <c r="AS18" s="4">
         <v>1</v>
       </c>
-      <c r="AS18" s="5"/>
-      <c r="AT18" s="4">
+      <c r="AT18" s="5"/>
+      <c r="AU18" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU18" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV18" s="4">
+      <c r="AV18" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW18" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW18" s="4">
+      <c r="AX18" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX18" s="4"/>
-      <c r="AY18" s="4" t="s">
+      <c r="AY18" s="4"/>
+      <c r="AZ18" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="AZ18" s="4" t="s">
+      <c r="BA18" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA18" s="4" t="s">
+      <c r="BB18" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>198</v>
       </c>
@@ -6585,68 +6645,69 @@
       </c>
       <c r="AE19" s="6"/>
       <c r="AF19" s="6"/>
-      <c r="AG19" s="6">
+      <c r="AG19" s="6"/>
+      <c r="AH19" s="6">
         <v>46157</v>
       </c>
-      <c r="AH19" s="4" t="s">
+      <c r="AI19" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="AI19" s="4" t="s">
+      <c r="AJ19" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ19" s="6">
+      <c r="AK19" s="6">
         <v>46157</v>
       </c>
-      <c r="AK19" s="4"/>
       <c r="AL19" s="4"/>
       <c r="AM19" s="4"/>
-      <c r="AN19" s="4">
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO19" s="4">
+      <c r="AP19" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP19" s="4">
+      <c r="AQ19" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ19" s="4">
+      <c r="AR19" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR19" s="4">
+      <c r="AS19" s="4">
         <v>1</v>
       </c>
-      <c r="AS19" s="5"/>
-      <c r="AT19" s="4">
+      <c r="AT19" s="5"/>
+      <c r="AU19" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV19" s="4">
+      <c r="AV19" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW19" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW19" s="4">
+      <c r="AX19" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX19" s="4"/>
-      <c r="AY19" s="4" t="s">
+      <c r="AY19" s="4"/>
+      <c r="AZ19" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="AZ19" s="4" t="s">
+      <c r="BA19" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA19" s="4" t="s">
+      <c r="BB19" s="4" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>204</v>
       </c>
@@ -6733,72 +6794,73 @@
       <c r="AD20" s="6">
         <v>45549</v>
       </c>
-      <c r="AE20" s="6">
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6">
         <v>45549</v>
       </c>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6">
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6">
         <v>46157</v>
       </c>
-      <c r="AH20" s="4" t="s">
+      <c r="AI20" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="AI20" s="4" t="s">
+      <c r="AJ20" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="AJ20" s="6">
+      <c r="AK20" s="6">
         <v>46157</v>
       </c>
-      <c r="AK20" s="4"/>
       <c r="AL20" s="4"/>
       <c r="AM20" s="4"/>
-      <c r="AN20" s="4" t="str">
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO20" s="4" t="str">
+      <c r="AP20" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP20" s="4" t="str">
+      <c r="AQ20" s="4" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="AQ20" s="4" t="str">
+      <c r="AR20" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR20" s="4">
+      <c r="AS20" s="4">
         <v>1</v>
       </c>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="4">
+      <c r="AT20" s="5"/>
+      <c r="AU20" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV20" s="4">
+      <c r="AV20" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW20" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW20" s="4" t="str">
+      <c r="AX20" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX20" s="4"/>
-      <c r="AY20" s="4" t="s">
+      <c r="AY20" s="4"/>
+      <c r="AZ20" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ20" s="4" t="s">
+      <c r="BA20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA20" s="4" t="s">
+      <c r="BB20" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>209</v>
       </c>
@@ -6891,68 +6953,69 @@
       </c>
       <c r="AE21" s="6"/>
       <c r="AF21" s="6"/>
-      <c r="AG21" s="6">
+      <c r="AG21" s="6"/>
+      <c r="AH21" s="6">
         <v>46157</v>
       </c>
-      <c r="AH21" s="4" t="s">
+      <c r="AI21" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="AI21" s="4" t="s">
+      <c r="AJ21" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="AJ21" s="6">
+      <c r="AK21" s="6">
         <v>46152</v>
       </c>
-      <c r="AK21" s="4"/>
       <c r="AL21" s="4"/>
       <c r="AM21" s="4"/>
-      <c r="AN21" s="4">
+      <c r="AN21" s="4"/>
+      <c r="AO21" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO21" s="4">
+      <c r="AP21" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP21" s="4">
+      <c r="AQ21" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ21" s="4">
+      <c r="AR21" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR21" s="4">
+      <c r="AS21" s="4">
         <v>1</v>
       </c>
-      <c r="AS21" s="5"/>
-      <c r="AT21" s="4">
+      <c r="AT21" s="5"/>
+      <c r="AU21" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU21" s="5">
+      <c r="AV21" s="5">
         <v>10</v>
       </c>
-      <c r="AV21" s="4">
+      <c r="AW21" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW21" s="4">
+      <c r="AX21" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX21" s="4"/>
-      <c r="AY21" s="4" t="s">
+      <c r="AY21" s="4"/>
+      <c r="AZ21" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="AZ21" s="4" t="s">
+      <c r="BA21" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="BA21" s="4" t="s">
+      <c r="BB21" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>218</v>
       </c>
@@ -7045,68 +7108,69 @@
       </c>
       <c r="AE22" s="6"/>
       <c r="AF22" s="6"/>
-      <c r="AG22" s="6">
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6">
         <v>46157</v>
       </c>
-      <c r="AH22" s="4" t="s">
+      <c r="AI22" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="AI22" s="4" t="s">
+      <c r="AJ22" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="AJ22" s="6">
+      <c r="AK22" s="6">
         <v>46152</v>
       </c>
-      <c r="AK22" s="4"/>
       <c r="AL22" s="4"/>
       <c r="AM22" s="4"/>
-      <c r="AN22" s="4">
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AO22" s="4">
+      <c r="AP22" s="4">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AP22" s="4">
+      <c r="AQ22" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ22" s="4">
+      <c r="AR22" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR22" s="4">
+      <c r="AS22" s="4">
         <v>1</v>
       </c>
-      <c r="AS22" s="5"/>
-      <c r="AT22" s="4">
+      <c r="AT22" s="5"/>
+      <c r="AU22" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU22" s="5">
+      <c r="AV22" s="5">
         <v>90</v>
       </c>
-      <c r="AV22" s="4">
+      <c r="AW22" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW22" s="4">
+      <c r="AX22" s="4">
         <f t="shared" si="6"/>
         <v>90</v>
       </c>
-      <c r="AX22" s="4"/>
-      <c r="AY22" s="4" t="s">
+      <c r="AY22" s="4"/>
+      <c r="AZ22" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="AZ22" s="4" t="s">
+      <c r="BA22" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA22" s="4" t="s">
+      <c r="BB22" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>226</v>
       </c>
@@ -7193,66 +7257,67 @@
       <c r="AD23" s="6">
         <v>45407</v>
       </c>
-      <c r="AE23" s="6">
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6">
         <v>45407</v>
       </c>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6">
+      <c r="AG23" s="6"/>
+      <c r="AH23" s="6">
         <v>46157</v>
       </c>
-      <c r="AH23" s="4"/>
       <c r="AI23" s="4"/>
-      <c r="AJ23" s="6">
+      <c r="AJ23" s="4"/>
+      <c r="AK23" s="6">
         <v>46152</v>
       </c>
-      <c r="AK23" s="4"/>
       <c r="AL23" s="4"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="4" t="str">
+      <c r="AN23" s="4"/>
+      <c r="AO23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO23" s="4" t="str">
+      <c r="AP23" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP23" s="4">
+      <c r="AQ23" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ23" s="4" t="str">
+      <c r="AR23" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR23" s="4">
+      <c r="AS23" s="4">
         <v>1</v>
       </c>
-      <c r="AS23" s="5"/>
-      <c r="AT23" s="4">
+      <c r="AT23" s="5"/>
+      <c r="AU23" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU23" s="5"/>
-      <c r="AV23" s="4">
+      <c r="AV23" s="5"/>
+      <c r="AW23" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW23" s="4" t="str">
+      <c r="AX23" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX23" s="4"/>
-      <c r="AY23" s="4" t="s">
+      <c r="AY23" s="4"/>
+      <c r="AZ23" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ23" s="4" t="s">
+      <c r="BA23" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA23" s="4" t="s">
+      <c r="BB23" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>232</v>
       </c>
@@ -7339,66 +7404,67 @@
       <c r="AD24" s="6">
         <v>44651</v>
       </c>
-      <c r="AE24" s="6">
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6">
         <v>44651</v>
       </c>
-      <c r="AF24" s="6"/>
-      <c r="AG24" s="6">
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6">
         <v>46157</v>
       </c>
-      <c r="AH24" s="4"/>
       <c r="AI24" s="4"/>
-      <c r="AJ24" s="6">
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="6">
         <v>46152</v>
       </c>
-      <c r="AK24" s="4"/>
       <c r="AL24" s="4"/>
       <c r="AM24" s="4"/>
-      <c r="AN24" s="4" t="str">
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO24" s="4" t="str">
+      <c r="AP24" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP24" s="4">
+      <c r="AQ24" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ24" s="4" t="str">
+      <c r="AR24" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR24" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS24" s="5"/>
-      <c r="AT24" s="4">
+      <c r="AS24" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT24" s="5"/>
+      <c r="AU24" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU24" s="5"/>
-      <c r="AV24" s="4">
+      <c r="AV24" s="5"/>
+      <c r="AW24" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW24" s="4" t="str">
+      <c r="AX24" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX24" s="4"/>
-      <c r="AY24" s="4" t="s">
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="AZ24" s="4" t="s">
+      <c r="BA24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA24" s="4" t="s">
+      <c r="BB24" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>241</v>
       </c>
@@ -7485,64 +7551,65 @@
       <c r="AD25" s="6">
         <v>45046</v>
       </c>
-      <c r="AE25" s="6">
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6">
         <v>45046</v>
       </c>
-      <c r="AF25" s="6"/>
-      <c r="AG25" s="6">
+      <c r="AG25" s="6"/>
+      <c r="AH25" s="6">
         <v>46157</v>
       </c>
-      <c r="AH25" s="4"/>
       <c r="AI25" s="4"/>
-      <c r="AJ25" s="6"/>
-      <c r="AK25" s="4"/>
+      <c r="AJ25" s="4"/>
+      <c r="AK25" s="6"/>
       <c r="AL25" s="4"/>
       <c r="AM25" s="4"/>
-      <c r="AN25" s="4" t="str">
+      <c r="AN25" s="4"/>
+      <c r="AO25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO25" s="4" t="str">
+      <c r="AP25" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP25" s="4">
+      <c r="AQ25" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ25" s="4" t="str">
+      <c r="AR25" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR25" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS25" s="5"/>
-      <c r="AT25" s="4" t="str">
+      <c r="AS25" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT25" s="5"/>
+      <c r="AU25" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AU25" s="5"/>
-      <c r="AV25" s="4">
+      <c r="AV25" s="5"/>
+      <c r="AW25" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW25" s="4" t="str">
+      <c r="AX25" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX25" s="4"/>
-      <c r="AY25" s="4" t="s">
+      <c r="AY25" s="4"/>
+      <c r="AZ25" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ25" s="4" t="s">
+      <c r="BA25" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA25" s="4" t="s">
+      <c r="BB25" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>246</v>
       </c>
@@ -7635,68 +7702,69 @@
       </c>
       <c r="AE26" s="6"/>
       <c r="AF26" s="6"/>
-      <c r="AG26" s="6">
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6">
         <v>46157</v>
       </c>
-      <c r="AH26" s="4" t="s">
+      <c r="AI26" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="AI26" s="4" t="s">
+      <c r="AJ26" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="AJ26" s="6">
+      <c r="AK26" s="6">
         <v>46152</v>
       </c>
-      <c r="AK26" s="4"/>
       <c r="AL26" s="4"/>
       <c r="AM26" s="4"/>
-      <c r="AN26" s="4">
+      <c r="AN26" s="4"/>
+      <c r="AO26" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO26" s="4">
+      <c r="AP26" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP26" s="4">
+      <c r="AQ26" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ26" s="4">
+      <c r="AR26" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR26" s="4">
+      <c r="AS26" s="4">
         <v>2</v>
       </c>
-      <c r="AS26" s="5"/>
-      <c r="AT26" s="4">
+      <c r="AT26" s="5"/>
+      <c r="AU26" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU26" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV26" s="4">
+      <c r="AV26" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW26" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AW26" s="4">
+      <c r="AX26" s="4">
         <f t="shared" si="6"/>
         <v>30</v>
       </c>
-      <c r="AX26" s="4"/>
-      <c r="AY26" s="4" t="s">
+      <c r="AY26" s="4"/>
+      <c r="AZ26" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="AZ26" s="4" t="s">
+      <c r="BA26" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA26" s="4" t="s">
+      <c r="BB26" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>254</v>
       </c>
@@ -7783,72 +7851,73 @@
       <c r="AD27" s="6">
         <v>45412</v>
       </c>
-      <c r="AE27" s="6">
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6">
         <v>45412</v>
       </c>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6">
+      <c r="AG27" s="6"/>
+      <c r="AH27" s="6">
         <v>46157</v>
       </c>
-      <c r="AH27" s="4" t="s">
+      <c r="AI27" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="AI27" s="4" t="s">
+      <c r="AJ27" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="AJ27" s="6">
+      <c r="AK27" s="6">
         <v>46157</v>
       </c>
-      <c r="AK27" s="4"/>
       <c r="AL27" s="4"/>
       <c r="AM27" s="4"/>
-      <c r="AN27" s="4" t="str">
+      <c r="AN27" s="4"/>
+      <c r="AO27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO27" s="4" t="str">
+      <c r="AP27" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP27" s="4">
+      <c r="AQ27" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ27" s="4" t="str">
+      <c r="AR27" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR27" s="4">
+      <c r="AS27" s="4">
         <v>1</v>
       </c>
-      <c r="AS27" s="5"/>
-      <c r="AT27" s="4">
+      <c r="AT27" s="5"/>
+      <c r="AU27" s="4">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AU27" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV27" s="4">
+      <c r="AV27" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW27" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW27" s="4" t="str">
+      <c r="AX27" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX27" s="4"/>
-      <c r="AY27" s="4" t="s">
+      <c r="AY27" s="4"/>
+      <c r="AZ27" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="AZ27" s="4" t="s">
+      <c r="BA27" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA27" s="4" t="s">
+      <c r="BB27" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>260</v>
       </c>
@@ -7935,70 +8004,71 @@
       <c r="AD28" s="6">
         <v>45746</v>
       </c>
-      <c r="AE28" s="6">
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6">
         <v>45746</v>
       </c>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6">
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6">
         <v>46157</v>
       </c>
-      <c r="AH28" s="4" t="s">
+      <c r="AI28" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="AI28" s="4" t="s">
+      <c r="AJ28" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AJ28" s="6">
+      <c r="AK28" s="6">
         <v>46152</v>
       </c>
-      <c r="AK28" s="4"/>
       <c r="AL28" s="4"/>
       <c r="AM28" s="4"/>
-      <c r="AN28" s="4" t="str">
+      <c r="AN28" s="4"/>
+      <c r="AO28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO28" s="4" t="str">
+      <c r="AP28" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP28" s="4">
+      <c r="AQ28" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ28" s="4" t="str">
+      <c r="AR28" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR28" s="4">
+      <c r="AS28" s="4">
         <v>1</v>
       </c>
-      <c r="AS28" s="5"/>
-      <c r="AT28" s="4">
+      <c r="AT28" s="5"/>
+      <c r="AU28" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU28" s="5"/>
-      <c r="AV28" s="4">
+      <c r="AV28" s="5"/>
+      <c r="AW28" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW28" s="4" t="str">
+      <c r="AX28" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX28" s="4"/>
-      <c r="AY28" s="4" t="s">
+      <c r="AY28" s="4"/>
+      <c r="AZ28" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ28" s="4" t="s">
+      <c r="BA28" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA28" s="4" t="s">
+      <c r="BB28" s="4" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>267</v>
       </c>
@@ -8085,72 +8155,73 @@
       <c r="AD29" s="6">
         <v>45858</v>
       </c>
-      <c r="AE29" s="6">
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6">
         <v>45858</v>
       </c>
-      <c r="AF29" s="6"/>
-      <c r="AG29" s="6">
+      <c r="AG29" s="6"/>
+      <c r="AH29" s="6">
         <v>46157</v>
       </c>
-      <c r="AH29" s="4" t="s">
+      <c r="AI29" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="AI29" s="4" t="s">
+      <c r="AJ29" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="AJ29" s="6">
+      <c r="AK29" s="6">
         <v>46152</v>
       </c>
-      <c r="AK29" s="4"/>
       <c r="AL29" s="4"/>
       <c r="AM29" s="4"/>
-      <c r="AN29" s="4" t="str">
+      <c r="AN29" s="4"/>
+      <c r="AO29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO29" s="4" t="str">
+      <c r="AP29" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP29" s="4">
+      <c r="AQ29" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ29" s="4" t="str">
+      <c r="AR29" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR29" s="4">
+      <c r="AS29" s="4">
         <v>2</v>
       </c>
-      <c r="AS29" s="5"/>
-      <c r="AT29" s="4">
+      <c r="AT29" s="5"/>
+      <c r="AU29" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU29" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV29" s="4">
+      <c r="AV29" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW29" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AW29" s="4" t="str">
+      <c r="AX29" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX29" s="4"/>
-      <c r="AY29" s="4" t="s">
+      <c r="AY29" s="4"/>
+      <c r="AZ29" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AZ29" s="4" t="s">
+      <c r="BA29" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA29" s="4" t="s">
+      <c r="BB29" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>274</v>
       </c>
@@ -8237,66 +8308,67 @@
       <c r="AD30" s="6">
         <v>45569</v>
       </c>
-      <c r="AE30" s="6">
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6">
         <v>45569</v>
       </c>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6">
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6">
         <v>46157</v>
       </c>
-      <c r="AH30" s="4" t="s">
+      <c r="AI30" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AI30" s="4"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="4"/>
+      <c r="AJ30" s="4"/>
+      <c r="AK30" s="6"/>
       <c r="AL30" s="4"/>
       <c r="AM30" s="4"/>
-      <c r="AN30" s="4" t="str">
+      <c r="AN30" s="4"/>
+      <c r="AO30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO30" s="4" t="str">
+      <c r="AP30" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP30" s="4">
+      <c r="AQ30" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ30" s="4" t="str">
+      <c r="AR30" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR30" s="4">
+      <c r="AS30" s="4">
         <v>1</v>
       </c>
-      <c r="AS30" s="5"/>
-      <c r="AT30" s="4" t="str">
+      <c r="AT30" s="5"/>
+      <c r="AU30" s="4" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="AU30" s="5"/>
-      <c r="AV30" s="4">
+      <c r="AV30" s="5"/>
+      <c r="AW30" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW30" s="4" t="str">
+      <c r="AX30" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX30" s="4"/>
-      <c r="AY30" s="4" t="s">
+      <c r="AY30" s="4"/>
+      <c r="AZ30" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ30" s="4" t="s">
+      <c r="BA30" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA30" s="4" t="s">
+      <c r="BB30" s="4" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>279</v>
       </c>
@@ -8383,70 +8455,71 @@
       <c r="AD31" s="6">
         <v>45900</v>
       </c>
-      <c r="AE31" s="6">
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6">
         <v>45900</v>
       </c>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6">
+      <c r="AG31" s="6"/>
+      <c r="AH31" s="6">
         <v>46157</v>
       </c>
-      <c r="AH31" s="4" t="s">
+      <c r="AI31" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="AI31" s="4" t="s">
+      <c r="AJ31" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="AJ31" s="6">
+      <c r="AK31" s="6">
         <v>46152</v>
       </c>
-      <c r="AK31" s="4"/>
       <c r="AL31" s="4"/>
       <c r="AM31" s="4"/>
-      <c r="AN31" s="4" t="str">
+      <c r="AN31" s="4"/>
+      <c r="AO31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO31" s="4" t="str">
+      <c r="AP31" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP31" s="4">
+      <c r="AQ31" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ31" s="4" t="str">
+      <c r="AR31" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR31" s="4">
+      <c r="AS31" s="4">
         <v>2</v>
       </c>
-      <c r="AS31" s="5"/>
-      <c r="AT31" s="4">
+      <c r="AT31" s="5"/>
+      <c r="AU31" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU31" s="5"/>
-      <c r="AV31" s="4">
+      <c r="AV31" s="5"/>
+      <c r="AW31" s="4">
         <f t="shared" si="5"/>
         <v>75</v>
       </c>
-      <c r="AW31" s="4" t="str">
+      <c r="AX31" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX31" s="4"/>
-      <c r="AY31" s="4" t="s">
+      <c r="AY31" s="4"/>
+      <c r="AZ31" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ31" s="4" t="s">
+      <c r="BA31" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA31" s="4" t="s">
+      <c r="BB31" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>286</v>
       </c>
@@ -8539,68 +8612,69 @@
       </c>
       <c r="AE32" s="6"/>
       <c r="AF32" s="6"/>
-      <c r="AG32" s="6">
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6">
         <v>46157</v>
       </c>
-      <c r="AH32" s="4" t="s">
+      <c r="AI32" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="AI32" s="4" t="s">
+      <c r="AJ32" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="AJ32" s="6">
+      <c r="AK32" s="6">
         <v>46152</v>
       </c>
-      <c r="AK32" s="4"/>
       <c r="AL32" s="4"/>
       <c r="AM32" s="4"/>
-      <c r="AN32" s="4">
+      <c r="AN32" s="4"/>
+      <c r="AO32" s="4">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="AO32" s="4">
+      <c r="AP32" s="4">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="AP32" s="4">
+      <c r="AQ32" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ32" s="4">
+      <c r="AR32" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR32" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS32" s="5"/>
-      <c r="AT32" s="4">
+      <c r="AS32" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT32" s="5"/>
+      <c r="AU32" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU32" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV32" s="4">
+      <c r="AV32" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW32" s="4">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="AW32" s="4">
+      <c r="AX32" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX32" s="4"/>
-      <c r="AY32" s="4" t="s">
+      <c r="AY32" s="4"/>
+      <c r="AZ32" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="AZ32" s="4" t="s">
+      <c r="BA32" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA32" s="4" t="s">
+      <c r="BB32" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>294</v>
       </c>
@@ -8693,68 +8767,69 @@
       </c>
       <c r="AE33" s="6"/>
       <c r="AF33" s="6"/>
-      <c r="AG33" s="6">
+      <c r="AG33" s="6"/>
+      <c r="AH33" s="6">
         <v>46157</v>
       </c>
-      <c r="AH33" s="4" t="s">
+      <c r="AI33" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="AI33" s="4" t="s">
+      <c r="AJ33" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="AJ33" s="6">
+      <c r="AK33" s="6">
         <v>46152</v>
       </c>
-      <c r="AK33" s="4"/>
       <c r="AL33" s="4"/>
       <c r="AM33" s="4"/>
-      <c r="AN33" s="4">
+      <c r="AN33" s="4"/>
+      <c r="AO33" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AO33" s="4">
+      <c r="AP33" s="4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AP33" s="4">
+      <c r="AQ33" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ33" s="4">
+      <c r="AR33" s="4">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AR33" s="4">
+      <c r="AS33" s="4">
         <v>3</v>
       </c>
-      <c r="AS33" s="5"/>
-      <c r="AT33" s="4">
+      <c r="AT33" s="5"/>
+      <c r="AU33" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU33" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV33" s="4">
+      <c r="AV33" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW33" s="4">
         <f t="shared" si="5"/>
         <v>60</v>
       </c>
-      <c r="AW33" s="4">
+      <c r="AX33" s="4">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AX33" s="4"/>
-      <c r="AY33" s="4" t="s">
+      <c r="AY33" s="4"/>
+      <c r="AZ33" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="AZ33" s="4" t="s">
+      <c r="BA33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA33" s="4" t="s">
+      <c r="BB33" s="4" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>304</v>
       </c>
@@ -8841,70 +8916,71 @@
       <c r="AD34" s="6">
         <v>45716</v>
       </c>
-      <c r="AE34" s="6">
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6">
         <v>45716</v>
       </c>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6">
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6">
         <v>46157</v>
       </c>
-      <c r="AH34" s="4" t="s">
+      <c r="AI34" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="AI34" s="4" t="s">
+      <c r="AJ34" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AJ34" s="6">
+      <c r="AK34" s="6">
         <v>46152</v>
       </c>
-      <c r="AK34" s="4"/>
       <c r="AL34" s="4"/>
       <c r="AM34" s="4"/>
-      <c r="AN34" s="4" t="str">
+      <c r="AN34" s="4"/>
+      <c r="AO34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="AO34" s="4" t="str">
+      <c r="AP34" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="AP34" s="4">
+      <c r="AQ34" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AQ34" s="4" t="str">
+      <c r="AR34" s="4" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="AR34" s="4">
+      <c r="AS34" s="4">
         <v>1</v>
       </c>
-      <c r="AS34" s="5"/>
-      <c r="AT34" s="4">
+      <c r="AT34" s="5"/>
+      <c r="AU34" s="4">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="AU34" s="5"/>
-      <c r="AV34" s="4">
+      <c r="AV34" s="5"/>
+      <c r="AW34" s="4">
         <f t="shared" si="5"/>
         <v>90</v>
       </c>
-      <c r="AW34" s="4" t="str">
+      <c r="AX34" s="4" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="AX34" s="4"/>
-      <c r="AY34" s="4" t="s">
+      <c r="AY34" s="4"/>
+      <c r="AZ34" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ34" s="4" t="s">
+      <c r="BA34" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA34" s="4" t="s">
+      <c r="BB34" s="4" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>311</v>
       </c>
@@ -8989,64 +9065,65 @@
       <c r="AD35" s="6">
         <v>45288</v>
       </c>
-      <c r="AE35" s="6">
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6">
         <v>45288</v>
       </c>
-      <c r="AF35" s="6"/>
-      <c r="AG35" s="6">
+      <c r="AG35" s="6"/>
+      <c r="AH35" s="6">
         <v>46157</v>
       </c>
-      <c r="AH35" s="4"/>
       <c r="AI35" s="4"/>
-      <c r="AJ35" s="6"/>
-      <c r="AK35" s="4"/>
+      <c r="AJ35" s="4"/>
+      <c r="AK35" s="6"/>
       <c r="AL35" s="4"/>
       <c r="AM35" s="4"/>
-      <c r="AN35" s="4" t="str">
-        <f t="shared" ref="AN35:AN60" si="7">IF(AND($X35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X35&gt;1.25,$X35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X35&gt;1.2,$X35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X35&gt;=0.84,$X35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X35&gt;=0.38,$X35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($X35-0.38)/(0.84-0.38))*100,IF(AND($X35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AN35" s="4"/>
+      <c r="AO35" s="4" t="str">
+        <f t="shared" ref="AO35:AO60" si="7">IF(AND($X35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($X35&gt;1.25,$X35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($X35&gt;1.2,$X35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($X35&gt;=0.84,$X35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($X35&gt;=0.38,$X35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($X35-0.38)/(0.84-0.38))*100,IF(AND($X35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AO35" s="4" t="str">
-        <f t="shared" ref="AO35:AO60" si="8">IF(AND($W35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W35&gt;1.25,$W35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W35&gt;1.2,$W35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W35&gt;=0.84,$W35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W35&gt;=0.38,$W35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($W35-0.38)/(0.84-0.38))*100,IF(AND($W35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
+      <c r="AP35" s="4" t="str">
+        <f t="shared" ref="AP35:AP60" si="8">IF(AND($W35&gt;1.3,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($W35&gt;1.25,$W35&lt;=1.3,$G35="CONTRATADO EN EJECUCIÓN"),30,IF(AND($W35&gt;1.2,$W35&lt;=1.25,$G35="CONTRATADO EN EJECUCIÓN"),90,IF(AND($W35&gt;=0.84,$W35&lt;1.2,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($W35&gt;=0.38,$W35&lt;0.84,$G35="CONTRATADO EN EJECUCIÓN"),(($W35-0.38)/(0.84-0.38))*100,IF(AND($W35&lt;0.38,$G35="CONTRATADO EN EJECUCIÓN"),0,""))))))</f>
         <v/>
       </c>
-      <c r="AP35" s="4">
-        <f t="shared" ref="AP35:AP60" si="9">IF(AND($V35&lt;60,($V35-$U35)&lt;=50),100,IF(AND($V35&lt;60,($V35-$U35)&gt;50),0,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&lt;=40),100,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&gt;40),0,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&lt;=30),100,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&gt;30),0,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&lt;=20),100,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&gt;20),0,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&lt;=10),100,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&gt;10),0,""))))))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AQ35" s="4" t="str">
-        <f t="shared" ref="AQ35:AQ60" si="10">IF(AND($U35&gt;$V35,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V35&gt;$U35,($V35-$U35)&gt;50,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&lt;=60),100,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&gt;60),$AP35,""))))</f>
+      <c r="AQ35" s="4">
+        <f t="shared" ref="AQ35:AQ60" si="9">IF(AND($V35&lt;60,($V35-$U35)&lt;=50),100,IF(AND($V35&lt;60,($V35-$U35)&gt;50),0,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&lt;=40),100,IF(AND($V35&gt;=60,$V35&lt;70,($V35-$U35)&gt;40),0,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&lt;=30),100,IF(AND($V35&gt;=70,$V35&lt;80,($V35-$U35)&gt;30),0,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&lt;=20),100,IF(AND($V35&gt;=80,$V35&lt;90,($V35-$U35)&gt;20),0,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&lt;=10),100,IF(AND($V35&gt;=90,$V35&lt;=100,($V35-$U35)&gt;10),0,""))))))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AR35" s="4" t="str">
+        <f t="shared" ref="AR35:AR60" si="10">IF(AND($U35&gt;$V35,$G35="CONTRATADO EN EJECUCIÓN"),100,IF(AND($V35&gt;$U35,($V35-$U35)&gt;50,$G35="CONTRATADO EN EJECUCIÓN"),0,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&lt;=60),100,IF(AND($V35&gt;$U35,($V35-$U35)&lt;=50,$V35&gt;60),$AQ35,""))))</f>
         <v/>
       </c>
-      <c r="AR35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS35" s="5"/>
-      <c r="AT35" s="4" t="str">
-        <f t="shared" ref="AT35:AT60" si="11">IF(ISNUMBER($AJ35),IF(DAY($AJ35)=10,100,IF(DAY($AJ35)=11,80,IF(DAY($AJ35)=12,50,0))),"")</f>
+      <c r="AS35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT35" s="5"/>
+      <c r="AU35" s="4" t="str">
+        <f t="shared" ref="AU35:AU60" si="11">IF(ISNUMBER($AK35),IF(DAY($AK35)=10,100,IF(DAY($AK35)=11,80,IF(DAY($AK35)=12,50,0))),"")</f>
         <v/>
       </c>
-      <c r="AU35" s="5"/>
-      <c r="AV35" s="4">
-        <f t="shared" ref="AV35:AV60" si="12">IF($AR35=0,100,IF($AR35=1,90,IF($AR35=2,75,IF($AR35=3,60,IF($AR35=4,50,IF($AR35=5,25,IF($AR35&gt;=6,0,"")))))))</f>
-        <v>100</v>
-      </c>
-      <c r="AW35" s="4" t="str">
-        <f t="shared" ref="AW35:AW60" si="13">IFERROR(IF($G35="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($AD35),ISNUMBER($AG35),$AD35&lt;$AG35),0,IF($AR35&gt;=1,(IFERROR(IF(ISTEXT($AH35),($AN35*0.4+$AO35*0.2+$AQ35*0.4),""),""))*$AV35/100,IFERROR(IF(ISTEXT($AH35),($AN35*0.4+$AO35*0.2+$AQ35*0.4),""),""))),IF($G35="CONTRATADO SIN ACTA DE INICIO",IF(AND($AG35-$AB35&gt;=0,$AG35-$AB35&lt;=30),100,0),"")),"Revisar")</f>
+      <c r="AV35" s="5"/>
+      <c r="AW35" s="4">
+        <f t="shared" ref="AW35:AW60" si="12">IF($AS35=0,100,IF($AS35=1,90,IF($AS35=2,75,IF($AS35=3,60,IF($AS35=4,50,IF($AS35=5,25,IF($AS35&gt;=6,0,"")))))))</f>
+        <v>100</v>
+      </c>
+      <c r="AX35" s="4" t="str">
+        <f t="shared" ref="AX35:AX60" si="13">IFERROR(IF($G35="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($AD35),ISNUMBER($AH35),$AD35&lt;$AH35),0,IF($AS35&gt;=1,(IFERROR(IF(ISTEXT($AI35),($AO35*0.4+$AP35*0.2+$AR35*0.4),""),""))*$AW35/100,IFERROR(IF(ISTEXT($AI35),($AO35*0.4+$AP35*0.2+$AR35*0.4),""),""))),IF($G35="CONTRATADO SIN ACTA DE INICIO",IF(AND($AH35-$AB35&gt;=0,$AH35-$AB35&lt;=30),100,0),"")),"Revisar")</f>
         <v/>
       </c>
-      <c r="AX35" s="4"/>
-      <c r="AY35" s="4" t="s">
+      <c r="AY35" s="4"/>
+      <c r="AZ35" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="AZ35" s="4" t="s">
+      <c r="BA35" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA35" s="4" t="s">
+      <c r="BB35" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>316</v>
       </c>
@@ -9137,68 +9214,69 @@
       </c>
       <c r="AE36" s="6"/>
       <c r="AF36" s="6"/>
-      <c r="AG36" s="6">
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6">
         <v>46157</v>
       </c>
-      <c r="AH36" s="4" t="s">
+      <c r="AI36" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="AI36" s="4" t="s">
+      <c r="AJ36" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="AJ36" s="6">
+      <c r="AK36" s="6">
         <v>46152</v>
       </c>
-      <c r="AK36" s="4"/>
       <c r="AL36" s="4"/>
       <c r="AM36" s="4"/>
-      <c r="AN36" s="4">
+      <c r="AN36" s="4"/>
+      <c r="AO36" s="4">
         <f t="shared" si="7"/>
         <v>71.739130434782609</v>
       </c>
-      <c r="AO36" s="4">
+      <c r="AP36" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP36" s="4">
+      <c r="AQ36" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ36" s="4">
+      <c r="AR36" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR36" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS36" s="5"/>
-      <c r="AT36" s="4">
+      <c r="AS36" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT36" s="5"/>
+      <c r="AU36" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU36" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV36" s="4">
+      <c r="AV36" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW36" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW36" s="4">
+      <c r="AX36" s="4">
         <f t="shared" si="13"/>
         <v>88.695652173913047</v>
       </c>
-      <c r="AX36" s="4"/>
-      <c r="AY36" s="4" t="s">
+      <c r="AY36" s="4"/>
+      <c r="AZ36" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="AZ36" s="4" t="s">
+      <c r="BA36" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA36" s="4" t="s">
+      <c r="BB36" s="4" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>324</v>
       </c>
@@ -9285,72 +9363,73 @@
       <c r="AD37" s="6">
         <v>45900</v>
       </c>
-      <c r="AE37" s="6">
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="6">
         <v>45968</v>
       </c>
-      <c r="AF37" s="6"/>
-      <c r="AG37" s="6">
+      <c r="AG37" s="6"/>
+      <c r="AH37" s="6">
         <v>46157</v>
       </c>
-      <c r="AH37" s="4" t="s">
+      <c r="AI37" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="AI37" s="4" t="s">
+      <c r="AJ37" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="AJ37" s="6">
+      <c r="AK37" s="6">
         <v>46155</v>
       </c>
-      <c r="AK37" s="4"/>
       <c r="AL37" s="4"/>
       <c r="AM37" s="4"/>
-      <c r="AN37" s="4" t="str">
+      <c r="AN37" s="4"/>
+      <c r="AO37" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO37" s="4" t="str">
+      <c r="AP37" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP37" s="4">
+      <c r="AQ37" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ37" s="4">
+      <c r="AR37" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR37" s="4">
+      <c r="AS37" s="4">
         <v>1</v>
       </c>
-      <c r="AS37" s="5"/>
-      <c r="AT37" s="4">
+      <c r="AT37" s="5"/>
+      <c r="AU37" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU37" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV37" s="4">
+      <c r="AV37" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW37" s="4">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AW37" s="4" t="str">
+      <c r="AX37" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX37" s="4"/>
-      <c r="AY37" s="4" t="s">
+      <c r="AY37" s="4"/>
+      <c r="AZ37" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="AZ37" s="4" t="s">
+      <c r="BA37" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA37" s="4" t="s">
+      <c r="BB37" s="4" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>332</v>
       </c>
@@ -9443,68 +9522,69 @@
       </c>
       <c r="AE38" s="6"/>
       <c r="AF38" s="6"/>
-      <c r="AG38" s="6">
+      <c r="AG38" s="6"/>
+      <c r="AH38" s="6">
         <v>46157</v>
       </c>
-      <c r="AH38" s="4" t="s">
+      <c r="AI38" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="AI38" s="4" t="s">
+      <c r="AJ38" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="AJ38" s="6">
+      <c r="AK38" s="6">
         <v>46152</v>
       </c>
-      <c r="AK38" s="4"/>
       <c r="AL38" s="4"/>
       <c r="AM38" s="4"/>
-      <c r="AN38" s="4">
+      <c r="AN38" s="4"/>
+      <c r="AO38" s="4">
         <f t="shared" si="7"/>
         <v>69.565217391304344</v>
       </c>
-      <c r="AO38" s="4">
+      <c r="AP38" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP38" s="4">
+      <c r="AQ38" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ38" s="4">
+      <c r="AR38" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR38" s="4">
+      <c r="AS38" s="4">
         <v>1</v>
       </c>
-      <c r="AS38" s="5"/>
-      <c r="AT38" s="4">
+      <c r="AT38" s="5"/>
+      <c r="AU38" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU38" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV38" s="4">
+      <c r="AV38" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW38" s="4">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AW38" s="4">
+      <c r="AX38" s="4">
         <f t="shared" si="13"/>
         <v>79.043478260869563</v>
       </c>
-      <c r="AX38" s="4"/>
-      <c r="AY38" s="4" t="s">
+      <c r="AY38" s="4"/>
+      <c r="AZ38" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="AZ38" s="4" t="s">
+      <c r="BA38" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA38" s="4" t="s">
+      <c r="BB38" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>339</v>
       </c>
@@ -9591,72 +9671,73 @@
       <c r="AD39" s="6">
         <v>45656</v>
       </c>
-      <c r="AE39" s="6">
+      <c r="AE39" s="6"/>
+      <c r="AF39" s="6">
         <v>45656</v>
       </c>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6">
+      <c r="AG39" s="6"/>
+      <c r="AH39" s="6">
         <v>46157</v>
       </c>
-      <c r="AH39" s="4" t="s">
+      <c r="AI39" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="AI39" s="4" t="s">
+      <c r="AJ39" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AJ39" s="6">
+      <c r="AK39" s="6">
         <v>46157</v>
       </c>
-      <c r="AK39" s="4"/>
       <c r="AL39" s="4"/>
       <c r="AM39" s="4"/>
-      <c r="AN39" s="4" t="str">
+      <c r="AN39" s="4"/>
+      <c r="AO39" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO39" s="4" t="str">
+      <c r="AP39" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP39" s="4">
+      <c r="AQ39" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ39" s="4" t="str">
+      <c r="AR39" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR39" s="4">
+      <c r="AS39" s="4">
         <v>1</v>
       </c>
-      <c r="AS39" s="5"/>
-      <c r="AT39" s="4">
+      <c r="AT39" s="5"/>
+      <c r="AU39" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU39" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV39" s="4">
+      <c r="AV39" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW39" s="4">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AW39" s="4" t="str">
+      <c r="AX39" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX39" s="4"/>
-      <c r="AY39" s="4" t="s">
+      <c r="AY39" s="4"/>
+      <c r="AZ39" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="AZ39" s="4" t="s">
+      <c r="BA39" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA39" s="4" t="s">
+      <c r="BB39" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>346</v>
       </c>
@@ -9749,68 +9830,69 @@
       </c>
       <c r="AE40" s="6"/>
       <c r="AF40" s="6"/>
-      <c r="AG40" s="6">
+      <c r="AG40" s="6"/>
+      <c r="AH40" s="6">
         <v>46157</v>
       </c>
-      <c r="AH40" s="4" t="s">
+      <c r="AI40" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="AI40" s="4" t="s">
+      <c r="AJ40" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="AJ40" s="6">
+      <c r="AK40" s="6">
         <v>46152</v>
       </c>
-      <c r="AK40" s="4"/>
       <c r="AL40" s="4"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="4">
+      <c r="AN40" s="4"/>
+      <c r="AO40" s="4">
         <f t="shared" si="7"/>
         <v>67.391304347826079</v>
       </c>
-      <c r="AO40" s="4">
+      <c r="AP40" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP40" s="4">
+      <c r="AQ40" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ40" s="4">
+      <c r="AR40" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR40" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS40" s="5"/>
-      <c r="AT40" s="4">
+      <c r="AS40" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT40" s="5"/>
+      <c r="AU40" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU40" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV40" s="4">
+      <c r="AV40" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW40" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW40" s="4">
+      <c r="AX40" s="4">
         <f t="shared" si="13"/>
         <v>86.956521739130437</v>
       </c>
-      <c r="AX40" s="4"/>
-      <c r="AY40" s="4" t="s">
+      <c r="AY40" s="4"/>
+      <c r="AZ40" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="AZ40" s="4" t="s">
+      <c r="BA40" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA40" s="4" t="s">
+      <c r="BB40" s="4" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>354</v>
       </c>
@@ -9903,68 +9985,69 @@
       </c>
       <c r="AE41" s="6"/>
       <c r="AF41" s="6"/>
-      <c r="AG41" s="6">
+      <c r="AG41" s="6"/>
+      <c r="AH41" s="6">
         <v>46157</v>
       </c>
-      <c r="AH41" s="4" t="s">
+      <c r="AI41" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="AI41" s="4" t="s">
+      <c r="AJ41" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="AJ41" s="6">
+      <c r="AK41" s="6">
         <v>46152</v>
       </c>
-      <c r="AK41" s="4"/>
       <c r="AL41" s="4"/>
       <c r="AM41" s="4"/>
-      <c r="AN41" s="4">
+      <c r="AN41" s="4"/>
+      <c r="AO41" s="4">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AO41" s="4">
+      <c r="AP41" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP41" s="4">
+      <c r="AQ41" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ41" s="4">
+      <c r="AR41" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR41" s="4">
+      <c r="AS41" s="4">
         <v>2</v>
       </c>
-      <c r="AS41" s="5"/>
-      <c r="AT41" s="4">
+      <c r="AT41" s="5"/>
+      <c r="AU41" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU41" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV41" s="4">
+      <c r="AV41" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW41" s="4">
         <f t="shared" si="12"/>
         <v>75</v>
       </c>
-      <c r="AW41" s="4">
+      <c r="AX41" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX41" s="4"/>
-      <c r="AY41" s="4" t="s">
+      <c r="AY41" s="4"/>
+      <c r="AZ41" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="AZ41" s="4" t="s">
+      <c r="BA41" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA41" s="4" t="s">
+      <c r="BB41" s="4" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
         <v>362</v>
       </c>
@@ -10055,68 +10138,69 @@
       </c>
       <c r="AE42" s="6"/>
       <c r="AF42" s="6"/>
-      <c r="AG42" s="6">
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6">
         <v>46157</v>
       </c>
-      <c r="AH42" s="4" t="s">
+      <c r="AI42" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="AI42" s="4" t="s">
+      <c r="AJ42" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="AJ42" s="6">
+      <c r="AK42" s="6">
         <v>46152</v>
       </c>
-      <c r="AK42" s="4"/>
       <c r="AL42" s="4"/>
       <c r="AM42" s="4"/>
-      <c r="AN42" s="4">
+      <c r="AN42" s="4"/>
+      <c r="AO42" s="4">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AO42" s="4">
+      <c r="AP42" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP42" s="4">
+      <c r="AQ42" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ42" s="4">
+      <c r="AR42" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS42" s="5"/>
-      <c r="AT42" s="4">
+      <c r="AS42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU42" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV42" s="4">
+      <c r="AV42" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW42" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW42" s="4">
+      <c r="AX42" s="4">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AX42" s="4"/>
-      <c r="AY42" s="4" t="s">
+      <c r="AY42" s="4"/>
+      <c r="AZ42" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="AZ42" s="4" t="s">
+      <c r="BA42" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA42" s="4" t="s">
+      <c r="BB42" s="4" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>369</v>
       </c>
@@ -10191,72 +10275,73 @@
       <c r="AD43" s="6"/>
       <c r="AE43" s="6"/>
       <c r="AF43" s="6"/>
-      <c r="AG43" s="6">
+      <c r="AG43" s="6"/>
+      <c r="AH43" s="6">
         <v>46157</v>
       </c>
-      <c r="AH43" s="4" t="s">
+      <c r="AI43" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="AI43" s="4" t="s">
+      <c r="AJ43" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="AJ43" s="6">
+      <c r="AK43" s="6">
         <v>46152</v>
       </c>
-      <c r="AK43" s="4">
+      <c r="AL43" s="4">
         <v>542</v>
       </c>
-      <c r="AL43" s="4"/>
       <c r="AM43" s="4"/>
-      <c r="AN43" s="4" t="str">
+      <c r="AN43" s="4"/>
+      <c r="AO43" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO43" s="4" t="str">
+      <c r="AP43" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP43" s="4">
+      <c r="AQ43" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ43" s="4" t="str">
+      <c r="AR43" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS43" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT43" s="4">
+      <c r="AS43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT43" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU43" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV43" s="4">
+      <c r="AV43" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW43" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW43" s="4" t="str">
+      <c r="AX43" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX43" s="4"/>
-      <c r="AY43" s="4" t="s">
+      <c r="AY43" s="4"/>
+      <c r="AZ43" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="AZ43" s="4" t="s">
+      <c r="BA43" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA43" s="4" t="s">
+      <c r="BB43" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>377</v>
       </c>
@@ -10349,68 +10434,69 @@
       </c>
       <c r="AE44" s="6"/>
       <c r="AF44" s="6"/>
-      <c r="AG44" s="6">
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="6">
         <v>46157</v>
       </c>
-      <c r="AH44" s="4" t="s">
+      <c r="AI44" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="AI44" s="4" t="s">
+      <c r="AJ44" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="AJ44" s="6">
+      <c r="AK44" s="6">
         <v>46152</v>
       </c>
-      <c r="AK44" s="4"/>
       <c r="AL44" s="4"/>
       <c r="AM44" s="4"/>
-      <c r="AN44" s="4">
+      <c r="AN44" s="4"/>
+      <c r="AO44" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AO44" s="4">
+      <c r="AP44" s="4">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AP44" s="4">
+      <c r="AQ44" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ44" s="4">
+      <c r="AR44" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR44" s="4">
+      <c r="AS44" s="4">
         <v>1</v>
       </c>
-      <c r="AS44" s="5"/>
-      <c r="AT44" s="4">
+      <c r="AT44" s="5"/>
+      <c r="AU44" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU44" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV44" s="4">
+      <c r="AV44" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW44" s="4">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AW44" s="4">
+      <c r="AX44" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX44" s="4"/>
-      <c r="AY44" s="4" t="s">
+      <c r="AY44" s="4"/>
+      <c r="AZ44" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="AZ44" s="4" t="s">
+      <c r="BA44" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA44" s="4" t="s">
+      <c r="BB44" s="4" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>385</v>
       </c>
@@ -10501,68 +10587,69 @@
       </c>
       <c r="AE45" s="6"/>
       <c r="AF45" s="6"/>
-      <c r="AG45" s="6">
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6">
         <v>46157</v>
       </c>
-      <c r="AH45" s="4" t="s">
+      <c r="AI45" s="4" t="s">
         <v>392</v>
       </c>
-      <c r="AI45" s="4" t="s">
+      <c r="AJ45" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="AJ45" s="6">
+      <c r="AK45" s="6">
         <v>46152</v>
       </c>
-      <c r="AK45" s="4"/>
       <c r="AL45" s="4"/>
       <c r="AM45" s="4"/>
-      <c r="AN45" s="4">
+      <c r="AN45" s="4"/>
+      <c r="AO45" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AO45" s="4">
+      <c r="AP45" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP45" s="4">
+      <c r="AQ45" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ45" s="4">
+      <c r="AR45" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS45" s="5"/>
-      <c r="AT45" s="4">
+      <c r="AS45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="5"/>
+      <c r="AU45" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU45" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV45" s="4">
+      <c r="AV45" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW45" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW45" s="4">
+      <c r="AX45" s="4">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="AX45" s="4"/>
-      <c r="AY45" s="4" t="s">
+      <c r="AY45" s="4"/>
+      <c r="AZ45" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="AZ45" s="4" t="s">
+      <c r="BA45" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA45" s="4" t="s">
+      <c r="BB45" s="4" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>396</v>
       </c>
@@ -10647,70 +10734,71 @@
       <c r="AD46" s="6"/>
       <c r="AE46" s="6"/>
       <c r="AF46" s="6"/>
-      <c r="AG46" s="6">
+      <c r="AG46" s="6"/>
+      <c r="AH46" s="6">
         <v>46157</v>
       </c>
-      <c r="AH46" s="4" t="s">
+      <c r="AI46" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="AI46" s="4" t="s">
+      <c r="AJ46" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="AJ46" s="6">
+      <c r="AK46" s="6">
         <v>46152</v>
       </c>
-      <c r="AK46" s="4"/>
       <c r="AL46" s="4"/>
-      <c r="AM46" s="4">
+      <c r="AM46" s="4"/>
+      <c r="AN46" s="4">
         <v>330</v>
       </c>
-      <c r="AN46" s="4" t="str">
+      <c r="AO46" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO46" s="4" t="str">
+      <c r="AP46" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP46" s="4">
+      <c r="AQ46" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ46" s="4" t="str">
+      <c r="AR46" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR46" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS46" s="5"/>
-      <c r="AT46" s="4">
+      <c r="AS46" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="5"/>
+      <c r="AU46" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU46" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV46" s="4">
+      <c r="AV46" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW46" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW46" s="4">
+      <c r="AX46" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX46" s="4"/>
-      <c r="AY46" s="4" t="s">
+      <c r="AY46" s="4"/>
+      <c r="AZ46" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="AZ46" s="4" t="s">
+      <c r="BA46" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA46" s="4" t="s">
+      <c r="BB46" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>406</v>
       </c>
@@ -10803,68 +10891,69 @@
       </c>
       <c r="AE47" s="6"/>
       <c r="AF47" s="6"/>
-      <c r="AG47" s="6">
+      <c r="AG47" s="6"/>
+      <c r="AH47" s="6">
         <v>46157</v>
       </c>
-      <c r="AH47" s="4" t="s">
+      <c r="AI47" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="AI47" s="4" t="s">
+      <c r="AJ47" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="AJ47" s="6">
+      <c r="AK47" s="6">
         <v>46152</v>
       </c>
-      <c r="AK47" s="4"/>
       <c r="AL47" s="4"/>
       <c r="AM47" s="4"/>
-      <c r="AN47" s="4">
+      <c r="AN47" s="4"/>
+      <c r="AO47" s="4">
         <f t="shared" si="7"/>
         <v>95.65217391304347</v>
       </c>
-      <c r="AO47" s="4">
+      <c r="AP47" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP47" s="4">
+      <c r="AQ47" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ47" s="4">
+      <c r="AR47" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR47" s="4">
+      <c r="AS47" s="4">
         <v>1</v>
       </c>
-      <c r="AS47" s="5"/>
-      <c r="AT47" s="4">
+      <c r="AT47" s="5"/>
+      <c r="AU47" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU47" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV47" s="4">
+      <c r="AV47" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW47" s="4">
         <f t="shared" si="12"/>
         <v>90</v>
       </c>
-      <c r="AW47" s="4">
+      <c r="AX47" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX47" s="4"/>
-      <c r="AY47" s="4" t="s">
+      <c r="AY47" s="4"/>
+      <c r="AZ47" s="4" t="s">
         <v>412</v>
       </c>
-      <c r="AZ47" s="4" t="s">
+      <c r="BA47" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="BA47" s="4" t="s">
+      <c r="BB47" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>413</v>
       </c>
@@ -10937,62 +11026,63 @@
       <c r="AD48" s="6"/>
       <c r="AE48" s="6"/>
       <c r="AF48" s="6"/>
-      <c r="AG48" s="6">
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6">
         <v>46157</v>
       </c>
-      <c r="AH48" s="4"/>
       <c r="AI48" s="4"/>
-      <c r="AJ48" s="6"/>
-      <c r="AK48" s="4">
+      <c r="AJ48" s="4"/>
+      <c r="AK48" s="6"/>
+      <c r="AL48" s="4">
         <v>36</v>
       </c>
-      <c r="AL48" s="4"/>
       <c r="AM48" s="4"/>
-      <c r="AN48" s="4" t="str">
+      <c r="AN48" s="4"/>
+      <c r="AO48" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO48" s="4" t="str">
+      <c r="AP48" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP48" s="4">
+      <c r="AQ48" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ48" s="4" t="str">
+      <c r="AR48" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT48" s="4" t="str">
+      <c r="AS48" s="4"/>
+      <c r="AT48" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU48" s="4" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AU48" s="5"/>
-      <c r="AV48" s="4">
+      <c r="AV48" s="5"/>
+      <c r="AW48" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW48" s="4" t="str">
+      <c r="AX48" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4" t="s">
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="AZ48" s="4" t="s">
+      <c r="BA48" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="BA48" s="4" t="s">
+      <c r="BB48" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>418</v>
       </c>
@@ -11063,70 +11153,71 @@
       <c r="AD49" s="6"/>
       <c r="AE49" s="6"/>
       <c r="AF49" s="6"/>
-      <c r="AG49" s="6">
+      <c r="AG49" s="6"/>
+      <c r="AH49" s="6">
         <v>46157</v>
       </c>
-      <c r="AH49" s="4" t="s">
+      <c r="AI49" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="AI49" s="4" t="s">
+      <c r="AJ49" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="AJ49" s="6">
+      <c r="AK49" s="6">
         <v>46152</v>
       </c>
-      <c r="AK49" s="4">
+      <c r="AL49" s="4">
         <v>64</v>
       </c>
-      <c r="AL49" s="4"/>
       <c r="AM49" s="4"/>
-      <c r="AN49" s="4" t="str">
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO49" s="4" t="str">
+      <c r="AP49" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP49" s="4">
+      <c r="AQ49" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ49" s="4" t="str">
+      <c r="AR49" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT49" s="4">
+      <c r="AS49" s="4"/>
+      <c r="AT49" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU49" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU49" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV49" s="4">
+      <c r="AV49" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW49" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW49" s="4" t="str">
+      <c r="AX49" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4" t="s">
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="AZ49" s="4" t="s">
+      <c r="BA49" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA49" s="4" t="s">
+      <c r="BB49" s="4" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>426</v>
       </c>
@@ -11213,72 +11304,73 @@
       <c r="AD50" s="6">
         <v>46021</v>
       </c>
-      <c r="AE50" s="6">
+      <c r="AE50" s="6"/>
+      <c r="AF50" s="6">
         <v>46021</v>
       </c>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6">
+      <c r="AG50" s="6"/>
+      <c r="AH50" s="6">
         <v>46157</v>
       </c>
-      <c r="AH50" s="4" t="s">
+      <c r="AI50" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="AI50" s="4" t="s">
+      <c r="AJ50" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AJ50" s="6">
+      <c r="AK50" s="6">
         <v>46157</v>
       </c>
-      <c r="AK50" s="4"/>
       <c r="AL50" s="4"/>
       <c r="AM50" s="4"/>
-      <c r="AN50" s="4" t="str">
+      <c r="AN50" s="4"/>
+      <c r="AO50" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO50" s="4" t="str">
+      <c r="AP50" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP50" s="4">
+      <c r="AQ50" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ50" s="4">
+      <c r="AR50" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR50" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS50" s="5"/>
-      <c r="AT50" s="4">
+      <c r="AS50" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT50" s="5"/>
+      <c r="AU50" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AU50" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV50" s="4">
+      <c r="AV50" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW50" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW50" s="4" t="str">
+      <c r="AX50" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4" t="s">
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="AZ50" s="4" t="s">
+      <c r="BA50" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA50" s="4" t="s">
+      <c r="BB50" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
         <v>433</v>
       </c>
@@ -11369,68 +11461,69 @@
       </c>
       <c r="AE51" s="6"/>
       <c r="AF51" s="6"/>
-      <c r="AG51" s="6">
+      <c r="AG51" s="6"/>
+      <c r="AH51" s="6">
         <v>46157</v>
       </c>
-      <c r="AH51" s="4" t="s">
+      <c r="AI51" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="AI51" s="4" t="s">
+      <c r="AJ51" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="AJ51" s="6">
+      <c r="AK51" s="6">
         <v>46152</v>
       </c>
-      <c r="AK51" s="4"/>
       <c r="AL51" s="4"/>
       <c r="AM51" s="4"/>
-      <c r="AN51" s="4">
+      <c r="AN51" s="4"/>
+      <c r="AO51" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AO51" s="4">
+      <c r="AP51" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP51" s="4">
+      <c r="AQ51" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ51" s="4">
+      <c r="AR51" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR51" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS51" s="5"/>
-      <c r="AT51" s="4">
+      <c r="AS51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="5"/>
+      <c r="AU51" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU51" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV51" s="4">
+      <c r="AV51" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW51" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW51" s="4">
+      <c r="AX51" s="4">
         <f t="shared" si="13"/>
         <v>60</v>
       </c>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4" t="s">
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="AZ51" s="4" t="s">
+      <c r="BA51" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA51" s="4" t="s">
+      <c r="BB51" s="4" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>442</v>
       </c>
@@ -11523,68 +11616,69 @@
       </c>
       <c r="AE52" s="6"/>
       <c r="AF52" s="6"/>
-      <c r="AG52" s="6">
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6">
         <v>46157</v>
       </c>
-      <c r="AH52" s="4" t="s">
+      <c r="AI52" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="AI52" s="4" t="s">
+      <c r="AJ52" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="AJ52" s="6">
+      <c r="AK52" s="6">
         <v>46152</v>
       </c>
-      <c r="AK52" s="4"/>
       <c r="AL52" s="4"/>
       <c r="AM52" s="4"/>
-      <c r="AN52" s="4">
+      <c r="AN52" s="4"/>
+      <c r="AO52" s="4">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AO52" s="4">
+      <c r="AP52" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP52" s="4">
+      <c r="AQ52" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ52" s="4">
+      <c r="AR52" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR52" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS52" s="5"/>
-      <c r="AT52" s="4">
+      <c r="AS52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="5"/>
+      <c r="AU52" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU52" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV52" s="4">
+      <c r="AV52" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW52" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW52" s="4">
+      <c r="AX52" s="4">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4" t="s">
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="AZ52" s="4" t="s">
+      <c r="BA52" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA52" s="4" t="s">
+      <c r="BB52" s="4" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>446</v>
       </c>
@@ -11667,70 +11761,71 @@
       <c r="AD53" s="6"/>
       <c r="AE53" s="6"/>
       <c r="AF53" s="6"/>
-      <c r="AG53" s="6">
+      <c r="AG53" s="6"/>
+      <c r="AH53" s="6">
         <v>46163</v>
       </c>
-      <c r="AH53" s="4" t="s">
+      <c r="AI53" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="AI53" s="4" t="s">
+      <c r="AJ53" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="AJ53" s="6">
+      <c r="AK53" s="6">
         <v>46152</v>
       </c>
-      <c r="AK53" s="4"/>
       <c r="AL53" s="4"/>
-      <c r="AM53" s="4">
-        <v>0</v>
-      </c>
-      <c r="AN53" s="4" t="str">
+      <c r="AM53" s="4"/>
+      <c r="AN53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO53" s="4" t="str">
+      <c r="AP53" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP53" s="4">
+      <c r="AQ53" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ53" s="4" t="str">
+      <c r="AR53" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR53" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS53" s="5"/>
-      <c r="AT53" s="4">
+      <c r="AS53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="5"/>
+      <c r="AU53" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU53" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV53" s="4">
+      <c r="AV53" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW53" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW53" s="4">
+      <c r="AX53" s="4">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4" t="s">
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="AZ53" s="4" t="s">
+      <c r="BA53" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA53" s="4" t="s">
+      <c r="BB53" s="4" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>453</v>
       </c>
@@ -11801,72 +11896,73 @@
       <c r="AD54" s="6"/>
       <c r="AE54" s="6"/>
       <c r="AF54" s="6"/>
-      <c r="AG54" s="6">
+      <c r="AG54" s="6"/>
+      <c r="AH54" s="6">
         <v>46157</v>
       </c>
-      <c r="AH54" s="4" t="s">
+      <c r="AI54" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="AI54" s="4" t="s">
+      <c r="AJ54" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="AJ54" s="6">
+      <c r="AK54" s="6">
         <v>46152</v>
       </c>
-      <c r="AK54" s="4">
+      <c r="AL54" s="4">
         <v>77</v>
       </c>
-      <c r="AL54" s="4"/>
       <c r="AM54" s="4"/>
-      <c r="AN54" s="4" t="str">
+      <c r="AN54" s="4"/>
+      <c r="AO54" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO54" s="4" t="str">
+      <c r="AP54" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP54" s="4">
+      <c r="AQ54" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ54" s="4" t="str">
+      <c r="AR54" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR54" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS54" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT54" s="4">
+      <c r="AS54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT54" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU54" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU54" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV54" s="4">
+      <c r="AV54" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW54" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW54" s="4" t="str">
+      <c r="AX54" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4" t="s">
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="AZ54" s="4" t="s">
+      <c r="BA54" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA54" s="4" t="s">
+      <c r="BB54" s="4" t="s">
         <v>460</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>461</v>
       </c>
@@ -11957,68 +12053,69 @@
       </c>
       <c r="AE55" s="6"/>
       <c r="AF55" s="6"/>
-      <c r="AG55" s="6">
+      <c r="AG55" s="6"/>
+      <c r="AH55" s="6">
         <v>46157</v>
       </c>
-      <c r="AH55" s="4" t="s">
+      <c r="AI55" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="AI55" s="4" t="s">
+      <c r="AJ55" s="4" t="s">
         <v>466</v>
       </c>
-      <c r="AJ55" s="6">
+      <c r="AK55" s="6">
         <v>46152</v>
       </c>
-      <c r="AK55" s="4"/>
       <c r="AL55" s="4"/>
       <c r="AM55" s="4"/>
-      <c r="AN55" s="4">
+      <c r="AN55" s="4"/>
+      <c r="AO55" s="4">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="AO55" s="4">
+      <c r="AP55" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AP55" s="4">
+      <c r="AQ55" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ55" s="4">
+      <c r="AR55" s="4">
         <f t="shared" si="10"/>
         <v>100</v>
       </c>
-      <c r="AR55" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS55" s="5"/>
-      <c r="AT55" s="4">
+      <c r="AS55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT55" s="5"/>
+      <c r="AU55" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU55" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV55" s="4">
+      <c r="AV55" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW55" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW55" s="4">
+      <c r="AX55" s="4">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="AX55" s="4"/>
-      <c r="AY55" s="4" t="s">
+      <c r="AY55" s="4"/>
+      <c r="AZ55" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="AZ55" s="4" t="s">
+      <c r="BA55" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA55" s="4" t="s">
+      <c r="BB55" s="4" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>469</v>
       </c>
@@ -12101,72 +12198,73 @@
       <c r="AD56" s="6"/>
       <c r="AE56" s="6"/>
       <c r="AF56" s="6"/>
-      <c r="AG56" s="6">
+      <c r="AG56" s="6"/>
+      <c r="AH56" s="6">
         <v>46157</v>
       </c>
-      <c r="AH56" s="4" t="s">
+      <c r="AI56" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="AI56" s="4" t="s">
+      <c r="AJ56" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="AJ56" s="6">
+      <c r="AK56" s="6">
         <v>46152</v>
       </c>
-      <c r="AK56" s="4"/>
       <c r="AL56" s="4"/>
-      <c r="AM56" s="4">
-        <v>100</v>
-      </c>
-      <c r="AN56" s="4" t="str">
+      <c r="AM56" s="4"/>
+      <c r="AN56" s="4">
+        <v>100</v>
+      </c>
+      <c r="AO56" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO56" s="4" t="str">
+      <c r="AP56" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP56" s="4">
+      <c r="AQ56" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ56" s="4" t="str">
+      <c r="AR56" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR56" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT56" s="4">
+      <c r="AS56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU56" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV56" s="4">
+      <c r="AV56" s="5">
+        <v>0</v>
+      </c>
+      <c r="AW56" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW56" s="4">
+      <c r="AX56" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AX56" s="4"/>
-      <c r="AY56" s="4" t="s">
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="AZ56" s="4" t="s">
+      <c r="BA56" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA56" s="4" t="s">
+      <c r="BB56" s="4" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>478</v>
       </c>
@@ -12241,72 +12339,73 @@
       <c r="AD57" s="6"/>
       <c r="AE57" s="6"/>
       <c r="AF57" s="6"/>
-      <c r="AG57" s="6">
+      <c r="AG57" s="6"/>
+      <c r="AH57" s="6">
         <v>46157</v>
       </c>
-      <c r="AH57" s="4" t="s">
+      <c r="AI57" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="AI57" s="4" t="s">
+      <c r="AJ57" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="AJ57" s="6">
+      <c r="AK57" s="6">
         <v>46152</v>
       </c>
-      <c r="AK57" s="4">
+      <c r="AL57" s="4">
         <v>177</v>
       </c>
-      <c r="AL57" s="4"/>
       <c r="AM57" s="4"/>
-      <c r="AN57" s="4" t="str">
+      <c r="AN57" s="4"/>
+      <c r="AO57" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO57" s="4" t="str">
+      <c r="AP57" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP57" s="4">
+      <c r="AQ57" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ57" s="4" t="str">
+      <c r="AR57" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR57" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS57" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT57" s="4">
+      <c r="AS57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU57" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU57" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV57" s="4">
+      <c r="AV57" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW57" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW57" s="4" t="str">
+      <c r="AX57" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX57" s="4"/>
-      <c r="AY57" s="4" t="s">
+      <c r="AY57" s="4"/>
+      <c r="AZ57" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="AZ57" s="4" t="s">
+      <c r="BA57" s="4" t="s">
         <v>440</v>
       </c>
-      <c r="BA57" s="4" t="s">
+      <c r="BB57" s="4" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>487</v>
       </c>
@@ -12377,72 +12476,73 @@
       <c r="AD58" s="6"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="6"/>
-      <c r="AG58" s="6">
+      <c r="AG58" s="6"/>
+      <c r="AH58" s="6">
         <v>46157</v>
       </c>
-      <c r="AH58" s="4" t="s">
+      <c r="AI58" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="AI58" s="4" t="s">
+      <c r="AJ58" s="4" t="s">
         <v>491</v>
       </c>
-      <c r="AJ58" s="6">
+      <c r="AK58" s="6">
         <v>46152</v>
       </c>
-      <c r="AK58" s="4">
+      <c r="AL58" s="4">
         <v>147</v>
       </c>
-      <c r="AL58" s="4"/>
       <c r="AM58" s="4"/>
-      <c r="AN58" s="4" t="str">
+      <c r="AN58" s="4"/>
+      <c r="AO58" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO58" s="4" t="str">
+      <c r="AP58" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP58" s="4">
+      <c r="AQ58" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ58" s="4" t="str">
+      <c r="AR58" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR58" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS58" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT58" s="4">
+      <c r="AS58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT58" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU58" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU58" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV58" s="4">
+      <c r="AV58" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW58" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW58" s="4" t="str">
+      <c r="AX58" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX58" s="4"/>
-      <c r="AY58" s="4" t="s">
+      <c r="AY58" s="4"/>
+      <c r="AZ58" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="AZ58" s="4" t="s">
+      <c r="BA58" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA58" s="4" t="s">
+      <c r="BB58" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>493</v>
       </c>
@@ -12511,72 +12611,73 @@
       <c r="AD59" s="6"/>
       <c r="AE59" s="6"/>
       <c r="AF59" s="6"/>
-      <c r="AG59" s="6">
+      <c r="AG59" s="6"/>
+      <c r="AH59" s="6">
         <v>46157</v>
       </c>
-      <c r="AH59" s="4" t="s">
+      <c r="AI59" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="AI59" s="4" t="s">
+      <c r="AJ59" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="AJ59" s="6">
+      <c r="AK59" s="6">
         <v>46152</v>
       </c>
-      <c r="AK59" s="4">
+      <c r="AL59" s="4">
         <v>77</v>
       </c>
-      <c r="AL59" s="4"/>
       <c r="AM59" s="4"/>
-      <c r="AN59" s="4" t="str">
+      <c r="AN59" s="4"/>
+      <c r="AO59" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO59" s="4" t="str">
+      <c r="AP59" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP59" s="4">
+      <c r="AQ59" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ59" s="4" t="str">
+      <c r="AR59" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR59" s="4">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="5">
-        <v>100</v>
-      </c>
-      <c r="AT59" s="4">
+      <c r="AS59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT59" s="5">
+        <v>100</v>
+      </c>
+      <c r="AU59" s="4">
         <f t="shared" si="11"/>
         <v>100</v>
       </c>
-      <c r="AU59" s="5">
-        <v>100</v>
-      </c>
-      <c r="AV59" s="4">
+      <c r="AV59" s="5">
+        <v>100</v>
+      </c>
+      <c r="AW59" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW59" s="4" t="str">
+      <c r="AX59" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX59" s="4"/>
-      <c r="AY59" s="4" t="s">
+      <c r="AY59" s="4"/>
+      <c r="AZ59" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="AZ59" s="4" t="s">
+      <c r="BA59" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="BA59" s="4" t="s">
+      <c r="BB59" s="4" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:54" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>501</v>
       </c>
@@ -12649,64 +12750,65 @@
       <c r="AD60" s="6"/>
       <c r="AE60" s="6"/>
       <c r="AF60" s="6"/>
-      <c r="AG60" s="6">
+      <c r="AG60" s="6"/>
+      <c r="AH60" s="6">
         <v>46188</v>
       </c>
-      <c r="AH60" s="4"/>
       <c r="AI60" s="4"/>
-      <c r="AJ60" s="6"/>
-      <c r="AK60" s="4">
+      <c r="AJ60" s="4"/>
+      <c r="AK60" s="6"/>
+      <c r="AL60" s="4">
         <v>19</v>
       </c>
-      <c r="AL60" s="4"/>
       <c r="AM60" s="4"/>
-      <c r="AN60" s="4" t="str">
+      <c r="AN60" s="4"/>
+      <c r="AO60" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AO60" s="4" t="str">
+      <c r="AP60" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
-      <c r="AP60" s="4">
+      <c r="AQ60" s="4">
         <f t="shared" si="9"/>
         <v>100</v>
       </c>
-      <c r="AQ60" s="4" t="str">
+      <c r="AR60" s="4" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="AR60" s="4"/>
-      <c r="AS60" s="5"/>
-      <c r="AT60" s="4" t="str">
+      <c r="AS60" s="4"/>
+      <c r="AT60" s="5"/>
+      <c r="AU60" s="4" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AU60" s="5"/>
-      <c r="AV60" s="4">
+      <c r="AV60" s="5"/>
+      <c r="AW60" s="4">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="AW60" s="4" t="str">
+      <c r="AX60" s="4" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="AX60" s="4"/>
-      <c r="AY60" s="4" t="s">
+      <c r="AY60" s="4"/>
+      <c r="AZ60" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="AZ60" s="4" t="s">
+      <c r="BA60" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="BA60" s="4" t="s">
+      <c r="BB60" s="4" t="s">
         <v>285</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:T1"/>
-    <mergeCell ref="U1:AR1"/>
-    <mergeCell ref="AS1:BA1"/>
+    <mergeCell ref="U1:AS1"/>
+    <mergeCell ref="AT1:BB1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -20396,6 +20498,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -20539,7 +20647,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -20548,20 +20656,37 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FEB4F2-FA00-4CCF-8658-BE991A4AFC68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65E8F416-0DD0-4166-9ACF-D00744BB634B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B86AA879-F6E4-4512-AC7A-AB9CD1300842}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71FEB4F2-FA00-4CCF-8658-BE991A4AFC68}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65E8F416-0DD0-4166-9ACF-D00744BB634B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B86AA879-F6E4-4512-AC7A-AB9CD1300842}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="551" documentId="13_ncr:1_{3BFAFFED-789E-4342-9BAC-067C8672E2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE51D121-7D99-4A40-8811-E86776B33D12}"/>
+  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{3BFAFFED-789E-4342-9BAC-067C8672E2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E14EECF-CD20-4D0F-9F72-524C56A4073E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="1007">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="1008">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -3229,6 +3229,9 @@
   <si>
     <t xml:space="preserve">Proyecto en estado terminado. Se está a la espera de mesa técnica con DNP para definir unos pagos que no han migrado a la plataforma, además falta liquidar contratod e interventoría para proceder con su cierre. 
 </t>
+  </si>
+  <si>
+    <t>Proyecto en estado de ejecución, con contrato en ejecución , su programación se está ejecutando dentro de los rangos normales. Tiene horizonte hasta el 04 de junio sin embargo se está a la espera de una reprogramación</t>
   </si>
 </sst>
 </file>
@@ -3359,13 +3362,13 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3387,7 +3390,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:BA61" totalsRowShown="0">
-  <autoFilter ref="A2:BA61" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A2:BA61" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Construcción de Obras para la Mitigación del Riesgo de Inundación y Socavación en el barrio Altos del Rosario en el Municipio de Sincelejo   Sucre"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="53">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="ENTIDAD O SECRETARIA"/>
@@ -3825,7 +3834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BA60"/>
+  <dimension ref="A1:BA61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
@@ -3850,65 +3859,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="10" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
+      <c r="T1" s="10"/>
+      <c r="U1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="10"/>
-      <c r="AJ1" s="10"/>
-      <c r="AK1" s="10"/>
-      <c r="AL1" s="10"/>
-      <c r="AM1" s="10"/>
-      <c r="AN1" s="10"/>
-      <c r="AO1" s="10"/>
-      <c r="AP1" s="10"/>
-      <c r="AQ1" s="10"/>
-      <c r="AR1" s="10"/>
-      <c r="AS1" s="9" t="s">
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="11"/>
+      <c r="AJ1" s="11"/>
+      <c r="AK1" s="11"/>
+      <c r="AL1" s="11"/>
+      <c r="AM1" s="11"/>
+      <c r="AN1" s="11"/>
+      <c r="AO1" s="11"/>
+      <c r="AP1" s="11"/>
+      <c r="AQ1" s="11"/>
+      <c r="AR1" s="11"/>
+      <c r="AS1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="AT1" s="9"/>
-      <c r="AU1" s="9"/>
-      <c r="AV1" s="9"/>
-      <c r="AW1" s="9"/>
-      <c r="AX1" s="9"/>
-      <c r="AY1" s="9"/>
-      <c r="AZ1" s="9"/>
-      <c r="BA1" s="9"/>
+      <c r="AT1" s="10"/>
+      <c r="AU1" s="10"/>
+      <c r="AV1" s="10"/>
+      <c r="AW1" s="10"/>
+      <c r="AX1" s="10"/>
+      <c r="AY1" s="10"/>
+      <c r="AZ1" s="10"/>
+      <c r="BA1" s="10"/>
     </row>
     <row r="2" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -4071,7 +4080,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:53" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" ht="92.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>56</v>
       </c>
@@ -4215,7 +4224,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>69</v>
       </c>
@@ -4357,7 +4366,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:53" ht="179.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" ht="179.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>79</v>
       </c>
@@ -4511,7 +4520,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:53" ht="156" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" ht="156" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>85</v>
       </c>
@@ -4665,7 +4674,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:53" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" ht="109.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>94</v>
       </c>
@@ -4819,7 +4828,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="117" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" ht="117" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -4973,7 +4982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:53" ht="192.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" ht="192.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>112</v>
       </c>
@@ -5131,7 +5140,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="10" spans="1:53" ht="149.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" ht="149.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>117</v>
       </c>
@@ -5285,7 +5294,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:53" ht="141.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" ht="141.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>125</v>
       </c>
@@ -5439,7 +5448,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:53" ht="104.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:53" ht="104.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>130</v>
       </c>
@@ -5589,7 +5598,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="13" spans="1:53" ht="182.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:53" ht="182.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>136</v>
       </c>
@@ -5741,7 +5750,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:53" ht="133.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:53" ht="133.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>145</v>
       </c>
@@ -5895,7 +5904,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:53" ht="230.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:53" ht="230.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>152</v>
       </c>
@@ -6049,7 +6058,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:53" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:53" ht="94.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>156</v>
       </c>
@@ -6203,7 +6212,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>163</v>
       </c>
@@ -6357,7 +6366,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>169</v>
       </c>
@@ -6511,7 +6520,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>174</v>
       </c>
@@ -6665,7 +6674,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>178</v>
       </c>
@@ -6819,7 +6828,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="21" spans="1:53" ht="193.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:53" ht="193.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>182</v>
       </c>
@@ -6975,7 +6984,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:53" ht="99.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:53" ht="99.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>188</v>
       </c>
@@ -7129,7 +7138,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" ht="150" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>194</v>
       </c>
@@ -7273,7 +7282,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>199</v>
       </c>
@@ -7417,7 +7426,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>208</v>
       </c>
@@ -7563,7 +7572,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:53" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:53" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>2021002700364</v>
       </c>
@@ -7717,7 +7726,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="27" spans="1:53" ht="103.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:53" ht="103.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>216</v>
       </c>
@@ -7871,7 +7880,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>221</v>
       </c>
@@ -8015,7 +8024,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="29" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>2022002700005</v>
       </c>
@@ -8169,7 +8178,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>230</v>
       </c>
@@ -8313,7 +8322,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>235</v>
       </c>
@@ -8457,7 +8466,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>2023002700030</v>
       </c>
@@ -8610,7 +8619,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:53" ht="121.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:53" ht="121.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>245</v>
       </c>
@@ -8764,7 +8773,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>252</v>
       </c>
@@ -8908,7 +8917,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>258</v>
       </c>
@@ -9050,7 +9059,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>2023002700134</v>
       </c>
@@ -9202,7 +9211,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="37" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>267</v>
       </c>
@@ -9496,7 +9505,7 @@
       </c>
       <c r="AX38" s="5"/>
       <c r="AY38" s="4" t="s">
-        <v>973</v>
+        <v>1007</v>
       </c>
       <c r="AZ38" s="4" t="s">
         <v>103</v>
@@ -9505,7 +9514,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="39" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>276</v>
       </c>
@@ -9659,7 +9668,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:53" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:53" ht="120" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>283</v>
       </c>
@@ -9813,7 +9822,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="41" spans="1:53" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:53" ht="108" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>288</v>
       </c>
@@ -9967,7 +9976,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="42" spans="1:53" ht="111.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:53" ht="111.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>2024002700151</v>
       </c>
@@ -10119,7 +10128,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="43" spans="1:53" ht="207.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:53" ht="207.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>296</v>
       </c>
@@ -10259,7 +10268,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:53" ht="162.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:53" ht="162.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>2024002700176</v>
       </c>
@@ -10413,7 +10422,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="45" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>2024002700177</v>
       </c>
@@ -10565,7 +10574,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="46" spans="1:53" ht="194.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:53" ht="194.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>313</v>
       </c>
@@ -10713,7 +10722,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
         <v>322</v>
       </c>
@@ -10867,7 +10876,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:53" ht="196.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:53" ht="196.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
         <v>326</v>
       </c>
@@ -10974,7 +10983,7 @@
         <v/>
       </c>
       <c r="AR48" s="4"/>
-      <c r="AS48" s="11">
+      <c r="AS48" s="9">
         <v>100</v>
       </c>
       <c r="AT48" s="4">
@@ -11003,7 +11012,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:53" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:53" ht="99" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>2025000020006</v>
       </c>
@@ -11137,7 +11146,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="50" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>336</v>
       </c>
@@ -11291,7 +11300,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="51" spans="1:53" ht="93" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:53" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>2025000020037</v>
       </c>
@@ -11443,7 +11452,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="52" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>2025002700015</v>
       </c>
@@ -11597,7 +11606,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="53" spans="1:53" ht="192" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:53" ht="192" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>349</v>
       </c>
@@ -11743,7 +11752,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="54" spans="1:53" ht="107.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:53" ht="107.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>353</v>
       </c>
@@ -11879,7 +11888,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="55" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
         <v>359</v>
       </c>
@@ -12031,7 +12040,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="56" spans="1:53" ht="212.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:53" ht="212.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
         <v>364</v>
       </c>
@@ -12179,7 +12188,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="57" spans="1:53" ht="126" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:53" ht="126" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
         <v>370</v>
       </c>
@@ -12319,7 +12328,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="58" spans="1:53" ht="113.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:53" ht="113.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
         <v>376</v>
       </c>
@@ -12455,7 +12464,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="59" spans="1:53" ht="97.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:53" ht="97.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
         <v>381</v>
       </c>
@@ -12589,7 +12598,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="60" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
         <v>388</v>
       </c>
@@ -12723,6 +12732,7 @@
         <v>240</v>
       </c>
     </row>
+    <row r="61" spans="1:53" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:T1"/>
@@ -12749,54 +12759,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="10" t="s">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
-      <c r="AD1" s="10"/>
-      <c r="AE1" s="10"/>
-      <c r="AF1" s="10"/>
-      <c r="AG1" s="10"/>
-      <c r="AH1" s="10"/>
-      <c r="AI1" s="9" t="s">
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+      <c r="AH1" s="11"/>
+      <c r="AI1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="AJ1" s="9"/>
-      <c r="AK1" s="9"/>
-      <c r="AL1" s="9"/>
-      <c r="AM1" s="9"/>
-      <c r="AN1" s="9"/>
-      <c r="AO1" s="9"/>
-      <c r="AP1" s="9"/>
+      <c r="AJ1" s="10"/>
+      <c r="AK1" s="10"/>
+      <c r="AL1" s="10"/>
+      <c r="AM1" s="10"/>
+      <c r="AN1" s="10"/>
+      <c r="AO1" s="10"/>
+      <c r="AP1" s="10"/>
     </row>
     <row r="2" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -14766,27 +14776,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="39.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+      <c r="S1" s="10"/>
     </row>
     <row r="2" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -20439,6 +20449,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008B3DFA865F6F034EB448FC5A52568A32" ma:contentTypeVersion="4" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="2f51a7d93a285d3941b6523f943e8fd4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b00b06bb-bd7e-41cd-b698-c4070c092581" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="efc4bcf9a5ebed2856ce64dac4174bb4" ns2:_="">
     <xsd:import namespace="b00b06bb-bd7e-41cd-b698-c4070c092581"/>
@@ -20582,22 +20607,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0748028-BAD5-48C9-88CC-EC67F793CDEA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9AE3758-66BB-4C1D-BA31-F4D1BF400D5C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35043621-4ADB-44F3-A907-2E95B3BEBE93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20613,21 +20640,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9AE3758-66BB-4C1D-BA31-F4D1BF400D5C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0748028-BAD5-48C9-88CC-EC67F793CDEA}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/data/MatrizSeguimientoEvaluacion.xlsx
+++ b/data/MatrizSeguimientoEvaluacion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/ARCHIVOS CARGUE REPOSITORIO/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://departamentodesucre.sharepoint.com/sites/SeguimientoRegalas/Documentos compartidos/Regalías/GESTION Y SEGUIMIENTO SGR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="553" documentId="13_ncr:1_{3BFAFFED-789E-4342-9BAC-067C8672E2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E14EECF-CD20-4D0F-9F72-524C56A4073E}"/>
+  <xr:revisionPtr revIDLastSave="678" documentId="13_ncr:1_{3BFAFFED-789E-4342-9BAC-067C8672E2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32423158-76AF-45C8-BD15-8070C1706C83}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2007" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="999">
   <si>
     <t>DATOS GENERALES</t>
   </si>
@@ -1306,9 +1306,6 @@
     <t>AVANCE FÍSICO</t>
   </si>
   <si>
-    <t>2020700010140</t>
-  </si>
-  <si>
     <t>EMPRESA AGUAS DE SUCRE S.A. E.S.P.</t>
   </si>
   <si>
@@ -1326,12 +1323,6 @@
     <t>Terminado</t>
   </si>
   <si>
-    <t>Proyecto terminado</t>
-  </si>
-  <si>
-    <t>2020700010143</t>
-  </si>
-  <si>
     <t>Construcción de redes de alcantarillado sanitario en el barrio puerta roja del municipio de Sincelejo Sincelejo</t>
   </si>
   <si>
@@ -1342,9 +1333,6 @@
 Recursos Propios - Departamento de Sucre</t>
   </si>
   <si>
-    <t>2021000020028</t>
-  </si>
-  <si>
     <t>FONDO MIXTO DE PROMOCION DE LA CULTURA Y LAS ARTES DE SUCRE</t>
   </si>
   <si>
@@ -1355,12 +1343,6 @@
   </si>
   <si>
     <t>En ejecución</t>
-  </si>
-  <si>
-    <t>Proyecto en estado de ejecución, con contrato en ejecución y calificación de 75 puntos en el mes de febrero, conforme a su avance de ejecución, teniendo en cuenta el costo, la programación y la brecha entre lo físico y lo financiero.</t>
-  </si>
-  <si>
-    <t>2021002700194</t>
   </si>
   <si>
     <t>Ampliación y optimización del sistema de acueducto de la cabecera municipal de la Unión departamento de Sucre</t>
@@ -1378,9 +1360,6 @@
   </si>
   <si>
     <t>Proyecto en ejecución con contrato suspendido</t>
-  </si>
-  <si>
-    <t>20221301010208</t>
   </si>
   <si>
     <t>Ampliación y optimización del sistema de acueducto primera etapa de la cabecera municipal de Morroa departamento de Sucre</t>
@@ -1396,9 +1375,6 @@
 SGP Propósito General Libre Inversión - Morroa</t>
   </si>
   <si>
-    <t>2023002700011</t>
-  </si>
-  <si>
     <t>Fortalecimiento de las artes plásticas y visuales en los municipios de Sincelejo Corozal Morroa Santiago de Tolú y San Pedro en el departamento de Sucre</t>
   </si>
   <si>
@@ -1406,9 +1382,6 @@
   </si>
   <si>
     <t>Morroa, San Pedro, Santiago de Tolú, Sincelejo, Corozal</t>
-  </si>
-  <si>
-    <t>2023002700070</t>
   </si>
   <si>
     <t>Adecuación y Mejoramiento de Sedes Educativas de la Subregión San Jorge y Sabana por una Educación Diferente Departamento de Sucre</t>
@@ -1424,27 +1397,18 @@
     <t>San Luis de Sincé, Caimito</t>
   </si>
   <si>
-    <t>2023002700127</t>
-  </si>
-  <si>
     <t>Construcción de los embarcaderos marítimos públicos ubicados en el municipio de Santiago de Tolú departamento de Sucre</t>
   </si>
   <si>
     <t xml:space="preserve">SE CONSTRUIRA UN EMBARCADEROS MARITIMOS EN EL MUNICIPIO DE SANTIAGO DE TOLU DEL DEPARTAMENTO DE SUCRE </t>
   </si>
   <si>
-    <t>2023002700169</t>
-  </si>
-  <si>
     <t>Ampliación y optimización del sistema de acueducto del corregimiento de Santiago Apóstol en el municipio de San Benito de Abad Sucre</t>
   </si>
   <si>
     <t xml:space="preserve">Mejorar la prestación del servicio de acueducto en el Corregimiento Santiago Apóstol en el municipio de San Benito de Abad. </t>
   </si>
   <si>
-    <t>2024002700075</t>
-  </si>
-  <si>
     <t>INSTITUTO DEPARTAMENTAL DE DEPORTES Y RECREACION DE SUCRE INDERSUCRE</t>
   </si>
   <si>
@@ -1454,24 +1418,15 @@
     <t xml:space="preserve">MEJORAMIENTO Y ADECUACIÓN DEL PARQUE CENTRAL DEL MUNICIPIO DE SANTIAGO DE TOLÚ Y DEL PARQUE PRINCIPAL DEL BARRIO LAS MARGARITAS DEL MUNICIPIO DE SINCELEJO, DEPARTAMENTO DE SUCRE contemplando la remodelación y/o construcción del parque las Margaritas en un área de 4756m2, y Parque Principal Santiago de Tolú con un área de intervención de 11819.25 M2. Más de 53.889 beneficiados con la ejecución de este proyecto. </t>
   </si>
   <si>
-    <t>Proyecto terminado pero sigue apareciendo en la plataforma en ejecución</t>
-  </si>
-  <si>
     <t>Sincelejo, Santiago de Tolú</t>
   </si>
   <si>
-    <t>2024002700158</t>
-  </si>
-  <si>
     <t>Estudios de prefactibilidad y factibilidad para la estructuración de proyectos de generación de energía eléctrica fotovoltaica en Sucre</t>
   </si>
   <si>
     <t xml:space="preserve">INCREMENTAR LA ACCESIBILIDAD Y CALIDAD EN LA PRESTACIÓN DEL SERVICIO ELÉCTRICO EN SUCRE. </t>
   </si>
   <si>
-    <t>2024002700193</t>
-  </si>
-  <si>
     <t>Construcción de Villa Olímpica Fase I municipio de Tolú Departamento de Sucre</t>
   </si>
   <si>
@@ -1481,9 +1436,6 @@
     <t>Contratado sin ejecución</t>
   </si>
   <si>
-    <t>2024002700194</t>
-  </si>
-  <si>
     <t>Diseño de la alternativa sostenible de provisión de agua para las subregiones sabana y montes de maría Sucre</t>
   </si>
   <si>
@@ -1493,16 +1445,10 @@
     <t>Chalán, Sincelejo, Ovejas, Buenavista, San Juan de Betulia, Los Palmitos, Galeras, Sampués, El Roble, Corozal, San Pedro, Colosó, Morroa, San Luis de Sincé</t>
   </si>
   <si>
-    <t>2025002700010</t>
-  </si>
-  <si>
     <t>Construcción de Parque Recreo Deportivo en el Corregimiento de las Piedras municipio de Toluviejo Departamento de Sucre</t>
   </si>
   <si>
     <t xml:space="preserve">ESTA ALTERNATIVA CONTEMPLA LA CONSTRUCCIÓN DE UN PARQUE RECREO DEPORTIVO EN EL CORREGIMIENTO DE LAS PIEDRAS MUNICIPIO DE TOLUVIEJO, DEPARTAMENTO DE SUCRE, CON UN ÁREA A INTERVENIR DE (1.700 MTS2), INCLUYE CANCHA MÚLTIPLE (MICROFUTBOL - BALONCESTO - VOLEIBOL, CON DEMARCACIÓN DE CANCHAS), PLAZOLETAS DE ACCESO, RECEPCIÓN, DE EVENTOS SOCIALES, PARQUE INFANTIL, SUMINISTRO E INSTALACIÓN DE MÁQUINAS BIOSALUDABLES. EL TIEMPO DE EJECUCIÓN FÍSICA SERÁ DE 5 MESES. 964 BENEFICIARIOS DE ESTE PROYECTO. </t>
-  </si>
-  <si>
-    <t>2025002700011</t>
   </si>
   <si>
     <t>Construcción de cancha deportiva energética en el corregimiento de El Sitio municipio de El Roble Sucre</t>
@@ -3231,7 +3177,34 @@
 </t>
   </si>
   <si>
-    <t>Proyecto en estado de ejecución, con contrato en ejecución , su programación se está ejecutando dentro de los rangos normales. Tiene horizonte hasta el 04 de junio sin embargo se está a la espera de una reprogramación</t>
+    <t>Proyecto terminado, en espera de liquidación</t>
+  </si>
+  <si>
+    <t>Proyecto en ejecución con normalidad</t>
+  </si>
+  <si>
+    <t>Proyecto en ejecución</t>
+  </si>
+  <si>
+    <t>Proyecto terminado en espera de liquidaciones</t>
+  </si>
+  <si>
+    <t>Proyecto sin contratar dentro de los tiempos para su contratación</t>
+  </si>
+  <si>
+    <t>Proyecto terminado pero sigue apareciendo en la plataforma en ejecución.</t>
+  </si>
+  <si>
+    <t>Proyecto en ejecución, sin embargo, no presenta avance físico en la plataforma y presenta horizonte vencido</t>
+  </si>
+  <si>
+    <t>Proyecto en estado de ejecución</t>
+  </si>
+  <si>
+    <t>CERRADO</t>
+  </si>
+  <si>
+    <t>Proyecto cerrado</t>
   </si>
 </sst>
 </file>
@@ -3391,9 +3364,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MatrizSeguimientoEvaluacion" displayName="MatrizSeguimientoEvaluacion" ref="A2:BA61" totalsRowShown="0">
   <autoFilter ref="A2:BA61" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="2">
+    <filterColumn colId="6">
       <filters>
-        <filter val="Construcción de Obras para la Mitigación del Riesgo de Inundación y Socavación en el barrio Altos del Rosario en el Municipio de Sincelejo   Sucre"/>
+        <filter val="PARA CIERRE"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3458,7 +3431,13 @@
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="OtrosEjecutoresDescentralizadas" displayName="OtrosEjecutoresDescentralizadas" ref="A2:AP18" totalsRowShown="0">
-  <autoFilter ref="A2:AP18" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+  <autoFilter ref="A2:AP18" xr:uid="{00000000-0009-0000-0100-000002000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="FONDO MIXTO DE PROMOCION DE LA CULTURA Y LAS ARTES DE SUCRE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="42">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="BPIN"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EJECUTOR"/>
@@ -3839,11 +3818,12 @@
   <cols>
     <col min="1" max="2" width="25.6640625" customWidth="1"/>
     <col min="3" max="3" width="48.6640625" customWidth="1"/>
-    <col min="4" max="4" width="44.6640625" customWidth="1"/>
-    <col min="5" max="5" width="33.109375" customWidth="1"/>
-    <col min="6" max="6" width="45.109375" customWidth="1"/>
-    <col min="7" max="7" width="34.44140625" customWidth="1"/>
-    <col min="8" max="33" width="25.6640625" customWidth="1"/>
+    <col min="4" max="4" width="44.6640625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="33.109375" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="45.109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="34.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="31" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="32" max="33" width="25.6640625" customWidth="1"/>
     <col min="34" max="34" width="50.88671875" customWidth="1"/>
     <col min="35" max="35" width="59.77734375" customWidth="1"/>
     <col min="36" max="41" width="25.6640625" customWidth="1"/>
@@ -4215,7 +4195,7 @@
       </c>
       <c r="AX3" s="5"/>
       <c r="AY3" s="4" t="s">
-        <v>1006</v>
+        <v>988</v>
       </c>
       <c r="AZ3" s="4" t="s">
         <v>67</v>
@@ -4464,7 +4444,7 @@
         <v>84</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="AJ5" s="6">
         <v>46183</v>
@@ -4511,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="AY5" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ5" s="4" t="s">
         <v>78</v>
@@ -4617,10 +4597,10 @@
         <v>46188</v>
       </c>
       <c r="AH6" s="7" t="s">
-        <v>1000</v>
+        <v>982</v>
       </c>
       <c r="AI6" s="4" t="s">
-        <v>1004</v>
+        <v>986</v>
       </c>
       <c r="AJ6" s="6">
         <v>46184</v>
@@ -4772,7 +4752,7 @@
         <v>102</v>
       </c>
       <c r="AI7" s="4" t="s">
-        <v>964</v>
+        <v>946</v>
       </c>
       <c r="AJ7" s="6">
         <v>46184</v>
@@ -4819,7 +4799,7 @@
         <v>50</v>
       </c>
       <c r="AY7" s="4" t="s">
-        <v>965</v>
+        <v>947</v>
       </c>
       <c r="AZ7" s="4" t="s">
         <v>103</v>
@@ -4828,7 +4808,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:53" ht="117" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
@@ -4918,7 +4898,9 @@
       <c r="AE8" s="6">
         <v>44926</v>
       </c>
-      <c r="AF8" s="6"/>
+      <c r="AF8" s="6">
+        <v>46187</v>
+      </c>
       <c r="AG8" s="6">
         <v>46188</v>
       </c>
@@ -4926,7 +4908,7 @@
         <v>66</v>
       </c>
       <c r="AI8" s="4" t="s">
-        <v>1001</v>
+        <v>983</v>
       </c>
       <c r="AJ8" s="6">
         <v>46184</v>
@@ -5081,10 +5063,10 @@
         <v>46188</v>
       </c>
       <c r="AH9" s="4" t="s">
-        <v>925</v>
+        <v>907</v>
       </c>
       <c r="AI9" s="4" t="s">
-        <v>955</v>
+        <v>937</v>
       </c>
       <c r="AJ9" s="6">
         <v>46184</v>
@@ -5131,7 +5113,7 @@
         <v>0</v>
       </c>
       <c r="AY9" s="4" t="s">
-        <v>966</v>
+        <v>948</v>
       </c>
       <c r="AZ9" s="4" t="s">
         <v>78</v>
@@ -5238,7 +5220,7 @@
         <v>122</v>
       </c>
       <c r="AI10" s="4" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="AJ10" s="6">
         <v>46183</v>
@@ -5285,7 +5267,7 @@
         <v>0</v>
       </c>
       <c r="AY10" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ10" s="4" t="s">
         <v>123</v>
@@ -5392,7 +5374,7 @@
         <v>84</v>
       </c>
       <c r="AI11" s="4" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="AJ11" s="6">
         <v>46183</v>
@@ -5439,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="AY11" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ11" s="4" t="s">
         <v>78</v>
@@ -5543,10 +5525,10 @@
         <v>46188</v>
       </c>
       <c r="AH12" s="4" t="s">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="AI12" s="4" t="s">
-        <v>962</v>
+        <v>944</v>
       </c>
       <c r="AJ12" s="6">
         <v>46184</v>
@@ -5589,7 +5571,7 @@
       </c>
       <c r="AX12" s="5"/>
       <c r="AY12" s="4" t="s">
-        <v>967</v>
+        <v>949</v>
       </c>
       <c r="AZ12" s="4" t="s">
         <v>123</v>
@@ -5698,7 +5680,7 @@
         <v>304</v>
       </c>
       <c r="AI13" s="4" t="s">
-        <v>911</v>
+        <v>893</v>
       </c>
       <c r="AJ13" s="6">
         <v>46183</v>
@@ -5848,7 +5830,7 @@
         <v>149</v>
       </c>
       <c r="AI14" s="4" t="s">
-        <v>963</v>
+        <v>945</v>
       </c>
       <c r="AJ14" s="6">
         <v>46184</v>
@@ -6001,10 +5983,10 @@
         <v>46188</v>
       </c>
       <c r="AH15" s="7" t="s">
-        <v>903</v>
+        <v>885</v>
       </c>
       <c r="AI15" s="7" t="s">
-        <v>912</v>
+        <v>894</v>
       </c>
       <c r="AJ15" s="6">
         <v>46183</v>
@@ -6049,7 +6031,7 @@
       </c>
       <c r="AX15" s="5"/>
       <c r="AY15" s="7" t="s">
-        <v>913</v>
+        <v>895</v>
       </c>
       <c r="AZ15" s="4" t="s">
         <v>78</v>
@@ -6156,7 +6138,7 @@
         <v>161</v>
       </c>
       <c r="AI16" s="7" t="s">
-        <v>914</v>
+        <v>896</v>
       </c>
       <c r="AJ16" s="6">
         <v>46183</v>
@@ -6203,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="AY16" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ16" s="4" t="s">
         <v>123</v>
@@ -6307,10 +6289,10 @@
         <v>46188</v>
       </c>
       <c r="AH17" s="4" t="s">
-        <v>927</v>
+        <v>909</v>
       </c>
       <c r="AI17" s="4" t="s">
-        <v>958</v>
+        <v>940</v>
       </c>
       <c r="AJ17" s="6">
         <v>46184</v>
@@ -6357,7 +6339,7 @@
         <v>100</v>
       </c>
       <c r="AY17" s="4" t="s">
-        <v>968</v>
+        <v>950</v>
       </c>
       <c r="AZ17" s="4" t="s">
         <v>123</v>
@@ -6461,10 +6443,10 @@
         <v>46188</v>
       </c>
       <c r="AH18" s="4" t="s">
-        <v>906</v>
+        <v>888</v>
       </c>
       <c r="AI18" s="4" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="AJ18" s="6">
         <v>46183</v>
@@ -6511,7 +6493,7 @@
         <v>50</v>
       </c>
       <c r="AY18" s="4" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="AZ18" s="4" t="s">
         <v>78</v>
@@ -6615,10 +6597,10 @@
         <v>46188</v>
       </c>
       <c r="AH19" s="4" t="s">
-        <v>905</v>
+        <v>887</v>
       </c>
       <c r="AI19" s="4" t="s">
-        <v>915</v>
+        <v>897</v>
       </c>
       <c r="AJ19" s="6">
         <v>46183</v>
@@ -6665,7 +6647,7 @@
         <v>50</v>
       </c>
       <c r="AY19" s="4" t="s">
-        <v>916</v>
+        <v>898</v>
       </c>
       <c r="AZ19" s="4" t="s">
         <v>78</v>
@@ -6769,10 +6751,10 @@
         <v>46188</v>
       </c>
       <c r="AH20" s="4" t="s">
-        <v>909</v>
+        <v>891</v>
       </c>
       <c r="AI20" s="4" t="s">
-        <v>910</v>
+        <v>892</v>
       </c>
       <c r="AJ20" s="6">
         <v>46183</v>
@@ -6819,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="AY20" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ20" s="4" t="s">
         <v>78</v>
@@ -6925,10 +6907,10 @@
         <v>46188</v>
       </c>
       <c r="AH21" s="4" t="s">
-        <v>904</v>
+        <v>886</v>
       </c>
       <c r="AI21" s="4" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="AJ21" s="6">
         <v>46183</v>
@@ -6975,7 +6957,7 @@
         <v>100</v>
       </c>
       <c r="AY21" s="4" t="s">
-        <v>917</v>
+        <v>899</v>
       </c>
       <c r="AZ21" s="4" t="s">
         <v>187</v>
@@ -7081,10 +7063,10 @@
         <v>46188</v>
       </c>
       <c r="AH22" s="4" t="s">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="AI22" s="4" t="s">
-        <v>959</v>
+        <v>941</v>
       </c>
       <c r="AJ22" s="6">
         <v>46184</v>
@@ -7129,7 +7111,7 @@
       </c>
       <c r="AX22" s="5"/>
       <c r="AY22" s="4" t="s">
-        <v>969</v>
+        <v>951</v>
       </c>
       <c r="AZ22" s="4" t="s">
         <v>67</v>
@@ -7138,7 +7120,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:53" ht="150" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:53" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>194</v>
       </c>
@@ -7426,7 +7408,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="25" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>208</v>
       </c>
@@ -7669,10 +7651,10 @@
         <v>46188</v>
       </c>
       <c r="AH26" s="4" t="s">
-        <v>929</v>
+        <v>911</v>
       </c>
       <c r="AI26" s="4" t="s">
-        <v>957</v>
+        <v>939</v>
       </c>
       <c r="AJ26" s="6">
         <v>46184</v>
@@ -7717,7 +7699,7 @@
       </c>
       <c r="AX26" s="5"/>
       <c r="AY26" s="4" t="s">
-        <v>970</v>
+        <v>952</v>
       </c>
       <c r="AZ26" s="4" t="s">
         <v>123</v>
@@ -7821,10 +7803,10 @@
         <v>46188</v>
       </c>
       <c r="AH27" s="4" t="s">
-        <v>907</v>
+        <v>889</v>
       </c>
       <c r="AI27" s="7" t="s">
-        <v>919</v>
+        <v>901</v>
       </c>
       <c r="AJ27" s="6">
         <v>46183</v>
@@ -7871,7 +7853,7 @@
         <v>0</v>
       </c>
       <c r="AY27" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ27" s="4" t="s">
         <v>67</v>
@@ -7880,7 +7862,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>221</v>
       </c>
@@ -8119,10 +8101,10 @@
         <v>46188</v>
       </c>
       <c r="AH29" s="4" t="s">
-        <v>930</v>
+        <v>912</v>
       </c>
       <c r="AI29" s="4" t="s">
-        <v>971</v>
+        <v>953</v>
       </c>
       <c r="AJ29" s="6">
         <v>46184</v>
@@ -8178,7 +8160,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="30" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>230</v>
       </c>
@@ -8322,7 +8304,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="31" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>235</v>
       </c>
@@ -8563,10 +8545,10 @@
         <v>46188</v>
       </c>
       <c r="AH32" s="4" t="s">
-        <v>931</v>
+        <v>913</v>
       </c>
       <c r="AI32" s="4" t="s">
-        <v>961</v>
+        <v>943</v>
       </c>
       <c r="AJ32" s="6">
         <v>46184</v>
@@ -8610,7 +8592,7 @@
       </c>
       <c r="AX32" s="5"/>
       <c r="AY32" s="4" t="s">
-        <v>972</v>
+        <v>954</v>
       </c>
       <c r="AZ32" s="4" t="s">
         <v>103</v>
@@ -8714,10 +8696,10 @@
         <v>46188</v>
       </c>
       <c r="AH33" s="7" t="s">
-        <v>987</v>
+        <v>969</v>
       </c>
       <c r="AI33" s="7" t="s">
-        <v>997</v>
+        <v>979</v>
       </c>
       <c r="AJ33" s="6">
         <v>46183</v>
@@ -8764,7 +8746,7 @@
         <v>100</v>
       </c>
       <c r="AY33" s="4" t="s">
-        <v>980</v>
+        <v>962</v>
       </c>
       <c r="AZ33" s="4" t="s">
         <v>123</v>
@@ -8773,7 +8755,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="34" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>252</v>
       </c>
@@ -8917,7 +8899,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="35" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>258</v>
       </c>
@@ -9154,10 +9136,10 @@
         <v>46188</v>
       </c>
       <c r="AH36" s="4" t="s">
-        <v>932</v>
+        <v>914</v>
       </c>
       <c r="AI36" s="4" t="s">
-        <v>954</v>
+        <v>936</v>
       </c>
       <c r="AJ36" s="6">
         <v>46184</v>
@@ -9202,7 +9184,7 @@
       </c>
       <c r="AX36" s="5"/>
       <c r="AY36" s="4" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="AZ36" s="4" t="s">
         <v>123</v>
@@ -9306,10 +9288,10 @@
         <v>46188</v>
       </c>
       <c r="AH37" s="4" t="s">
-        <v>908</v>
+        <v>890</v>
       </c>
       <c r="AI37" s="7" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
       <c r="AJ37" s="6">
         <v>46183</v>
@@ -9352,7 +9334,7 @@
       </c>
       <c r="AX37" s="5"/>
       <c r="AY37" s="4" t="s">
-        <v>900</v>
+        <v>882</v>
       </c>
       <c r="AZ37" s="4" t="s">
         <v>78</v>
@@ -9361,7 +9343,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:53" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:53" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>2023002700171</v>
       </c>
@@ -9458,10 +9440,10 @@
         <v>46188</v>
       </c>
       <c r="AH38" s="4" t="s">
-        <v>933</v>
+        <v>915</v>
       </c>
       <c r="AI38" s="4" t="s">
-        <v>960</v>
+        <v>942</v>
       </c>
       <c r="AJ38" s="6">
         <v>46184</v>
@@ -9505,7 +9487,7 @@
       </c>
       <c r="AX38" s="5"/>
       <c r="AY38" s="4" t="s">
-        <v>1007</v>
+        <v>955</v>
       </c>
       <c r="AZ38" s="4" t="s">
         <v>103</v>
@@ -9612,7 +9594,7 @@
         <v>281</v>
       </c>
       <c r="AI39" s="4" t="s">
-        <v>1002</v>
+        <v>984</v>
       </c>
       <c r="AJ39" s="6">
         <v>46184</v>
@@ -9765,10 +9747,10 @@
         <v>46188</v>
       </c>
       <c r="AH40" s="4" t="s">
-        <v>934</v>
+        <v>916</v>
       </c>
       <c r="AI40" s="7" t="s">
-        <v>953</v>
+        <v>935</v>
       </c>
       <c r="AJ40" s="6">
         <v>46184</v>
@@ -9813,7 +9795,7 @@
       </c>
       <c r="AX40" s="5"/>
       <c r="AY40" s="4" t="s">
-        <v>974</v>
+        <v>956</v>
       </c>
       <c r="AZ40" s="4" t="s">
         <v>103</v>
@@ -9919,10 +9901,10 @@
         <v>46188</v>
       </c>
       <c r="AH41" s="4" t="s">
-        <v>988</v>
+        <v>970</v>
       </c>
       <c r="AI41" s="7" t="s">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="AJ41" s="6">
         <v>46183</v>
@@ -9967,7 +9949,7 @@
       </c>
       <c r="AX41" s="5"/>
       <c r="AY41" s="4" t="s">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="AZ41" s="4" t="s">
         <v>123</v>
@@ -10071,10 +10053,10 @@
         <v>46188</v>
       </c>
       <c r="AH42" s="4" t="s">
-        <v>989</v>
+        <v>971</v>
       </c>
       <c r="AI42" s="7" t="s">
-        <v>999</v>
+        <v>981</v>
       </c>
       <c r="AJ42" s="6">
         <v>46183</v>
@@ -10119,7 +10101,7 @@
       </c>
       <c r="AX42" s="5"/>
       <c r="AY42" s="4" t="s">
-        <v>982</v>
+        <v>964</v>
       </c>
       <c r="AZ42" s="4" t="s">
         <v>67</v>
@@ -10207,10 +10189,10 @@
         <v>46188</v>
       </c>
       <c r="AH43" s="4" t="s">
-        <v>901</v>
+        <v>883</v>
       </c>
       <c r="AI43" s="7" t="s">
-        <v>921</v>
+        <v>903</v>
       </c>
       <c r="AJ43" s="6">
         <v>46183</v>
@@ -10259,7 +10241,7 @@
       </c>
       <c r="AX43" s="5"/>
       <c r="AY43" s="7" t="s">
-        <v>922</v>
+        <v>904</v>
       </c>
       <c r="AZ43" s="4" t="s">
         <v>67</v>
@@ -10368,7 +10350,7 @@
         <v>304</v>
       </c>
       <c r="AI44" s="7" t="s">
-        <v>994</v>
+        <v>976</v>
       </c>
       <c r="AJ44" s="6">
         <v>46183</v>
@@ -10413,7 +10395,7 @@
       </c>
       <c r="AX44" s="5"/>
       <c r="AY44" s="4" t="s">
-        <v>983</v>
+        <v>965</v>
       </c>
       <c r="AZ44" s="4" t="s">
         <v>103</v>
@@ -10517,10 +10499,10 @@
         <v>46188</v>
       </c>
       <c r="AH45" s="4" t="s">
-        <v>935</v>
+        <v>917</v>
       </c>
       <c r="AI45" s="4" t="s">
-        <v>956</v>
+        <v>938</v>
       </c>
       <c r="AJ45" s="6">
         <v>46184</v>
@@ -10565,7 +10547,7 @@
       </c>
       <c r="AX45" s="5"/>
       <c r="AY45" s="4" t="s">
-        <v>975</v>
+        <v>957</v>
       </c>
       <c r="AZ45" s="4" t="s">
         <v>123</v>
@@ -10666,7 +10648,7 @@
         <v>320</v>
       </c>
       <c r="AI46" s="4" t="s">
-        <v>949</v>
+        <v>931</v>
       </c>
       <c r="AJ46" s="6">
         <v>46184</v>
@@ -10817,10 +10799,10 @@
         <v>46188</v>
       </c>
       <c r="AH47" s="4" t="s">
-        <v>902</v>
+        <v>884</v>
       </c>
       <c r="AI47" s="4" t="s">
-        <v>923</v>
+        <v>905</v>
       </c>
       <c r="AJ47" s="6">
         <v>46183</v>
@@ -10867,7 +10849,7 @@
         <v>100</v>
       </c>
       <c r="AY47" s="4" t="s">
-        <v>924</v>
+        <v>906</v>
       </c>
       <c r="AZ47" s="4" t="s">
         <v>123</v>
@@ -10953,10 +10935,10 @@
         <v>46188</v>
       </c>
       <c r="AH48" s="4" t="s">
-        <v>990</v>
+        <v>972</v>
       </c>
       <c r="AI48" s="7" t="s">
-        <v>995</v>
+        <v>977</v>
       </c>
       <c r="AJ48" s="6">
         <v>46183</v>
@@ -11003,7 +10985,7 @@
       </c>
       <c r="AX48" s="5"/>
       <c r="AY48" s="4" t="s">
-        <v>984</v>
+        <v>966</v>
       </c>
       <c r="AZ48" s="4" t="s">
         <v>67</v>
@@ -11087,10 +11069,10 @@
         <v>46188</v>
       </c>
       <c r="AH49" s="4" t="s">
-        <v>936</v>
+        <v>918</v>
       </c>
       <c r="AI49" s="4" t="s">
-        <v>948</v>
+        <v>930</v>
       </c>
       <c r="AJ49" s="6">
         <v>46184</v>
@@ -11244,7 +11226,7 @@
         <v>341</v>
       </c>
       <c r="AI50" s="4" t="s">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="AJ50" s="6">
         <v>46184</v>
@@ -11291,7 +11273,7 @@
         <v>0</v>
       </c>
       <c r="AY50" s="4" t="s">
-        <v>1005</v>
+        <v>987</v>
       </c>
       <c r="AZ50" s="4" t="s">
         <v>78</v>
@@ -11395,10 +11377,10 @@
         <v>46188</v>
       </c>
       <c r="AH51" s="4" t="s">
-        <v>937</v>
+        <v>919</v>
       </c>
       <c r="AI51" s="4" t="s">
-        <v>951</v>
+        <v>933</v>
       </c>
       <c r="AJ51" s="6">
         <v>46184</v>
@@ -11443,7 +11425,7 @@
       </c>
       <c r="AX51" s="5"/>
       <c r="AY51" s="4" t="s">
-        <v>976</v>
+        <v>958</v>
       </c>
       <c r="AZ51" s="4" t="s">
         <v>345</v>
@@ -11549,10 +11531,10 @@
         <v>46188</v>
       </c>
       <c r="AH52" s="4" t="s">
-        <v>938</v>
+        <v>920</v>
       </c>
       <c r="AI52" s="4" t="s">
-        <v>952</v>
+        <v>934</v>
       </c>
       <c r="AJ52" s="6">
         <v>46184</v>
@@ -11597,7 +11579,7 @@
       </c>
       <c r="AX52" s="5"/>
       <c r="AY52" s="4" t="s">
-        <v>973</v>
+        <v>955</v>
       </c>
       <c r="AZ52" s="4" t="s">
         <v>345</v>
@@ -11693,10 +11675,10 @@
         <v>46188</v>
       </c>
       <c r="AH53" s="7" t="s">
-        <v>939</v>
+        <v>921</v>
       </c>
       <c r="AI53" s="4" t="s">
-        <v>950</v>
+        <v>932</v>
       </c>
       <c r="AJ53" s="6">
         <v>46184</v>
@@ -11743,7 +11725,7 @@
       </c>
       <c r="AX53" s="5"/>
       <c r="AY53" s="4" t="s">
-        <v>977</v>
+        <v>959</v>
       </c>
       <c r="AZ53" s="4" t="s">
         <v>345</v>
@@ -11827,10 +11809,10 @@
         <v>46188</v>
       </c>
       <c r="AH54" s="4" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="AI54" s="4" t="s">
-        <v>946</v>
+        <v>928</v>
       </c>
       <c r="AJ54" s="6">
         <v>46184</v>
@@ -11983,10 +11965,10 @@
         <v>46188</v>
       </c>
       <c r="AH55" s="4" t="s">
-        <v>991</v>
+        <v>973</v>
       </c>
       <c r="AI55" s="7" t="s">
-        <v>993</v>
+        <v>975</v>
       </c>
       <c r="AJ55" s="6">
         <v>46183</v>
@@ -12031,7 +12013,7 @@
       </c>
       <c r="AX55" s="5"/>
       <c r="AY55" s="4" t="s">
-        <v>985</v>
+        <v>967</v>
       </c>
       <c r="AZ55" s="4" t="s">
         <v>345</v>
@@ -12127,10 +12109,10 @@
         <v>46188</v>
       </c>
       <c r="AH56" s="7" t="s">
-        <v>992</v>
+        <v>974</v>
       </c>
       <c r="AI56" s="7" t="s">
-        <v>998</v>
+        <v>980</v>
       </c>
       <c r="AJ56" s="6">
         <v>46183</v>
@@ -12179,7 +12161,7 @@
       </c>
       <c r="AX56" s="5"/>
       <c r="AY56" s="4" t="s">
-        <v>986</v>
+        <v>968</v>
       </c>
       <c r="AZ56" s="4" t="s">
         <v>345</v>
@@ -12267,10 +12249,10 @@
         <v>46188</v>
       </c>
       <c r="AH57" s="4" t="s">
-        <v>941</v>
+        <v>923</v>
       </c>
       <c r="AI57" s="4" t="s">
-        <v>944</v>
+        <v>926</v>
       </c>
       <c r="AJ57" s="6">
         <v>46184</v>
@@ -12319,7 +12301,7 @@
       </c>
       <c r="AX57" s="5"/>
       <c r="AY57" s="4" t="s">
-        <v>978</v>
+        <v>960</v>
       </c>
       <c r="AZ57" s="4" t="s">
         <v>345</v>
@@ -12403,10 +12385,10 @@
         <v>46188</v>
       </c>
       <c r="AH58" s="4" t="s">
-        <v>942</v>
+        <v>924</v>
       </c>
       <c r="AI58" s="4" t="s">
-        <v>945</v>
+        <v>927</v>
       </c>
       <c r="AJ58" s="6">
         <v>46184</v>
@@ -12537,10 +12519,10 @@
         <v>46188</v>
       </c>
       <c r="AH59" s="4" t="s">
-        <v>940</v>
+        <v>922</v>
       </c>
       <c r="AI59" s="4" t="s">
-        <v>947</v>
+        <v>929</v>
       </c>
       <c r="AJ59" s="6">
         <v>46184</v>
@@ -12675,7 +12657,7 @@
         <v>46188</v>
       </c>
       <c r="AH60" s="4" t="s">
-        <v>943</v>
+        <v>925</v>
       </c>
       <c r="AI60" s="4"/>
       <c r="AJ60" s="6">
@@ -12723,7 +12705,7 @@
       </c>
       <c r="AX60" s="5"/>
       <c r="AY60" s="4" t="s">
-        <v>979</v>
+        <v>961</v>
       </c>
       <c r="AZ60" s="4" t="s">
         <v>103</v>
@@ -12751,7 +12733,12 @@
   <dimension ref="A1:AP18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="31" width="25.6640625" customWidth="1"/>
+    <col min="1" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.44140625" customWidth="1"/>
+    <col min="4" max="4" width="46.109375" customWidth="1"/>
+    <col min="5" max="5" width="25.6640625" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" customWidth="1"/>
+    <col min="7" max="31" width="25.6640625" customWidth="1"/>
     <col min="32" max="32" width="25.6640625" hidden="1" customWidth="1"/>
     <col min="33" max="37" width="25.6640625" customWidth="1"/>
     <col min="38" max="38" width="25.6640625" hidden="1" customWidth="1"/>
@@ -12936,30 +12923,30 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:42" ht="100.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2020700010140</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>402</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>255</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I3" s="5">
         <v>2006938345.6700001</v>
@@ -13038,38 +13025,40 @@
         <f t="shared" ref="AM3:AM18" si="5">IFERROR(IF($G3="CONTRATADO EN EJECUCIÓN",IF(AND(ISNUMBER($X3),ISNUMBER($Z3),$X3&lt;$Z3),0,IF($AH3&gt;=1,(IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))*$AL3/100,IFERROR(IF(ISNUMBER($AJ3),($AD3*0.4+$AE3*0.2+$AG3*0.4),""),""))),IF($G3="CONTRATADO SIN ACTA DE INICIO",IF(AND($Z3-$V3&gt;=0,$Z3-$V3&lt;=30),100,0),"")),"")</f>
         <v/>
       </c>
-      <c r="AN3" s="5"/>
+      <c r="AN3" s="5">
+        <v>0</v>
+      </c>
       <c r="AO3" s="4" t="s">
-        <v>405</v>
+        <v>989</v>
       </c>
       <c r="AP3" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>406</v>
+    <row r="4" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>2020700010143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>255</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I4" s="5">
         <v>1295118639.0699999</v>
@@ -13148,26 +13137,28 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AN4" s="5"/>
+      <c r="AN4" s="5">
+        <v>0</v>
+      </c>
       <c r="AO4" s="4" t="s">
-        <v>405</v>
+        <v>989</v>
       </c>
       <c r="AP4" s="4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>410</v>
+    <row r="5" spans="1:42" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>2021000020028</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>60</v>
@@ -13179,7 +13170,7 @@
         <v>90</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I5" s="5">
         <v>3153851580.9099998</v>
@@ -13198,10 +13189,10 @@
       </c>
       <c r="N5" s="6"/>
       <c r="O5" s="5">
-        <v>96.02</v>
+        <v>96.72</v>
       </c>
       <c r="P5" s="5">
-        <v>94.36</v>
+        <v>97.86</v>
       </c>
       <c r="Q5" s="4">
         <v>1</v>
@@ -13222,10 +13213,12 @@
       <c r="W5" s="6">
         <v>44722</v>
       </c>
-      <c r="X5" s="6"/>
+      <c r="X5" s="6">
+        <v>46562</v>
+      </c>
       <c r="Y5" s="6"/>
       <c r="Z5" s="6">
-        <v>46096</v>
+        <v>46188</v>
       </c>
       <c r="AA5" s="4"/>
       <c r="AB5" s="4"/>
@@ -13266,36 +13259,36 @@
       </c>
       <c r="AN5" s="5"/>
       <c r="AO5" s="4" t="s">
-        <v>415</v>
+        <v>996</v>
       </c>
       <c r="AP5" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>416</v>
+    <row r="6" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>2021002700194</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>255</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="I6" s="5">
         <v>6026477761</v>
@@ -13316,7 +13309,7 @@
         <v>44509</v>
       </c>
       <c r="O6" s="5">
-        <v>73.45</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="P6" s="5">
         <v>49.45</v>
@@ -13325,7 +13318,7 @@
         <v>1</v>
       </c>
       <c r="R6" s="4">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="S6" s="6">
         <v>44503</v>
@@ -13340,7 +13333,9 @@
       <c r="W6" s="6">
         <v>44810</v>
       </c>
-      <c r="X6" s="6"/>
+      <c r="X6" s="6">
+        <v>46307</v>
+      </c>
       <c r="Y6" s="6"/>
       <c r="Z6" s="6">
         <v>46127</v>
@@ -13365,7 +13360,7 @@
         <v>100</v>
       </c>
       <c r="AH6" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI6" s="4"/>
       <c r="AJ6" s="4">
@@ -13376,44 +13371,44 @@
       </c>
       <c r="AL6" s="4">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM6" s="4">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AN6" s="5"/>
       <c r="AO6" s="4" t="s">
-        <v>421</v>
+        <v>990</v>
       </c>
       <c r="AP6" s="4" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>422</v>
+    <row r="7" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>20221301010208</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>255</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I7" s="5">
         <v>1800000000</v>
@@ -13440,10 +13435,10 @@
         <v>45.29</v>
       </c>
       <c r="Q7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" s="6">
         <v>44924</v>
@@ -13458,7 +13453,9 @@
       <c r="W7" s="6">
         <v>45175</v>
       </c>
-      <c r="X7" s="6"/>
+      <c r="X7" s="6">
+        <v>46293</v>
+      </c>
       <c r="Y7" s="6"/>
       <c r="Z7" s="6">
         <v>46127</v>
@@ -13468,11 +13465,11 @@
       <c r="AC7" s="4"/>
       <c r="AD7" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="4">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF7" s="4">
         <f t="shared" si="2"/>
@@ -13483,7 +13480,7 @@
         <v>100</v>
       </c>
       <c r="AH7" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI7" s="4"/>
       <c r="AJ7" s="4">
@@ -13494,32 +13491,32 @@
       </c>
       <c r="AL7" s="4">
         <f t="shared" si="4"/>
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM7" s="4">
         <f t="shared" si="5"/>
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AN7" s="5"/>
       <c r="AO7" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="AP7" s="4" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>426</v>
+      <c r="A8" s="4">
+        <v>2023002700011</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>60</v>
@@ -13531,7 +13528,7 @@
         <v>62</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I8" s="5">
         <v>1702007732.2</v>
@@ -13575,7 +13572,7 @@
       <c r="X8" s="6"/>
       <c r="Y8" s="6"/>
       <c r="Z8" s="6">
-        <v>46096</v>
+        <v>46188</v>
       </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
@@ -13610,38 +13607,40 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AN8" s="5"/>
+      <c r="AN8" s="5">
+        <v>0</v>
+      </c>
       <c r="AO8" s="4" t="s">
-        <v>405</v>
+        <v>989</v>
       </c>
       <c r="AP8" s="4" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>430</v>
+      <c r="A9" s="4">
+        <v>2023002700070</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>261</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>109</v>
+        <v>997</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I9" s="5">
         <v>13713002364.719999</v>
@@ -13667,12 +13666,8 @@
       <c r="P9" s="5">
         <v>99.99</v>
       </c>
-      <c r="Q9" s="4">
-        <v>1</v>
-      </c>
-      <c r="R9" s="4">
-        <v>1</v>
-      </c>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
       <c r="S9" s="6">
         <v>45290</v>
       </c>
@@ -13689,7 +13684,7 @@
       <c r="X9" s="6"/>
       <c r="Y9" s="6"/>
       <c r="Z9" s="6">
-        <v>46096</v>
+        <v>46188</v>
       </c>
       <c r="AA9" s="4"/>
       <c r="AB9" s="4"/>
@@ -13714,12 +13709,8 @@
         <v>2</v>
       </c>
       <c r="AI9" s="4"/>
-      <c r="AJ9" s="4">
-        <v>100</v>
-      </c>
-      <c r="AK9" s="4">
-        <v>100</v>
-      </c>
+      <c r="AJ9" s="4"/>
+      <c r="AK9" s="4"/>
       <c r="AL9" s="4">
         <f t="shared" si="4"/>
         <v>75</v>
@@ -13730,24 +13721,24 @@
       </c>
       <c r="AN9" s="5"/>
       <c r="AO9" s="4" t="s">
-        <v>405</v>
+        <v>998</v>
       </c>
       <c r="AP9" s="4" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>435</v>
+      <c r="A10" s="4">
+        <v>2023002700127</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>211</v>
@@ -13759,7 +13750,7 @@
         <v>90</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I10" s="5">
         <v>9056051736.6399994</v>
@@ -13780,16 +13771,16 @@
         <v>45290</v>
       </c>
       <c r="O10" s="5">
-        <v>15.79</v>
+        <v>64.319999999999993</v>
       </c>
       <c r="P10" s="5">
-        <v>31.78</v>
+        <v>49.49</v>
       </c>
       <c r="Q10" s="4">
         <v>1</v>
       </c>
       <c r="R10" s="4">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="S10" s="6">
         <v>45290</v>
@@ -13804,10 +13795,12 @@
       <c r="W10" s="6">
         <v>45772</v>
       </c>
-      <c r="X10" s="6"/>
+      <c r="X10" s="6">
+        <v>46735</v>
+      </c>
       <c r="Y10" s="6"/>
       <c r="Z10" s="6">
-        <v>46096</v>
+        <v>46188</v>
       </c>
       <c r="AA10" s="4"/>
       <c r="AB10" s="4"/>
@@ -13828,7 +13821,9 @@
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="AH10" s="4"/>
+      <c r="AH10" s="4">
+        <v>0</v>
+      </c>
       <c r="AI10" s="4"/>
       <c r="AJ10" s="4">
         <v>100</v>
@@ -13845,23 +13840,25 @@
         <v>100</v>
       </c>
       <c r="AN10" s="5"/>
-      <c r="AO10" s="4"/>
+      <c r="AO10" s="4" t="s">
+        <v>996</v>
+      </c>
       <c r="AP10" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>438</v>
+    <row r="11" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>2023002700169</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>255</v>
@@ -13873,7 +13870,7 @@
         <v>90</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I11" s="5">
         <v>7862105021</v>
@@ -13894,7 +13891,7 @@
         <v>45485</v>
       </c>
       <c r="O11" s="5">
-        <v>94.7</v>
+        <v>94.83</v>
       </c>
       <c r="P11" s="5">
         <v>89.87</v>
@@ -13918,7 +13915,9 @@
       <c r="W11" s="6">
         <v>45624</v>
       </c>
-      <c r="X11" s="6"/>
+      <c r="X11" s="6">
+        <v>46293</v>
+      </c>
       <c r="Y11" s="6"/>
       <c r="Z11" s="6">
         <v>46127</v>
@@ -13943,7 +13942,7 @@
         <v>100</v>
       </c>
       <c r="AH11" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI11" s="4"/>
       <c r="AJ11" s="4">
@@ -13954,30 +13953,32 @@
       </c>
       <c r="AL11" s="4">
         <f t="shared" si="4"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AM11" s="4">
         <f t="shared" si="5"/>
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="4"/>
+      <c r="AO11" s="4" t="s">
+        <v>990</v>
+      </c>
       <c r="AP11" s="4" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>441</v>
+    <row r="12" spans="1:42" ht="110.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>2024002700075</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>238</v>
@@ -13989,7 +13990,7 @@
         <v>90</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I12" s="5">
         <v>15100656106.639999</v>
@@ -14016,10 +14017,10 @@
         <v>88.74</v>
       </c>
       <c r="Q12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="6">
         <v>45470</v>
@@ -14034,7 +14035,9 @@
       <c r="W12" s="6">
         <v>45723</v>
       </c>
-      <c r="X12" s="6"/>
+      <c r="X12" s="6">
+        <v>46088</v>
+      </c>
       <c r="Y12" s="6"/>
       <c r="Z12" s="6">
         <v>46096</v>
@@ -14044,11 +14047,11 @@
       <c r="AC12" s="4"/>
       <c r="AD12" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="4">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="2"/>
@@ -14074,28 +14077,28 @@
       </c>
       <c r="AM12" s="4">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="5"/>
       <c r="AO12" s="4" t="s">
-        <v>445</v>
+        <v>994</v>
       </c>
       <c r="AP12" s="4" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
     </row>
-    <row r="13" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>447</v>
+    <row r="13" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>2024002700158</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>448</v>
+        <v>434</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>249</v>
@@ -14107,7 +14110,7 @@
         <v>62</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I13" s="5">
         <v>3068416428</v>
@@ -14131,14 +14134,10 @@
         <v>99.99</v>
       </c>
       <c r="P13" s="5">
-        <v>64.38</v>
-      </c>
-      <c r="Q13" s="4">
-        <v>1</v>
-      </c>
-      <c r="R13" s="4">
-        <v>1</v>
-      </c>
+        <v>86.72</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
       <c r="S13" s="6">
         <v>45650</v>
       </c>
@@ -14152,7 +14151,9 @@
       <c r="W13" s="6">
         <v>45863</v>
       </c>
-      <c r="X13" s="6"/>
+      <c r="X13" s="6">
+        <v>46136</v>
+      </c>
       <c r="Y13" s="6"/>
       <c r="Z13" s="6">
         <v>46127</v>
@@ -14192,24 +14193,28 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AN13" s="5"/>
-      <c r="AO13" s="4"/>
+      <c r="AN13" s="5">
+        <v>100</v>
+      </c>
+      <c r="AO13" s="4" t="s">
+        <v>992</v>
+      </c>
       <c r="AP13" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>450</v>
+    <row r="14" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>2024002700193</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>238</v>
@@ -14221,7 +14226,7 @@
         <v>90</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="I14" s="5">
         <v>63850574205.629997</v>
@@ -14242,16 +14247,16 @@
         <v>45656</v>
       </c>
       <c r="O14" s="5">
-        <v>27.35</v>
+        <v>34.15</v>
       </c>
       <c r="P14" s="5">
-        <v>48.74</v>
+        <v>48.79</v>
       </c>
       <c r="Q14" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="4">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="S14" s="6">
         <v>45653</v>
@@ -14266,7 +14271,9 @@
       <c r="W14" s="6">
         <v>45672</v>
       </c>
-      <c r="X14" s="6"/>
+      <c r="X14" s="6">
+        <v>46494</v>
+      </c>
       <c r="Y14" s="6"/>
       <c r="Z14" s="6">
         <v>46096</v>
@@ -14276,11 +14283,11 @@
       <c r="AC14" s="4"/>
       <c r="AD14" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>28.260869565217394</v>
       </c>
       <c r="AE14" s="4">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="2"/>
@@ -14304,28 +14311,30 @@
         <f t="shared" si="4"/>
         <v>75</v>
       </c>
-      <c r="AM14" s="4">
+      <c r="AM14" s="8">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>53.478260869565226</v>
       </c>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="4"/>
+      <c r="AO14" s="4" t="s">
+        <v>991</v>
+      </c>
       <c r="AP14" s="4" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="15" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>454</v>
+    <row r="15" spans="1:42" ht="123" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>2024002700194</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>255</v>
@@ -14337,7 +14346,7 @@
         <v>90</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I15" s="5">
         <v>11318403530.17</v>
@@ -14358,7 +14367,7 @@
         <v>45825</v>
       </c>
       <c r="O15" s="5">
-        <v>19.2</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="P15" s="5">
         <v>40</v>
@@ -14367,7 +14376,7 @@
         <v>1</v>
       </c>
       <c r="R15" s="4">
-        <v>1.06</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="S15" s="6">
         <v>45818</v>
@@ -14382,7 +14391,9 @@
       <c r="W15" s="6">
         <v>46030</v>
       </c>
-      <c r="X15" s="6"/>
+      <c r="X15" s="6">
+        <v>46637</v>
+      </c>
       <c r="Y15" s="6"/>
       <c r="Z15" s="6">
         <v>46127</v>
@@ -14423,23 +14434,25 @@
         <v>100</v>
       </c>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="4"/>
+      <c r="AO15" s="4" t="s">
+        <v>990</v>
+      </c>
       <c r="AP15" s="4" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
     </row>
-    <row r="16" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>458</v>
+    <row r="16" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>2025002700010</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>459</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>238</v>
@@ -14448,10 +14461,10 @@
         <v>205</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>317</v>
+        <v>90</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>453</v>
+        <v>410</v>
       </c>
       <c r="I16" s="5">
         <v>1903272161</v>
@@ -14472,13 +14485,17 @@
         <v>45803</v>
       </c>
       <c r="O16" s="5">
-        <v>0</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="P16" s="5">
         <v>0</v>
       </c>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
+      <c r="Q16" s="4">
+        <v>1</v>
+      </c>
+      <c r="R16" s="4">
+        <v>0.37</v>
+      </c>
       <c r="S16" s="6">
         <v>45785</v>
       </c>
@@ -14491,8 +14508,12 @@
       <c r="V16" s="6">
         <v>46058</v>
       </c>
-      <c r="W16" s="6"/>
-      <c r="X16" s="6"/>
+      <c r="W16" s="6">
+        <v>46125</v>
+      </c>
+      <c r="X16" s="6">
+        <v>46293</v>
+      </c>
       <c r="Y16" s="6"/>
       <c r="Z16" s="6">
         <v>46096</v>
@@ -14502,21 +14523,21 @@
       <c r="AC16" s="4">
         <v>38</v>
       </c>
-      <c r="AD16" s="4" t="str">
+      <c r="AD16" s="4">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="AE16" s="4" t="str">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="4">
         <f t="shared" si="1"/>
-        <v/>
+        <v>100</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="AG16" s="4" t="str">
+      <c r="AG16" s="4">
         <f t="shared" si="3"/>
-        <v/>
+        <v>100</v>
       </c>
       <c r="AH16" s="4"/>
       <c r="AI16" s="4">
@@ -14534,26 +14555,28 @@
       </c>
       <c r="AM16" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="4"/>
+      <c r="AO16" s="4" t="s">
+        <v>991</v>
+      </c>
       <c r="AP16" s="4" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>461</v>
+    <row r="17" spans="1:42" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>2025002700011</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>462</v>
+        <v>444</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>463</v>
+        <v>445</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>238</v>
@@ -14565,7 +14588,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="I17" s="5">
         <v>1484402616</v>
@@ -14576,19 +14599,27 @@
       <c r="K17" s="5">
         <v>1884402616</v>
       </c>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
+      <c r="L17" s="6">
+        <v>45800</v>
+      </c>
+      <c r="M17" s="6">
+        <v>45801</v>
+      </c>
       <c r="N17" s="6">
         <v>45803</v>
       </c>
       <c r="O17" s="5">
-        <v>9.6000000000000002E-2</v>
+        <v>0</v>
       </c>
       <c r="P17" s="5">
         <v>22.11</v>
       </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
+      <c r="Q17" s="4">
+        <v>0</v>
+      </c>
+      <c r="R17" s="4">
+        <v>0</v>
+      </c>
       <c r="S17" s="6">
         <v>45796</v>
       </c>
@@ -14602,7 +14633,9 @@
       <c r="W17" s="6">
         <v>46120</v>
       </c>
-      <c r="X17" s="6"/>
+      <c r="X17" s="6">
+        <v>46100</v>
+      </c>
       <c r="Y17" s="6"/>
       <c r="Z17" s="6">
         <v>46096</v>
@@ -14643,35 +14676,37 @@
         <v>40</v>
       </c>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="4"/>
+      <c r="AO17" s="4" t="s">
+        <v>995</v>
+      </c>
       <c r="AP17" s="4" t="s">
-        <v>464</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="18" spans="1:42" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" ht="121.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>467</v>
+        <v>449</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>255</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>300</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="I18" s="5">
         <v>627486059.86000001</v>
@@ -14747,9 +14782,11 @@
         <v/>
       </c>
       <c r="AN18" s="5"/>
-      <c r="AO18" s="4"/>
+      <c r="AO18" s="4" t="s">
+        <v>993</v>
+      </c>
       <c r="AP18" s="4" t="s">
-        <v>470</v>
+        <v>452</v>
       </c>
     </row>
   </sheetData>
@@ -14851,7 +14888,7 @@
         <v>24</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="S2" s="3" t="s">
         <v>55</v>
@@ -14859,16 +14896,16 @@
     </row>
     <row r="3" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>473</v>
+        <v>455</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>474</v>
+        <v>456</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>98</v>
@@ -14880,7 +14917,7 @@
         <v>62</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="I3" s="5">
         <v>22526692745</v>
@@ -14909,21 +14946,21 @@
       </c>
       <c r="R3" s="4"/>
       <c r="S3" s="4" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>481</v>
+        <v>463</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>98</v>
@@ -14935,7 +14972,7 @@
         <v>62</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I4" s="5">
         <v>924979909</v>
@@ -14964,21 +15001,21 @@
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4" t="s">
-        <v>482</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>483</v>
+        <v>465</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>486</v>
+        <v>468</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>98</v>
@@ -14990,7 +15027,7 @@
         <v>62</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="I5" s="5">
         <v>999998309</v>
@@ -15019,21 +15056,21 @@
       </c>
       <c r="R5" s="4"/>
       <c r="S5" s="4" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>489</v>
+        <v>471</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>490</v>
+        <v>472</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>491</v>
+        <v>473</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>98</v>
@@ -15045,7 +15082,7 @@
         <v>62</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="I6" s="5">
         <v>16567304387</v>
@@ -15074,33 +15111,33 @@
       </c>
       <c r="R6" s="4"/>
       <c r="S6" s="4" t="s">
-        <v>492</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>493</v>
+        <v>475</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>484</v>
+        <v>466</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>495</v>
+        <v>477</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>496</v>
+        <v>478</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I7" s="5">
         <v>12429000000</v>
@@ -15129,21 +15166,21 @@
       </c>
       <c r="R7" s="4"/>
       <c r="S7" s="4" t="s">
-        <v>487</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>308</v>
@@ -15155,7 +15192,7 @@
         <v>90</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="I8" s="5">
         <v>14996018261</v>
@@ -15184,33 +15221,33 @@
       </c>
       <c r="R8" s="4"/>
       <c r="S8" s="4" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I9" s="5">
         <v>14913362760</v>
@@ -15244,28 +15281,28 @@
     </row>
     <row r="10" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I10" s="5">
         <v>7037696704</v>
@@ -15294,21 +15331,21 @@
       </c>
       <c r="R10" s="4"/>
       <c r="S10" s="4" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>516</v>
+        <v>498</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>73</v>
@@ -15320,7 +15357,7 @@
         <v>62</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I11" s="5">
         <v>13800000000</v>
@@ -15354,28 +15391,28 @@
     </row>
     <row r="12" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I12" s="5">
         <v>16094650077</v>
@@ -15409,28 +15446,28 @@
     </row>
     <row r="13" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>523</v>
+        <v>505</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>525</v>
+        <v>507</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>526</v>
+        <v>508</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>527</v>
+        <v>509</v>
       </c>
       <c r="I13" s="5">
         <v>54337268559</v>
@@ -15459,33 +15496,33 @@
       </c>
       <c r="R13" s="4"/>
       <c r="S13" s="4" t="s">
-        <v>528</v>
+        <v>510</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>529</v>
+        <v>511</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>530</v>
+        <v>512</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>531</v>
+        <v>513</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>98</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>90</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I14" s="5">
         <v>5261488233</v>
@@ -15519,16 +15556,16 @@
     </row>
     <row r="15" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>534</v>
+        <v>516</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>536</v>
+        <v>518</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>537</v>
+        <v>519</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>139</v>
@@ -15540,7 +15577,7 @@
         <v>62</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I15" s="5">
         <v>8077068482</v>
@@ -15569,21 +15606,21 @@
       </c>
       <c r="R15" s="4"/>
       <c r="S15" s="4" t="s">
-        <v>538</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>539</v>
+        <v>521</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>540</v>
+        <v>522</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>541</v>
+        <v>523</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>542</v>
+        <v>524</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>73</v>
@@ -15595,7 +15632,7 @@
         <v>90</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I16" s="5">
         <v>7750000000</v>
@@ -15624,21 +15661,21 @@
       </c>
       <c r="R16" s="4"/>
       <c r="S16" s="4" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>545</v>
+        <v>527</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>546</v>
+        <v>528</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>547</v>
+        <v>529</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>73</v>
@@ -15650,7 +15687,7 @@
         <v>90</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="I17" s="5">
         <v>1027100000</v>
@@ -15679,21 +15716,21 @@
       </c>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>548</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>549</v>
+        <v>531</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>550</v>
+        <v>532</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>551</v>
+        <v>533</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>552</v>
+        <v>534</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>73</v>
@@ -15705,7 +15742,7 @@
         <v>90</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I18" s="5">
         <v>9491491960</v>
@@ -15734,21 +15771,21 @@
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>553</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>554</v>
+        <v>536</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>73</v>
@@ -15760,7 +15797,7 @@
         <v>90</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I19" s="5">
         <v>4024500000</v>
@@ -15789,21 +15826,21 @@
       </c>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>561</v>
+        <v>543</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>562</v>
+        <v>544</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>73</v>
@@ -15815,7 +15852,7 @@
         <v>90</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I20" s="5">
         <v>20233937500</v>
@@ -15844,21 +15881,21 @@
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>563</v>
+        <v>545</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>564</v>
+        <v>546</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>565</v>
+        <v>547</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>566</v>
+        <v>548</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>567</v>
+        <v>549</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>73</v>
@@ -15870,7 +15907,7 @@
         <v>90</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I21" s="5">
         <v>6524500000</v>
@@ -15904,16 +15941,16 @@
     </row>
     <row r="22" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>568</v>
+        <v>550</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>569</v>
+        <v>551</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>571</v>
+        <v>553</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>73</v>
@@ -15925,7 +15962,7 @@
         <v>90</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I22" s="5">
         <v>2500000000</v>
@@ -15959,16 +15996,16 @@
     </row>
     <row r="23" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>572</v>
+        <v>554</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>573</v>
+        <v>555</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>574</v>
+        <v>556</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>575</v>
+        <v>557</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>73</v>
@@ -15980,7 +16017,7 @@
         <v>90</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I23" s="5">
         <v>3500000000</v>
@@ -16009,21 +16046,21 @@
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4" t="s">
-        <v>543</v>
+        <v>525</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>577</v>
+        <v>559</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>578</v>
+        <v>560</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>579</v>
+        <v>561</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>73</v>
@@ -16035,7 +16072,7 @@
         <v>90</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I24" s="5">
         <v>3250000000</v>
@@ -16064,21 +16101,21 @@
       </c>
       <c r="R24" s="4"/>
       <c r="S24" s="4" t="s">
-        <v>580</v>
+        <v>562</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>581</v>
+        <v>563</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>584</v>
+        <v>566</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>73</v>
@@ -16090,7 +16127,7 @@
         <v>90</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I25" s="5">
         <v>946000000</v>
@@ -16119,21 +16156,21 @@
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
-        <v>585</v>
+        <v>567</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>587</v>
+        <v>569</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>589</v>
+        <v>571</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>73</v>
@@ -16145,7 +16182,7 @@
         <v>90</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I26" s="5">
         <v>1943625000</v>
@@ -16174,21 +16211,21 @@
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
-        <v>590</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>592</v>
+        <v>574</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>593</v>
+        <v>575</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>594</v>
+        <v>576</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>73</v>
@@ -16200,7 +16237,7 @@
         <v>90</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="I27" s="5">
         <v>1999999962.27</v>
@@ -16229,33 +16266,33 @@
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4" t="s">
-        <v>595</v>
+        <v>577</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>596</v>
+        <v>578</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>597</v>
+        <v>579</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>598</v>
+        <v>580</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>599</v>
+        <v>581</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>60</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>600</v>
+        <v>582</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I28" s="5">
         <v>729826686</v>
@@ -16284,33 +16321,33 @@
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4" t="s">
-        <v>601</v>
+        <v>583</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>238</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>605</v>
+        <v>587</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>62</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I29" s="5">
         <v>37141732473</v>
@@ -16344,16 +16381,16 @@
     </row>
     <row r="30" spans="1:19" ht="69.900000000000006" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A